--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\1. AVALIAÇÕES\01. AVALIAÇÕES SICREDI\01. RURAL\Processo Nº 12941255 MAURICIO MIYASAKI\PEÇAS TECNICAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\automacao_laudo\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954650A9-9A53-495A-867F-2741DCA9C6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -27,10 +26,10 @@
     <sheet name="quadro_resumo" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'LAUDO DE AVALIAÇÃO 12-12.4'!$B$1:$H$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'LAUDO DE AVALIAÇÃO 13'!$B$1:$G$8</definedName>
+    <definedName name="Print_Area" localSheetId="9">'LAUDO DE AVALIAÇÃO 12-12.4'!$B$1:$H$24</definedName>
+    <definedName name="Print_Area" localSheetId="10">'LAUDO DE AVALIAÇÃO 13'!$B$1:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,12 +47,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -70,12 +69,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
+    <comment ref="D5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1012,7 +1011,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="12">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -2792,6 +2791,12 @@
     <xf numFmtId="0" fontId="68" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="67" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2833,6 +2838,15 @@
     <xf numFmtId="170" fontId="50" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="50" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="50" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2861,26 +2875,17 @@
     <xf numFmtId="2" fontId="49" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="50" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="50" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2910,29 +2915,71 @@
     <xf numFmtId="168" fontId="52" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="46" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2995,136 +3042,145 @@
     <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="53" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3171,34 +3227,34 @@
     <xf numFmtId="170" fontId="46" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="46" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="46" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3352,63 +3408,6 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="67" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3537,9 +3536,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3577,9 +3576,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3614,7 +3613,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3649,7 +3648,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3822,39 +3821,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:M47"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="240" t="s">
+      <c r="B3" s="242" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="249"/>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="249"/>
-      <c r="I3" s="249"/>
-      <c r="J3" s="249"/>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="M3" s="250"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="251"/>
+      <c r="I3" s="251"/>
+      <c r="J3" s="251"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
+      <c r="M3" s="252"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="259"/>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="252"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="254"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -3885,100 +3884,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="245" t="s">
+      <c r="B7" s="247" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="246"/>
-      <c r="D7" s="246"/>
-      <c r="E7" s="260"/>
-      <c r="F7" s="246"/>
-      <c r="G7" s="246"/>
-      <c r="H7" s="246"/>
-      <c r="I7" s="246"/>
-      <c r="J7" s="246"/>
-      <c r="K7" s="246"/>
-      <c r="L7" s="246"/>
-      <c r="M7" s="256"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="265"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="258"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="245" t="s">
+      <c r="B8" s="247" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="246"/>
-      <c r="D8" s="246"/>
-      <c r="E8" s="260"/>
-      <c r="F8" s="246"/>
-      <c r="G8" s="246"/>
-      <c r="H8" s="246"/>
-      <c r="I8" s="246"/>
-      <c r="J8" s="246"/>
-      <c r="K8" s="246"/>
-      <c r="L8" s="246"/>
-      <c r="M8" s="256"/>
+      <c r="C8" s="248"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="248"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="248"/>
+      <c r="I8" s="248"/>
+      <c r="J8" s="248"/>
+      <c r="K8" s="248"/>
+      <c r="L8" s="248"/>
+      <c r="M8" s="258"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="245" t="s">
+      <c r="B9" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="246"/>
-      <c r="D9" s="246"/>
-      <c r="E9" s="260"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="246"/>
-      <c r="H9" s="246"/>
-      <c r="I9" s="246"/>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246"/>
-      <c r="L9" s="246"/>
-      <c r="M9" s="256"/>
+      <c r="C9" s="248"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="265"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
+      <c r="M9" s="258"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="245" t="s">
+      <c r="B10" s="247" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="246"/>
-      <c r="D10" s="246"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="246"/>
-      <c r="H10" s="246"/>
-      <c r="I10" s="246"/>
-      <c r="J10" s="246"/>
-      <c r="K10" s="246"/>
-      <c r="L10" s="246"/>
-      <c r="M10" s="256"/>
+      <c r="C10" s="248"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="265"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="248"/>
+      <c r="K10" s="248"/>
+      <c r="L10" s="248"/>
+      <c r="M10" s="258"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="245" t="s">
+      <c r="B11" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="246"/>
-      <c r="D11" s="246"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="246"/>
-      <c r="G11" s="246"/>
-      <c r="H11" s="246"/>
-      <c r="I11" s="246"/>
-      <c r="J11" s="246"/>
-      <c r="K11" s="246"/>
-      <c r="L11" s="246"/>
-      <c r="M11" s="256"/>
+      <c r="C11" s="248"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="265"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
+      <c r="M11" s="258"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="245" t="s">
+      <c r="B12" s="247" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="246"/>
-      <c r="D12" s="246"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="246"/>
-      <c r="G12" s="246"/>
-      <c r="H12" s="246"/>
-      <c r="I12" s="246"/>
-      <c r="J12" s="246"/>
-      <c r="K12" s="246"/>
-      <c r="L12" s="246"/>
-      <c r="M12" s="256"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="265"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
+      <c r="M12" s="258"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4037,20 +4036,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="275" t="s">
+      <c r="B17" s="276" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="246"/>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="246"/>
-      <c r="G17" s="246"/>
-      <c r="H17" s="246"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="246"/>
-      <c r="K17" s="246"/>
-      <c r="L17" s="246"/>
-      <c r="M17" s="246"/>
+      <c r="C17" s="248"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
+      <c r="M17" s="248"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4067,150 +4066,150 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="277" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="249"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="272"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="249"/>
-      <c r="I19" s="249"/>
-      <c r="J19" s="249"/>
-      <c r="K19" s="249"/>
-      <c r="L19" s="249"/>
-      <c r="M19" s="250"/>
+      <c r="C19" s="251"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="275"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="251"/>
+      <c r="J19" s="251"/>
+      <c r="K19" s="251"/>
+      <c r="L19" s="251"/>
+      <c r="M19" s="252"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="245" t="s">
+      <c r="B20" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="246"/>
-      <c r="D20" s="246"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="246"/>
-      <c r="G20" s="246"/>
-      <c r="H20" s="246"/>
-      <c r="I20" s="246"/>
-      <c r="J20" s="246"/>
-      <c r="K20" s="246"/>
-      <c r="L20" s="246"/>
-      <c r="M20" s="256"/>
+      <c r="C20" s="248"/>
+      <c r="D20" s="248"/>
+      <c r="E20" s="265"/>
+      <c r="F20" s="248"/>
+      <c r="G20" s="248"/>
+      <c r="H20" s="248"/>
+      <c r="I20" s="248"/>
+      <c r="J20" s="248"/>
+      <c r="K20" s="248"/>
+      <c r="L20" s="248"/>
+      <c r="M20" s="258"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="245" t="s">
+      <c r="B21" s="247" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="246"/>
-      <c r="D21" s="246"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-      <c r="K21" s="246"/>
-      <c r="L21" s="246"/>
-      <c r="M21" s="256"/>
+      <c r="C21" s="248"/>
+      <c r="D21" s="248"/>
+      <c r="E21" s="265"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="248"/>
+      <c r="K21" s="248"/>
+      <c r="L21" s="248"/>
+      <c r="M21" s="258"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="267" t="s">
+      <c r="B22" s="272" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="261"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
+      <c r="C22" s="246"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="246"/>
+      <c r="G22" s="246"/>
+      <c r="H22" s="246"/>
+      <c r="I22" s="246"/>
+      <c r="J22" s="246"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="265"/>
-      <c r="M22" s="252"/>
+      <c r="L22" s="270"/>
+      <c r="M22" s="254"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="240" t="s">
+      <c r="B23" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="241"/>
-      <c r="D23" s="241"/>
-      <c r="E23" s="241"/>
-      <c r="F23" s="241"/>
-      <c r="G23" s="241"/>
-      <c r="H23" s="241"/>
-      <c r="I23" s="241"/>
-      <c r="J23" s="241"/>
-      <c r="K23" s="241"/>
-      <c r="L23" s="241"/>
-      <c r="M23" s="242"/>
+      <c r="C23" s="243"/>
+      <c r="D23" s="243"/>
+      <c r="E23" s="243"/>
+      <c r="F23" s="243"/>
+      <c r="G23" s="243"/>
+      <c r="H23" s="243"/>
+      <c r="I23" s="243"/>
+      <c r="J23" s="243"/>
+      <c r="K23" s="243"/>
+      <c r="L23" s="243"/>
+      <c r="M23" s="244"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="253" t="s">
+      <c r="B24" s="255" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="241"/>
-      <c r="D24" s="242"/>
-      <c r="E24" s="253" t="s">
+      <c r="C24" s="243"/>
+      <c r="D24" s="244"/>
+      <c r="E24" s="255" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="241"/>
-      <c r="G24" s="242"/>
-      <c r="H24" s="253" t="s">
+      <c r="F24" s="243"/>
+      <c r="G24" s="244"/>
+      <c r="H24" s="255" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="241"/>
-      <c r="J24" s="242"/>
-      <c r="K24" s="253" t="s">
+      <c r="I24" s="243"/>
+      <c r="J24" s="244"/>
+      <c r="K24" s="255" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="241"/>
-      <c r="M24" s="242"/>
+      <c r="L24" s="243"/>
+      <c r="M24" s="244"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="264"/>
-      <c r="C25" s="249"/>
-      <c r="D25" s="250"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="246"/>
-      <c r="G25" s="246"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="249"/>
-      <c r="J25" s="250"/>
-      <c r="K25" s="266"/>
-      <c r="L25" s="249"/>
-      <c r="M25" s="250"/>
+      <c r="B25" s="269"/>
+      <c r="C25" s="251"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="256"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="250"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="252"/>
+      <c r="K25" s="271"/>
+      <c r="L25" s="251"/>
+      <c r="M25" s="252"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="262"/>
-      <c r="C26" s="244"/>
-      <c r="D26" s="252"/>
-      <c r="E26" s="271"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="263"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="252"/>
-      <c r="K26" s="268"/>
-      <c r="L26" s="244"/>
-      <c r="M26" s="252"/>
+      <c r="B26" s="267"/>
+      <c r="C26" s="246"/>
+      <c r="D26" s="254"/>
+      <c r="E26" s="274"/>
+      <c r="F26" s="246"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="268"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="254"/>
+      <c r="K26" s="273"/>
+      <c r="L26" s="246"/>
+      <c r="M26" s="254"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="240" t="s">
+      <c r="B27" s="242" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="241"/>
-      <c r="D27" s="241"/>
-      <c r="E27" s="241"/>
-      <c r="F27" s="241"/>
-      <c r="G27" s="241"/>
-      <c r="H27" s="241"/>
-      <c r="I27" s="241"/>
-      <c r="J27" s="241"/>
-      <c r="K27" s="241"/>
-      <c r="L27" s="241"/>
-      <c r="M27" s="242"/>
+      <c r="C27" s="243"/>
+      <c r="D27" s="243"/>
+      <c r="E27" s="243"/>
+      <c r="F27" s="243"/>
+      <c r="G27" s="243"/>
+      <c r="H27" s="243"/>
+      <c r="I27" s="243"/>
+      <c r="J27" s="243"/>
+      <c r="K27" s="243"/>
+      <c r="L27" s="243"/>
+      <c r="M27" s="244"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4297,100 +4296,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="240" t="s">
+      <c r="B34" s="242" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="241"/>
-      <c r="D34" s="241"/>
-      <c r="E34" s="241"/>
-      <c r="F34" s="241"/>
-      <c r="G34" s="241"/>
-      <c r="H34" s="241"/>
-      <c r="I34" s="241"/>
-      <c r="J34" s="241"/>
-      <c r="K34" s="241"/>
-      <c r="L34" s="241"/>
-      <c r="M34" s="242"/>
+      <c r="C34" s="243"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="243"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="243"/>
+      <c r="I34" s="243"/>
+      <c r="J34" s="243"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="243"/>
+      <c r="M34" s="244"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="253" t="s">
+      <c r="B35" s="255" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="241"/>
-      <c r="D35" s="241"/>
-      <c r="E35" s="242"/>
-      <c r="F35" s="253" t="s">
+      <c r="C35" s="243"/>
+      <c r="D35" s="243"/>
+      <c r="E35" s="244"/>
+      <c r="F35" s="255" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="241"/>
-      <c r="H35" s="241"/>
-      <c r="I35" s="242"/>
-      <c r="J35" s="253" t="s">
+      <c r="G35" s="243"/>
+      <c r="H35" s="243"/>
+      <c r="I35" s="244"/>
+      <c r="J35" s="255" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="241"/>
-      <c r="L35" s="241"/>
-      <c r="M35" s="242"/>
+      <c r="K35" s="243"/>
+      <c r="L35" s="243"/>
+      <c r="M35" s="244"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="269"/>
-      <c r="C36" s="249"/>
-      <c r="D36" s="249"/>
-      <c r="E36" s="249"/>
-      <c r="F36" s="273"/>
-      <c r="G36" s="249"/>
-      <c r="H36" s="249"/>
-      <c r="I36" s="249"/>
-      <c r="J36" s="274"/>
-      <c r="K36" s="249"/>
-      <c r="L36" s="249"/>
-      <c r="M36" s="250"/>
+      <c r="B36" s="261"/>
+      <c r="C36" s="251"/>
+      <c r="D36" s="251"/>
+      <c r="E36" s="251"/>
+      <c r="F36" s="262"/>
+      <c r="G36" s="251"/>
+      <c r="H36" s="251"/>
+      <c r="I36" s="251"/>
+      <c r="J36" s="263"/>
+      <c r="K36" s="251"/>
+      <c r="L36" s="251"/>
+      <c r="M36" s="252"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="247"/>
-      <c r="C37" s="246"/>
-      <c r="D37" s="246"/>
-      <c r="E37" s="246"/>
-      <c r="F37" s="258"/>
-      <c r="G37" s="246"/>
-      <c r="H37" s="246"/>
-      <c r="I37" s="246"/>
-      <c r="J37" s="255"/>
-      <c r="K37" s="246"/>
-      <c r="L37" s="246"/>
-      <c r="M37" s="256"/>
+      <c r="B37" s="249"/>
+      <c r="C37" s="248"/>
+      <c r="D37" s="248"/>
+      <c r="E37" s="248"/>
+      <c r="F37" s="260"/>
+      <c r="G37" s="248"/>
+      <c r="H37" s="248"/>
+      <c r="I37" s="248"/>
+      <c r="J37" s="257"/>
+      <c r="K37" s="248"/>
+      <c r="L37" s="248"/>
+      <c r="M37" s="258"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="257" t="s">
+      <c r="B38" s="259" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="244"/>
-      <c r="D38" s="244"/>
-      <c r="E38" s="244"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="244"/>
-      <c r="H38" s="244"/>
-      <c r="I38" s="244"/>
-      <c r="J38" s="251"/>
-      <c r="K38" s="244"/>
-      <c r="L38" s="244"/>
-      <c r="M38" s="252"/>
+      <c r="C38" s="246"/>
+      <c r="D38" s="246"/>
+      <c r="E38" s="246"/>
+      <c r="F38" s="245"/>
+      <c r="G38" s="246"/>
+      <c r="H38" s="246"/>
+      <c r="I38" s="246"/>
+      <c r="J38" s="253"/>
+      <c r="K38" s="246"/>
+      <c r="L38" s="246"/>
+      <c r="M38" s="254"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="240" t="s">
+      <c r="B39" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="241"/>
-      <c r="D39" s="241"/>
-      <c r="E39" s="241"/>
-      <c r="F39" s="241"/>
-      <c r="G39" s="241"/>
-      <c r="H39" s="241"/>
-      <c r="I39" s="241"/>
-      <c r="J39" s="241"/>
-      <c r="K39" s="241"/>
-      <c r="L39" s="241"/>
-      <c r="M39" s="242"/>
+      <c r="C39" s="243"/>
+      <c r="D39" s="243"/>
+      <c r="E39" s="243"/>
+      <c r="F39" s="243"/>
+      <c r="G39" s="243"/>
+      <c r="H39" s="243"/>
+      <c r="I39" s="243"/>
+      <c r="J39" s="243"/>
+      <c r="K39" s="243"/>
+      <c r="L39" s="243"/>
+      <c r="M39" s="244"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4514,7 +4513,7 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E20:M20"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B34:M34"/>
+    <mergeCell ref="E10:M10"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="E11:M11"/>
@@ -4522,7 +4521,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E19:M19"/>
-    <mergeCell ref="E10:M10"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="J35:M35"/>
@@ -4557,13 +4555,14 @@
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
+    <mergeCell ref="B34:M34"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:L24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -4580,24 +4579,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="418" t="s">
+      <c r="B1" s="437" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="419"/>
-      <c r="D1" s="419"/>
-      <c r="E1" s="419"/>
-      <c r="F1" s="419"/>
-      <c r="G1" s="419"/>
-      <c r="H1" s="420"/>
+      <c r="C1" s="438"/>
+      <c r="D1" s="438"/>
+      <c r="E1" s="438"/>
+      <c r="F1" s="438"/>
+      <c r="G1" s="438"/>
+      <c r="H1" s="439"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="414"/>
-      <c r="C2" s="415"/>
-      <c r="D2" s="415"/>
-      <c r="E2" s="415"/>
-      <c r="F2" s="415"/>
-      <c r="G2" s="415"/>
-      <c r="H2" s="416"/>
+      <c r="B2" s="433"/>
+      <c r="C2" s="434"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="435"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -4632,32 +4631,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="423" t="s">
+      <c r="B6" s="442" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="425" t="s">
+      <c r="C6" s="444" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="427" t="s">
+      <c r="D6" s="446" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="428" t="s">
+      <c r="E6" s="447" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="428" t="s">
+      <c r="F6" s="447" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="421" t="s">
+      <c r="G6" s="440" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="422"/>
+      <c r="H6" s="441"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="424"/>
-      <c r="C7" s="426"/>
-      <c r="D7" s="426"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="252"/>
+      <c r="B7" s="443"/>
+      <c r="C7" s="445"/>
+      <c r="D7" s="445"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
       <c r="G7" s="47" t="s">
         <v>265</v>
       </c>
@@ -4678,14 +4677,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="429" t="s">
+      <c r="B9" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="241"/>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="242"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="244"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -4703,32 +4702,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="423" t="s">
+      <c r="B11" s="442" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="425" t="s">
+      <c r="C11" s="444" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="427" t="s">
+      <c r="D11" s="446" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="417" t="s">
+      <c r="E11" s="436" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="417" t="s">
+      <c r="F11" s="436" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="421" t="s">
+      <c r="G11" s="440" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="422"/>
+      <c r="H11" s="441"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="424"/>
-      <c r="C12" s="426"/>
-      <c r="D12" s="426"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="252"/>
+      <c r="B12" s="443"/>
+      <c r="C12" s="445"/>
+      <c r="D12" s="445"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="254"/>
       <c r="G12" s="47" t="s">
         <v>265</v>
       </c>
@@ -4749,14 +4748,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="429" t="s">
+      <c r="B14" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="241"/>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="242"/>
+      <c r="C14" s="243"/>
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="244"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -4774,32 +4773,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="423" t="s">
+      <c r="B16" s="442" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="425" t="s">
+      <c r="C16" s="444" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="427" t="s">
+      <c r="D16" s="446" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="417" t="s">
+      <c r="E16" s="436" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="417" t="s">
+      <c r="F16" s="436" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="421" t="s">
+      <c r="G16" s="440" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="422"/>
+      <c r="H16" s="441"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="424"/>
-      <c r="C17" s="426"/>
-      <c r="D17" s="426"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
+      <c r="B17" s="443"/>
+      <c r="C17" s="445"/>
+      <c r="D17" s="445"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
       <c r="G17" s="22" t="s">
         <v>265</v>
       </c>
@@ -4822,14 +4821,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="429" t="s">
+      <c r="B19" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="241"/>
-      <c r="D19" s="241"/>
-      <c r="E19" s="241"/>
-      <c r="F19" s="241"/>
-      <c r="G19" s="242"/>
+      <c r="C19" s="243"/>
+      <c r="D19" s="243"/>
+      <c r="E19" s="243"/>
+      <c r="F19" s="243"/>
+      <c r="G19" s="244"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -4847,32 +4846,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="423" t="s">
+      <c r="B21" s="442" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="425" t="s">
+      <c r="C21" s="444" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="427" t="s">
+      <c r="D21" s="446" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="417" t="s">
+      <c r="E21" s="436" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="417" t="s">
+      <c r="F21" s="436" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="421" t="s">
+      <c r="G21" s="440" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="422"/>
+      <c r="H21" s="441"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="424"/>
-      <c r="C22" s="426"/>
-      <c r="D22" s="426"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
+      <c r="B22" s="443"/>
+      <c r="C22" s="445"/>
+      <c r="D22" s="445"/>
+      <c r="E22" s="254"/>
+      <c r="F22" s="254"/>
       <c r="G22" s="47" t="s">
         <v>265</v>
       </c>
@@ -4893,14 +4892,14 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="412" t="s">
+      <c r="B24" s="431" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="413"/>
-      <c r="D24" s="413"/>
-      <c r="E24" s="413"/>
-      <c r="F24" s="413"/>
-      <c r="G24" s="362"/>
+      <c r="C24" s="432"/>
+      <c r="D24" s="432"/>
+      <c r="E24" s="432"/>
+      <c r="F24" s="432"/>
+      <c r="G24" s="381"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
@@ -4944,7 +4943,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:M8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -4960,14 +4959,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="432" t="s">
+      <c r="B1" s="451" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="415"/>
-      <c r="D1" s="415"/>
-      <c r="E1" s="415"/>
-      <c r="F1" s="415"/>
-      <c r="G1" s="415"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -4991,40 +4990,40 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="433" t="s">
+      <c r="B4" s="452" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="241"/>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="242"/>
+      <c r="C4" s="243"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="244"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="434" t="s">
+      <c r="B5" s="453" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="430" t="s">
+      <c r="C5" s="449" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="430" t="s">
+      <c r="D5" s="449" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="430" t="s">
+      <c r="E5" s="449" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="431" t="s">
+      <c r="F5" s="450" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="241"/>
+      <c r="G5" s="243"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="252"/>
-      <c r="C6" s="426"/>
-      <c r="D6" s="426"/>
-      <c r="E6" s="426"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="445"/>
+      <c r="D6" s="445"/>
+      <c r="E6" s="445"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -5067,7 +5066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -5076,151 +5075,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="442" t="s">
+      <c r="A1" s="461" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="246"/>
-      <c r="C1" s="246"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="246"/>
-      <c r="H1" s="246"/>
-      <c r="I1" s="246"/>
-      <c r="J1" s="246"/>
-      <c r="K1" s="246"/>
-      <c r="L1" s="246"/>
-      <c r="M1" s="246"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="435"/>
-      <c r="P1" s="246"/>
-      <c r="Q1" s="246"/>
-      <c r="R1" s="246"/>
-      <c r="S1" s="246"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
+      <c r="N1" s="248"/>
+      <c r="O1" s="454"/>
+      <c r="P1" s="248"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="248"/>
+      <c r="S1" s="248"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="440" t="s">
+      <c r="A2" s="459" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="246"/>
-      <c r="C2" s="440" t="s">
+      <c r="B2" s="248"/>
+      <c r="C2" s="459" t="s">
         <v>278</v>
       </c>
-      <c r="D2" s="246"/>
-      <c r="E2" s="246"/>
-      <c r="F2" s="246"/>
-      <c r="G2" s="246"/>
-      <c r="H2" s="246"/>
-      <c r="I2" s="246"/>
-      <c r="J2" s="441" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="460" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="M2" s="246"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="437" t="s">
+      <c r="A3" s="456" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="246"/>
-      <c r="C3" s="437" t="s">
+      <c r="B3" s="248"/>
+      <c r="C3" s="456" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="246"/>
-      <c r="H3" s="246"/>
-      <c r="I3" s="246"/>
-      <c r="J3" s="437" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="248"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="456" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="M3" s="246"/>
-      <c r="N3" s="246"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="M3" s="248"/>
+      <c r="N3" s="248"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="437" t="s">
+      <c r="A4" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="246"/>
-      <c r="C4" s="437" t="s">
+      <c r="B4" s="248"/>
+      <c r="C4" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="439"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="246"/>
-      <c r="N4" s="246"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="458"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="M4" s="248"/>
+      <c r="N4" s="248"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="437" t="s">
+      <c r="A5" s="456" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="437" t="s">
+      <c r="B5" s="248"/>
+      <c r="C5" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="439"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="246"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="458"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="M5" s="248"/>
+      <c r="N5" s="248"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="437" t="s">
+      <c r="A6" s="456" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="246"/>
-      <c r="C6" s="437" t="s">
+      <c r="B6" s="248"/>
+      <c r="C6" s="456" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="246"/>
-      <c r="E6" s="246"/>
-      <c r="F6" s="246"/>
-      <c r="G6" s="246"/>
-      <c r="H6" s="246"/>
-      <c r="I6" s="246"/>
-      <c r="J6" s="437" t="s">
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
+      <c r="I6" s="248"/>
+      <c r="J6" s="456" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="246"/>
-      <c r="L6" s="246"/>
-      <c r="M6" s="246"/>
-      <c r="N6" s="246"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="248"/>
+      <c r="N6" s="248"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="436" t="s">
+      <c r="A7" s="455" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="246"/>
-      <c r="C7" s="246"/>
-      <c r="D7" s="246"/>
-      <c r="E7" s="246"/>
-      <c r="F7" s="246"/>
-      <c r="G7" s="246"/>
-      <c r="H7" s="246"/>
-      <c r="I7" s="246"/>
-      <c r="J7" s="246"/>
-      <c r="K7" s="246"/>
-      <c r="L7" s="246"/>
-      <c r="M7" s="246"/>
-      <c r="N7" s="246"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="248"/>
+      <c r="N7" s="248"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -5246,120 +5245,120 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="436" t="s">
+      <c r="A31" s="455" t="s">
         <v>288</v>
       </c>
-      <c r="B31" s="246"/>
-      <c r="C31" s="246"/>
-      <c r="D31" s="246"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="246"/>
-      <c r="G31" s="246"/>
-      <c r="H31" s="246"/>
-      <c r="I31" s="246"/>
-      <c r="J31" s="246"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="246"/>
-      <c r="M31" s="246"/>
-      <c r="N31" s="246"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
+      <c r="M31" s="248"/>
+      <c r="N31" s="248"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="438" t="s">
+      <c r="A32" s="457" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="246"/>
-      <c r="D32" s="438" t="s">
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="457" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="246"/>
-      <c r="F32" s="246"/>
-      <c r="G32" s="438" t="s">
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
+      <c r="G32" s="457" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="246"/>
-      <c r="I32" s="246"/>
-      <c r="J32" s="438" t="s">
+      <c r="H32" s="248"/>
+      <c r="I32" s="248"/>
+      <c r="J32" s="457" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="246"/>
-      <c r="L32" s="246"/>
-      <c r="M32" s="246"/>
+      <c r="K32" s="248"/>
+      <c r="L32" s="248"/>
+      <c r="M32" s="248"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="438" t="s">
+      <c r="A33" s="457" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="246"/>
-      <c r="C33" s="246"/>
-      <c r="D33" s="438" t="s">
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="457" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="246"/>
-      <c r="F33" s="246"/>
-      <c r="G33" s="438" t="s">
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="457" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="246"/>
-      <c r="I33" s="246"/>
-      <c r="J33" s="438" t="s">
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="457" t="s">
         <v>293</v>
       </c>
-      <c r="K33" s="246"/>
-      <c r="L33" s="246"/>
-      <c r="M33" s="246"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
+      <c r="M33" s="248"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="436" t="s">
+      <c r="A34" s="455" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="246"/>
-      <c r="C34" s="246"/>
-      <c r="D34" s="246"/>
-      <c r="E34" s="246"/>
-      <c r="F34" s="246"/>
-      <c r="G34" s="246"/>
-      <c r="H34" s="246"/>
-      <c r="I34" s="246"/>
-      <c r="J34" s="246"/>
-      <c r="K34" s="246"/>
-      <c r="L34" s="246"/>
-      <c r="M34" s="246"/>
-      <c r="N34" s="246"/>
+      <c r="B34" s="248"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="248"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="248"/>
+      <c r="N34" s="248"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="438" t="s">
+      <c r="A35" s="457" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="246"/>
-      <c r="C35" s="246"/>
-      <c r="F35" s="438" t="s">
+      <c r="B35" s="248"/>
+      <c r="C35" s="248"/>
+      <c r="F35" s="457" t="s">
         <v>294</v>
       </c>
-      <c r="G35" s="246"/>
-      <c r="H35" s="246"/>
-      <c r="K35" s="438" t="s">
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
+      <c r="K35" s="457" t="s">
         <v>295</v>
       </c>
-      <c r="L35" s="246"/>
-      <c r="M35" s="246"/>
+      <c r="L35" s="248"/>
+      <c r="M35" s="248"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="438" t="s">
+      <c r="A36" s="457" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="246"/>
-      <c r="C36" s="246"/>
-      <c r="F36" s="438" t="s">
+      <c r="B36" s="248"/>
+      <c r="C36" s="248"/>
+      <c r="F36" s="457" t="s">
         <v>296</v>
       </c>
-      <c r="G36" s="246"/>
-      <c r="H36" s="246"/>
-      <c r="K36" s="438" t="s">
+      <c r="G36" s="248"/>
+      <c r="H36" s="248"/>
+      <c r="K36" s="457" t="s">
         <v>297</v>
       </c>
-      <c r="L36" s="246"/>
-      <c r="M36" s="246"/>
+      <c r="L36" s="248"/>
+      <c r="M36" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -5404,7 +5403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="D8:G47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -5539,7 +5538,7 @@
       </c>
     </row>
     <row r="32" spans="4:7" ht="15" customHeight="1">
-      <c r="D32" s="276" t="s">
+      <c r="D32" s="278" t="s">
         <v>40</v>
       </c>
       <c r="E32" s="193" t="s">
@@ -5549,7 +5548,7 @@
       <c r="G32" s="193"/>
     </row>
     <row r="33" spans="4:7" ht="30" customHeight="1">
-      <c r="D33" s="277"/>
+      <c r="D33" s="279"/>
       <c r="E33" s="194" t="s">
         <v>42</v>
       </c>
@@ -5659,7 +5658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C2:T21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -5700,17 +5699,17 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="278" t="str">
+      <c r="C4" s="280" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
-      <c r="F4" s="277"/>
-      <c r="G4" s="277"/>
-      <c r="H4" s="277"/>
-      <c r="I4" s="277"/>
-      <c r="J4" s="277"/>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+      <c r="I4" s="279"/>
+      <c r="J4" s="279"/>
       <c r="L4" s="207"/>
       <c r="M4" s="207"/>
       <c r="N4" s="207"/>
@@ -5729,22 +5728,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="287" t="s">
+      <c r="C5" s="293" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="287" t="s">
+      <c r="D5" s="254"/>
+      <c r="E5" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="252"/>
-      <c r="G5" s="287" t="s">
+      <c r="F5" s="254"/>
+      <c r="G5" s="293" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="252"/>
-      <c r="I5" s="289" t="s">
+      <c r="H5" s="254"/>
+      <c r="I5" s="297" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="252"/>
+      <c r="J5" s="254"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -5758,23 +5757,23 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="281">
+      <c r="C6" s="283">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="242"/>
-      <c r="E6" s="284" t="s">
+      <c r="D6" s="244"/>
+      <c r="E6" s="286" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="242"/>
-      <c r="G6" s="282" t="s">
+      <c r="F6" s="244"/>
+      <c r="G6" s="284" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="242"/>
-      <c r="I6" s="292" t="s">
+      <c r="H6" s="244"/>
+      <c r="I6" s="300" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="242"/>
+      <c r="J6" s="244"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -5794,16 +5793,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="279" t="s">
+      <c r="C7" s="281" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="241"/>
-      <c r="E7" s="241"/>
-      <c r="F7" s="241"/>
-      <c r="G7" s="241"/>
-      <c r="H7" s="241"/>
-      <c r="I7" s="241"/>
-      <c r="J7" s="242"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="244"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -5820,22 +5819,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="283" t="s">
+      <c r="C8" s="285" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="242"/>
-      <c r="E8" s="283" t="s">
+      <c r="D8" s="244"/>
+      <c r="E8" s="285" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="242"/>
-      <c r="G8" s="283" t="s">
+      <c r="F8" s="244"/>
+      <c r="G8" s="285" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="242"/>
-      <c r="I8" s="288" t="s">
+      <c r="H8" s="244"/>
+      <c r="I8" s="294" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="242"/>
+      <c r="J8" s="244"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -5847,22 +5846,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="284">
+      <c r="C9" s="286">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="282" t="s">
+      <c r="D9" s="244"/>
+      <c r="E9" s="284" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="242"/>
-      <c r="G9" s="281">
+      <c r="F9" s="244"/>
+      <c r="G9" s="283">
         <v>80</v>
       </c>
-      <c r="H9" s="242"/>
-      <c r="I9" s="292">
+      <c r="H9" s="244"/>
+      <c r="I9" s="300">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="242"/>
+      <c r="J9" s="244"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -5874,16 +5873,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="279" t="s">
+      <c r="C10" s="281" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="242"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="244"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -5895,158 +5894,156 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="283" t="s">
+      <c r="C11" s="285" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="E11" s="283" t="s">
+      <c r="D11" s="244"/>
+      <c r="E11" s="285" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="242"/>
-      <c r="G11" s="283" t="s">
+      <c r="F11" s="244"/>
+      <c r="G11" s="285" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="242"/>
-      <c r="I11" s="288" t="s">
+      <c r="H11" s="244"/>
+      <c r="I11" s="294" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="242"/>
+      <c r="J11" s="244"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="284">
+      <c r="C12" s="286">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="242"/>
-      <c r="E12" s="284">
+      <c r="D12" s="244"/>
+      <c r="E12" s="286">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="242"/>
-      <c r="G12" s="282">
+      <c r="F12" s="244"/>
+      <c r="G12" s="284">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="242"/>
-      <c r="I12" s="285">
+      <c r="H12" s="244"/>
+      <c r="I12" s="287">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="242"/>
+      <c r="J12" s="244"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="283" t="s">
+      <c r="C13" s="285" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="E13" s="282" t="s">
+      <c r="D13" s="244"/>
+      <c r="E13" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="242"/>
-      <c r="G13" s="283" t="s">
+      <c r="F13" s="244"/>
+      <c r="G13" s="285" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="242"/>
-      <c r="I13" s="292" t="s">
+      <c r="H13" s="244"/>
+      <c r="I13" s="300" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="242"/>
+      <c r="J13" s="244"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="291" t="s">
+      <c r="C16" s="298" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="242"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="244"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="279" t="s">
+      <c r="C17" s="281" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="279" t="s">
+      <c r="D17" s="243"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="281" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="242"/>
-      <c r="H17" s="279" t="s">
+      <c r="G17" s="244"/>
+      <c r="H17" s="281" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="242"/>
+      <c r="I17" s="244"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="457" t="s">
+      <c r="C18" s="306" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="458"/>
-      <c r="E18" s="459"/>
-      <c r="F18" s="455">
+      <c r="D18" s="307"/>
+      <c r="E18" s="308"/>
+      <c r="F18" s="291">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="456"/>
-      <c r="H18" s="460">
+      <c r="G18" s="292"/>
+      <c r="H18" s="295">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="461"/>
+      <c r="I18" s="296"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="286" t="s">
+      <c r="C19" s="309" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="241"/>
-      <c r="E19" s="242"/>
-      <c r="F19" s="281">
+      <c r="D19" s="243"/>
+      <c r="E19" s="244"/>
+      <c r="F19" s="283">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="242"/>
-      <c r="H19" s="290">
+      <c r="G19" s="244"/>
+      <c r="H19" s="299">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="242"/>
+      <c r="I19" s="244"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="448" t="s">
+      <c r="C20" s="288" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="449"/>
-      <c r="E20" s="450"/>
-      <c r="F20" s="453">
+      <c r="D20" s="289"/>
+      <c r="E20" s="290"/>
+      <c r="F20" s="304">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="454"/>
-      <c r="H20" s="451">
+      <c r="G20" s="305"/>
+      <c r="H20" s="302">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="452"/>
+      <c r="I20" s="303"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="293" t="s">
+      <c r="C21" s="301" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="241"/>
-      <c r="E21" s="242"/>
-      <c r="F21" s="280">
+      <c r="D21" s="243"/>
+      <c r="E21" s="244"/>
+      <c r="F21" s="282">
         <f>SUM(F18:G20)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G21" s="242"/>
-      <c r="H21" s="290">
+      <c r="G21" s="244"/>
+      <c r="H21" s="299">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="242"/>
+      <c r="I21" s="244"/>
       <c r="J21" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="H21:I21"/>
@@ -6061,6 +6058,7 @@
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="I11:J11"/>
@@ -6070,12 +6068,13 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="H18:I18"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="F21:G21"/>
@@ -6099,7 +6098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:N112"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -6119,38 +6118,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="312" t="s">
+      <c r="B3" s="328" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="277"/>
-      <c r="D3" s="277"/>
-      <c r="E3" s="277"/>
-      <c r="F3" s="277"/>
-      <c r="G3" s="277"/>
-      <c r="H3" s="277"/>
-      <c r="I3" s="277"/>
-      <c r="L3" s="353" t="s">
+      <c r="C3" s="279"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+      <c r="I3" s="279"/>
+      <c r="L3" s="371" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="242"/>
+      <c r="M3" s="244"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="304" t="s">
+      <c r="B4" s="320" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="305"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="341" t="s">
+      <c r="C4" s="321"/>
+      <c r="D4" s="321"/>
+      <c r="E4" s="373" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="277"/>
+      <c r="F4" s="279"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="324" t="s">
+      <c r="H4" s="341" t="s">
         <v>299</v>
       </c>
-      <c r="I4" s="256"/>
+      <c r="I4" s="258"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>88</v>
@@ -6161,22 +6160,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="302" t="s">
+      <c r="B5" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="277"/>
-      <c r="D5" s="277"/>
-      <c r="E5" s="315" t="s">
+      <c r="C5" s="279"/>
+      <c r="D5" s="279"/>
+      <c r="E5" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="277"/>
+      <c r="F5" s="279"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="324" t="s">
+      <c r="H5" s="341" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="256"/>
+      <c r="I5" s="258"/>
       <c r="L5" s="153" t="s">
         <v>92</v>
       </c>
@@ -6186,57 +6185,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="302" t="s">
+      <c r="B6" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="277"/>
-      <c r="D6" s="277"/>
-      <c r="E6" s="333">
+      <c r="C6" s="279"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="351">
         <v>52.034300000000002</v>
       </c>
-      <c r="F6" s="277"/>
+      <c r="F6" s="279"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="329" t="s">
+      <c r="H6" s="346" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="256"/>
+      <c r="I6" s="258"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="321" t="s">
+      <c r="C7" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="277"/>
-      <c r="E7" s="337" t="s">
+      <c r="D7" s="279"/>
+      <c r="E7" s="353" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="277"/>
+      <c r="F7" s="279"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="301">
+      <c r="H7" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I7" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I7" s="258"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="321" t="s">
+      <c r="C8" s="334" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="277"/>
-      <c r="E8" s="352">
+      <c r="D8" s="279"/>
+      <c r="E8" s="360">
         <v>11173</v>
       </c>
-      <c r="F8" s="277"/>
+      <c r="F8" s="279"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H8" s="336"/>
-      <c r="I8" s="256"/>
+      <c r="I8" s="258"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -6244,16 +6243,16 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="308" t="s">
+      <c r="B9" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="277"/>
-      <c r="D9" s="277"/>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="256"/>
+      <c r="C9" s="279"/>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
+      <c r="G9" s="279"/>
+      <c r="H9" s="279"/>
+      <c r="I9" s="258"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -6261,21 +6260,21 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="319" t="s">
+      <c r="B10" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="277"/>
-      <c r="D10" s="277"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="279"/>
       <c r="E10" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F10" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="309" t="s">
+      <c r="G10" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="277"/>
+      <c r="H10" s="279"/>
       <c r="I10" s="167"/>
       <c r="J10" s="226"/>
       <c r="K10" s="226"/>
@@ -6284,22 +6283,22 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="444" t="s">
+      <c r="B11" s="368" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="443"/>
-      <c r="D11" s="443"/>
-      <c r="E11" s="445">
+      <c r="C11" s="369"/>
+      <c r="D11" s="369"/>
+      <c r="E11" s="240">
         <v>7.23</v>
       </c>
-      <c r="F11" s="446">
+      <c r="F11" s="241">
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="447">
+      <c r="G11" s="370">
         <v>1</v>
       </c>
-      <c r="H11" s="447"/>
+      <c r="H11" s="370"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -6308,11 +6307,11 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="354" t="s">
+      <c r="B12" s="359" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="277"/>
-      <c r="D12" s="277"/>
+      <c r="C12" s="279"/>
+      <c r="D12" s="279"/>
       <c r="E12" s="220">
         <f>32.0811-E11</f>
         <v>24.851099999999999</v>
@@ -6321,10 +6320,10 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="298">
+      <c r="G12" s="314">
         <v>0.8</v>
       </c>
-      <c r="H12" s="277"/>
+      <c r="H12" s="279"/>
       <c r="I12" s="167"/>
       <c r="J12" s="226"/>
       <c r="K12" s="226"/>
@@ -6333,11 +6332,11 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="330" t="s">
+      <c r="B13" s="354" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="277"/>
-      <c r="D13" s="277"/>
+      <c r="C13" s="279"/>
+      <c r="D13" s="279"/>
       <c r="E13" s="202">
         <f>18.2121+1.7411</f>
         <v>19.953199999999999</v>
@@ -6346,10 +6345,10 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="298">
+      <c r="G13" s="314">
         <v>0.6</v>
       </c>
-      <c r="H13" s="277"/>
+      <c r="H13" s="279"/>
       <c r="I13" s="167"/>
       <c r="J13" s="226"/>
       <c r="K13" s="229">
@@ -6362,11 +6361,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="303" t="s">
+      <c r="B14" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -6375,11 +6374,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="294">
+      <c r="G14" s="310">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="244"/>
+      <c r="H14" s="246"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -6403,96 +6402,96 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="312" t="s">
+      <c r="B16" s="328" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="277"/>
-      <c r="D16" s="277"/>
-      <c r="E16" s="277"/>
-      <c r="F16" s="277"/>
-      <c r="G16" s="277"/>
-      <c r="H16" s="277"/>
-      <c r="I16" s="277"/>
+      <c r="C16" s="279"/>
+      <c r="D16" s="279"/>
+      <c r="E16" s="279"/>
+      <c r="F16" s="279"/>
+      <c r="G16" s="279"/>
+      <c r="H16" s="279"/>
+      <c r="I16" s="279"/>
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="304" t="s">
+      <c r="B17" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="305"/>
-      <c r="D17" s="305"/>
-      <c r="E17" s="296" t="s">
+      <c r="C17" s="321"/>
+      <c r="D17" s="321"/>
+      <c r="E17" s="312" t="s">
         <v>110</v>
       </c>
-      <c r="F17" s="277"/>
+      <c r="F17" s="279"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="325" t="s">
+      <c r="H17" s="342" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="256"/>
+      <c r="I17" s="258"/>
       <c r="K17" s="203" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="302" t="s">
+      <c r="B18" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="277"/>
-      <c r="D18" s="277"/>
-      <c r="E18" s="315" t="s">
+      <c r="C18" s="279"/>
+      <c r="D18" s="279"/>
+      <c r="E18" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="277"/>
+      <c r="F18" s="279"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="328" t="s">
+      <c r="H18" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="256"/>
+      <c r="I18" s="258"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="302" t="s">
+      <c r="B19" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="277"/>
-      <c r="D19" s="277"/>
-      <c r="E19" s="334">
+      <c r="C19" s="279"/>
+      <c r="D19" s="279"/>
+      <c r="E19" s="352">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
-      <c r="F19" s="277"/>
+      <c r="F19" s="279"/>
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="299" t="s">
+      <c r="H19" s="315" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="256"/>
+      <c r="I19" s="258"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="321" t="s">
+      <c r="C20" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="277"/>
-      <c r="E20" s="323">
+      <c r="D20" s="279"/>
+      <c r="E20" s="340">
         <f>180000000</f>
         <v>180000000</v>
       </c>
-      <c r="F20" s="277"/>
+      <c r="F20" s="279"/>
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="300">
+      <c r="H20" s="316">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="256"/>
+      <c r="I20" s="258"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -6500,76 +6499,76 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="321" t="s">
+      <c r="C21" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="277"/>
-      <c r="E21" s="340" t="s">
+      <c r="D21" s="279"/>
+      <c r="E21" s="356" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="277"/>
+      <c r="F21" s="279"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="301">
+      <c r="H21" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I21" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I21" s="258"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="321" t="s">
+      <c r="C22" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="277"/>
-      <c r="E22" s="296" t="s">
+      <c r="D22" s="279"/>
+      <c r="E22" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="277"/>
+      <c r="F22" s="279"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="331"/>
-      <c r="I22" s="256"/>
+      <c r="H22" s="348"/>
+      <c r="I22" s="258"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="308" t="s">
+      <c r="B23" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="277"/>
-      <c r="D23" s="277"/>
-      <c r="E23" s="277"/>
-      <c r="F23" s="277"/>
-      <c r="G23" s="277"/>
-      <c r="H23" s="277"/>
-      <c r="I23" s="256"/>
+      <c r="C23" s="279"/>
+      <c r="D23" s="279"/>
+      <c r="E23" s="279"/>
+      <c r="F23" s="279"/>
+      <c r="G23" s="279"/>
+      <c r="H23" s="279"/>
+      <c r="I23" s="258"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="319" t="s">
+      <c r="B24" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="277"/>
-      <c r="D24" s="277"/>
+      <c r="C24" s="279"/>
+      <c r="D24" s="279"/>
       <c r="E24" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F24" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="309" t="s">
+      <c r="G24" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="277"/>
+      <c r="H24" s="279"/>
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="306" t="s">
+      <c r="B25" s="322" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="277"/>
-      <c r="D25" s="277"/>
+      <c r="C25" s="279"/>
+      <c r="D25" s="279"/>
       <c r="E25" s="214">
         <f>600 *4.84</f>
         <v>2904</v>
@@ -6578,10 +6577,10 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="307">
+      <c r="G25" s="323">
         <v>1</v>
       </c>
-      <c r="H25" s="277"/>
+      <c r="H25" s="279"/>
       <c r="I25" s="213"/>
     </row>
     <row r="26" spans="2:11" ht="15" customHeight="1">
@@ -6598,18 +6597,18 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="307">
+      <c r="G26" s="323">
         <v>0.8</v>
       </c>
-      <c r="H26" s="277"/>
+      <c r="H26" s="279"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="314" t="s">
+      <c r="B27" s="347" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="277"/>
-      <c r="D27" s="277"/>
+      <c r="C27" s="279"/>
+      <c r="D27" s="279"/>
       <c r="E27" s="214">
         <f>E19*0.35</f>
         <v>5929</v>
@@ -6618,18 +6617,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="307">
+      <c r="G27" s="323">
         <v>0.6</v>
       </c>
-      <c r="H27" s="277"/>
+      <c r="H27" s="279"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="303" t="s">
+      <c r="B28" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="244"/>
-      <c r="D28" s="244"/>
+      <c r="C28" s="246"/>
+      <c r="D28" s="246"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -6638,11 +6637,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="294">
+      <c r="G28" s="310">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="244"/>
+      <c r="H28" s="246"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -6656,95 +6655,95 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="312" t="s">
+      <c r="B30" s="328" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="277"/>
-      <c r="D30" s="277"/>
-      <c r="E30" s="277"/>
-      <c r="F30" s="277"/>
-      <c r="G30" s="277"/>
-      <c r="H30" s="277"/>
-      <c r="I30" s="277"/>
+      <c r="C30" s="279"/>
+      <c r="D30" s="279"/>
+      <c r="E30" s="279"/>
+      <c r="F30" s="279"/>
+      <c r="G30" s="279"/>
+      <c r="H30" s="279"/>
+      <c r="I30" s="279"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="304" t="s">
+      <c r="B31" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="305"/>
-      <c r="D31" s="305"/>
-      <c r="E31" s="296" t="s">
+      <c r="C31" s="321"/>
+      <c r="D31" s="321"/>
+      <c r="E31" s="312" t="s">
         <v>119</v>
       </c>
-      <c r="F31" s="277"/>
+      <c r="F31" s="279"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="325" t="s">
+      <c r="H31" s="342" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="256"/>
+      <c r="I31" s="258"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="302" t="s">
+      <c r="B32" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="277"/>
-      <c r="D32" s="277"/>
-      <c r="E32" s="315" t="s">
+      <c r="C32" s="279"/>
+      <c r="D32" s="279"/>
+      <c r="E32" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="277"/>
+      <c r="F32" s="279"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="328" t="s">
+      <c r="H32" s="345" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="256"/>
+      <c r="I32" s="258"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="302" t="s">
+      <c r="B33" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="277"/>
-      <c r="D33" s="277"/>
-      <c r="E33" s="326">
+      <c r="C33" s="279"/>
+      <c r="D33" s="279"/>
+      <c r="E33" s="343">
         <v>1258.4000000000001</v>
       </c>
-      <c r="F33" s="277"/>
+      <c r="F33" s="279"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="328" t="s">
+      <c r="H33" s="345" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="256"/>
+      <c r="I33" s="258"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="321" t="s">
+      <c r="C34" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="277"/>
-      <c r="E34" s="323">
+      <c r="D34" s="279"/>
+      <c r="E34" s="340">
         <v>16900000</v>
       </c>
-      <c r="F34" s="277"/>
+      <c r="F34" s="279"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="300">
+      <c r="H34" s="316">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="256"/>
+      <c r="I34" s="258"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -6752,76 +6751,76 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="321" t="s">
+      <c r="C35" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="277"/>
-      <c r="E35" s="340" t="s">
+      <c r="D35" s="279"/>
+      <c r="E35" s="356" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="277"/>
+      <c r="F35" s="279"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="301">
+      <c r="H35" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I35" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I35" s="258"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="321" t="s">
+      <c r="C36" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="277"/>
-      <c r="E36" s="296" t="s">
+      <c r="D36" s="279"/>
+      <c r="E36" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="277"/>
+      <c r="F36" s="279"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="331"/>
-      <c r="I36" s="256"/>
+      <c r="H36" s="348"/>
+      <c r="I36" s="258"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="308" t="s">
+      <c r="B37" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="277"/>
-      <c r="D37" s="277"/>
-      <c r="E37" s="277"/>
-      <c r="F37" s="277"/>
-      <c r="G37" s="277"/>
-      <c r="H37" s="277"/>
-      <c r="I37" s="256"/>
+      <c r="C37" s="279"/>
+      <c r="D37" s="279"/>
+      <c r="E37" s="279"/>
+      <c r="F37" s="279"/>
+      <c r="G37" s="279"/>
+      <c r="H37" s="279"/>
+      <c r="I37" s="258"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="319" t="s">
+      <c r="B38" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="277"/>
-      <c r="D38" s="277"/>
+      <c r="C38" s="279"/>
+      <c r="D38" s="279"/>
       <c r="E38" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F38" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="309" t="s">
+      <c r="G38" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H38" s="277"/>
+      <c r="H38" s="279"/>
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="306" t="s">
+      <c r="B39" s="322" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="277"/>
-      <c r="D39" s="277"/>
+      <c r="C39" s="279"/>
+      <c r="D39" s="279"/>
       <c r="E39" s="214">
         <v>145.19999999999999</v>
       </c>
@@ -6829,10 +6828,10 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="307">
+      <c r="G39" s="323">
         <v>1</v>
       </c>
-      <c r="H39" s="277"/>
+      <c r="H39" s="279"/>
       <c r="I39" s="213"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1">
@@ -6849,18 +6848,18 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="307">
+      <c r="G40" s="323">
         <v>0.8</v>
       </c>
-      <c r="H40" s="277"/>
+      <c r="H40" s="279"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="314" t="s">
+      <c r="B41" s="347" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="277"/>
-      <c r="D41" s="277"/>
+      <c r="C41" s="279"/>
+      <c r="D41" s="279"/>
       <c r="E41" s="214">
         <f>E33*0.3512</f>
         <v>441.95008000000007</v>
@@ -6869,18 +6868,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="307">
+      <c r="G41" s="323">
         <v>0.6</v>
       </c>
-      <c r="H41" s="277"/>
+      <c r="H41" s="279"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="303" t="s">
+      <c r="B42" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="244"/>
-      <c r="D42" s="244"/>
+      <c r="C42" s="246"/>
+      <c r="D42" s="246"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -6889,11 +6888,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="294">
+      <c r="G42" s="310">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="244"/>
+      <c r="H42" s="246"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -6907,93 +6906,93 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="327" t="s">
+      <c r="B44" s="344" t="s">
         <v>122</v>
       </c>
-      <c r="C44" s="277"/>
-      <c r="D44" s="277"/>
-      <c r="E44" s="277"/>
-      <c r="F44" s="277"/>
-      <c r="G44" s="277"/>
-      <c r="H44" s="277"/>
-      <c r="I44" s="277"/>
+      <c r="C44" s="279"/>
+      <c r="D44" s="279"/>
+      <c r="E44" s="279"/>
+      <c r="F44" s="279"/>
+      <c r="G44" s="279"/>
+      <c r="H44" s="279"/>
+      <c r="I44" s="279"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="304" t="s">
+      <c r="B45" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="305"/>
-      <c r="D45" s="305"/>
-      <c r="E45" s="315" t="s">
+      <c r="C45" s="321"/>
+      <c r="D45" s="321"/>
+      <c r="E45" s="335" t="s">
         <v>119</v>
       </c>
-      <c r="F45" s="277"/>
+      <c r="F45" s="279"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="325" t="s">
+      <c r="H45" s="342" t="s">
         <v>120</v>
       </c>
-      <c r="I45" s="256"/>
+      <c r="I45" s="258"/>
       <c r="K45" s="203" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="302" t="s">
+      <c r="B46" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="277"/>
-      <c r="D46" s="277"/>
-      <c r="E46" s="315" t="s">
+      <c r="C46" s="279"/>
+      <c r="D46" s="279"/>
+      <c r="E46" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="277"/>
+      <c r="F46" s="279"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="328" t="s">
+      <c r="H46" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="256"/>
+      <c r="I46" s="258"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="302" t="s">
+      <c r="B47" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="277"/>
-      <c r="D47" s="277"/>
-      <c r="E47" s="334">
+      <c r="C47" s="279"/>
+      <c r="D47" s="279"/>
+      <c r="E47" s="352">
         <v>430.76</v>
       </c>
-      <c r="F47" s="277"/>
+      <c r="F47" s="279"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="299" t="s">
+      <c r="H47" s="315" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="256"/>
+      <c r="I47" s="258"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="321" t="s">
+      <c r="C48" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D48" s="277"/>
-      <c r="E48" s="295">
+      <c r="D48" s="279"/>
+      <c r="E48" s="311">
         <v>7120000</v>
       </c>
-      <c r="F48" s="277"/>
+      <c r="F48" s="279"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="317">
+      <c r="H48" s="331">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="256"/>
+      <c r="I48" s="258"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -7002,76 +7001,76 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="321" t="s">
+      <c r="C49" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="277"/>
-      <c r="E49" s="340" t="s">
+      <c r="D49" s="279"/>
+      <c r="E49" s="356" t="s">
         <v>116</v>
       </c>
-      <c r="F49" s="277"/>
+      <c r="F49" s="279"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="301">
+      <c r="H49" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I49" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I49" s="258"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="321" t="s">
+      <c r="C50" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="277"/>
-      <c r="E50" s="296" t="s">
+      <c r="D50" s="279"/>
+      <c r="E50" s="312" t="s">
         <v>124</v>
       </c>
-      <c r="F50" s="277"/>
+      <c r="F50" s="279"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H50" s="336"/>
-      <c r="I50" s="256"/>
+      <c r="I50" s="258"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="308" t="s">
+      <c r="B51" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="277"/>
-      <c r="D51" s="277"/>
-      <c r="E51" s="277"/>
-      <c r="F51" s="277"/>
-      <c r="G51" s="277"/>
-      <c r="H51" s="277"/>
-      <c r="I51" s="256"/>
+      <c r="C51" s="279"/>
+      <c r="D51" s="279"/>
+      <c r="E51" s="279"/>
+      <c r="F51" s="279"/>
+      <c r="G51" s="279"/>
+      <c r="H51" s="279"/>
+      <c r="I51" s="258"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="319" t="s">
+      <c r="B52" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="277"/>
-      <c r="D52" s="277"/>
+      <c r="C52" s="279"/>
+      <c r="D52" s="279"/>
       <c r="E52" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F52" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="309" t="s">
+      <c r="G52" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H52" s="277"/>
+      <c r="H52" s="279"/>
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="306" t="s">
+      <c r="B53" s="322" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="277"/>
-      <c r="D53" s="277"/>
+      <c r="C53" s="279"/>
+      <c r="D53" s="279"/>
       <c r="E53" s="168">
         <v>145.19999999999999</v>
       </c>
@@ -7079,10 +7078,10 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="298">
+      <c r="G53" s="314">
         <v>1</v>
       </c>
-      <c r="H53" s="277"/>
+      <c r="H53" s="279"/>
       <c r="I53" s="167"/>
     </row>
     <row r="54" spans="2:11" ht="15" customHeight="1">
@@ -7099,10 +7098,10 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="298">
+      <c r="G54" s="314">
         <v>0.8</v>
       </c>
-      <c r="H54" s="277"/>
+      <c r="H54" s="279"/>
       <c r="I54" s="167"/>
     </row>
     <row r="55" spans="2:11" ht="15" customHeight="1">
@@ -7119,18 +7118,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="298">
+      <c r="G55" s="314">
         <v>0.6</v>
       </c>
-      <c r="H55" s="277"/>
+      <c r="H55" s="279"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="303" t="s">
+      <c r="B56" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="244"/>
-      <c r="D56" s="244"/>
+      <c r="C56" s="246"/>
+      <c r="D56" s="246"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -7139,11 +7138,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="294">
+      <c r="G56" s="310">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="244"/>
+      <c r="H56" s="246"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -7157,93 +7156,93 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="312" t="s">
+      <c r="B58" s="328" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="277"/>
-      <c r="D58" s="277"/>
-      <c r="E58" s="277"/>
-      <c r="F58" s="277"/>
-      <c r="G58" s="277"/>
-      <c r="H58" s="277"/>
-      <c r="I58" s="277"/>
+      <c r="C58" s="279"/>
+      <c r="D58" s="279"/>
+      <c r="E58" s="279"/>
+      <c r="F58" s="279"/>
+      <c r="G58" s="279"/>
+      <c r="H58" s="279"/>
+      <c r="I58" s="279"/>
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="304" t="s">
+      <c r="B59" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="305"/>
-      <c r="D59" s="305"/>
-      <c r="E59" s="315" t="s">
+      <c r="C59" s="321"/>
+      <c r="D59" s="321"/>
+      <c r="E59" s="335" t="s">
         <v>126</v>
       </c>
-      <c r="F59" s="277"/>
+      <c r="F59" s="279"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="339" t="s">
+      <c r="H59" s="355" t="s">
         <v>127</v>
       </c>
-      <c r="I59" s="256"/>
+      <c r="I59" s="258"/>
       <c r="K59" s="203" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="302" t="s">
+      <c r="B60" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="277"/>
-      <c r="D60" s="277"/>
-      <c r="E60" s="315" t="s">
+      <c r="C60" s="279"/>
+      <c r="D60" s="279"/>
+      <c r="E60" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F60" s="277"/>
+      <c r="F60" s="279"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="328" t="s">
+      <c r="H60" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="256"/>
+      <c r="I60" s="258"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="302" t="s">
+      <c r="B61" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="277"/>
-      <c r="D61" s="277"/>
-      <c r="E61" s="310">
+      <c r="C61" s="279"/>
+      <c r="D61" s="279"/>
+      <c r="E61" s="326">
         <v>626</v>
       </c>
-      <c r="F61" s="277"/>
+      <c r="F61" s="279"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="328" t="s">
+      <c r="H61" s="345" t="s">
         <v>129</v>
       </c>
-      <c r="I61" s="256"/>
+      <c r="I61" s="258"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="321" t="s">
+      <c r="C62" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="277"/>
-      <c r="E62" s="335">
+      <c r="D62" s="279"/>
+      <c r="E62" s="350">
         <v>10500000</v>
       </c>
-      <c r="F62" s="277"/>
+      <c r="F62" s="279"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="311">
+      <c r="H62" s="327">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="256"/>
+      <c r="I62" s="258"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -7252,68 +7251,68 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="321" t="s">
+      <c r="C63" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="277"/>
-      <c r="E63" s="332" t="s">
+      <c r="D63" s="279"/>
+      <c r="E63" s="349" t="s">
         <v>116</v>
       </c>
-      <c r="F63" s="277"/>
+      <c r="F63" s="279"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="301">
+      <c r="H63" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I63" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I63" s="258"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="321" t="s">
+      <c r="C64" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D64" s="277"/>
-      <c r="E64" s="296" t="s">
+      <c r="D64" s="279"/>
+      <c r="E64" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="F64" s="277"/>
+      <c r="F64" s="279"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H64" s="336"/>
-      <c r="I64" s="256"/>
+      <c r="I64" s="258"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="308" t="s">
+      <c r="B65" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C65" s="277"/>
-      <c r="D65" s="277"/>
-      <c r="E65" s="277"/>
-      <c r="F65" s="277"/>
-      <c r="G65" s="277"/>
-      <c r="H65" s="277"/>
-      <c r="I65" s="256"/>
+      <c r="C65" s="279"/>
+      <c r="D65" s="279"/>
+      <c r="E65" s="279"/>
+      <c r="F65" s="279"/>
+      <c r="G65" s="279"/>
+      <c r="H65" s="279"/>
+      <c r="I65" s="258"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="319" t="s">
+      <c r="B66" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="277"/>
-      <c r="D66" s="277"/>
+      <c r="C66" s="279"/>
+      <c r="D66" s="279"/>
       <c r="E66" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F66" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="309" t="s">
+      <c r="G66" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H66" s="277"/>
+      <c r="H66" s="279"/>
       <c r="I66" s="167"/>
     </row>
     <row r="67" spans="2:11" ht="15" customHeight="1">
@@ -7329,10 +7328,10 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="298">
+      <c r="G67" s="314">
         <v>1</v>
       </c>
-      <c r="H67" s="277"/>
+      <c r="H67" s="279"/>
       <c r="I67" s="167"/>
     </row>
     <row r="68" spans="2:11" ht="15" customHeight="1">
@@ -7348,18 +7347,18 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="298">
+      <c r="G68" s="314">
         <v>0.9</v>
       </c>
-      <c r="H68" s="277"/>
+      <c r="H68" s="279"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="342" t="s">
+      <c r="B69" s="358" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="277"/>
-      <c r="D69" s="277"/>
+      <c r="C69" s="279"/>
+      <c r="D69" s="279"/>
       <c r="E69" s="168">
         <f>E61-E67-E68</f>
         <v>263</v>
@@ -7368,18 +7367,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="298">
+      <c r="G69" s="314">
         <v>0.6</v>
       </c>
-      <c r="H69" s="277"/>
+      <c r="H69" s="279"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="303" t="s">
+      <c r="B70" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="244"/>
-      <c r="D70" s="244"/>
+      <c r="C70" s="246"/>
+      <c r="D70" s="246"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -7388,11 +7387,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="294">
+      <c r="G70" s="310">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="244"/>
+      <c r="H70" s="246"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -7406,112 +7405,112 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="312" t="s">
+      <c r="B72" s="328" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="277"/>
-      <c r="D72" s="277"/>
-      <c r="E72" s="277"/>
-      <c r="F72" s="277"/>
-      <c r="G72" s="277"/>
-      <c r="H72" s="277"/>
-      <c r="I72" s="277"/>
+      <c r="C72" s="279"/>
+      <c r="D72" s="279"/>
+      <c r="E72" s="279"/>
+      <c r="F72" s="279"/>
+      <c r="G72" s="279"/>
+      <c r="H72" s="279"/>
+      <c r="I72" s="279"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="304" t="s">
+      <c r="B73" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="305"/>
-      <c r="D73" s="305"/>
-      <c r="E73" s="296" t="s">
+      <c r="C73" s="321"/>
+      <c r="D73" s="321"/>
+      <c r="E73" s="312" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="277"/>
+      <c r="F73" s="279"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="325" t="s">
+      <c r="H73" s="342" t="s">
         <v>133</v>
       </c>
-      <c r="I73" s="256"/>
+      <c r="I73" s="258"/>
       <c r="K73" s="203" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="302" t="s">
+      <c r="B74" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="277"/>
-      <c r="D74" s="277"/>
-      <c r="E74" s="296" t="s">
+      <c r="C74" s="279"/>
+      <c r="D74" s="279"/>
+      <c r="E74" s="312" t="s">
         <v>135</v>
       </c>
-      <c r="F74" s="277"/>
+      <c r="F74" s="279"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="328" t="s">
+      <c r="H74" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="256"/>
+      <c r="I74" s="258"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="302" t="s">
+      <c r="B75" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C75" s="277"/>
-      <c r="D75" s="277"/>
-      <c r="E75" s="313">
+      <c r="C75" s="279"/>
+      <c r="D75" s="279"/>
+      <c r="E75" s="329">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
-      <c r="F75" s="277"/>
+      <c r="F75" s="279"/>
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="299" t="s">
+      <c r="H75" s="315" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="256"/>
+      <c r="I75" s="258"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="321" t="s">
+      <c r="C76" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D76" s="277"/>
-      <c r="E76" s="295">
+      <c r="D76" s="279"/>
+      <c r="E76" s="311">
         <v>60000000</v>
       </c>
-      <c r="F76" s="277"/>
+      <c r="F76" s="279"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="317">
+      <c r="H76" s="331">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="256"/>
+      <c r="I76" s="258"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="321" t="s">
+      <c r="C77" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D77" s="277"/>
-      <c r="E77" s="347" t="s">
+      <c r="D77" s="279"/>
+      <c r="E77" s="364" t="s">
         <v>116</v>
       </c>
-      <c r="F77" s="277"/>
+      <c r="F77" s="279"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="301">
+      <c r="H77" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I77" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I77" s="258"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -7519,57 +7518,57 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="321" t="s">
+      <c r="C78" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="277"/>
-      <c r="E78" s="296" t="s">
+      <c r="D78" s="279"/>
+      <c r="E78" s="312" t="s">
         <v>136</v>
       </c>
-      <c r="F78" s="277"/>
+      <c r="F78" s="279"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H78" s="336"/>
-      <c r="I78" s="256"/>
+      <c r="I78" s="258"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="308" t="s">
+      <c r="B79" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C79" s="277"/>
-      <c r="D79" s="277"/>
-      <c r="E79" s="277"/>
-      <c r="F79" s="277"/>
-      <c r="G79" s="277"/>
-      <c r="H79" s="277"/>
-      <c r="I79" s="256"/>
+      <c r="C79" s="279"/>
+      <c r="D79" s="279"/>
+      <c r="E79" s="279"/>
+      <c r="F79" s="279"/>
+      <c r="G79" s="279"/>
+      <c r="H79" s="279"/>
+      <c r="I79" s="258"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="319" t="s">
+      <c r="B80" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C80" s="277"/>
-      <c r="D80" s="277"/>
+      <c r="C80" s="279"/>
+      <c r="D80" s="279"/>
       <c r="E80" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F80" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G80" s="309" t="s">
+      <c r="G80" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H80" s="277"/>
+      <c r="H80" s="279"/>
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="318" t="s">
+      <c r="B81" s="332" t="s">
         <v>130</v>
       </c>
-      <c r="C81" s="277"/>
-      <c r="D81" s="277"/>
+      <c r="C81" s="279"/>
+      <c r="D81" s="279"/>
       <c r="E81" s="168">
         <f>410*4.84</f>
         <v>1984.3999999999999</v>
@@ -7578,18 +7577,18 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="298">
+      <c r="G81" s="314">
         <v>0.9</v>
       </c>
-      <c r="H81" s="277"/>
+      <c r="H81" s="279"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="318" t="s">
+      <c r="B82" s="332" t="s">
         <v>117</v>
       </c>
-      <c r="C82" s="277"/>
-      <c r="D82" s="277"/>
+      <c r="C82" s="279"/>
+      <c r="D82" s="279"/>
       <c r="E82" s="168">
         <f>E75-(E81+E83)</f>
         <v>306.52687999999989</v>
@@ -7598,10 +7597,10 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="298">
+      <c r="G82" s="314">
         <v>0.8</v>
       </c>
-      <c r="H82" s="277"/>
+      <c r="H82" s="279"/>
       <c r="I82" s="167"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1">
@@ -7618,18 +7617,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="298">
+      <c r="G83" s="314">
         <v>0.6</v>
       </c>
-      <c r="H83" s="277"/>
+      <c r="H83" s="279"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="303" t="s">
+      <c r="B84" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="244"/>
-      <c r="D84" s="244"/>
+      <c r="C84" s="246"/>
+      <c r="D84" s="246"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -7638,11 +7637,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="294">
+      <c r="G84" s="310">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="244"/>
+      <c r="H84" s="246"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -7656,95 +7655,95 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="312" t="s">
+      <c r="B86" s="328" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="277"/>
-      <c r="D86" s="277"/>
-      <c r="E86" s="277"/>
-      <c r="F86" s="277"/>
-      <c r="G86" s="277"/>
-      <c r="H86" s="277"/>
-      <c r="I86" s="277"/>
+      <c r="C86" s="279"/>
+      <c r="D86" s="279"/>
+      <c r="E86" s="279"/>
+      <c r="F86" s="279"/>
+      <c r="G86" s="279"/>
+      <c r="H86" s="279"/>
+      <c r="I86" s="279"/>
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="304" t="s">
+      <c r="B87" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="305"/>
-      <c r="D87" s="305"/>
-      <c r="E87" s="315" t="s">
+      <c r="C87" s="321"/>
+      <c r="D87" s="321"/>
+      <c r="E87" s="335" t="s">
         <v>119</v>
       </c>
-      <c r="F87" s="277"/>
+      <c r="F87" s="279"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="338" t="str">
+      <c r="H87" s="357" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="256"/>
+      <c r="I87" s="258"/>
       <c r="K87" s="203" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="302" t="s">
+      <c r="B88" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="277"/>
-      <c r="D88" s="277"/>
-      <c r="E88" s="315" t="s">
+      <c r="C88" s="279"/>
+      <c r="D88" s="279"/>
+      <c r="E88" s="335" t="s">
         <v>90</v>
       </c>
-      <c r="F88" s="277"/>
+      <c r="F88" s="279"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="328" t="s">
+      <c r="H88" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="256"/>
+      <c r="I88" s="258"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="302" t="s">
+      <c r="B89" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="277"/>
-      <c r="D89" s="277"/>
-      <c r="E89" s="326">
+      <c r="C89" s="279"/>
+      <c r="D89" s="279"/>
+      <c r="E89" s="343">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
-      <c r="F89" s="277"/>
+      <c r="F89" s="279"/>
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="299" t="s">
+      <c r="H89" s="315" t="s">
         <v>95</v>
       </c>
-      <c r="I89" s="256"/>
+      <c r="I89" s="258"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="321" t="s">
+      <c r="C90" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D90" s="277"/>
-      <c r="E90" s="346">
+      <c r="D90" s="279"/>
+      <c r="E90" s="337">
         <v>43980000</v>
       </c>
-      <c r="F90" s="277"/>
+      <c r="F90" s="279"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="311">
+      <c r="H90" s="327">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="256"/>
+      <c r="I90" s="258"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -7752,75 +7751,75 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="321" t="s">
+      <c r="C91" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D91" s="277"/>
-      <c r="E91" s="344" t="s">
+      <c r="D91" s="279"/>
+      <c r="E91" s="362" t="s">
         <v>116</v>
       </c>
-      <c r="F91" s="277"/>
+      <c r="F91" s="279"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="301">
+      <c r="H91" s="317">
         <f ca="1">TODAY()</f>
-        <v>45712</v>
-      </c>
-      <c r="I91" s="256"/>
+        <v>45824</v>
+      </c>
+      <c r="I91" s="258"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="321" t="s">
+      <c r="C92" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D92" s="277"/>
-      <c r="E92" s="296" t="s">
+      <c r="D92" s="279"/>
+      <c r="E92" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="F92" s="277"/>
+      <c r="F92" s="279"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H92" s="336"/>
-      <c r="I92" s="256"/>
+      <c r="I92" s="258"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="308" t="s">
+      <c r="B93" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C93" s="277"/>
-      <c r="D93" s="277"/>
-      <c r="E93" s="277"/>
-      <c r="F93" s="277"/>
-      <c r="G93" s="277"/>
-      <c r="H93" s="277"/>
-      <c r="I93" s="256"/>
+      <c r="C93" s="279"/>
+      <c r="D93" s="279"/>
+      <c r="E93" s="279"/>
+      <c r="F93" s="279"/>
+      <c r="G93" s="279"/>
+      <c r="H93" s="279"/>
+      <c r="I93" s="258"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="319" t="s">
+      <c r="B94" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C94" s="277"/>
-      <c r="D94" s="277"/>
+      <c r="C94" s="279"/>
+      <c r="D94" s="279"/>
       <c r="E94" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F94" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G94" s="309" t="s">
+      <c r="G94" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H94" s="277"/>
+      <c r="H94" s="279"/>
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="306" t="s">
+      <c r="B95" s="322" t="s">
         <v>106</v>
       </c>
-      <c r="C95" s="277"/>
-      <c r="D95" s="277"/>
+      <c r="C95" s="279"/>
+      <c r="D95" s="279"/>
       <c r="E95" s="234">
         <v>1100</v>
       </c>
@@ -7828,10 +7827,10 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="350">
+      <c r="G95" s="366">
         <v>1</v>
       </c>
-      <c r="H95" s="277"/>
+      <c r="H95" s="279"/>
       <c r="I95" s="206"/>
     </row>
     <row r="96" spans="2:11" ht="15" customHeight="1">
@@ -7848,18 +7847,18 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="350">
+      <c r="G96" s="366">
         <v>0.8</v>
       </c>
-      <c r="H96" s="277"/>
+      <c r="H96" s="279"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="345" t="s">
+      <c r="B97" s="363" t="s">
         <v>107</v>
       </c>
-      <c r="C97" s="277"/>
-      <c r="D97" s="277"/>
+      <c r="C97" s="279"/>
+      <c r="D97" s="279"/>
       <c r="E97" s="168">
         <f>E89*0.3514</f>
         <v>1246.6688079999999</v>
@@ -7868,20 +7867,20 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="298">
+      <c r="G97" s="314">
         <v>0.6</v>
       </c>
-      <c r="H97" s="277"/>
+      <c r="H97" s="279"/>
       <c r="I97" s="167"/>
       <c r="K97" s="207"/>
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="303" t="s">
+      <c r="B98" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C98" s="244"/>
-      <c r="D98" s="244"/>
+      <c r="C98" s="246"/>
+      <c r="D98" s="246"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -7890,11 +7889,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="294">
+      <c r="G98" s="310">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="244"/>
+      <c r="H98" s="246"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -7915,177 +7914,177 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="316"/>
-      <c r="C100" s="277"/>
-      <c r="D100" s="277"/>
-      <c r="E100" s="277"/>
-      <c r="F100" s="277"/>
-      <c r="G100" s="277"/>
-      <c r="H100" s="277"/>
-      <c r="I100" s="277"/>
+      <c r="B100" s="330"/>
+      <c r="C100" s="279"/>
+      <c r="D100" s="279"/>
+      <c r="E100" s="279"/>
+      <c r="F100" s="279"/>
+      <c r="G100" s="279"/>
+      <c r="H100" s="279"/>
+      <c r="I100" s="279"/>
       <c r="K100" s="207"/>
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="312" t="s">
+      <c r="B101" s="328" t="s">
         <v>139</v>
       </c>
-      <c r="C101" s="277"/>
-      <c r="D101" s="277"/>
-      <c r="E101" s="277"/>
-      <c r="F101" s="277"/>
-      <c r="G101" s="277"/>
-      <c r="H101" s="277"/>
-      <c r="I101" s="277"/>
+      <c r="C101" s="279"/>
+      <c r="D101" s="279"/>
+      <c r="E101" s="279"/>
+      <c r="F101" s="279"/>
+      <c r="G101" s="279"/>
+      <c r="H101" s="279"/>
+      <c r="I101" s="279"/>
       <c r="K101" s="207"/>
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="304" t="s">
+      <c r="B102" s="320" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="305"/>
-      <c r="D102" s="305"/>
-      <c r="E102" s="348"/>
-      <c r="F102" s="277"/>
+      <c r="C102" s="321"/>
+      <c r="D102" s="321"/>
+      <c r="E102" s="372"/>
+      <c r="F102" s="279"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="297"/>
-      <c r="I102" s="256"/>
+      <c r="H102" s="313"/>
+      <c r="I102" s="258"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="302" t="s">
+      <c r="B103" s="318" t="s">
         <v>89</v>
       </c>
-      <c r="C103" s="277"/>
-      <c r="D103" s="277"/>
-      <c r="E103" s="351"/>
-      <c r="F103" s="277"/>
+      <c r="C103" s="279"/>
+      <c r="D103" s="279"/>
+      <c r="E103" s="367"/>
+      <c r="F103" s="279"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="343"/>
-      <c r="I103" s="256"/>
+      <c r="H103" s="361"/>
+      <c r="I103" s="258"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="302" t="s">
+      <c r="B104" s="318" t="s">
         <v>93</v>
       </c>
-      <c r="C104" s="277"/>
-      <c r="D104" s="277"/>
-      <c r="E104" s="310"/>
-      <c r="F104" s="277"/>
+      <c r="C104" s="279"/>
+      <c r="D104" s="279"/>
+      <c r="E104" s="326"/>
+      <c r="F104" s="279"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="322"/>
-      <c r="I104" s="256"/>
+      <c r="H104" s="339"/>
+      <c r="I104" s="258"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="321" t="s">
+      <c r="C105" s="334" t="s">
         <v>113</v>
       </c>
-      <c r="D105" s="277"/>
-      <c r="E105" s="346"/>
-      <c r="F105" s="277"/>
+      <c r="D105" s="279"/>
+      <c r="E105" s="337"/>
+      <c r="F105" s="279"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="311"/>
-      <c r="I105" s="256"/>
+      <c r="H105" s="327"/>
+      <c r="I105" s="258"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="321" t="s">
+      <c r="C106" s="334" t="s">
         <v>115</v>
       </c>
-      <c r="D106" s="277"/>
-      <c r="E106" s="344"/>
-      <c r="F106" s="277"/>
+      <c r="D106" s="279"/>
+      <c r="E106" s="362"/>
+      <c r="F106" s="279"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="349"/>
-      <c r="I106" s="256"/>
+      <c r="H106" s="365"/>
+      <c r="I106" s="258"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="321" t="s">
+      <c r="C107" s="334" t="s">
         <v>96</v>
       </c>
-      <c r="D107" s="277"/>
-      <c r="E107" s="320"/>
-      <c r="F107" s="277"/>
+      <c r="D107" s="279"/>
+      <c r="E107" s="338"/>
+      <c r="F107" s="279"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
       <c r="H107" s="336"/>
-      <c r="I107" s="256"/>
+      <c r="I107" s="258"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="308" t="s">
+      <c r="B108" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="C108" s="277"/>
-      <c r="D108" s="277"/>
-      <c r="E108" s="277"/>
-      <c r="F108" s="277"/>
-      <c r="G108" s="277"/>
-      <c r="H108" s="277"/>
-      <c r="I108" s="256"/>
+      <c r="C108" s="279"/>
+      <c r="D108" s="279"/>
+      <c r="E108" s="279"/>
+      <c r="F108" s="279"/>
+      <c r="G108" s="279"/>
+      <c r="H108" s="279"/>
+      <c r="I108" s="258"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="319" t="s">
+      <c r="B109" s="333" t="s">
         <v>102</v>
       </c>
-      <c r="C109" s="277"/>
-      <c r="D109" s="277"/>
+      <c r="C109" s="279"/>
+      <c r="D109" s="279"/>
       <c r="E109" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F109" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="309" t="s">
+      <c r="G109" s="325" t="s">
         <v>105</v>
       </c>
-      <c r="H109" s="277"/>
+      <c r="H109" s="279"/>
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="345" t="s">
+      <c r="B110" s="363" t="s">
         <v>106</v>
       </c>
-      <c r="C110" s="277"/>
-      <c r="D110" s="277"/>
+      <c r="C110" s="279"/>
+      <c r="D110" s="279"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="298"/>
-      <c r="H110" s="277"/>
+      <c r="G110" s="314"/>
+      <c r="H110" s="279"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="345" t="s">
+      <c r="B111" s="363" t="s">
         <v>107</v>
       </c>
-      <c r="C111" s="277"/>
-      <c r="D111" s="277"/>
+      <c r="C111" s="279"/>
+      <c r="D111" s="279"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="298"/>
-      <c r="H111" s="277"/>
+      <c r="G111" s="314"/>
+      <c r="H111" s="279"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="303" t="s">
+      <c r="B112" s="319" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="244"/>
-      <c r="D112" s="244"/>
+      <c r="C112" s="246"/>
+      <c r="D112" s="246"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -8094,19 +8093,15 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="294">
+      <c r="G112" s="310">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="244"/>
+      <c r="H112" s="246"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E74:F74"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="E88:F88"/>
     <mergeCell ref="B38:D38"/>
@@ -8127,9 +8122,10 @@
     <mergeCell ref="G109:H109"/>
     <mergeCell ref="H73:I73"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="B12:D12"/>
     <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G39:H39"/>
     <mergeCell ref="G111:H111"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B73:D73"/>
@@ -8151,7 +8147,8 @@
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="G96:H96"/>
-    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="C107:D107"/>
     <mergeCell ref="B112:D112"/>
     <mergeCell ref="H92:I92"/>
@@ -8175,16 +8172,8 @@
     <mergeCell ref="B110:D110"/>
     <mergeCell ref="C92:D92"/>
     <mergeCell ref="E77:F77"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E50:F50"/>
     <mergeCell ref="H35:I35"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B84:D84"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B79:I79"/>
@@ -8199,8 +8188,8 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B65:I65"/>
     <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E59:F59"/>
@@ -8223,8 +8212,12 @@
     <mergeCell ref="H61:I61"/>
     <mergeCell ref="E104:F104"/>
     <mergeCell ref="G38:H38"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="B30:I30"/>
@@ -8232,31 +8225,23 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H87:I87"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="H21:I21"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="G82:H82"/>
@@ -8264,7 +8249,6 @@
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C90:D90"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="C77:D77"/>
@@ -8272,7 +8256,16 @@
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="E107:F107"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B102:D102"/>
@@ -8297,8 +8290,6 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="H47:I47"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
     <mergeCell ref="B98:D98"/>
     <mergeCell ref="B100:I100"/>
     <mergeCell ref="H48:I48"/>
@@ -8308,6 +8299,14 @@
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E22:F22"/>
@@ -8339,7 +8338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:M10"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -8654,7 +8653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8683,16 +8682,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="355"/>
-      <c r="F1" s="356"/>
-      <c r="G1" s="356"/>
-      <c r="H1" s="356"/>
-      <c r="I1" s="356"/>
-      <c r="J1" s="356"/>
-      <c r="K1" s="356"/>
-      <c r="L1" s="356"/>
-      <c r="M1" s="356"/>
-      <c r="N1" s="356"/>
+      <c r="E1" s="375"/>
+      <c r="F1" s="376"/>
+      <c r="G1" s="376"/>
+      <c r="H1" s="376"/>
+      <c r="I1" s="376"/>
+      <c r="J1" s="376"/>
+      <c r="K1" s="376"/>
+      <c r="L1" s="376"/>
+      <c r="M1" s="376"/>
+      <c r="N1" s="376"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -9240,21 +9239,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="357" t="s">
+      <c r="A12" s="374" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="242"/>
-      <c r="C12" s="358" t="s">
+      <c r="B12" s="244"/>
+      <c r="C12" s="377" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="356"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
-      <c r="G12" s="356"/>
-      <c r="H12" s="356"/>
-      <c r="I12" s="356"/>
-      <c r="J12" s="356"/>
-      <c r="K12" s="356"/>
+      <c r="D12" s="376"/>
+      <c r="E12" s="376"/>
+      <c r="F12" s="376"/>
+      <c r="G12" s="376"/>
+      <c r="H12" s="376"/>
+      <c r="I12" s="376"/>
+      <c r="J12" s="376"/>
+      <c r="K12" s="376"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -9269,21 +9268,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="357" t="s">
+      <c r="A13" s="374" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="242"/>
-      <c r="C13" s="358" t="s">
+      <c r="B13" s="244"/>
+      <c r="C13" s="377" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="356"/>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
-      <c r="G13" s="356"/>
-      <c r="H13" s="356"/>
-      <c r="I13" s="356"/>
-      <c r="J13" s="356"/>
-      <c r="K13" s="356"/>
+      <c r="D13" s="376"/>
+      <c r="E13" s="376"/>
+      <c r="F13" s="376"/>
+      <c r="G13" s="376"/>
+      <c r="H13" s="376"/>
+      <c r="I13" s="376"/>
+      <c r="J13" s="376"/>
+      <c r="K13" s="376"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -9298,22 +9297,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="357" t="str">
+      <c r="A14" s="374" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="242"/>
-      <c r="C14" s="358" t="s">
+      <c r="B14" s="244"/>
+      <c r="C14" s="377" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="356"/>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
-      <c r="G14" s="356"/>
-      <c r="H14" s="356"/>
-      <c r="I14" s="356"/>
-      <c r="J14" s="356"/>
-      <c r="K14" s="356"/>
+      <c r="D14" s="376"/>
+      <c r="E14" s="376"/>
+      <c r="F14" s="376"/>
+      <c r="G14" s="376"/>
+      <c r="H14" s="376"/>
+      <c r="I14" s="376"/>
+      <c r="J14" s="376"/>
+      <c r="K14" s="376"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -9328,21 +9327,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="357" t="s">
+      <c r="A15" s="374" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="242"/>
-      <c r="C15" s="358" t="s">
+      <c r="B15" s="244"/>
+      <c r="C15" s="377" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="356"/>
-      <c r="E15" s="356"/>
-      <c r="F15" s="356"/>
-      <c r="G15" s="356"/>
-      <c r="H15" s="356"/>
-      <c r="I15" s="356"/>
-      <c r="J15" s="356"/>
-      <c r="K15" s="356"/>
+      <c r="D15" s="376"/>
+      <c r="E15" s="376"/>
+      <c r="F15" s="376"/>
+      <c r="G15" s="376"/>
+      <c r="H15" s="376"/>
+      <c r="I15" s="376"/>
+      <c r="J15" s="376"/>
+      <c r="K15" s="376"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -9357,21 +9356,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="357" t="s">
+      <c r="A16" s="374" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="242"/>
-      <c r="C16" s="360" t="s">
+      <c r="B16" s="244"/>
+      <c r="C16" s="379" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="356"/>
-      <c r="E16" s="356"/>
-      <c r="F16" s="356"/>
-      <c r="G16" s="356"/>
-      <c r="H16" s="356"/>
-      <c r="I16" s="356"/>
-      <c r="J16" s="356"/>
-      <c r="K16" s="356"/>
+      <c r="D16" s="376"/>
+      <c r="E16" s="376"/>
+      <c r="F16" s="376"/>
+      <c r="G16" s="376"/>
+      <c r="H16" s="376"/>
+      <c r="I16" s="376"/>
+      <c r="J16" s="376"/>
+      <c r="K16" s="376"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -9381,21 +9380,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="357" t="s">
+      <c r="A17" s="374" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="242"/>
-      <c r="C17" s="360" t="s">
+      <c r="B17" s="244"/>
+      <c r="C17" s="379" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="356"/>
-      <c r="E17" s="356"/>
-      <c r="F17" s="356"/>
-      <c r="G17" s="356"/>
-      <c r="H17" s="356"/>
-      <c r="I17" s="356"/>
-      <c r="J17" s="356"/>
-      <c r="K17" s="356"/>
+      <c r="D17" s="376"/>
+      <c r="E17" s="376"/>
+      <c r="F17" s="376"/>
+      <c r="G17" s="376"/>
+      <c r="H17" s="376"/>
+      <c r="I17" s="376"/>
+      <c r="J17" s="376"/>
+      <c r="K17" s="376"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>185</v>
@@ -9414,21 +9413,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="357" t="s">
+      <c r="A18" s="374" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="242"/>
-      <c r="C18" s="360" t="s">
+      <c r="B18" s="244"/>
+      <c r="C18" s="379" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-      <c r="G18" s="356"/>
-      <c r="H18" s="356"/>
-      <c r="I18" s="356"/>
-      <c r="J18" s="356"/>
-      <c r="K18" s="356"/>
+      <c r="D18" s="376"/>
+      <c r="E18" s="376"/>
+      <c r="F18" s="376"/>
+      <c r="G18" s="376"/>
+      <c r="H18" s="376"/>
+      <c r="I18" s="376"/>
+      <c r="J18" s="376"/>
+      <c r="K18" s="376"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>188</v>
@@ -9442,21 +9441,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="357" t="s">
+      <c r="A19" s="374" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="242"/>
-      <c r="C19" s="360" t="s">
+      <c r="B19" s="244"/>
+      <c r="C19" s="379" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="356"/>
-      <c r="E19" s="356"/>
-      <c r="F19" s="356"/>
-      <c r="G19" s="356"/>
-      <c r="H19" s="356"/>
-      <c r="I19" s="356"/>
-      <c r="J19" s="356"/>
-      <c r="K19" s="356"/>
+      <c r="D19" s="376"/>
+      <c r="E19" s="376"/>
+      <c r="F19" s="376"/>
+      <c r="G19" s="376"/>
+      <c r="H19" s="376"/>
+      <c r="I19" s="376"/>
+      <c r="J19" s="376"/>
+      <c r="K19" s="376"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -9471,21 +9470,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="357" t="s">
+      <c r="A20" s="374" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="242"/>
-      <c r="C20" s="360" t="s">
+      <c r="B20" s="244"/>
+      <c r="C20" s="379" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="356"/>
-      <c r="E20" s="356"/>
-      <c r="F20" s="356"/>
-      <c r="G20" s="356"/>
-      <c r="H20" s="356"/>
-      <c r="I20" s="356"/>
-      <c r="J20" s="356"/>
-      <c r="K20" s="356"/>
+      <c r="D20" s="376"/>
+      <c r="E20" s="376"/>
+      <c r="F20" s="376"/>
+      <c r="G20" s="376"/>
+      <c r="H20" s="376"/>
+      <c r="I20" s="376"/>
+      <c r="J20" s="376"/>
+      <c r="K20" s="376"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -9500,21 +9499,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="357" t="s">
+      <c r="A21" s="374" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="242"/>
-      <c r="C21" s="360" t="s">
+      <c r="B21" s="244"/>
+      <c r="C21" s="379" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="356"/>
-      <c r="E21" s="356"/>
-      <c r="F21" s="356"/>
-      <c r="G21" s="356"/>
-      <c r="H21" s="356"/>
-      <c r="I21" s="356"/>
-      <c r="J21" s="356"/>
-      <c r="K21" s="356"/>
+      <c r="D21" s="376"/>
+      <c r="E21" s="376"/>
+      <c r="F21" s="376"/>
+      <c r="G21" s="376"/>
+      <c r="H21" s="376"/>
+      <c r="I21" s="376"/>
+      <c r="J21" s="376"/>
+      <c r="K21" s="376"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -9529,25 +9528,25 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="357" t="s">
+      <c r="A22" s="374" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="242"/>
-      <c r="C22" s="359" t="s">
+      <c r="B22" s="244"/>
+      <c r="C22" s="378" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="356"/>
-      <c r="E22" s="356"/>
-      <c r="F22" s="356"/>
-      <c r="G22" s="356"/>
-      <c r="H22" s="356"/>
-      <c r="I22" s="356"/>
-      <c r="J22" s="356"/>
-      <c r="K22" s="356"/>
-      <c r="L22" s="356"/>
-      <c r="M22" s="356"/>
-      <c r="N22" s="356"/>
-      <c r="O22" s="256"/>
+      <c r="D22" s="376"/>
+      <c r="E22" s="376"/>
+      <c r="F22" s="376"/>
+      <c r="G22" s="376"/>
+      <c r="H22" s="376"/>
+      <c r="I22" s="376"/>
+      <c r="J22" s="376"/>
+      <c r="K22" s="376"/>
+      <c r="L22" s="376"/>
+      <c r="M22" s="376"/>
+      <c r="N22" s="376"/>
+      <c r="O22" s="258"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
       </c>
@@ -9558,22 +9557,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="357" t="s">
+      <c r="A23" s="374" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="242"/>
-      <c r="C23" s="360" t="s">
+      <c r="B23" s="244"/>
+      <c r="C23" s="379" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="356"/>
-      <c r="E23" s="356"/>
-      <c r="F23" s="356"/>
-      <c r="G23" s="356"/>
-      <c r="H23" s="356"/>
-      <c r="I23" s="356"/>
-      <c r="J23" s="356"/>
-      <c r="K23" s="356"/>
-      <c r="L23" s="356"/>
+      <c r="D23" s="376"/>
+      <c r="E23" s="376"/>
+      <c r="F23" s="376"/>
+      <c r="G23" s="376"/>
+      <c r="H23" s="376"/>
+      <c r="I23" s="376"/>
+      <c r="J23" s="376"/>
+      <c r="K23" s="376"/>
+      <c r="L23" s="376"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -9587,22 +9586,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="357" t="s">
+      <c r="A24" s="374" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="242"/>
-      <c r="C24" s="360" t="s">
+      <c r="B24" s="244"/>
+      <c r="C24" s="379" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="356"/>
-      <c r="E24" s="356"/>
-      <c r="F24" s="356"/>
-      <c r="G24" s="356"/>
-      <c r="H24" s="356"/>
-      <c r="I24" s="356"/>
-      <c r="J24" s="356"/>
-      <c r="K24" s="356"/>
-      <c r="L24" s="356"/>
+      <c r="D24" s="376"/>
+      <c r="E24" s="376"/>
+      <c r="F24" s="376"/>
+      <c r="G24" s="376"/>
+      <c r="H24" s="376"/>
+      <c r="I24" s="376"/>
+      <c r="J24" s="376"/>
+      <c r="K24" s="376"/>
+      <c r="L24" s="376"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -9616,21 +9615,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="357" t="s">
+      <c r="A25" s="374" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="242"/>
-      <c r="C25" s="360" t="s">
+      <c r="B25" s="244"/>
+      <c r="C25" s="379" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="356"/>
-      <c r="E25" s="356"/>
-      <c r="F25" s="356"/>
-      <c r="G25" s="356"/>
-      <c r="H25" s="356"/>
-      <c r="I25" s="356"/>
-      <c r="J25" s="356"/>
-      <c r="K25" s="356"/>
+      <c r="D25" s="376"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
+      <c r="G25" s="376"/>
+      <c r="H25" s="376"/>
+      <c r="I25" s="376"/>
+      <c r="J25" s="376"/>
+      <c r="K25" s="376"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -9640,21 +9639,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="361" t="s">
+      <c r="A26" s="380" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="362"/>
-      <c r="C26" s="363" t="s">
+      <c r="B26" s="381"/>
+      <c r="C26" s="382" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="364"/>
-      <c r="E26" s="364"/>
-      <c r="F26" s="364"/>
-      <c r="G26" s="364"/>
-      <c r="H26" s="364"/>
-      <c r="I26" s="364"/>
-      <c r="J26" s="364"/>
-      <c r="K26" s="364"/>
+      <c r="D26" s="383"/>
+      <c r="E26" s="383"/>
+      <c r="F26" s="383"/>
+      <c r="G26" s="383"/>
+      <c r="H26" s="383"/>
+      <c r="I26" s="383"/>
+      <c r="J26" s="383"/>
+      <c r="K26" s="383"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -9753,7 +9752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C4:L34"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -9762,360 +9761,358 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="365" t="str">
+      <c r="C4" s="384" t="str">
         <f>'AREA UTIL '!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="365" t="s">
+      <c r="C5" s="384" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="370" t="s">
+      <c r="C6" s="389" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="246"/>
-      <c r="E6" s="246"/>
-      <c r="F6" s="367">
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="386">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="246"/>
-      <c r="H6" s="256"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="258"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="370" t="s">
+      <c r="C7" s="389" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="246"/>
-      <c r="E7" s="246"/>
-      <c r="F7" s="367">
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="386">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="246"/>
-      <c r="H7" s="256"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="258"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="370" t="s">
+      <c r="C8" s="389" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="246"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="367">
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="386">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="246"/>
-      <c r="H8" s="256"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="258"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="370" t="s">
+      <c r="C9" s="389" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="366">
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="385">
         <v>6</v>
       </c>
-      <c r="G9" s="246"/>
-      <c r="H9" s="256"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="258"/>
       <c r="J9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="370" t="s">
+      <c r="C10" s="389" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="366">
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="385">
         <v>1</v>
       </c>
-      <c r="G10" s="246"/>
-      <c r="H10" s="256"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="258"/>
       <c r="J10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="370" t="s">
+      <c r="C11" s="389" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="246"/>
-      <c r="E11" s="246"/>
-      <c r="F11" s="375">
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="399">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="246"/>
-      <c r="H11" s="256"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="258"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="370" t="s">
+      <c r="C12" s="389" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="246"/>
-      <c r="E12" s="246"/>
-      <c r="F12" s="366">
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="385">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="246"/>
-      <c r="H12" s="256"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="258"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="370" t="s">
+      <c r="C13" s="389" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="367">
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="386">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="246"/>
-      <c r="H13" s="256"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="258"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="374" t="s">
+      <c r="C14" s="396" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="373">
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="392">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="241"/>
-      <c r="H14" s="242"/>
-      <c r="J14" s="371">
+      <c r="G14" s="243"/>
+      <c r="H14" s="244"/>
+      <c r="J14" s="390">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="246"/>
-      <c r="L14" s="246"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="376"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="246"/>
-      <c r="G15" s="246"/>
-      <c r="H15" s="246"/>
+      <c r="C15" s="394"/>
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="248"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="248"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="382" t="s">
+      <c r="C16" s="398" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="246"/>
-      <c r="G16" s="246"/>
-      <c r="H16" s="246"/>
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="248"/>
+      <c r="G16" s="248"/>
+      <c r="H16" s="248"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="370" t="s">
+      <c r="C17" s="389" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="366">
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="385">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="246"/>
-      <c r="H17" s="256"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="258"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="370" t="s">
+      <c r="C18" s="389" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="246"/>
-      <c r="E18" s="246"/>
-      <c r="F18" s="367">
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="386">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="246"/>
-      <c r="H18" s="256"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="258"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="370" t="s">
+      <c r="C19" s="389" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="246"/>
-      <c r="E19" s="246"/>
-      <c r="F19" s="367">
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="386">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="246"/>
-      <c r="H19" s="256"/>
+      <c r="G19" s="248"/>
+      <c r="H19" s="258"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="374" t="s">
+      <c r="C20" s="396" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="241"/>
-      <c r="E20" s="241"/>
-      <c r="F20" s="373">
+      <c r="D20" s="243"/>
+      <c r="E20" s="243"/>
+      <c r="F20" s="392">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="241"/>
-      <c r="H20" s="242"/>
+      <c r="G20" s="243"/>
+      <c r="H20" s="244"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="381"/>
-      <c r="D21" s="246"/>
-      <c r="E21" s="246"/>
-      <c r="F21" s="368"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
+      <c r="C21" s="400"/>
+      <c r="D21" s="248"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="387"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="381"/>
-      <c r="D22" s="246"/>
-      <c r="E22" s="246"/>
-      <c r="F22" s="368"/>
-      <c r="G22" s="246"/>
-      <c r="H22" s="246"/>
+      <c r="C22" s="400"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="387"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="381"/>
-      <c r="D23" s="246"/>
-      <c r="E23" s="246"/>
-      <c r="F23" s="379"/>
-      <c r="G23" s="246"/>
-      <c r="H23" s="246"/>
+      <c r="C23" s="400"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="393"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="248"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="372" t="s">
+      <c r="C24" s="391" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="246"/>
-      <c r="E24" s="246"/>
-      <c r="F24" s="246"/>
-      <c r="G24" s="246"/>
-      <c r="H24" s="246"/>
+      <c r="D24" s="248"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="248"/>
+      <c r="G24" s="248"/>
+      <c r="H24" s="248"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="369" t="s">
+      <c r="C25" s="388" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="246"/>
-      <c r="E25" s="246"/>
-      <c r="F25" s="377">
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="395">
         <v>2000000</v>
       </c>
-      <c r="G25" s="246"/>
-      <c r="H25" s="256"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="258"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="369" t="s">
+      <c r="C26" s="388" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="246"/>
-      <c r="E26" s="246"/>
-      <c r="F26" s="383">
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="401">
         <v>0.8</v>
       </c>
-      <c r="G26" s="246"/>
-      <c r="H26" s="256"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="258"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="369" t="s">
+      <c r="C27" s="388" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="246"/>
-      <c r="E27" s="246"/>
-      <c r="F27" s="377">
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="395">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="246"/>
-      <c r="H27" s="256"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="258"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="378" t="s">
+      <c r="C28" s="397" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="241"/>
-      <c r="E28" s="241"/>
-      <c r="F28" s="380">
+      <c r="D28" s="243"/>
+      <c r="E28" s="243"/>
+      <c r="F28" s="402">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="241"/>
-      <c r="H28" s="242"/>
+      <c r="G28" s="243"/>
+      <c r="H28" s="244"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="382" t="s">
+      <c r="C31" s="398" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="246"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="246"/>
-      <c r="G31" s="246"/>
-      <c r="H31" s="246"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="370" t="s">
+      <c r="C32" s="389" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="246"/>
-      <c r="E32" s="246"/>
-      <c r="F32" s="367">
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="386">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="246"/>
-      <c r="H32" s="256"/>
+      <c r="G32" s="248"/>
+      <c r="H32" s="258"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="370" t="s">
+      <c r="C33" s="389" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="246"/>
-      <c r="E33" s="246"/>
-      <c r="F33" s="367">
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="386">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="246"/>
-      <c r="H33" s="256"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="258"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="374" t="s">
+      <c r="C34" s="396" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="241"/>
-      <c r="E34" s="241"/>
-      <c r="F34" s="373">
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="392">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="241"/>
-      <c r="H34" s="242"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="F32:H32"/>
@@ -10125,29 +10122,25 @@
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F13:H13"/>
     <mergeCell ref="F27:H27"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="F20:H20"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C15:H15"/>
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
     <mergeCell ref="C32:E32"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F19:H19"/>
@@ -10161,12 +10154,18 @@
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F21:H21"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10174,7 +10173,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C5:K18"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -10184,166 +10183,166 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="365" t="str">
+      <c r="C5" s="384" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="365" t="s">
+      <c r="C6" s="384" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="246"/>
-      <c r="E6" s="246"/>
-      <c r="F6" s="246"/>
-      <c r="G6" s="246"/>
-      <c r="H6" s="246"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="370" t="s">
+      <c r="C7" s="389" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="246"/>
-      <c r="E7" s="246"/>
-      <c r="F7" s="385">
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="404">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="246"/>
-      <c r="H7" s="256"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="258"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="370" t="s">
+      <c r="C8" s="389" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="246"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="366">
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="385">
         <v>36</v>
       </c>
-      <c r="G8" s="246"/>
-      <c r="H8" s="256"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="258"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="370" t="s">
+      <c r="C9" s="389" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="384">
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="403">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="246"/>
-      <c r="H9" s="256"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="258"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="370" t="s">
+      <c r="C10" s="389" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="246"/>
-      <c r="E10" s="246"/>
-      <c r="F10" s="367">
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="386">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="246"/>
-      <c r="H10" s="256"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="258"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="374" t="s">
+      <c r="C11" s="396" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="373">
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="392">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="241"/>
-      <c r="H11" s="242"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="244"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="382" t="s">
+      <c r="C13" s="398" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="246"/>
-      <c r="E13" s="246"/>
-      <c r="F13" s="246"/>
-      <c r="G13" s="246"/>
-      <c r="H13" s="246"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="370" t="s">
+      <c r="C14" s="389" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="246"/>
-      <c r="E14" s="246"/>
-      <c r="F14" s="385">
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="404">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="246"/>
-      <c r="H14" s="256"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="258"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="370" t="s">
+      <c r="C15" s="389" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="246"/>
-      <c r="E15" s="246"/>
-      <c r="F15" s="366">
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="385">
         <v>36</v>
       </c>
-      <c r="G15" s="246"/>
-      <c r="H15" s="256"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="258"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="370" t="s">
+      <c r="C16" s="389" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="246"/>
-      <c r="E16" s="246"/>
-      <c r="F16" s="384">
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="403">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="246"/>
-      <c r="H16" s="256"/>
+      <c r="G16" s="248"/>
+      <c r="H16" s="258"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="370" t="s">
+      <c r="C17" s="389" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="246"/>
-      <c r="E17" s="246"/>
-      <c r="F17" s="367">
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="386">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="246"/>
-      <c r="H17" s="256"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="258"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="374" t="s">
+      <c r="C18" s="396" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="373">
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="392">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="241"/>
-      <c r="H18" s="242"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -10376,7 +10375,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AK58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -10410,37 +10409,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="386" t="s">
+      <c r="B2" s="405" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="387"/>
-      <c r="D2" s="387"/>
-      <c r="E2" s="387"/>
-      <c r="F2" s="387"/>
-      <c r="G2" s="387"/>
-      <c r="H2" s="387"/>
-      <c r="I2" s="387"/>
-      <c r="J2" s="387"/>
-      <c r="K2" s="387"/>
-      <c r="L2" s="387"/>
-      <c r="M2" s="387"/>
-      <c r="N2" s="387"/>
-      <c r="O2" s="387"/>
-      <c r="P2" s="387"/>
-      <c r="Q2" s="387"/>
-      <c r="R2" s="387"/>
-      <c r="S2" s="387"/>
-      <c r="T2" s="387"/>
-      <c r="U2" s="387"/>
-      <c r="V2" s="387"/>
-      <c r="W2" s="387"/>
-      <c r="X2" s="387"/>
-      <c r="Y2" s="387"/>
-      <c r="Z2" s="387"/>
-      <c r="AA2" s="387"/>
-      <c r="AB2" s="387"/>
-      <c r="AC2" s="387"/>
-      <c r="AD2" s="387"/>
+      <c r="C2" s="406"/>
+      <c r="D2" s="406"/>
+      <c r="E2" s="406"/>
+      <c r="F2" s="406"/>
+      <c r="G2" s="406"/>
+      <c r="H2" s="406"/>
+      <c r="I2" s="406"/>
+      <c r="J2" s="406"/>
+      <c r="K2" s="406"/>
+      <c r="L2" s="406"/>
+      <c r="M2" s="406"/>
+      <c r="N2" s="406"/>
+      <c r="O2" s="406"/>
+      <c r="P2" s="406"/>
+      <c r="Q2" s="406"/>
+      <c r="R2" s="406"/>
+      <c r="S2" s="406"/>
+      <c r="T2" s="406"/>
+      <c r="U2" s="406"/>
+      <c r="V2" s="406"/>
+      <c r="W2" s="406"/>
+      <c r="X2" s="406"/>
+      <c r="Y2" s="406"/>
+      <c r="Z2" s="406"/>
+      <c r="AA2" s="406"/>
+      <c r="AB2" s="406"/>
+      <c r="AC2" s="406"/>
+      <c r="AD2" s="406"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -10567,39 +10566,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="404">
+      <c r="B10" s="423">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="389"/>
-      <c r="D10" s="389"/>
-      <c r="E10" s="389"/>
-      <c r="F10" s="389"/>
-      <c r="G10" s="389"/>
+      <c r="C10" s="408"/>
+      <c r="D10" s="408"/>
+      <c r="E10" s="408"/>
+      <c r="F10" s="408"/>
+      <c r="G10" s="408"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="403">
+      <c r="I10" s="422">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="389"/>
-      <c r="K10" s="389"/>
-      <c r="L10" s="389"/>
-      <c r="M10" s="389"/>
-      <c r="N10" s="389"/>
-      <c r="O10" s="389"/>
-      <c r="P10" s="389"/>
+      <c r="J10" s="408"/>
+      <c r="K10" s="408"/>
+      <c r="L10" s="408"/>
+      <c r="M10" s="408"/>
+      <c r="N10" s="408"/>
+      <c r="O10" s="408"/>
+      <c r="P10" s="408"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="388">
+      <c r="R10" s="407">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="389"/>
-      <c r="T10" s="389"/>
-      <c r="U10" s="389"/>
+      <c r="S10" s="408"/>
+      <c r="T10" s="408"/>
+      <c r="U10" s="408"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -10634,13 +10633,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="388">
+      <c r="W11" s="407">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="389"/>
-      <c r="Y11" s="389"/>
-      <c r="Z11" s="389"/>
+      <c r="X11" s="408"/>
+      <c r="Y11" s="408"/>
+      <c r="Z11" s="408"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -10667,13 +10666,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="400">
+      <c r="R12" s="419">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="389"/>
-      <c r="T12" s="389"/>
-      <c r="U12" s="389"/>
+      <c r="S12" s="408"/>
+      <c r="T12" s="408"/>
+      <c r="U12" s="408"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -10693,10 +10692,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="393"/>
-      <c r="X14" s="389"/>
-      <c r="Y14" s="389"/>
-      <c r="Z14" s="389"/>
+      <c r="W14" s="412"/>
+      <c r="X14" s="408"/>
+      <c r="Y14" s="408"/>
+      <c r="Z14" s="408"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -10722,38 +10721,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="397" t="s">
+      <c r="B16" s="416" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="389"/>
-      <c r="D16" s="389"/>
-      <c r="E16" s="389"/>
-      <c r="F16" s="389"/>
-      <c r="G16" s="389"/>
+      <c r="C16" s="408"/>
+      <c r="D16" s="408"/>
+      <c r="E16" s="408"/>
+      <c r="F16" s="408"/>
+      <c r="G16" s="408"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="406" t="str">
+      <c r="I16" s="425" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="389"/>
-      <c r="K16" s="389"/>
-      <c r="L16" s="389"/>
-      <c r="M16" s="389"/>
-      <c r="N16" s="389"/>
-      <c r="O16" s="389"/>
-      <c r="P16" s="389"/>
+      <c r="J16" s="408"/>
+      <c r="K16" s="408"/>
+      <c r="L16" s="408"/>
+      <c r="M16" s="408"/>
+      <c r="N16" s="408"/>
+      <c r="O16" s="408"/>
+      <c r="P16" s="408"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="393" t="str">
+      <c r="R16" s="412" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="389"/>
-      <c r="T16" s="389"/>
-      <c r="U16" s="389"/>
+      <c r="S16" s="408"/>
+      <c r="T16" s="408"/>
+      <c r="U16" s="408"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -10765,10 +10764,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="393"/>
-      <c r="X17" s="389"/>
-      <c r="Y17" s="389"/>
-      <c r="Z17" s="389"/>
+      <c r="W17" s="412"/>
+      <c r="X17" s="408"/>
+      <c r="Y17" s="408"/>
+      <c r="Z17" s="408"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -10792,13 +10791,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="409" t="str">
+      <c r="R18" s="428" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="389"/>
-      <c r="T18" s="389"/>
-      <c r="U18" s="389"/>
+      <c r="S18" s="408"/>
+      <c r="T18" s="408"/>
+      <c r="U18" s="408"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -10880,13 +10879,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="401">
+      <c r="W22" s="420">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="396"/>
-      <c r="Y22" s="396"/>
-      <c r="Z22" s="396"/>
+      <c r="X22" s="415"/>
+      <c r="Y22" s="415"/>
+      <c r="Z22" s="415"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -10895,13 +10894,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="395" t="str">
+      <c r="W23" s="414" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="396"/>
-      <c r="Y23" s="396"/>
-      <c r="Z23" s="396"/>
+      <c r="X23" s="415"/>
+      <c r="Y23" s="415"/>
+      <c r="Z23" s="415"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -10910,13 +10909,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="390">
+      <c r="W24" s="409">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="391"/>
-      <c r="Y24" s="391"/>
-      <c r="Z24" s="391"/>
+      <c r="X24" s="410"/>
+      <c r="Y24" s="410"/>
+      <c r="Z24" s="410"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -10925,13 +10924,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="395">
+      <c r="W25" s="414">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="396"/>
-      <c r="Y25" s="396"/>
-      <c r="Z25" s="396"/>
+      <c r="X25" s="415"/>
+      <c r="Y25" s="415"/>
+      <c r="Z25" s="415"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -10940,13 +10939,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="395">
+      <c r="W26" s="414">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="396"/>
-      <c r="Y26" s="396"/>
-      <c r="Z26" s="396"/>
+      <c r="X26" s="415"/>
+      <c r="Y26" s="415"/>
+      <c r="Z26" s="415"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -10955,13 +10954,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="395">
+      <c r="W27" s="414">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="396"/>
-      <c r="Y27" s="396"/>
-      <c r="Z27" s="396"/>
+      <c r="X27" s="415"/>
+      <c r="Y27" s="415"/>
+      <c r="Z27" s="415"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -10970,13 +10969,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="395">
+      <c r="W28" s="414">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="396"/>
-      <c r="Y28" s="396"/>
-      <c r="Z28" s="396"/>
+      <c r="X28" s="415"/>
+      <c r="Y28" s="415"/>
+      <c r="Z28" s="415"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -10985,13 +10984,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="395">
+      <c r="W29" s="414">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="396"/>
-      <c r="Y29" s="396"/>
-      <c r="Z29" s="396"/>
+      <c r="X29" s="415"/>
+      <c r="Y29" s="415"/>
+      <c r="Z29" s="415"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -11000,13 +10999,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="394">
+      <c r="W30" s="413">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="391"/>
-      <c r="Y30" s="391"/>
-      <c r="Z30" s="391"/>
+      <c r="X30" s="410"/>
+      <c r="Y30" s="410"/>
+      <c r="Z30" s="410"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -11016,83 +11015,83 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="399">
+      <c r="W31" s="418">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="391"/>
-      <c r="Y31" s="391"/>
-      <c r="Z31" s="391"/>
+      <c r="X31" s="410"/>
+      <c r="Y31" s="410"/>
+      <c r="Z31" s="410"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="398">
+      <c r="K32" s="417">
         <v>43009</v>
       </c>
-      <c r="L32" s="396"/>
-      <c r="M32" s="396"/>
-      <c r="N32" s="396"/>
-      <c r="O32" s="396"/>
-      <c r="P32" s="396"/>
-      <c r="Q32" s="396"/>
-      <c r="R32" s="396"/>
-      <c r="S32" s="396"/>
-      <c r="T32" s="396"/>
-      <c r="U32" s="396"/>
-      <c r="V32" s="396"/>
-      <c r="W32" s="396"/>
-      <c r="X32" s="396"/>
-      <c r="Y32" s="396"/>
-      <c r="Z32" s="396"/>
+      <c r="L32" s="415"/>
+      <c r="M32" s="415"/>
+      <c r="N32" s="415"/>
+      <c r="O32" s="415"/>
+      <c r="P32" s="415"/>
+      <c r="Q32" s="415"/>
+      <c r="R32" s="415"/>
+      <c r="S32" s="415"/>
+      <c r="T32" s="415"/>
+      <c r="U32" s="415"/>
+      <c r="V32" s="415"/>
+      <c r="W32" s="415"/>
+      <c r="X32" s="415"/>
+      <c r="Y32" s="415"/>
+      <c r="Z32" s="415"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="410" t="s">
+      <c r="O33" s="429" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="391"/>
-      <c r="Q33" s="391"/>
-      <c r="R33" s="391"/>
-      <c r="S33" s="391"/>
-      <c r="T33" s="391"/>
-      <c r="U33" s="391"/>
-      <c r="V33" s="391"/>
-      <c r="W33" s="411" t="s">
+      <c r="P33" s="410"/>
+      <c r="Q33" s="410"/>
+      <c r="R33" s="410"/>
+      <c r="S33" s="410"/>
+      <c r="T33" s="410"/>
+      <c r="U33" s="410"/>
+      <c r="V33" s="410"/>
+      <c r="W33" s="430" t="s">
         <v>256</v>
       </c>
-      <c r="X33" s="305"/>
-      <c r="Y33" s="305"/>
-      <c r="Z33" s="305"/>
-      <c r="AA33" s="305"/>
-      <c r="AB33" s="305"/>
-      <c r="AC33" s="305"/>
-      <c r="AD33" s="305"/>
+      <c r="X33" s="321"/>
+      <c r="Y33" s="321"/>
+      <c r="Z33" s="321"/>
+      <c r="AA33" s="321"/>
+      <c r="AB33" s="321"/>
+      <c r="AC33" s="321"/>
+      <c r="AD33" s="321"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="402">
+      <c r="Q34" s="421">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="396"/>
-      <c r="S34" s="396"/>
-      <c r="T34" s="396"/>
+      <c r="R34" s="415"/>
+      <c r="S34" s="415"/>
+      <c r="T34" s="415"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="402">
+      <c r="Y34" s="421">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="396"/>
-      <c r="AA34" s="396"/>
-      <c r="AB34" s="396"/>
+      <c r="Z34" s="415"/>
+      <c r="AA34" s="415"/>
+      <c r="AB34" s="415"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -11155,32 +11154,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="392"/>
-      <c r="C38" s="389"/>
+      <c r="B38" s="411"/>
+      <c r="C38" s="408"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="392"/>
-      <c r="C39" s="389"/>
+      <c r="B39" s="411"/>
+      <c r="C39" s="408"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="392"/>
-      <c r="C40" s="389"/>
+      <c r="B40" s="411"/>
+      <c r="C40" s="408"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="392"/>
-      <c r="C41" s="389"/>
+      <c r="B41" s="411"/>
+      <c r="C41" s="408"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="392"/>
-      <c r="C42" s="389"/>
+      <c r="B42" s="411"/>
+      <c r="C42" s="408"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="392"/>
-      <c r="C43" s="389"/>
+      <c r="B43" s="411"/>
+      <c r="C43" s="408"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="392"/>
-      <c r="C44" s="389"/>
+      <c r="B44" s="411"/>
+      <c r="C44" s="408"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -11251,10 +11250,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="408"/>
-      <c r="F49" s="389"/>
-      <c r="G49" s="389"/>
-      <c r="H49" s="389"/>
+      <c r="E49" s="427"/>
+      <c r="F49" s="408"/>
+      <c r="G49" s="408"/>
+      <c r="H49" s="408"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -11277,40 +11276,40 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="405"/>
-      <c r="I52" s="305"/>
-      <c r="J52" s="305"/>
-      <c r="K52" s="305"/>
-      <c r="L52" s="305"/>
-      <c r="M52" s="305"/>
-      <c r="N52" s="305"/>
-      <c r="O52" s="305"/>
-      <c r="P52" s="305"/>
+      <c r="H52" s="424"/>
+      <c r="I52" s="321"/>
+      <c r="J52" s="321"/>
+      <c r="K52" s="321"/>
+      <c r="L52" s="321"/>
+      <c r="M52" s="321"/>
+      <c r="N52" s="321"/>
+      <c r="O52" s="321"/>
+      <c r="P52" s="321"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="407"/>
-      <c r="I55" s="305"/>
-      <c r="J55" s="305"/>
-      <c r="K55" s="305"/>
-      <c r="L55" s="305"/>
-      <c r="M55" s="305"/>
-      <c r="N55" s="305"/>
-      <c r="O55" s="305"/>
-      <c r="P55" s="305"/>
+      <c r="H55" s="426"/>
+      <c r="I55" s="321"/>
+      <c r="J55" s="321"/>
+      <c r="K55" s="321"/>
+      <c r="L55" s="321"/>
+      <c r="M55" s="321"/>
+      <c r="N55" s="321"/>
+      <c r="O55" s="321"/>
+      <c r="P55" s="321"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="405"/>
-      <c r="I57" s="305"/>
-      <c r="J57" s="305"/>
-      <c r="K57" s="305"/>
-      <c r="L57" s="305"/>
-      <c r="M57" s="305"/>
-      <c r="N57" s="305"/>
-      <c r="O57" s="305"/>
-      <c r="P57" s="305"/>
+      <c r="H57" s="424"/>
+      <c r="I57" s="321"/>
+      <c r="J57" s="321"/>
+      <c r="K57" s="321"/>
+      <c r="L57" s="321"/>
+      <c r="M57" s="321"/>
+      <c r="N57" s="321"/>
+      <c r="O57" s="321"/>
+      <c r="P57" s="321"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -2179,7 +2179,7 @@
     <xf numFmtId="9" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="462">
+  <cellXfs count="464">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2924,62 +2924,59 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="46" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3093,20 +3090,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3126,13 +3123,13 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3218,6 +3215,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3247,9 +3247,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3409,6 +3406,11 @@
     <xf numFmtId="0" fontId="61" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="56" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hiperlink" xfId="4" builtinId="8"/>
@@ -4579,24 +4581,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="437" t="s">
+      <c r="B1" s="436" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="438"/>
-      <c r="D1" s="438"/>
-      <c r="E1" s="438"/>
-      <c r="F1" s="438"/>
-      <c r="G1" s="438"/>
-      <c r="H1" s="439"/>
+      <c r="C1" s="437"/>
+      <c r="D1" s="437"/>
+      <c r="E1" s="437"/>
+      <c r="F1" s="437"/>
+      <c r="G1" s="437"/>
+      <c r="H1" s="438"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="433"/>
-      <c r="C2" s="434"/>
-      <c r="D2" s="434"/>
-      <c r="E2" s="434"/>
-      <c r="F2" s="434"/>
-      <c r="G2" s="434"/>
-      <c r="H2" s="435"/>
+      <c r="B2" s="432"/>
+      <c r="C2" s="433"/>
+      <c r="D2" s="433"/>
+      <c r="E2" s="433"/>
+      <c r="F2" s="433"/>
+      <c r="G2" s="433"/>
+      <c r="H2" s="434"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -4631,30 +4633,30 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="442" t="s">
+      <c r="B6" s="441" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="444" t="s">
+      <c r="C6" s="443" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="446" t="s">
+      <c r="D6" s="445" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="447" t="s">
+      <c r="E6" s="446" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="447" t="s">
+      <c r="F6" s="446" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="440" t="s">
+      <c r="G6" s="439" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="441"/>
+      <c r="H6" s="440"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="443"/>
-      <c r="C7" s="445"/>
-      <c r="D7" s="445"/>
+      <c r="B7" s="442"/>
+      <c r="C7" s="444"/>
+      <c r="D7" s="444"/>
       <c r="E7" s="254"/>
       <c r="F7" s="254"/>
       <c r="G7" s="47" t="s">
@@ -4677,7 +4679,7 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="448" t="s">
+      <c r="B9" s="447" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="243"/>
@@ -4702,30 +4704,30 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="442" t="s">
+      <c r="B11" s="441" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="444" t="s">
+      <c r="C11" s="443" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="446" t="s">
+      <c r="D11" s="445" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="436" t="s">
+      <c r="E11" s="435" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="436" t="s">
+      <c r="F11" s="435" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="440" t="s">
+      <c r="G11" s="439" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="441"/>
+      <c r="H11" s="440"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="443"/>
-      <c r="C12" s="445"/>
-      <c r="D12" s="445"/>
+      <c r="B12" s="442"/>
+      <c r="C12" s="444"/>
+      <c r="D12" s="444"/>
       <c r="E12" s="254"/>
       <c r="F12" s="254"/>
       <c r="G12" s="47" t="s">
@@ -4748,7 +4750,7 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="448" t="s">
+      <c r="B14" s="447" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="243"/>
@@ -4773,30 +4775,30 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="442" t="s">
+      <c r="B16" s="441" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="444" t="s">
+      <c r="C16" s="443" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="446" t="s">
+      <c r="D16" s="445" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="436" t="s">
+      <c r="E16" s="435" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="436" t="s">
+      <c r="F16" s="435" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="440" t="s">
+      <c r="G16" s="439" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="441"/>
+      <c r="H16" s="440"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="443"/>
-      <c r="C17" s="445"/>
-      <c r="D17" s="445"/>
+      <c r="B17" s="442"/>
+      <c r="C17" s="444"/>
+      <c r="D17" s="444"/>
       <c r="E17" s="254"/>
       <c r="F17" s="254"/>
       <c r="G17" s="22" t="s">
@@ -4821,7 +4823,7 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="448" t="s">
+      <c r="B19" s="447" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="243"/>
@@ -4846,30 +4848,30 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="442" t="s">
+      <c r="B21" s="441" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="444" t="s">
+      <c r="C21" s="443" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="446" t="s">
+      <c r="D21" s="445" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="436" t="s">
+      <c r="E21" s="435" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="436" t="s">
+      <c r="F21" s="435" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="440" t="s">
+      <c r="G21" s="439" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="441"/>
+      <c r="H21" s="440"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="443"/>
-      <c r="C22" s="445"/>
-      <c r="D22" s="445"/>
+      <c r="B22" s="442"/>
+      <c r="C22" s="444"/>
+      <c r="D22" s="444"/>
       <c r="E22" s="254"/>
       <c r="F22" s="254"/>
       <c r="G22" s="47" t="s">
@@ -4892,14 +4894,14 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="431" t="s">
+      <c r="B24" s="430" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="432"/>
-      <c r="D24" s="432"/>
-      <c r="E24" s="432"/>
-      <c r="F24" s="432"/>
-      <c r="G24" s="381"/>
+      <c r="C24" s="431"/>
+      <c r="D24" s="431"/>
+      <c r="E24" s="431"/>
+      <c r="F24" s="431"/>
+      <c r="G24" s="380"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
@@ -4959,14 +4961,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="451" t="s">
+      <c r="B1" s="450" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="434"/>
-      <c r="D1" s="434"/>
-      <c r="E1" s="434"/>
-      <c r="F1" s="434"/>
-      <c r="G1" s="434"/>
+      <c r="C1" s="433"/>
+      <c r="D1" s="433"/>
+      <c r="E1" s="433"/>
+      <c r="F1" s="433"/>
+      <c r="G1" s="433"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -4990,7 +4992,7 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="452" t="s">
+      <c r="B4" s="451" t="s">
         <v>272</v>
       </c>
       <c r="C4" s="243"/>
@@ -5001,19 +5003,19 @@
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="453" t="s">
+      <c r="B5" s="452" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="449" t="s">
+      <c r="C5" s="448" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="449" t="s">
+      <c r="D5" s="448" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="449" t="s">
+      <c r="E5" s="448" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="450" t="s">
+      <c r="F5" s="449" t="s">
         <v>277</v>
       </c>
       <c r="G5" s="243"/>
@@ -5021,9 +5023,9 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="254"/>
-      <c r="C6" s="445"/>
-      <c r="D6" s="445"/>
-      <c r="E6" s="445"/>
+      <c r="C6" s="444"/>
+      <c r="D6" s="444"/>
+      <c r="E6" s="444"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -5075,7 +5077,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="461" t="s">
+      <c r="A1" s="460" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="248"/>
@@ -5091,18 +5093,18 @@
       <c r="L1" s="248"/>
       <c r="M1" s="248"/>
       <c r="N1" s="248"/>
-      <c r="O1" s="454"/>
+      <c r="O1" s="453"/>
       <c r="P1" s="248"/>
       <c r="Q1" s="248"/>
       <c r="R1" s="248"/>
       <c r="S1" s="248"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="459" t="s">
+      <c r="A2" s="458" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="248"/>
-      <c r="C2" s="459" t="s">
+      <c r="C2" s="458" t="s">
         <v>278</v>
       </c>
       <c r="D2" s="248"/>
@@ -5111,7 +5113,7 @@
       <c r="G2" s="248"/>
       <c r="H2" s="248"/>
       <c r="I2" s="248"/>
-      <c r="J2" s="460" t="s">
+      <c r="J2" s="459" t="s">
         <v>279</v>
       </c>
       <c r="K2" s="248"/>
@@ -5120,11 +5122,11 @@
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="456" t="s">
+      <c r="A3" s="455" t="s">
         <v>280</v>
       </c>
       <c r="B3" s="248"/>
-      <c r="C3" s="456" t="s">
+      <c r="C3" s="455" t="s">
         <v>278</v>
       </c>
       <c r="D3" s="248"/>
@@ -5133,7 +5135,7 @@
       <c r="G3" s="248"/>
       <c r="H3" s="248"/>
       <c r="I3" s="248"/>
-      <c r="J3" s="456" t="s">
+      <c r="J3" s="455" t="s">
         <v>281</v>
       </c>
       <c r="K3" s="248"/>
@@ -5142,11 +5144,11 @@
       <c r="N3" s="248"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="456" t="s">
+      <c r="A4" s="455" t="s">
         <v>282</v>
       </c>
       <c r="B4" s="248"/>
-      <c r="C4" s="456" t="s">
+      <c r="C4" s="455" t="s">
         <v>283</v>
       </c>
       <c r="D4" s="248"/>
@@ -5155,18 +5157,18 @@
       <c r="G4" s="248"/>
       <c r="H4" s="248"/>
       <c r="I4" s="248"/>
-      <c r="J4" s="458"/>
+      <c r="J4" s="457"/>
       <c r="K4" s="248"/>
       <c r="L4" s="248"/>
       <c r="M4" s="248"/>
       <c r="N4" s="248"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="456" t="s">
+      <c r="A5" s="455" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="248"/>
-      <c r="C5" s="456" t="s">
+      <c r="C5" s="455" t="s">
         <v>284</v>
       </c>
       <c r="D5" s="248"/>
@@ -5175,18 +5177,18 @@
       <c r="G5" s="248"/>
       <c r="H5" s="248"/>
       <c r="I5" s="248"/>
-      <c r="J5" s="458"/>
+      <c r="J5" s="457"/>
       <c r="K5" s="248"/>
       <c r="L5" s="248"/>
       <c r="M5" s="248"/>
       <c r="N5" s="248"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="456" t="s">
+      <c r="A6" s="455" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="248"/>
-      <c r="C6" s="456" t="s">
+      <c r="C6" s="455" t="s">
         <v>285</v>
       </c>
       <c r="D6" s="248"/>
@@ -5195,7 +5197,7 @@
       <c r="G6" s="248"/>
       <c r="H6" s="248"/>
       <c r="I6" s="248"/>
-      <c r="J6" s="456" t="s">
+      <c r="J6" s="455" t="s">
         <v>286</v>
       </c>
       <c r="K6" s="248"/>
@@ -5204,7 +5206,7 @@
       <c r="N6" s="248"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="455" t="s">
+      <c r="A7" s="454" t="s">
         <v>287</v>
       </c>
       <c r="B7" s="248"/>
@@ -5245,7 +5247,7 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="455" t="s">
+      <c r="A31" s="454" t="s">
         <v>288</v>
       </c>
       <c r="B31" s="248"/>
@@ -5263,22 +5265,22 @@
       <c r="N31" s="248"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="457" t="s">
+      <c r="A32" s="456" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="248"/>
       <c r="C32" s="248"/>
-      <c r="D32" s="457" t="s">
+      <c r="D32" s="456" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="248"/>
       <c r="F32" s="248"/>
-      <c r="G32" s="457" t="s">
+      <c r="G32" s="456" t="s">
         <v>289</v>
       </c>
       <c r="H32" s="248"/>
       <c r="I32" s="248"/>
-      <c r="J32" s="457" t="s">
+      <c r="J32" s="456" t="s">
         <v>14</v>
       </c>
       <c r="K32" s="248"/>
@@ -5286,22 +5288,22 @@
       <c r="M32" s="248"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="457" t="s">
+      <c r="A33" s="456" t="s">
         <v>290</v>
       </c>
       <c r="B33" s="248"/>
       <c r="C33" s="248"/>
-      <c r="D33" s="457" t="s">
+      <c r="D33" s="456" t="s">
         <v>291</v>
       </c>
       <c r="E33" s="248"/>
       <c r="F33" s="248"/>
-      <c r="G33" s="457" t="s">
+      <c r="G33" s="456" t="s">
         <v>292</v>
       </c>
       <c r="H33" s="248"/>
       <c r="I33" s="248"/>
-      <c r="J33" s="457" t="s">
+      <c r="J33" s="456" t="s">
         <v>293</v>
       </c>
       <c r="K33" s="248"/>
@@ -5309,7 +5311,7 @@
       <c r="M33" s="248"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="455" t="s">
+      <c r="A34" s="454" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="248"/>
@@ -5327,34 +5329,34 @@
       <c r="N34" s="248"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="457" t="s">
+      <c r="A35" s="456" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="248"/>
       <c r="C35" s="248"/>
-      <c r="F35" s="457" t="s">
+      <c r="F35" s="456" t="s">
         <v>294</v>
       </c>
       <c r="G35" s="248"/>
       <c r="H35" s="248"/>
-      <c r="K35" s="457" t="s">
+      <c r="K35" s="456" t="s">
         <v>295</v>
       </c>
       <c r="L35" s="248"/>
       <c r="M35" s="248"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="457" t="s">
+      <c r="A36" s="456" t="s">
         <v>290</v>
       </c>
       <c r="B36" s="248"/>
       <c r="C36" s="248"/>
-      <c r="F36" s="457" t="s">
+      <c r="F36" s="456" t="s">
         <v>296</v>
       </c>
       <c r="G36" s="248"/>
       <c r="H36" s="248"/>
-      <c r="K36" s="457" t="s">
+      <c r="K36" s="456" t="s">
         <v>297</v>
       </c>
       <c r="L36" s="248"/>
@@ -5728,19 +5730,19 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="293" t="s">
+      <c r="C5" s="295" t="s">
         <v>61</v>
       </c>
       <c r="D5" s="254"/>
-      <c r="E5" s="293" t="s">
+      <c r="E5" s="295" t="s">
         <v>62</v>
       </c>
       <c r="F5" s="254"/>
-      <c r="G5" s="293" t="s">
+      <c r="G5" s="295" t="s">
         <v>63</v>
       </c>
       <c r="H5" s="254"/>
-      <c r="I5" s="297" t="s">
+      <c r="I5" s="293" t="s">
         <v>64</v>
       </c>
       <c r="J5" s="254"/>
@@ -5770,7 +5772,7 @@
         <v>67</v>
       </c>
       <c r="H6" s="244"/>
-      <c r="I6" s="300" t="s">
+      <c r="I6" s="297" t="s">
         <v>67</v>
       </c>
       <c r="J6" s="244"/>
@@ -5858,7 +5860,7 @@
         <v>80</v>
       </c>
       <c r="H9" s="244"/>
-      <c r="I9" s="300">
+      <c r="I9" s="297">
         <v>0.65039999999999998</v>
       </c>
       <c r="J9" s="244"/>
@@ -5942,21 +5944,21 @@
         <v>77</v>
       </c>
       <c r="H13" s="244"/>
-      <c r="I13" s="300" t="s">
+      <c r="I13" s="297" t="s">
         <v>78</v>
       </c>
       <c r="J13" s="244"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="461" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
-      <c r="F16" s="243"/>
-      <c r="G16" s="243"/>
-      <c r="H16" s="243"/>
-      <c r="I16" s="244"/>
+      <c r="D16" s="462"/>
+      <c r="E16" s="462"/>
+      <c r="F16" s="462"/>
+      <c r="G16" s="462"/>
+      <c r="H16" s="462"/>
+      <c r="I16" s="463"/>
     </row>
     <row r="17" spans="3:10">
       <c r="C17" s="281" t="s">
@@ -5974,24 +5976,24 @@
       <c r="I17" s="244"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="306" t="s">
+      <c r="C18" s="303" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="307"/>
-      <c r="E18" s="308"/>
-      <c r="F18" s="291">
+      <c r="D18" s="304"/>
+      <c r="E18" s="305"/>
+      <c r="F18" s="307">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="292"/>
-      <c r="H18" s="295">
+      <c r="G18" s="308"/>
+      <c r="H18" s="291">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="296"/>
+      <c r="I18" s="292"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="309" t="s">
+      <c r="C19" s="306" t="s">
         <v>301</v>
       </c>
       <c r="D19" s="243"/>
@@ -6001,7 +6003,7 @@
         <v>24.851099999999999</v>
       </c>
       <c r="G19" s="244"/>
-      <c r="H19" s="299">
+      <c r="H19" s="296">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
@@ -6013,19 +6015,19 @@
       </c>
       <c r="D20" s="289"/>
       <c r="E20" s="290"/>
-      <c r="F20" s="304">
+      <c r="F20" s="301">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="305"/>
-      <c r="H20" s="302">
+      <c r="G20" s="302"/>
+      <c r="H20" s="299">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="303"/>
+      <c r="I20" s="300"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="301" t="s">
+      <c r="C21" s="298" t="s">
         <v>83</v>
       </c>
       <c r="D21" s="243"/>
@@ -6035,7 +6037,7 @@
         <v>52.034300000000002</v>
       </c>
       <c r="G21" s="244"/>
-      <c r="H21" s="299">
+      <c r="H21" s="296">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
@@ -6044,7 +6046,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="I6:J6"/>
@@ -6060,6 +6061,13 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="E5:F5"/>
@@ -6068,13 +6076,7 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="F21:G21"/>
@@ -6093,7 +6095,7 @@
     <mergeCell ref="C20:E20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6118,7 +6120,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="328" t="s">
+      <c r="B3" s="327" t="s">
         <v>84</v>
       </c>
       <c r="C3" s="279"/>
@@ -6128,25 +6130,25 @@
       <c r="G3" s="279"/>
       <c r="H3" s="279"/>
       <c r="I3" s="279"/>
-      <c r="L3" s="371" t="s">
+      <c r="L3" s="370" t="s">
         <v>85</v>
       </c>
       <c r="M3" s="244"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="320" t="s">
+      <c r="B4" s="319" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="321"/>
-      <c r="D4" s="321"/>
-      <c r="E4" s="373" t="s">
+      <c r="C4" s="320"/>
+      <c r="D4" s="320"/>
+      <c r="E4" s="372" t="s">
         <v>298</v>
       </c>
       <c r="F4" s="279"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="341" t="s">
+      <c r="H4" s="340" t="s">
         <v>299</v>
       </c>
       <c r="I4" s="258"/>
@@ -6160,19 +6162,19 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="318" t="s">
+      <c r="B5" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="279"/>
       <c r="D5" s="279"/>
-      <c r="E5" s="335" t="s">
+      <c r="E5" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F5" s="279"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="341" t="s">
+      <c r="H5" s="340" t="s">
         <v>49</v>
       </c>
       <c r="I5" s="258"/>
@@ -6185,56 +6187,56 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="318" t="s">
+      <c r="B6" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="279"/>
       <c r="D6" s="279"/>
-      <c r="E6" s="351">
+      <c r="E6" s="359">
         <v>52.034300000000002</v>
       </c>
       <c r="F6" s="279"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="346" t="s">
+      <c r="H6" s="345" t="s">
         <v>300</v>
       </c>
       <c r="I6" s="258"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="334" t="s">
+      <c r="C7" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="279"/>
-      <c r="E7" s="353" t="s">
+      <c r="E7" s="352" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="279"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="317">
+      <c r="H7" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I7" s="258"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="334" t="s">
+      <c r="C8" s="333" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="279"/>
-      <c r="E8" s="360">
+      <c r="E8" s="358">
         <v>11173</v>
       </c>
       <c r="F8" s="279"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="336"/>
+      <c r="H8" s="335"/>
       <c r="I8" s="258"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
@@ -6243,7 +6245,7 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="324" t="s">
+      <c r="B9" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="279"/>
@@ -6260,7 +6262,7 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="333" t="s">
+      <c r="B10" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="279"/>
@@ -6271,7 +6273,7 @@
       <c r="F10" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="325" t="s">
+      <c r="G10" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H10" s="279"/>
@@ -6283,11 +6285,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="368" t="s">
+      <c r="B11" s="367" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="369"/>
-      <c r="D11" s="369"/>
+      <c r="C11" s="368"/>
+      <c r="D11" s="368"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -6295,10 +6297,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="370">
+      <c r="G11" s="369">
         <v>1</v>
       </c>
-      <c r="H11" s="370"/>
+      <c r="H11" s="369"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -6307,7 +6309,7 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="359" t="s">
+      <c r="B12" s="357" t="s">
         <v>117</v>
       </c>
       <c r="C12" s="279"/>
@@ -6320,7 +6322,7 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="314">
+      <c r="G12" s="313">
         <v>0.8</v>
       </c>
       <c r="H12" s="279"/>
@@ -6332,7 +6334,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="354" t="s">
+      <c r="B13" s="353" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="279"/>
@@ -6345,7 +6347,7 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="314">
+      <c r="G13" s="313">
         <v>0.6</v>
       </c>
       <c r="H13" s="279"/>
@@ -6361,7 +6363,7 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="319" t="s">
+      <c r="B14" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="246"/>
@@ -6374,7 +6376,7 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="310">
+      <c r="G14" s="309">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
@@ -6402,7 +6404,7 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="328" t="s">
+      <c r="B16" s="327" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="279"/>
@@ -6415,19 +6417,19 @@
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="320" t="s">
+      <c r="B17" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="321"/>
-      <c r="D17" s="321"/>
-      <c r="E17" s="312" t="s">
+      <c r="C17" s="320"/>
+      <c r="D17" s="320"/>
+      <c r="E17" s="311" t="s">
         <v>110</v>
       </c>
       <c r="F17" s="279"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="342" t="s">
+      <c r="H17" s="341" t="s">
         <v>111</v>
       </c>
       <c r="I17" s="258"/>
@@ -6436,31 +6438,31 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="318" t="s">
+      <c r="B18" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="279"/>
       <c r="D18" s="279"/>
-      <c r="E18" s="335" t="s">
+      <c r="E18" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="279"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="345" t="s">
+      <c r="H18" s="344" t="s">
         <v>49</v>
       </c>
       <c r="I18" s="258"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="318" t="s">
+      <c r="B19" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C19" s="279"/>
       <c r="D19" s="279"/>
-      <c r="E19" s="352">
+      <c r="E19" s="351">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
@@ -6468,18 +6470,18 @@
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="315" t="s">
+      <c r="H19" s="314" t="s">
         <v>95</v>
       </c>
       <c r="I19" s="258"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="334" t="s">
+      <c r="C20" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D20" s="279"/>
-      <c r="E20" s="340">
+      <c r="E20" s="339">
         <f>180000000</f>
         <v>180000000</v>
       </c>
@@ -6487,7 +6489,7 @@
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="316">
+      <c r="H20" s="315">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
@@ -6499,42 +6501,42 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="334" t="s">
+      <c r="C21" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="279"/>
-      <c r="E21" s="356" t="s">
+      <c r="E21" s="355" t="s">
         <v>116</v>
       </c>
       <c r="F21" s="279"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="317">
+      <c r="H21" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I21" s="258"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="334" t="s">
+      <c r="C22" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="279"/>
-      <c r="E22" s="312" t="s">
+      <c r="E22" s="311" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="279"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="348"/>
+      <c r="H22" s="346"/>
       <c r="I22" s="258"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="324" t="s">
+      <c r="B23" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="279"/>
@@ -6546,7 +6548,7 @@
       <c r="I23" s="258"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="333" t="s">
+      <c r="B24" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="279"/>
@@ -6557,14 +6559,14 @@
       <c r="F24" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="325" t="s">
+      <c r="G24" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H24" s="279"/>
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="322" t="s">
+      <c r="B25" s="321" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="279"/>
@@ -6577,7 +6579,7 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="323">
+      <c r="G25" s="322">
         <v>1</v>
       </c>
       <c r="H25" s="279"/>
@@ -6597,14 +6599,14 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="323">
+      <c r="G26" s="322">
         <v>0.8</v>
       </c>
       <c r="H26" s="279"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="347" t="s">
+      <c r="B27" s="348" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="279"/>
@@ -6617,14 +6619,14 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="323">
+      <c r="G27" s="322">
         <v>0.6</v>
       </c>
       <c r="H27" s="279"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="319" t="s">
+      <c r="B28" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="246"/>
@@ -6637,7 +6639,7 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="310">
+      <c r="G28" s="309">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
@@ -6655,7 +6657,7 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="328" t="s">
+      <c r="B30" s="327" t="s">
         <v>118</v>
       </c>
       <c r="C30" s="279"/>
@@ -6667,19 +6669,19 @@
       <c r="I30" s="279"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="320" t="s">
+      <c r="B31" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="321"/>
-      <c r="D31" s="321"/>
-      <c r="E31" s="312" t="s">
+      <c r="C31" s="320"/>
+      <c r="D31" s="320"/>
+      <c r="E31" s="311" t="s">
         <v>119</v>
       </c>
       <c r="F31" s="279"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="342" t="s">
+      <c r="H31" s="341" t="s">
         <v>120</v>
       </c>
       <c r="I31" s="258"/>
@@ -6689,38 +6691,38 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="318" t="s">
+      <c r="B32" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="279"/>
       <c r="D32" s="279"/>
-      <c r="E32" s="335" t="s">
+      <c r="E32" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F32" s="279"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="345" t="s">
+      <c r="H32" s="344" t="s">
         <v>44</v>
       </c>
       <c r="I32" s="258"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="318" t="s">
+      <c r="B33" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="279"/>
       <c r="D33" s="279"/>
-      <c r="E33" s="343">
+      <c r="E33" s="342">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="279"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="345" t="s">
+      <c r="H33" s="344" t="s">
         <v>95</v>
       </c>
       <c r="I33" s="258"/>
@@ -6728,18 +6730,18 @@
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="334" t="s">
+      <c r="C34" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="279"/>
-      <c r="E34" s="340">
+      <c r="E34" s="339">
         <v>16900000</v>
       </c>
       <c r="F34" s="279"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="316">
+      <c r="H34" s="315">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
@@ -6751,41 +6753,41 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="334" t="s">
+      <c r="C35" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D35" s="279"/>
-      <c r="E35" s="356" t="s">
+      <c r="E35" s="355" t="s">
         <v>116</v>
       </c>
       <c r="F35" s="279"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="317">
+      <c r="H35" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I35" s="258"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="334" t="s">
+      <c r="C36" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="279"/>
-      <c r="E36" s="312" t="s">
+      <c r="E36" s="311" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="279"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="348"/>
+      <c r="H36" s="346"/>
       <c r="I36" s="258"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="324" t="s">
+      <c r="B37" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="279"/>
@@ -6798,7 +6800,7 @@
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="333" t="s">
+      <c r="B38" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C38" s="279"/>
@@ -6809,14 +6811,14 @@
       <c r="F38" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="325" t="s">
+      <c r="G38" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="279"/>
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="322" t="s">
+      <c r="B39" s="321" t="s">
         <v>106</v>
       </c>
       <c r="C39" s="279"/>
@@ -6828,7 +6830,7 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="322">
         <v>1</v>
       </c>
       <c r="H39" s="279"/>
@@ -6848,14 +6850,14 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="323">
+      <c r="G40" s="322">
         <v>0.8</v>
       </c>
       <c r="H40" s="279"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="347" t="s">
+      <c r="B41" s="348" t="s">
         <v>107</v>
       </c>
       <c r="C41" s="279"/>
@@ -6868,14 +6870,14 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="323">
+      <c r="G41" s="322">
         <v>0.6</v>
       </c>
       <c r="H41" s="279"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="319" t="s">
+      <c r="B42" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C42" s="246"/>
@@ -6888,7 +6890,7 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="310">
+      <c r="G42" s="309">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
@@ -6906,7 +6908,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="343" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="279"/>
@@ -6918,19 +6920,19 @@
       <c r="I44" s="279"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="320" t="s">
+      <c r="B45" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="321"/>
-      <c r="D45" s="321"/>
-      <c r="E45" s="335" t="s">
+      <c r="C45" s="320"/>
+      <c r="D45" s="320"/>
+      <c r="E45" s="334" t="s">
         <v>119</v>
       </c>
       <c r="F45" s="279"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="342" t="s">
+      <c r="H45" s="341" t="s">
         <v>120</v>
       </c>
       <c r="I45" s="258"/>
@@ -6939,37 +6941,37 @@
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="318" t="s">
+      <c r="B46" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="279"/>
       <c r="D46" s="279"/>
-      <c r="E46" s="335" t="s">
+      <c r="E46" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F46" s="279"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="345" t="s">
+      <c r="H46" s="344" t="s">
         <v>49</v>
       </c>
       <c r="I46" s="258"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="318" t="s">
+      <c r="B47" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C47" s="279"/>
       <c r="D47" s="279"/>
-      <c r="E47" s="352">
+      <c r="E47" s="351">
         <v>430.76</v>
       </c>
       <c r="F47" s="279"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="315" t="s">
+      <c r="H47" s="314" t="s">
         <v>95</v>
       </c>
       <c r="I47" s="258"/>
@@ -6977,18 +6979,18 @@
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="334" t="s">
+      <c r="C48" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D48" s="279"/>
-      <c r="E48" s="311">
+      <c r="E48" s="310">
         <v>7120000</v>
       </c>
       <c r="F48" s="279"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="331">
+      <c r="H48" s="330">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
@@ -7001,42 +7003,42 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="334" t="s">
+      <c r="C49" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="279"/>
-      <c r="E49" s="356" t="s">
+      <c r="E49" s="355" t="s">
         <v>116</v>
       </c>
       <c r="F49" s="279"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="317">
+      <c r="H49" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I49" s="258"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="334" t="s">
+      <c r="C50" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="279"/>
-      <c r="E50" s="312" t="s">
+      <c r="E50" s="311" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="279"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="336"/>
+      <c r="H50" s="335"/>
       <c r="I50" s="258"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="324" t="s">
+      <c r="B51" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C51" s="279"/>
@@ -7048,7 +7050,7 @@
       <c r="I51" s="258"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="333" t="s">
+      <c r="B52" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="279"/>
@@ -7059,14 +7061,14 @@
       <c r="F52" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="325" t="s">
+      <c r="G52" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H52" s="279"/>
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="322" t="s">
+      <c r="B53" s="321" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="279"/>
@@ -7078,7 +7080,7 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="314">
+      <c r="G53" s="313">
         <v>1</v>
       </c>
       <c r="H53" s="279"/>
@@ -7098,7 +7100,7 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="314">
+      <c r="G54" s="313">
         <v>0.8</v>
       </c>
       <c r="H54" s="279"/>
@@ -7118,14 +7120,14 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="314">
+      <c r="G55" s="313">
         <v>0.6</v>
       </c>
       <c r="H55" s="279"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="319" t="s">
+      <c r="B56" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C56" s="246"/>
@@ -7138,7 +7140,7 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="310">
+      <c r="G56" s="309">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
@@ -7156,7 +7158,7 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="328" t="s">
+      <c r="B58" s="327" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="279"/>
@@ -7169,19 +7171,19 @@
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="320" t="s">
+      <c r="B59" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="321"/>
-      <c r="D59" s="321"/>
-      <c r="E59" s="335" t="s">
+      <c r="C59" s="320"/>
+      <c r="D59" s="320"/>
+      <c r="E59" s="334" t="s">
         <v>126</v>
       </c>
       <c r="F59" s="279"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="355" t="s">
+      <c r="H59" s="354" t="s">
         <v>127</v>
       </c>
       <c r="I59" s="258"/>
@@ -7190,55 +7192,55 @@
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="318" t="s">
+      <c r="B60" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C60" s="279"/>
       <c r="D60" s="279"/>
-      <c r="E60" s="335" t="s">
+      <c r="E60" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F60" s="279"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="345" t="s">
+      <c r="H60" s="344" t="s">
         <v>49</v>
       </c>
       <c r="I60" s="258"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="318" t="s">
+      <c r="B61" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C61" s="279"/>
       <c r="D61" s="279"/>
-      <c r="E61" s="326">
+      <c r="E61" s="325">
         <v>626</v>
       </c>
       <c r="F61" s="279"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="345" t="s">
+      <c r="H61" s="344" t="s">
         <v>129</v>
       </c>
       <c r="I61" s="258"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="334" t="s">
+      <c r="C62" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="279"/>
-      <c r="E62" s="350">
+      <c r="E62" s="349">
         <v>10500000</v>
       </c>
       <c r="F62" s="279"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="327">
+      <c r="H62" s="326">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
@@ -7251,42 +7253,42 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="334" t="s">
+      <c r="C63" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="279"/>
-      <c r="E63" s="349" t="s">
+      <c r="E63" s="347" t="s">
         <v>116</v>
       </c>
       <c r="F63" s="279"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="317">
+      <c r="H63" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I63" s="258"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="334" t="s">
+      <c r="C64" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D64" s="279"/>
-      <c r="E64" s="312" t="s">
+      <c r="E64" s="311" t="s">
         <v>97</v>
       </c>
       <c r="F64" s="279"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="336"/>
+      <c r="H64" s="335"/>
       <c r="I64" s="258"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="324" t="s">
+      <c r="B65" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C65" s="279"/>
@@ -7298,7 +7300,7 @@
       <c r="I65" s="258"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="333" t="s">
+      <c r="B66" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="279"/>
@@ -7309,7 +7311,7 @@
       <c r="F66" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="325" t="s">
+      <c r="G66" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H66" s="279"/>
@@ -7328,7 +7330,7 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="314">
+      <c r="G67" s="313">
         <v>1</v>
       </c>
       <c r="H67" s="279"/>
@@ -7347,14 +7349,14 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="314">
+      <c r="G68" s="313">
         <v>0.9</v>
       </c>
       <c r="H68" s="279"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="358" t="s">
+      <c r="B69" s="350" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="279"/>
@@ -7367,14 +7369,14 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="314">
+      <c r="G69" s="313">
         <v>0.6</v>
       </c>
       <c r="H69" s="279"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="319" t="s">
+      <c r="B70" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C70" s="246"/>
@@ -7387,7 +7389,7 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="310">
+      <c r="G70" s="309">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
@@ -7405,7 +7407,7 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="328" t="s">
+      <c r="B72" s="327" t="s">
         <v>131</v>
       </c>
       <c r="C72" s="279"/>
@@ -7417,19 +7419,19 @@
       <c r="I72" s="279"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="320" t="s">
+      <c r="B73" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="321"/>
-      <c r="D73" s="321"/>
-      <c r="E73" s="312" t="s">
+      <c r="C73" s="320"/>
+      <c r="D73" s="320"/>
+      <c r="E73" s="311" t="s">
         <v>132</v>
       </c>
       <c r="F73" s="279"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="342" t="s">
+      <c r="H73" s="341" t="s">
         <v>133</v>
       </c>
       <c r="I73" s="258"/>
@@ -7438,30 +7440,30 @@
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="318" t="s">
+      <c r="B74" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="279"/>
       <c r="D74" s="279"/>
-      <c r="E74" s="312" t="s">
+      <c r="E74" s="311" t="s">
         <v>135</v>
       </c>
       <c r="F74" s="279"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="345" t="s">
+      <c r="H74" s="344" t="s">
         <v>49</v>
       </c>
       <c r="I74" s="258"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="318" t="s">
+      <c r="B75" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C75" s="279"/>
       <c r="D75" s="279"/>
-      <c r="E75" s="329">
+      <c r="E75" s="328">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -7469,25 +7471,25 @@
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="315" t="s">
+      <c r="H75" s="314" t="s">
         <v>95</v>
       </c>
       <c r="I75" s="258"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="334" t="s">
+      <c r="C76" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D76" s="279"/>
-      <c r="E76" s="311">
+      <c r="E76" s="310">
         <v>60000000</v>
       </c>
       <c r="F76" s="279"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="331">
+      <c r="H76" s="330">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
@@ -7495,20 +7497,20 @@
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="334" t="s">
+      <c r="C77" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D77" s="279"/>
-      <c r="E77" s="364" t="s">
+      <c r="E77" s="363" t="s">
         <v>116</v>
       </c>
       <c r="F77" s="279"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="317">
+      <c r="H77" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I77" s="258"/>
       <c r="K77" s="221">
@@ -7518,22 +7520,22 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="334" t="s">
+      <c r="C78" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="279"/>
-      <c r="E78" s="312" t="s">
+      <c r="E78" s="311" t="s">
         <v>136</v>
       </c>
       <c r="F78" s="279"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H78" s="336"/>
+      <c r="H78" s="335"/>
       <c r="I78" s="258"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="324" t="s">
+      <c r="B79" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C79" s="279"/>
@@ -7546,7 +7548,7 @@
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="333" t="s">
+      <c r="B80" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C80" s="279"/>
@@ -7557,14 +7559,14 @@
       <c r="F80" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G80" s="325" t="s">
+      <c r="G80" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H80" s="279"/>
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="332" t="s">
+      <c r="B81" s="331" t="s">
         <v>130</v>
       </c>
       <c r="C81" s="279"/>
@@ -7577,14 +7579,14 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="314">
+      <c r="G81" s="313">
         <v>0.9</v>
       </c>
       <c r="H81" s="279"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="332" t="s">
+      <c r="B82" s="331" t="s">
         <v>117</v>
       </c>
       <c r="C82" s="279"/>
@@ -7597,7 +7599,7 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="314">
+      <c r="G82" s="313">
         <v>0.8</v>
       </c>
       <c r="H82" s="279"/>
@@ -7617,14 +7619,14 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="314">
+      <c r="G83" s="313">
         <v>0.6</v>
       </c>
       <c r="H83" s="279"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="319" t="s">
+      <c r="B84" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C84" s="246"/>
@@ -7637,7 +7639,7 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="310">
+      <c r="G84" s="309">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
@@ -7655,7 +7657,7 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="328" t="s">
+      <c r="B86" s="327" t="s">
         <v>137</v>
       </c>
       <c r="C86" s="279"/>
@@ -7668,19 +7670,19 @@
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="320" t="s">
+      <c r="B87" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="321"/>
-      <c r="D87" s="321"/>
-      <c r="E87" s="335" t="s">
+      <c r="C87" s="320"/>
+      <c r="D87" s="320"/>
+      <c r="E87" s="334" t="s">
         <v>119</v>
       </c>
       <c r="F87" s="279"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="357" t="str">
+      <c r="H87" s="356" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
@@ -7690,30 +7692,30 @@
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="318" t="s">
+      <c r="B88" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C88" s="279"/>
       <c r="D88" s="279"/>
-      <c r="E88" s="335" t="s">
+      <c r="E88" s="334" t="s">
         <v>90</v>
       </c>
       <c r="F88" s="279"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="345" t="s">
+      <c r="H88" s="344" t="s">
         <v>49</v>
       </c>
       <c r="I88" s="258"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="318" t="s">
+      <c r="B89" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="279"/>
       <c r="D89" s="279"/>
-      <c r="E89" s="343">
+      <c r="E89" s="342">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -7721,25 +7723,25 @@
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="315" t="s">
+      <c r="H89" s="314" t="s">
         <v>95</v>
       </c>
       <c r="I89" s="258"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="334" t="s">
+      <c r="C90" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D90" s="279"/>
-      <c r="E90" s="337">
+      <c r="E90" s="336">
         <v>43980000</v>
       </c>
       <c r="F90" s="279"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="327">
+      <c r="H90" s="326">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
@@ -7751,41 +7753,41 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="334" t="s">
+      <c r="C91" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="279"/>
-      <c r="E91" s="362" t="s">
+      <c r="E91" s="361" t="s">
         <v>116</v>
       </c>
       <c r="F91" s="279"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="317">
+      <c r="H91" s="316">
         <f ca="1">TODAY()</f>
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="I91" s="258"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="334" t="s">
+      <c r="C92" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D92" s="279"/>
-      <c r="E92" s="312" t="s">
+      <c r="E92" s="311" t="s">
         <v>97</v>
       </c>
       <c r="F92" s="279"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="336"/>
+      <c r="H92" s="335"/>
       <c r="I92" s="258"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="324" t="s">
+      <c r="B93" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C93" s="279"/>
@@ -7797,7 +7799,7 @@
       <c r="I93" s="258"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="333" t="s">
+      <c r="B94" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C94" s="279"/>
@@ -7808,14 +7810,14 @@
       <c r="F94" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G94" s="325" t="s">
+      <c r="G94" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H94" s="279"/>
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="322" t="s">
+      <c r="B95" s="321" t="s">
         <v>106</v>
       </c>
       <c r="C95" s="279"/>
@@ -7827,7 +7829,7 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="366">
+      <c r="G95" s="365">
         <v>1</v>
       </c>
       <c r="H95" s="279"/>
@@ -7847,14 +7849,14 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="366">
+      <c r="G96" s="365">
         <v>0.8</v>
       </c>
       <c r="H96" s="279"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="363" t="s">
+      <c r="B97" s="362" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="279"/>
@@ -7867,7 +7869,7 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="314">
+      <c r="G97" s="313">
         <v>0.6</v>
       </c>
       <c r="H97" s="279"/>
@@ -7876,7 +7878,7 @@
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="319" t="s">
+      <c r="B98" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C98" s="246"/>
@@ -7889,7 +7891,7 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="310">
+      <c r="G98" s="309">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
@@ -7914,7 +7916,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="330"/>
+      <c r="B100" s="329"/>
       <c r="C100" s="279"/>
       <c r="D100" s="279"/>
       <c r="E100" s="279"/>
@@ -7926,7 +7928,7 @@
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="328" t="s">
+      <c r="B101" s="327" t="s">
         <v>139</v>
       </c>
       <c r="C101" s="279"/>
@@ -7940,93 +7942,93 @@
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="320" t="s">
+      <c r="B102" s="319" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="321"/>
-      <c r="D102" s="321"/>
-      <c r="E102" s="372"/>
+      <c r="C102" s="320"/>
+      <c r="D102" s="320"/>
+      <c r="E102" s="371"/>
       <c r="F102" s="279"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="313"/>
+      <c r="H102" s="312"/>
       <c r="I102" s="258"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="318" t="s">
+      <c r="B103" s="317" t="s">
         <v>89</v>
       </c>
       <c r="C103" s="279"/>
       <c r="D103" s="279"/>
-      <c r="E103" s="367"/>
+      <c r="E103" s="366"/>
       <c r="F103" s="279"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="361"/>
+      <c r="H103" s="360"/>
       <c r="I103" s="258"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="318" t="s">
+      <c r="B104" s="317" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="279"/>
       <c r="D104" s="279"/>
-      <c r="E104" s="326"/>
+      <c r="E104" s="325"/>
       <c r="F104" s="279"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="339"/>
+      <c r="H104" s="338"/>
       <c r="I104" s="258"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="334" t="s">
+      <c r="C105" s="333" t="s">
         <v>113</v>
       </c>
       <c r="D105" s="279"/>
-      <c r="E105" s="337"/>
+      <c r="E105" s="336"/>
       <c r="F105" s="279"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="327"/>
+      <c r="H105" s="326"/>
       <c r="I105" s="258"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="334" t="s">
+      <c r="C106" s="333" t="s">
         <v>115</v>
       </c>
       <c r="D106" s="279"/>
-      <c r="E106" s="362"/>
+      <c r="E106" s="361"/>
       <c r="F106" s="279"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="365"/>
+      <c r="H106" s="364"/>
       <c r="I106" s="258"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="334" t="s">
+      <c r="C107" s="333" t="s">
         <v>96</v>
       </c>
       <c r="D107" s="279"/>
-      <c r="E107" s="338"/>
+      <c r="E107" s="337"/>
       <c r="F107" s="279"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="336"/>
+      <c r="H107" s="335"/>
       <c r="I107" s="258"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="324" t="s">
+      <c r="B108" s="323" t="s">
         <v>101</v>
       </c>
       <c r="C108" s="279"/>
@@ -8038,7 +8040,7 @@
       <c r="I108" s="258"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="333" t="s">
+      <c r="B109" s="332" t="s">
         <v>102</v>
       </c>
       <c r="C109" s="279"/>
@@ -8049,38 +8051,38 @@
       <c r="F109" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="325" t="s">
+      <c r="G109" s="324" t="s">
         <v>105</v>
       </c>
       <c r="H109" s="279"/>
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="363" t="s">
+      <c r="B110" s="362" t="s">
         <v>106</v>
       </c>
       <c r="C110" s="279"/>
       <c r="D110" s="279"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="314"/>
+      <c r="G110" s="313"/>
       <c r="H110" s="279"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="363" t="s">
+      <c r="B111" s="362" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="279"/>
       <c r="D111" s="279"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="314"/>
+      <c r="G111" s="313"/>
       <c r="H111" s="279"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="319" t="s">
+      <c r="B112" s="318" t="s">
         <v>83</v>
       </c>
       <c r="C112" s="246"/>
@@ -8093,7 +8095,7 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="310">
+      <c r="G112" s="309">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
@@ -8174,7 +8176,6 @@
     <mergeCell ref="E77:F77"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H18:I18"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B79:I79"/>
     <mergeCell ref="G25:H25"/>
@@ -8194,6 +8195,10 @@
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
     <mergeCell ref="H107:I107"/>
     <mergeCell ref="C78:D78"/>
     <mergeCell ref="C35:D35"/>
@@ -8218,16 +8223,6 @@
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E74:F74"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="E33:F33"/>
@@ -8239,12 +8234,11 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C76:D76"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="H18:I18"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="C63:D63"/>
@@ -8254,18 +8248,21 @@
     <mergeCell ref="C77:D77"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B80:D80"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G81:H81"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="G80:H80"/>
     <mergeCell ref="H50:I50"/>
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
     <mergeCell ref="E107:F107"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B102:D102"/>
@@ -8307,6 +8304,11 @@
     <mergeCell ref="H78:I78"/>
     <mergeCell ref="E90:F90"/>
     <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E22:F22"/>
@@ -8682,16 +8684,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="375"/>
-      <c r="F1" s="376"/>
-      <c r="G1" s="376"/>
-      <c r="H1" s="376"/>
-      <c r="I1" s="376"/>
-      <c r="J1" s="376"/>
-      <c r="K1" s="376"/>
-      <c r="L1" s="376"/>
-      <c r="M1" s="376"/>
-      <c r="N1" s="376"/>
+      <c r="E1" s="374"/>
+      <c r="F1" s="375"/>
+      <c r="G1" s="375"/>
+      <c r="H1" s="375"/>
+      <c r="I1" s="375"/>
+      <c r="J1" s="375"/>
+      <c r="K1" s="375"/>
+      <c r="L1" s="375"/>
+      <c r="M1" s="375"/>
+      <c r="N1" s="375"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -9239,21 +9241,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="374" t="s">
+      <c r="A12" s="373" t="s">
         <v>173</v>
       </c>
       <c r="B12" s="244"/>
-      <c r="C12" s="377" t="s">
+      <c r="C12" s="376" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="376"/>
-      <c r="E12" s="376"/>
-      <c r="F12" s="376"/>
-      <c r="G12" s="376"/>
-      <c r="H12" s="376"/>
-      <c r="I12" s="376"/>
-      <c r="J12" s="376"/>
-      <c r="K12" s="376"/>
+      <c r="D12" s="375"/>
+      <c r="E12" s="375"/>
+      <c r="F12" s="375"/>
+      <c r="G12" s="375"/>
+      <c r="H12" s="375"/>
+      <c r="I12" s="375"/>
+      <c r="J12" s="375"/>
+      <c r="K12" s="375"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -9268,21 +9270,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="374" t="s">
+      <c r="A13" s="373" t="s">
         <v>176</v>
       </c>
       <c r="B13" s="244"/>
-      <c r="C13" s="377" t="s">
+      <c r="C13" s="376" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="376"/>
-      <c r="E13" s="376"/>
-      <c r="F13" s="376"/>
-      <c r="G13" s="376"/>
-      <c r="H13" s="376"/>
-      <c r="I13" s="376"/>
-      <c r="J13" s="376"/>
-      <c r="K13" s="376"/>
+      <c r="D13" s="375"/>
+      <c r="E13" s="375"/>
+      <c r="F13" s="375"/>
+      <c r="G13" s="375"/>
+      <c r="H13" s="375"/>
+      <c r="I13" s="375"/>
+      <c r="J13" s="375"/>
+      <c r="K13" s="375"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -9297,22 +9299,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="374" t="str">
+      <c r="A14" s="373" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
       <c r="B14" s="244"/>
-      <c r="C14" s="377" t="s">
+      <c r="C14" s="376" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="376"/>
-      <c r="E14" s="376"/>
-      <c r="F14" s="376"/>
-      <c r="G14" s="376"/>
-      <c r="H14" s="376"/>
-      <c r="I14" s="376"/>
-      <c r="J14" s="376"/>
-      <c r="K14" s="376"/>
+      <c r="D14" s="375"/>
+      <c r="E14" s="375"/>
+      <c r="F14" s="375"/>
+      <c r="G14" s="375"/>
+      <c r="H14" s="375"/>
+      <c r="I14" s="375"/>
+      <c r="J14" s="375"/>
+      <c r="K14" s="375"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -9327,21 +9329,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="374" t="s">
+      <c r="A15" s="373" t="s">
         <v>160</v>
       </c>
       <c r="B15" s="244"/>
-      <c r="C15" s="377" t="s">
+      <c r="C15" s="376" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="376"/>
-      <c r="E15" s="376"/>
-      <c r="F15" s="376"/>
-      <c r="G15" s="376"/>
-      <c r="H15" s="376"/>
-      <c r="I15" s="376"/>
-      <c r="J15" s="376"/>
-      <c r="K15" s="376"/>
+      <c r="D15" s="375"/>
+      <c r="E15" s="375"/>
+      <c r="F15" s="375"/>
+      <c r="G15" s="375"/>
+      <c r="H15" s="375"/>
+      <c r="I15" s="375"/>
+      <c r="J15" s="375"/>
+      <c r="K15" s="375"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -9356,21 +9358,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="374" t="s">
+      <c r="A16" s="373" t="s">
         <v>162</v>
       </c>
       <c r="B16" s="244"/>
-      <c r="C16" s="379" t="s">
+      <c r="C16" s="378" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="376"/>
-      <c r="E16" s="376"/>
-      <c r="F16" s="376"/>
-      <c r="G16" s="376"/>
-      <c r="H16" s="376"/>
-      <c r="I16" s="376"/>
-      <c r="J16" s="376"/>
-      <c r="K16" s="376"/>
+      <c r="D16" s="375"/>
+      <c r="E16" s="375"/>
+      <c r="F16" s="375"/>
+      <c r="G16" s="375"/>
+      <c r="H16" s="375"/>
+      <c r="I16" s="375"/>
+      <c r="J16" s="375"/>
+      <c r="K16" s="375"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -9380,21 +9382,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="374" t="s">
+      <c r="A17" s="373" t="s">
         <v>163</v>
       </c>
       <c r="B17" s="244"/>
-      <c r="C17" s="379" t="s">
+      <c r="C17" s="378" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="376"/>
-      <c r="E17" s="376"/>
-      <c r="F17" s="376"/>
-      <c r="G17" s="376"/>
-      <c r="H17" s="376"/>
-      <c r="I17" s="376"/>
-      <c r="J17" s="376"/>
-      <c r="K17" s="376"/>
+      <c r="D17" s="375"/>
+      <c r="E17" s="375"/>
+      <c r="F17" s="375"/>
+      <c r="G17" s="375"/>
+      <c r="H17" s="375"/>
+      <c r="I17" s="375"/>
+      <c r="J17" s="375"/>
+      <c r="K17" s="375"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>185</v>
@@ -9413,21 +9415,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="374" t="s">
+      <c r="A18" s="373" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="244"/>
-      <c r="C18" s="379" t="s">
+      <c r="C18" s="378" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="376"/>
-      <c r="E18" s="376"/>
-      <c r="F18" s="376"/>
-      <c r="G18" s="376"/>
-      <c r="H18" s="376"/>
-      <c r="I18" s="376"/>
-      <c r="J18" s="376"/>
-      <c r="K18" s="376"/>
+      <c r="D18" s="375"/>
+      <c r="E18" s="375"/>
+      <c r="F18" s="375"/>
+      <c r="G18" s="375"/>
+      <c r="H18" s="375"/>
+      <c r="I18" s="375"/>
+      <c r="J18" s="375"/>
+      <c r="K18" s="375"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>188</v>
@@ -9441,21 +9443,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="374" t="s">
+      <c r="A19" s="373" t="s">
         <v>182</v>
       </c>
       <c r="B19" s="244"/>
-      <c r="C19" s="379" t="s">
+      <c r="C19" s="378" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="376"/>
-      <c r="E19" s="376"/>
-      <c r="F19" s="376"/>
-      <c r="G19" s="376"/>
-      <c r="H19" s="376"/>
-      <c r="I19" s="376"/>
-      <c r="J19" s="376"/>
-      <c r="K19" s="376"/>
+      <c r="D19" s="375"/>
+      <c r="E19" s="375"/>
+      <c r="F19" s="375"/>
+      <c r="G19" s="375"/>
+      <c r="H19" s="375"/>
+      <c r="I19" s="375"/>
+      <c r="J19" s="375"/>
+      <c r="K19" s="375"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -9470,21 +9472,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="374" t="s">
+      <c r="A20" s="373" t="s">
         <v>164</v>
       </c>
       <c r="B20" s="244"/>
-      <c r="C20" s="379" t="s">
+      <c r="C20" s="378" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="376"/>
-      <c r="E20" s="376"/>
-      <c r="F20" s="376"/>
-      <c r="G20" s="376"/>
-      <c r="H20" s="376"/>
-      <c r="I20" s="376"/>
-      <c r="J20" s="376"/>
-      <c r="K20" s="376"/>
+      <c r="D20" s="375"/>
+      <c r="E20" s="375"/>
+      <c r="F20" s="375"/>
+      <c r="G20" s="375"/>
+      <c r="H20" s="375"/>
+      <c r="I20" s="375"/>
+      <c r="J20" s="375"/>
+      <c r="K20" s="375"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -9499,21 +9501,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="374" t="s">
+      <c r="A21" s="373" t="s">
         <v>186</v>
       </c>
       <c r="B21" s="244"/>
-      <c r="C21" s="379" t="s">
+      <c r="C21" s="378" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="376"/>
-      <c r="E21" s="376"/>
-      <c r="F21" s="376"/>
-      <c r="G21" s="376"/>
-      <c r="H21" s="376"/>
-      <c r="I21" s="376"/>
-      <c r="J21" s="376"/>
-      <c r="K21" s="376"/>
+      <c r="D21" s="375"/>
+      <c r="E21" s="375"/>
+      <c r="F21" s="375"/>
+      <c r="G21" s="375"/>
+      <c r="H21" s="375"/>
+      <c r="I21" s="375"/>
+      <c r="J21" s="375"/>
+      <c r="K21" s="375"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -9528,24 +9530,24 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="374" t="s">
+      <c r="A22" s="373" t="s">
         <v>192</v>
       </c>
       <c r="B22" s="244"/>
-      <c r="C22" s="378" t="s">
+      <c r="C22" s="377" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="376"/>
-      <c r="E22" s="376"/>
-      <c r="F22" s="376"/>
-      <c r="G22" s="376"/>
-      <c r="H22" s="376"/>
-      <c r="I22" s="376"/>
-      <c r="J22" s="376"/>
-      <c r="K22" s="376"/>
-      <c r="L22" s="376"/>
-      <c r="M22" s="376"/>
-      <c r="N22" s="376"/>
+      <c r="D22" s="375"/>
+      <c r="E22" s="375"/>
+      <c r="F22" s="375"/>
+      <c r="G22" s="375"/>
+      <c r="H22" s="375"/>
+      <c r="I22" s="375"/>
+      <c r="J22" s="375"/>
+      <c r="K22" s="375"/>
+      <c r="L22" s="375"/>
+      <c r="M22" s="375"/>
+      <c r="N22" s="375"/>
       <c r="O22" s="258"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
@@ -9557,22 +9559,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="374" t="s">
+      <c r="A23" s="373" t="s">
         <v>194</v>
       </c>
       <c r="B23" s="244"/>
-      <c r="C23" s="379" t="s">
+      <c r="C23" s="378" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="376"/>
-      <c r="E23" s="376"/>
-      <c r="F23" s="376"/>
-      <c r="G23" s="376"/>
-      <c r="H23" s="376"/>
-      <c r="I23" s="376"/>
-      <c r="J23" s="376"/>
-      <c r="K23" s="376"/>
-      <c r="L23" s="376"/>
+      <c r="D23" s="375"/>
+      <c r="E23" s="375"/>
+      <c r="F23" s="375"/>
+      <c r="G23" s="375"/>
+      <c r="H23" s="375"/>
+      <c r="I23" s="375"/>
+      <c r="J23" s="375"/>
+      <c r="K23" s="375"/>
+      <c r="L23" s="375"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -9586,22 +9588,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="374" t="s">
+      <c r="A24" s="373" t="s">
         <v>196</v>
       </c>
       <c r="B24" s="244"/>
-      <c r="C24" s="379" t="s">
+      <c r="C24" s="378" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="376"/>
-      <c r="E24" s="376"/>
-      <c r="F24" s="376"/>
-      <c r="G24" s="376"/>
-      <c r="H24" s="376"/>
-      <c r="I24" s="376"/>
-      <c r="J24" s="376"/>
-      <c r="K24" s="376"/>
-      <c r="L24" s="376"/>
+      <c r="D24" s="375"/>
+      <c r="E24" s="375"/>
+      <c r="F24" s="375"/>
+      <c r="G24" s="375"/>
+      <c r="H24" s="375"/>
+      <c r="I24" s="375"/>
+      <c r="J24" s="375"/>
+      <c r="K24" s="375"/>
+      <c r="L24" s="375"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -9615,21 +9617,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="374" t="s">
+      <c r="A25" s="373" t="s">
         <v>198</v>
       </c>
       <c r="B25" s="244"/>
-      <c r="C25" s="379" t="s">
+      <c r="C25" s="378" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="376"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
-      <c r="G25" s="376"/>
-      <c r="H25" s="376"/>
-      <c r="I25" s="376"/>
-      <c r="J25" s="376"/>
-      <c r="K25" s="376"/>
+      <c r="D25" s="375"/>
+      <c r="E25" s="375"/>
+      <c r="F25" s="375"/>
+      <c r="G25" s="375"/>
+      <c r="H25" s="375"/>
+      <c r="I25" s="375"/>
+      <c r="J25" s="375"/>
+      <c r="K25" s="375"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -9639,21 +9641,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="380" t="s">
+      <c r="A26" s="379" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="381"/>
-      <c r="C26" s="382" t="s">
+      <c r="B26" s="380"/>
+      <c r="C26" s="381" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="383"/>
-      <c r="E26" s="383"/>
-      <c r="F26" s="383"/>
-      <c r="G26" s="383"/>
-      <c r="H26" s="383"/>
-      <c r="I26" s="383"/>
-      <c r="J26" s="383"/>
-      <c r="K26" s="383"/>
+      <c r="D26" s="382"/>
+      <c r="E26" s="382"/>
+      <c r="F26" s="382"/>
+      <c r="G26" s="382"/>
+      <c r="H26" s="382"/>
+      <c r="I26" s="382"/>
+      <c r="J26" s="382"/>
+      <c r="K26" s="382"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -9761,7 +9763,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="384" t="str">
+      <c r="C4" s="383" t="str">
         <f>'AREA UTIL '!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -9772,7 +9774,7 @@
       <c r="H4" s="248"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="384" t="s">
+      <c r="C5" s="383" t="s">
         <v>204</v>
       </c>
       <c r="D5" s="248"/>
@@ -9782,12 +9784,12 @@
       <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="389" t="s">
+      <c r="C6" s="388" t="s">
         <v>190</v>
       </c>
       <c r="D6" s="248"/>
       <c r="E6" s="248"/>
-      <c r="F6" s="386">
+      <c r="F6" s="385">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
@@ -9795,12 +9797,12 @@
       <c r="H6" s="258"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="389" t="s">
+      <c r="C7" s="388" t="s">
         <v>205</v>
       </c>
       <c r="D7" s="248"/>
       <c r="E7" s="248"/>
-      <c r="F7" s="386">
+      <c r="F7" s="385">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
@@ -9808,12 +9810,12 @@
       <c r="H7" s="258"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="389" t="s">
+      <c r="C8" s="388" t="s">
         <v>206</v>
       </c>
       <c r="D8" s="248"/>
       <c r="E8" s="248"/>
-      <c r="F8" s="386">
+      <c r="F8" s="385">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
@@ -9821,12 +9823,12 @@
       <c r="H8" s="258"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="389" t="s">
+      <c r="C9" s="388" t="s">
         <v>207</v>
       </c>
       <c r="D9" s="248"/>
       <c r="E9" s="248"/>
-      <c r="F9" s="385">
+      <c r="F9" s="384">
         <v>6</v>
       </c>
       <c r="G9" s="248"/>
@@ -9836,12 +9838,12 @@
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="389" t="s">
+      <c r="C10" s="388" t="s">
         <v>209</v>
       </c>
       <c r="D10" s="248"/>
       <c r="E10" s="248"/>
-      <c r="F10" s="385">
+      <c r="F10" s="384">
         <v>1</v>
       </c>
       <c r="G10" s="248"/>
@@ -9851,7 +9853,7 @@
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="389" t="s">
+      <c r="C11" s="388" t="s">
         <v>200</v>
       </c>
       <c r="D11" s="248"/>
@@ -9864,12 +9866,12 @@
       <c r="H11" s="258"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="389" t="s">
+      <c r="C12" s="388" t="s">
         <v>210</v>
       </c>
       <c r="D12" s="248"/>
       <c r="E12" s="248"/>
-      <c r="F12" s="385">
+      <c r="F12" s="384">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
@@ -9877,12 +9879,12 @@
       <c r="H12" s="258"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="389" t="s">
+      <c r="C13" s="388" t="s">
         <v>198</v>
       </c>
       <c r="D13" s="248"/>
       <c r="E13" s="248"/>
-      <c r="F13" s="386">
+      <c r="F13" s="385">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
@@ -9927,12 +9929,12 @@
       <c r="H16" s="248"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="389" t="s">
+      <c r="C17" s="388" t="s">
         <v>213</v>
       </c>
       <c r="D17" s="248"/>
       <c r="E17" s="248"/>
-      <c r="F17" s="385">
+      <c r="F17" s="384">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
@@ -9940,12 +9942,12 @@
       <c r="H17" s="258"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="389" t="s">
+      <c r="C18" s="388" t="s">
         <v>214</v>
       </c>
       <c r="D18" s="248"/>
       <c r="E18" s="248"/>
-      <c r="F18" s="386">
+      <c r="F18" s="385">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
@@ -9953,12 +9955,12 @@
       <c r="H18" s="258"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="389" t="s">
+      <c r="C19" s="388" t="s">
         <v>215</v>
       </c>
       <c r="D19" s="248"/>
       <c r="E19" s="248"/>
-      <c r="F19" s="386">
+      <c r="F19" s="385">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
@@ -9979,23 +9981,23 @@
       <c r="H20" s="244"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="400"/>
+      <c r="C21" s="389"/>
       <c r="D21" s="248"/>
       <c r="E21" s="248"/>
-      <c r="F21" s="387"/>
+      <c r="F21" s="386"/>
       <c r="G21" s="248"/>
       <c r="H21" s="248"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="400"/>
+      <c r="C22" s="389"/>
       <c r="D22" s="248"/>
       <c r="E22" s="248"/>
-      <c r="F22" s="387"/>
+      <c r="F22" s="386"/>
       <c r="G22" s="248"/>
       <c r="H22" s="248"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="400"/>
+      <c r="C23" s="389"/>
       <c r="D23" s="248"/>
       <c r="E23" s="248"/>
       <c r="F23" s="393"/>
@@ -10013,7 +10015,7 @@
       <c r="H24" s="248"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="388" t="s">
+      <c r="C25" s="387" t="s">
         <v>218</v>
       </c>
       <c r="D25" s="248"/>
@@ -10025,19 +10027,19 @@
       <c r="H25" s="258"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="388" t="s">
+      <c r="C26" s="387" t="s">
         <v>219</v>
       </c>
       <c r="D26" s="248"/>
       <c r="E26" s="248"/>
-      <c r="F26" s="401">
+      <c r="F26" s="400">
         <v>0.8</v>
       </c>
       <c r="G26" s="248"/>
       <c r="H26" s="258"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="388" t="s">
+      <c r="C27" s="387" t="s">
         <v>220</v>
       </c>
       <c r="D27" s="248"/>
@@ -10055,7 +10057,7 @@
       </c>
       <c r="D28" s="243"/>
       <c r="E28" s="243"/>
-      <c r="F28" s="402">
+      <c r="F28" s="401">
         <f>F27</f>
         <v>1600000</v>
       </c>
@@ -10073,12 +10075,12 @@
       <c r="H31" s="248"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="389" t="s">
+      <c r="C32" s="388" t="s">
         <v>222</v>
       </c>
       <c r="D32" s="248"/>
       <c r="E32" s="248"/>
-      <c r="F32" s="386">
+      <c r="F32" s="385">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
@@ -10086,12 +10088,12 @@
       <c r="H32" s="258"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="389" t="s">
+      <c r="C33" s="388" t="s">
         <v>223</v>
       </c>
       <c r="D33" s="248"/>
       <c r="E33" s="248"/>
-      <c r="F33" s="386">
+      <c r="F33" s="385">
         <f>F28</f>
         <v>1600000</v>
       </c>
@@ -10183,7 +10185,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="384" t="str">
+      <c r="C5" s="383" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -10194,7 +10196,7 @@
       <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="384" t="s">
+      <c r="C6" s="383" t="s">
         <v>225</v>
       </c>
       <c r="D6" s="248"/>
@@ -10204,36 +10206,36 @@
       <c r="H6" s="248"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="389" t="s">
+      <c r="C7" s="388" t="s">
         <v>226</v>
       </c>
       <c r="D7" s="248"/>
       <c r="E7" s="248"/>
-      <c r="F7" s="404">
+      <c r="F7" s="403">
         <v>0.13250000000000001</v>
       </c>
       <c r="G7" s="248"/>
       <c r="H7" s="258"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="389" t="s">
+      <c r="C8" s="388" t="s">
         <v>227</v>
       </c>
       <c r="D8" s="248"/>
       <c r="E8" s="248"/>
-      <c r="F8" s="385">
+      <c r="F8" s="384">
         <v>36</v>
       </c>
       <c r="G8" s="248"/>
       <c r="H8" s="258"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="389" t="s">
+      <c r="C9" s="388" t="s">
         <v>228</v>
       </c>
       <c r="D9" s="248"/>
       <c r="E9" s="248"/>
-      <c r="F9" s="403">
+      <c r="F9" s="402">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
@@ -10241,12 +10243,12 @@
       <c r="H9" s="258"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="389" t="s">
+      <c r="C10" s="388" t="s">
         <v>229</v>
       </c>
       <c r="D10" s="248"/>
       <c r="E10" s="248"/>
-      <c r="F10" s="386">
+      <c r="F10" s="385">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
@@ -10282,36 +10284,36 @@
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="389" t="s">
+      <c r="C14" s="388" t="s">
         <v>226</v>
       </c>
       <c r="D14" s="248"/>
       <c r="E14" s="248"/>
-      <c r="F14" s="404">
+      <c r="F14" s="403">
         <v>0.12767999999999999</v>
       </c>
       <c r="G14" s="248"/>
       <c r="H14" s="258"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="389" t="s">
+      <c r="C15" s="388" t="s">
         <v>227</v>
       </c>
       <c r="D15" s="248"/>
       <c r="E15" s="248"/>
-      <c r="F15" s="385">
+      <c r="F15" s="384">
         <v>36</v>
       </c>
       <c r="G15" s="248"/>
       <c r="H15" s="258"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="389" t="s">
+      <c r="C16" s="388" t="s">
         <v>228</v>
       </c>
       <c r="D16" s="248"/>
       <c r="E16" s="248"/>
-      <c r="F16" s="403">
+      <c r="F16" s="402">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
@@ -10319,12 +10321,12 @@
       <c r="H16" s="258"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="389" t="s">
+      <c r="C17" s="388" t="s">
         <v>229</v>
       </c>
       <c r="D17" s="248"/>
       <c r="E17" s="248"/>
-      <c r="F17" s="386">
+      <c r="F17" s="385">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
@@ -10409,37 +10411,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="405" t="s">
+      <c r="B2" s="404" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="406"/>
-      <c r="D2" s="406"/>
-      <c r="E2" s="406"/>
-      <c r="F2" s="406"/>
-      <c r="G2" s="406"/>
-      <c r="H2" s="406"/>
-      <c r="I2" s="406"/>
-      <c r="J2" s="406"/>
-      <c r="K2" s="406"/>
-      <c r="L2" s="406"/>
-      <c r="M2" s="406"/>
-      <c r="N2" s="406"/>
-      <c r="O2" s="406"/>
-      <c r="P2" s="406"/>
-      <c r="Q2" s="406"/>
-      <c r="R2" s="406"/>
-      <c r="S2" s="406"/>
-      <c r="T2" s="406"/>
-      <c r="U2" s="406"/>
-      <c r="V2" s="406"/>
-      <c r="W2" s="406"/>
-      <c r="X2" s="406"/>
-      <c r="Y2" s="406"/>
-      <c r="Z2" s="406"/>
-      <c r="AA2" s="406"/>
-      <c r="AB2" s="406"/>
-      <c r="AC2" s="406"/>
-      <c r="AD2" s="406"/>
+      <c r="C2" s="405"/>
+      <c r="D2" s="405"/>
+      <c r="E2" s="405"/>
+      <c r="F2" s="405"/>
+      <c r="G2" s="405"/>
+      <c r="H2" s="405"/>
+      <c r="I2" s="405"/>
+      <c r="J2" s="405"/>
+      <c r="K2" s="405"/>
+      <c r="L2" s="405"/>
+      <c r="M2" s="405"/>
+      <c r="N2" s="405"/>
+      <c r="O2" s="405"/>
+      <c r="P2" s="405"/>
+      <c r="Q2" s="405"/>
+      <c r="R2" s="405"/>
+      <c r="S2" s="405"/>
+      <c r="T2" s="405"/>
+      <c r="U2" s="405"/>
+      <c r="V2" s="405"/>
+      <c r="W2" s="405"/>
+      <c r="X2" s="405"/>
+      <c r="Y2" s="405"/>
+      <c r="Z2" s="405"/>
+      <c r="AA2" s="405"/>
+      <c r="AB2" s="405"/>
+      <c r="AC2" s="405"/>
+      <c r="AD2" s="405"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -10566,39 +10568,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="423">
+      <c r="B10" s="422">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="408"/>
-      <c r="D10" s="408"/>
-      <c r="E10" s="408"/>
-      <c r="F10" s="408"/>
-      <c r="G10" s="408"/>
+      <c r="C10" s="407"/>
+      <c r="D10" s="407"/>
+      <c r="E10" s="407"/>
+      <c r="F10" s="407"/>
+      <c r="G10" s="407"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="422">
+      <c r="I10" s="421">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="408"/>
-      <c r="K10" s="408"/>
-      <c r="L10" s="408"/>
-      <c r="M10" s="408"/>
-      <c r="N10" s="408"/>
-      <c r="O10" s="408"/>
-      <c r="P10" s="408"/>
+      <c r="J10" s="407"/>
+      <c r="K10" s="407"/>
+      <c r="L10" s="407"/>
+      <c r="M10" s="407"/>
+      <c r="N10" s="407"/>
+      <c r="O10" s="407"/>
+      <c r="P10" s="407"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="407">
+      <c r="R10" s="406">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="408"/>
-      <c r="T10" s="408"/>
-      <c r="U10" s="408"/>
+      <c r="S10" s="407"/>
+      <c r="T10" s="407"/>
+      <c r="U10" s="407"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -10633,13 +10635,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="407">
+      <c r="W11" s="406">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="408"/>
-      <c r="Y11" s="408"/>
-      <c r="Z11" s="408"/>
+      <c r="X11" s="407"/>
+      <c r="Y11" s="407"/>
+      <c r="Z11" s="407"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -10666,13 +10668,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="419">
+      <c r="R12" s="418">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="408"/>
-      <c r="T12" s="408"/>
-      <c r="U12" s="408"/>
+      <c r="S12" s="407"/>
+      <c r="T12" s="407"/>
+      <c r="U12" s="407"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -10692,10 +10694,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="412"/>
-      <c r="X14" s="408"/>
-      <c r="Y14" s="408"/>
-      <c r="Z14" s="408"/>
+      <c r="W14" s="411"/>
+      <c r="X14" s="407"/>
+      <c r="Y14" s="407"/>
+      <c r="Z14" s="407"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -10721,38 +10723,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="416" t="s">
+      <c r="B16" s="415" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="408"/>
-      <c r="D16" s="408"/>
-      <c r="E16" s="408"/>
-      <c r="F16" s="408"/>
-      <c r="G16" s="408"/>
+      <c r="C16" s="407"/>
+      <c r="D16" s="407"/>
+      <c r="E16" s="407"/>
+      <c r="F16" s="407"/>
+      <c r="G16" s="407"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="425" t="str">
+      <c r="I16" s="424" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="408"/>
-      <c r="K16" s="408"/>
-      <c r="L16" s="408"/>
-      <c r="M16" s="408"/>
-      <c r="N16" s="408"/>
-      <c r="O16" s="408"/>
-      <c r="P16" s="408"/>
+      <c r="J16" s="407"/>
+      <c r="K16" s="407"/>
+      <c r="L16" s="407"/>
+      <c r="M16" s="407"/>
+      <c r="N16" s="407"/>
+      <c r="O16" s="407"/>
+      <c r="P16" s="407"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="412" t="str">
+      <c r="R16" s="411" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="408"/>
-      <c r="T16" s="408"/>
-      <c r="U16" s="408"/>
+      <c r="S16" s="407"/>
+      <c r="T16" s="407"/>
+      <c r="U16" s="407"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -10764,10 +10766,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="412"/>
-      <c r="X17" s="408"/>
-      <c r="Y17" s="408"/>
-      <c r="Z17" s="408"/>
+      <c r="W17" s="411"/>
+      <c r="X17" s="407"/>
+      <c r="Y17" s="407"/>
+      <c r="Z17" s="407"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -10791,13 +10793,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="428" t="str">
+      <c r="R18" s="427" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="408"/>
-      <c r="T18" s="408"/>
-      <c r="U18" s="408"/>
+      <c r="S18" s="407"/>
+      <c r="T18" s="407"/>
+      <c r="U18" s="407"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -10879,13 +10881,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="420">
+      <c r="W22" s="419">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="415"/>
-      <c r="Y22" s="415"/>
-      <c r="Z22" s="415"/>
+      <c r="X22" s="414"/>
+      <c r="Y22" s="414"/>
+      <c r="Z22" s="414"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -10894,13 +10896,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="414" t="str">
+      <c r="W23" s="413" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="415"/>
-      <c r="Y23" s="415"/>
-      <c r="Z23" s="415"/>
+      <c r="X23" s="414"/>
+      <c r="Y23" s="414"/>
+      <c r="Z23" s="414"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -10909,13 +10911,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="409">
+      <c r="W24" s="408">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="410"/>
-      <c r="Y24" s="410"/>
-      <c r="Z24" s="410"/>
+      <c r="X24" s="409"/>
+      <c r="Y24" s="409"/>
+      <c r="Z24" s="409"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -10924,13 +10926,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="414">
+      <c r="W25" s="413">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="415"/>
-      <c r="Y25" s="415"/>
-      <c r="Z25" s="415"/>
+      <c r="X25" s="414"/>
+      <c r="Y25" s="414"/>
+      <c r="Z25" s="414"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -10939,13 +10941,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="414">
+      <c r="W26" s="413">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="415"/>
-      <c r="Y26" s="415"/>
-      <c r="Z26" s="415"/>
+      <c r="X26" s="414"/>
+      <c r="Y26" s="414"/>
+      <c r="Z26" s="414"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -10954,13 +10956,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="414">
+      <c r="W27" s="413">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="415"/>
-      <c r="Y27" s="415"/>
-      <c r="Z27" s="415"/>
+      <c r="X27" s="414"/>
+      <c r="Y27" s="414"/>
+      <c r="Z27" s="414"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -10969,13 +10971,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="414">
+      <c r="W28" s="413">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="415"/>
-      <c r="Y28" s="415"/>
-      <c r="Z28" s="415"/>
+      <c r="X28" s="414"/>
+      <c r="Y28" s="414"/>
+      <c r="Z28" s="414"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -10984,13 +10986,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="414">
+      <c r="W29" s="413">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="415"/>
-      <c r="Y29" s="415"/>
-      <c r="Z29" s="415"/>
+      <c r="X29" s="414"/>
+      <c r="Y29" s="414"/>
+      <c r="Z29" s="414"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -10999,13 +11001,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="413">
+      <c r="W30" s="412">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="410"/>
-      <c r="Y30" s="410"/>
-      <c r="Z30" s="410"/>
+      <c r="X30" s="409"/>
+      <c r="Y30" s="409"/>
+      <c r="Z30" s="409"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -11015,83 +11017,83 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="418">
+      <c r="W31" s="417">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="410"/>
-      <c r="Y31" s="410"/>
-      <c r="Z31" s="410"/>
+      <c r="X31" s="409"/>
+      <c r="Y31" s="409"/>
+      <c r="Z31" s="409"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="417">
+      <c r="K32" s="416">
         <v>43009</v>
       </c>
-      <c r="L32" s="415"/>
-      <c r="M32" s="415"/>
-      <c r="N32" s="415"/>
-      <c r="O32" s="415"/>
-      <c r="P32" s="415"/>
-      <c r="Q32" s="415"/>
-      <c r="R32" s="415"/>
-      <c r="S32" s="415"/>
-      <c r="T32" s="415"/>
-      <c r="U32" s="415"/>
-      <c r="V32" s="415"/>
-      <c r="W32" s="415"/>
-      <c r="X32" s="415"/>
-      <c r="Y32" s="415"/>
-      <c r="Z32" s="415"/>
+      <c r="L32" s="414"/>
+      <c r="M32" s="414"/>
+      <c r="N32" s="414"/>
+      <c r="O32" s="414"/>
+      <c r="P32" s="414"/>
+      <c r="Q32" s="414"/>
+      <c r="R32" s="414"/>
+      <c r="S32" s="414"/>
+      <c r="T32" s="414"/>
+      <c r="U32" s="414"/>
+      <c r="V32" s="414"/>
+      <c r="W32" s="414"/>
+      <c r="X32" s="414"/>
+      <c r="Y32" s="414"/>
+      <c r="Z32" s="414"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="429" t="s">
+      <c r="O33" s="428" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="410"/>
-      <c r="Q33" s="410"/>
-      <c r="R33" s="410"/>
-      <c r="S33" s="410"/>
-      <c r="T33" s="410"/>
-      <c r="U33" s="410"/>
-      <c r="V33" s="410"/>
-      <c r="W33" s="430" t="s">
+      <c r="P33" s="409"/>
+      <c r="Q33" s="409"/>
+      <c r="R33" s="409"/>
+      <c r="S33" s="409"/>
+      <c r="T33" s="409"/>
+      <c r="U33" s="409"/>
+      <c r="V33" s="409"/>
+      <c r="W33" s="429" t="s">
         <v>256</v>
       </c>
-      <c r="X33" s="321"/>
-      <c r="Y33" s="321"/>
-      <c r="Z33" s="321"/>
-      <c r="AA33" s="321"/>
-      <c r="AB33" s="321"/>
-      <c r="AC33" s="321"/>
-      <c r="AD33" s="321"/>
+      <c r="X33" s="320"/>
+      <c r="Y33" s="320"/>
+      <c r="Z33" s="320"/>
+      <c r="AA33" s="320"/>
+      <c r="AB33" s="320"/>
+      <c r="AC33" s="320"/>
+      <c r="AD33" s="320"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="421">
+      <c r="Q34" s="420">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="415"/>
-      <c r="S34" s="415"/>
-      <c r="T34" s="415"/>
+      <c r="R34" s="414"/>
+      <c r="S34" s="414"/>
+      <c r="T34" s="414"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="421">
+      <c r="Y34" s="420">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="415"/>
-      <c r="AA34" s="415"/>
-      <c r="AB34" s="415"/>
+      <c r="Z34" s="414"/>
+      <c r="AA34" s="414"/>
+      <c r="AB34" s="414"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -11154,32 +11156,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="411"/>
-      <c r="C38" s="408"/>
+      <c r="B38" s="410"/>
+      <c r="C38" s="407"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="411"/>
-      <c r="C39" s="408"/>
+      <c r="B39" s="410"/>
+      <c r="C39" s="407"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="411"/>
-      <c r="C40" s="408"/>
+      <c r="B40" s="410"/>
+      <c r="C40" s="407"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="411"/>
-      <c r="C41" s="408"/>
+      <c r="B41" s="410"/>
+      <c r="C41" s="407"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="411"/>
-      <c r="C42" s="408"/>
+      <c r="B42" s="410"/>
+      <c r="C42" s="407"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="411"/>
-      <c r="C43" s="408"/>
+      <c r="B43" s="410"/>
+      <c r="C43" s="407"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="411"/>
-      <c r="C44" s="408"/>
+      <c r="B44" s="410"/>
+      <c r="C44" s="407"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -11250,10 +11252,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="427"/>
-      <c r="F49" s="408"/>
-      <c r="G49" s="408"/>
-      <c r="H49" s="408"/>
+      <c r="E49" s="426"/>
+      <c r="F49" s="407"/>
+      <c r="G49" s="407"/>
+      <c r="H49" s="407"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -11276,40 +11278,40 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="424"/>
-      <c r="I52" s="321"/>
-      <c r="J52" s="321"/>
-      <c r="K52" s="321"/>
-      <c r="L52" s="321"/>
-      <c r="M52" s="321"/>
-      <c r="N52" s="321"/>
-      <c r="O52" s="321"/>
-      <c r="P52" s="321"/>
+      <c r="H52" s="423"/>
+      <c r="I52" s="320"/>
+      <c r="J52" s="320"/>
+      <c r="K52" s="320"/>
+      <c r="L52" s="320"/>
+      <c r="M52" s="320"/>
+      <c r="N52" s="320"/>
+      <c r="O52" s="320"/>
+      <c r="P52" s="320"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="426"/>
-      <c r="I55" s="321"/>
-      <c r="J55" s="321"/>
-      <c r="K55" s="321"/>
-      <c r="L55" s="321"/>
-      <c r="M55" s="321"/>
-      <c r="N55" s="321"/>
-      <c r="O55" s="321"/>
-      <c r="P55" s="321"/>
+      <c r="H55" s="425"/>
+      <c r="I55" s="320"/>
+      <c r="J55" s="320"/>
+      <c r="K55" s="320"/>
+      <c r="L55" s="320"/>
+      <c r="M55" s="320"/>
+      <c r="N55" s="320"/>
+      <c r="O55" s="320"/>
+      <c r="P55" s="320"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="424"/>
-      <c r="I57" s="321"/>
-      <c r="J57" s="321"/>
-      <c r="K57" s="321"/>
-      <c r="L57" s="321"/>
-      <c r="M57" s="321"/>
-      <c r="N57" s="321"/>
-      <c r="O57" s="321"/>
-      <c r="P57" s="321"/>
+      <c r="H57" s="423"/>
+      <c r="I57" s="320"/>
+      <c r="J57" s="320"/>
+      <c r="K57" s="320"/>
+      <c r="L57" s="320"/>
+      <c r="M57" s="320"/>
+      <c r="N57" s="320"/>
+      <c r="O57" s="320"/>
+      <c r="P57" s="320"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -2797,41 +2797,81 @@
     <xf numFmtId="10" fontId="67" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="49" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="49" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="49" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="170" fontId="50" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="49" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="170" fontId="50" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="50" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2847,71 +2887,90 @@
     <xf numFmtId="170" fontId="50" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="49" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="49" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="55" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="52" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2924,88 +2983,22 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="63" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="54" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3015,179 +3008,182 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="171" fontId="22" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="46" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3197,122 +3193,104 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="46" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="46" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="46" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="46" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="37" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="45" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="44" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="44" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="45" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="37" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="37" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="44" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3320,18 +3298,69 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="37" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="39" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="42" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="39" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="39" fontId="45" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="44" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3342,35 +3371,11 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3386,31 +3391,26 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="61" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="68" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="69" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="61" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hiperlink" xfId="4" builtinId="8"/>
@@ -3828,7 +3828,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="242" t="s">
+      <c r="B3" s="244" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="251"/>
@@ -3841,21 +3841,21 @@
       <c r="J3" s="251"/>
       <c r="K3" s="251"/>
       <c r="L3" s="251"/>
-      <c r="M3" s="252"/>
+      <c r="M3" s="256"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="264"/>
-      <c r="C4" s="246"/>
-      <c r="D4" s="246"/>
-      <c r="E4" s="246"/>
-      <c r="F4" s="246"/>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
-      <c r="I4" s="246"/>
-      <c r="J4" s="246"/>
-      <c r="K4" s="246"/>
-      <c r="L4" s="246"/>
-      <c r="M4" s="254"/>
+      <c r="B4" s="257"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="258"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -3886,100 +3886,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="247" t="s">
+      <c r="B7" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="265"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="258"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="248"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="242" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="248"/>
-      <c r="E8" s="265"/>
-      <c r="F8" s="248"/>
-      <c r="G8" s="248"/>
-      <c r="H8" s="248"/>
-      <c r="I8" s="248"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="248"/>
-      <c r="L8" s="248"/>
-      <c r="M8" s="258"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="247"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="243"/>
+      <c r="I8" s="243"/>
+      <c r="J8" s="243"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="243"/>
+      <c r="M8" s="248"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="242" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="248"/>
-      <c r="E9" s="265"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
-      <c r="M9" s="258"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="247"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="248"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="247" t="s">
+      <c r="B10" s="242" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="248"/>
-      <c r="D10" s="248"/>
-      <c r="E10" s="265"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="248"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="248"/>
-      <c r="K10" s="248"/>
-      <c r="L10" s="248"/>
-      <c r="M10" s="258"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="247"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="248"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="247" t="s">
+      <c r="B11" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="265"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
-      <c r="M11" s="258"/>
+      <c r="C11" s="243"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="247"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
+      <c r="K11" s="243"/>
+      <c r="L11" s="243"/>
+      <c r="M11" s="248"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="247" t="s">
+      <c r="B12" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="265"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="258"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="243"/>
+      <c r="E12" s="247"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
+      <c r="K12" s="243"/>
+      <c r="L12" s="243"/>
+      <c r="M12" s="248"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4038,20 +4038,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="276" t="s">
+      <c r="B17" s="249" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
-      <c r="M17" s="248"/>
+      <c r="C17" s="243"/>
+      <c r="D17" s="243"/>
+      <c r="E17" s="243"/>
+      <c r="F17" s="243"/>
+      <c r="G17" s="243"/>
+      <c r="H17" s="243"/>
+      <c r="I17" s="243"/>
+      <c r="J17" s="243"/>
+      <c r="K17" s="243"/>
+      <c r="L17" s="243"/>
+      <c r="M17" s="243"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4068,12 +4068,12 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="277" t="s">
+      <c r="B19" s="250" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="251"/>
       <c r="D19" s="251"/>
-      <c r="E19" s="275"/>
+      <c r="E19" s="255"/>
       <c r="F19" s="251"/>
       <c r="G19" s="251"/>
       <c r="H19" s="251"/>
@@ -4081,137 +4081,137 @@
       <c r="J19" s="251"/>
       <c r="K19" s="251"/>
       <c r="L19" s="251"/>
-      <c r="M19" s="252"/>
+      <c r="M19" s="256"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="242" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="248"/>
-      <c r="D20" s="248"/>
-      <c r="E20" s="265"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="248"/>
-      <c r="H20" s="248"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="248"/>
-      <c r="K20" s="248"/>
-      <c r="L20" s="248"/>
-      <c r="M20" s="258"/>
+      <c r="C20" s="243"/>
+      <c r="D20" s="243"/>
+      <c r="E20" s="247"/>
+      <c r="F20" s="243"/>
+      <c r="G20" s="243"/>
+      <c r="H20" s="243"/>
+      <c r="I20" s="243"/>
+      <c r="J20" s="243"/>
+      <c r="K20" s="243"/>
+      <c r="L20" s="243"/>
+      <c r="M20" s="248"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="242" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="248"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="265"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="M21" s="258"/>
+      <c r="C21" s="243"/>
+      <c r="D21" s="243"/>
+      <c r="E21" s="247"/>
+      <c r="F21" s="243"/>
+      <c r="G21" s="243"/>
+      <c r="H21" s="243"/>
+      <c r="I21" s="243"/>
+      <c r="J21" s="243"/>
+      <c r="K21" s="243"/>
+      <c r="L21" s="243"/>
+      <c r="M21" s="248"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="272" t="s">
+      <c r="B22" s="265" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="246"/>
-      <c r="D22" s="246"/>
-      <c r="E22" s="266"/>
-      <c r="F22" s="246"/>
-      <c r="G22" s="246"/>
-      <c r="H22" s="246"/>
-      <c r="I22" s="246"/>
-      <c r="J22" s="246"/>
+      <c r="C22" s="254"/>
+      <c r="D22" s="254"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="254"/>
+      <c r="I22" s="254"/>
+      <c r="J22" s="254"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="270"/>
-      <c r="M22" s="254"/>
+      <c r="L22" s="263"/>
+      <c r="M22" s="258"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="242" t="s">
+      <c r="B23" s="244" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="243"/>
-      <c r="D23" s="243"/>
-      <c r="E23" s="243"/>
-      <c r="F23" s="243"/>
-      <c r="G23" s="243"/>
-      <c r="H23" s="243"/>
-      <c r="I23" s="243"/>
-      <c r="J23" s="243"/>
-      <c r="K23" s="243"/>
-      <c r="L23" s="243"/>
-      <c r="M23" s="244"/>
+      <c r="C23" s="245"/>
+      <c r="D23" s="245"/>
+      <c r="E23" s="245"/>
+      <c r="F23" s="245"/>
+      <c r="G23" s="245"/>
+      <c r="H23" s="245"/>
+      <c r="I23" s="245"/>
+      <c r="J23" s="245"/>
+      <c r="K23" s="245"/>
+      <c r="L23" s="245"/>
+      <c r="M23" s="246"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="255" t="s">
+      <c r="B24" s="252" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="243"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="255" t="s">
+      <c r="C24" s="245"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="252" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="243"/>
-      <c r="G24" s="244"/>
-      <c r="H24" s="255" t="s">
+      <c r="F24" s="245"/>
+      <c r="G24" s="246"/>
+      <c r="H24" s="252" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="243"/>
-      <c r="J24" s="244"/>
-      <c r="K24" s="255" t="s">
+      <c r="I24" s="245"/>
+      <c r="J24" s="246"/>
+      <c r="K24" s="252" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="243"/>
-      <c r="M24" s="244"/>
+      <c r="L24" s="245"/>
+      <c r="M24" s="246"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="269"/>
+      <c r="B25" s="262"/>
       <c r="C25" s="251"/>
-      <c r="D25" s="252"/>
-      <c r="E25" s="256"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="250"/>
+      <c r="D25" s="256"/>
+      <c r="E25" s="271"/>
+      <c r="F25" s="243"/>
+      <c r="G25" s="243"/>
+      <c r="H25" s="269"/>
       <c r="I25" s="251"/>
-      <c r="J25" s="252"/>
-      <c r="K25" s="271"/>
+      <c r="J25" s="256"/>
+      <c r="K25" s="264"/>
       <c r="L25" s="251"/>
-      <c r="M25" s="252"/>
+      <c r="M25" s="256"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="267"/>
-      <c r="C26" s="246"/>
-      <c r="D26" s="254"/>
-      <c r="E26" s="274"/>
-      <c r="F26" s="246"/>
-      <c r="G26" s="246"/>
-      <c r="H26" s="268"/>
-      <c r="I26" s="246"/>
-      <c r="J26" s="254"/>
-      <c r="K26" s="273"/>
-      <c r="L26" s="246"/>
-      <c r="M26" s="254"/>
+      <c r="B26" s="260"/>
+      <c r="C26" s="254"/>
+      <c r="D26" s="258"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="254"/>
+      <c r="G26" s="254"/>
+      <c r="H26" s="261"/>
+      <c r="I26" s="254"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="266"/>
+      <c r="L26" s="254"/>
+      <c r="M26" s="258"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="242" t="s">
+      <c r="B27" s="244" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="243"/>
-      <c r="D27" s="243"/>
-      <c r="E27" s="243"/>
-      <c r="F27" s="243"/>
-      <c r="G27" s="243"/>
-      <c r="H27" s="243"/>
-      <c r="I27" s="243"/>
-      <c r="J27" s="243"/>
-      <c r="K27" s="243"/>
-      <c r="L27" s="243"/>
-      <c r="M27" s="244"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
+      <c r="M27" s="246"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4298,100 +4298,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="242" t="s">
+      <c r="B34" s="244" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="243"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="244"/>
+      <c r="C34" s="245"/>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="245"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="245"/>
+      <c r="I34" s="245"/>
+      <c r="J34" s="245"/>
+      <c r="K34" s="245"/>
+      <c r="L34" s="245"/>
+      <c r="M34" s="246"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="255" t="s">
+      <c r="B35" s="252" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="243"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="244"/>
-      <c r="F35" s="255" t="s">
+      <c r="C35" s="245"/>
+      <c r="D35" s="245"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="243"/>
-      <c r="H35" s="243"/>
-      <c r="I35" s="244"/>
-      <c r="J35" s="255" t="s">
+      <c r="G35" s="245"/>
+      <c r="H35" s="245"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="252" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="243"/>
-      <c r="L35" s="243"/>
-      <c r="M35" s="244"/>
+      <c r="K35" s="245"/>
+      <c r="L35" s="245"/>
+      <c r="M35" s="246"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="261"/>
+      <c r="B36" s="275"/>
       <c r="C36" s="251"/>
       <c r="D36" s="251"/>
       <c r="E36" s="251"/>
-      <c r="F36" s="262"/>
+      <c r="F36" s="276"/>
       <c r="G36" s="251"/>
       <c r="H36" s="251"/>
       <c r="I36" s="251"/>
-      <c r="J36" s="263"/>
+      <c r="J36" s="277"/>
       <c r="K36" s="251"/>
       <c r="L36" s="251"/>
-      <c r="M36" s="252"/>
+      <c r="M36" s="256"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="249"/>
-      <c r="C37" s="248"/>
-      <c r="D37" s="248"/>
-      <c r="E37" s="248"/>
-      <c r="F37" s="260"/>
-      <c r="G37" s="248"/>
-      <c r="H37" s="248"/>
-      <c r="I37" s="248"/>
-      <c r="J37" s="257"/>
-      <c r="K37" s="248"/>
-      <c r="L37" s="248"/>
-      <c r="M37" s="258"/>
+      <c r="B37" s="268"/>
+      <c r="C37" s="243"/>
+      <c r="D37" s="243"/>
+      <c r="E37" s="243"/>
+      <c r="F37" s="274"/>
+      <c r="G37" s="243"/>
+      <c r="H37" s="243"/>
+      <c r="I37" s="243"/>
+      <c r="J37" s="272"/>
+      <c r="K37" s="243"/>
+      <c r="L37" s="243"/>
+      <c r="M37" s="248"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="259" t="s">
+      <c r="B38" s="273" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="246"/>
-      <c r="D38" s="246"/>
-      <c r="E38" s="246"/>
-      <c r="F38" s="245"/>
-      <c r="G38" s="246"/>
-      <c r="H38" s="246"/>
-      <c r="I38" s="246"/>
-      <c r="J38" s="253"/>
-      <c r="K38" s="246"/>
-      <c r="L38" s="246"/>
-      <c r="M38" s="254"/>
+      <c r="C38" s="254"/>
+      <c r="D38" s="254"/>
+      <c r="E38" s="254"/>
+      <c r="F38" s="267"/>
+      <c r="G38" s="254"/>
+      <c r="H38" s="254"/>
+      <c r="I38" s="254"/>
+      <c r="J38" s="270"/>
+      <c r="K38" s="254"/>
+      <c r="L38" s="254"/>
+      <c r="M38" s="258"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="244" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="243"/>
-      <c r="D39" s="243"/>
-      <c r="E39" s="243"/>
-      <c r="F39" s="243"/>
-      <c r="G39" s="243"/>
-      <c r="H39" s="243"/>
-      <c r="I39" s="243"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="243"/>
-      <c r="L39" s="243"/>
-      <c r="M39" s="244"/>
+      <c r="C39" s="245"/>
+      <c r="D39" s="245"/>
+      <c r="E39" s="245"/>
+      <c r="F39" s="245"/>
+      <c r="G39" s="245"/>
+      <c r="H39" s="245"/>
+      <c r="I39" s="245"/>
+      <c r="J39" s="245"/>
+      <c r="K39" s="245"/>
+      <c r="L39" s="245"/>
+      <c r="M39" s="246"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4507,25 +4507,22 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B39:M39"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="B34:M34"/>
     <mergeCell ref="B3:M4"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
@@ -4542,22 +4539,25 @@
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B39:M39"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="B34:M34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4581,24 +4581,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="436" t="s">
+      <c r="B1" s="448" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="437"/>
-      <c r="D1" s="437"/>
-      <c r="E1" s="437"/>
-      <c r="F1" s="437"/>
-      <c r="G1" s="437"/>
-      <c r="H1" s="438"/>
+      <c r="C1" s="449"/>
+      <c r="D1" s="449"/>
+      <c r="E1" s="449"/>
+      <c r="F1" s="449"/>
+      <c r="G1" s="449"/>
+      <c r="H1" s="450"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="432"/>
-      <c r="C2" s="433"/>
-      <c r="D2" s="433"/>
-      <c r="E2" s="433"/>
-      <c r="F2" s="433"/>
-      <c r="G2" s="433"/>
-      <c r="H2" s="434"/>
+      <c r="B2" s="445"/>
+      <c r="C2" s="446"/>
+      <c r="D2" s="446"/>
+      <c r="E2" s="446"/>
+      <c r="F2" s="446"/>
+      <c r="G2" s="446"/>
+      <c r="H2" s="447"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -4633,32 +4633,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="441" t="s">
+      <c r="B6" s="438" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="443" t="s">
+      <c r="C6" s="440" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="445" t="s">
+      <c r="D6" s="436" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="446" t="s">
+      <c r="E6" s="442" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="446" t="s">
+      <c r="F6" s="442" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="439" t="s">
+      <c r="G6" s="433" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="440"/>
+      <c r="H6" s="434"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="442"/>
-      <c r="C7" s="444"/>
-      <c r="D7" s="444"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="254"/>
+      <c r="B7" s="439"/>
+      <c r="C7" s="437"/>
+      <c r="D7" s="437"/>
+      <c r="E7" s="258"/>
+      <c r="F7" s="258"/>
       <c r="G7" s="47" t="s">
         <v>265</v>
       </c>
@@ -4679,14 +4679,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="447" t="s">
+      <c r="B9" s="435" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="243"/>
-      <c r="D9" s="243"/>
-      <c r="E9" s="243"/>
-      <c r="F9" s="243"/>
-      <c r="G9" s="244"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="246"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -4704,32 +4704,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="441" t="s">
+      <c r="B11" s="438" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="443" t="s">
+      <c r="C11" s="440" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="445" t="s">
+      <c r="D11" s="436" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="435" t="s">
+      <c r="E11" s="441" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="435" t="s">
+      <c r="F11" s="441" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="439" t="s">
+      <c r="G11" s="433" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="440"/>
+      <c r="H11" s="434"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="442"/>
-      <c r="C12" s="444"/>
-      <c r="D12" s="444"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="254"/>
+      <c r="B12" s="439"/>
+      <c r="C12" s="437"/>
+      <c r="D12" s="437"/>
+      <c r="E12" s="258"/>
+      <c r="F12" s="258"/>
       <c r="G12" s="47" t="s">
         <v>265</v>
       </c>
@@ -4750,14 +4750,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="447" t="s">
+      <c r="B14" s="435" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="243"/>
-      <c r="D14" s="243"/>
-      <c r="E14" s="243"/>
-      <c r="F14" s="243"/>
-      <c r="G14" s="244"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="246"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -4775,32 +4775,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="441" t="s">
+      <c r="B16" s="438" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="443" t="s">
+      <c r="C16" s="440" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="445" t="s">
+      <c r="D16" s="436" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="435" t="s">
+      <c r="E16" s="441" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="435" t="s">
+      <c r="F16" s="441" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="439" t="s">
+      <c r="G16" s="433" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="440"/>
+      <c r="H16" s="434"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="442"/>
-      <c r="C17" s="444"/>
-      <c r="D17" s="444"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="254"/>
+      <c r="B17" s="439"/>
+      <c r="C17" s="437"/>
+      <c r="D17" s="437"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="258"/>
       <c r="G17" s="22" t="s">
         <v>265</v>
       </c>
@@ -4823,14 +4823,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="447" t="s">
+      <c r="B19" s="435" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="243"/>
-      <c r="D19" s="243"/>
-      <c r="E19" s="243"/>
-      <c r="F19" s="243"/>
-      <c r="G19" s="244"/>
+      <c r="C19" s="245"/>
+      <c r="D19" s="245"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="245"/>
+      <c r="G19" s="246"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -4848,32 +4848,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="441" t="s">
+      <c r="B21" s="438" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="443" t="s">
+      <c r="C21" s="440" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="445" t="s">
+      <c r="D21" s="436" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="435" t="s">
+      <c r="E21" s="441" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="435" t="s">
+      <c r="F21" s="441" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="439" t="s">
+      <c r="G21" s="433" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="440"/>
+      <c r="H21" s="434"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="442"/>
-      <c r="C22" s="444"/>
-      <c r="D22" s="444"/>
-      <c r="E22" s="254"/>
-      <c r="F22" s="254"/>
+      <c r="B22" s="439"/>
+      <c r="C22" s="437"/>
+      <c r="D22" s="437"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
       <c r="G22" s="47" t="s">
         <v>265</v>
       </c>
@@ -4894,32 +4894,18 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="430" t="s">
+      <c r="B24" s="443" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="431"/>
-      <c r="D24" s="431"/>
-      <c r="E24" s="431"/>
-      <c r="F24" s="431"/>
+      <c r="C24" s="444"/>
+      <c r="D24" s="444"/>
+      <c r="E24" s="444"/>
+      <c r="F24" s="444"/>
       <c r="G24" s="380"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -4936,6 +4922,20 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -4961,14 +4961,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="450" t="s">
+      <c r="B1" s="453" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="433"/>
-      <c r="D1" s="433"/>
-      <c r="E1" s="433"/>
-      <c r="F1" s="433"/>
-      <c r="G1" s="433"/>
+      <c r="C1" s="446"/>
+      <c r="D1" s="446"/>
+      <c r="E1" s="446"/>
+      <c r="F1" s="446"/>
+      <c r="G1" s="446"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -4992,40 +4992,40 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="451" t="s">
+      <c r="B4" s="454" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="D4" s="243"/>
-      <c r="E4" s="243"/>
-      <c r="F4" s="243"/>
-      <c r="G4" s="244"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="246"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="452" t="s">
+      <c r="B5" s="455" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="448" t="s">
+      <c r="C5" s="451" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="448" t="s">
+      <c r="D5" s="451" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="448" t="s">
+      <c r="E5" s="451" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="449" t="s">
+      <c r="F5" s="452" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="243"/>
+      <c r="G5" s="245"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="254"/>
-      <c r="C6" s="444"/>
-      <c r="D6" s="444"/>
-      <c r="E6" s="444"/>
+      <c r="B6" s="258"/>
+      <c r="C6" s="437"/>
+      <c r="D6" s="437"/>
+      <c r="E6" s="437"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -5077,151 +5077,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="460" t="s">
+      <c r="A1" s="461" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="453"/>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="248"/>
-      <c r="S1" s="248"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="243"/>
+      <c r="N1" s="243"/>
+      <c r="O1" s="462"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
+      <c r="S1" s="243"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="458" t="s">
+      <c r="A2" s="463" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="458" t="s">
+      <c r="B2" s="243"/>
+      <c r="C2" s="463" t="s">
         <v>278</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
       <c r="J2" s="459" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="455" t="s">
+      <c r="A3" s="460" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="455" t="s">
+      <c r="B3" s="243"/>
+      <c r="C3" s="460" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="248"/>
-      <c r="J3" s="455" t="s">
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="M3" s="248"/>
-      <c r="N3" s="248"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="M3" s="243"/>
+      <c r="N3" s="243"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="455" t="s">
+      <c r="A4" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="248"/>
-      <c r="C4" s="455" t="s">
+      <c r="B4" s="243"/>
+      <c r="C4" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="457"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="M4" s="248"/>
-      <c r="N4" s="248"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="458"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="M4" s="243"/>
+      <c r="N4" s="243"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="455" t="s">
+      <c r="A5" s="460" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="248"/>
-      <c r="C5" s="455" t="s">
+      <c r="B5" s="243"/>
+      <c r="C5" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="457"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="M5" s="248"/>
-      <c r="N5" s="248"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="458"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="455" t="s">
+      <c r="A6" s="460" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="248"/>
-      <c r="C6" s="455" t="s">
+      <c r="B6" s="243"/>
+      <c r="C6" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
-      <c r="I6" s="248"/>
-      <c r="J6" s="455" t="s">
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="460" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="248"/>
-      <c r="L6" s="248"/>
-      <c r="M6" s="248"/>
-      <c r="N6" s="248"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="454" t="s">
+      <c r="A7" s="457" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="248"/>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="248"/>
-      <c r="N7" s="248"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="243"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -5247,141 +5247,123 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="454" t="s">
+      <c r="A31" s="457" t="s">
         <v>288</v>
       </c>
-      <c r="B31" s="248"/>
-      <c r="C31" s="248"/>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
-      <c r="M31" s="248"/>
-      <c r="N31" s="248"/>
+      <c r="B31" s="243"/>
+      <c r="C31" s="243"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="243"/>
+      <c r="I31" s="243"/>
+      <c r="J31" s="243"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="243"/>
+      <c r="M31" s="243"/>
+      <c r="N31" s="243"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="456" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="248"/>
-      <c r="C32" s="248"/>
+      <c r="B32" s="243"/>
+      <c r="C32" s="243"/>
       <c r="D32" s="456" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="248"/>
-      <c r="F32" s="248"/>
+      <c r="E32" s="243"/>
+      <c r="F32" s="243"/>
       <c r="G32" s="456" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="248"/>
-      <c r="I32" s="248"/>
+      <c r="H32" s="243"/>
+      <c r="I32" s="243"/>
       <c r="J32" s="456" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="248"/>
-      <c r="L32" s="248"/>
-      <c r="M32" s="248"/>
+      <c r="K32" s="243"/>
+      <c r="L32" s="243"/>
+      <c r="M32" s="243"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="456" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="248"/>
-      <c r="C33" s="248"/>
+      <c r="B33" s="243"/>
+      <c r="C33" s="243"/>
       <c r="D33" s="456" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
       <c r="G33" s="456" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
+      <c r="H33" s="243"/>
+      <c r="I33" s="243"/>
       <c r="J33" s="456" t="s">
         <v>293</v>
       </c>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
-      <c r="M33" s="248"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="243"/>
+      <c r="M33" s="243"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="454" t="s">
+      <c r="A34" s="457" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="248"/>
-      <c r="C34" s="248"/>
-      <c r="D34" s="248"/>
-      <c r="E34" s="248"/>
-      <c r="F34" s="248"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="248"/>
-      <c r="I34" s="248"/>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
+      <c r="B34" s="243"/>
+      <c r="C34" s="243"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="243"/>
+      <c r="G34" s="243"/>
+      <c r="H34" s="243"/>
+      <c r="I34" s="243"/>
+      <c r="J34" s="243"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="243"/>
+      <c r="M34" s="243"/>
+      <c r="N34" s="243"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="456" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="248"/>
-      <c r="C35" s="248"/>
+      <c r="B35" s="243"/>
+      <c r="C35" s="243"/>
       <c r="F35" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="G35" s="248"/>
-      <c r="H35" s="248"/>
+      <c r="G35" s="243"/>
+      <c r="H35" s="243"/>
       <c r="K35" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="L35" s="248"/>
-      <c r="M35" s="248"/>
+      <c r="L35" s="243"/>
+      <c r="M35" s="243"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="456" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="248"/>
-      <c r="C36" s="248"/>
+      <c r="B36" s="243"/>
+      <c r="C36" s="243"/>
       <c r="F36" s="456" t="s">
         <v>296</v>
       </c>
-      <c r="G36" s="248"/>
-      <c r="H36" s="248"/>
+      <c r="G36" s="243"/>
+      <c r="H36" s="243"/>
       <c r="K36" s="456" t="s">
         <v>297</v>
       </c>
-      <c r="L36" s="248"/>
-      <c r="M36" s="248"/>
+      <c r="L36" s="243"/>
+      <c r="M36" s="243"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -5398,6 +5380,24 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5701,7 +5701,7 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="280" t="str">
+      <c r="C4" s="306" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -5730,22 +5730,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="295" t="s">
+      <c r="C5" s="304" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="254"/>
-      <c r="E5" s="295" t="s">
+      <c r="D5" s="258"/>
+      <c r="E5" s="304" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="254"/>
-      <c r="G5" s="295" t="s">
+      <c r="F5" s="258"/>
+      <c r="G5" s="304" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="254"/>
-      <c r="I5" s="293" t="s">
+      <c r="H5" s="258"/>
+      <c r="I5" s="297" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="254"/>
+      <c r="J5" s="258"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -5759,23 +5759,23 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="283">
+      <c r="C6" s="280">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="244"/>
-      <c r="E6" s="286" t="s">
+      <c r="D6" s="246"/>
+      <c r="E6" s="303" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="244"/>
-      <c r="G6" s="284" t="s">
+      <c r="F6" s="246"/>
+      <c r="G6" s="305" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="244"/>
-      <c r="I6" s="297" t="s">
+      <c r="H6" s="246"/>
+      <c r="I6" s="282" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="244"/>
+      <c r="J6" s="246"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -5795,16 +5795,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="281" t="s">
+      <c r="C7" s="302" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="243"/>
-      <c r="E7" s="243"/>
-      <c r="F7" s="243"/>
-      <c r="G7" s="243"/>
-      <c r="H7" s="243"/>
-      <c r="I7" s="243"/>
-      <c r="J7" s="244"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="245"/>
+      <c r="J7" s="246"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -5821,22 +5821,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="285" t="s">
+      <c r="C8" s="283" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="244"/>
-      <c r="E8" s="285" t="s">
+      <c r="D8" s="246"/>
+      <c r="E8" s="283" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="244"/>
-      <c r="G8" s="285" t="s">
+      <c r="F8" s="246"/>
+      <c r="G8" s="283" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="244"/>
-      <c r="I8" s="294" t="s">
+      <c r="H8" s="246"/>
+      <c r="I8" s="301" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="244"/>
+      <c r="J8" s="246"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -5848,22 +5848,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="286">
+      <c r="C9" s="303">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="284" t="s">
+      <c r="D9" s="246"/>
+      <c r="E9" s="305" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="244"/>
-      <c r="G9" s="283">
+      <c r="F9" s="246"/>
+      <c r="G9" s="280">
         <v>80</v>
       </c>
-      <c r="H9" s="244"/>
-      <c r="I9" s="297">
+      <c r="H9" s="246"/>
+      <c r="I9" s="282">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="244"/>
+      <c r="J9" s="246"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -5875,16 +5875,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="281" t="s">
+      <c r="C10" s="302" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="243"/>
-      <c r="E10" s="243"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="243"/>
-      <c r="H10" s="243"/>
-      <c r="I10" s="243"/>
-      <c r="J10" s="244"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="246"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -5896,156 +5896,187 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="285" t="s">
+      <c r="C11" s="283" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="285" t="s">
+      <c r="D11" s="246"/>
+      <c r="E11" s="283" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="244"/>
-      <c r="G11" s="285" t="s">
+      <c r="F11" s="246"/>
+      <c r="G11" s="283" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="244"/>
-      <c r="I11" s="294" t="s">
+      <c r="H11" s="246"/>
+      <c r="I11" s="301" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="244"/>
+      <c r="J11" s="246"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="286">
+      <c r="C12" s="303">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="244"/>
-      <c r="E12" s="286">
+      <c r="D12" s="246"/>
+      <c r="E12" s="303">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="244"/>
-      <c r="G12" s="284">
+      <c r="F12" s="246"/>
+      <c r="G12" s="305">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="244"/>
-      <c r="I12" s="287">
+      <c r="H12" s="246"/>
+      <c r="I12" s="308">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="244"/>
+      <c r="J12" s="246"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="285" t="s">
+      <c r="C13" s="283" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="284" t="s">
+      <c r="D13" s="246"/>
+      <c r="E13" s="305" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="244"/>
-      <c r="G13" s="285" t="s">
+      <c r="F13" s="246"/>
+      <c r="G13" s="283" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="244"/>
-      <c r="I13" s="297" t="s">
+      <c r="H13" s="246"/>
+      <c r="I13" s="282" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="244"/>
+      <c r="J13" s="246"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="461" t="s">
+      <c r="C16" s="298" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="462"/>
-      <c r="E16" s="462"/>
-      <c r="F16" s="462"/>
-      <c r="G16" s="462"/>
-      <c r="H16" s="462"/>
-      <c r="I16" s="463"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
+      <c r="F16" s="299"/>
+      <c r="G16" s="299"/>
+      <c r="H16" s="299"/>
+      <c r="I16" s="300"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="281" t="s">
+      <c r="C17" s="302" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="243"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="281" t="s">
+      <c r="D17" s="245"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="302" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="244"/>
-      <c r="H17" s="281" t="s">
+      <c r="G17" s="246"/>
+      <c r="H17" s="302" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="244"/>
+      <c r="I17" s="246"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="303" t="s">
+      <c r="C18" s="289" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="304"/>
-      <c r="E18" s="305"/>
-      <c r="F18" s="307">
+      <c r="D18" s="290"/>
+      <c r="E18" s="291"/>
+      <c r="F18" s="293">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="308"/>
-      <c r="H18" s="291">
+      <c r="G18" s="294"/>
+      <c r="H18" s="295">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="292"/>
+      <c r="I18" s="296"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="306" t="s">
+      <c r="C19" s="292" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="243"/>
-      <c r="E19" s="244"/>
-      <c r="F19" s="283">
+      <c r="D19" s="245"/>
+      <c r="E19" s="246"/>
+      <c r="F19" s="280">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="244"/>
-      <c r="H19" s="296">
+      <c r="G19" s="246"/>
+      <c r="H19" s="281">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="244"/>
+      <c r="I19" s="246"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="288" t="s">
+      <c r="C20" s="309" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="289"/>
-      <c r="E20" s="290"/>
-      <c r="F20" s="301">
+      <c r="D20" s="310"/>
+      <c r="E20" s="311"/>
+      <c r="F20" s="287">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="302"/>
-      <c r="H20" s="299">
+      <c r="G20" s="288"/>
+      <c r="H20" s="285">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="300"/>
+      <c r="I20" s="286"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="298" t="s">
+      <c r="C21" s="284" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="243"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="282">
+      <c r="D21" s="245"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="307">
         <f>SUM(F18:G20)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G21" s="244"/>
-      <c r="H21" s="296">
+      <c r="G21" s="246"/>
+      <c r="H21" s="281">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="244"/>
+      <c r="I21" s="246"/>
       <c r="J21" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="I6:J6"/>
@@ -6062,37 +6093,6 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C20:E20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6120,7 +6120,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="327" t="s">
+      <c r="B3" s="338" t="s">
         <v>84</v>
       </c>
       <c r="C3" s="279"/>
@@ -6130,28 +6130,28 @@
       <c r="G3" s="279"/>
       <c r="H3" s="279"/>
       <c r="I3" s="279"/>
-      <c r="L3" s="370" t="s">
+      <c r="L3" s="312" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="244"/>
+      <c r="M3" s="246"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="319" t="s">
+      <c r="B4" s="318" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="320"/>
-      <c r="D4" s="320"/>
-      <c r="E4" s="372" t="s">
+      <c r="C4" s="319"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="330" t="s">
         <v>298</v>
       </c>
       <c r="F4" s="279"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="340" t="s">
+      <c r="H4" s="354" t="s">
         <v>299</v>
       </c>
-      <c r="I4" s="258"/>
+      <c r="I4" s="248"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>88</v>
@@ -6162,22 +6162,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="317" t="s">
+      <c r="B5" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="279"/>
       <c r="D5" s="279"/>
-      <c r="E5" s="334" t="s">
+      <c r="E5" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F5" s="279"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="340" t="s">
+      <c r="H5" s="354" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="258"/>
+      <c r="I5" s="248"/>
       <c r="L5" s="153" t="s">
         <v>92</v>
       </c>
@@ -6187,57 +6187,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="317" t="s">
+      <c r="B6" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="279"/>
       <c r="D6" s="279"/>
-      <c r="E6" s="359">
+      <c r="E6" s="356">
         <v>52.034300000000002</v>
       </c>
       <c r="F6" s="279"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="345" t="s">
+      <c r="H6" s="372" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="258"/>
+      <c r="I6" s="248"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="333" t="s">
+      <c r="C7" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="279"/>
-      <c r="E7" s="352" t="s">
+      <c r="E7" s="363" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="279"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="316">
+      <c r="H7" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I7" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I7" s="248"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="333" t="s">
+      <c r="C8" s="315" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="279"/>
-      <c r="E8" s="358">
+      <c r="E8" s="353">
         <v>11173</v>
       </c>
       <c r="F8" s="279"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="335"/>
-      <c r="I8" s="258"/>
+      <c r="H8" s="345"/>
+      <c r="I8" s="248"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -6245,7 +6245,7 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="323" t="s">
+      <c r="B9" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="279"/>
@@ -6254,7 +6254,7 @@
       <c r="F9" s="279"/>
       <c r="G9" s="279"/>
       <c r="H9" s="279"/>
-      <c r="I9" s="258"/>
+      <c r="I9" s="248"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -6262,7 +6262,7 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="332" t="s">
+      <c r="B10" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="279"/>
@@ -6273,7 +6273,7 @@
       <c r="F10" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="324" t="s">
+      <c r="G10" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H10" s="279"/>
@@ -6285,11 +6285,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="367" t="s">
+      <c r="B11" s="341" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="368"/>
-      <c r="D11" s="368"/>
+      <c r="C11" s="342"/>
+      <c r="D11" s="342"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -6297,10 +6297,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="369">
+      <c r="G11" s="343">
         <v>1</v>
       </c>
-      <c r="H11" s="369"/>
+      <c r="H11" s="343"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -6309,7 +6309,7 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="357" t="s">
+      <c r="B12" s="352" t="s">
         <v>117</v>
       </c>
       <c r="C12" s="279"/>
@@ -6322,7 +6322,7 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="313">
+      <c r="G12" s="317">
         <v>0.8</v>
       </c>
       <c r="H12" s="279"/>
@@ -6334,7 +6334,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="353" t="s">
+      <c r="B13" s="364" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="279"/>
@@ -6347,7 +6347,7 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="313">
+      <c r="G13" s="317">
         <v>0.6</v>
       </c>
       <c r="H13" s="279"/>
@@ -6363,11 +6363,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="318" t="s">
+      <c r="B14" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="246"/>
-      <c r="D14" s="246"/>
+      <c r="C14" s="254"/>
+      <c r="D14" s="254"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -6376,11 +6376,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="309">
+      <c r="G14" s="340">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="246"/>
+      <c r="H14" s="254"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -6404,7 +6404,7 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="327" t="s">
+      <c r="B16" s="338" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="279"/>
@@ -6417,52 +6417,52 @@
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="319" t="s">
+      <c r="B17" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="320"/>
-      <c r="D17" s="320"/>
-      <c r="E17" s="311" t="s">
+      <c r="C17" s="319"/>
+      <c r="D17" s="319"/>
+      <c r="E17" s="316" t="s">
         <v>110</v>
       </c>
       <c r="F17" s="279"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="341" t="s">
+      <c r="H17" s="328" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="258"/>
+      <c r="I17" s="248"/>
       <c r="K17" s="203" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="317" t="s">
+      <c r="B18" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="279"/>
       <c r="D18" s="279"/>
-      <c r="E18" s="334" t="s">
+      <c r="E18" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="279"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="344" t="s">
+      <c r="H18" s="326" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="258"/>
+      <c r="I18" s="248"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="317" t="s">
+      <c r="B19" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C19" s="279"/>
       <c r="D19" s="279"/>
-      <c r="E19" s="351">
+      <c r="E19" s="355">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
@@ -6470,18 +6470,18 @@
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="314" t="s">
+      <c r="H19" s="347" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="258"/>
+      <c r="I19" s="248"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="333" t="s">
+      <c r="C20" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D20" s="279"/>
-      <c r="E20" s="339">
+      <c r="E20" s="361">
         <f>180000000</f>
         <v>180000000</v>
       </c>
@@ -6489,11 +6489,11 @@
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="315">
+      <c r="H20" s="350">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="258"/>
+      <c r="I20" s="248"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -6501,42 +6501,42 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="333" t="s">
+      <c r="C21" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="279"/>
-      <c r="E21" s="355" t="s">
+      <c r="E21" s="322" t="s">
         <v>116</v>
       </c>
       <c r="F21" s="279"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="316">
+      <c r="H21" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I21" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I21" s="248"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="333" t="s">
+      <c r="C22" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="279"/>
-      <c r="E22" s="311" t="s">
+      <c r="E22" s="316" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="279"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="346"/>
-      <c r="I22" s="258"/>
+      <c r="H22" s="358"/>
+      <c r="I22" s="248"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="323" t="s">
+      <c r="B23" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="279"/>
@@ -6545,10 +6545,10 @@
       <c r="F23" s="279"/>
       <c r="G23" s="279"/>
       <c r="H23" s="279"/>
-      <c r="I23" s="258"/>
+      <c r="I23" s="248"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="332" t="s">
+      <c r="B24" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="279"/>
@@ -6559,14 +6559,14 @@
       <c r="F24" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="324" t="s">
+      <c r="G24" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H24" s="279"/>
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="321" t="s">
+      <c r="B25" s="325" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="279"/>
@@ -6579,7 +6579,7 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="322">
+      <c r="G25" s="331">
         <v>1</v>
       </c>
       <c r="H25" s="279"/>
@@ -6599,14 +6599,14 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="322">
+      <c r="G26" s="331">
         <v>0.8</v>
       </c>
       <c r="H26" s="279"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="348" t="s">
+      <c r="B27" s="365" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="279"/>
@@ -6619,18 +6619,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="322">
+      <c r="G27" s="331">
         <v>0.6</v>
       </c>
       <c r="H27" s="279"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="318" t="s">
+      <c r="B28" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="246"/>
-      <c r="D28" s="246"/>
+      <c r="C28" s="254"/>
+      <c r="D28" s="254"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -6639,11 +6639,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="309">
+      <c r="G28" s="340">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="246"/>
+      <c r="H28" s="254"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -6657,7 +6657,7 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="327" t="s">
+      <c r="B30" s="338" t="s">
         <v>118</v>
       </c>
       <c r="C30" s="279"/>
@@ -6669,83 +6669,83 @@
       <c r="I30" s="279"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="319" t="s">
+      <c r="B31" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="320"/>
-      <c r="D31" s="320"/>
-      <c r="E31" s="311" t="s">
+      <c r="C31" s="319"/>
+      <c r="D31" s="319"/>
+      <c r="E31" s="316" t="s">
         <v>119</v>
       </c>
       <c r="F31" s="279"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="341" t="s">
+      <c r="H31" s="328" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="258"/>
+      <c r="I31" s="248"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="317" t="s">
+      <c r="B32" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="279"/>
       <c r="D32" s="279"/>
-      <c r="E32" s="334" t="s">
+      <c r="E32" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F32" s="279"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="344" t="s">
+      <c r="H32" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="258"/>
+      <c r="I32" s="248"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="317" t="s">
+      <c r="B33" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="279"/>
       <c r="D33" s="279"/>
-      <c r="E33" s="342">
+      <c r="E33" s="362">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="279"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="344" t="s">
+      <c r="H33" s="326" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="258"/>
+      <c r="I33" s="248"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="333" t="s">
+      <c r="C34" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="279"/>
-      <c r="E34" s="339">
+      <c r="E34" s="361">
         <v>16900000</v>
       </c>
       <c r="F34" s="279"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="315">
+      <c r="H34" s="350">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="258"/>
+      <c r="I34" s="248"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -6753,41 +6753,41 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="333" t="s">
+      <c r="C35" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D35" s="279"/>
-      <c r="E35" s="355" t="s">
+      <c r="E35" s="322" t="s">
         <v>116</v>
       </c>
       <c r="F35" s="279"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="316">
+      <c r="H35" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I35" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I35" s="248"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="333" t="s">
+      <c r="C36" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="279"/>
-      <c r="E36" s="311" t="s">
+      <c r="E36" s="316" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="279"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="346"/>
-      <c r="I36" s="258"/>
+      <c r="H36" s="358"/>
+      <c r="I36" s="248"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="323" t="s">
+      <c r="B37" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="279"/>
@@ -6796,11 +6796,11 @@
       <c r="F37" s="279"/>
       <c r="G37" s="279"/>
       <c r="H37" s="279"/>
-      <c r="I37" s="258"/>
+      <c r="I37" s="248"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="332" t="s">
+      <c r="B38" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C38" s="279"/>
@@ -6811,14 +6811,14 @@
       <c r="F38" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="324" t="s">
+      <c r="G38" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="279"/>
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="321" t="s">
+      <c r="B39" s="325" t="s">
         <v>106</v>
       </c>
       <c r="C39" s="279"/>
@@ -6830,7 +6830,7 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="322">
+      <c r="G39" s="331">
         <v>1</v>
       </c>
       <c r="H39" s="279"/>
@@ -6850,14 +6850,14 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="322">
+      <c r="G40" s="331">
         <v>0.8</v>
       </c>
       <c r="H40" s="279"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="348" t="s">
+      <c r="B41" s="365" t="s">
         <v>107</v>
       </c>
       <c r="C41" s="279"/>
@@ -6870,18 +6870,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="322">
+      <c r="G41" s="331">
         <v>0.6</v>
       </c>
       <c r="H41" s="279"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="318" t="s">
+      <c r="B42" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="246"/>
-      <c r="D42" s="246"/>
+      <c r="C42" s="254"/>
+      <c r="D42" s="254"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -6890,11 +6890,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="309">
+      <c r="G42" s="340">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="246"/>
+      <c r="H42" s="254"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -6908,7 +6908,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="343" t="s">
+      <c r="B44" s="371" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="279"/>
@@ -6920,81 +6920,81 @@
       <c r="I44" s="279"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="319" t="s">
+      <c r="B45" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="320"/>
-      <c r="D45" s="320"/>
-      <c r="E45" s="334" t="s">
+      <c r="C45" s="319"/>
+      <c r="D45" s="319"/>
+      <c r="E45" s="313" t="s">
         <v>119</v>
       </c>
       <c r="F45" s="279"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="341" t="s">
+      <c r="H45" s="328" t="s">
         <v>120</v>
       </c>
-      <c r="I45" s="258"/>
+      <c r="I45" s="248"/>
       <c r="K45" s="203" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="317" t="s">
+      <c r="B46" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="279"/>
       <c r="D46" s="279"/>
-      <c r="E46" s="334" t="s">
+      <c r="E46" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F46" s="279"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="344" t="s">
+      <c r="H46" s="326" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="258"/>
+      <c r="I46" s="248"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="317" t="s">
+      <c r="B47" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C47" s="279"/>
       <c r="D47" s="279"/>
-      <c r="E47" s="351">
+      <c r="E47" s="355">
         <v>430.76</v>
       </c>
       <c r="F47" s="279"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="314" t="s">
+      <c r="H47" s="347" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="258"/>
+      <c r="I47" s="248"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="333" t="s">
+      <c r="C48" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D48" s="279"/>
-      <c r="E48" s="310">
+      <c r="E48" s="337">
         <v>7120000</v>
       </c>
       <c r="F48" s="279"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="330">
+      <c r="H48" s="351">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="258"/>
+      <c r="I48" s="248"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -7003,42 +7003,42 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="333" t="s">
+      <c r="C49" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="279"/>
-      <c r="E49" s="355" t="s">
+      <c r="E49" s="322" t="s">
         <v>116</v>
       </c>
       <c r="F49" s="279"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="316">
+      <c r="H49" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I49" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I49" s="248"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="333" t="s">
+      <c r="C50" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="279"/>
-      <c r="E50" s="311" t="s">
+      <c r="E50" s="316" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="279"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="335"/>
-      <c r="I50" s="258"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="248"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="323" t="s">
+      <c r="B51" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C51" s="279"/>
@@ -7047,10 +7047,10 @@
       <c r="F51" s="279"/>
       <c r="G51" s="279"/>
       <c r="H51" s="279"/>
-      <c r="I51" s="258"/>
+      <c r="I51" s="248"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="332" t="s">
+      <c r="B52" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="279"/>
@@ -7061,14 +7061,14 @@
       <c r="F52" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="324" t="s">
+      <c r="G52" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H52" s="279"/>
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="321" t="s">
+      <c r="B53" s="325" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="279"/>
@@ -7080,7 +7080,7 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="313">
+      <c r="G53" s="317">
         <v>1</v>
       </c>
       <c r="H53" s="279"/>
@@ -7100,7 +7100,7 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="313">
+      <c r="G54" s="317">
         <v>0.8</v>
       </c>
       <c r="H54" s="279"/>
@@ -7120,18 +7120,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="313">
+      <c r="G55" s="317">
         <v>0.6</v>
       </c>
       <c r="H55" s="279"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="318" t="s">
+      <c r="B56" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="246"/>
-      <c r="D56" s="246"/>
+      <c r="C56" s="254"/>
+      <c r="D56" s="254"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -7140,11 +7140,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="309">
+      <c r="G56" s="340">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="246"/>
+      <c r="H56" s="254"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -7158,7 +7158,7 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="327" t="s">
+      <c r="B58" s="338" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="279"/>
@@ -7171,80 +7171,80 @@
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="319" t="s">
+      <c r="B59" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="320"/>
-      <c r="D59" s="320"/>
-      <c r="E59" s="334" t="s">
+      <c r="C59" s="319"/>
+      <c r="D59" s="319"/>
+      <c r="E59" s="313" t="s">
         <v>126</v>
       </c>
       <c r="F59" s="279"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="354" t="s">
+      <c r="H59" s="357" t="s">
         <v>127</v>
       </c>
-      <c r="I59" s="258"/>
+      <c r="I59" s="248"/>
       <c r="K59" s="203" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="317" t="s">
+      <c r="B60" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C60" s="279"/>
       <c r="D60" s="279"/>
-      <c r="E60" s="334" t="s">
+      <c r="E60" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F60" s="279"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="344" t="s">
+      <c r="H60" s="326" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="258"/>
+      <c r="I60" s="248"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="317" t="s">
+      <c r="B61" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C61" s="279"/>
       <c r="D61" s="279"/>
-      <c r="E61" s="325">
+      <c r="E61" s="359">
         <v>626</v>
       </c>
       <c r="F61" s="279"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="344" t="s">
+      <c r="H61" s="326" t="s">
         <v>129</v>
       </c>
-      <c r="I61" s="258"/>
+      <c r="I61" s="248"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="333" t="s">
+      <c r="C62" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="279"/>
-      <c r="E62" s="349">
+      <c r="E62" s="367">
         <v>10500000</v>
       </c>
       <c r="F62" s="279"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="326">
+      <c r="H62" s="320">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="258"/>
+      <c r="I62" s="248"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -7253,42 +7253,42 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="333" t="s">
+      <c r="C63" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="279"/>
-      <c r="E63" s="347" t="s">
+      <c r="E63" s="366" t="s">
         <v>116</v>
       </c>
       <c r="F63" s="279"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="316">
+      <c r="H63" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I63" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I63" s="248"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="333" t="s">
+      <c r="C64" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D64" s="279"/>
-      <c r="E64" s="311" t="s">
+      <c r="E64" s="316" t="s">
         <v>97</v>
       </c>
       <c r="F64" s="279"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="335"/>
-      <c r="I64" s="258"/>
+      <c r="H64" s="345"/>
+      <c r="I64" s="248"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="323" t="s">
+      <c r="B65" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C65" s="279"/>
@@ -7297,10 +7297,10 @@
       <c r="F65" s="279"/>
       <c r="G65" s="279"/>
       <c r="H65" s="279"/>
-      <c r="I65" s="258"/>
+      <c r="I65" s="248"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="332" t="s">
+      <c r="B66" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="279"/>
@@ -7311,7 +7311,7 @@
       <c r="F66" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="324" t="s">
+      <c r="G66" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H66" s="279"/>
@@ -7330,7 +7330,7 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="313">
+      <c r="G67" s="317">
         <v>1</v>
       </c>
       <c r="H67" s="279"/>
@@ -7349,14 +7349,14 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="313">
+      <c r="G68" s="317">
         <v>0.9</v>
       </c>
       <c r="H68" s="279"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="350" t="s">
+      <c r="B69" s="368" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="279"/>
@@ -7369,18 +7369,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="313">
+      <c r="G69" s="317">
         <v>0.6</v>
       </c>
       <c r="H69" s="279"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="318" t="s">
+      <c r="B70" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="246"/>
-      <c r="D70" s="246"/>
+      <c r="C70" s="254"/>
+      <c r="D70" s="254"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -7389,11 +7389,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="309">
+      <c r="G70" s="340">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="246"/>
+      <c r="H70" s="254"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -7407,7 +7407,7 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="327" t="s">
+      <c r="B72" s="338" t="s">
         <v>131</v>
       </c>
       <c r="C72" s="279"/>
@@ -7419,51 +7419,51 @@
       <c r="I72" s="279"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="319" t="s">
+      <c r="B73" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="320"/>
-      <c r="D73" s="320"/>
-      <c r="E73" s="311" t="s">
+      <c r="C73" s="319"/>
+      <c r="D73" s="319"/>
+      <c r="E73" s="316" t="s">
         <v>132</v>
       </c>
       <c r="F73" s="279"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="341" t="s">
+      <c r="H73" s="328" t="s">
         <v>133</v>
       </c>
-      <c r="I73" s="258"/>
+      <c r="I73" s="248"/>
       <c r="K73" s="203" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="317" t="s">
+      <c r="B74" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="279"/>
       <c r="D74" s="279"/>
-      <c r="E74" s="311" t="s">
+      <c r="E74" s="316" t="s">
         <v>135</v>
       </c>
       <c r="F74" s="279"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="344" t="s">
+      <c r="H74" s="326" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="258"/>
+      <c r="I74" s="248"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="317" t="s">
+      <c r="B75" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C75" s="279"/>
       <c r="D75" s="279"/>
-      <c r="E75" s="328">
+      <c r="E75" s="375">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -7471,48 +7471,48 @@
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="314" t="s">
+      <c r="H75" s="347" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="258"/>
+      <c r="I75" s="248"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="333" t="s">
+      <c r="C76" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D76" s="279"/>
-      <c r="E76" s="310">
+      <c r="E76" s="337">
         <v>60000000</v>
       </c>
       <c r="F76" s="279"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="330">
+      <c r="H76" s="351">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="258"/>
+      <c r="I76" s="248"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="333" t="s">
+      <c r="C77" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D77" s="279"/>
-      <c r="E77" s="363" t="s">
+      <c r="E77" s="349" t="s">
         <v>116</v>
       </c>
       <c r="F77" s="279"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="316">
+      <c r="H77" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I77" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I77" s="248"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="333" t="s">
+      <c r="C78" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="279"/>
-      <c r="E78" s="311" t="s">
+      <c r="E78" s="316" t="s">
         <v>136</v>
       </c>
       <c r="F78" s="279"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H78" s="335"/>
-      <c r="I78" s="258"/>
+      <c r="H78" s="345"/>
+      <c r="I78" s="248"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="323" t="s">
+      <c r="B79" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C79" s="279"/>
@@ -7544,11 +7544,11 @@
       <c r="F79" s="279"/>
       <c r="G79" s="279"/>
       <c r="H79" s="279"/>
-      <c r="I79" s="258"/>
+      <c r="I79" s="248"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="332" t="s">
+      <c r="B80" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C80" s="279"/>
@@ -7559,14 +7559,14 @@
       <c r="F80" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G80" s="324" t="s">
+      <c r="G80" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H80" s="279"/>
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="331" t="s">
+      <c r="B81" s="324" t="s">
         <v>130</v>
       </c>
       <c r="C81" s="279"/>
@@ -7579,14 +7579,14 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="313">
+      <c r="G81" s="317">
         <v>0.9</v>
       </c>
       <c r="H81" s="279"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="331" t="s">
+      <c r="B82" s="324" t="s">
         <v>117</v>
       </c>
       <c r="C82" s="279"/>
@@ -7599,7 +7599,7 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="313">
+      <c r="G82" s="317">
         <v>0.8</v>
       </c>
       <c r="H82" s="279"/>
@@ -7619,18 +7619,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="313">
+      <c r="G83" s="317">
         <v>0.6</v>
       </c>
       <c r="H83" s="279"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="318" t="s">
+      <c r="B84" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="246"/>
-      <c r="D84" s="246"/>
+      <c r="C84" s="254"/>
+      <c r="D84" s="254"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -7639,11 +7639,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="309">
+      <c r="G84" s="340">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="246"/>
+      <c r="H84" s="254"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -7657,7 +7657,7 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="327" t="s">
+      <c r="B86" s="338" t="s">
         <v>137</v>
       </c>
       <c r="C86" s="279"/>
@@ -7670,52 +7670,52 @@
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="319" t="s">
+      <c r="B87" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="320"/>
-      <c r="D87" s="320"/>
-      <c r="E87" s="334" t="s">
+      <c r="C87" s="319"/>
+      <c r="D87" s="319"/>
+      <c r="E87" s="313" t="s">
         <v>119</v>
       </c>
       <c r="F87" s="279"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="356" t="str">
+      <c r="H87" s="360" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="258"/>
+      <c r="I87" s="248"/>
       <c r="K87" s="203" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="317" t="s">
+      <c r="B88" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C88" s="279"/>
       <c r="D88" s="279"/>
-      <c r="E88" s="334" t="s">
+      <c r="E88" s="313" t="s">
         <v>90</v>
       </c>
       <c r="F88" s="279"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="344" t="s">
+      <c r="H88" s="326" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="258"/>
+      <c r="I88" s="248"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="317" t="s">
+      <c r="B89" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="279"/>
       <c r="D89" s="279"/>
-      <c r="E89" s="342">
+      <c r="E89" s="362">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -7723,29 +7723,29 @@
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="314" t="s">
+      <c r="H89" s="347" t="s">
         <v>95</v>
       </c>
-      <c r="I89" s="258"/>
+      <c r="I89" s="248"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="333" t="s">
+      <c r="C90" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D90" s="279"/>
-      <c r="E90" s="336">
+      <c r="E90" s="348">
         <v>43980000</v>
       </c>
       <c r="F90" s="279"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="326">
+      <c r="H90" s="320">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="258"/>
+      <c r="I90" s="248"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -7753,41 +7753,41 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="333" t="s">
+      <c r="C91" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="279"/>
-      <c r="E91" s="361" t="s">
+      <c r="E91" s="323" t="s">
         <v>116</v>
       </c>
       <c r="F91" s="279"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="316">
+      <c r="H91" s="334">
         <f ca="1">TODAY()</f>
-        <v>45828</v>
-      </c>
-      <c r="I91" s="258"/>
+        <v>45832</v>
+      </c>
+      <c r="I91" s="248"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="333" t="s">
+      <c r="C92" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D92" s="279"/>
-      <c r="E92" s="311" t="s">
+      <c r="E92" s="316" t="s">
         <v>97</v>
       </c>
       <c r="F92" s="279"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="335"/>
-      <c r="I92" s="258"/>
+      <c r="H92" s="345"/>
+      <c r="I92" s="248"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="323" t="s">
+      <c r="B93" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C93" s="279"/>
@@ -7796,10 +7796,10 @@
       <c r="F93" s="279"/>
       <c r="G93" s="279"/>
       <c r="H93" s="279"/>
-      <c r="I93" s="258"/>
+      <c r="I93" s="248"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="332" t="s">
+      <c r="B94" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C94" s="279"/>
@@ -7810,14 +7810,14 @@
       <c r="F94" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G94" s="324" t="s">
+      <c r="G94" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H94" s="279"/>
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="321" t="s">
+      <c r="B95" s="325" t="s">
         <v>106</v>
       </c>
       <c r="C95" s="279"/>
@@ -7829,7 +7829,7 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="365">
+      <c r="G95" s="335">
         <v>1</v>
       </c>
       <c r="H95" s="279"/>
@@ -7849,14 +7849,14 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="365">
+      <c r="G96" s="335">
         <v>0.8</v>
       </c>
       <c r="H96" s="279"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="362" t="s">
+      <c r="B97" s="336" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="279"/>
@@ -7869,7 +7869,7 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="313">
+      <c r="G97" s="317">
         <v>0.6</v>
       </c>
       <c r="H97" s="279"/>
@@ -7878,11 +7878,11 @@
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="318" t="s">
+      <c r="B98" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C98" s="246"/>
-      <c r="D98" s="246"/>
+      <c r="C98" s="254"/>
+      <c r="D98" s="254"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -7891,11 +7891,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="309">
+      <c r="G98" s="340">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="246"/>
+      <c r="H98" s="254"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -7916,7 +7916,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="329"/>
+      <c r="B100" s="373"/>
       <c r="C100" s="279"/>
       <c r="D100" s="279"/>
       <c r="E100" s="279"/>
@@ -7928,7 +7928,7 @@
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="327" t="s">
+      <c r="B101" s="338" t="s">
         <v>139</v>
       </c>
       <c r="C101" s="279"/>
@@ -7942,93 +7942,93 @@
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="319" t="s">
+      <c r="B102" s="318" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="320"/>
-      <c r="D102" s="320"/>
-      <c r="E102" s="371"/>
+      <c r="C102" s="319"/>
+      <c r="D102" s="319"/>
+      <c r="E102" s="329"/>
       <c r="F102" s="279"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="312"/>
-      <c r="I102" s="258"/>
+      <c r="H102" s="374"/>
+      <c r="I102" s="248"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="317" t="s">
+      <c r="B103" s="321" t="s">
         <v>89</v>
       </c>
       <c r="C103" s="279"/>
       <c r="D103" s="279"/>
-      <c r="E103" s="366"/>
+      <c r="E103" s="339"/>
       <c r="F103" s="279"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="360"/>
-      <c r="I103" s="258"/>
+      <c r="H103" s="346"/>
+      <c r="I103" s="248"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="317" t="s">
+      <c r="B104" s="321" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="279"/>
       <c r="D104" s="279"/>
-      <c r="E104" s="325"/>
+      <c r="E104" s="359"/>
       <c r="F104" s="279"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="338"/>
-      <c r="I104" s="258"/>
+      <c r="H104" s="370"/>
+      <c r="I104" s="248"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="333" t="s">
+      <c r="C105" s="315" t="s">
         <v>113</v>
       </c>
       <c r="D105" s="279"/>
-      <c r="E105" s="336"/>
+      <c r="E105" s="348"/>
       <c r="F105" s="279"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="326"/>
-      <c r="I105" s="258"/>
+      <c r="H105" s="320"/>
+      <c r="I105" s="248"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="333" t="s">
+      <c r="C106" s="315" t="s">
         <v>115</v>
       </c>
       <c r="D106" s="279"/>
-      <c r="E106" s="361"/>
+      <c r="E106" s="323"/>
       <c r="F106" s="279"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="364"/>
-      <c r="I106" s="258"/>
+      <c r="H106" s="333"/>
+      <c r="I106" s="248"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="333" t="s">
+      <c r="C107" s="315" t="s">
         <v>96</v>
       </c>
       <c r="D107" s="279"/>
-      <c r="E107" s="337"/>
+      <c r="E107" s="369"/>
       <c r="F107" s="279"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="335"/>
-      <c r="I107" s="258"/>
+      <c r="H107" s="345"/>
+      <c r="I107" s="248"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="323" t="s">
+      <c r="B108" s="332" t="s">
         <v>101</v>
       </c>
       <c r="C108" s="279"/>
@@ -8037,10 +8037,10 @@
       <c r="F108" s="279"/>
       <c r="G108" s="279"/>
       <c r="H108" s="279"/>
-      <c r="I108" s="258"/>
+      <c r="I108" s="248"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="332" t="s">
+      <c r="B109" s="314" t="s">
         <v>102</v>
       </c>
       <c r="C109" s="279"/>
@@ -8051,42 +8051,42 @@
       <c r="F109" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="324" t="s">
+      <c r="G109" s="327" t="s">
         <v>105</v>
       </c>
       <c r="H109" s="279"/>
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="362" t="s">
+      <c r="B110" s="336" t="s">
         <v>106</v>
       </c>
       <c r="C110" s="279"/>
       <c r="D110" s="279"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="313"/>
+      <c r="G110" s="317"/>
       <c r="H110" s="279"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="362" t="s">
+      <c r="B111" s="336" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="279"/>
       <c r="D111" s="279"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="313"/>
+      <c r="G111" s="317"/>
       <c r="H111" s="279"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="318" t="s">
+      <c r="B112" s="344" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="246"/>
-      <c r="D112" s="246"/>
+      <c r="C112" s="254"/>
+      <c r="D112" s="254"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -8095,15 +8095,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="309">
+      <c r="G112" s="340">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="246"/>
+      <c r="H112" s="254"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="E88:F88"/>
     <mergeCell ref="B38:D38"/>
@@ -8128,211 +8333,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B108:I108"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="G84:H84"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8684,16 +8684,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="374"/>
-      <c r="F1" s="375"/>
-      <c r="G1" s="375"/>
-      <c r="H1" s="375"/>
-      <c r="I1" s="375"/>
-      <c r="J1" s="375"/>
-      <c r="K1" s="375"/>
-      <c r="L1" s="375"/>
-      <c r="M1" s="375"/>
-      <c r="N1" s="375"/>
+      <c r="E1" s="383"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="378"/>
+      <c r="I1" s="378"/>
+      <c r="J1" s="378"/>
+      <c r="K1" s="378"/>
+      <c r="L1" s="378"/>
+      <c r="M1" s="378"/>
+      <c r="N1" s="378"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -9241,21 +9241,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="373" t="s">
+      <c r="A12" s="376" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="244"/>
-      <c r="C12" s="376" t="s">
+      <c r="B12" s="246"/>
+      <c r="C12" s="384" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="375"/>
-      <c r="E12" s="375"/>
-      <c r="F12" s="375"/>
-      <c r="G12" s="375"/>
-      <c r="H12" s="375"/>
-      <c r="I12" s="375"/>
-      <c r="J12" s="375"/>
-      <c r="K12" s="375"/>
+      <c r="D12" s="378"/>
+      <c r="E12" s="378"/>
+      <c r="F12" s="378"/>
+      <c r="G12" s="378"/>
+      <c r="H12" s="378"/>
+      <c r="I12" s="378"/>
+      <c r="J12" s="378"/>
+      <c r="K12" s="378"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -9270,21 +9270,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="373" t="s">
+      <c r="A13" s="376" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="244"/>
-      <c r="C13" s="376" t="s">
+      <c r="B13" s="246"/>
+      <c r="C13" s="384" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="375"/>
-      <c r="E13" s="375"/>
-      <c r="F13" s="375"/>
-      <c r="G13" s="375"/>
-      <c r="H13" s="375"/>
-      <c r="I13" s="375"/>
-      <c r="J13" s="375"/>
-      <c r="K13" s="375"/>
+      <c r="D13" s="378"/>
+      <c r="E13" s="378"/>
+      <c r="F13" s="378"/>
+      <c r="G13" s="378"/>
+      <c r="H13" s="378"/>
+      <c r="I13" s="378"/>
+      <c r="J13" s="378"/>
+      <c r="K13" s="378"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -9299,22 +9299,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="373" t="str">
+      <c r="A14" s="376" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="244"/>
-      <c r="C14" s="376" t="s">
+      <c r="B14" s="246"/>
+      <c r="C14" s="384" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="375"/>
-      <c r="E14" s="375"/>
-      <c r="F14" s="375"/>
-      <c r="G14" s="375"/>
-      <c r="H14" s="375"/>
-      <c r="I14" s="375"/>
-      <c r="J14" s="375"/>
-      <c r="K14" s="375"/>
+      <c r="D14" s="378"/>
+      <c r="E14" s="378"/>
+      <c r="F14" s="378"/>
+      <c r="G14" s="378"/>
+      <c r="H14" s="378"/>
+      <c r="I14" s="378"/>
+      <c r="J14" s="378"/>
+      <c r="K14" s="378"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -9329,21 +9329,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="373" t="s">
+      <c r="A15" s="376" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="244"/>
-      <c r="C15" s="376" t="s">
+      <c r="B15" s="246"/>
+      <c r="C15" s="384" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="375"/>
-      <c r="E15" s="375"/>
-      <c r="F15" s="375"/>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
-      <c r="K15" s="375"/>
+      <c r="D15" s="378"/>
+      <c r="E15" s="378"/>
+      <c r="F15" s="378"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="378"/>
+      <c r="K15" s="378"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -9358,21 +9358,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="373" t="s">
+      <c r="A16" s="376" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="244"/>
-      <c r="C16" s="378" t="s">
+      <c r="B16" s="246"/>
+      <c r="C16" s="377" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="375"/>
-      <c r="E16" s="375"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
-      <c r="K16" s="375"/>
+      <c r="D16" s="378"/>
+      <c r="E16" s="378"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="378"/>
+      <c r="J16" s="378"/>
+      <c r="K16" s="378"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -9382,21 +9382,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="373" t="s">
+      <c r="A17" s="376" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="244"/>
-      <c r="C17" s="378" t="s">
+      <c r="B17" s="246"/>
+      <c r="C17" s="377" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="375"/>
-      <c r="E17" s="375"/>
-      <c r="F17" s="375"/>
-      <c r="G17" s="375"/>
-      <c r="H17" s="375"/>
-      <c r="I17" s="375"/>
-      <c r="J17" s="375"/>
-      <c r="K17" s="375"/>
+      <c r="D17" s="378"/>
+      <c r="E17" s="378"/>
+      <c r="F17" s="378"/>
+      <c r="G17" s="378"/>
+      <c r="H17" s="378"/>
+      <c r="I17" s="378"/>
+      <c r="J17" s="378"/>
+      <c r="K17" s="378"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>185</v>
@@ -9415,21 +9415,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="373" t="s">
+      <c r="A18" s="376" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="244"/>
-      <c r="C18" s="378" t="s">
+      <c r="B18" s="246"/>
+      <c r="C18" s="377" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="375"/>
-      <c r="E18" s="375"/>
-      <c r="F18" s="375"/>
-      <c r="G18" s="375"/>
-      <c r="H18" s="375"/>
-      <c r="I18" s="375"/>
-      <c r="J18" s="375"/>
-      <c r="K18" s="375"/>
+      <c r="D18" s="378"/>
+      <c r="E18" s="378"/>
+      <c r="F18" s="378"/>
+      <c r="G18" s="378"/>
+      <c r="H18" s="378"/>
+      <c r="I18" s="378"/>
+      <c r="J18" s="378"/>
+      <c r="K18" s="378"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>188</v>
@@ -9443,21 +9443,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="373" t="s">
+      <c r="A19" s="376" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="244"/>
-      <c r="C19" s="378" t="s">
+      <c r="B19" s="246"/>
+      <c r="C19" s="377" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="375"/>
-      <c r="E19" s="375"/>
-      <c r="F19" s="375"/>
-      <c r="G19" s="375"/>
-      <c r="H19" s="375"/>
-      <c r="I19" s="375"/>
-      <c r="J19" s="375"/>
-      <c r="K19" s="375"/>
+      <c r="D19" s="378"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
+      <c r="G19" s="378"/>
+      <c r="H19" s="378"/>
+      <c r="I19" s="378"/>
+      <c r="J19" s="378"/>
+      <c r="K19" s="378"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -9472,21 +9472,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="373" t="s">
+      <c r="A20" s="376" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="244"/>
-      <c r="C20" s="378" t="s">
+      <c r="B20" s="246"/>
+      <c r="C20" s="377" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="375"/>
-      <c r="E20" s="375"/>
-      <c r="F20" s="375"/>
-      <c r="G20" s="375"/>
-      <c r="H20" s="375"/>
-      <c r="I20" s="375"/>
-      <c r="J20" s="375"/>
-      <c r="K20" s="375"/>
+      <c r="D20" s="378"/>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
+      <c r="G20" s="378"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="378"/>
+      <c r="J20" s="378"/>
+      <c r="K20" s="378"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -9501,21 +9501,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="373" t="s">
+      <c r="A21" s="376" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="244"/>
-      <c r="C21" s="378" t="s">
+      <c r="B21" s="246"/>
+      <c r="C21" s="377" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="375"/>
-      <c r="E21" s="375"/>
-      <c r="F21" s="375"/>
-      <c r="G21" s="375"/>
-      <c r="H21" s="375"/>
-      <c r="I21" s="375"/>
-      <c r="J21" s="375"/>
-      <c r="K21" s="375"/>
+      <c r="D21" s="378"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
+      <c r="G21" s="378"/>
+      <c r="H21" s="378"/>
+      <c r="I21" s="378"/>
+      <c r="J21" s="378"/>
+      <c r="K21" s="378"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -9530,25 +9530,25 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="373" t="s">
+      <c r="A22" s="376" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="244"/>
-      <c r="C22" s="377" t="s">
+      <c r="B22" s="246"/>
+      <c r="C22" s="385" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="375"/>
-      <c r="E22" s="375"/>
-      <c r="F22" s="375"/>
-      <c r="G22" s="375"/>
-      <c r="H22" s="375"/>
-      <c r="I22" s="375"/>
-      <c r="J22" s="375"/>
-      <c r="K22" s="375"/>
-      <c r="L22" s="375"/>
-      <c r="M22" s="375"/>
-      <c r="N22" s="375"/>
-      <c r="O22" s="258"/>
+      <c r="D22" s="378"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
+      <c r="G22" s="378"/>
+      <c r="H22" s="378"/>
+      <c r="I22" s="378"/>
+      <c r="J22" s="378"/>
+      <c r="K22" s="378"/>
+      <c r="L22" s="378"/>
+      <c r="M22" s="378"/>
+      <c r="N22" s="378"/>
+      <c r="O22" s="248"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
       </c>
@@ -9559,22 +9559,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="373" t="s">
+      <c r="A23" s="376" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="244"/>
-      <c r="C23" s="378" t="s">
+      <c r="B23" s="246"/>
+      <c r="C23" s="377" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="375"/>
-      <c r="E23" s="375"/>
-      <c r="F23" s="375"/>
-      <c r="G23" s="375"/>
-      <c r="H23" s="375"/>
-      <c r="I23" s="375"/>
-      <c r="J23" s="375"/>
-      <c r="K23" s="375"/>
-      <c r="L23" s="375"/>
+      <c r="D23" s="378"/>
+      <c r="E23" s="378"/>
+      <c r="F23" s="378"/>
+      <c r="G23" s="378"/>
+      <c r="H23" s="378"/>
+      <c r="I23" s="378"/>
+      <c r="J23" s="378"/>
+      <c r="K23" s="378"/>
+      <c r="L23" s="378"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -9588,22 +9588,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="373" t="s">
+      <c r="A24" s="376" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="244"/>
-      <c r="C24" s="378" t="s">
+      <c r="B24" s="246"/>
+      <c r="C24" s="377" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="375"/>
-      <c r="E24" s="375"/>
-      <c r="F24" s="375"/>
-      <c r="G24" s="375"/>
-      <c r="H24" s="375"/>
-      <c r="I24" s="375"/>
-      <c r="J24" s="375"/>
-      <c r="K24" s="375"/>
-      <c r="L24" s="375"/>
+      <c r="D24" s="378"/>
+      <c r="E24" s="378"/>
+      <c r="F24" s="378"/>
+      <c r="G24" s="378"/>
+      <c r="H24" s="378"/>
+      <c r="I24" s="378"/>
+      <c r="J24" s="378"/>
+      <c r="K24" s="378"/>
+      <c r="L24" s="378"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -9617,21 +9617,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="373" t="s">
+      <c r="A25" s="376" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="244"/>
-      <c r="C25" s="378" t="s">
+      <c r="B25" s="246"/>
+      <c r="C25" s="377" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="375"/>
-      <c r="E25" s="375"/>
-      <c r="F25" s="375"/>
-      <c r="G25" s="375"/>
-      <c r="H25" s="375"/>
-      <c r="I25" s="375"/>
-      <c r="J25" s="375"/>
-      <c r="K25" s="375"/>
+      <c r="D25" s="378"/>
+      <c r="E25" s="378"/>
+      <c r="F25" s="378"/>
+      <c r="G25" s="378"/>
+      <c r="H25" s="378"/>
+      <c r="I25" s="378"/>
+      <c r="J25" s="378"/>
+      <c r="K25" s="378"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -9676,6 +9676,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -9692,21 +9707,6 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -9763,370 +9763,383 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="383" t="str">
+      <c r="C4" s="402" t="str">
         <f>'AREA UTIL '!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="383" t="s">
+      <c r="C5" s="402" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="388" t="s">
+      <c r="C6" s="387" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="385">
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="388">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="248"/>
-      <c r="H6" s="258"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="248"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="388" t="s">
+      <c r="C7" s="387" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="385">
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="388">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="258"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="248"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="388" t="s">
+      <c r="C8" s="387" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
-      <c r="F8" s="385">
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="388">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="258"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="248"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="388" t="s">
+      <c r="C9" s="387" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="384">
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="390">
         <v>6</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="258"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="248"/>
       <c r="J9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="388" t="s">
+      <c r="C10" s="387" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="384">
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="390">
         <v>1</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="258"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="248"/>
       <c r="J10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="388" t="s">
+      <c r="C11" s="387" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
       <c r="F11" s="399">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="248"/>
-      <c r="H11" s="258"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="248"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="388" t="s">
+      <c r="C12" s="387" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="384">
+      <c r="D12" s="243"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="390">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="248"/>
-      <c r="H12" s="258"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="248"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="388" t="s">
+      <c r="C13" s="387" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="385">
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="388">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="248"/>
-      <c r="H13" s="258"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="248"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="396" t="s">
+      <c r="C14" s="397" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="243"/>
-      <c r="E14" s="243"/>
-      <c r="F14" s="392">
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="396">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="243"/>
-      <c r="H14" s="244"/>
-      <c r="J14" s="390">
+      <c r="G14" s="245"/>
+      <c r="H14" s="246"/>
+      <c r="J14" s="400">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="394"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="248"/>
-      <c r="H15" s="248"/>
+      <c r="C15" s="404"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="398" t="s">
+      <c r="C16" s="386" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="388" t="s">
+      <c r="C17" s="387" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="384">
+      <c r="D17" s="243"/>
+      <c r="E17" s="243"/>
+      <c r="F17" s="390">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="258"/>
+      <c r="G17" s="243"/>
+      <c r="H17" s="248"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="388" t="s">
+      <c r="C18" s="387" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="385">
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="388">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="248"/>
-      <c r="H18" s="258"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="248"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="388" t="s">
+      <c r="C19" s="387" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
-      <c r="F19" s="385">
+      <c r="D19" s="243"/>
+      <c r="E19" s="243"/>
+      <c r="F19" s="388">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="248"/>
-      <c r="H19" s="258"/>
+      <c r="G19" s="243"/>
+      <c r="H19" s="248"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="396" t="s">
+      <c r="C20" s="397" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="243"/>
-      <c r="E20" s="243"/>
-      <c r="F20" s="392">
+      <c r="D20" s="245"/>
+      <c r="E20" s="245"/>
+      <c r="F20" s="396">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="243"/>
-      <c r="H20" s="244"/>
+      <c r="G20" s="245"/>
+      <c r="H20" s="246"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="389"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="386"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
+      <c r="C21" s="391"/>
+      <c r="D21" s="243"/>
+      <c r="E21" s="243"/>
+      <c r="F21" s="394"/>
+      <c r="G21" s="243"/>
+      <c r="H21" s="243"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="389"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="386"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
+      <c r="C22" s="391"/>
+      <c r="D22" s="243"/>
+      <c r="E22" s="243"/>
+      <c r="F22" s="394"/>
+      <c r="G22" s="243"/>
+      <c r="H22" s="243"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="389"/>
-      <c r="D23" s="248"/>
-      <c r="E23" s="248"/>
-      <c r="F23" s="393"/>
-      <c r="G23" s="248"/>
-      <c r="H23" s="248"/>
+      <c r="C23" s="391"/>
+      <c r="D23" s="243"/>
+      <c r="E23" s="243"/>
+      <c r="F23" s="403"/>
+      <c r="G23" s="243"/>
+      <c r="H23" s="243"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="391" t="s">
+      <c r="C24" s="401" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
-      <c r="G24" s="248"/>
-      <c r="H24" s="248"/>
+      <c r="D24" s="243"/>
+      <c r="E24" s="243"/>
+      <c r="F24" s="243"/>
+      <c r="G24" s="243"/>
+      <c r="H24" s="243"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="387" t="s">
+      <c r="C25" s="392" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="243"/>
       <c r="F25" s="395">
         <v>2000000</v>
       </c>
-      <c r="G25" s="248"/>
-      <c r="H25" s="258"/>
+      <c r="G25" s="243"/>
+      <c r="H25" s="248"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="387" t="s">
+      <c r="C26" s="392" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="400">
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="389">
         <v>0.8</v>
       </c>
-      <c r="G26" s="248"/>
-      <c r="H26" s="258"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="248"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="387" t="s">
+      <c r="C27" s="392" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
+      <c r="D27" s="243"/>
+      <c r="E27" s="243"/>
       <c r="F27" s="395">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="248"/>
-      <c r="H27" s="258"/>
+      <c r="G27" s="243"/>
+      <c r="H27" s="248"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="397" t="s">
+      <c r="C28" s="398" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="243"/>
-      <c r="E28" s="243"/>
-      <c r="F28" s="401">
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="393">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="243"/>
-      <c r="H28" s="244"/>
+      <c r="G28" s="245"/>
+      <c r="H28" s="246"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="398" t="s">
+      <c r="C31" s="386" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="243"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="388" t="s">
+      <c r="C32" s="387" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="E32" s="248"/>
-      <c r="F32" s="385">
+      <c r="D32" s="243"/>
+      <c r="E32" s="243"/>
+      <c r="F32" s="388">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="248"/>
-      <c r="H32" s="258"/>
+      <c r="G32" s="243"/>
+      <c r="H32" s="248"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="388" t="s">
+      <c r="C33" s="387" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="385">
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="388">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="248"/>
-      <c r="H33" s="258"/>
+      <c r="G33" s="243"/>
+      <c r="H33" s="248"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="396" t="s">
+      <c r="C34" s="397" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="243"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="392">
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="396">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="243"/>
-      <c r="H34" s="244"/>
+      <c r="G34" s="245"/>
+      <c r="H34" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="F10:H10"/>
@@ -10143,31 +10156,18 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10185,178 +10185,169 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="383" t="str">
+      <c r="C5" s="402" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="383" t="s">
+      <c r="C6" s="402" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="388" t="s">
+      <c r="C7" s="387" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="403">
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="406">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="258"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="248"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="388" t="s">
+      <c r="C8" s="387" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
-      <c r="F8" s="384">
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="390">
         <v>36</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="258"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="248"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="388" t="s">
+      <c r="C9" s="387" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="402">
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="405">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="258"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="248"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="388" t="s">
+      <c r="C10" s="387" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="385">
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="388">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="258"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="248"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="396" t="s">
+      <c r="C11" s="397" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="243"/>
-      <c r="E11" s="243"/>
-      <c r="F11" s="392">
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="396">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="243"/>
-      <c r="H11" s="244"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="246"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="398" t="s">
+      <c r="C13" s="386" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="388" t="s">
+      <c r="C14" s="387" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="403">
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="406">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="248"/>
-      <c r="H14" s="258"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="248"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="388" t="s">
+      <c r="C15" s="387" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="384">
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="390">
         <v>36</v>
       </c>
-      <c r="G15" s="248"/>
-      <c r="H15" s="258"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="248"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="388" t="s">
+      <c r="C16" s="387" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="402">
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="405">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="248"/>
-      <c r="H16" s="258"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="248"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="388" t="s">
+      <c r="C17" s="387" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="385">
+      <c r="D17" s="243"/>
+      <c r="E17" s="243"/>
+      <c r="F17" s="388">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="258"/>
+      <c r="G17" s="243"/>
+      <c r="H17" s="248"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="396" t="s">
+      <c r="C18" s="397" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="243"/>
-      <c r="E18" s="243"/>
-      <c r="F18" s="392">
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="396">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="243"/>
-      <c r="H18" s="244"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -10371,6 +10362,15 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -10411,37 +10411,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="404" t="s">
+      <c r="B2" s="423" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="405"/>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
-      <c r="F2" s="405"/>
-      <c r="G2" s="405"/>
-      <c r="H2" s="405"/>
-      <c r="I2" s="405"/>
-      <c r="J2" s="405"/>
-      <c r="K2" s="405"/>
-      <c r="L2" s="405"/>
-      <c r="M2" s="405"/>
-      <c r="N2" s="405"/>
-      <c r="O2" s="405"/>
-      <c r="P2" s="405"/>
-      <c r="Q2" s="405"/>
-      <c r="R2" s="405"/>
-      <c r="S2" s="405"/>
-      <c r="T2" s="405"/>
-      <c r="U2" s="405"/>
-      <c r="V2" s="405"/>
-      <c r="W2" s="405"/>
-      <c r="X2" s="405"/>
-      <c r="Y2" s="405"/>
-      <c r="Z2" s="405"/>
-      <c r="AA2" s="405"/>
-      <c r="AB2" s="405"/>
-      <c r="AC2" s="405"/>
-      <c r="AD2" s="405"/>
+      <c r="C2" s="424"/>
+      <c r="D2" s="424"/>
+      <c r="E2" s="424"/>
+      <c r="F2" s="424"/>
+      <c r="G2" s="424"/>
+      <c r="H2" s="424"/>
+      <c r="I2" s="424"/>
+      <c r="J2" s="424"/>
+      <c r="K2" s="424"/>
+      <c r="L2" s="424"/>
+      <c r="M2" s="424"/>
+      <c r="N2" s="424"/>
+      <c r="O2" s="424"/>
+      <c r="P2" s="424"/>
+      <c r="Q2" s="424"/>
+      <c r="R2" s="424"/>
+      <c r="S2" s="424"/>
+      <c r="T2" s="424"/>
+      <c r="U2" s="424"/>
+      <c r="V2" s="424"/>
+      <c r="W2" s="424"/>
+      <c r="X2" s="424"/>
+      <c r="Y2" s="424"/>
+      <c r="Z2" s="424"/>
+      <c r="AA2" s="424"/>
+      <c r="AB2" s="424"/>
+      <c r="AC2" s="424"/>
+      <c r="AD2" s="424"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -10568,39 +10568,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="422">
+      <c r="B10" s="415">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="407"/>
-      <c r="D10" s="407"/>
-      <c r="E10" s="407"/>
-      <c r="F10" s="407"/>
-      <c r="G10" s="407"/>
+      <c r="C10" s="411"/>
+      <c r="D10" s="411"/>
+      <c r="E10" s="411"/>
+      <c r="F10" s="411"/>
+      <c r="G10" s="411"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="421">
+      <c r="I10" s="432">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="407"/>
-      <c r="K10" s="407"/>
-      <c r="L10" s="407"/>
-      <c r="M10" s="407"/>
-      <c r="N10" s="407"/>
-      <c r="O10" s="407"/>
-      <c r="P10" s="407"/>
+      <c r="J10" s="411"/>
+      <c r="K10" s="411"/>
+      <c r="L10" s="411"/>
+      <c r="M10" s="411"/>
+      <c r="N10" s="411"/>
+      <c r="O10" s="411"/>
+      <c r="P10" s="411"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="406">
+      <c r="R10" s="410">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="407"/>
-      <c r="T10" s="407"/>
-      <c r="U10" s="407"/>
+      <c r="S10" s="411"/>
+      <c r="T10" s="411"/>
+      <c r="U10" s="411"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -10635,13 +10635,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="406">
+      <c r="W11" s="410">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="407"/>
-      <c r="Y11" s="407"/>
-      <c r="Z11" s="407"/>
+      <c r="X11" s="411"/>
+      <c r="Y11" s="411"/>
+      <c r="Z11" s="411"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -10668,13 +10668,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="418">
+      <c r="R12" s="430">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="407"/>
-      <c r="T12" s="407"/>
-      <c r="U12" s="407"/>
+      <c r="S12" s="411"/>
+      <c r="T12" s="411"/>
+      <c r="U12" s="411"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -10694,10 +10694,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="411"/>
-      <c r="X14" s="407"/>
-      <c r="Y14" s="407"/>
-      <c r="Z14" s="407"/>
+      <c r="W14" s="422"/>
+      <c r="X14" s="411"/>
+      <c r="Y14" s="411"/>
+      <c r="Z14" s="411"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -10723,38 +10723,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="415" t="s">
+      <c r="B16" s="427" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="407"/>
-      <c r="D16" s="407"/>
-      <c r="E16" s="407"/>
-      <c r="F16" s="407"/>
-      <c r="G16" s="407"/>
+      <c r="C16" s="411"/>
+      <c r="D16" s="411"/>
+      <c r="E16" s="411"/>
+      <c r="F16" s="411"/>
+      <c r="G16" s="411"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="424" t="str">
+      <c r="I16" s="417" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="407"/>
-      <c r="K16" s="407"/>
-      <c r="L16" s="407"/>
-      <c r="M16" s="407"/>
-      <c r="N16" s="407"/>
-      <c r="O16" s="407"/>
-      <c r="P16" s="407"/>
+      <c r="J16" s="411"/>
+      <c r="K16" s="411"/>
+      <c r="L16" s="411"/>
+      <c r="M16" s="411"/>
+      <c r="N16" s="411"/>
+      <c r="O16" s="411"/>
+      <c r="P16" s="411"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="411" t="str">
+      <c r="R16" s="422" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="407"/>
-      <c r="T16" s="407"/>
-      <c r="U16" s="407"/>
+      <c r="S16" s="411"/>
+      <c r="T16" s="411"/>
+      <c r="U16" s="411"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -10766,10 +10766,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="411"/>
-      <c r="X17" s="407"/>
-      <c r="Y17" s="407"/>
-      <c r="Z17" s="407"/>
+      <c r="W17" s="422"/>
+      <c r="X17" s="411"/>
+      <c r="Y17" s="411"/>
+      <c r="Z17" s="411"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -10793,13 +10793,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="427" t="str">
+      <c r="R18" s="421" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="407"/>
-      <c r="T18" s="407"/>
-      <c r="U18" s="407"/>
+      <c r="S18" s="411"/>
+      <c r="T18" s="411"/>
+      <c r="U18" s="411"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -10881,7 +10881,7 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="419">
+      <c r="W22" s="431">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
@@ -10911,13 +10911,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="408">
+      <c r="W24" s="425">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="409"/>
-      <c r="Y24" s="409"/>
-      <c r="Z24" s="409"/>
+      <c r="X24" s="408"/>
+      <c r="Y24" s="408"/>
+      <c r="Z24" s="408"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -11001,13 +11001,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="412">
+      <c r="W30" s="426">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="409"/>
-      <c r="Y30" s="409"/>
-      <c r="Z30" s="409"/>
+      <c r="X30" s="408"/>
+      <c r="Y30" s="408"/>
+      <c r="Z30" s="408"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -11017,20 +11017,20 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="417">
+      <c r="W31" s="429">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="409"/>
-      <c r="Y31" s="409"/>
-      <c r="Z31" s="409"/>
+      <c r="X31" s="408"/>
+      <c r="Y31" s="408"/>
+      <c r="Z31" s="408"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="416">
+      <c r="K32" s="428">
         <v>43009</v>
       </c>
       <c r="L32" s="414"/>
@@ -11051,32 +11051,32 @@
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="428" t="s">
+      <c r="O33" s="407" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="409"/>
-      <c r="Q33" s="409"/>
-      <c r="R33" s="409"/>
-      <c r="S33" s="409"/>
-      <c r="T33" s="409"/>
-      <c r="U33" s="409"/>
-      <c r="V33" s="409"/>
-      <c r="W33" s="429" t="s">
+      <c r="P33" s="408"/>
+      <c r="Q33" s="408"/>
+      <c r="R33" s="408"/>
+      <c r="S33" s="408"/>
+      <c r="T33" s="408"/>
+      <c r="U33" s="408"/>
+      <c r="V33" s="408"/>
+      <c r="W33" s="412" t="s">
         <v>256</v>
       </c>
-      <c r="X33" s="320"/>
-      <c r="Y33" s="320"/>
-      <c r="Z33" s="320"/>
-      <c r="AA33" s="320"/>
-      <c r="AB33" s="320"/>
-      <c r="AC33" s="320"/>
-      <c r="AD33" s="320"/>
+      <c r="X33" s="319"/>
+      <c r="Y33" s="319"/>
+      <c r="Z33" s="319"/>
+      <c r="AA33" s="319"/>
+      <c r="AB33" s="319"/>
+      <c r="AC33" s="319"/>
+      <c r="AD33" s="319"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="420">
+      <c r="Q34" s="419">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
@@ -11087,7 +11087,7 @@
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="420">
+      <c r="Y34" s="419">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
@@ -11156,32 +11156,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="410"/>
-      <c r="C38" s="407"/>
+      <c r="B38" s="416"/>
+      <c r="C38" s="411"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="410"/>
-      <c r="C39" s="407"/>
+      <c r="B39" s="416"/>
+      <c r="C39" s="411"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="410"/>
-      <c r="C40" s="407"/>
+      <c r="B40" s="416"/>
+      <c r="C40" s="411"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="410"/>
-      <c r="C41" s="407"/>
+      <c r="B41" s="416"/>
+      <c r="C41" s="411"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="410"/>
-      <c r="C42" s="407"/>
+      <c r="B42" s="416"/>
+      <c r="C42" s="411"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="410"/>
-      <c r="C43" s="407"/>
+      <c r="B43" s="416"/>
+      <c r="C43" s="411"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="410"/>
-      <c r="C44" s="407"/>
+      <c r="B44" s="416"/>
+      <c r="C44" s="411"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -11252,10 +11252,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="426"/>
-      <c r="F49" s="407"/>
-      <c r="G49" s="407"/>
-      <c r="H49" s="407"/>
+      <c r="E49" s="420"/>
+      <c r="F49" s="411"/>
+      <c r="G49" s="411"/>
+      <c r="H49" s="411"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -11278,50 +11278,60 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="423"/>
-      <c r="I52" s="320"/>
-      <c r="J52" s="320"/>
-      <c r="K52" s="320"/>
-      <c r="L52" s="320"/>
-      <c r="M52" s="320"/>
-      <c r="N52" s="320"/>
-      <c r="O52" s="320"/>
-      <c r="P52" s="320"/>
+      <c r="H52" s="409"/>
+      <c r="I52" s="319"/>
+      <c r="J52" s="319"/>
+      <c r="K52" s="319"/>
+      <c r="L52" s="319"/>
+      <c r="M52" s="319"/>
+      <c r="N52" s="319"/>
+      <c r="O52" s="319"/>
+      <c r="P52" s="319"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="425"/>
-      <c r="I55" s="320"/>
-      <c r="J55" s="320"/>
-      <c r="K55" s="320"/>
-      <c r="L55" s="320"/>
-      <c r="M55" s="320"/>
-      <c r="N55" s="320"/>
-      <c r="O55" s="320"/>
-      <c r="P55" s="320"/>
+      <c r="H55" s="418"/>
+      <c r="I55" s="319"/>
+      <c r="J55" s="319"/>
+      <c r="K55" s="319"/>
+      <c r="L55" s="319"/>
+      <c r="M55" s="319"/>
+      <c r="N55" s="319"/>
+      <c r="O55" s="319"/>
+      <c r="P55" s="319"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="423"/>
-      <c r="I57" s="320"/>
-      <c r="J57" s="320"/>
-      <c r="K57" s="320"/>
-      <c r="L57" s="320"/>
-      <c r="M57" s="320"/>
-      <c r="N57" s="320"/>
-      <c r="O57" s="320"/>
-      <c r="P57" s="320"/>
+      <c r="H57" s="409"/>
+      <c r="I57" s="319"/>
+      <c r="J57" s="319"/>
+      <c r="K57" s="319"/>
+      <c r="L57" s="319"/>
+      <c r="M57" s="319"/>
+      <c r="N57" s="319"/>
+      <c r="O57" s="319"/>
+      <c r="P57" s="319"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="W26:Z26"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="K32:Z32"/>
+    <mergeCell ref="W31:Z31"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="I10:P10"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H57:P57"/>
     <mergeCell ref="B42:C42"/>
@@ -11338,22 +11348,12 @@
     <mergeCell ref="W28:Z28"/>
     <mergeCell ref="W27:Z27"/>
     <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="W30:Z30"/>
-    <mergeCell ref="W26:Z26"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="K32:Z32"/>
-    <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="874" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="316">
   <si>
     <t>LAUDO DE AVALIAÇÃO Nº 435420</t>
   </si>
@@ -1006,6 +1006,39 @@
   </si>
   <si>
     <t>Área de Pastagem</t>
+  </si>
+  <si>
+    <t>ÍNDICES DE DEPRECIAÇÃO FÍSICA E FUNCIONAL</t>
+  </si>
+  <si>
+    <t>Depreciação Física</t>
+  </si>
+  <si>
+    <t>Depreciação Funcional</t>
+  </si>
+  <si>
+    <t>Adequada</t>
+  </si>
+  <si>
+    <t>Inadequada</t>
+  </si>
+  <si>
+    <t>Superada</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Ótimo</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Precária</t>
+  </si>
+  <si>
+    <t>Mau</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1059,7 @@
     <numFmt numFmtId="172" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="71">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1473,8 +1506,14 @@
       <sz val="12"/>
       <name val="Century Gothic"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1535,6 +1574,12 @@
         <bgColor rgb="FF00B050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EA65D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="52">
     <border>
@@ -2179,7 +2224,7 @@
     <xf numFmtId="9" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="464">
+  <cellXfs count="471">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2891,9 +2936,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="54" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2901,6 +2943,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3134,33 +3179,37 @@
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3410,6 +3459,21 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4581,24 +4645,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="448" t="s">
+      <c r="B1" s="450" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="449"/>
-      <c r="D1" s="449"/>
-      <c r="E1" s="449"/>
-      <c r="F1" s="449"/>
-      <c r="G1" s="449"/>
-      <c r="H1" s="450"/>
+      <c r="C1" s="451"/>
+      <c r="D1" s="451"/>
+      <c r="E1" s="451"/>
+      <c r="F1" s="451"/>
+      <c r="G1" s="451"/>
+      <c r="H1" s="452"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="445"/>
-      <c r="C2" s="446"/>
-      <c r="D2" s="446"/>
-      <c r="E2" s="446"/>
-      <c r="F2" s="446"/>
-      <c r="G2" s="446"/>
-      <c r="H2" s="447"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="448"/>
+      <c r="D2" s="448"/>
+      <c r="E2" s="448"/>
+      <c r="F2" s="448"/>
+      <c r="G2" s="448"/>
+      <c r="H2" s="449"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -4633,30 +4697,30 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="438" t="s">
+      <c r="B6" s="440" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="440" t="s">
+      <c r="C6" s="442" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="436" t="s">
+      <c r="D6" s="438" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="442" t="s">
+      <c r="E6" s="444" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="442" t="s">
+      <c r="F6" s="444" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="433" t="s">
+      <c r="G6" s="435" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="434"/>
+      <c r="H6" s="436"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="439"/>
-      <c r="C7" s="437"/>
-      <c r="D7" s="437"/>
+      <c r="B7" s="441"/>
+      <c r="C7" s="439"/>
+      <c r="D7" s="439"/>
       <c r="E7" s="258"/>
       <c r="F7" s="258"/>
       <c r="G7" s="47" t="s">
@@ -4679,7 +4743,7 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="435" t="s">
+      <c r="B9" s="437" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="245"/>
@@ -4704,30 +4768,30 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="438" t="s">
+      <c r="B11" s="440" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="440" t="s">
+      <c r="C11" s="442" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="436" t="s">
+      <c r="D11" s="438" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="441" t="s">
+      <c r="E11" s="443" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="441" t="s">
+      <c r="F11" s="443" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="433" t="s">
+      <c r="G11" s="435" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="434"/>
+      <c r="H11" s="436"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="439"/>
-      <c r="C12" s="437"/>
-      <c r="D12" s="437"/>
+      <c r="B12" s="441"/>
+      <c r="C12" s="439"/>
+      <c r="D12" s="439"/>
       <c r="E12" s="258"/>
       <c r="F12" s="258"/>
       <c r="G12" s="47" t="s">
@@ -4750,7 +4814,7 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="435" t="s">
+      <c r="B14" s="437" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="245"/>
@@ -4775,30 +4839,30 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="438" t="s">
+      <c r="B16" s="440" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="440" t="s">
+      <c r="C16" s="442" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="436" t="s">
+      <c r="D16" s="438" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="441" t="s">
+      <c r="E16" s="443" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="441" t="s">
+      <c r="F16" s="443" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="433" t="s">
+      <c r="G16" s="435" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="434"/>
+      <c r="H16" s="436"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="439"/>
-      <c r="C17" s="437"/>
-      <c r="D17" s="437"/>
+      <c r="B17" s="441"/>
+      <c r="C17" s="439"/>
+      <c r="D17" s="439"/>
       <c r="E17" s="258"/>
       <c r="F17" s="258"/>
       <c r="G17" s="22" t="s">
@@ -4823,7 +4887,7 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="435" t="s">
+      <c r="B19" s="437" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="245"/>
@@ -4848,30 +4912,30 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="438" t="s">
+      <c r="B21" s="440" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="440" t="s">
+      <c r="C21" s="442" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="436" t="s">
+      <c r="D21" s="438" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="441" t="s">
+      <c r="E21" s="443" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="441" t="s">
+      <c r="F21" s="443" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="433" t="s">
+      <c r="G21" s="435" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="434"/>
+      <c r="H21" s="436"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="439"/>
-      <c r="C22" s="437"/>
-      <c r="D22" s="437"/>
+      <c r="B22" s="441"/>
+      <c r="C22" s="439"/>
+      <c r="D22" s="439"/>
       <c r="E22" s="258"/>
       <c r="F22" s="258"/>
       <c r="G22" s="47" t="s">
@@ -4894,14 +4958,14 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="443" t="s">
+      <c r="B24" s="445" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="444"/>
-      <c r="D24" s="444"/>
-      <c r="E24" s="444"/>
-      <c r="F24" s="444"/>
-      <c r="G24" s="380"/>
+      <c r="C24" s="446"/>
+      <c r="D24" s="446"/>
+      <c r="E24" s="446"/>
+      <c r="F24" s="446"/>
+      <c r="G24" s="382"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
@@ -4961,14 +5025,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="453" t="s">
+      <c r="B1" s="455" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="446"/>
-      <c r="D1" s="446"/>
-      <c r="E1" s="446"/>
-      <c r="F1" s="446"/>
-      <c r="G1" s="446"/>
+      <c r="C1" s="448"/>
+      <c r="D1" s="448"/>
+      <c r="E1" s="448"/>
+      <c r="F1" s="448"/>
+      <c r="G1" s="448"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -4992,7 +5056,7 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="454" t="s">
+      <c r="B4" s="456" t="s">
         <v>272</v>
       </c>
       <c r="C4" s="245"/>
@@ -5003,19 +5067,19 @@
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="455" t="s">
+      <c r="B5" s="457" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="451" t="s">
+      <c r="C5" s="453" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="451" t="s">
+      <c r="D5" s="453" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="451" t="s">
+      <c r="E5" s="453" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="452" t="s">
+      <c r="F5" s="454" t="s">
         <v>277</v>
       </c>
       <c r="G5" s="245"/>
@@ -5023,9 +5087,9 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="258"/>
-      <c r="C6" s="437"/>
-      <c r="D6" s="437"/>
-      <c r="E6" s="437"/>
+      <c r="C6" s="439"/>
+      <c r="D6" s="439"/>
+      <c r="E6" s="439"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -5077,7 +5141,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="461" t="s">
+      <c r="A1" s="463" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="243"/>
@@ -5093,18 +5157,18 @@
       <c r="L1" s="243"/>
       <c r="M1" s="243"/>
       <c r="N1" s="243"/>
-      <c r="O1" s="462"/>
+      <c r="O1" s="464"/>
       <c r="P1" s="243"/>
       <c r="Q1" s="243"/>
       <c r="R1" s="243"/>
       <c r="S1" s="243"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="463" t="s">
+      <c r="A2" s="465" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="243"/>
-      <c r="C2" s="463" t="s">
+      <c r="C2" s="465" t="s">
         <v>278</v>
       </c>
       <c r="D2" s="243"/>
@@ -5113,7 +5177,7 @@
       <c r="G2" s="243"/>
       <c r="H2" s="243"/>
       <c r="I2" s="243"/>
-      <c r="J2" s="459" t="s">
+      <c r="J2" s="461" t="s">
         <v>279</v>
       </c>
       <c r="K2" s="243"/>
@@ -5122,11 +5186,11 @@
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="460" t="s">
+      <c r="A3" s="462" t="s">
         <v>280</v>
       </c>
       <c r="B3" s="243"/>
-      <c r="C3" s="460" t="s">
+      <c r="C3" s="462" t="s">
         <v>278</v>
       </c>
       <c r="D3" s="243"/>
@@ -5135,7 +5199,7 @@
       <c r="G3" s="243"/>
       <c r="H3" s="243"/>
       <c r="I3" s="243"/>
-      <c r="J3" s="460" t="s">
+      <c r="J3" s="462" t="s">
         <v>281</v>
       </c>
       <c r="K3" s="243"/>
@@ -5144,11 +5208,11 @@
       <c r="N3" s="243"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="460" t="s">
+      <c r="A4" s="462" t="s">
         <v>282</v>
       </c>
       <c r="B4" s="243"/>
-      <c r="C4" s="460" t="s">
+      <c r="C4" s="462" t="s">
         <v>283</v>
       </c>
       <c r="D4" s="243"/>
@@ -5157,18 +5221,18 @@
       <c r="G4" s="243"/>
       <c r="H4" s="243"/>
       <c r="I4" s="243"/>
-      <c r="J4" s="458"/>
+      <c r="J4" s="460"/>
       <c r="K4" s="243"/>
       <c r="L4" s="243"/>
       <c r="M4" s="243"/>
       <c r="N4" s="243"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="460" t="s">
+      <c r="A5" s="462" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="243"/>
-      <c r="C5" s="460" t="s">
+      <c r="C5" s="462" t="s">
         <v>284</v>
       </c>
       <c r="D5" s="243"/>
@@ -5177,18 +5241,18 @@
       <c r="G5" s="243"/>
       <c r="H5" s="243"/>
       <c r="I5" s="243"/>
-      <c r="J5" s="458"/>
+      <c r="J5" s="460"/>
       <c r="K5" s="243"/>
       <c r="L5" s="243"/>
       <c r="M5" s="243"/>
       <c r="N5" s="243"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="460" t="s">
+      <c r="A6" s="462" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="243"/>
-      <c r="C6" s="460" t="s">
+      <c r="C6" s="462" t="s">
         <v>285</v>
       </c>
       <c r="D6" s="243"/>
@@ -5197,7 +5261,7 @@
       <c r="G6" s="243"/>
       <c r="H6" s="243"/>
       <c r="I6" s="243"/>
-      <c r="J6" s="460" t="s">
+      <c r="J6" s="462" t="s">
         <v>286</v>
       </c>
       <c r="K6" s="243"/>
@@ -5206,7 +5270,7 @@
       <c r="N6" s="243"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="457" t="s">
+      <c r="A7" s="459" t="s">
         <v>287</v>
       </c>
       <c r="B7" s="243"/>
@@ -5247,7 +5311,7 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="457" t="s">
+      <c r="A31" s="459" t="s">
         <v>288</v>
       </c>
       <c r="B31" s="243"/>
@@ -5265,22 +5329,22 @@
       <c r="N31" s="243"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="456" t="s">
+      <c r="A32" s="458" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="243"/>
       <c r="C32" s="243"/>
-      <c r="D32" s="456" t="s">
+      <c r="D32" s="458" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="243"/>
       <c r="F32" s="243"/>
-      <c r="G32" s="456" t="s">
+      <c r="G32" s="458" t="s">
         <v>289</v>
       </c>
       <c r="H32" s="243"/>
       <c r="I32" s="243"/>
-      <c r="J32" s="456" t="s">
+      <c r="J32" s="458" t="s">
         <v>14</v>
       </c>
       <c r="K32" s="243"/>
@@ -5288,22 +5352,22 @@
       <c r="M32" s="243"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="456" t="s">
+      <c r="A33" s="458" t="s">
         <v>290</v>
       </c>
       <c r="B33" s="243"/>
       <c r="C33" s="243"/>
-      <c r="D33" s="456" t="s">
+      <c r="D33" s="458" t="s">
         <v>291</v>
       </c>
       <c r="E33" s="243"/>
       <c r="F33" s="243"/>
-      <c r="G33" s="456" t="s">
+      <c r="G33" s="458" t="s">
         <v>292</v>
       </c>
       <c r="H33" s="243"/>
       <c r="I33" s="243"/>
-      <c r="J33" s="456" t="s">
+      <c r="J33" s="458" t="s">
         <v>293</v>
       </c>
       <c r="K33" s="243"/>
@@ -5311,7 +5375,7 @@
       <c r="M33" s="243"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="457" t="s">
+      <c r="A34" s="459" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="243"/>
@@ -5329,34 +5393,34 @@
       <c r="N34" s="243"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="456" t="s">
+      <c r="A35" s="458" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="243"/>
       <c r="C35" s="243"/>
-      <c r="F35" s="456" t="s">
+      <c r="F35" s="458" t="s">
         <v>294</v>
       </c>
       <c r="G35" s="243"/>
       <c r="H35" s="243"/>
-      <c r="K35" s="456" t="s">
+      <c r="K35" s="458" t="s">
         <v>295</v>
       </c>
       <c r="L35" s="243"/>
       <c r="M35" s="243"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="456" t="s">
+      <c r="A36" s="458" t="s">
         <v>290</v>
       </c>
       <c r="B36" s="243"/>
       <c r="C36" s="243"/>
-      <c r="F36" s="456" t="s">
+      <c r="F36" s="458" t="s">
         <v>296</v>
       </c>
       <c r="G36" s="243"/>
       <c r="H36" s="243"/>
-      <c r="K36" s="456" t="s">
+      <c r="K36" s="458" t="s">
         <v>297</v>
       </c>
       <c r="L36" s="243"/>
@@ -5406,14 +5470,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D8:G47"/>
+  <dimension ref="D8:L47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="152" customWidth="1"/>
     <col min="4" max="4" width="29.85546875" style="152" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="152" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="152" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="152"/>
+    <col min="7" max="7" width="9.140625" style="152"/>
+    <col min="8" max="8" width="21" style="152" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" style="152" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="152" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="152" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="152"/>
   </cols>
   <sheetData>
     <row r="8" spans="4:5" ht="13.5" customHeight="1" thickBot="1"/>
@@ -5473,73 +5542,179 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="4:7">
+    <row r="17" spans="4:12">
       <c r="D17" s="159" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="4:7">
+    <row r="18" spans="4:12">
       <c r="D18" s="159" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="4:7" ht="15" customHeight="1">
+    <row r="21" spans="4:12" ht="15" customHeight="1">
       <c r="D21" s="160" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="160" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" spans="4:7" ht="15" customHeight="1">
+      <c r="H21" s="469" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" s="469"/>
+      <c r="J21" s="469"/>
+      <c r="K21" s="469"/>
+      <c r="L21" s="469"/>
+    </row>
+    <row r="22" spans="4:12" ht="15" customHeight="1">
       <c r="D22" s="153" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="123">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="23" spans="4:7" ht="15" customHeight="1">
+      <c r="H22" s="470" t="s">
+        <v>306</v>
+      </c>
+      <c r="I22" s="470" t="s">
+        <v>307</v>
+      </c>
+      <c r="J22" s="470"/>
+      <c r="K22" s="470"/>
+      <c r="L22" s="470"/>
+    </row>
+    <row r="23" spans="4:12" ht="15" customHeight="1">
       <c r="D23" s="153" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="123">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="4:7" ht="15" customHeight="1">
+      <c r="H23" s="470"/>
+      <c r="I23" s="466" t="s">
+        <v>308</v>
+      </c>
+      <c r="J23" s="466" t="s">
+        <v>309</v>
+      </c>
+      <c r="K23" s="466" t="s">
+        <v>310</v>
+      </c>
+      <c r="L23" s="466" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="4:12" ht="15" customHeight="1">
       <c r="D24" s="153" t="s">
         <v>36</v>
       </c>
       <c r="E24" s="123">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="4:7" ht="15" customHeight="1">
+      <c r="H24" s="467" t="s">
+        <v>312</v>
+      </c>
+      <c r="I24" s="468">
+        <v>1</v>
+      </c>
+      <c r="J24" s="468">
+        <v>0.75</v>
+      </c>
+      <c r="K24" s="468">
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="468">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="4:12" ht="15" customHeight="1">
       <c r="D25" s="153" t="s">
         <v>37</v>
       </c>
       <c r="E25" s="123">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="26" spans="4:7" ht="15" customHeight="1">
+      <c r="H25" s="467" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="468">
+        <v>0.8</v>
+      </c>
+      <c r="J25" s="468">
+        <v>0.6</v>
+      </c>
+      <c r="K25" s="468">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="468">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="26" spans="4:12" ht="15" customHeight="1">
       <c r="D26" s="153" t="s">
         <v>38</v>
       </c>
       <c r="E26" s="123">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="27" spans="4:7" ht="15" customHeight="1">
+      <c r="H26" s="467" t="s">
+        <v>313</v>
+      </c>
+      <c r="I26" s="468">
+        <v>0.6</v>
+      </c>
+      <c r="J26" s="468">
+        <v>0.45</v>
+      </c>
+      <c r="K26" s="468">
+        <v>0.3</v>
+      </c>
+      <c r="L26" s="468">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="4:12" ht="15" customHeight="1">
       <c r="D27" s="153" t="s">
         <v>39</v>
       </c>
       <c r="E27" s="123">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="32" spans="4:7" ht="15" customHeight="1">
+      <c r="H27" s="467" t="s">
+        <v>314</v>
+      </c>
+      <c r="I27" s="468">
+        <v>0.4</v>
+      </c>
+      <c r="J27" s="468">
+        <v>0.3</v>
+      </c>
+      <c r="K27" s="468">
+        <v>0.2</v>
+      </c>
+      <c r="L27" s="468">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="28" spans="4:12" ht="15">
+      <c r="H28" s="467" t="s">
+        <v>315</v>
+      </c>
+      <c r="I28" s="468">
+        <v>0.2</v>
+      </c>
+      <c r="J28" s="468">
+        <v>0.15</v>
+      </c>
+      <c r="K28" s="468">
+        <v>0.1</v>
+      </c>
+      <c r="L28" s="468">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="32" spans="4:12" ht="15" customHeight="1">
       <c r="D32" s="278" t="s">
         <v>40</v>
       </c>
@@ -5651,11 +5826,14 @@
     <row r="46" spans="4:7" ht="44.25" customHeight="1"/>
     <row r="47" spans="4:7" ht="64.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="D32:D33"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:L22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5759,7 +5937,7 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="280">
+      <c r="C6" s="283">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
@@ -5772,7 +5950,7 @@
         <v>67</v>
       </c>
       <c r="H6" s="246"/>
-      <c r="I6" s="282" t="s">
+      <c r="I6" s="281" t="s">
         <v>67</v>
       </c>
       <c r="J6" s="246"/>
@@ -5821,15 +5999,15 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="283" t="s">
+      <c r="C8" s="282" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="246"/>
-      <c r="E8" s="283" t="s">
+      <c r="E8" s="282" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="246"/>
-      <c r="G8" s="283" t="s">
+      <c r="G8" s="282" t="s">
         <v>71</v>
       </c>
       <c r="H8" s="246"/>
@@ -5856,11 +6034,11 @@
         <v>303</v>
       </c>
       <c r="F9" s="246"/>
-      <c r="G9" s="280">
+      <c r="G9" s="283">
         <v>80</v>
       </c>
       <c r="H9" s="246"/>
-      <c r="I9" s="282">
+      <c r="I9" s="281">
         <v>0.65039999999999998</v>
       </c>
       <c r="J9" s="246"/>
@@ -5896,15 +6074,15 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="283" t="s">
+      <c r="C11" s="282" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="246"/>
-      <c r="E11" s="283" t="s">
+      <c r="E11" s="282" t="s">
         <v>62</v>
       </c>
       <c r="F11" s="246"/>
-      <c r="G11" s="283" t="s">
+      <c r="G11" s="282" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="246"/>
@@ -5932,7 +6110,7 @@
       <c r="J12" s="246"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="283" t="s">
+      <c r="C13" s="282" t="s">
         <v>75</v>
       </c>
       <c r="D13" s="246"/>
@@ -5940,11 +6118,11 @@
         <v>76</v>
       </c>
       <c r="F13" s="246"/>
-      <c r="G13" s="283" t="s">
+      <c r="G13" s="282" t="s">
         <v>77</v>
       </c>
       <c r="H13" s="246"/>
-      <c r="I13" s="282" t="s">
+      <c r="I13" s="281" t="s">
         <v>78</v>
       </c>
       <c r="J13" s="246"/>
@@ -5998,12 +6176,12 @@
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="246"/>
-      <c r="F19" s="280">
+      <c r="F19" s="283">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
       <c r="G19" s="246"/>
-      <c r="H19" s="281">
+      <c r="H19" s="280">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
@@ -6037,7 +6215,7 @@
         <v>52.034300000000002</v>
       </c>
       <c r="G21" s="246"/>
-      <c r="H21" s="281">
+      <c r="H21" s="280">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
@@ -6120,16 +6298,16 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="338" t="s">
+      <c r="B3" s="371" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="279"/>
-      <c r="D3" s="279"/>
-      <c r="E3" s="279"/>
-      <c r="F3" s="279"/>
-      <c r="G3" s="279"/>
-      <c r="H3" s="279"/>
-      <c r="I3" s="279"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
+      <c r="H3" s="372"/>
+      <c r="I3" s="372"/>
       <c r="L3" s="312" t="s">
         <v>85</v>
       </c>
@@ -6199,7 +6377,7 @@
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="372" t="s">
+      <c r="H6" s="374" t="s">
         <v>300</v>
       </c>
       <c r="I6" s="248"/>
@@ -6210,7 +6388,7 @@
         <v>96</v>
       </c>
       <c r="D7" s="279"/>
-      <c r="E7" s="363" t="s">
+      <c r="E7" s="362" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="279"/>
@@ -6219,7 +6397,7 @@
       </c>
       <c r="H7" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I7" s="248"/>
     </row>
@@ -6334,7 +6512,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="364" t="s">
+      <c r="B13" s="363" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="279"/>
@@ -6514,7 +6692,7 @@
       </c>
       <c r="H21" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I21" s="248"/>
     </row>
@@ -6606,7 +6784,7 @@
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="365" t="s">
+      <c r="B27" s="364" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="279"/>
@@ -6715,7 +6893,7 @@
       </c>
       <c r="C33" s="279"/>
       <c r="D33" s="279"/>
-      <c r="E33" s="362">
+      <c r="E33" s="367">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="279"/>
@@ -6766,7 +6944,7 @@
       </c>
       <c r="H35" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I35" s="248"/>
     </row>
@@ -6857,7 +7035,7 @@
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="365" t="s">
+      <c r="B41" s="364" t="s">
         <v>107</v>
       </c>
       <c r="C41" s="279"/>
@@ -6908,7 +7086,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="371" t="s">
+      <c r="B44" s="373" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="279"/>
@@ -7016,7 +7194,7 @@
       </c>
       <c r="H49" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I49" s="248"/>
     </row>
@@ -7233,7 +7411,7 @@
         <v>113</v>
       </c>
       <c r="D62" s="279"/>
-      <c r="E62" s="367">
+      <c r="E62" s="368">
         <v>10500000</v>
       </c>
       <c r="F62" s="279"/>
@@ -7257,7 +7435,7 @@
         <v>115</v>
       </c>
       <c r="D63" s="279"/>
-      <c r="E63" s="366" t="s">
+      <c r="E63" s="365" t="s">
         <v>116</v>
       </c>
       <c r="F63" s="279"/>
@@ -7266,7 +7444,7 @@
       </c>
       <c r="H63" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I63" s="248"/>
     </row>
@@ -7356,7 +7534,7 @@
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="368" t="s">
+      <c r="B69" s="366" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="279"/>
@@ -7463,7 +7641,7 @@
       </c>
       <c r="C75" s="279"/>
       <c r="D75" s="279"/>
-      <c r="E75" s="375">
+      <c r="E75" s="377">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -7510,7 +7688,7 @@
       </c>
       <c r="H77" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I77" s="248"/>
       <c r="K77" s="221">
@@ -7715,7 +7893,7 @@
       </c>
       <c r="C89" s="279"/>
       <c r="D89" s="279"/>
-      <c r="E89" s="362">
+      <c r="E89" s="367">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -7766,7 +7944,7 @@
       </c>
       <c r="H91" s="334">
         <f ca="1">TODAY()</f>
-        <v>45832</v>
+        <v>45841</v>
       </c>
       <c r="I91" s="248"/>
     </row>
@@ -7916,7 +8094,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="373"/>
+      <c r="B100" s="375"/>
       <c r="C100" s="279"/>
       <c r="D100" s="279"/>
       <c r="E100" s="279"/>
@@ -7952,7 +8130,7 @@
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="374"/>
+      <c r="H102" s="376"/>
       <c r="I102" s="248"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
@@ -8150,6 +8328,8 @@
     <mergeCell ref="G81:H81"/>
     <mergeCell ref="G80:H80"/>
     <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="E107:F107"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B102:D102"/>
@@ -8174,7 +8354,10 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="H47:I47"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="B33:D33"/>
@@ -8184,16 +8367,6 @@
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="C49:D49"/>
     <mergeCell ref="H50:I50"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="E73:F73"/>
@@ -8213,6 +8386,11 @@
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
     <mergeCell ref="H107:I107"/>
     <mergeCell ref="C78:D78"/>
     <mergeCell ref="C35:D35"/>
@@ -8684,16 +8862,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="383"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="378"/>
-      <c r="I1" s="378"/>
-      <c r="J1" s="378"/>
-      <c r="K1" s="378"/>
-      <c r="L1" s="378"/>
-      <c r="M1" s="378"/>
-      <c r="N1" s="378"/>
+      <c r="E1" s="385"/>
+      <c r="F1" s="380"/>
+      <c r="G1" s="380"/>
+      <c r="H1" s="380"/>
+      <c r="I1" s="380"/>
+      <c r="J1" s="380"/>
+      <c r="K1" s="380"/>
+      <c r="L1" s="380"/>
+      <c r="M1" s="380"/>
+      <c r="N1" s="380"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -9241,21 +9419,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="376" t="s">
+      <c r="A12" s="378" t="s">
         <v>173</v>
       </c>
       <c r="B12" s="246"/>
-      <c r="C12" s="384" t="s">
+      <c r="C12" s="386" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="378"/>
-      <c r="E12" s="378"/>
-      <c r="F12" s="378"/>
-      <c r="G12" s="378"/>
-      <c r="H12" s="378"/>
-      <c r="I12" s="378"/>
-      <c r="J12" s="378"/>
-      <c r="K12" s="378"/>
+      <c r="D12" s="380"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
+      <c r="G12" s="380"/>
+      <c r="H12" s="380"/>
+      <c r="I12" s="380"/>
+      <c r="J12" s="380"/>
+      <c r="K12" s="380"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -9270,21 +9448,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="376" t="s">
+      <c r="A13" s="378" t="s">
         <v>176</v>
       </c>
       <c r="B13" s="246"/>
-      <c r="C13" s="384" t="s">
+      <c r="C13" s="386" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="378"/>
-      <c r="E13" s="378"/>
-      <c r="F13" s="378"/>
-      <c r="G13" s="378"/>
-      <c r="H13" s="378"/>
-      <c r="I13" s="378"/>
-      <c r="J13" s="378"/>
-      <c r="K13" s="378"/>
+      <c r="D13" s="380"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
+      <c r="G13" s="380"/>
+      <c r="H13" s="380"/>
+      <c r="I13" s="380"/>
+      <c r="J13" s="380"/>
+      <c r="K13" s="380"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -9299,22 +9477,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="376" t="str">
+      <c r="A14" s="378" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
       <c r="B14" s="246"/>
-      <c r="C14" s="384" t="s">
+      <c r="C14" s="386" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="378"/>
-      <c r="E14" s="378"/>
-      <c r="F14" s="378"/>
-      <c r="G14" s="378"/>
-      <c r="H14" s="378"/>
-      <c r="I14" s="378"/>
-      <c r="J14" s="378"/>
-      <c r="K14" s="378"/>
+      <c r="D14" s="380"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
+      <c r="G14" s="380"/>
+      <c r="H14" s="380"/>
+      <c r="I14" s="380"/>
+      <c r="J14" s="380"/>
+      <c r="K14" s="380"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -9329,21 +9507,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="376" t="s">
+      <c r="A15" s="378" t="s">
         <v>160</v>
       </c>
       <c r="B15" s="246"/>
-      <c r="C15" s="384" t="s">
+      <c r="C15" s="386" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="378"/>
-      <c r="E15" s="378"/>
-      <c r="F15" s="378"/>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="378"/>
-      <c r="K15" s="378"/>
+      <c r="D15" s="380"/>
+      <c r="E15" s="380"/>
+      <c r="F15" s="380"/>
+      <c r="G15" s="380"/>
+      <c r="H15" s="380"/>
+      <c r="I15" s="380"/>
+      <c r="J15" s="380"/>
+      <c r="K15" s="380"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -9358,21 +9536,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="376" t="s">
+      <c r="A16" s="378" t="s">
         <v>162</v>
       </c>
       <c r="B16" s="246"/>
-      <c r="C16" s="377" t="s">
+      <c r="C16" s="379" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="378"/>
-      <c r="E16" s="378"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="378"/>
-      <c r="K16" s="378"/>
+      <c r="D16" s="380"/>
+      <c r="E16" s="380"/>
+      <c r="F16" s="380"/>
+      <c r="G16" s="380"/>
+      <c r="H16" s="380"/>
+      <c r="I16" s="380"/>
+      <c r="J16" s="380"/>
+      <c r="K16" s="380"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -9382,21 +9560,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="376" t="s">
+      <c r="A17" s="378" t="s">
         <v>163</v>
       </c>
       <c r="B17" s="246"/>
-      <c r="C17" s="377" t="s">
+      <c r="C17" s="379" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="378"/>
-      <c r="E17" s="378"/>
-      <c r="F17" s="378"/>
-      <c r="G17" s="378"/>
-      <c r="H17" s="378"/>
-      <c r="I17" s="378"/>
-      <c r="J17" s="378"/>
-      <c r="K17" s="378"/>
+      <c r="D17" s="380"/>
+      <c r="E17" s="380"/>
+      <c r="F17" s="380"/>
+      <c r="G17" s="380"/>
+      <c r="H17" s="380"/>
+      <c r="I17" s="380"/>
+      <c r="J17" s="380"/>
+      <c r="K17" s="380"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>185</v>
@@ -9415,21 +9593,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="376" t="s">
+      <c r="A18" s="378" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="246"/>
-      <c r="C18" s="377" t="s">
+      <c r="C18" s="379" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="378"/>
-      <c r="E18" s="378"/>
-      <c r="F18" s="378"/>
-      <c r="G18" s="378"/>
-      <c r="H18" s="378"/>
-      <c r="I18" s="378"/>
-      <c r="J18" s="378"/>
-      <c r="K18" s="378"/>
+      <c r="D18" s="380"/>
+      <c r="E18" s="380"/>
+      <c r="F18" s="380"/>
+      <c r="G18" s="380"/>
+      <c r="H18" s="380"/>
+      <c r="I18" s="380"/>
+      <c r="J18" s="380"/>
+      <c r="K18" s="380"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>188</v>
@@ -9443,21 +9621,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="376" t="s">
+      <c r="A19" s="378" t="s">
         <v>182</v>
       </c>
       <c r="B19" s="246"/>
-      <c r="C19" s="377" t="s">
+      <c r="C19" s="379" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="378"/>
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
-      <c r="G19" s="378"/>
-      <c r="H19" s="378"/>
-      <c r="I19" s="378"/>
-      <c r="J19" s="378"/>
-      <c r="K19" s="378"/>
+      <c r="D19" s="380"/>
+      <c r="E19" s="380"/>
+      <c r="F19" s="380"/>
+      <c r="G19" s="380"/>
+      <c r="H19" s="380"/>
+      <c r="I19" s="380"/>
+      <c r="J19" s="380"/>
+      <c r="K19" s="380"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -9472,21 +9650,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="376" t="s">
+      <c r="A20" s="378" t="s">
         <v>164</v>
       </c>
       <c r="B20" s="246"/>
-      <c r="C20" s="377" t="s">
+      <c r="C20" s="379" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="378"/>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
-      <c r="K20" s="378"/>
+      <c r="D20" s="380"/>
+      <c r="E20" s="380"/>
+      <c r="F20" s="380"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="380"/>
+      <c r="I20" s="380"/>
+      <c r="J20" s="380"/>
+      <c r="K20" s="380"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -9501,21 +9679,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="376" t="s">
+      <c r="A21" s="378" t="s">
         <v>186</v>
       </c>
       <c r="B21" s="246"/>
-      <c r="C21" s="377" t="s">
+      <c r="C21" s="379" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="378"/>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
-      <c r="K21" s="378"/>
+      <c r="D21" s="380"/>
+      <c r="E21" s="380"/>
+      <c r="F21" s="380"/>
+      <c r="G21" s="380"/>
+      <c r="H21" s="380"/>
+      <c r="I21" s="380"/>
+      <c r="J21" s="380"/>
+      <c r="K21" s="380"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -9530,24 +9708,24 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="376" t="s">
+      <c r="A22" s="378" t="s">
         <v>192</v>
       </c>
       <c r="B22" s="246"/>
-      <c r="C22" s="385" t="s">
+      <c r="C22" s="387" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="378"/>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
-      <c r="K22" s="378"/>
-      <c r="L22" s="378"/>
-      <c r="M22" s="378"/>
-      <c r="N22" s="378"/>
+      <c r="D22" s="380"/>
+      <c r="E22" s="380"/>
+      <c r="F22" s="380"/>
+      <c r="G22" s="380"/>
+      <c r="H22" s="380"/>
+      <c r="I22" s="380"/>
+      <c r="J22" s="380"/>
+      <c r="K22" s="380"/>
+      <c r="L22" s="380"/>
+      <c r="M22" s="380"/>
+      <c r="N22" s="380"/>
       <c r="O22" s="248"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
@@ -9559,22 +9737,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="376" t="s">
+      <c r="A23" s="378" t="s">
         <v>194</v>
       </c>
       <c r="B23" s="246"/>
-      <c r="C23" s="377" t="s">
+      <c r="C23" s="379" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="378"/>
-      <c r="E23" s="378"/>
-      <c r="F23" s="378"/>
-      <c r="G23" s="378"/>
-      <c r="H23" s="378"/>
-      <c r="I23" s="378"/>
-      <c r="J23" s="378"/>
-      <c r="K23" s="378"/>
-      <c r="L23" s="378"/>
+      <c r="D23" s="380"/>
+      <c r="E23" s="380"/>
+      <c r="F23" s="380"/>
+      <c r="G23" s="380"/>
+      <c r="H23" s="380"/>
+      <c r="I23" s="380"/>
+      <c r="J23" s="380"/>
+      <c r="K23" s="380"/>
+      <c r="L23" s="380"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -9588,22 +9766,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="376" t="s">
+      <c r="A24" s="378" t="s">
         <v>196</v>
       </c>
       <c r="B24" s="246"/>
-      <c r="C24" s="377" t="s">
+      <c r="C24" s="379" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="378"/>
-      <c r="E24" s="378"/>
-      <c r="F24" s="378"/>
-      <c r="G24" s="378"/>
-      <c r="H24" s="378"/>
-      <c r="I24" s="378"/>
-      <c r="J24" s="378"/>
-      <c r="K24" s="378"/>
-      <c r="L24" s="378"/>
+      <c r="D24" s="380"/>
+      <c r="E24" s="380"/>
+      <c r="F24" s="380"/>
+      <c r="G24" s="380"/>
+      <c r="H24" s="380"/>
+      <c r="I24" s="380"/>
+      <c r="J24" s="380"/>
+      <c r="K24" s="380"/>
+      <c r="L24" s="380"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -9617,21 +9795,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="376" t="s">
+      <c r="A25" s="378" t="s">
         <v>198</v>
       </c>
       <c r="B25" s="246"/>
-      <c r="C25" s="377" t="s">
+      <c r="C25" s="379" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="378"/>
-      <c r="E25" s="378"/>
-      <c r="F25" s="378"/>
-      <c r="G25" s="378"/>
-      <c r="H25" s="378"/>
-      <c r="I25" s="378"/>
-      <c r="J25" s="378"/>
-      <c r="K25" s="378"/>
+      <c r="D25" s="380"/>
+      <c r="E25" s="380"/>
+      <c r="F25" s="380"/>
+      <c r="G25" s="380"/>
+      <c r="H25" s="380"/>
+      <c r="I25" s="380"/>
+      <c r="J25" s="380"/>
+      <c r="K25" s="380"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -9641,21 +9819,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="379" t="s">
+      <c r="A26" s="381" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="380"/>
-      <c r="C26" s="381" t="s">
+      <c r="B26" s="382"/>
+      <c r="C26" s="383" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="382"/>
-      <c r="E26" s="382"/>
-      <c r="F26" s="382"/>
-      <c r="G26" s="382"/>
-      <c r="H26" s="382"/>
-      <c r="I26" s="382"/>
-      <c r="J26" s="382"/>
-      <c r="K26" s="382"/>
+      <c r="D26" s="384"/>
+      <c r="E26" s="384"/>
+      <c r="F26" s="384"/>
+      <c r="G26" s="384"/>
+      <c r="H26" s="384"/>
+      <c r="I26" s="384"/>
+      <c r="J26" s="384"/>
+      <c r="K26" s="384"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -9763,7 +9941,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="402" t="str">
+      <c r="C4" s="404" t="str">
         <f>'AREA UTIL '!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -9774,7 +9952,7 @@
       <c r="H4" s="243"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="402" t="s">
+      <c r="C5" s="404" t="s">
         <v>204</v>
       </c>
       <c r="D5" s="243"/>
@@ -9784,12 +9962,12 @@
       <c r="H5" s="243"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="387" t="s">
+      <c r="C6" s="389" t="s">
         <v>190</v>
       </c>
       <c r="D6" s="243"/>
       <c r="E6" s="243"/>
-      <c r="F6" s="388">
+      <c r="F6" s="390">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
@@ -9797,12 +9975,12 @@
       <c r="H6" s="248"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="387" t="s">
+      <c r="C7" s="389" t="s">
         <v>205</v>
       </c>
       <c r="D7" s="243"/>
       <c r="E7" s="243"/>
-      <c r="F7" s="388">
+      <c r="F7" s="390">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
@@ -9810,12 +9988,12 @@
       <c r="H7" s="248"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="387" t="s">
+      <c r="C8" s="389" t="s">
         <v>206</v>
       </c>
       <c r="D8" s="243"/>
       <c r="E8" s="243"/>
-      <c r="F8" s="388">
+      <c r="F8" s="390">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
@@ -9823,12 +10001,12 @@
       <c r="H8" s="248"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="387" t="s">
+      <c r="C9" s="389" t="s">
         <v>207</v>
       </c>
       <c r="D9" s="243"/>
       <c r="E9" s="243"/>
-      <c r="F9" s="390">
+      <c r="F9" s="392">
         <v>6</v>
       </c>
       <c r="G9" s="243"/>
@@ -9838,12 +10016,12 @@
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="387" t="s">
+      <c r="C10" s="389" t="s">
         <v>209</v>
       </c>
       <c r="D10" s="243"/>
       <c r="E10" s="243"/>
-      <c r="F10" s="390">
+      <c r="F10" s="392">
         <v>1</v>
       </c>
       <c r="G10" s="243"/>
@@ -9853,12 +10031,12 @@
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="387" t="s">
+      <c r="C11" s="389" t="s">
         <v>200</v>
       </c>
       <c r="D11" s="243"/>
       <c r="E11" s="243"/>
-      <c r="F11" s="399">
+      <c r="F11" s="401">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
@@ -9866,12 +10044,12 @@
       <c r="H11" s="248"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="387" t="s">
+      <c r="C12" s="389" t="s">
         <v>210</v>
       </c>
       <c r="D12" s="243"/>
       <c r="E12" s="243"/>
-      <c r="F12" s="390">
+      <c r="F12" s="392">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
@@ -9879,12 +10057,12 @@
       <c r="H12" s="248"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="387" t="s">
+      <c r="C13" s="389" t="s">
         <v>198</v>
       </c>
       <c r="D13" s="243"/>
       <c r="E13" s="243"/>
-      <c r="F13" s="388">
+      <c r="F13" s="390">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
@@ -9892,18 +10070,18 @@
       <c r="H13" s="248"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="397" t="s">
+      <c r="C14" s="399" t="s">
         <v>211</v>
       </c>
       <c r="D14" s="245"/>
       <c r="E14" s="245"/>
-      <c r="F14" s="396">
+      <c r="F14" s="398">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
       <c r="G14" s="245"/>
       <c r="H14" s="246"/>
-      <c r="J14" s="400">
+      <c r="J14" s="402">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
@@ -9911,7 +10089,7 @@
       <c r="L14" s="243"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="404"/>
+      <c r="C15" s="406"/>
       <c r="D15" s="243"/>
       <c r="E15" s="243"/>
       <c r="F15" s="243"/>
@@ -9919,7 +10097,7 @@
       <c r="H15" s="243"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="386" t="s">
+      <c r="C16" s="388" t="s">
         <v>212</v>
       </c>
       <c r="D16" s="243"/>
@@ -9929,12 +10107,12 @@
       <c r="H16" s="243"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="387" t="s">
+      <c r="C17" s="389" t="s">
         <v>213</v>
       </c>
       <c r="D17" s="243"/>
       <c r="E17" s="243"/>
-      <c r="F17" s="390">
+      <c r="F17" s="392">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
@@ -9942,12 +10120,12 @@
       <c r="H17" s="248"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="387" t="s">
+      <c r="C18" s="389" t="s">
         <v>214</v>
       </c>
       <c r="D18" s="243"/>
       <c r="E18" s="243"/>
-      <c r="F18" s="388">
+      <c r="F18" s="390">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
@@ -9955,12 +10133,12 @@
       <c r="H18" s="248"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="387" t="s">
+      <c r="C19" s="389" t="s">
         <v>215</v>
       </c>
       <c r="D19" s="243"/>
       <c r="E19" s="243"/>
-      <c r="F19" s="388">
+      <c r="F19" s="390">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
@@ -9968,12 +10146,12 @@
       <c r="H19" s="248"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="397" t="s">
+      <c r="C20" s="399" t="s">
         <v>216</v>
       </c>
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="396">
+      <c r="F20" s="398">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
@@ -9981,31 +10159,31 @@
       <c r="H20" s="246"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="391"/>
+      <c r="C21" s="393"/>
       <c r="D21" s="243"/>
       <c r="E21" s="243"/>
-      <c r="F21" s="394"/>
+      <c r="F21" s="396"/>
       <c r="G21" s="243"/>
       <c r="H21" s="243"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="391"/>
+      <c r="C22" s="393"/>
       <c r="D22" s="243"/>
       <c r="E22" s="243"/>
-      <c r="F22" s="394"/>
+      <c r="F22" s="396"/>
       <c r="G22" s="243"/>
       <c r="H22" s="243"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="391"/>
+      <c r="C23" s="393"/>
       <c r="D23" s="243"/>
       <c r="E23" s="243"/>
-      <c r="F23" s="403"/>
+      <c r="F23" s="405"/>
       <c r="G23" s="243"/>
       <c r="H23" s="243"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="401" t="s">
+      <c r="C24" s="403" t="s">
         <v>217</v>
       </c>
       <c r="D24" s="243"/>
@@ -10015,36 +10193,36 @@
       <c r="H24" s="243"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="392" t="s">
+      <c r="C25" s="394" t="s">
         <v>218</v>
       </c>
       <c r="D25" s="243"/>
       <c r="E25" s="243"/>
-      <c r="F25" s="395">
+      <c r="F25" s="397">
         <v>2000000</v>
       </c>
       <c r="G25" s="243"/>
       <c r="H25" s="248"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="392" t="s">
+      <c r="C26" s="394" t="s">
         <v>219</v>
       </c>
       <c r="D26" s="243"/>
       <c r="E26" s="243"/>
-      <c r="F26" s="389">
+      <c r="F26" s="391">
         <v>0.8</v>
       </c>
       <c r="G26" s="243"/>
       <c r="H26" s="248"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="392" t="s">
+      <c r="C27" s="394" t="s">
         <v>220</v>
       </c>
       <c r="D27" s="243"/>
       <c r="E27" s="243"/>
-      <c r="F27" s="395">
+      <c r="F27" s="397">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
@@ -10052,12 +10230,12 @@
       <c r="H27" s="248"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="398" t="s">
+      <c r="C28" s="400" t="s">
         <v>216</v>
       </c>
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="393">
+      <c r="F28" s="395">
         <f>F27</f>
         <v>1600000</v>
       </c>
@@ -10065,7 +10243,7 @@
       <c r="H28" s="246"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="386" t="s">
+      <c r="C31" s="388" t="s">
         <v>221</v>
       </c>
       <c r="D31" s="243"/>
@@ -10075,12 +10253,12 @@
       <c r="H31" s="243"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="387" t="s">
+      <c r="C32" s="389" t="s">
         <v>222</v>
       </c>
       <c r="D32" s="243"/>
       <c r="E32" s="243"/>
-      <c r="F32" s="388">
+      <c r="F32" s="390">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
@@ -10088,12 +10266,12 @@
       <c r="H32" s="248"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="387" t="s">
+      <c r="C33" s="389" t="s">
         <v>223</v>
       </c>
       <c r="D33" s="243"/>
       <c r="E33" s="243"/>
-      <c r="F33" s="388">
+      <c r="F33" s="390">
         <f>F28</f>
         <v>1600000</v>
       </c>
@@ -10101,12 +10279,12 @@
       <c r="H33" s="248"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="397" t="s">
+      <c r="C34" s="399" t="s">
         <v>224</v>
       </c>
       <c r="D34" s="245"/>
       <c r="E34" s="245"/>
-      <c r="F34" s="396">
+      <c r="F34" s="398">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
@@ -10185,7 +10363,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="402" t="str">
+      <c r="C5" s="404" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -10196,7 +10374,7 @@
       <c r="H5" s="243"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="402" t="s">
+      <c r="C6" s="404" t="s">
         <v>225</v>
       </c>
       <c r="D6" s="243"/>
@@ -10206,36 +10384,36 @@
       <c r="H6" s="243"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="387" t="s">
+      <c r="C7" s="389" t="s">
         <v>226</v>
       </c>
       <c r="D7" s="243"/>
       <c r="E7" s="243"/>
-      <c r="F7" s="406">
+      <c r="F7" s="408">
         <v>0.13250000000000001</v>
       </c>
       <c r="G7" s="243"/>
       <c r="H7" s="248"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="387" t="s">
+      <c r="C8" s="389" t="s">
         <v>227</v>
       </c>
       <c r="D8" s="243"/>
       <c r="E8" s="243"/>
-      <c r="F8" s="390">
+      <c r="F8" s="392">
         <v>36</v>
       </c>
       <c r="G8" s="243"/>
       <c r="H8" s="248"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="387" t="s">
+      <c r="C9" s="389" t="s">
         <v>228</v>
       </c>
       <c r="D9" s="243"/>
       <c r="E9" s="243"/>
-      <c r="F9" s="405">
+      <c r="F9" s="407">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
@@ -10243,12 +10421,12 @@
       <c r="H9" s="248"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="387" t="s">
+      <c r="C10" s="389" t="s">
         <v>229</v>
       </c>
       <c r="D10" s="243"/>
       <c r="E10" s="243"/>
-      <c r="F10" s="388">
+      <c r="F10" s="390">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
@@ -10256,12 +10434,12 @@
       <c r="H10" s="248"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="397" t="s">
+      <c r="C11" s="399" t="s">
         <v>230</v>
       </c>
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="396">
+      <c r="F11" s="398">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
@@ -10273,7 +10451,7 @@
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="386" t="s">
+      <c r="C13" s="388" t="s">
         <v>225</v>
       </c>
       <c r="D13" s="243"/>
@@ -10284,36 +10462,36 @@
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="387" t="s">
+      <c r="C14" s="389" t="s">
         <v>226</v>
       </c>
       <c r="D14" s="243"/>
       <c r="E14" s="243"/>
-      <c r="F14" s="406">
+      <c r="F14" s="408">
         <v>0.12767999999999999</v>
       </c>
       <c r="G14" s="243"/>
       <c r="H14" s="248"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="387" t="s">
+      <c r="C15" s="389" t="s">
         <v>227</v>
       </c>
       <c r="D15" s="243"/>
       <c r="E15" s="243"/>
-      <c r="F15" s="390">
+      <c r="F15" s="392">
         <v>36</v>
       </c>
       <c r="G15" s="243"/>
       <c r="H15" s="248"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="387" t="s">
+      <c r="C16" s="389" t="s">
         <v>228</v>
       </c>
       <c r="D16" s="243"/>
       <c r="E16" s="243"/>
-      <c r="F16" s="405">
+      <c r="F16" s="407">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
@@ -10321,12 +10499,12 @@
       <c r="H16" s="248"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="387" t="s">
+      <c r="C17" s="389" t="s">
         <v>229</v>
       </c>
       <c r="D17" s="243"/>
       <c r="E17" s="243"/>
-      <c r="F17" s="388">
+      <c r="F17" s="390">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
@@ -10334,12 +10512,12 @@
       <c r="H17" s="248"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="397" t="s">
+      <c r="C18" s="399" t="s">
         <v>230</v>
       </c>
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="396">
+      <c r="F18" s="398">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
@@ -10411,37 +10589,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="423" t="s">
+      <c r="B2" s="425" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="424"/>
-      <c r="D2" s="424"/>
-      <c r="E2" s="424"/>
-      <c r="F2" s="424"/>
-      <c r="G2" s="424"/>
-      <c r="H2" s="424"/>
-      <c r="I2" s="424"/>
-      <c r="J2" s="424"/>
-      <c r="K2" s="424"/>
-      <c r="L2" s="424"/>
-      <c r="M2" s="424"/>
-      <c r="N2" s="424"/>
-      <c r="O2" s="424"/>
-      <c r="P2" s="424"/>
-      <c r="Q2" s="424"/>
-      <c r="R2" s="424"/>
-      <c r="S2" s="424"/>
-      <c r="T2" s="424"/>
-      <c r="U2" s="424"/>
-      <c r="V2" s="424"/>
-      <c r="W2" s="424"/>
-      <c r="X2" s="424"/>
-      <c r="Y2" s="424"/>
-      <c r="Z2" s="424"/>
-      <c r="AA2" s="424"/>
-      <c r="AB2" s="424"/>
-      <c r="AC2" s="424"/>
-      <c r="AD2" s="424"/>
+      <c r="C2" s="426"/>
+      <c r="D2" s="426"/>
+      <c r="E2" s="426"/>
+      <c r="F2" s="426"/>
+      <c r="G2" s="426"/>
+      <c r="H2" s="426"/>
+      <c r="I2" s="426"/>
+      <c r="J2" s="426"/>
+      <c r="K2" s="426"/>
+      <c r="L2" s="426"/>
+      <c r="M2" s="426"/>
+      <c r="N2" s="426"/>
+      <c r="O2" s="426"/>
+      <c r="P2" s="426"/>
+      <c r="Q2" s="426"/>
+      <c r="R2" s="426"/>
+      <c r="S2" s="426"/>
+      <c r="T2" s="426"/>
+      <c r="U2" s="426"/>
+      <c r="V2" s="426"/>
+      <c r="W2" s="426"/>
+      <c r="X2" s="426"/>
+      <c r="Y2" s="426"/>
+      <c r="Z2" s="426"/>
+      <c r="AA2" s="426"/>
+      <c r="AB2" s="426"/>
+      <c r="AC2" s="426"/>
+      <c r="AD2" s="426"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -10568,39 +10746,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="415">
+      <c r="B10" s="417">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="411"/>
-      <c r="D10" s="411"/>
-      <c r="E10" s="411"/>
-      <c r="F10" s="411"/>
-      <c r="G10" s="411"/>
+      <c r="C10" s="413"/>
+      <c r="D10" s="413"/>
+      <c r="E10" s="413"/>
+      <c r="F10" s="413"/>
+      <c r="G10" s="413"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="432">
+      <c r="I10" s="434">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="411"/>
-      <c r="K10" s="411"/>
-      <c r="L10" s="411"/>
-      <c r="M10" s="411"/>
-      <c r="N10" s="411"/>
-      <c r="O10" s="411"/>
-      <c r="P10" s="411"/>
+      <c r="J10" s="413"/>
+      <c r="K10" s="413"/>
+      <c r="L10" s="413"/>
+      <c r="M10" s="413"/>
+      <c r="N10" s="413"/>
+      <c r="O10" s="413"/>
+      <c r="P10" s="413"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="410">
+      <c r="R10" s="412">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="411"/>
-      <c r="T10" s="411"/>
-      <c r="U10" s="411"/>
+      <c r="S10" s="413"/>
+      <c r="T10" s="413"/>
+      <c r="U10" s="413"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -10635,13 +10813,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="410">
+      <c r="W11" s="412">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="411"/>
-      <c r="Y11" s="411"/>
-      <c r="Z11" s="411"/>
+      <c r="X11" s="413"/>
+      <c r="Y11" s="413"/>
+      <c r="Z11" s="413"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -10668,13 +10846,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="430">
+      <c r="R12" s="432">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="411"/>
-      <c r="T12" s="411"/>
-      <c r="U12" s="411"/>
+      <c r="S12" s="413"/>
+      <c r="T12" s="413"/>
+      <c r="U12" s="413"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -10694,10 +10872,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="422"/>
-      <c r="X14" s="411"/>
-      <c r="Y14" s="411"/>
-      <c r="Z14" s="411"/>
+      <c r="W14" s="424"/>
+      <c r="X14" s="413"/>
+      <c r="Y14" s="413"/>
+      <c r="Z14" s="413"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -10723,38 +10901,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="427" t="s">
+      <c r="B16" s="429" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="411"/>
-      <c r="D16" s="411"/>
-      <c r="E16" s="411"/>
-      <c r="F16" s="411"/>
-      <c r="G16" s="411"/>
+      <c r="C16" s="413"/>
+      <c r="D16" s="413"/>
+      <c r="E16" s="413"/>
+      <c r="F16" s="413"/>
+      <c r="G16" s="413"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="417" t="str">
+      <c r="I16" s="419" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="411"/>
-      <c r="K16" s="411"/>
-      <c r="L16" s="411"/>
-      <c r="M16" s="411"/>
-      <c r="N16" s="411"/>
-      <c r="O16" s="411"/>
-      <c r="P16" s="411"/>
+      <c r="J16" s="413"/>
+      <c r="K16" s="413"/>
+      <c r="L16" s="413"/>
+      <c r="M16" s="413"/>
+      <c r="N16" s="413"/>
+      <c r="O16" s="413"/>
+      <c r="P16" s="413"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="422" t="str">
+      <c r="R16" s="424" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="411"/>
-      <c r="T16" s="411"/>
-      <c r="U16" s="411"/>
+      <c r="S16" s="413"/>
+      <c r="T16" s="413"/>
+      <c r="U16" s="413"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -10766,10 +10944,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="422"/>
-      <c r="X17" s="411"/>
-      <c r="Y17" s="411"/>
-      <c r="Z17" s="411"/>
+      <c r="W17" s="424"/>
+      <c r="X17" s="413"/>
+      <c r="Y17" s="413"/>
+      <c r="Z17" s="413"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -10793,13 +10971,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="421" t="str">
+      <c r="R18" s="423" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="411"/>
-      <c r="T18" s="411"/>
-      <c r="U18" s="411"/>
+      <c r="S18" s="413"/>
+      <c r="T18" s="413"/>
+      <c r="U18" s="413"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -10881,13 +11059,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="431">
+      <c r="W22" s="433">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="414"/>
-      <c r="Y22" s="414"/>
-      <c r="Z22" s="414"/>
+      <c r="X22" s="416"/>
+      <c r="Y22" s="416"/>
+      <c r="Z22" s="416"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -10896,13 +11074,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="413" t="str">
+      <c r="W23" s="415" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="414"/>
-      <c r="Y23" s="414"/>
-      <c r="Z23" s="414"/>
+      <c r="X23" s="416"/>
+      <c r="Y23" s="416"/>
+      <c r="Z23" s="416"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -10911,13 +11089,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="425">
+      <c r="W24" s="427">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="408"/>
-      <c r="Y24" s="408"/>
-      <c r="Z24" s="408"/>
+      <c r="X24" s="410"/>
+      <c r="Y24" s="410"/>
+      <c r="Z24" s="410"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -10926,13 +11104,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="413">
+      <c r="W25" s="415">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="414"/>
-      <c r="Y25" s="414"/>
-      <c r="Z25" s="414"/>
+      <c r="X25" s="416"/>
+      <c r="Y25" s="416"/>
+      <c r="Z25" s="416"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -10941,13 +11119,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="413">
+      <c r="W26" s="415">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="414"/>
-      <c r="Y26" s="414"/>
-      <c r="Z26" s="414"/>
+      <c r="X26" s="416"/>
+      <c r="Y26" s="416"/>
+      <c r="Z26" s="416"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -10956,13 +11134,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="413">
+      <c r="W27" s="415">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="414"/>
-      <c r="Y27" s="414"/>
-      <c r="Z27" s="414"/>
+      <c r="X27" s="416"/>
+      <c r="Y27" s="416"/>
+      <c r="Z27" s="416"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -10971,13 +11149,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="413">
+      <c r="W28" s="415">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="414"/>
-      <c r="Y28" s="414"/>
-      <c r="Z28" s="414"/>
+      <c r="X28" s="416"/>
+      <c r="Y28" s="416"/>
+      <c r="Z28" s="416"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -10986,13 +11164,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="413">
+      <c r="W29" s="415">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="414"/>
-      <c r="Y29" s="414"/>
-      <c r="Z29" s="414"/>
+      <c r="X29" s="416"/>
+      <c r="Y29" s="416"/>
+      <c r="Z29" s="416"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -11001,13 +11179,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="426">
+      <c r="W30" s="428">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="408"/>
-      <c r="Y30" s="408"/>
-      <c r="Z30" s="408"/>
+      <c r="X30" s="410"/>
+      <c r="Y30" s="410"/>
+      <c r="Z30" s="410"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -11017,51 +11195,51 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="429">
+      <c r="W31" s="431">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="408"/>
-      <c r="Y31" s="408"/>
-      <c r="Z31" s="408"/>
+      <c r="X31" s="410"/>
+      <c r="Y31" s="410"/>
+      <c r="Z31" s="410"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="428">
+      <c r="K32" s="430">
         <v>43009</v>
       </c>
-      <c r="L32" s="414"/>
-      <c r="M32" s="414"/>
-      <c r="N32" s="414"/>
-      <c r="O32" s="414"/>
-      <c r="P32" s="414"/>
-      <c r="Q32" s="414"/>
-      <c r="R32" s="414"/>
-      <c r="S32" s="414"/>
-      <c r="T32" s="414"/>
-      <c r="U32" s="414"/>
-      <c r="V32" s="414"/>
-      <c r="W32" s="414"/>
-      <c r="X32" s="414"/>
-      <c r="Y32" s="414"/>
-      <c r="Z32" s="414"/>
+      <c r="L32" s="416"/>
+      <c r="M32" s="416"/>
+      <c r="N32" s="416"/>
+      <c r="O32" s="416"/>
+      <c r="P32" s="416"/>
+      <c r="Q32" s="416"/>
+      <c r="R32" s="416"/>
+      <c r="S32" s="416"/>
+      <c r="T32" s="416"/>
+      <c r="U32" s="416"/>
+      <c r="V32" s="416"/>
+      <c r="W32" s="416"/>
+      <c r="X32" s="416"/>
+      <c r="Y32" s="416"/>
+      <c r="Z32" s="416"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="407" t="s">
+      <c r="O33" s="409" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="408"/>
-      <c r="Q33" s="408"/>
-      <c r="R33" s="408"/>
-      <c r="S33" s="408"/>
-      <c r="T33" s="408"/>
-      <c r="U33" s="408"/>
-      <c r="V33" s="408"/>
-      <c r="W33" s="412" t="s">
+      <c r="P33" s="410"/>
+      <c r="Q33" s="410"/>
+      <c r="R33" s="410"/>
+      <c r="S33" s="410"/>
+      <c r="T33" s="410"/>
+      <c r="U33" s="410"/>
+      <c r="V33" s="410"/>
+      <c r="W33" s="414" t="s">
         <v>256</v>
       </c>
       <c r="X33" s="319"/>
@@ -11076,24 +11254,24 @@
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="419">
+      <c r="Q34" s="421">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="414"/>
-      <c r="S34" s="414"/>
-      <c r="T34" s="414"/>
+      <c r="R34" s="416"/>
+      <c r="S34" s="416"/>
+      <c r="T34" s="416"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="419">
+      <c r="Y34" s="421">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="414"/>
-      <c r="AA34" s="414"/>
-      <c r="AB34" s="414"/>
+      <c r="Z34" s="416"/>
+      <c r="AA34" s="416"/>
+      <c r="AB34" s="416"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -11156,32 +11334,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="416"/>
-      <c r="C38" s="411"/>
+      <c r="B38" s="418"/>
+      <c r="C38" s="413"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="416"/>
-      <c r="C39" s="411"/>
+      <c r="B39" s="418"/>
+      <c r="C39" s="413"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="416"/>
-      <c r="C40" s="411"/>
+      <c r="B40" s="418"/>
+      <c r="C40" s="413"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="416"/>
-      <c r="C41" s="411"/>
+      <c r="B41" s="418"/>
+      <c r="C41" s="413"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="416"/>
-      <c r="C42" s="411"/>
+      <c r="B42" s="418"/>
+      <c r="C42" s="413"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="416"/>
-      <c r="C43" s="411"/>
+      <c r="B43" s="418"/>
+      <c r="C43" s="413"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="416"/>
-      <c r="C44" s="411"/>
+      <c r="B44" s="418"/>
+      <c r="C44" s="413"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -11252,10 +11430,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="420"/>
-      <c r="F49" s="411"/>
-      <c r="G49" s="411"/>
-      <c r="H49" s="411"/>
+      <c r="E49" s="422"/>
+      <c r="F49" s="413"/>
+      <c r="G49" s="413"/>
+      <c r="H49" s="413"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -11278,7 +11456,7 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="409"/>
+      <c r="H52" s="411"/>
       <c r="I52" s="319"/>
       <c r="J52" s="319"/>
       <c r="K52" s="319"/>
@@ -11291,7 +11469,7 @@
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="418"/>
+      <c r="H55" s="420"/>
       <c r="I55" s="319"/>
       <c r="J55" s="319"/>
       <c r="K55" s="319"/>
@@ -11303,7 +11481,7 @@
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="409"/>
+      <c r="H57" s="411"/>
       <c r="I57" s="319"/>
       <c r="J57" s="319"/>
       <c r="K57" s="319"/>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\1. AVALIAÇÕES\01. AVALIAÇÕES SICREDI\01. RURAL\07. JULHO\Processo nº 123456789 - JOELSON SOUSA JUNIOR\PEÇAS TÉCNICAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\automacao_laudo\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930" tabRatio="874" activeTab="4"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930" tabRatio="874" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -2904,41 +2904,84 @@
     <xf numFmtId="0" fontId="63" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="63" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2953,46 +2996,6 @@
     </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3004,38 +3007,65 @@
     <xf numFmtId="0" fontId="63" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3048,82 +3078,52 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3133,61 +3133,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3197,119 +3293,29 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3319,122 +3325,104 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3442,18 +3430,69 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3464,35 +3503,11 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3508,40 +3523,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3960,34 +3960,34 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="246" t="s">
+      <c r="B3" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="255"/>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="255"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="255"/>
-      <c r="K3" s="255"/>
-      <c r="L3" s="255"/>
-      <c r="M3" s="256"/>
+      <c r="C3" s="256"/>
+      <c r="D3" s="256"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="256"/>
+      <c r="I3" s="256"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="256"/>
+      <c r="L3" s="256"/>
+      <c r="M3" s="261"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="268"/>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="250"/>
-      <c r="H4" s="250"/>
-      <c r="I4" s="250"/>
-      <c r="J4" s="250"/>
-      <c r="K4" s="250"/>
-      <c r="L4" s="250"/>
-      <c r="M4" s="258"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="M4" s="263"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -4018,100 +4018,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="251" t="s">
+      <c r="B7" s="247" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="252"/>
-      <c r="D7" s="252"/>
-      <c r="E7" s="269"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="252"/>
-      <c r="L7" s="252"/>
-      <c r="M7" s="262"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="252"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="253"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="251" t="s">
+      <c r="B8" s="247" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="252"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="269"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="252"/>
-      <c r="H8" s="252"/>
-      <c r="I8" s="252"/>
-      <c r="J8" s="252"/>
-      <c r="K8" s="252"/>
-      <c r="L8" s="252"/>
-      <c r="M8" s="262"/>
+      <c r="C8" s="248"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="252"/>
+      <c r="F8" s="248"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="248"/>
+      <c r="I8" s="248"/>
+      <c r="J8" s="248"/>
+      <c r="K8" s="248"/>
+      <c r="L8" s="248"/>
+      <c r="M8" s="253"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="251" t="s">
+      <c r="B9" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="252"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="269"/>
-      <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
-      <c r="H9" s="252"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="252"/>
-      <c r="K9" s="252"/>
-      <c r="L9" s="252"/>
-      <c r="M9" s="262"/>
+      <c r="C9" s="248"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="252"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
+      <c r="M9" s="253"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="251" t="s">
+      <c r="B10" s="247" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="252"/>
-      <c r="D10" s="252"/>
-      <c r="E10" s="269"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
-      <c r="M10" s="262"/>
+      <c r="C10" s="248"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="248"/>
+      <c r="K10" s="248"/>
+      <c r="L10" s="248"/>
+      <c r="M10" s="253"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="251" t="s">
+      <c r="B11" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="252"/>
-      <c r="D11" s="252"/>
-      <c r="E11" s="269"/>
-      <c r="F11" s="252"/>
-      <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="252"/>
-      <c r="K11" s="252"/>
-      <c r="L11" s="252"/>
-      <c r="M11" s="262"/>
+      <c r="C11" s="248"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="252"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
+      <c r="M11" s="253"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="251" t="s">
+      <c r="B12" s="247" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="252"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="269"/>
-      <c r="F12" s="252"/>
-      <c r="G12" s="252"/>
-      <c r="H12" s="252"/>
-      <c r="I12" s="252"/>
-      <c r="J12" s="252"/>
-      <c r="K12" s="252"/>
-      <c r="L12" s="252"/>
-      <c r="M12" s="262"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="252"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
+      <c r="M12" s="253"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4170,20 +4170,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="280" t="s">
+      <c r="B17" s="254" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="252"/>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
-      <c r="J17" s="252"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="252"/>
-      <c r="M17" s="252"/>
+      <c r="C17" s="248"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
+      <c r="M17" s="248"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4200,150 +4200,150 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="281" t="s">
+      <c r="B19" s="255" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="255"/>
-      <c r="D19" s="255"/>
-      <c r="E19" s="279"/>
-      <c r="F19" s="255"/>
-      <c r="G19" s="255"/>
-      <c r="H19" s="255"/>
-      <c r="I19" s="255"/>
-      <c r="J19" s="255"/>
-      <c r="K19" s="255"/>
-      <c r="L19" s="255"/>
-      <c r="M19" s="256"/>
+      <c r="C19" s="256"/>
+      <c r="D19" s="256"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="256"/>
+      <c r="H19" s="256"/>
+      <c r="I19" s="256"/>
+      <c r="J19" s="256"/>
+      <c r="K19" s="256"/>
+      <c r="L19" s="256"/>
+      <c r="M19" s="261"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="251" t="s">
+      <c r="B20" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="252"/>
-      <c r="D20" s="252"/>
-      <c r="E20" s="269"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
-      <c r="H20" s="252"/>
-      <c r="I20" s="252"/>
-      <c r="J20" s="252"/>
-      <c r="K20" s="252"/>
-      <c r="L20" s="252"/>
-      <c r="M20" s="262"/>
+      <c r="C20" s="248"/>
+      <c r="D20" s="248"/>
+      <c r="E20" s="252"/>
+      <c r="F20" s="248"/>
+      <c r="G20" s="248"/>
+      <c r="H20" s="248"/>
+      <c r="I20" s="248"/>
+      <c r="J20" s="248"/>
+      <c r="K20" s="248"/>
+      <c r="L20" s="248"/>
+      <c r="M20" s="253"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="251" t="s">
+      <c r="B21" s="247" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="252"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="269"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="252"/>
-      <c r="J21" s="252"/>
-      <c r="K21" s="252"/>
-      <c r="L21" s="252"/>
-      <c r="M21" s="262"/>
+      <c r="C21" s="248"/>
+      <c r="D21" s="248"/>
+      <c r="E21" s="252"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="248"/>
+      <c r="K21" s="248"/>
+      <c r="L21" s="248"/>
+      <c r="M21" s="253"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="276" t="s">
+      <c r="B22" s="270" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="250"/>
-      <c r="D22" s="250"/>
-      <c r="E22" s="270"/>
-      <c r="F22" s="250"/>
-      <c r="G22" s="250"/>
-      <c r="H22" s="250"/>
-      <c r="I22" s="250"/>
-      <c r="J22" s="250"/>
+      <c r="C22" s="259"/>
+      <c r="D22" s="259"/>
+      <c r="E22" s="264"/>
+      <c r="F22" s="259"/>
+      <c r="G22" s="259"/>
+      <c r="H22" s="259"/>
+      <c r="I22" s="259"/>
+      <c r="J22" s="259"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="274"/>
-      <c r="M22" s="258"/>
+      <c r="L22" s="268"/>
+      <c r="M22" s="263"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="246" t="s">
+      <c r="B23" s="249" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="247"/>
-      <c r="D23" s="247"/>
-      <c r="E23" s="247"/>
-      <c r="F23" s="247"/>
-      <c r="G23" s="247"/>
-      <c r="H23" s="247"/>
-      <c r="I23" s="247"/>
-      <c r="J23" s="247"/>
-      <c r="K23" s="247"/>
-      <c r="L23" s="247"/>
-      <c r="M23" s="248"/>
+      <c r="C23" s="250"/>
+      <c r="D23" s="250"/>
+      <c r="E23" s="250"/>
+      <c r="F23" s="250"/>
+      <c r="G23" s="250"/>
+      <c r="H23" s="250"/>
+      <c r="I23" s="250"/>
+      <c r="J23" s="250"/>
+      <c r="K23" s="250"/>
+      <c r="L23" s="250"/>
+      <c r="M23" s="251"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="259" t="s">
+      <c r="B24" s="257" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="247"/>
-      <c r="D24" s="248"/>
-      <c r="E24" s="259" t="s">
+      <c r="C24" s="250"/>
+      <c r="D24" s="251"/>
+      <c r="E24" s="257" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="247"/>
-      <c r="G24" s="248"/>
-      <c r="H24" s="259" t="s">
+      <c r="F24" s="250"/>
+      <c r="G24" s="251"/>
+      <c r="H24" s="257" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="247"/>
-      <c r="J24" s="248"/>
-      <c r="K24" s="259" t="s">
+      <c r="I24" s="250"/>
+      <c r="J24" s="251"/>
+      <c r="K24" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="247"/>
-      <c r="M24" s="248"/>
+      <c r="L24" s="250"/>
+      <c r="M24" s="251"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="273"/>
-      <c r="C25" s="255"/>
-      <c r="D25" s="256"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
-      <c r="H25" s="254"/>
-      <c r="I25" s="255"/>
-      <c r="J25" s="256"/>
-      <c r="K25" s="275"/>
-      <c r="L25" s="255"/>
-      <c r="M25" s="256"/>
+      <c r="B25" s="267"/>
+      <c r="C25" s="256"/>
+      <c r="D25" s="261"/>
+      <c r="E25" s="276"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="274"/>
+      <c r="I25" s="256"/>
+      <c r="J25" s="261"/>
+      <c r="K25" s="269"/>
+      <c r="L25" s="256"/>
+      <c r="M25" s="261"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="271"/>
-      <c r="C26" s="250"/>
-      <c r="D26" s="258"/>
-      <c r="E26" s="278"/>
-      <c r="F26" s="250"/>
-      <c r="G26" s="250"/>
-      <c r="H26" s="272"/>
-      <c r="I26" s="250"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="277"/>
-      <c r="L26" s="250"/>
-      <c r="M26" s="258"/>
+      <c r="B26" s="265"/>
+      <c r="C26" s="259"/>
+      <c r="D26" s="263"/>
+      <c r="E26" s="258"/>
+      <c r="F26" s="259"/>
+      <c r="G26" s="259"/>
+      <c r="H26" s="266"/>
+      <c r="I26" s="259"/>
+      <c r="J26" s="263"/>
+      <c r="K26" s="271"/>
+      <c r="L26" s="259"/>
+      <c r="M26" s="263"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="246" t="s">
+      <c r="B27" s="249" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="247"/>
-      <c r="D27" s="247"/>
-      <c r="E27" s="247"/>
-      <c r="F27" s="247"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="247"/>
-      <c r="I27" s="247"/>
-      <c r="J27" s="247"/>
-      <c r="K27" s="247"/>
-      <c r="L27" s="247"/>
-      <c r="M27" s="248"/>
+      <c r="C27" s="250"/>
+      <c r="D27" s="250"/>
+      <c r="E27" s="250"/>
+      <c r="F27" s="250"/>
+      <c r="G27" s="250"/>
+      <c r="H27" s="250"/>
+      <c r="I27" s="250"/>
+      <c r="J27" s="250"/>
+      <c r="K27" s="250"/>
+      <c r="L27" s="250"/>
+      <c r="M27" s="251"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4430,100 +4430,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="246" t="s">
+      <c r="B34" s="249" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="247"/>
-      <c r="D34" s="247"/>
-      <c r="E34" s="247"/>
-      <c r="F34" s="247"/>
-      <c r="G34" s="247"/>
-      <c r="H34" s="247"/>
-      <c r="I34" s="247"/>
-      <c r="J34" s="247"/>
-      <c r="K34" s="247"/>
-      <c r="L34" s="247"/>
-      <c r="M34" s="248"/>
+      <c r="C34" s="250"/>
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="250"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="250"/>
+      <c r="I34" s="250"/>
+      <c r="J34" s="250"/>
+      <c r="K34" s="250"/>
+      <c r="L34" s="250"/>
+      <c r="M34" s="251"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="259" t="s">
+      <c r="B35" s="257" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="247"/>
-      <c r="D35" s="247"/>
-      <c r="E35" s="248"/>
-      <c r="F35" s="259" t="s">
+      <c r="C35" s="250"/>
+      <c r="D35" s="250"/>
+      <c r="E35" s="251"/>
+      <c r="F35" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="247"/>
-      <c r="H35" s="247"/>
-      <c r="I35" s="248"/>
-      <c r="J35" s="259" t="s">
+      <c r="G35" s="250"/>
+      <c r="H35" s="250"/>
+      <c r="I35" s="251"/>
+      <c r="J35" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="247"/>
-      <c r="L35" s="247"/>
-      <c r="M35" s="248"/>
+      <c r="K35" s="250"/>
+      <c r="L35" s="250"/>
+      <c r="M35" s="251"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="265"/>
-      <c r="C36" s="255"/>
-      <c r="D36" s="255"/>
-      <c r="E36" s="255"/>
-      <c r="F36" s="266"/>
-      <c r="G36" s="255"/>
-      <c r="H36" s="255"/>
-      <c r="I36" s="255"/>
-      <c r="J36" s="267"/>
-      <c r="K36" s="255"/>
-      <c r="L36" s="255"/>
-      <c r="M36" s="256"/>
+      <c r="B36" s="280"/>
+      <c r="C36" s="256"/>
+      <c r="D36" s="256"/>
+      <c r="E36" s="256"/>
+      <c r="F36" s="281"/>
+      <c r="G36" s="256"/>
+      <c r="H36" s="256"/>
+      <c r="I36" s="256"/>
+      <c r="J36" s="282"/>
+      <c r="K36" s="256"/>
+      <c r="L36" s="256"/>
+      <c r="M36" s="261"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="253"/>
-      <c r="C37" s="252"/>
-      <c r="D37" s="252"/>
-      <c r="E37" s="252"/>
-      <c r="F37" s="264"/>
-      <c r="G37" s="252"/>
-      <c r="H37" s="252"/>
-      <c r="I37" s="252"/>
-      <c r="J37" s="261"/>
-      <c r="K37" s="252"/>
-      <c r="L37" s="252"/>
-      <c r="M37" s="262"/>
+      <c r="B37" s="273"/>
+      <c r="C37" s="248"/>
+      <c r="D37" s="248"/>
+      <c r="E37" s="248"/>
+      <c r="F37" s="279"/>
+      <c r="G37" s="248"/>
+      <c r="H37" s="248"/>
+      <c r="I37" s="248"/>
+      <c r="J37" s="277"/>
+      <c r="K37" s="248"/>
+      <c r="L37" s="248"/>
+      <c r="M37" s="253"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="263" t="s">
+      <c r="B38" s="278" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="250"/>
-      <c r="D38" s="250"/>
-      <c r="E38" s="250"/>
-      <c r="F38" s="249"/>
-      <c r="G38" s="250"/>
-      <c r="H38" s="250"/>
-      <c r="I38" s="250"/>
-      <c r="J38" s="257"/>
-      <c r="K38" s="250"/>
-      <c r="L38" s="250"/>
-      <c r="M38" s="258"/>
+      <c r="C38" s="259"/>
+      <c r="D38" s="259"/>
+      <c r="E38" s="259"/>
+      <c r="F38" s="272"/>
+      <c r="G38" s="259"/>
+      <c r="H38" s="259"/>
+      <c r="I38" s="259"/>
+      <c r="J38" s="275"/>
+      <c r="K38" s="259"/>
+      <c r="L38" s="259"/>
+      <c r="M38" s="263"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="246" t="s">
+      <c r="B39" s="249" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="247"/>
-      <c r="D39" s="247"/>
-      <c r="E39" s="247"/>
-      <c r="F39" s="247"/>
-      <c r="G39" s="247"/>
-      <c r="H39" s="247"/>
-      <c r="I39" s="247"/>
-      <c r="J39" s="247"/>
-      <c r="K39" s="247"/>
-      <c r="L39" s="247"/>
-      <c r="M39" s="248"/>
+      <c r="C39" s="250"/>
+      <c r="D39" s="250"/>
+      <c r="E39" s="250"/>
+      <c r="F39" s="250"/>
+      <c r="G39" s="250"/>
+      <c r="H39" s="250"/>
+      <c r="I39" s="250"/>
+      <c r="J39" s="250"/>
+      <c r="K39" s="250"/>
+      <c r="L39" s="250"/>
+      <c r="M39" s="251"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4639,25 +4639,22 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B39:M39"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="B34:M34"/>
     <mergeCell ref="B3:M4"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
@@ -4674,22 +4671,25 @@
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B39:M39"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="B34:M34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4730,37 +4730,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="415" t="s">
+      <c r="B2" s="436" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="416"/>
-      <c r="D2" s="416"/>
-      <c r="E2" s="416"/>
-      <c r="F2" s="416"/>
-      <c r="G2" s="416"/>
-      <c r="H2" s="416"/>
-      <c r="I2" s="416"/>
-      <c r="J2" s="416"/>
-      <c r="K2" s="416"/>
-      <c r="L2" s="416"/>
-      <c r="M2" s="416"/>
-      <c r="N2" s="416"/>
-      <c r="O2" s="416"/>
-      <c r="P2" s="416"/>
-      <c r="Q2" s="416"/>
-      <c r="R2" s="416"/>
-      <c r="S2" s="416"/>
-      <c r="T2" s="416"/>
-      <c r="U2" s="416"/>
-      <c r="V2" s="416"/>
-      <c r="W2" s="416"/>
-      <c r="X2" s="416"/>
-      <c r="Y2" s="416"/>
-      <c r="Z2" s="416"/>
-      <c r="AA2" s="416"/>
-      <c r="AB2" s="416"/>
-      <c r="AC2" s="416"/>
-      <c r="AD2" s="416"/>
+      <c r="C2" s="437"/>
+      <c r="D2" s="437"/>
+      <c r="E2" s="437"/>
+      <c r="F2" s="437"/>
+      <c r="G2" s="437"/>
+      <c r="H2" s="437"/>
+      <c r="I2" s="437"/>
+      <c r="J2" s="437"/>
+      <c r="K2" s="437"/>
+      <c r="L2" s="437"/>
+      <c r="M2" s="437"/>
+      <c r="N2" s="437"/>
+      <c r="O2" s="437"/>
+      <c r="P2" s="437"/>
+      <c r="Q2" s="437"/>
+      <c r="R2" s="437"/>
+      <c r="S2" s="437"/>
+      <c r="T2" s="437"/>
+      <c r="U2" s="437"/>
+      <c r="V2" s="437"/>
+      <c r="W2" s="437"/>
+      <c r="X2" s="437"/>
+      <c r="Y2" s="437"/>
+      <c r="Z2" s="437"/>
+      <c r="AA2" s="437"/>
+      <c r="AB2" s="437"/>
+      <c r="AC2" s="437"/>
+      <c r="AD2" s="437"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -4887,39 +4887,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="433">
+      <c r="B10" s="428">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="418"/>
-      <c r="D10" s="418"/>
-      <c r="E10" s="418"/>
-      <c r="F10" s="418"/>
-      <c r="G10" s="418"/>
+      <c r="C10" s="424"/>
+      <c r="D10" s="424"/>
+      <c r="E10" s="424"/>
+      <c r="F10" s="424"/>
+      <c r="G10" s="424"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="432">
+      <c r="I10" s="445">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="418"/>
-      <c r="K10" s="418"/>
-      <c r="L10" s="418"/>
-      <c r="M10" s="418"/>
-      <c r="N10" s="418"/>
-      <c r="O10" s="418"/>
-      <c r="P10" s="418"/>
+      <c r="J10" s="424"/>
+      <c r="K10" s="424"/>
+      <c r="L10" s="424"/>
+      <c r="M10" s="424"/>
+      <c r="N10" s="424"/>
+      <c r="O10" s="424"/>
+      <c r="P10" s="424"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="417">
+      <c r="R10" s="423">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="418"/>
-      <c r="T10" s="418"/>
-      <c r="U10" s="418"/>
+      <c r="S10" s="424"/>
+      <c r="T10" s="424"/>
+      <c r="U10" s="424"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -4954,13 +4954,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="417">
+      <c r="W11" s="423">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="418"/>
-      <c r="Y11" s="418"/>
-      <c r="Z11" s="418"/>
+      <c r="X11" s="424"/>
+      <c r="Y11" s="424"/>
+      <c r="Z11" s="424"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -4987,13 +4987,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="429">
+      <c r="R12" s="443">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="418"/>
-      <c r="T12" s="418"/>
-      <c r="U12" s="418"/>
+      <c r="S12" s="424"/>
+      <c r="T12" s="424"/>
+      <c r="U12" s="424"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -5013,10 +5013,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="422"/>
-      <c r="X14" s="418"/>
-      <c r="Y14" s="418"/>
-      <c r="Z14" s="418"/>
+      <c r="W14" s="435"/>
+      <c r="X14" s="424"/>
+      <c r="Y14" s="424"/>
+      <c r="Z14" s="424"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -5042,38 +5042,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="426" t="s">
+      <c r="B16" s="440" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="418"/>
-      <c r="D16" s="418"/>
-      <c r="E16" s="418"/>
-      <c r="F16" s="418"/>
-      <c r="G16" s="418"/>
+      <c r="C16" s="424"/>
+      <c r="D16" s="424"/>
+      <c r="E16" s="424"/>
+      <c r="F16" s="424"/>
+      <c r="G16" s="424"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="435" t="str">
+      <c r="I16" s="430" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="418"/>
-      <c r="K16" s="418"/>
-      <c r="L16" s="418"/>
-      <c r="M16" s="418"/>
-      <c r="N16" s="418"/>
-      <c r="O16" s="418"/>
-      <c r="P16" s="418"/>
+      <c r="J16" s="424"/>
+      <c r="K16" s="424"/>
+      <c r="L16" s="424"/>
+      <c r="M16" s="424"/>
+      <c r="N16" s="424"/>
+      <c r="O16" s="424"/>
+      <c r="P16" s="424"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="422" t="str">
+      <c r="R16" s="435" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="418"/>
-      <c r="T16" s="418"/>
-      <c r="U16" s="418"/>
+      <c r="S16" s="424"/>
+      <c r="T16" s="424"/>
+      <c r="U16" s="424"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -5085,10 +5085,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="422"/>
-      <c r="X17" s="418"/>
-      <c r="Y17" s="418"/>
-      <c r="Z17" s="418"/>
+      <c r="W17" s="435"/>
+      <c r="X17" s="424"/>
+      <c r="Y17" s="424"/>
+      <c r="Z17" s="424"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -5112,13 +5112,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="438" t="str">
+      <c r="R18" s="434" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="418"/>
-      <c r="T18" s="418"/>
-      <c r="U18" s="418"/>
+      <c r="S18" s="424"/>
+      <c r="T18" s="424"/>
+      <c r="U18" s="424"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -5200,13 +5200,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="430">
+      <c r="W22" s="444">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="425"/>
-      <c r="Y22" s="425"/>
-      <c r="Z22" s="425"/>
+      <c r="X22" s="427"/>
+      <c r="Y22" s="427"/>
+      <c r="Z22" s="427"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -5215,13 +5215,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="424" t="str">
+      <c r="W23" s="426" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="425"/>
-      <c r="Y23" s="425"/>
-      <c r="Z23" s="425"/>
+      <c r="X23" s="427"/>
+      <c r="Y23" s="427"/>
+      <c r="Z23" s="427"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -5230,13 +5230,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="419">
+      <c r="W24" s="438">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="420"/>
-      <c r="Y24" s="420"/>
-      <c r="Z24" s="420"/>
+      <c r="X24" s="421"/>
+      <c r="Y24" s="421"/>
+      <c r="Z24" s="421"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -5245,13 +5245,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="424">
+      <c r="W25" s="426">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="425"/>
-      <c r="Y25" s="425"/>
-      <c r="Z25" s="425"/>
+      <c r="X25" s="427"/>
+      <c r="Y25" s="427"/>
+      <c r="Z25" s="427"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -5260,13 +5260,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="424">
+      <c r="W26" s="426">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="425"/>
-      <c r="Y26" s="425"/>
-      <c r="Z26" s="425"/>
+      <c r="X26" s="427"/>
+      <c r="Y26" s="427"/>
+      <c r="Z26" s="427"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -5275,13 +5275,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="424">
+      <c r="W27" s="426">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="425"/>
-      <c r="Y27" s="425"/>
-      <c r="Z27" s="425"/>
+      <c r="X27" s="427"/>
+      <c r="Y27" s="427"/>
+      <c r="Z27" s="427"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -5290,13 +5290,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="424">
+      <c r="W28" s="426">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="425"/>
-      <c r="Y28" s="425"/>
-      <c r="Z28" s="425"/>
+      <c r="X28" s="427"/>
+      <c r="Y28" s="427"/>
+      <c r="Z28" s="427"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -5305,13 +5305,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="424">
+      <c r="W29" s="426">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="425"/>
-      <c r="Y29" s="425"/>
-      <c r="Z29" s="425"/>
+      <c r="X29" s="427"/>
+      <c r="Y29" s="427"/>
+      <c r="Z29" s="427"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -5320,13 +5320,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="423">
+      <c r="W30" s="439">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="420"/>
-      <c r="Y30" s="420"/>
-      <c r="Z30" s="420"/>
+      <c r="X30" s="421"/>
+      <c r="Y30" s="421"/>
+      <c r="Z30" s="421"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -5336,51 +5336,51 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="428">
+      <c r="W31" s="442">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="420"/>
-      <c r="Y31" s="420"/>
-      <c r="Z31" s="420"/>
+      <c r="X31" s="421"/>
+      <c r="Y31" s="421"/>
+      <c r="Z31" s="421"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="427">
+      <c r="K32" s="441">
         <v>43009</v>
       </c>
-      <c r="L32" s="425"/>
-      <c r="M32" s="425"/>
-      <c r="N32" s="425"/>
-      <c r="O32" s="425"/>
-      <c r="P32" s="425"/>
-      <c r="Q32" s="425"/>
-      <c r="R32" s="425"/>
-      <c r="S32" s="425"/>
-      <c r="T32" s="425"/>
-      <c r="U32" s="425"/>
-      <c r="V32" s="425"/>
-      <c r="W32" s="425"/>
-      <c r="X32" s="425"/>
-      <c r="Y32" s="425"/>
-      <c r="Z32" s="425"/>
+      <c r="L32" s="427"/>
+      <c r="M32" s="427"/>
+      <c r="N32" s="427"/>
+      <c r="O32" s="427"/>
+      <c r="P32" s="427"/>
+      <c r="Q32" s="427"/>
+      <c r="R32" s="427"/>
+      <c r="S32" s="427"/>
+      <c r="T32" s="427"/>
+      <c r="U32" s="427"/>
+      <c r="V32" s="427"/>
+      <c r="W32" s="427"/>
+      <c r="X32" s="427"/>
+      <c r="Y32" s="427"/>
+      <c r="Z32" s="427"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="439" t="s">
+      <c r="O33" s="420" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="420"/>
-      <c r="Q33" s="420"/>
-      <c r="R33" s="420"/>
-      <c r="S33" s="420"/>
-      <c r="T33" s="420"/>
-      <c r="U33" s="420"/>
-      <c r="V33" s="420"/>
-      <c r="W33" s="440" t="s">
+      <c r="P33" s="421"/>
+      <c r="Q33" s="421"/>
+      <c r="R33" s="421"/>
+      <c r="S33" s="421"/>
+      <c r="T33" s="421"/>
+      <c r="U33" s="421"/>
+      <c r="V33" s="421"/>
+      <c r="W33" s="425" t="s">
         <v>256</v>
       </c>
       <c r="X33" s="329"/>
@@ -5395,24 +5395,24 @@
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="431">
+      <c r="Q34" s="432">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="425"/>
-      <c r="S34" s="425"/>
-      <c r="T34" s="425"/>
+      <c r="R34" s="427"/>
+      <c r="S34" s="427"/>
+      <c r="T34" s="427"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="431">
+      <c r="Y34" s="432">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="425"/>
-      <c r="AA34" s="425"/>
-      <c r="AB34" s="425"/>
+      <c r="Z34" s="427"/>
+      <c r="AA34" s="427"/>
+      <c r="AB34" s="427"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -5475,32 +5475,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="421"/>
-      <c r="C38" s="418"/>
+      <c r="B38" s="429"/>
+      <c r="C38" s="424"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="421"/>
-      <c r="C39" s="418"/>
+      <c r="B39" s="429"/>
+      <c r="C39" s="424"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="421"/>
-      <c r="C40" s="418"/>
+      <c r="B40" s="429"/>
+      <c r="C40" s="424"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="421"/>
-      <c r="C41" s="418"/>
+      <c r="B41" s="429"/>
+      <c r="C41" s="424"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="421"/>
-      <c r="C42" s="418"/>
+      <c r="B42" s="429"/>
+      <c r="C42" s="424"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="421"/>
-      <c r="C43" s="418"/>
+      <c r="B43" s="429"/>
+      <c r="C43" s="424"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="421"/>
-      <c r="C44" s="418"/>
+      <c r="B44" s="429"/>
+      <c r="C44" s="424"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="437"/>
-      <c r="F49" s="418"/>
-      <c r="G49" s="418"/>
-      <c r="H49" s="418"/>
+      <c r="E49" s="433"/>
+      <c r="F49" s="424"/>
+      <c r="G49" s="424"/>
+      <c r="H49" s="424"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -5597,7 +5597,7 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="434"/>
+      <c r="H52" s="422"/>
       <c r="I52" s="329"/>
       <c r="J52" s="329"/>
       <c r="K52" s="329"/>
@@ -5610,7 +5610,7 @@
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="436"/>
+      <c r="H55" s="431"/>
       <c r="I55" s="329"/>
       <c r="J55" s="329"/>
       <c r="K55" s="329"/>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="434"/>
+      <c r="H57" s="422"/>
       <c r="I57" s="329"/>
       <c r="J57" s="329"/>
       <c r="K57" s="329"/>
@@ -5635,12 +5635,22 @@
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="W26:Z26"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="K32:Z32"/>
+    <mergeCell ref="W31:Z31"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="I10:P10"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H57:P57"/>
     <mergeCell ref="B42:C42"/>
@@ -5657,22 +5667,12 @@
     <mergeCell ref="W28:Z28"/>
     <mergeCell ref="W27:Z27"/>
     <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="W30:Z30"/>
-    <mergeCell ref="W26:Z26"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="K32:Z32"/>
-    <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
@@ -5708,24 +5708,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="447" t="s">
+      <c r="B1" s="461" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="449"/>
+      <c r="C1" s="462"/>
+      <c r="D1" s="462"/>
+      <c r="E1" s="462"/>
+      <c r="F1" s="462"/>
+      <c r="G1" s="462"/>
+      <c r="H1" s="463"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="443"/>
-      <c r="C2" s="444"/>
-      <c r="D2" s="444"/>
-      <c r="E2" s="444"/>
-      <c r="F2" s="444"/>
-      <c r="G2" s="444"/>
-      <c r="H2" s="445"/>
+      <c r="B2" s="458"/>
+      <c r="C2" s="459"/>
+      <c r="D2" s="459"/>
+      <c r="E2" s="459"/>
+      <c r="F2" s="459"/>
+      <c r="G2" s="459"/>
+      <c r="H2" s="460"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -5760,32 +5760,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="452" t="s">
+      <c r="B6" s="451" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="454" t="s">
+      <c r="C6" s="453" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="456" t="s">
+      <c r="D6" s="449" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="457" t="s">
+      <c r="E6" s="455" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="457" t="s">
+      <c r="F6" s="455" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="450" t="s">
+      <c r="G6" s="446" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="451"/>
+      <c r="H6" s="447"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="453"/>
-      <c r="C7" s="455"/>
-      <c r="D7" s="455"/>
-      <c r="E7" s="258"/>
-      <c r="F7" s="258"/>
+      <c r="B7" s="452"/>
+      <c r="C7" s="450"/>
+      <c r="D7" s="450"/>
+      <c r="E7" s="263"/>
+      <c r="F7" s="263"/>
       <c r="G7" s="47" t="s">
         <v>265</v>
       </c>
@@ -5806,14 +5806,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="458" t="s">
+      <c r="B9" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="247"/>
-      <c r="D9" s="247"/>
-      <c r="E9" s="247"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="248"/>
+      <c r="C9" s="250"/>
+      <c r="D9" s="250"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="250"/>
+      <c r="G9" s="251"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -5831,32 +5831,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="452" t="s">
+      <c r="B11" s="451" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="454" t="s">
+      <c r="C11" s="453" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="456" t="s">
+      <c r="D11" s="449" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="446" t="s">
+      <c r="E11" s="454" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="446" t="s">
+      <c r="F11" s="454" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="450" t="s">
+      <c r="G11" s="446" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="451"/>
+      <c r="H11" s="447"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="453"/>
-      <c r="C12" s="455"/>
-      <c r="D12" s="455"/>
-      <c r="E12" s="258"/>
-      <c r="F12" s="258"/>
+      <c r="B12" s="452"/>
+      <c r="C12" s="450"/>
+      <c r="D12" s="450"/>
+      <c r="E12" s="263"/>
+      <c r="F12" s="263"/>
       <c r="G12" s="47" t="s">
         <v>265</v>
       </c>
@@ -5877,14 +5877,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="458" t="s">
+      <c r="B14" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="247"/>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="247"/>
-      <c r="G14" s="248"/>
+      <c r="C14" s="250"/>
+      <c r="D14" s="250"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="251"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -5902,32 +5902,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="452" t="s">
+      <c r="B16" s="451" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="454" t="s">
+      <c r="C16" s="453" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="456" t="s">
+      <c r="D16" s="449" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="446" t="s">
+      <c r="E16" s="454" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="446" t="s">
+      <c r="F16" s="454" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="450" t="s">
+      <c r="G16" s="446" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="451"/>
+      <c r="H16" s="447"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="453"/>
-      <c r="C17" s="455"/>
-      <c r="D17" s="455"/>
-      <c r="E17" s="258"/>
-      <c r="F17" s="258"/>
+      <c r="B17" s="452"/>
+      <c r="C17" s="450"/>
+      <c r="D17" s="450"/>
+      <c r="E17" s="263"/>
+      <c r="F17" s="263"/>
       <c r="G17" s="22" t="s">
         <v>265</v>
       </c>
@@ -5950,14 +5950,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="458" t="s">
+      <c r="B19" s="448" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="247"/>
-      <c r="D19" s="247"/>
-      <c r="E19" s="247"/>
-      <c r="F19" s="247"/>
-      <c r="G19" s="248"/>
+      <c r="C19" s="250"/>
+      <c r="D19" s="250"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="250"/>
+      <c r="G19" s="251"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -5975,32 +5975,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="452" t="s">
+      <c r="B21" s="451" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="454" t="s">
+      <c r="C21" s="453" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="456" t="s">
+      <c r="D21" s="449" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="446" t="s">
+      <c r="E21" s="454" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="446" t="s">
+      <c r="F21" s="454" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="450" t="s">
+      <c r="G21" s="446" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="451"/>
+      <c r="H21" s="447"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="453"/>
-      <c r="C22" s="455"/>
-      <c r="D22" s="455"/>
-      <c r="E22" s="258"/>
-      <c r="F22" s="258"/>
+      <c r="B22" s="452"/>
+      <c r="C22" s="450"/>
+      <c r="D22" s="450"/>
+      <c r="E22" s="263"/>
+      <c r="F22" s="263"/>
       <c r="G22" s="47" t="s">
         <v>265</v>
       </c>
@@ -6021,32 +6021,18 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="441" t="s">
+      <c r="B24" s="456" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="442"/>
-      <c r="D24" s="442"/>
-      <c r="E24" s="442"/>
-      <c r="F24" s="442"/>
-      <c r="G24" s="391"/>
+      <c r="C24" s="457"/>
+      <c r="D24" s="457"/>
+      <c r="E24" s="457"/>
+      <c r="F24" s="457"/>
+      <c r="G24" s="393"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -6063,6 +6049,20 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -6088,14 +6088,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="461" t="s">
+      <c r="B1" s="466" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="444"/>
-      <c r="D1" s="444"/>
-      <c r="E1" s="444"/>
-      <c r="F1" s="444"/>
-      <c r="G1" s="444"/>
+      <c r="C1" s="459"/>
+      <c r="D1" s="459"/>
+      <c r="E1" s="459"/>
+      <c r="F1" s="459"/>
+      <c r="G1" s="459"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -6119,40 +6119,40 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="462" t="s">
+      <c r="B4" s="467" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="247"/>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="248"/>
+      <c r="C4" s="250"/>
+      <c r="D4" s="250"/>
+      <c r="E4" s="250"/>
+      <c r="F4" s="250"/>
+      <c r="G4" s="251"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="463" t="s">
+      <c r="B5" s="468" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="459" t="s">
+      <c r="C5" s="464" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="459" t="s">
+      <c r="D5" s="464" t="s">
         <v>275</v>
       </c>
-      <c r="E5" s="459" t="s">
+      <c r="E5" s="464" t="s">
         <v>276</v>
       </c>
-      <c r="F5" s="460" t="s">
+      <c r="F5" s="465" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="247"/>
+      <c r="G5" s="250"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="258"/>
-      <c r="C6" s="455"/>
-      <c r="D6" s="455"/>
-      <c r="E6" s="455"/>
+      <c r="B6" s="263"/>
+      <c r="C6" s="450"/>
+      <c r="D6" s="450"/>
+      <c r="E6" s="450"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -6204,151 +6204,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="471" t="s">
+      <c r="A1" s="474" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="252"/>
-      <c r="C1" s="252"/>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="252"/>
-      <c r="H1" s="252"/>
-      <c r="I1" s="252"/>
-      <c r="J1" s="252"/>
-      <c r="K1" s="252"/>
-      <c r="L1" s="252"/>
-      <c r="M1" s="252"/>
-      <c r="N1" s="252"/>
-      <c r="O1" s="464"/>
-      <c r="P1" s="252"/>
-      <c r="Q1" s="252"/>
-      <c r="R1" s="252"/>
-      <c r="S1" s="252"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
+      <c r="N1" s="248"/>
+      <c r="O1" s="475"/>
+      <c r="P1" s="248"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="248"/>
+      <c r="S1" s="248"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="469" t="s">
+      <c r="A2" s="476" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="252"/>
-      <c r="C2" s="469" t="s">
+      <c r="B2" s="248"/>
+      <c r="C2" s="476" t="s">
         <v>278</v>
       </c>
-      <c r="D2" s="252"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="252"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="252"/>
-      <c r="I2" s="252"/>
-      <c r="J2" s="470" t="s">
+      <c r="D2" s="248"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="472" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="466" t="s">
+      <c r="A3" s="473" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="252"/>
-      <c r="C3" s="466" t="s">
+      <c r="B3" s="248"/>
+      <c r="C3" s="473" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
-      <c r="G3" s="252"/>
-      <c r="H3" s="252"/>
-      <c r="I3" s="252"/>
-      <c r="J3" s="466" t="s">
+      <c r="D3" s="248"/>
+      <c r="E3" s="248"/>
+      <c r="F3" s="248"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="248"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="473" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
-      <c r="M3" s="252"/>
-      <c r="N3" s="252"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="M3" s="248"/>
+      <c r="N3" s="248"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="466" t="s">
+      <c r="A4" s="473" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="252"/>
-      <c r="C4" s="466" t="s">
+      <c r="B4" s="248"/>
+      <c r="C4" s="473" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="468"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="M4" s="252"/>
-      <c r="N4" s="252"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="471"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="M4" s="248"/>
+      <c r="N4" s="248"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="466" t="s">
+      <c r="A5" s="473" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="466" t="s">
+      <c r="B5" s="248"/>
+      <c r="C5" s="473" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="468"/>
-      <c r="K5" s="252"/>
-      <c r="L5" s="252"/>
-      <c r="M5" s="252"/>
-      <c r="N5" s="252"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="471"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="M5" s="248"/>
+      <c r="N5" s="248"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="466" t="s">
+      <c r="A6" s="473" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="252"/>
-      <c r="C6" s="466" t="s">
+      <c r="B6" s="248"/>
+      <c r="C6" s="473" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="466" t="s">
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
+      <c r="I6" s="248"/>
+      <c r="J6" s="473" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="252"/>
-      <c r="L6" s="252"/>
-      <c r="M6" s="252"/>
-      <c r="N6" s="252"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="248"/>
+      <c r="N6" s="248"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="465" t="s">
+      <c r="A7" s="470" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="252"/>
-      <c r="C7" s="252"/>
-      <c r="D7" s="252"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="252"/>
-      <c r="L7" s="252"/>
-      <c r="M7" s="252"/>
-      <c r="N7" s="252"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="248"/>
+      <c r="K7" s="248"/>
+      <c r="L7" s="248"/>
+      <c r="M7" s="248"/>
+      <c r="N7" s="248"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -6374,141 +6374,123 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="465" t="s">
+      <c r="A31" s="470" t="s">
         <v>288</v>
       </c>
-      <c r="B31" s="252"/>
-      <c r="C31" s="252"/>
-      <c r="D31" s="252"/>
-      <c r="E31" s="252"/>
-      <c r="F31" s="252"/>
-      <c r="G31" s="252"/>
-      <c r="H31" s="252"/>
-      <c r="I31" s="252"/>
-      <c r="J31" s="252"/>
-      <c r="K31" s="252"/>
-      <c r="L31" s="252"/>
-      <c r="M31" s="252"/>
-      <c r="N31" s="252"/>
+      <c r="B31" s="248"/>
+      <c r="C31" s="248"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
+      <c r="M31" s="248"/>
+      <c r="N31" s="248"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="467" t="s">
+      <c r="A32" s="469" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="252"/>
-      <c r="C32" s="252"/>
-      <c r="D32" s="467" t="s">
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="469" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="252"/>
-      <c r="F32" s="252"/>
-      <c r="G32" s="467" t="s">
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
+      <c r="G32" s="469" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="252"/>
-      <c r="I32" s="252"/>
-      <c r="J32" s="467" t="s">
+      <c r="H32" s="248"/>
+      <c r="I32" s="248"/>
+      <c r="J32" s="469" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="252"/>
-      <c r="L32" s="252"/>
-      <c r="M32" s="252"/>
+      <c r="K32" s="248"/>
+      <c r="L32" s="248"/>
+      <c r="M32" s="248"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="467" t="s">
+      <c r="A33" s="469" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="252"/>
-      <c r="C33" s="252"/>
-      <c r="D33" s="467" t="s">
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="469" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="252"/>
-      <c r="F33" s="252"/>
-      <c r="G33" s="467" t="s">
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="469" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="252"/>
-      <c r="I33" s="252"/>
-      <c r="J33" s="467" t="s">
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="469" t="s">
         <v>293</v>
       </c>
-      <c r="K33" s="252"/>
-      <c r="L33" s="252"/>
-      <c r="M33" s="252"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
+      <c r="M33" s="248"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="465" t="s">
+      <c r="A34" s="470" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="252"/>
-      <c r="C34" s="252"/>
-      <c r="D34" s="252"/>
-      <c r="E34" s="252"/>
-      <c r="F34" s="252"/>
-      <c r="G34" s="252"/>
-      <c r="H34" s="252"/>
-      <c r="I34" s="252"/>
-      <c r="J34" s="252"/>
-      <c r="K34" s="252"/>
-      <c r="L34" s="252"/>
-      <c r="M34" s="252"/>
-      <c r="N34" s="252"/>
+      <c r="B34" s="248"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="248"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="248"/>
+      <c r="N34" s="248"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="467" t="s">
+      <c r="A35" s="469" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="252"/>
-      <c r="C35" s="252"/>
-      <c r="F35" s="467" t="s">
+      <c r="B35" s="248"/>
+      <c r="C35" s="248"/>
+      <c r="F35" s="469" t="s">
         <v>294</v>
       </c>
-      <c r="G35" s="252"/>
-      <c r="H35" s="252"/>
-      <c r="K35" s="467" t="s">
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
+      <c r="K35" s="469" t="s">
         <v>295</v>
       </c>
-      <c r="L35" s="252"/>
-      <c r="M35" s="252"/>
+      <c r="L35" s="248"/>
+      <c r="M35" s="248"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="467" t="s">
+      <c r="A36" s="469" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="252"/>
-      <c r="C36" s="252"/>
-      <c r="F36" s="467" t="s">
+      <c r="B36" s="248"/>
+      <c r="C36" s="248"/>
+      <c r="F36" s="469" t="s">
         <v>296</v>
       </c>
-      <c r="G36" s="252"/>
-      <c r="H36" s="252"/>
-      <c r="K36" s="467" t="s">
+      <c r="G36" s="248"/>
+      <c r="H36" s="248"/>
+      <c r="K36" s="469" t="s">
         <v>297</v>
       </c>
-      <c r="L36" s="252"/>
-      <c r="M36" s="252"/>
+      <c r="L36" s="248"/>
+      <c r="M36" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -6525,6 +6507,24 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6622,13 +6622,13 @@
       <c r="E21" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="284" t="s">
+      <c r="H21" s="285" t="s">
         <v>305</v>
       </c>
-      <c r="I21" s="284"/>
-      <c r="J21" s="284"/>
-      <c r="K21" s="284"/>
-      <c r="L21" s="284"/>
+      <c r="I21" s="285"/>
+      <c r="J21" s="285"/>
+      <c r="K21" s="285"/>
+      <c r="L21" s="285"/>
     </row>
     <row r="22" spans="4:12" ht="15" customHeight="1">
       <c r="D22" s="153" t="s">
@@ -6637,15 +6637,15 @@
       <c r="E22" s="123">
         <v>1.2</v>
       </c>
-      <c r="H22" s="285" t="s">
+      <c r="H22" s="286" t="s">
         <v>306</v>
       </c>
-      <c r="I22" s="285" t="s">
+      <c r="I22" s="286" t="s">
         <v>307</v>
       </c>
-      <c r="J22" s="285"/>
-      <c r="K22" s="285"/>
-      <c r="L22" s="285"/>
+      <c r="J22" s="286"/>
+      <c r="K22" s="286"/>
+      <c r="L22" s="286"/>
     </row>
     <row r="23" spans="4:12" ht="15" customHeight="1">
       <c r="D23" s="153" t="s">
@@ -6654,7 +6654,7 @@
       <c r="E23" s="123">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H23" s="285"/>
+      <c r="H23" s="286"/>
       <c r="I23" s="242" t="s">
         <v>308</v>
       </c>
@@ -6778,7 +6778,7 @@
       </c>
     </row>
     <row r="32" spans="4:12" ht="15" customHeight="1">
-      <c r="D32" s="282" t="s">
+      <c r="D32" s="283" t="s">
         <v>40</v>
       </c>
       <c r="E32" s="193" t="s">
@@ -6788,7 +6788,7 @@
       <c r="G32" s="193"/>
     </row>
     <row r="33" spans="4:7" ht="30" customHeight="1">
-      <c r="D33" s="283"/>
+      <c r="D33" s="284"/>
       <c r="E33" s="194" t="s">
         <v>42</v>
       </c>
@@ -6915,166 +6915,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1">
-      <c r="A1" s="472" t="s">
+      <c r="A1" s="246" t="s">
         <v>316</v>
       </c>
-      <c r="B1" s="472" t="s">
+      <c r="B1" s="246" t="s">
         <v>317</v>
       </c>
-      <c r="C1" s="472" t="s">
+      <c r="C1" s="246" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
-      <c r="A2" s="473" t="s">
+      <c r="A2" s="287" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="474" t="s">
+      <c r="B2" s="288" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="475">
+      <c r="C2" s="289">
         <v>1.3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A3" s="473"/>
-      <c r="B3" s="474"/>
-      <c r="C3" s="475"/>
+      <c r="A3" s="287"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="289"/>
     </row>
     <row r="4" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A4" s="473" t="s">
+      <c r="A4" s="287" t="s">
         <v>320</v>
       </c>
-      <c r="B4" s="474" t="s">
+      <c r="B4" s="288" t="s">
         <v>321</v>
       </c>
-      <c r="C4" s="475">
+      <c r="C4" s="289">
         <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A5" s="473"/>
-      <c r="B5" s="474"/>
-      <c r="C5" s="475"/>
+      <c r="A5" s="287"/>
+      <c r="B5" s="288"/>
+      <c r="C5" s="289"/>
     </row>
     <row r="6" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A6" s="473" t="s">
+      <c r="A6" s="287" t="s">
         <v>322</v>
       </c>
-      <c r="B6" s="474" t="s">
+      <c r="B6" s="288" t="s">
         <v>323</v>
       </c>
-      <c r="C6" s="475">
+      <c r="C6" s="289">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A7" s="473"/>
-      <c r="B7" s="474"/>
-      <c r="C7" s="475"/>
+      <c r="A7" s="287"/>
+      <c r="B7" s="288"/>
+      <c r="C7" s="289"/>
     </row>
     <row r="8" spans="1:3" ht="44.25" customHeight="1">
-      <c r="A8" s="473" t="s">
+      <c r="A8" s="287" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="474" t="s">
+      <c r="B8" s="288" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="475">
+      <c r="C8" s="289">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A9" s="473"/>
-      <c r="B9" s="474"/>
-      <c r="C9" s="475"/>
+      <c r="A9" s="287"/>
+      <c r="B9" s="288"/>
+      <c r="C9" s="289"/>
     </row>
     <row r="10" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A10" s="473" t="s">
+      <c r="A10" s="287" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="474" t="s">
+      <c r="B10" s="288" t="s">
         <v>325</v>
       </c>
-      <c r="C10" s="475">
+      <c r="C10" s="289">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A11" s="473"/>
-      <c r="B11" s="474"/>
-      <c r="C11" s="475"/>
+      <c r="A11" s="287"/>
+      <c r="B11" s="288"/>
+      <c r="C11" s="289"/>
     </row>
     <row r="12" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A12" s="473" t="s">
+      <c r="A12" s="287" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="288" t="s">
         <v>326</v>
       </c>
-      <c r="C12" s="475">
+      <c r="C12" s="289">
         <v>0.8</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A13" s="473"/>
-      <c r="B13" s="474"/>
-      <c r="C13" s="475"/>
+      <c r="A13" s="287"/>
+      <c r="B13" s="288"/>
+      <c r="C13" s="289"/>
     </row>
     <row r="14" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A14" s="473" t="s">
+      <c r="A14" s="287" t="s">
         <v>327</v>
       </c>
-      <c r="B14" s="474" t="s">
+      <c r="B14" s="288" t="s">
         <v>328</v>
       </c>
-      <c r="C14" s="475">
+      <c r="C14" s="289">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A15" s="473"/>
-      <c r="B15" s="474"/>
-      <c r="C15" s="475"/>
+      <c r="A15" s="287"/>
+      <c r="B15" s="288"/>
+      <c r="C15" s="289"/>
     </row>
     <row r="16" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A16" s="473" t="s">
+      <c r="A16" s="287" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="474" t="s">
+      <c r="B16" s="288" t="s">
         <v>329</v>
       </c>
-      <c r="C16" s="475">
+      <c r="C16" s="289">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="473"/>
-      <c r="B17" s="474"/>
-      <c r="C17" s="475"/>
+      <c r="A17" s="287"/>
+      <c r="B17" s="288"/>
+      <c r="C17" s="289"/>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="E18" s="284" t="s">
+      <c r="E18" s="285" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="284"/>
-      <c r="G18" s="284"/>
-      <c r="H18" s="284"/>
-      <c r="I18" s="284"/>
+      <c r="F18" s="285"/>
+      <c r="G18" s="285"/>
+      <c r="H18" s="285"/>
+      <c r="I18" s="285"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="E19" s="285" t="s">
+      <c r="E19" s="286" t="s">
         <v>306</v>
       </c>
-      <c r="F19" s="285" t="s">
+      <c r="F19" s="286" t="s">
         <v>307</v>
       </c>
-      <c r="G19" s="285"/>
-      <c r="H19" s="285"/>
-      <c r="I19" s="285"/>
+      <c r="G19" s="286"/>
+      <c r="H19" s="286"/>
+      <c r="I19" s="286"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="E20" s="285"/>
+      <c r="E20" s="286"/>
       <c r="F20" s="245" t="s">
         <v>308</v>
       </c>
@@ -7175,6 +7175,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:I19"/>
@@ -7184,24 +7202,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7250,17 +7250,17 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="286" t="str">
+      <c r="C4" s="316" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="283"/>
-      <c r="E4" s="283"/>
-      <c r="F4" s="283"/>
-      <c r="G4" s="283"/>
-      <c r="H4" s="283"/>
-      <c r="I4" s="283"/>
-      <c r="J4" s="283"/>
+      <c r="D4" s="284"/>
+      <c r="E4" s="284"/>
+      <c r="F4" s="284"/>
+      <c r="G4" s="284"/>
+      <c r="H4" s="284"/>
+      <c r="I4" s="284"/>
+      <c r="J4" s="284"/>
       <c r="L4" s="207"/>
       <c r="M4" s="207"/>
       <c r="N4" s="207"/>
@@ -7279,22 +7279,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="302" t="s">
+      <c r="C5" s="314" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="302" t="s">
+      <c r="D5" s="263"/>
+      <c r="E5" s="314" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="258"/>
-      <c r="G5" s="302" t="s">
+      <c r="F5" s="263"/>
+      <c r="G5" s="314" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="258"/>
-      <c r="I5" s="297" t="s">
+      <c r="H5" s="263"/>
+      <c r="I5" s="307" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="258"/>
+      <c r="J5" s="263"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -7308,23 +7308,23 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="289">
+      <c r="C6" s="293">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="292" t="s">
+      <c r="D6" s="251"/>
+      <c r="E6" s="313" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="248"/>
-      <c r="G6" s="290" t="s">
+      <c r="F6" s="251"/>
+      <c r="G6" s="315" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="248"/>
-      <c r="I6" s="304" t="s">
+      <c r="H6" s="251"/>
+      <c r="I6" s="291" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="248"/>
+      <c r="J6" s="251"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -7344,16 +7344,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="287" t="s">
+      <c r="C7" s="312" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="247"/>
-      <c r="E7" s="247"/>
-      <c r="F7" s="247"/>
-      <c r="G7" s="247"/>
-      <c r="H7" s="247"/>
-      <c r="I7" s="247"/>
-      <c r="J7" s="248"/>
+      <c r="D7" s="250"/>
+      <c r="E7" s="250"/>
+      <c r="F7" s="250"/>
+      <c r="G7" s="250"/>
+      <c r="H7" s="250"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="251"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -7370,22 +7370,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="291" t="s">
+      <c r="C8" s="292" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="291" t="s">
+      <c r="D8" s="251"/>
+      <c r="E8" s="292" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="248"/>
-      <c r="G8" s="291" t="s">
+      <c r="F8" s="251"/>
+      <c r="G8" s="292" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="248"/>
-      <c r="I8" s="301" t="s">
+      <c r="H8" s="251"/>
+      <c r="I8" s="311" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="248"/>
+      <c r="J8" s="251"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -7397,22 +7397,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="292">
+      <c r="C9" s="313">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="290" t="s">
+      <c r="D9" s="251"/>
+      <c r="E9" s="315" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="248"/>
-      <c r="G9" s="289">
+      <c r="F9" s="251"/>
+      <c r="G9" s="293">
         <v>80</v>
       </c>
-      <c r="H9" s="248"/>
-      <c r="I9" s="304">
+      <c r="H9" s="251"/>
+      <c r="I9" s="291">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="248"/>
+      <c r="J9" s="251"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -7424,16 +7424,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="287" t="s">
+      <c r="C10" s="312" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="248"/>
+      <c r="D10" s="250"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="250"/>
+      <c r="J10" s="251"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -7445,171 +7445,172 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="291" t="s">
+      <c r="C11" s="292" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="291" t="s">
+      <c r="D11" s="251"/>
+      <c r="E11" s="292" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="248"/>
-      <c r="G11" s="291" t="s">
+      <c r="F11" s="251"/>
+      <c r="G11" s="292" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="248"/>
-      <c r="I11" s="301" t="s">
+      <c r="H11" s="251"/>
+      <c r="I11" s="311" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="248"/>
+      <c r="J11" s="251"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="292">
+      <c r="C12" s="313">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="292">
+      <c r="D12" s="251"/>
+      <c r="E12" s="313">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="248"/>
-      <c r="G12" s="290">
+      <c r="F12" s="251"/>
+      <c r="G12" s="315">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="248"/>
-      <c r="I12" s="293">
+      <c r="H12" s="251"/>
+      <c r="I12" s="318">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="248"/>
+      <c r="J12" s="251"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="291" t="s">
+      <c r="C13" s="292" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="290" t="s">
+      <c r="D13" s="251"/>
+      <c r="E13" s="315" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="248"/>
-      <c r="G13" s="291" t="s">
+      <c r="F13" s="251"/>
+      <c r="G13" s="292" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="248"/>
-      <c r="I13" s="304" t="s">
+      <c r="H13" s="251"/>
+      <c r="I13" s="291" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="248"/>
+      <c r="J13" s="251"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="298" t="s">
+      <c r="C16" s="308" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="299"/>
-      <c r="E16" s="299"/>
-      <c r="F16" s="299"/>
-      <c r="G16" s="299"/>
-      <c r="H16" s="299"/>
-      <c r="I16" s="300"/>
+      <c r="D16" s="309"/>
+      <c r="E16" s="309"/>
+      <c r="F16" s="309"/>
+      <c r="G16" s="309"/>
+      <c r="H16" s="309"/>
+      <c r="I16" s="310"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="287" t="s">
+      <c r="C17" s="312" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="247"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="287" t="s">
+      <c r="D17" s="250"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="312" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="287" t="s">
+      <c r="G17" s="251"/>
+      <c r="H17" s="312" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="248"/>
+      <c r="I17" s="251"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="310" t="s">
+      <c r="C18" s="299" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="311"/>
-      <c r="E18" s="312"/>
-      <c r="F18" s="314">
+      <c r="D18" s="300"/>
+      <c r="E18" s="301"/>
+      <c r="F18" s="303">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="315"/>
-      <c r="H18" s="316">
+      <c r="G18" s="304"/>
+      <c r="H18" s="305">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="317"/>
+      <c r="I18" s="306"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="313" t="s">
+      <c r="C19" s="302" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="247"/>
-      <c r="E19" s="248"/>
-      <c r="F19" s="289">
+      <c r="D19" s="250"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="293">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="248"/>
-      <c r="H19" s="303">
+      <c r="G19" s="251"/>
+      <c r="H19" s="290">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="248"/>
+      <c r="I19" s="251"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="294" t="s">
+      <c r="C20" s="319" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="295"/>
-      <c r="E20" s="296"/>
-      <c r="F20" s="308">
+      <c r="D20" s="320"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="297">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="309"/>
-      <c r="H20" s="306">
+      <c r="G20" s="298"/>
+      <c r="H20" s="295">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="307"/>
+      <c r="I20" s="296"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="305" t="s">
+      <c r="C21" s="294" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="247"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="288">
+      <c r="D21" s="250"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="317">
         <f>SUM(F18:G20)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G21" s="248"/>
-      <c r="H21" s="303">
+      <c r="G21" s="251"/>
+      <c r="H21" s="290">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="248"/>
+      <c r="I21" s="251"/>
       <c r="J21" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="I8:J8"/>
@@ -7626,22 +7627,21 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7669,20 +7669,20 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="349" t="s">
+      <c r="B3" s="381" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="350"/>
-      <c r="E3" s="350"/>
-      <c r="F3" s="350"/>
-      <c r="G3" s="350"/>
-      <c r="H3" s="350"/>
-      <c r="I3" s="350"/>
-      <c r="L3" s="381" t="s">
+      <c r="C3" s="382"/>
+      <c r="D3" s="382"/>
+      <c r="E3" s="382"/>
+      <c r="F3" s="382"/>
+      <c r="G3" s="382"/>
+      <c r="H3" s="382"/>
+      <c r="I3" s="382"/>
+      <c r="L3" s="322" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="248"/>
+      <c r="M3" s="251"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
       <c r="B4" s="328" t="s">
@@ -7690,17 +7690,17 @@
       </c>
       <c r="C4" s="329"/>
       <c r="D4" s="329"/>
-      <c r="E4" s="383" t="s">
+      <c r="E4" s="340" t="s">
         <v>298</v>
       </c>
-      <c r="F4" s="283"/>
+      <c r="F4" s="284"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="351" t="s">
+      <c r="H4" s="383" t="s">
         <v>299</v>
       </c>
-      <c r="I4" s="262"/>
+      <c r="I4" s="253"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>88</v>
@@ -7711,22 +7711,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="326" t="s">
+      <c r="B5" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="283"/>
-      <c r="D5" s="283"/>
-      <c r="E5" s="343" t="s">
+      <c r="C5" s="284"/>
+      <c r="D5" s="284"/>
+      <c r="E5" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="283"/>
+      <c r="F5" s="284"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="476" t="s">
+      <c r="H5" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="262"/>
+      <c r="I5" s="253"/>
       <c r="L5" s="153" t="s">
         <v>92</v>
       </c>
@@ -7736,57 +7736,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="326" t="s">
+      <c r="B6" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="283"/>
-      <c r="D6" s="283"/>
-      <c r="E6" s="370">
+      <c r="C6" s="284"/>
+      <c r="D6" s="284"/>
+      <c r="E6" s="366">
         <v>52.034300000000002</v>
       </c>
-      <c r="F6" s="283"/>
+      <c r="F6" s="284"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="356" t="s">
+      <c r="H6" s="385" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="262"/>
+      <c r="I6" s="253"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="342" t="s">
+      <c r="C7" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="283"/>
-      <c r="E7" s="359" t="s">
+      <c r="D7" s="284"/>
+      <c r="E7" s="372" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="283"/>
+      <c r="F7" s="284"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="325">
+      <c r="H7" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I7" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I7" s="253"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="342" t="s">
+      <c r="C8" s="325" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="283"/>
-      <c r="E8" s="369">
+      <c r="D8" s="284"/>
+      <c r="E8" s="363">
         <v>11173</v>
       </c>
-      <c r="F8" s="283"/>
+      <c r="F8" s="284"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="344"/>
-      <c r="I8" s="262"/>
+      <c r="H8" s="355"/>
+      <c r="I8" s="253"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -7794,16 +7794,16 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="332" t="s">
+      <c r="B9" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="283"/>
-      <c r="D9" s="283"/>
-      <c r="E9" s="283"/>
-      <c r="F9" s="283"/>
-      <c r="G9" s="283"/>
-      <c r="H9" s="283"/>
-      <c r="I9" s="262"/>
+      <c r="C9" s="284"/>
+      <c r="D9" s="284"/>
+      <c r="E9" s="284"/>
+      <c r="F9" s="284"/>
+      <c r="G9" s="284"/>
+      <c r="H9" s="284"/>
+      <c r="I9" s="253"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -7811,21 +7811,21 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="341" t="s">
+      <c r="B10" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="283"/>
-      <c r="D10" s="283"/>
+      <c r="C10" s="284"/>
+      <c r="D10" s="284"/>
       <c r="E10" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F10" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="333" t="s">
+      <c r="G10" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="283"/>
+      <c r="H10" s="284"/>
       <c r="I10" s="167"/>
       <c r="J10" s="226"/>
       <c r="K10" s="226"/>
@@ -7834,11 +7834,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="378" t="s">
+      <c r="B11" s="351" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="379"/>
-      <c r="D11" s="379"/>
+      <c r="C11" s="352"/>
+      <c r="D11" s="352"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -7846,10 +7846,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="380">
+      <c r="G11" s="353">
         <v>1</v>
       </c>
-      <c r="H11" s="380"/>
+      <c r="H11" s="353"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -7858,11 +7858,11 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="368" t="s">
+      <c r="B12" s="362" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="283"/>
-      <c r="D12" s="283"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="284"/>
       <c r="E12" s="220">
         <f>32.0811-E11</f>
         <v>24.851099999999999</v>
@@ -7871,10 +7871,10 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="322">
+      <c r="G12" s="327">
         <v>0.8</v>
       </c>
-      <c r="H12" s="283"/>
+      <c r="H12" s="284"/>
       <c r="I12" s="167"/>
       <c r="J12" s="226"/>
       <c r="K12" s="226"/>
@@ -7883,11 +7883,11 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="360" t="s">
+      <c r="B13" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="283"/>
-      <c r="D13" s="283"/>
+      <c r="C13" s="284"/>
+      <c r="D13" s="284"/>
       <c r="E13" s="202">
         <f>18.2121+1.7411</f>
         <v>19.953199999999999</v>
@@ -7896,10 +7896,10 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="322">
+      <c r="G13" s="327">
         <v>0.6</v>
       </c>
-      <c r="H13" s="283"/>
+      <c r="H13" s="284"/>
       <c r="I13" s="167"/>
       <c r="J13" s="226"/>
       <c r="K13" s="229">
@@ -7912,11 +7912,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="327" t="s">
+      <c r="B14" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="250"/>
-      <c r="D14" s="250"/>
+      <c r="C14" s="259"/>
+      <c r="D14" s="259"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -7925,11 +7925,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="318">
+      <c r="G14" s="350">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="250"/>
+      <c r="H14" s="259"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -7953,16 +7953,16 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="336" t="s">
+      <c r="B16" s="348" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="283"/>
-      <c r="D16" s="283"/>
-      <c r="E16" s="283"/>
-      <c r="F16" s="283"/>
-      <c r="G16" s="283"/>
-      <c r="H16" s="283"/>
-      <c r="I16" s="283"/>
+      <c r="C16" s="284"/>
+      <c r="D16" s="284"/>
+      <c r="E16" s="284"/>
+      <c r="F16" s="284"/>
+      <c r="G16" s="284"/>
+      <c r="H16" s="284"/>
+      <c r="I16" s="284"/>
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
@@ -7971,78 +7971,78 @@
       </c>
       <c r="C17" s="329"/>
       <c r="D17" s="329"/>
-      <c r="E17" s="320" t="s">
+      <c r="E17" s="326" t="s">
         <v>110</v>
       </c>
-      <c r="F17" s="283"/>
+      <c r="F17" s="284"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="352" t="s">
+      <c r="H17" s="338" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="262"/>
+      <c r="I17" s="253"/>
       <c r="K17" s="203" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="326" t="s">
+      <c r="B18" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="283"/>
-      <c r="D18" s="283"/>
-      <c r="E18" s="343" t="s">
+      <c r="C18" s="284"/>
+      <c r="D18" s="284"/>
+      <c r="E18" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="283"/>
+      <c r="F18" s="284"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="355" t="s">
+      <c r="H18" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="262"/>
+      <c r="I18" s="253"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="326" t="s">
+      <c r="B19" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="283"/>
-      <c r="D19" s="283"/>
-      <c r="E19" s="364">
+      <c r="C19" s="284"/>
+      <c r="D19" s="284"/>
+      <c r="E19" s="365">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
-      <c r="F19" s="283"/>
+      <c r="F19" s="284"/>
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="323" t="s">
+      <c r="H19" s="357" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="262"/>
+      <c r="I19" s="253"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="342" t="s">
+      <c r="C20" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="283"/>
-      <c r="E20" s="348">
+      <c r="D20" s="284"/>
+      <c r="E20" s="371">
         <f>180000000</f>
         <v>180000000</v>
       </c>
-      <c r="F20" s="283"/>
+      <c r="F20" s="284"/>
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="324">
+      <c r="H20" s="360">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="262"/>
+      <c r="I20" s="253"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -8050,76 +8050,76 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="342" t="s">
+      <c r="C21" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="283"/>
-      <c r="E21" s="366" t="s">
+      <c r="D21" s="284"/>
+      <c r="E21" s="332" t="s">
         <v>116</v>
       </c>
-      <c r="F21" s="283"/>
+      <c r="F21" s="284"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="325">
+      <c r="H21" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I21" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I21" s="253"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="342" t="s">
+      <c r="C22" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="283"/>
-      <c r="E22" s="320" t="s">
+      <c r="D22" s="284"/>
+      <c r="E22" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="283"/>
+      <c r="F22" s="284"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="361"/>
-      <c r="I22" s="262"/>
+      <c r="H22" s="368"/>
+      <c r="I22" s="253"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="332" t="s">
+      <c r="B23" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="283"/>
-      <c r="D23" s="283"/>
-      <c r="E23" s="283"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="283"/>
-      <c r="H23" s="283"/>
-      <c r="I23" s="262"/>
+      <c r="C23" s="284"/>
+      <c r="D23" s="284"/>
+      <c r="E23" s="284"/>
+      <c r="F23" s="284"/>
+      <c r="G23" s="284"/>
+      <c r="H23" s="284"/>
+      <c r="I23" s="253"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="341" t="s">
+      <c r="B24" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="283"/>
-      <c r="D24" s="283"/>
+      <c r="C24" s="284"/>
+      <c r="D24" s="284"/>
       <c r="E24" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F24" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="333" t="s">
+      <c r="G24" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="283"/>
+      <c r="H24" s="284"/>
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="330" t="s">
+      <c r="B25" s="335" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="283"/>
-      <c r="D25" s="283"/>
+      <c r="C25" s="284"/>
+      <c r="D25" s="284"/>
       <c r="E25" s="214">
         <f>600 *4.84</f>
         <v>2904</v>
@@ -8128,10 +8128,10 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="331">
+      <c r="G25" s="341">
         <v>1</v>
       </c>
-      <c r="H25" s="283"/>
+      <c r="H25" s="284"/>
       <c r="I25" s="213"/>
     </row>
     <row r="26" spans="2:11" ht="15" customHeight="1">
@@ -8148,18 +8148,18 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="331">
+      <c r="G26" s="341">
         <v>0.8</v>
       </c>
-      <c r="H26" s="283"/>
+      <c r="H26" s="284"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="357" t="s">
+      <c r="B27" s="374" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="283"/>
-      <c r="D27" s="283"/>
+      <c r="C27" s="284"/>
+      <c r="D27" s="284"/>
       <c r="E27" s="214">
         <f>E19*0.35</f>
         <v>5929</v>
@@ -8168,18 +8168,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="331">
+      <c r="G27" s="341">
         <v>0.6</v>
       </c>
-      <c r="H27" s="283"/>
+      <c r="H27" s="284"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="327" t="s">
+      <c r="B28" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="250"/>
-      <c r="D28" s="250"/>
+      <c r="C28" s="259"/>
+      <c r="D28" s="259"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -8188,11 +8188,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="318">
+      <c r="G28" s="350">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="250"/>
+      <c r="H28" s="259"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -8206,16 +8206,16 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="336" t="s">
+      <c r="B30" s="348" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="283"/>
-      <c r="D30" s="283"/>
-      <c r="E30" s="283"/>
-      <c r="F30" s="283"/>
-      <c r="G30" s="283"/>
-      <c r="H30" s="283"/>
-      <c r="I30" s="283"/>
+      <c r="C30" s="284"/>
+      <c r="D30" s="284"/>
+      <c r="E30" s="284"/>
+      <c r="F30" s="284"/>
+      <c r="G30" s="284"/>
+      <c r="H30" s="284"/>
+      <c r="I30" s="284"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
       <c r="B31" s="328" t="s">
@@ -8223,78 +8223,78 @@
       </c>
       <c r="C31" s="329"/>
       <c r="D31" s="329"/>
-      <c r="E31" s="320" t="s">
+      <c r="E31" s="326" t="s">
         <v>119</v>
       </c>
-      <c r="F31" s="283"/>
+      <c r="F31" s="284"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="352" t="s">
+      <c r="H31" s="338" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="262"/>
+      <c r="I31" s="253"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="326" t="s">
+      <c r="B32" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="283"/>
-      <c r="D32" s="283"/>
-      <c r="E32" s="343" t="s">
+      <c r="C32" s="284"/>
+      <c r="D32" s="284"/>
+      <c r="E32" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="283"/>
+      <c r="F32" s="284"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="355" t="s">
+      <c r="H32" s="336" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="262"/>
+      <c r="I32" s="253"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="326" t="s">
+      <c r="B33" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="283"/>
-      <c r="D33" s="283"/>
-      <c r="E33" s="353">
+      <c r="C33" s="284"/>
+      <c r="D33" s="284"/>
+      <c r="E33" s="377">
         <v>1258.4000000000001</v>
       </c>
-      <c r="F33" s="283"/>
+      <c r="F33" s="284"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="355" t="s">
+      <c r="H33" s="336" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="262"/>
+      <c r="I33" s="253"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="342" t="s">
+      <c r="C34" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="283"/>
-      <c r="E34" s="348">
+      <c r="D34" s="284"/>
+      <c r="E34" s="371">
         <v>16900000</v>
       </c>
-      <c r="F34" s="283"/>
+      <c r="F34" s="284"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="324">
+      <c r="H34" s="360">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="262"/>
+      <c r="I34" s="253"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -8302,76 +8302,76 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="342" t="s">
+      <c r="C35" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="283"/>
-      <c r="E35" s="366" t="s">
+      <c r="D35" s="284"/>
+      <c r="E35" s="332" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="283"/>
+      <c r="F35" s="284"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="325">
+      <c r="H35" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I35" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I35" s="253"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="342" t="s">
+      <c r="C36" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="283"/>
-      <c r="E36" s="320" t="s">
+      <c r="D36" s="284"/>
+      <c r="E36" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="283"/>
+      <c r="F36" s="284"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="361"/>
-      <c r="I36" s="262"/>
+      <c r="H36" s="368"/>
+      <c r="I36" s="253"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="332" t="s">
+      <c r="B37" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="283"/>
-      <c r="D37" s="283"/>
-      <c r="E37" s="283"/>
-      <c r="F37" s="283"/>
-      <c r="G37" s="283"/>
-      <c r="H37" s="283"/>
-      <c r="I37" s="262"/>
+      <c r="C37" s="284"/>
+      <c r="D37" s="284"/>
+      <c r="E37" s="284"/>
+      <c r="F37" s="284"/>
+      <c r="G37" s="284"/>
+      <c r="H37" s="284"/>
+      <c r="I37" s="253"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="341" t="s">
+      <c r="B38" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="283"/>
-      <c r="D38" s="283"/>
+      <c r="C38" s="284"/>
+      <c r="D38" s="284"/>
       <c r="E38" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F38" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G38" s="333" t="s">
+      <c r="G38" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H38" s="283"/>
+      <c r="H38" s="284"/>
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="330" t="s">
+      <c r="B39" s="335" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="283"/>
-      <c r="D39" s="283"/>
+      <c r="C39" s="284"/>
+      <c r="D39" s="284"/>
       <c r="E39" s="214">
         <v>145.19999999999999</v>
       </c>
@@ -8379,10 +8379,10 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="331">
+      <c r="G39" s="341">
         <v>1</v>
       </c>
-      <c r="H39" s="283"/>
+      <c r="H39" s="284"/>
       <c r="I39" s="213"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1">
@@ -8399,18 +8399,18 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="331">
+      <c r="G40" s="341">
         <v>0.8</v>
       </c>
-      <c r="H40" s="283"/>
+      <c r="H40" s="284"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="357" t="s">
+      <c r="B41" s="374" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="283"/>
-      <c r="D41" s="283"/>
+      <c r="C41" s="284"/>
+      <c r="D41" s="284"/>
       <c r="E41" s="214">
         <f>E33*0.3512</f>
         <v>441.95008000000007</v>
@@ -8419,18 +8419,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="331">
+      <c r="G41" s="341">
         <v>0.6</v>
       </c>
-      <c r="H41" s="283"/>
+      <c r="H41" s="284"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="327" t="s">
+      <c r="B42" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="250"/>
-      <c r="D42" s="250"/>
+      <c r="C42" s="259"/>
+      <c r="D42" s="259"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -8439,11 +8439,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="318">
+      <c r="G42" s="350">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="250"/>
+      <c r="H42" s="259"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -8457,16 +8457,16 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="354" t="s">
+      <c r="B44" s="384" t="s">
         <v>122</v>
       </c>
-      <c r="C44" s="283"/>
-      <c r="D44" s="283"/>
-      <c r="E44" s="283"/>
-      <c r="F44" s="283"/>
-      <c r="G44" s="283"/>
-      <c r="H44" s="283"/>
-      <c r="I44" s="283"/>
+      <c r="C44" s="284"/>
+      <c r="D44" s="284"/>
+      <c r="E44" s="284"/>
+      <c r="F44" s="284"/>
+      <c r="G44" s="284"/>
+      <c r="H44" s="284"/>
+      <c r="I44" s="284"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
       <c r="B45" s="328" t="s">
@@ -8474,76 +8474,76 @@
       </c>
       <c r="C45" s="329"/>
       <c r="D45" s="329"/>
-      <c r="E45" s="343" t="s">
+      <c r="E45" s="323" t="s">
         <v>119</v>
       </c>
-      <c r="F45" s="283"/>
+      <c r="F45" s="284"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="352" t="s">
+      <c r="H45" s="338" t="s">
         <v>120</v>
       </c>
-      <c r="I45" s="262"/>
+      <c r="I45" s="253"/>
       <c r="K45" s="203" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="326" t="s">
+      <c r="B46" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="283"/>
-      <c r="D46" s="283"/>
-      <c r="E46" s="343" t="s">
+      <c r="C46" s="284"/>
+      <c r="D46" s="284"/>
+      <c r="E46" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="284"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="355" t="s">
+      <c r="H46" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="262"/>
+      <c r="I46" s="253"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="326" t="s">
+      <c r="B47" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="283"/>
-      <c r="D47" s="283"/>
-      <c r="E47" s="364">
+      <c r="C47" s="284"/>
+      <c r="D47" s="284"/>
+      <c r="E47" s="365">
         <v>430.76</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="284"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="323" t="s">
+      <c r="H47" s="357" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="262"/>
+      <c r="I47" s="253"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="342" t="s">
+      <c r="C48" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D48" s="283"/>
-      <c r="E48" s="319">
+      <c r="D48" s="284"/>
+      <c r="E48" s="347">
         <v>7120000</v>
       </c>
-      <c r="F48" s="283"/>
+      <c r="F48" s="284"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="339">
+      <c r="H48" s="361">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="262"/>
+      <c r="I48" s="253"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -8552,76 +8552,76 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="342" t="s">
+      <c r="C49" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="283"/>
-      <c r="E49" s="366" t="s">
+      <c r="D49" s="284"/>
+      <c r="E49" s="332" t="s">
         <v>116</v>
       </c>
-      <c r="F49" s="283"/>
+      <c r="F49" s="284"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="325">
+      <c r="H49" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I49" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I49" s="253"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="342" t="s">
+      <c r="C50" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="283"/>
-      <c r="E50" s="320" t="s">
+      <c r="D50" s="284"/>
+      <c r="E50" s="326" t="s">
         <v>124</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="284"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="344"/>
-      <c r="I50" s="262"/>
+      <c r="H50" s="355"/>
+      <c r="I50" s="253"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="332" t="s">
+      <c r="B51" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="283"/>
-      <c r="D51" s="283"/>
-      <c r="E51" s="283"/>
-      <c r="F51" s="283"/>
-      <c r="G51" s="283"/>
-      <c r="H51" s="283"/>
-      <c r="I51" s="262"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="284"/>
+      <c r="E51" s="284"/>
+      <c r="F51" s="284"/>
+      <c r="G51" s="284"/>
+      <c r="H51" s="284"/>
+      <c r="I51" s="253"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="341" t="s">
+      <c r="B52" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="283"/>
-      <c r="D52" s="283"/>
+      <c r="C52" s="284"/>
+      <c r="D52" s="284"/>
       <c r="E52" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F52" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G52" s="333" t="s">
+      <c r="G52" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H52" s="283"/>
+      <c r="H52" s="284"/>
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="330" t="s">
+      <c r="B53" s="335" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="283"/>
-      <c r="D53" s="283"/>
+      <c r="C53" s="284"/>
+      <c r="D53" s="284"/>
       <c r="E53" s="168">
         <v>145.19999999999999</v>
       </c>
@@ -8629,10 +8629,10 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="322">
+      <c r="G53" s="327">
         <v>1</v>
       </c>
-      <c r="H53" s="283"/>
+      <c r="H53" s="284"/>
       <c r="I53" s="167"/>
     </row>
     <row r="54" spans="2:11" ht="15" customHeight="1">
@@ -8649,10 +8649,10 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="322">
+      <c r="G54" s="327">
         <v>0.8</v>
       </c>
-      <c r="H54" s="283"/>
+      <c r="H54" s="284"/>
       <c r="I54" s="167"/>
     </row>
     <row r="55" spans="2:11" ht="15" customHeight="1">
@@ -8669,18 +8669,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="322">
+      <c r="G55" s="327">
         <v>0.6</v>
       </c>
-      <c r="H55" s="283"/>
+      <c r="H55" s="284"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="327" t="s">
+      <c r="B56" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="250"/>
-      <c r="D56" s="250"/>
+      <c r="C56" s="259"/>
+      <c r="D56" s="259"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -8689,11 +8689,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="318">
+      <c r="G56" s="350">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="250"/>
+      <c r="H56" s="259"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -8707,16 +8707,16 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="336" t="s">
+      <c r="B58" s="348" t="s">
         <v>125</v>
       </c>
-      <c r="C58" s="283"/>
-      <c r="D58" s="283"/>
-      <c r="E58" s="283"/>
-      <c r="F58" s="283"/>
-      <c r="G58" s="283"/>
-      <c r="H58" s="283"/>
-      <c r="I58" s="283"/>
+      <c r="C58" s="284"/>
+      <c r="D58" s="284"/>
+      <c r="E58" s="284"/>
+      <c r="F58" s="284"/>
+      <c r="G58" s="284"/>
+      <c r="H58" s="284"/>
+      <c r="I58" s="284"/>
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
@@ -8725,75 +8725,75 @@
       </c>
       <c r="C59" s="329"/>
       <c r="D59" s="329"/>
-      <c r="E59" s="343" t="s">
+      <c r="E59" s="323" t="s">
         <v>126</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="284"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="365" t="s">
+      <c r="H59" s="367" t="s">
         <v>127</v>
       </c>
-      <c r="I59" s="262"/>
+      <c r="I59" s="253"/>
       <c r="K59" s="203" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="326" t="s">
+      <c r="B60" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="283"/>
-      <c r="D60" s="283"/>
-      <c r="E60" s="343" t="s">
+      <c r="C60" s="284"/>
+      <c r="D60" s="284"/>
+      <c r="E60" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F60" s="283"/>
+      <c r="F60" s="284"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="355" t="s">
+      <c r="H60" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="262"/>
+      <c r="I60" s="253"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="326" t="s">
+      <c r="B61" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="283"/>
-      <c r="D61" s="283"/>
-      <c r="E61" s="334">
+      <c r="C61" s="284"/>
+      <c r="D61" s="284"/>
+      <c r="E61" s="369">
         <v>626</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="284"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="355" t="s">
+      <c r="H61" s="336" t="s">
         <v>129</v>
       </c>
-      <c r="I61" s="262"/>
+      <c r="I61" s="253"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="342" t="s">
+      <c r="C62" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="283"/>
-      <c r="E62" s="358">
+      <c r="D62" s="284"/>
+      <c r="E62" s="378">
         <v>10500000</v>
       </c>
-      <c r="F62" s="283"/>
+      <c r="F62" s="284"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="335">
+      <c r="H62" s="330">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="262"/>
+      <c r="I62" s="253"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -8802,68 +8802,68 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="342" t="s">
+      <c r="C63" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="283"/>
-      <c r="E63" s="362" t="s">
+      <c r="D63" s="284"/>
+      <c r="E63" s="375" t="s">
         <v>116</v>
       </c>
-      <c r="F63" s="283"/>
+      <c r="F63" s="284"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="325">
+      <c r="H63" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I63" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I63" s="253"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="342" t="s">
+      <c r="C64" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D64" s="283"/>
-      <c r="E64" s="320" t="s">
+      <c r="D64" s="284"/>
+      <c r="E64" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="F64" s="283"/>
+      <c r="F64" s="284"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="344"/>
-      <c r="I64" s="262"/>
+      <c r="H64" s="355"/>
+      <c r="I64" s="253"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="332" t="s">
+      <c r="B65" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C65" s="283"/>
-      <c r="D65" s="283"/>
-      <c r="E65" s="283"/>
-      <c r="F65" s="283"/>
-      <c r="G65" s="283"/>
-      <c r="H65" s="283"/>
-      <c r="I65" s="262"/>
+      <c r="C65" s="284"/>
+      <c r="D65" s="284"/>
+      <c r="E65" s="284"/>
+      <c r="F65" s="284"/>
+      <c r="G65" s="284"/>
+      <c r="H65" s="284"/>
+      <c r="I65" s="253"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="341" t="s">
+      <c r="B66" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="283"/>
-      <c r="D66" s="283"/>
+      <c r="C66" s="284"/>
+      <c r="D66" s="284"/>
       <c r="E66" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F66" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="333" t="s">
+      <c r="G66" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H66" s="283"/>
+      <c r="H66" s="284"/>
       <c r="I66" s="167"/>
     </row>
     <row r="67" spans="2:11" ht="15" customHeight="1">
@@ -8879,10 +8879,10 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="322">
+      <c r="G67" s="327">
         <v>1</v>
       </c>
-      <c r="H67" s="283"/>
+      <c r="H67" s="284"/>
       <c r="I67" s="167"/>
     </row>
     <row r="68" spans="2:11" ht="15" customHeight="1">
@@ -8898,18 +8898,18 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="322">
+      <c r="G68" s="327">
         <v>0.9</v>
       </c>
-      <c r="H68" s="283"/>
+      <c r="H68" s="284"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="363" t="s">
+      <c r="B69" s="376" t="s">
         <v>107</v>
       </c>
-      <c r="C69" s="283"/>
-      <c r="D69" s="283"/>
+      <c r="C69" s="284"/>
+      <c r="D69" s="284"/>
       <c r="E69" s="168">
         <f>E61-E67-E68</f>
         <v>263</v>
@@ -8918,18 +8918,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="322">
+      <c r="G69" s="327">
         <v>0.6</v>
       </c>
-      <c r="H69" s="283"/>
+      <c r="H69" s="284"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="327" t="s">
+      <c r="B70" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="250"/>
-      <c r="D70" s="250"/>
+      <c r="C70" s="259"/>
+      <c r="D70" s="259"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -8938,11 +8938,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="318">
+      <c r="G70" s="350">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="250"/>
+      <c r="H70" s="259"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -8956,16 +8956,16 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="336" t="s">
+      <c r="B72" s="348" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="283"/>
-      <c r="D72" s="283"/>
-      <c r="E72" s="283"/>
-      <c r="F72" s="283"/>
-      <c r="G72" s="283"/>
-      <c r="H72" s="283"/>
-      <c r="I72" s="283"/>
+      <c r="C72" s="284"/>
+      <c r="D72" s="284"/>
+      <c r="E72" s="284"/>
+      <c r="F72" s="284"/>
+      <c r="G72" s="284"/>
+      <c r="H72" s="284"/>
+      <c r="I72" s="284"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
       <c r="B73" s="328" t="s">
@@ -8973,95 +8973,95 @@
       </c>
       <c r="C73" s="329"/>
       <c r="D73" s="329"/>
-      <c r="E73" s="320" t="s">
+      <c r="E73" s="326" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="283"/>
+      <c r="F73" s="284"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="352" t="s">
+      <c r="H73" s="338" t="s">
         <v>133</v>
       </c>
-      <c r="I73" s="262"/>
+      <c r="I73" s="253"/>
       <c r="K73" s="203" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="326" t="s">
+      <c r="B74" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="283"/>
-      <c r="D74" s="283"/>
-      <c r="E74" s="320" t="s">
+      <c r="C74" s="284"/>
+      <c r="D74" s="284"/>
+      <c r="E74" s="326" t="s">
         <v>135</v>
       </c>
-      <c r="F74" s="283"/>
+      <c r="F74" s="284"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="355" t="s">
+      <c r="H74" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="262"/>
+      <c r="I74" s="253"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="326" t="s">
+      <c r="B75" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C75" s="283"/>
-      <c r="D75" s="283"/>
-      <c r="E75" s="337">
+      <c r="C75" s="284"/>
+      <c r="D75" s="284"/>
+      <c r="E75" s="388">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
-      <c r="F75" s="283"/>
+      <c r="F75" s="284"/>
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="323" t="s">
+      <c r="H75" s="357" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="262"/>
+      <c r="I75" s="253"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="342" t="s">
+      <c r="C76" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D76" s="283"/>
-      <c r="E76" s="319">
+      <c r="D76" s="284"/>
+      <c r="E76" s="347">
         <v>60000000</v>
       </c>
-      <c r="F76" s="283"/>
+      <c r="F76" s="284"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="339">
+      <c r="H76" s="361">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="262"/>
+      <c r="I76" s="253"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="342" t="s">
+      <c r="C77" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D77" s="283"/>
-      <c r="E77" s="374" t="s">
+      <c r="D77" s="284"/>
+      <c r="E77" s="359" t="s">
         <v>116</v>
       </c>
-      <c r="F77" s="283"/>
+      <c r="F77" s="284"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="325">
+      <c r="H77" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I77" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I77" s="253"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -9069,57 +9069,57 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="342" t="s">
+      <c r="C78" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D78" s="283"/>
-      <c r="E78" s="320" t="s">
+      <c r="D78" s="284"/>
+      <c r="E78" s="326" t="s">
         <v>136</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="284"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H78" s="344"/>
-      <c r="I78" s="262"/>
+      <c r="H78" s="355"/>
+      <c r="I78" s="253"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="332" t="s">
+      <c r="B79" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C79" s="283"/>
-      <c r="D79" s="283"/>
-      <c r="E79" s="283"/>
-      <c r="F79" s="283"/>
-      <c r="G79" s="283"/>
-      <c r="H79" s="283"/>
-      <c r="I79" s="262"/>
+      <c r="C79" s="284"/>
+      <c r="D79" s="284"/>
+      <c r="E79" s="284"/>
+      <c r="F79" s="284"/>
+      <c r="G79" s="284"/>
+      <c r="H79" s="284"/>
+      <c r="I79" s="253"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="341" t="s">
+      <c r="B80" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C80" s="283"/>
-      <c r="D80" s="283"/>
+      <c r="C80" s="284"/>
+      <c r="D80" s="284"/>
       <c r="E80" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F80" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G80" s="333" t="s">
+      <c r="G80" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H80" s="283"/>
+      <c r="H80" s="284"/>
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="334" t="s">
         <v>130</v>
       </c>
-      <c r="C81" s="283"/>
-      <c r="D81" s="283"/>
+      <c r="C81" s="284"/>
+      <c r="D81" s="284"/>
       <c r="E81" s="168">
         <f>410*4.84</f>
         <v>1984.3999999999999</v>
@@ -9128,18 +9128,18 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="322">
+      <c r="G81" s="327">
         <v>0.9</v>
       </c>
-      <c r="H81" s="283"/>
+      <c r="H81" s="284"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="340" t="s">
+      <c r="B82" s="334" t="s">
         <v>117</v>
       </c>
-      <c r="C82" s="283"/>
-      <c r="D82" s="283"/>
+      <c r="C82" s="284"/>
+      <c r="D82" s="284"/>
       <c r="E82" s="168">
         <f>E75-(E81+E83)</f>
         <v>306.52687999999989</v>
@@ -9148,10 +9148,10 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="322">
+      <c r="G82" s="327">
         <v>0.8</v>
       </c>
-      <c r="H82" s="283"/>
+      <c r="H82" s="284"/>
       <c r="I82" s="167"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1">
@@ -9168,18 +9168,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="322">
+      <c r="G83" s="327">
         <v>0.6</v>
       </c>
-      <c r="H83" s="283"/>
+      <c r="H83" s="284"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="327" t="s">
+      <c r="B84" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="250"/>
-      <c r="D84" s="250"/>
+      <c r="C84" s="259"/>
+      <c r="D84" s="259"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -9188,11 +9188,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="318">
+      <c r="G84" s="350">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="250"/>
+      <c r="H84" s="259"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -9206,16 +9206,16 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="336" t="s">
+      <c r="B86" s="348" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="283"/>
-      <c r="D86" s="283"/>
-      <c r="E86" s="283"/>
-      <c r="F86" s="283"/>
-      <c r="G86" s="283"/>
-      <c r="H86" s="283"/>
-      <c r="I86" s="283"/>
+      <c r="C86" s="284"/>
+      <c r="D86" s="284"/>
+      <c r="E86" s="284"/>
+      <c r="F86" s="284"/>
+      <c r="G86" s="284"/>
+      <c r="H86" s="284"/>
+      <c r="I86" s="284"/>
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
@@ -9224,77 +9224,77 @@
       </c>
       <c r="C87" s="329"/>
       <c r="D87" s="329"/>
-      <c r="E87" s="343" t="s">
+      <c r="E87" s="323" t="s">
         <v>119</v>
       </c>
-      <c r="F87" s="283"/>
+      <c r="F87" s="284"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="367" t="str">
+      <c r="H87" s="370" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="262"/>
+      <c r="I87" s="253"/>
       <c r="K87" s="203" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="326" t="s">
+      <c r="B88" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="283"/>
-      <c r="D88" s="283"/>
-      <c r="E88" s="343" t="s">
+      <c r="C88" s="284"/>
+      <c r="D88" s="284"/>
+      <c r="E88" s="323" t="s">
         <v>90</v>
       </c>
-      <c r="F88" s="283"/>
+      <c r="F88" s="284"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="355" t="s">
+      <c r="H88" s="336" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="262"/>
+      <c r="I88" s="253"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="326" t="s">
+      <c r="B89" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="283"/>
-      <c r="D89" s="283"/>
-      <c r="E89" s="353">
+      <c r="C89" s="284"/>
+      <c r="D89" s="284"/>
+      <c r="E89" s="377">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
-      <c r="F89" s="283"/>
+      <c r="F89" s="284"/>
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="323" t="s">
+      <c r="H89" s="357" t="s">
         <v>95</v>
       </c>
-      <c r="I89" s="262"/>
+      <c r="I89" s="253"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="342" t="s">
+      <c r="C90" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D90" s="283"/>
-      <c r="E90" s="345">
+      <c r="D90" s="284"/>
+      <c r="E90" s="358">
         <v>43980000</v>
       </c>
-      <c r="F90" s="283"/>
+      <c r="F90" s="284"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="335">
+      <c r="H90" s="330">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="262"/>
+      <c r="I90" s="253"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -9302,75 +9302,75 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="342" t="s">
+      <c r="C91" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D91" s="283"/>
-      <c r="E91" s="372" t="s">
+      <c r="D91" s="284"/>
+      <c r="E91" s="333" t="s">
         <v>116</v>
       </c>
-      <c r="F91" s="283"/>
+      <c r="F91" s="284"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="325">
+      <c r="H91" s="344">
         <f ca="1">TODAY()</f>
-        <v>45841</v>
-      </c>
-      <c r="I91" s="262"/>
+        <v>45842</v>
+      </c>
+      <c r="I91" s="253"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="342" t="s">
+      <c r="C92" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D92" s="283"/>
-      <c r="E92" s="320" t="s">
+      <c r="D92" s="284"/>
+      <c r="E92" s="326" t="s">
         <v>97</v>
       </c>
-      <c r="F92" s="283"/>
+      <c r="F92" s="284"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="344"/>
-      <c r="I92" s="262"/>
+      <c r="H92" s="355"/>
+      <c r="I92" s="253"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="332" t="s">
+      <c r="B93" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C93" s="283"/>
-      <c r="D93" s="283"/>
-      <c r="E93" s="283"/>
-      <c r="F93" s="283"/>
-      <c r="G93" s="283"/>
-      <c r="H93" s="283"/>
-      <c r="I93" s="262"/>
+      <c r="C93" s="284"/>
+      <c r="D93" s="284"/>
+      <c r="E93" s="284"/>
+      <c r="F93" s="284"/>
+      <c r="G93" s="284"/>
+      <c r="H93" s="284"/>
+      <c r="I93" s="253"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="341" t="s">
+      <c r="B94" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C94" s="283"/>
-      <c r="D94" s="283"/>
+      <c r="C94" s="284"/>
+      <c r="D94" s="284"/>
       <c r="E94" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F94" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G94" s="333" t="s">
+      <c r="G94" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H94" s="283"/>
+      <c r="H94" s="284"/>
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="330" t="s">
+      <c r="B95" s="335" t="s">
         <v>106</v>
       </c>
-      <c r="C95" s="283"/>
-      <c r="D95" s="283"/>
+      <c r="C95" s="284"/>
+      <c r="D95" s="284"/>
       <c r="E95" s="234">
         <v>1100</v>
       </c>
@@ -9378,10 +9378,10 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="376">
+      <c r="G95" s="345">
         <v>1</v>
       </c>
-      <c r="H95" s="283"/>
+      <c r="H95" s="284"/>
       <c r="I95" s="206"/>
     </row>
     <row r="96" spans="2:11" ht="15" customHeight="1">
@@ -9398,18 +9398,18 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="376">
+      <c r="G96" s="345">
         <v>0.8</v>
       </c>
-      <c r="H96" s="283"/>
+      <c r="H96" s="284"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="373" t="s">
+      <c r="B97" s="346" t="s">
         <v>107</v>
       </c>
-      <c r="C97" s="283"/>
-      <c r="D97" s="283"/>
+      <c r="C97" s="284"/>
+      <c r="D97" s="284"/>
       <c r="E97" s="168">
         <f>E89*0.3514</f>
         <v>1246.6688079999999</v>
@@ -9418,20 +9418,20 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="322">
+      <c r="G97" s="327">
         <v>0.6</v>
       </c>
-      <c r="H97" s="283"/>
+      <c r="H97" s="284"/>
       <c r="I97" s="167"/>
       <c r="K97" s="207"/>
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="327" t="s">
+      <c r="B98" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C98" s="250"/>
-      <c r="D98" s="250"/>
+      <c r="C98" s="259"/>
+      <c r="D98" s="259"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -9440,11 +9440,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="318">
+      <c r="G98" s="350">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="250"/>
+      <c r="H98" s="259"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -9465,28 +9465,28 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="338"/>
-      <c r="C100" s="283"/>
-      <c r="D100" s="283"/>
-      <c r="E100" s="283"/>
-      <c r="F100" s="283"/>
-      <c r="G100" s="283"/>
-      <c r="H100" s="283"/>
-      <c r="I100" s="283"/>
+      <c r="B100" s="386"/>
+      <c r="C100" s="284"/>
+      <c r="D100" s="284"/>
+      <c r="E100" s="284"/>
+      <c r="F100" s="284"/>
+      <c r="G100" s="284"/>
+      <c r="H100" s="284"/>
+      <c r="I100" s="284"/>
       <c r="K100" s="207"/>
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="336" t="s">
+      <c r="B101" s="348" t="s">
         <v>139</v>
       </c>
-      <c r="C101" s="283"/>
-      <c r="D101" s="283"/>
-      <c r="E101" s="283"/>
-      <c r="F101" s="283"/>
-      <c r="G101" s="283"/>
-      <c r="H101" s="283"/>
-      <c r="I101" s="283"/>
+      <c r="C101" s="284"/>
+      <c r="D101" s="284"/>
+      <c r="E101" s="284"/>
+      <c r="F101" s="284"/>
+      <c r="G101" s="284"/>
+      <c r="H101" s="284"/>
+      <c r="I101" s="284"/>
       <c r="K101" s="207"/>
       <c r="L101" s="207"/>
     </row>
@@ -9496,146 +9496,146 @@
       </c>
       <c r="C102" s="329"/>
       <c r="D102" s="329"/>
-      <c r="E102" s="382"/>
-      <c r="F102" s="283"/>
+      <c r="E102" s="339"/>
+      <c r="F102" s="284"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="321"/>
-      <c r="I102" s="262"/>
+      <c r="H102" s="387"/>
+      <c r="I102" s="253"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="326" t="s">
+      <c r="B103" s="331" t="s">
         <v>89</v>
       </c>
-      <c r="C103" s="283"/>
-      <c r="D103" s="283"/>
-      <c r="E103" s="377"/>
-      <c r="F103" s="283"/>
+      <c r="C103" s="284"/>
+      <c r="D103" s="284"/>
+      <c r="E103" s="349"/>
+      <c r="F103" s="284"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="371"/>
-      <c r="I103" s="262"/>
+      <c r="H103" s="356"/>
+      <c r="I103" s="253"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="326" t="s">
+      <c r="B104" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="C104" s="283"/>
-      <c r="D104" s="283"/>
-      <c r="E104" s="334"/>
-      <c r="F104" s="283"/>
+      <c r="C104" s="284"/>
+      <c r="D104" s="284"/>
+      <c r="E104" s="369"/>
+      <c r="F104" s="284"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="347"/>
-      <c r="I104" s="262"/>
+      <c r="H104" s="380"/>
+      <c r="I104" s="253"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="342" t="s">
+      <c r="C105" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="D105" s="283"/>
-      <c r="E105" s="345"/>
-      <c r="F105" s="283"/>
+      <c r="D105" s="284"/>
+      <c r="E105" s="358"/>
+      <c r="F105" s="284"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="335"/>
-      <c r="I105" s="262"/>
+      <c r="H105" s="330"/>
+      <c r="I105" s="253"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="342" t="s">
+      <c r="C106" s="325" t="s">
         <v>115</v>
       </c>
-      <c r="D106" s="283"/>
-      <c r="E106" s="372"/>
-      <c r="F106" s="283"/>
+      <c r="D106" s="284"/>
+      <c r="E106" s="333"/>
+      <c r="F106" s="284"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="375"/>
-      <c r="I106" s="262"/>
+      <c r="H106" s="343"/>
+      <c r="I106" s="253"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="342" t="s">
+      <c r="C107" s="325" t="s">
         <v>96</v>
       </c>
-      <c r="D107" s="283"/>
-      <c r="E107" s="346"/>
-      <c r="F107" s="283"/>
+      <c r="D107" s="284"/>
+      <c r="E107" s="379"/>
+      <c r="F107" s="284"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="344"/>
-      <c r="I107" s="262"/>
+      <c r="H107" s="355"/>
+      <c r="I107" s="253"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="332" t="s">
+      <c r="B108" s="342" t="s">
         <v>101</v>
       </c>
-      <c r="C108" s="283"/>
-      <c r="D108" s="283"/>
-      <c r="E108" s="283"/>
-      <c r="F108" s="283"/>
-      <c r="G108" s="283"/>
-      <c r="H108" s="283"/>
-      <c r="I108" s="262"/>
+      <c r="C108" s="284"/>
+      <c r="D108" s="284"/>
+      <c r="E108" s="284"/>
+      <c r="F108" s="284"/>
+      <c r="G108" s="284"/>
+      <c r="H108" s="284"/>
+      <c r="I108" s="253"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="341" t="s">
+      <c r="B109" s="324" t="s">
         <v>102</v>
       </c>
-      <c r="C109" s="283"/>
-      <c r="D109" s="283"/>
+      <c r="C109" s="284"/>
+      <c r="D109" s="284"/>
       <c r="E109" s="166" t="s">
         <v>103</v>
       </c>
       <c r="F109" s="166" t="s">
         <v>104</v>
       </c>
-      <c r="G109" s="333" t="s">
+      <c r="G109" s="337" t="s">
         <v>105</v>
       </c>
-      <c r="H109" s="283"/>
+      <c r="H109" s="284"/>
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="373" t="s">
+      <c r="B110" s="346" t="s">
         <v>106</v>
       </c>
-      <c r="C110" s="283"/>
-      <c r="D110" s="283"/>
+      <c r="C110" s="284"/>
+      <c r="D110" s="284"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="322"/>
-      <c r="H110" s="283"/>
+      <c r="G110" s="327"/>
+      <c r="H110" s="284"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="373" t="s">
+      <c r="B111" s="346" t="s">
         <v>107</v>
       </c>
-      <c r="C111" s="283"/>
-      <c r="D111" s="283"/>
+      <c r="C111" s="284"/>
+      <c r="D111" s="284"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="322"/>
-      <c r="H111" s="283"/>
+      <c r="G111" s="327"/>
+      <c r="H111" s="284"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="327" t="s">
+      <c r="B112" s="354" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="250"/>
-      <c r="D112" s="250"/>
+      <c r="C112" s="259"/>
+      <c r="D112" s="259"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -9644,15 +9644,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="318">
+      <c r="G112" s="350">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="250"/>
+      <c r="H112" s="259"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="E88:F88"/>
     <mergeCell ref="B38:D38"/>
@@ -9677,211 +9882,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B108:I108"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="G84:H84"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10233,16 +10233,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="385"/>
-      <c r="F1" s="386"/>
-      <c r="G1" s="386"/>
-      <c r="H1" s="386"/>
-      <c r="I1" s="386"/>
-      <c r="J1" s="386"/>
-      <c r="K1" s="386"/>
-      <c r="L1" s="386"/>
-      <c r="M1" s="386"/>
-      <c r="N1" s="386"/>
+      <c r="E1" s="396"/>
+      <c r="F1" s="391"/>
+      <c r="G1" s="391"/>
+      <c r="H1" s="391"/>
+      <c r="I1" s="391"/>
+      <c r="J1" s="391"/>
+      <c r="K1" s="391"/>
+      <c r="L1" s="391"/>
+      <c r="M1" s="391"/>
+      <c r="N1" s="391"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -10790,21 +10790,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="384" t="s">
+      <c r="A12" s="389" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="248"/>
-      <c r="C12" s="387" t="s">
+      <c r="B12" s="251"/>
+      <c r="C12" s="397" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="386"/>
-      <c r="E12" s="386"/>
-      <c r="F12" s="386"/>
-      <c r="G12" s="386"/>
-      <c r="H12" s="386"/>
-      <c r="I12" s="386"/>
-      <c r="J12" s="386"/>
-      <c r="K12" s="386"/>
+      <c r="D12" s="391"/>
+      <c r="E12" s="391"/>
+      <c r="F12" s="391"/>
+      <c r="G12" s="391"/>
+      <c r="H12" s="391"/>
+      <c r="I12" s="391"/>
+      <c r="J12" s="391"/>
+      <c r="K12" s="391"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -10819,21 +10819,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="384" t="s">
+      <c r="A13" s="389" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="248"/>
-      <c r="C13" s="387" t="s">
+      <c r="B13" s="251"/>
+      <c r="C13" s="397" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="386"/>
-      <c r="E13" s="386"/>
-      <c r="F13" s="386"/>
-      <c r="G13" s="386"/>
-      <c r="H13" s="386"/>
-      <c r="I13" s="386"/>
-      <c r="J13" s="386"/>
-      <c r="K13" s="386"/>
+      <c r="D13" s="391"/>
+      <c r="E13" s="391"/>
+      <c r="F13" s="391"/>
+      <c r="G13" s="391"/>
+      <c r="H13" s="391"/>
+      <c r="I13" s="391"/>
+      <c r="J13" s="391"/>
+      <c r="K13" s="391"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -10848,22 +10848,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="384" t="str">
+      <c r="A14" s="389" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="248"/>
-      <c r="C14" s="387" t="s">
+      <c r="B14" s="251"/>
+      <c r="C14" s="397" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="386"/>
-      <c r="E14" s="386"/>
-      <c r="F14" s="386"/>
-      <c r="G14" s="386"/>
-      <c r="H14" s="386"/>
-      <c r="I14" s="386"/>
-      <c r="J14" s="386"/>
-      <c r="K14" s="386"/>
+      <c r="D14" s="391"/>
+      <c r="E14" s="391"/>
+      <c r="F14" s="391"/>
+      <c r="G14" s="391"/>
+      <c r="H14" s="391"/>
+      <c r="I14" s="391"/>
+      <c r="J14" s="391"/>
+      <c r="K14" s="391"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -10878,21 +10878,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="384" t="s">
+      <c r="A15" s="389" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="248"/>
-      <c r="C15" s="387" t="s">
+      <c r="B15" s="251"/>
+      <c r="C15" s="397" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="386"/>
-      <c r="E15" s="386"/>
-      <c r="F15" s="386"/>
-      <c r="G15" s="386"/>
-      <c r="H15" s="386"/>
-      <c r="I15" s="386"/>
-      <c r="J15" s="386"/>
-      <c r="K15" s="386"/>
+      <c r="D15" s="391"/>
+      <c r="E15" s="391"/>
+      <c r="F15" s="391"/>
+      <c r="G15" s="391"/>
+      <c r="H15" s="391"/>
+      <c r="I15" s="391"/>
+      <c r="J15" s="391"/>
+      <c r="K15" s="391"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -10907,21 +10907,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="384" t="s">
+      <c r="A16" s="389" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="248"/>
-      <c r="C16" s="389" t="s">
+      <c r="B16" s="251"/>
+      <c r="C16" s="390" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="386"/>
-      <c r="E16" s="386"/>
-      <c r="F16" s="386"/>
-      <c r="G16" s="386"/>
-      <c r="H16" s="386"/>
-      <c r="I16" s="386"/>
-      <c r="J16" s="386"/>
-      <c r="K16" s="386"/>
+      <c r="D16" s="391"/>
+      <c r="E16" s="391"/>
+      <c r="F16" s="391"/>
+      <c r="G16" s="391"/>
+      <c r="H16" s="391"/>
+      <c r="I16" s="391"/>
+      <c r="J16" s="391"/>
+      <c r="K16" s="391"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -10931,21 +10931,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="384" t="s">
+      <c r="A17" s="389" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="248"/>
-      <c r="C17" s="389" t="s">
+      <c r="B17" s="251"/>
+      <c r="C17" s="390" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="386"/>
-      <c r="E17" s="386"/>
-      <c r="F17" s="386"/>
-      <c r="G17" s="386"/>
-      <c r="H17" s="386"/>
-      <c r="I17" s="386"/>
-      <c r="J17" s="386"/>
-      <c r="K17" s="386"/>
+      <c r="D17" s="391"/>
+      <c r="E17" s="391"/>
+      <c r="F17" s="391"/>
+      <c r="G17" s="391"/>
+      <c r="H17" s="391"/>
+      <c r="I17" s="391"/>
+      <c r="J17" s="391"/>
+      <c r="K17" s="391"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>185</v>
@@ -10964,21 +10964,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="384" t="s">
+      <c r="A18" s="389" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="248"/>
-      <c r="C18" s="389" t="s">
+      <c r="B18" s="251"/>
+      <c r="C18" s="390" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="386"/>
-      <c r="E18" s="386"/>
-      <c r="F18" s="386"/>
-      <c r="G18" s="386"/>
-      <c r="H18" s="386"/>
-      <c r="I18" s="386"/>
-      <c r="J18" s="386"/>
-      <c r="K18" s="386"/>
+      <c r="D18" s="391"/>
+      <c r="E18" s="391"/>
+      <c r="F18" s="391"/>
+      <c r="G18" s="391"/>
+      <c r="H18" s="391"/>
+      <c r="I18" s="391"/>
+      <c r="J18" s="391"/>
+      <c r="K18" s="391"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>188</v>
@@ -10992,21 +10992,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="384" t="s">
+      <c r="A19" s="389" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="248"/>
-      <c r="C19" s="389" t="s">
+      <c r="B19" s="251"/>
+      <c r="C19" s="390" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="386"/>
-      <c r="E19" s="386"/>
-      <c r="F19" s="386"/>
-      <c r="G19" s="386"/>
-      <c r="H19" s="386"/>
-      <c r="I19" s="386"/>
-      <c r="J19" s="386"/>
-      <c r="K19" s="386"/>
+      <c r="D19" s="391"/>
+      <c r="E19" s="391"/>
+      <c r="F19" s="391"/>
+      <c r="G19" s="391"/>
+      <c r="H19" s="391"/>
+      <c r="I19" s="391"/>
+      <c r="J19" s="391"/>
+      <c r="K19" s="391"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -11021,21 +11021,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="384" t="s">
+      <c r="A20" s="389" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="248"/>
-      <c r="C20" s="389" t="s">
+      <c r="B20" s="251"/>
+      <c r="C20" s="390" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="386"/>
-      <c r="E20" s="386"/>
-      <c r="F20" s="386"/>
-      <c r="G20" s="386"/>
-      <c r="H20" s="386"/>
-      <c r="I20" s="386"/>
-      <c r="J20" s="386"/>
-      <c r="K20" s="386"/>
+      <c r="D20" s="391"/>
+      <c r="E20" s="391"/>
+      <c r="F20" s="391"/>
+      <c r="G20" s="391"/>
+      <c r="H20" s="391"/>
+      <c r="I20" s="391"/>
+      <c r="J20" s="391"/>
+      <c r="K20" s="391"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -11050,21 +11050,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="384" t="s">
+      <c r="A21" s="389" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="248"/>
-      <c r="C21" s="389" t="s">
+      <c r="B21" s="251"/>
+      <c r="C21" s="390" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="386"/>
-      <c r="E21" s="386"/>
-      <c r="F21" s="386"/>
-      <c r="G21" s="386"/>
-      <c r="H21" s="386"/>
-      <c r="I21" s="386"/>
-      <c r="J21" s="386"/>
-      <c r="K21" s="386"/>
+      <c r="D21" s="391"/>
+      <c r="E21" s="391"/>
+      <c r="F21" s="391"/>
+      <c r="G21" s="391"/>
+      <c r="H21" s="391"/>
+      <c r="I21" s="391"/>
+      <c r="J21" s="391"/>
+      <c r="K21" s="391"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -11079,25 +11079,25 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="384" t="s">
+      <c r="A22" s="389" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="248"/>
-      <c r="C22" s="388" t="s">
+      <c r="B22" s="251"/>
+      <c r="C22" s="398" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="386"/>
-      <c r="E22" s="386"/>
-      <c r="F22" s="386"/>
-      <c r="G22" s="386"/>
-      <c r="H22" s="386"/>
-      <c r="I22" s="386"/>
-      <c r="J22" s="386"/>
-      <c r="K22" s="386"/>
-      <c r="L22" s="386"/>
-      <c r="M22" s="386"/>
-      <c r="N22" s="386"/>
-      <c r="O22" s="262"/>
+      <c r="D22" s="391"/>
+      <c r="E22" s="391"/>
+      <c r="F22" s="391"/>
+      <c r="G22" s="391"/>
+      <c r="H22" s="391"/>
+      <c r="I22" s="391"/>
+      <c r="J22" s="391"/>
+      <c r="K22" s="391"/>
+      <c r="L22" s="391"/>
+      <c r="M22" s="391"/>
+      <c r="N22" s="391"/>
+      <c r="O22" s="253"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
       </c>
@@ -11108,22 +11108,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="384" t="s">
+      <c r="A23" s="389" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="248"/>
-      <c r="C23" s="389" t="s">
+      <c r="B23" s="251"/>
+      <c r="C23" s="390" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="386"/>
-      <c r="E23" s="386"/>
-      <c r="F23" s="386"/>
-      <c r="G23" s="386"/>
-      <c r="H23" s="386"/>
-      <c r="I23" s="386"/>
-      <c r="J23" s="386"/>
-      <c r="K23" s="386"/>
-      <c r="L23" s="386"/>
+      <c r="D23" s="391"/>
+      <c r="E23" s="391"/>
+      <c r="F23" s="391"/>
+      <c r="G23" s="391"/>
+      <c r="H23" s="391"/>
+      <c r="I23" s="391"/>
+      <c r="J23" s="391"/>
+      <c r="K23" s="391"/>
+      <c r="L23" s="391"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -11137,22 +11137,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="384" t="s">
+      <c r="A24" s="389" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="248"/>
-      <c r="C24" s="389" t="s">
+      <c r="B24" s="251"/>
+      <c r="C24" s="390" t="s">
         <v>199</v>
       </c>
-      <c r="D24" s="386"/>
-      <c r="E24" s="386"/>
-      <c r="F24" s="386"/>
-      <c r="G24" s="386"/>
-      <c r="H24" s="386"/>
-      <c r="I24" s="386"/>
-      <c r="J24" s="386"/>
-      <c r="K24" s="386"/>
-      <c r="L24" s="386"/>
+      <c r="D24" s="391"/>
+      <c r="E24" s="391"/>
+      <c r="F24" s="391"/>
+      <c r="G24" s="391"/>
+      <c r="H24" s="391"/>
+      <c r="I24" s="391"/>
+      <c r="J24" s="391"/>
+      <c r="K24" s="391"/>
+      <c r="L24" s="391"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -11166,21 +11166,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="384" t="s">
+      <c r="A25" s="389" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="248"/>
-      <c r="C25" s="389" t="s">
+      <c r="B25" s="251"/>
+      <c r="C25" s="390" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="386"/>
-      <c r="E25" s="386"/>
-      <c r="F25" s="386"/>
-      <c r="G25" s="386"/>
-      <c r="H25" s="386"/>
-      <c r="I25" s="386"/>
-      <c r="J25" s="386"/>
-      <c r="K25" s="386"/>
+      <c r="D25" s="391"/>
+      <c r="E25" s="391"/>
+      <c r="F25" s="391"/>
+      <c r="G25" s="391"/>
+      <c r="H25" s="391"/>
+      <c r="I25" s="391"/>
+      <c r="J25" s="391"/>
+      <c r="K25" s="391"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -11190,21 +11190,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="390" t="s">
+      <c r="A26" s="392" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="391"/>
-      <c r="C26" s="392" t="s">
+      <c r="B26" s="393"/>
+      <c r="C26" s="394" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="393"/>
-      <c r="E26" s="393"/>
-      <c r="F26" s="393"/>
-      <c r="G26" s="393"/>
-      <c r="H26" s="393"/>
-      <c r="I26" s="393"/>
-      <c r="J26" s="393"/>
-      <c r="K26" s="393"/>
+      <c r="D26" s="395"/>
+      <c r="E26" s="395"/>
+      <c r="F26" s="395"/>
+      <c r="G26" s="395"/>
+      <c r="H26" s="395"/>
+      <c r="I26" s="395"/>
+      <c r="J26" s="395"/>
+      <c r="K26" s="395"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -11225,6 +11225,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -11241,21 +11256,6 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -11312,370 +11312,383 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="394" t="str">
+      <c r="C4" s="415" t="str">
         <f>'AREA UTIL '!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="394" t="s">
+      <c r="C5" s="415" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="399" t="s">
+      <c r="C6" s="400" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="396">
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="401">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="252"/>
-      <c r="H6" s="262"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="253"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="399" t="s">
+      <c r="C7" s="400" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="252"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="396">
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="401">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="252"/>
-      <c r="H7" s="262"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="253"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="399" t="s">
+      <c r="C8" s="400" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="252"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="396">
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="401">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="252"/>
-      <c r="H8" s="262"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="253"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="399" t="s">
+      <c r="C9" s="400" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="395">
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="403">
         <v>6</v>
       </c>
-      <c r="G9" s="252"/>
-      <c r="H9" s="262"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="253"/>
       <c r="J9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="399" t="s">
+      <c r="C10" s="400" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="395">
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="403">
         <v>1</v>
       </c>
-      <c r="G10" s="252"/>
-      <c r="H10" s="262"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="253"/>
       <c r="J10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="399" t="s">
+      <c r="C11" s="400" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="410">
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="412">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="252"/>
-      <c r="H11" s="262"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="253"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="399" t="s">
+      <c r="C12" s="400" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="252"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="395">
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="403">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="252"/>
-      <c r="H12" s="262"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="253"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="399" t="s">
+      <c r="C13" s="400" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="396">
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="401">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="252"/>
-      <c r="H13" s="262"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="253"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="407" t="s">
+      <c r="C14" s="410" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="403">
+      <c r="D14" s="250"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="409">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="247"/>
-      <c r="H14" s="248"/>
-      <c r="J14" s="401">
+      <c r="G14" s="250"/>
+      <c r="H14" s="251"/>
+      <c r="J14" s="413">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="252"/>
-      <c r="L14" s="252"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="405"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="252"/>
-      <c r="F15" s="252"/>
-      <c r="G15" s="252"/>
-      <c r="H15" s="252"/>
+      <c r="C15" s="417"/>
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="248"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="248"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="409" t="s">
+      <c r="C16" s="399" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="252"/>
-      <c r="E16" s="252"/>
-      <c r="F16" s="252"/>
-      <c r="G16" s="252"/>
-      <c r="H16" s="252"/>
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="248"/>
+      <c r="G16" s="248"/>
+      <c r="H16" s="248"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="399" t="s">
+      <c r="C17" s="400" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="395">
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="403">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="252"/>
-      <c r="H17" s="262"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="253"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="399" t="s">
+      <c r="C18" s="400" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="252"/>
-      <c r="E18" s="252"/>
-      <c r="F18" s="396">
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="401">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="252"/>
-      <c r="H18" s="262"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="253"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="399" t="s">
+      <c r="C19" s="400" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="252"/>
-      <c r="E19" s="252"/>
-      <c r="F19" s="396">
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="401">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="252"/>
-      <c r="H19" s="262"/>
+      <c r="G19" s="248"/>
+      <c r="H19" s="253"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="407" t="s">
+      <c r="C20" s="410" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="247"/>
-      <c r="E20" s="247"/>
-      <c r="F20" s="403">
+      <c r="D20" s="250"/>
+      <c r="E20" s="250"/>
+      <c r="F20" s="409">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="247"/>
-      <c r="H20" s="248"/>
+      <c r="G20" s="250"/>
+      <c r="H20" s="251"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="400"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="397"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
+      <c r="C21" s="404"/>
+      <c r="D21" s="248"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="407"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="400"/>
-      <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="397"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
+      <c r="C22" s="404"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="407"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="400"/>
-      <c r="D23" s="252"/>
-      <c r="E23" s="252"/>
-      <c r="F23" s="404"/>
-      <c r="G23" s="252"/>
-      <c r="H23" s="252"/>
+      <c r="C23" s="404"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="416"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="248"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="402" t="s">
+      <c r="C24" s="414" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="252"/>
-      <c r="E24" s="252"/>
-      <c r="F24" s="252"/>
-      <c r="G24" s="252"/>
-      <c r="H24" s="252"/>
+      <c r="D24" s="248"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="248"/>
+      <c r="G24" s="248"/>
+      <c r="H24" s="248"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="398" t="s">
+      <c r="C25" s="405" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="406">
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="408">
         <v>2000000</v>
       </c>
-      <c r="G25" s="252"/>
-      <c r="H25" s="262"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="253"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="398" t="s">
+      <c r="C26" s="405" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="252"/>
-      <c r="E26" s="252"/>
-      <c r="F26" s="411">
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="402">
         <v>0.8</v>
       </c>
-      <c r="G26" s="252"/>
-      <c r="H26" s="262"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="253"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="398" t="s">
+      <c r="C27" s="405" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="252"/>
-      <c r="E27" s="252"/>
-      <c r="F27" s="406">
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="408">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="252"/>
-      <c r="H27" s="262"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="253"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="408" t="s">
+      <c r="C28" s="411" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="247"/>
-      <c r="E28" s="247"/>
-      <c r="F28" s="412">
+      <c r="D28" s="250"/>
+      <c r="E28" s="250"/>
+      <c r="F28" s="406">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="247"/>
-      <c r="H28" s="248"/>
+      <c r="G28" s="250"/>
+      <c r="H28" s="251"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="409" t="s">
+      <c r="C31" s="399" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="252"/>
-      <c r="E31" s="252"/>
-      <c r="F31" s="252"/>
-      <c r="G31" s="252"/>
-      <c r="H31" s="252"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="399" t="s">
+      <c r="C32" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="252"/>
-      <c r="E32" s="252"/>
-      <c r="F32" s="396">
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="401">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="252"/>
-      <c r="H32" s="262"/>
+      <c r="G32" s="248"/>
+      <c r="H32" s="253"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="399" t="s">
+      <c r="C33" s="400" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="252"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="396">
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="401">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="252"/>
-      <c r="H33" s="262"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="253"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="407" t="s">
+      <c r="C34" s="410" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="247"/>
-      <c r="E34" s="247"/>
-      <c r="F34" s="403">
+      <c r="D34" s="250"/>
+      <c r="E34" s="250"/>
+      <c r="F34" s="409">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="247"/>
-      <c r="H34" s="248"/>
+      <c r="G34" s="250"/>
+      <c r="H34" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="F10:H10"/>
@@ -11692,31 +11705,18 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -11734,178 +11734,169 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="394" t="str">
+      <c r="C5" s="415" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="252"/>
-      <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
-      <c r="H5" s="252"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="394" t="s">
+      <c r="C6" s="415" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="399" t="s">
+      <c r="C7" s="400" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="252"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="414">
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="419">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="252"/>
-      <c r="H7" s="262"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="253"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="399" t="s">
+      <c r="C8" s="400" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="252"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="395">
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="403">
         <v>36</v>
       </c>
-      <c r="G8" s="252"/>
-      <c r="H8" s="262"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="253"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="399" t="s">
+      <c r="C9" s="400" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="413">
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="418">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="252"/>
-      <c r="H9" s="262"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="253"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="399" t="s">
+      <c r="C10" s="400" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="396">
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="401">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="252"/>
-      <c r="H10" s="262"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="253"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="407" t="s">
+      <c r="C11" s="410" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="247"/>
-      <c r="E11" s="247"/>
-      <c r="F11" s="403">
+      <c r="D11" s="250"/>
+      <c r="E11" s="250"/>
+      <c r="F11" s="409">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="247"/>
-      <c r="H11" s="248"/>
+      <c r="G11" s="250"/>
+      <c r="H11" s="251"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="409" t="s">
+      <c r="C13" s="399" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="252"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="399" t="s">
+      <c r="C14" s="400" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="252"/>
-      <c r="E14" s="252"/>
-      <c r="F14" s="414">
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="419">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="252"/>
-      <c r="H14" s="262"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="253"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="399" t="s">
+      <c r="C15" s="400" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="252"/>
-      <c r="E15" s="252"/>
-      <c r="F15" s="395">
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="403">
         <v>36</v>
       </c>
-      <c r="G15" s="252"/>
-      <c r="H15" s="262"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="253"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="399" t="s">
+      <c r="C16" s="400" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="252"/>
-      <c r="E16" s="252"/>
-      <c r="F16" s="413">
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="418">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="252"/>
-      <c r="H16" s="262"/>
+      <c r="G16" s="248"/>
+      <c r="H16" s="253"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="399" t="s">
+      <c r="C17" s="400" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="396">
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="401">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="252"/>
-      <c r="H17" s="262"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="253"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="407" t="s">
+      <c r="C18" s="410" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="247"/>
-      <c r="E18" s="247"/>
-      <c r="F18" s="403">
+      <c r="D18" s="250"/>
+      <c r="E18" s="250"/>
+      <c r="F18" s="409">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="247"/>
-      <c r="H18" s="248"/>
+      <c r="G18" s="250"/>
+      <c r="H18" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -11920,6 +11911,15 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\automacao_laudo\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dista\Desktop\projeto_laudo\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5A91DC-455D-4CB6-B034-79A72D035B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6930" tabRatio="874" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
     <sheet name="FATORES" sheetId="2" r:id="rId2"/>
     <sheet name="UTIL_LAUDO" sheetId="13" r:id="rId3"/>
-    <sheet name="AREA UTIL " sheetId="3" r:id="rId4"/>
+    <sheet name="AREA UTIL" sheetId="3" r:id="rId4"/>
     <sheet name="AMOSTRAS" sheetId="4" r:id="rId5"/>
     <sheet name="QUADRO" sheetId="5" r:id="rId6"/>
     <sheet name="PLANILHA HOMOG" sheetId="6" r:id="rId7"/>
@@ -30,30 +31,17 @@
     <definedName name="Print_Area" localSheetId="10">'LAUDO DE AVALIAÇÃO 12-12.4'!$B$1:$H$24</definedName>
     <definedName name="Print_Area" localSheetId="11">'LAUDO DE AVALIAÇÃO 13'!$B$1:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -70,12 +58,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>valec</author>
   </authors>
   <commentList>
-    <comment ref="D5" authorId="0" shapeId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1087,7 +1075,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="12">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -2907,95 +2895,95 @@
     <xf numFmtId="0" fontId="63" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3016,56 +3004,38 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3078,52 +3048,82 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3133,157 +3133,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3293,29 +3197,122 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3325,162 +3322,163 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3488,26 +3486,16 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3523,25 +3511,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3670,9 +3658,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3710,9 +3698,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3747,7 +3735,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3782,7 +3770,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3955,12 +3943,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:M47"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="249" t="s">
+      <c r="B3" s="247" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="256"/>
@@ -3973,21 +3961,21 @@
       <c r="J3" s="256"/>
       <c r="K3" s="256"/>
       <c r="L3" s="256"/>
-      <c r="M3" s="261"/>
+      <c r="M3" s="257"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="262"/>
-      <c r="C4" s="259"/>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259"/>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="M4" s="263"/>
+      <c r="B4" s="269"/>
+      <c r="C4" s="251"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="M4" s="259"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -4018,100 +4006,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="247" t="s">
+      <c r="B7" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="263"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="247" t="s">
+      <c r="B8" s="252" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="248"/>
-      <c r="D8" s="248"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="248"/>
-      <c r="G8" s="248"/>
-      <c r="H8" s="248"/>
-      <c r="I8" s="248"/>
-      <c r="J8" s="248"/>
-      <c r="K8" s="248"/>
-      <c r="L8" s="248"/>
-      <c r="M8" s="253"/>
+      <c r="C8" s="253"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="253"/>
+      <c r="I8" s="253"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="253"/>
+      <c r="L8" s="253"/>
+      <c r="M8" s="263"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="247" t="s">
+      <c r="B9" s="252" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="248"/>
-      <c r="D9" s="248"/>
-      <c r="E9" s="252"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
-      <c r="M9" s="253"/>
+      <c r="C9" s="253"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="270"/>
+      <c r="F9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="253"/>
+      <c r="I9" s="253"/>
+      <c r="J9" s="253"/>
+      <c r="K9" s="253"/>
+      <c r="L9" s="253"/>
+      <c r="M9" s="263"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="247" t="s">
+      <c r="B10" s="252" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="248"/>
-      <c r="D10" s="248"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="248"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="248"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="248"/>
-      <c r="K10" s="248"/>
-      <c r="L10" s="248"/>
-      <c r="M10" s="253"/>
+      <c r="C10" s="253"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="253"/>
+      <c r="I10" s="253"/>
+      <c r="J10" s="253"/>
+      <c r="K10" s="253"/>
+      <c r="L10" s="253"/>
+      <c r="M10" s="263"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="247" t="s">
+      <c r="B11" s="252" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="252"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
-      <c r="M11" s="253"/>
+      <c r="C11" s="253"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="270"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="253"/>
+      <c r="I11" s="253"/>
+      <c r="J11" s="253"/>
+      <c r="K11" s="253"/>
+      <c r="L11" s="253"/>
+      <c r="M11" s="263"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="247" t="s">
+      <c r="B12" s="252" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="248"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="252"/>
-      <c r="F12" s="248"/>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
-      <c r="K12" s="248"/>
-      <c r="L12" s="248"/>
-      <c r="M12" s="253"/>
+      <c r="C12" s="253"/>
+      <c r="D12" s="253"/>
+      <c r="E12" s="270"/>
+      <c r="F12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="253"/>
+      <c r="K12" s="253"/>
+      <c r="L12" s="253"/>
+      <c r="M12" s="263"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4170,20 +4158,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="254" t="s">
+      <c r="B17" s="281" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
-      <c r="M17" s="248"/>
+      <c r="C17" s="253"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
+      <c r="J17" s="253"/>
+      <c r="K17" s="253"/>
+      <c r="L17" s="253"/>
+      <c r="M17" s="253"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4200,12 +4188,12 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="282" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="256"/>
       <c r="D19" s="256"/>
-      <c r="E19" s="260"/>
+      <c r="E19" s="280"/>
       <c r="F19" s="256"/>
       <c r="G19" s="256"/>
       <c r="H19" s="256"/>
@@ -4213,137 +4201,137 @@
       <c r="J19" s="256"/>
       <c r="K19" s="256"/>
       <c r="L19" s="256"/>
-      <c r="M19" s="261"/>
+      <c r="M19" s="257"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="252" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="248"/>
-      <c r="D20" s="248"/>
-      <c r="E20" s="252"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="248"/>
-      <c r="H20" s="248"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="248"/>
-      <c r="K20" s="248"/>
-      <c r="L20" s="248"/>
-      <c r="M20" s="253"/>
+      <c r="C20" s="253"/>
+      <c r="D20" s="253"/>
+      <c r="E20" s="270"/>
+      <c r="F20" s="253"/>
+      <c r="G20" s="253"/>
+      <c r="H20" s="253"/>
+      <c r="I20" s="253"/>
+      <c r="J20" s="253"/>
+      <c r="K20" s="253"/>
+      <c r="L20" s="253"/>
+      <c r="M20" s="263"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="248"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="M21" s="253"/>
+      <c r="C21" s="253"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="270"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="253"/>
+      <c r="K21" s="253"/>
+      <c r="L21" s="253"/>
+      <c r="M21" s="263"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="270" t="s">
+      <c r="B22" s="277" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="259"/>
-      <c r="D22" s="259"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="259"/>
-      <c r="G22" s="259"/>
-      <c r="H22" s="259"/>
-      <c r="I22" s="259"/>
-      <c r="J22" s="259"/>
+      <c r="C22" s="251"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="268"/>
-      <c r="M22" s="263"/>
+      <c r="L22" s="275"/>
+      <c r="M22" s="259"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="249" t="s">
+      <c r="B23" s="247" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="250"/>
-      <c r="D23" s="250"/>
-      <c r="E23" s="250"/>
-      <c r="F23" s="250"/>
-      <c r="G23" s="250"/>
-      <c r="H23" s="250"/>
-      <c r="I23" s="250"/>
-      <c r="J23" s="250"/>
-      <c r="K23" s="250"/>
-      <c r="L23" s="250"/>
-      <c r="M23" s="251"/>
+      <c r="C23" s="248"/>
+      <c r="D23" s="248"/>
+      <c r="E23" s="248"/>
+      <c r="F23" s="248"/>
+      <c r="G23" s="248"/>
+      <c r="H23" s="248"/>
+      <c r="I23" s="248"/>
+      <c r="J23" s="248"/>
+      <c r="K23" s="248"/>
+      <c r="L23" s="248"/>
+      <c r="M23" s="249"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="257" t="s">
+      <c r="B24" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="250"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="257" t="s">
+      <c r="C24" s="248"/>
+      <c r="D24" s="249"/>
+      <c r="E24" s="260" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="250"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="257" t="s">
+      <c r="F24" s="248"/>
+      <c r="G24" s="249"/>
+      <c r="H24" s="260" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="250"/>
-      <c r="J24" s="251"/>
-      <c r="K24" s="257" t="s">
+      <c r="I24" s="248"/>
+      <c r="J24" s="249"/>
+      <c r="K24" s="260" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="250"/>
-      <c r="M24" s="251"/>
+      <c r="L24" s="248"/>
+      <c r="M24" s="249"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="267"/>
+      <c r="B25" s="274"/>
       <c r="C25" s="256"/>
-      <c r="D25" s="261"/>
-      <c r="E25" s="276"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="274"/>
+      <c r="D25" s="257"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="255"/>
       <c r="I25" s="256"/>
-      <c r="J25" s="261"/>
-      <c r="K25" s="269"/>
+      <c r="J25" s="257"/>
+      <c r="K25" s="276"/>
       <c r="L25" s="256"/>
-      <c r="M25" s="261"/>
+      <c r="M25" s="257"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="265"/>
-      <c r="C26" s="259"/>
-      <c r="D26" s="263"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="259"/>
-      <c r="G26" s="259"/>
-      <c r="H26" s="266"/>
-      <c r="I26" s="259"/>
-      <c r="J26" s="263"/>
-      <c r="K26" s="271"/>
-      <c r="L26" s="259"/>
-      <c r="M26" s="263"/>
+      <c r="B26" s="272"/>
+      <c r="C26" s="251"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="279"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="273"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="259"/>
+      <c r="K26" s="278"/>
+      <c r="L26" s="251"/>
+      <c r="M26" s="259"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="249" t="s">
+      <c r="B27" s="247" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="250"/>
-      <c r="D27" s="250"/>
-      <c r="E27" s="250"/>
-      <c r="F27" s="250"/>
-      <c r="G27" s="250"/>
-      <c r="H27" s="250"/>
-      <c r="I27" s="250"/>
-      <c r="J27" s="250"/>
-      <c r="K27" s="250"/>
-      <c r="L27" s="250"/>
-      <c r="M27" s="251"/>
+      <c r="C27" s="248"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
+      <c r="M27" s="249"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4430,100 +4418,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="249" t="s">
+      <c r="B34" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="250"/>
-      <c r="D34" s="250"/>
-      <c r="E34" s="250"/>
-      <c r="F34" s="250"/>
-      <c r="G34" s="250"/>
-      <c r="H34" s="250"/>
-      <c r="I34" s="250"/>
-      <c r="J34" s="250"/>
-      <c r="K34" s="250"/>
-      <c r="L34" s="250"/>
-      <c r="M34" s="251"/>
+      <c r="C34" s="248"/>
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="248"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="248"/>
+      <c r="I34" s="248"/>
+      <c r="J34" s="248"/>
+      <c r="K34" s="248"/>
+      <c r="L34" s="248"/>
+      <c r="M34" s="249"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="257" t="s">
+      <c r="B35" s="260" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="250"/>
-      <c r="D35" s="250"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="257" t="s">
+      <c r="C35" s="248"/>
+      <c r="D35" s="248"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="250"/>
-      <c r="H35" s="250"/>
-      <c r="I35" s="251"/>
-      <c r="J35" s="257" t="s">
+      <c r="G35" s="248"/>
+      <c r="H35" s="248"/>
+      <c r="I35" s="249"/>
+      <c r="J35" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="250"/>
-      <c r="L35" s="250"/>
-      <c r="M35" s="251"/>
+      <c r="K35" s="248"/>
+      <c r="L35" s="248"/>
+      <c r="M35" s="249"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="280"/>
+      <c r="B36" s="266"/>
       <c r="C36" s="256"/>
       <c r="D36" s="256"/>
       <c r="E36" s="256"/>
-      <c r="F36" s="281"/>
+      <c r="F36" s="267"/>
       <c r="G36" s="256"/>
       <c r="H36" s="256"/>
       <c r="I36" s="256"/>
-      <c r="J36" s="282"/>
+      <c r="J36" s="268"/>
       <c r="K36" s="256"/>
       <c r="L36" s="256"/>
-      <c r="M36" s="261"/>
+      <c r="M36" s="257"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="273"/>
-      <c r="C37" s="248"/>
-      <c r="D37" s="248"/>
-      <c r="E37" s="248"/>
-      <c r="F37" s="279"/>
-      <c r="G37" s="248"/>
-      <c r="H37" s="248"/>
-      <c r="I37" s="248"/>
-      <c r="J37" s="277"/>
-      <c r="K37" s="248"/>
-      <c r="L37" s="248"/>
-      <c r="M37" s="253"/>
+      <c r="B37" s="254"/>
+      <c r="C37" s="253"/>
+      <c r="D37" s="253"/>
+      <c r="E37" s="253"/>
+      <c r="F37" s="265"/>
+      <c r="G37" s="253"/>
+      <c r="H37" s="253"/>
+      <c r="I37" s="253"/>
+      <c r="J37" s="262"/>
+      <c r="K37" s="253"/>
+      <c r="L37" s="253"/>
+      <c r="M37" s="263"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="278" t="s">
+      <c r="B38" s="264" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="259"/>
-      <c r="D38" s="259"/>
-      <c r="E38" s="259"/>
-      <c r="F38" s="272"/>
-      <c r="G38" s="259"/>
-      <c r="H38" s="259"/>
-      <c r="I38" s="259"/>
-      <c r="J38" s="275"/>
-      <c r="K38" s="259"/>
-      <c r="L38" s="259"/>
-      <c r="M38" s="263"/>
+      <c r="C38" s="251"/>
+      <c r="D38" s="251"/>
+      <c r="E38" s="251"/>
+      <c r="F38" s="250"/>
+      <c r="G38" s="251"/>
+      <c r="H38" s="251"/>
+      <c r="I38" s="251"/>
+      <c r="J38" s="258"/>
+      <c r="K38" s="251"/>
+      <c r="L38" s="251"/>
+      <c r="M38" s="259"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="249" t="s">
+      <c r="B39" s="247" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="250"/>
-      <c r="D39" s="250"/>
-      <c r="E39" s="250"/>
-      <c r="F39" s="250"/>
-      <c r="G39" s="250"/>
-      <c r="H39" s="250"/>
-      <c r="I39" s="250"/>
-      <c r="J39" s="250"/>
-      <c r="K39" s="250"/>
-      <c r="L39" s="250"/>
-      <c r="M39" s="251"/>
+      <c r="C39" s="248"/>
+      <c r="D39" s="248"/>
+      <c r="E39" s="248"/>
+      <c r="F39" s="248"/>
+      <c r="G39" s="248"/>
+      <c r="H39" s="248"/>
+      <c r="I39" s="248"/>
+      <c r="J39" s="248"/>
+      <c r="K39" s="248"/>
+      <c r="L39" s="248"/>
+      <c r="M39" s="249"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4639,6 +4627,41 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B3:M4"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="B39:M39"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B21:D21"/>
@@ -4655,48 +4678,13 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
     <mergeCell ref="B34:M34"/>
-    <mergeCell ref="B3:M4"/>
-    <mergeCell ref="E7:M7"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E12:M12"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:AK58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -4730,37 +4718,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="436" t="s">
+      <c r="B2" s="420" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="437"/>
-      <c r="D2" s="437"/>
-      <c r="E2" s="437"/>
-      <c r="F2" s="437"/>
-      <c r="G2" s="437"/>
-      <c r="H2" s="437"/>
-      <c r="I2" s="437"/>
-      <c r="J2" s="437"/>
-      <c r="K2" s="437"/>
-      <c r="L2" s="437"/>
-      <c r="M2" s="437"/>
-      <c r="N2" s="437"/>
-      <c r="O2" s="437"/>
-      <c r="P2" s="437"/>
-      <c r="Q2" s="437"/>
-      <c r="R2" s="437"/>
-      <c r="S2" s="437"/>
-      <c r="T2" s="437"/>
-      <c r="U2" s="437"/>
-      <c r="V2" s="437"/>
-      <c r="W2" s="437"/>
-      <c r="X2" s="437"/>
-      <c r="Y2" s="437"/>
-      <c r="Z2" s="437"/>
-      <c r="AA2" s="437"/>
-      <c r="AB2" s="437"/>
-      <c r="AC2" s="437"/>
-      <c r="AD2" s="437"/>
+      <c r="C2" s="421"/>
+      <c r="D2" s="421"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
+      <c r="G2" s="421"/>
+      <c r="H2" s="421"/>
+      <c r="I2" s="421"/>
+      <c r="J2" s="421"/>
+      <c r="K2" s="421"/>
+      <c r="L2" s="421"/>
+      <c r="M2" s="421"/>
+      <c r="N2" s="421"/>
+      <c r="O2" s="421"/>
+      <c r="P2" s="421"/>
+      <c r="Q2" s="421"/>
+      <c r="R2" s="421"/>
+      <c r="S2" s="421"/>
+      <c r="T2" s="421"/>
+      <c r="U2" s="421"/>
+      <c r="V2" s="421"/>
+      <c r="W2" s="421"/>
+      <c r="X2" s="421"/>
+      <c r="Y2" s="421"/>
+      <c r="Z2" s="421"/>
+      <c r="AA2" s="421"/>
+      <c r="AB2" s="421"/>
+      <c r="AC2" s="421"/>
+      <c r="AD2" s="421"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -4887,39 +4875,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="428">
+      <c r="B10" s="438">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="424"/>
-      <c r="D10" s="424"/>
-      <c r="E10" s="424"/>
-      <c r="F10" s="424"/>
-      <c r="G10" s="424"/>
+      <c r="C10" s="423"/>
+      <c r="D10" s="423"/>
+      <c r="E10" s="423"/>
+      <c r="F10" s="423"/>
+      <c r="G10" s="423"/>
       <c r="H10" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="I10" s="445">
+      <c r="I10" s="437">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="424"/>
-      <c r="K10" s="424"/>
-      <c r="L10" s="424"/>
-      <c r="M10" s="424"/>
-      <c r="N10" s="424"/>
-      <c r="O10" s="424"/>
-      <c r="P10" s="424"/>
+      <c r="J10" s="423"/>
+      <c r="K10" s="423"/>
+      <c r="L10" s="423"/>
+      <c r="M10" s="423"/>
+      <c r="N10" s="423"/>
+      <c r="O10" s="423"/>
+      <c r="P10" s="423"/>
       <c r="Q10" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R10" s="423">
+      <c r="R10" s="422">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="424"/>
-      <c r="T10" s="424"/>
-      <c r="U10" s="424"/>
+      <c r="S10" s="423"/>
+      <c r="T10" s="423"/>
+      <c r="U10" s="423"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>239</v>
@@ -4954,13 +4942,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="423">
+      <c r="W11" s="422">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="424"/>
-      <c r="Y11" s="424"/>
-      <c r="Z11" s="424"/>
+      <c r="X11" s="423"/>
+      <c r="Y11" s="423"/>
+      <c r="Z11" s="423"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -4987,13 +4975,13 @@
       <c r="Q12" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="R12" s="443">
+      <c r="R12" s="434">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="424"/>
-      <c r="T12" s="424"/>
-      <c r="U12" s="424"/>
+      <c r="S12" s="423"/>
+      <c r="T12" s="423"/>
+      <c r="U12" s="423"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -5013,10 +5001,10 @@
         <v>240</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="435"/>
-      <c r="X14" s="424"/>
-      <c r="Y14" s="424"/>
-      <c r="Z14" s="424"/>
+      <c r="W14" s="427"/>
+      <c r="X14" s="423"/>
+      <c r="Y14" s="423"/>
+      <c r="Z14" s="423"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -5042,38 +5030,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="440" t="s">
+      <c r="B16" s="431" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="424"/>
-      <c r="D16" s="424"/>
-      <c r="E16" s="424"/>
-      <c r="F16" s="424"/>
-      <c r="G16" s="424"/>
+      <c r="C16" s="423"/>
+      <c r="D16" s="423"/>
+      <c r="E16" s="423"/>
+      <c r="F16" s="423"/>
+      <c r="G16" s="423"/>
       <c r="H16" s="67" t="s">
         <v>235</v>
       </c>
-      <c r="I16" s="430" t="str">
+      <c r="I16" s="440" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="424"/>
-      <c r="K16" s="424"/>
-      <c r="L16" s="424"/>
-      <c r="M16" s="424"/>
-      <c r="N16" s="424"/>
-      <c r="O16" s="424"/>
-      <c r="P16" s="424"/>
+      <c r="J16" s="423"/>
+      <c r="K16" s="423"/>
+      <c r="L16" s="423"/>
+      <c r="M16" s="423"/>
+      <c r="N16" s="423"/>
+      <c r="O16" s="423"/>
+      <c r="P16" s="423"/>
       <c r="Q16" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R16" s="435" t="str">
+      <c r="R16" s="427" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="424"/>
-      <c r="T16" s="424"/>
-      <c r="U16" s="424"/>
+      <c r="S16" s="423"/>
+      <c r="T16" s="423"/>
+      <c r="U16" s="423"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -5085,10 +5073,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="435"/>
-      <c r="X17" s="424"/>
-      <c r="Y17" s="424"/>
-      <c r="Z17" s="424"/>
+      <c r="W17" s="427"/>
+      <c r="X17" s="423"/>
+      <c r="Y17" s="423"/>
+      <c r="Z17" s="423"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -5112,13 +5100,13 @@
       <c r="Q18" s="67" t="s">
         <v>238</v>
       </c>
-      <c r="R18" s="434" t="str">
+      <c r="R18" s="443" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="424"/>
-      <c r="T18" s="424"/>
-      <c r="U18" s="424"/>
+      <c r="S18" s="423"/>
+      <c r="T18" s="423"/>
+      <c r="U18" s="423"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -5200,13 +5188,13 @@
       <c r="V22" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W22" s="444">
+      <c r="W22" s="435">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="427"/>
-      <c r="Y22" s="427"/>
-      <c r="Z22" s="427"/>
+      <c r="X22" s="430"/>
+      <c r="Y22" s="430"/>
+      <c r="Z22" s="430"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -5215,13 +5203,13 @@
       <c r="V23" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W23" s="426" t="str">
+      <c r="W23" s="429" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="427"/>
-      <c r="Y23" s="427"/>
-      <c r="Z23" s="427"/>
+      <c r="X23" s="430"/>
+      <c r="Y23" s="430"/>
+      <c r="Z23" s="430"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -5230,13 +5218,13 @@
       <c r="V24" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W24" s="438">
+      <c r="W24" s="424">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="421"/>
-      <c r="Y24" s="421"/>
-      <c r="Z24" s="421"/>
+      <c r="X24" s="425"/>
+      <c r="Y24" s="425"/>
+      <c r="Z24" s="425"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -5245,13 +5233,13 @@
       <c r="V25" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W25" s="426">
+      <c r="W25" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="427"/>
-      <c r="Y25" s="427"/>
-      <c r="Z25" s="427"/>
+      <c r="X25" s="430"/>
+      <c r="Y25" s="430"/>
+      <c r="Z25" s="430"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -5260,13 +5248,13 @@
       <c r="V26" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W26" s="426">
+      <c r="W26" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="427"/>
-      <c r="Y26" s="427"/>
-      <c r="Z26" s="427"/>
+      <c r="X26" s="430"/>
+      <c r="Y26" s="430"/>
+      <c r="Z26" s="430"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -5275,13 +5263,13 @@
       <c r="V27" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W27" s="426">
+      <c r="W27" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="427"/>
-      <c r="Y27" s="427"/>
-      <c r="Z27" s="427"/>
+      <c r="X27" s="430"/>
+      <c r="Y27" s="430"/>
+      <c r="Z27" s="430"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -5290,13 +5278,13 @@
       <c r="V28" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W28" s="426">
+      <c r="W28" s="429">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="427"/>
-      <c r="Y28" s="427"/>
-      <c r="Z28" s="427"/>
+      <c r="X28" s="430"/>
+      <c r="Y28" s="430"/>
+      <c r="Z28" s="430"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -5305,13 +5293,13 @@
       <c r="V29" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="W29" s="426">
+      <c r="W29" s="429">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="427"/>
-      <c r="Y29" s="427"/>
-      <c r="Z29" s="427"/>
+      <c r="X29" s="430"/>
+      <c r="Y29" s="430"/>
+      <c r="Z29" s="430"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -5320,13 +5308,13 @@
       <c r="V30" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="W30" s="439">
+      <c r="W30" s="428">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="421"/>
-      <c r="Y30" s="421"/>
-      <c r="Z30" s="421"/>
+      <c r="X30" s="425"/>
+      <c r="Y30" s="425"/>
+      <c r="Z30" s="425"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -5336,83 +5324,83 @@
       <c r="V31" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="W31" s="442">
+      <c r="W31" s="433">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="421"/>
-      <c r="Y31" s="421"/>
-      <c r="Z31" s="421"/>
+      <c r="X31" s="425"/>
+      <c r="Y31" s="425"/>
+      <c r="Z31" s="425"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="K32" s="441">
+      <c r="K32" s="432">
         <v>43009</v>
       </c>
-      <c r="L32" s="427"/>
-      <c r="M32" s="427"/>
-      <c r="N32" s="427"/>
-      <c r="O32" s="427"/>
-      <c r="P32" s="427"/>
-      <c r="Q32" s="427"/>
-      <c r="R32" s="427"/>
-      <c r="S32" s="427"/>
-      <c r="T32" s="427"/>
-      <c r="U32" s="427"/>
-      <c r="V32" s="427"/>
-      <c r="W32" s="427"/>
-      <c r="X32" s="427"/>
-      <c r="Y32" s="427"/>
-      <c r="Z32" s="427"/>
+      <c r="L32" s="430"/>
+      <c r="M32" s="430"/>
+      <c r="N32" s="430"/>
+      <c r="O32" s="430"/>
+      <c r="P32" s="430"/>
+      <c r="Q32" s="430"/>
+      <c r="R32" s="430"/>
+      <c r="S32" s="430"/>
+      <c r="T32" s="430"/>
+      <c r="U32" s="430"/>
+      <c r="V32" s="430"/>
+      <c r="W32" s="430"/>
+      <c r="X32" s="430"/>
+      <c r="Y32" s="430"/>
+      <c r="Z32" s="430"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="420" t="s">
+      <c r="O33" s="444" t="s">
         <v>255</v>
       </c>
-      <c r="P33" s="421"/>
-      <c r="Q33" s="421"/>
-      <c r="R33" s="421"/>
-      <c r="S33" s="421"/>
-      <c r="T33" s="421"/>
-      <c r="U33" s="421"/>
-      <c r="V33" s="421"/>
-      <c r="W33" s="425" t="s">
+      <c r="P33" s="425"/>
+      <c r="Q33" s="425"/>
+      <c r="R33" s="425"/>
+      <c r="S33" s="425"/>
+      <c r="T33" s="425"/>
+      <c r="U33" s="425"/>
+      <c r="V33" s="425"/>
+      <c r="W33" s="445" t="s">
         <v>256</v>
       </c>
-      <c r="X33" s="329"/>
-      <c r="Y33" s="329"/>
-      <c r="Z33" s="329"/>
-      <c r="AA33" s="329"/>
-      <c r="AB33" s="329"/>
-      <c r="AC33" s="329"/>
-      <c r="AD33" s="329"/>
+      <c r="X33" s="333"/>
+      <c r="Y33" s="333"/>
+      <c r="Z33" s="333"/>
+      <c r="AA33" s="333"/>
+      <c r="AB33" s="333"/>
+      <c r="AC33" s="333"/>
+      <c r="AD33" s="333"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="432">
+      <c r="Q34" s="436">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="427"/>
-      <c r="S34" s="427"/>
-      <c r="T34" s="427"/>
+      <c r="R34" s="430"/>
+      <c r="S34" s="430"/>
+      <c r="T34" s="430"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="432">
+      <c r="Y34" s="436">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="427"/>
-      <c r="AA34" s="427"/>
-      <c r="AB34" s="427"/>
+      <c r="Z34" s="430"/>
+      <c r="AA34" s="430"/>
+      <c r="AB34" s="430"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -5475,32 +5463,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="429"/>
-      <c r="C38" s="424"/>
+      <c r="B38" s="426"/>
+      <c r="C38" s="423"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="429"/>
-      <c r="C39" s="424"/>
+      <c r="B39" s="426"/>
+      <c r="C39" s="423"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="429"/>
-      <c r="C40" s="424"/>
+      <c r="B40" s="426"/>
+      <c r="C40" s="423"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="429"/>
-      <c r="C41" s="424"/>
+      <c r="B41" s="426"/>
+      <c r="C41" s="423"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="429"/>
-      <c r="C42" s="424"/>
+      <c r="B42" s="426"/>
+      <c r="C42" s="423"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="429"/>
-      <c r="C43" s="424"/>
+      <c r="B43" s="426"/>
+      <c r="C43" s="423"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="429"/>
-      <c r="C44" s="424"/>
+      <c r="B44" s="426"/>
+      <c r="C44" s="423"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -5571,10 +5559,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="433"/>
-      <c r="F49" s="424"/>
-      <c r="G49" s="424"/>
-      <c r="H49" s="424"/>
+      <c r="E49" s="442"/>
+      <c r="F49" s="423"/>
+      <c r="G49" s="423"/>
+      <c r="H49" s="423"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -5597,44 +5585,66 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="422"/>
-      <c r="I52" s="329"/>
-      <c r="J52" s="329"/>
-      <c r="K52" s="329"/>
-      <c r="L52" s="329"/>
-      <c r="M52" s="329"/>
-      <c r="N52" s="329"/>
-      <c r="O52" s="329"/>
-      <c r="P52" s="329"/>
+      <c r="H52" s="439"/>
+      <c r="I52" s="333"/>
+      <c r="J52" s="333"/>
+      <c r="K52" s="333"/>
+      <c r="L52" s="333"/>
+      <c r="M52" s="333"/>
+      <c r="N52" s="333"/>
+      <c r="O52" s="333"/>
+      <c r="P52" s="333"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="431"/>
-      <c r="I55" s="329"/>
-      <c r="J55" s="329"/>
-      <c r="K55" s="329"/>
-      <c r="L55" s="329"/>
-      <c r="M55" s="329"/>
-      <c r="N55" s="329"/>
-      <c r="O55" s="329"/>
-      <c r="P55" s="329"/>
+      <c r="H55" s="441"/>
+      <c r="I55" s="333"/>
+      <c r="J55" s="333"/>
+      <c r="K55" s="333"/>
+      <c r="L55" s="333"/>
+      <c r="M55" s="333"/>
+      <c r="N55" s="333"/>
+      <c r="O55" s="333"/>
+      <c r="P55" s="333"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="422"/>
-      <c r="I57" s="329"/>
-      <c r="J57" s="329"/>
-      <c r="K57" s="329"/>
-      <c r="L57" s="329"/>
-      <c r="M57" s="329"/>
-      <c r="N57" s="329"/>
-      <c r="O57" s="329"/>
-      <c r="P57" s="329"/>
+      <c r="H57" s="439"/>
+      <c r="I57" s="333"/>
+      <c r="J57" s="333"/>
+      <c r="K57" s="333"/>
+      <c r="L57" s="333"/>
+      <c r="M57" s="333"/>
+      <c r="N57" s="333"/>
+      <c r="O57" s="333"/>
+      <c r="P57" s="333"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="H57:P57"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="I16:P16"/>
+    <mergeCell ref="W25:Z25"/>
+    <mergeCell ref="H55:P55"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="W28:Z28"/>
+    <mergeCell ref="W27:Z27"/>
+    <mergeCell ref="W17:Z17"/>
     <mergeCell ref="B2:AD2"/>
     <mergeCell ref="R10:U10"/>
     <mergeCell ref="W24:Z24"/>
@@ -5651,28 +5661,6 @@
     <mergeCell ref="W22:Z22"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="H57:P57"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I16:P16"/>
-    <mergeCell ref="W25:Z25"/>
-    <mergeCell ref="H55:P55"/>
-    <mergeCell ref="Q34:T34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="W28:Z28"/>
-    <mergeCell ref="W27:Z27"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
@@ -5691,7 +5679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:L24"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -5708,24 +5696,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="461" t="s">
+      <c r="B1" s="452" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="462"/>
-      <c r="D1" s="462"/>
-      <c r="E1" s="462"/>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
-      <c r="H1" s="463"/>
+      <c r="C1" s="453"/>
+      <c r="D1" s="453"/>
+      <c r="E1" s="453"/>
+      <c r="F1" s="453"/>
+      <c r="G1" s="453"/>
+      <c r="H1" s="454"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="458"/>
-      <c r="C2" s="459"/>
-      <c r="D2" s="459"/>
-      <c r="E2" s="459"/>
-      <c r="F2" s="459"/>
-      <c r="G2" s="459"/>
-      <c r="H2" s="460"/>
+      <c r="B2" s="448"/>
+      <c r="C2" s="449"/>
+      <c r="D2" s="449"/>
+      <c r="E2" s="449"/>
+      <c r="F2" s="449"/>
+      <c r="G2" s="449"/>
+      <c r="H2" s="450"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -5760,32 +5748,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="451" t="s">
+      <c r="B6" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C6" s="453" t="s">
+      <c r="C6" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="449" t="s">
+      <c r="D6" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="455" t="s">
+      <c r="E6" s="462" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="455" t="s">
+      <c r="F6" s="462" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="446" t="s">
+      <c r="G6" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H6" s="447"/>
+      <c r="H6" s="456"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="452"/>
-      <c r="C7" s="450"/>
-      <c r="D7" s="450"/>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
+      <c r="B7" s="458"/>
+      <c r="C7" s="460"/>
+      <c r="D7" s="460"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="259"/>
       <c r="G7" s="47" t="s">
         <v>265</v>
       </c>
@@ -5806,14 +5794,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="448" t="s">
+      <c r="B9" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="250"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="251"/>
+      <c r="C9" s="248"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="249"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -5831,32 +5819,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="451" t="s">
+      <c r="B11" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C11" s="453" t="s">
+      <c r="C11" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D11" s="449" t="s">
+      <c r="D11" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="454" t="s">
+      <c r="E11" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F11" s="454" t="s">
+      <c r="F11" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="446" t="s">
+      <c r="G11" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="447"/>
+      <c r="H11" s="456"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="452"/>
-      <c r="C12" s="450"/>
-      <c r="D12" s="450"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="263"/>
+      <c r="B12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="259"/>
+      <c r="F12" s="259"/>
       <c r="G12" s="47" t="s">
         <v>265</v>
       </c>
@@ -5877,14 +5865,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="448" t="s">
+      <c r="B14" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="250"/>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="250"/>
-      <c r="G14" s="251"/>
+      <c r="C14" s="248"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="249"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -5902,32 +5890,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="451" t="s">
+      <c r="B16" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="453" t="s">
+      <c r="C16" s="459" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="449" t="s">
+      <c r="D16" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E16" s="454" t="s">
+      <c r="E16" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F16" s="454" t="s">
+      <c r="F16" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="446" t="s">
+      <c r="G16" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="447"/>
+      <c r="H16" s="456"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="452"/>
-      <c r="C17" s="450"/>
-      <c r="D17" s="450"/>
-      <c r="E17" s="263"/>
-      <c r="F17" s="263"/>
+      <c r="B17" s="458"/>
+      <c r="C17" s="460"/>
+      <c r="D17" s="460"/>
+      <c r="E17" s="259"/>
+      <c r="F17" s="259"/>
       <c r="G17" s="22" t="s">
         <v>265</v>
       </c>
@@ -5950,14 +5938,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="448" t="s">
+      <c r="B19" s="463" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="250"/>
-      <c r="D19" s="250"/>
-      <c r="E19" s="250"/>
-      <c r="F19" s="250"/>
-      <c r="G19" s="251"/>
+      <c r="C19" s="248"/>
+      <c r="D19" s="248"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="249"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -5975,32 +5963,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="451" t="s">
+      <c r="B21" s="457" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="453" t="s">
+      <c r="C21" s="459" t="s">
         <v>260</v>
       </c>
-      <c r="D21" s="449" t="s">
+      <c r="D21" s="461" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="454" t="s">
+      <c r="E21" s="451" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="454" t="s">
+      <c r="F21" s="451" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="446" t="s">
+      <c r="G21" s="455" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="447"/>
+      <c r="H21" s="456"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="452"/>
-      <c r="C22" s="450"/>
-      <c r="D22" s="450"/>
-      <c r="E22" s="263"/>
-      <c r="F22" s="263"/>
+      <c r="B22" s="458"/>
+      <c r="C22" s="460"/>
+      <c r="D22" s="460"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="259"/>
       <c r="G22" s="47" t="s">
         <v>265</v>
       </c>
@@ -6021,18 +6009,32 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="456" t="s">
+      <c r="B24" s="446" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="457"/>
-      <c r="D24" s="457"/>
-      <c r="E24" s="457"/>
-      <c r="F24" s="457"/>
-      <c r="G24" s="393"/>
+      <c r="C24" s="447"/>
+      <c r="D24" s="447"/>
+      <c r="E24" s="447"/>
+      <c r="F24" s="447"/>
+      <c r="G24" s="396"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -6049,20 +6051,6 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -6072,7 +6060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:M8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -6091,11 +6079,11 @@
       <c r="B1" s="466" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="459"/>
-      <c r="D1" s="459"/>
-      <c r="E1" s="459"/>
-      <c r="F1" s="459"/>
-      <c r="G1" s="459"/>
+      <c r="C1" s="449"/>
+      <c r="D1" s="449"/>
+      <c r="E1" s="449"/>
+      <c r="F1" s="449"/>
+      <c r="G1" s="449"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -6122,11 +6110,11 @@
       <c r="B4" s="467" t="s">
         <v>272</v>
       </c>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="251"/>
+      <c r="C4" s="248"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="249"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
@@ -6145,14 +6133,14 @@
       <c r="F5" s="465" t="s">
         <v>277</v>
       </c>
-      <c r="G5" s="250"/>
+      <c r="G5" s="248"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="263"/>
-      <c r="C6" s="450"/>
-      <c r="D6" s="450"/>
-      <c r="E6" s="450"/>
+      <c r="B6" s="259"/>
+      <c r="C6" s="460"/>
+      <c r="D6" s="460"/>
+      <c r="E6" s="460"/>
       <c r="F6" s="30" t="s">
         <v>265</v>
       </c>
@@ -6195,7 +6183,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -6204,151 +6192,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="474" t="s">
+      <c r="A1" s="476" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="248"/>
-      <c r="C1" s="248"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
-      <c r="N1" s="248"/>
-      <c r="O1" s="475"/>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="248"/>
-      <c r="S1" s="248"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="253"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="253"/>
+      <c r="O1" s="469"/>
+      <c r="P1" s="253"/>
+      <c r="Q1" s="253"/>
+      <c r="R1" s="253"/>
+      <c r="S1" s="253"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="476" t="s">
+      <c r="A2" s="474" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="248"/>
-      <c r="C2" s="476" t="s">
+      <c r="B2" s="253"/>
+      <c r="C2" s="474" t="s">
         <v>278</v>
       </c>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="472" t="s">
+      <c r="D2" s="253"/>
+      <c r="E2" s="253"/>
+      <c r="F2" s="253"/>
+      <c r="G2" s="253"/>
+      <c r="H2" s="253"/>
+      <c r="I2" s="253"/>
+      <c r="J2" s="475" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="248"/>
-      <c r="L2" s="248"/>
-      <c r="M2" s="248"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="473" t="s">
+      <c r="A3" s="471" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="473" t="s">
+      <c r="B3" s="253"/>
+      <c r="C3" s="471" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="248"/>
-      <c r="J3" s="473" t="s">
+      <c r="D3" s="253"/>
+      <c r="E3" s="253"/>
+      <c r="F3" s="253"/>
+      <c r="G3" s="253"/>
+      <c r="H3" s="253"/>
+      <c r="I3" s="253"/>
+      <c r="J3" s="471" t="s">
         <v>281</v>
       </c>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="M3" s="248"/>
-      <c r="N3" s="248"/>
+      <c r="K3" s="253"/>
+      <c r="L3" s="253"/>
+      <c r="M3" s="253"/>
+      <c r="N3" s="253"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="473" t="s">
+      <c r="A4" s="471" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="248"/>
-      <c r="C4" s="473" t="s">
+      <c r="B4" s="253"/>
+      <c r="C4" s="471" t="s">
         <v>283</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="471"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="M4" s="248"/>
-      <c r="N4" s="248"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
+      <c r="I4" s="253"/>
+      <c r="J4" s="473"/>
+      <c r="K4" s="253"/>
+      <c r="L4" s="253"/>
+      <c r="M4" s="253"/>
+      <c r="N4" s="253"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="473" t="s">
+      <c r="A5" s="471" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="248"/>
-      <c r="C5" s="473" t="s">
+      <c r="B5" s="253"/>
+      <c r="C5" s="471" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="471"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="M5" s="248"/>
-      <c r="N5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="473"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="M5" s="253"/>
+      <c r="N5" s="253"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="473" t="s">
+      <c r="A6" s="471" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="248"/>
-      <c r="C6" s="473" t="s">
+      <c r="B6" s="253"/>
+      <c r="C6" s="471" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
-      <c r="I6" s="248"/>
-      <c r="J6" s="473" t="s">
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="471" t="s">
         <v>286</v>
       </c>
-      <c r="K6" s="248"/>
-      <c r="L6" s="248"/>
-      <c r="M6" s="248"/>
-      <c r="N6" s="248"/>
+      <c r="K6" s="253"/>
+      <c r="L6" s="253"/>
+      <c r="M6" s="253"/>
+      <c r="N6" s="253"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
       <c r="A7" s="470" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="248"/>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="248"/>
-      <c r="N7" s="248"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="253"/>
+      <c r="N7" s="253"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -6377,120 +6365,138 @@
       <c r="A31" s="470" t="s">
         <v>288</v>
       </c>
-      <c r="B31" s="248"/>
-      <c r="C31" s="248"/>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
-      <c r="M31" s="248"/>
-      <c r="N31" s="248"/>
+      <c r="B31" s="253"/>
+      <c r="C31" s="253"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
+      <c r="I31" s="253"/>
+      <c r="J31" s="253"/>
+      <c r="K31" s="253"/>
+      <c r="L31" s="253"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="253"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="469" t="s">
+      <c r="A32" s="472" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="248"/>
-      <c r="C32" s="248"/>
-      <c r="D32" s="469" t="s">
+      <c r="B32" s="253"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="472" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="248"/>
-      <c r="F32" s="248"/>
-      <c r="G32" s="469" t="s">
+      <c r="E32" s="253"/>
+      <c r="F32" s="253"/>
+      <c r="G32" s="472" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="248"/>
-      <c r="I32" s="248"/>
-      <c r="J32" s="469" t="s">
+      <c r="H32" s="253"/>
+      <c r="I32" s="253"/>
+      <c r="J32" s="472" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="248"/>
-      <c r="L32" s="248"/>
-      <c r="M32" s="248"/>
+      <c r="K32" s="253"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="469" t="s">
+      <c r="A33" s="472" t="s">
         <v>290</v>
       </c>
-      <c r="B33" s="248"/>
-      <c r="C33" s="248"/>
-      <c r="D33" s="469" t="s">
+      <c r="B33" s="253"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="472" t="s">
         <v>291</v>
       </c>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="469" t="s">
+      <c r="E33" s="253"/>
+      <c r="F33" s="253"/>
+      <c r="G33" s="472" t="s">
         <v>292</v>
       </c>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="469" t="s">
+      <c r="H33" s="253"/>
+      <c r="I33" s="253"/>
+      <c r="J33" s="472" t="s">
         <v>293</v>
       </c>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
-      <c r="M33" s="248"/>
+      <c r="K33" s="253"/>
+      <c r="L33" s="253"/>
+      <c r="M33" s="253"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="470" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="248"/>
-      <c r="C34" s="248"/>
-      <c r="D34" s="248"/>
-      <c r="E34" s="248"/>
-      <c r="F34" s="248"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="248"/>
-      <c r="I34" s="248"/>
-      <c r="J34" s="248"/>
-      <c r="K34" s="248"/>
-      <c r="L34" s="248"/>
-      <c r="M34" s="248"/>
-      <c r="N34" s="248"/>
+      <c r="B34" s="253"/>
+      <c r="C34" s="253"/>
+      <c r="D34" s="253"/>
+      <c r="E34" s="253"/>
+      <c r="F34" s="253"/>
+      <c r="G34" s="253"/>
+      <c r="H34" s="253"/>
+      <c r="I34" s="253"/>
+      <c r="J34" s="253"/>
+      <c r="K34" s="253"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="253"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="469" t="s">
+      <c r="A35" s="472" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="248"/>
-      <c r="C35" s="248"/>
-      <c r="F35" s="469" t="s">
+      <c r="B35" s="253"/>
+      <c r="C35" s="253"/>
+      <c r="F35" s="472" t="s">
         <v>294</v>
       </c>
-      <c r="G35" s="248"/>
-      <c r="H35" s="248"/>
-      <c r="K35" s="469" t="s">
+      <c r="G35" s="253"/>
+      <c r="H35" s="253"/>
+      <c r="K35" s="472" t="s">
         <v>295</v>
       </c>
-      <c r="L35" s="248"/>
-      <c r="M35" s="248"/>
+      <c r="L35" s="253"/>
+      <c r="M35" s="253"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="469" t="s">
+      <c r="A36" s="472" t="s">
         <v>290</v>
       </c>
-      <c r="B36" s="248"/>
-      <c r="C36" s="248"/>
-      <c r="F36" s="469" t="s">
+      <c r="B36" s="253"/>
+      <c r="C36" s="253"/>
+      <c r="F36" s="472" t="s">
         <v>296</v>
       </c>
-      <c r="G36" s="248"/>
-      <c r="H36" s="248"/>
-      <c r="K36" s="469" t="s">
+      <c r="G36" s="253"/>
+      <c r="H36" s="253"/>
+      <c r="K36" s="472" t="s">
         <v>297</v>
       </c>
-      <c r="L36" s="248"/>
-      <c r="M36" s="248"/>
+      <c r="L36" s="253"/>
+      <c r="M36" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -6507,24 +6513,6 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6532,7 +6520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="D8:L47"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -6901,7 +6889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -7175,24 +7163,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:I19"/>
@@ -7202,6 +7172,24 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7209,7 +7197,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C2:T21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -7250,7 +7238,7 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="316" t="str">
+      <c r="C4" s="290" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -7279,22 +7267,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="314" t="s">
+      <c r="C5" s="306" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="263"/>
-      <c r="E5" s="314" t="s">
+      <c r="D5" s="259"/>
+      <c r="E5" s="306" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="263"/>
-      <c r="G5" s="314" t="s">
+      <c r="F5" s="259"/>
+      <c r="G5" s="306" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="263"/>
-      <c r="I5" s="307" t="s">
+      <c r="H5" s="259"/>
+      <c r="I5" s="301" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="263"/>
+      <c r="J5" s="259"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -7312,19 +7300,19 @@
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="251"/>
-      <c r="E6" s="313" t="s">
+      <c r="D6" s="249"/>
+      <c r="E6" s="296" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="251"/>
-      <c r="G6" s="315" t="s">
+      <c r="F6" s="249"/>
+      <c r="G6" s="294" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="251"/>
-      <c r="I6" s="291" t="s">
+      <c r="H6" s="249"/>
+      <c r="I6" s="308" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="251"/>
+      <c r="J6" s="249"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -7344,16 +7332,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="312" t="s">
+      <c r="C7" s="291" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="250"/>
-      <c r="E7" s="250"/>
-      <c r="F7" s="250"/>
-      <c r="G7" s="250"/>
-      <c r="H7" s="250"/>
-      <c r="I7" s="250"/>
-      <c r="J7" s="251"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="248"/>
+      <c r="I7" s="248"/>
+      <c r="J7" s="249"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -7370,22 +7358,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="292" t="s">
+      <c r="C8" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="251"/>
-      <c r="E8" s="292" t="s">
+      <c r="D8" s="249"/>
+      <c r="E8" s="295" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="251"/>
-      <c r="G8" s="292" t="s">
+      <c r="F8" s="249"/>
+      <c r="G8" s="295" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="251"/>
-      <c r="I8" s="311" t="s">
+      <c r="H8" s="249"/>
+      <c r="I8" s="305" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="251"/>
+      <c r="J8" s="249"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -7397,22 +7385,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="313">
+      <c r="C9" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="251"/>
-      <c r="E9" s="315" t="s">
+      <c r="D9" s="249"/>
+      <c r="E9" s="294" t="s">
         <v>303</v>
       </c>
-      <c r="F9" s="251"/>
+      <c r="F9" s="249"/>
       <c r="G9" s="293">
         <v>80</v>
       </c>
-      <c r="H9" s="251"/>
-      <c r="I9" s="291">
+      <c r="H9" s="249"/>
+      <c r="I9" s="308">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="251"/>
+      <c r="J9" s="249"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -7424,16 +7412,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="312" t="s">
+      <c r="C10" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="250"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="250"/>
-      <c r="G10" s="250"/>
-      <c r="H10" s="250"/>
-      <c r="I10" s="250"/>
-      <c r="J10" s="251"/>
+      <c r="D10" s="248"/>
+      <c r="E10" s="248"/>
+      <c r="F10" s="248"/>
+      <c r="G10" s="248"/>
+      <c r="H10" s="248"/>
+      <c r="I10" s="248"/>
+      <c r="J10" s="249"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -7445,156 +7433,187 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="292" t="s">
+      <c r="C11" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="292" t="s">
+      <c r="D11" s="249"/>
+      <c r="E11" s="295" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="251"/>
-      <c r="G11" s="292" t="s">
+      <c r="F11" s="249"/>
+      <c r="G11" s="295" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="251"/>
-      <c r="I11" s="311" t="s">
+      <c r="H11" s="249"/>
+      <c r="I11" s="305" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="251"/>
+      <c r="J11" s="249"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="313">
+      <c r="C12" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="251"/>
-      <c r="E12" s="313">
+      <c r="D12" s="249"/>
+      <c r="E12" s="296">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="251"/>
-      <c r="G12" s="315">
+      <c r="F12" s="249"/>
+      <c r="G12" s="294">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="251"/>
-      <c r="I12" s="318">
+      <c r="H12" s="249"/>
+      <c r="I12" s="297">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="251"/>
+      <c r="J12" s="249"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="292" t="s">
+      <c r="C13" s="295" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="251"/>
-      <c r="E13" s="315" t="s">
+      <c r="D13" s="249"/>
+      <c r="E13" s="294" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="251"/>
-      <c r="G13" s="292" t="s">
+      <c r="F13" s="249"/>
+      <c r="G13" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="251"/>
-      <c r="I13" s="291" t="s">
+      <c r="H13" s="249"/>
+      <c r="I13" s="308" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="251"/>
+      <c r="J13" s="249"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="308" t="s">
+      <c r="C16" s="302" t="s">
         <v>302</v>
       </c>
-      <c r="D16" s="309"/>
-      <c r="E16" s="309"/>
-      <c r="F16" s="309"/>
-      <c r="G16" s="309"/>
-      <c r="H16" s="309"/>
-      <c r="I16" s="310"/>
+      <c r="D16" s="303"/>
+      <c r="E16" s="303"/>
+      <c r="F16" s="303"/>
+      <c r="G16" s="303"/>
+      <c r="H16" s="303"/>
+      <c r="I16" s="304"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="312" t="s">
+      <c r="C17" s="291" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="250"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="312" t="s">
+      <c r="D17" s="248"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="291" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="251"/>
-      <c r="H17" s="312" t="s">
+      <c r="G17" s="249"/>
+      <c r="H17" s="291" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="251"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="299" t="s">
+      <c r="C18" s="314" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="300"/>
-      <c r="E18" s="301"/>
-      <c r="F18" s="303">
+      <c r="D18" s="315"/>
+      <c r="E18" s="316"/>
+      <c r="F18" s="318">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="304"/>
-      <c r="H18" s="305">
+      <c r="G18" s="319"/>
+      <c r="H18" s="320">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="306"/>
+      <c r="I18" s="321"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="302" t="s">
+      <c r="C19" s="317" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="250"/>
-      <c r="E19" s="251"/>
+      <c r="D19" s="248"/>
+      <c r="E19" s="249"/>
       <c r="F19" s="293">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="251"/>
-      <c r="H19" s="290">
+      <c r="G19" s="249"/>
+      <c r="H19" s="307">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="251"/>
+      <c r="I19" s="249"/>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="319" t="s">
+      <c r="C20" s="298" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="320"/>
-      <c r="E20" s="321"/>
-      <c r="F20" s="297">
+      <c r="D20" s="299"/>
+      <c r="E20" s="300"/>
+      <c r="F20" s="312">
         <f>AMOSTRAS!E13</f>
         <v>19.953199999999999</v>
       </c>
-      <c r="G20" s="298"/>
-      <c r="H20" s="295">
+      <c r="G20" s="313"/>
+      <c r="H20" s="310">
         <f>AMOSTRAS!F13</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="I20" s="296"/>
+      <c r="I20" s="311"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="294" t="s">
+      <c r="C21" s="309" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="250"/>
-      <c r="E21" s="251"/>
-      <c r="F21" s="317">
+      <c r="D21" s="248"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="292">
         <f>SUM(F18:G20)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G21" s="251"/>
-      <c r="H21" s="290">
+      <c r="G21" s="249"/>
+      <c r="H21" s="307">
         <f>SUM(H18:I20)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="251"/>
+      <c r="I21" s="249"/>
       <c r="J21" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="F21:G21"/>
@@ -7611,37 +7630,6 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7649,7 +7637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:N112"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -7669,38 +7657,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="381" t="s">
+      <c r="B3" s="353" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="382"/>
-      <c r="D3" s="382"/>
-      <c r="E3" s="382"/>
-      <c r="F3" s="382"/>
-      <c r="G3" s="382"/>
-      <c r="H3" s="382"/>
-      <c r="I3" s="382"/>
-      <c r="L3" s="322" t="s">
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="354"/>
+      <c r="F3" s="354"/>
+      <c r="G3" s="354"/>
+      <c r="H3" s="354"/>
+      <c r="I3" s="354"/>
+      <c r="L3" s="386" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="251"/>
+      <c r="M3" s="249"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="328" t="s">
+      <c r="B4" s="332" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="329"/>
-      <c r="D4" s="329"/>
-      <c r="E4" s="340" t="s">
+      <c r="C4" s="333"/>
+      <c r="D4" s="333"/>
+      <c r="E4" s="388" t="s">
         <v>298</v>
       </c>
       <c r="F4" s="284"/>
       <c r="G4" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="383" t="s">
+      <c r="H4" s="355" t="s">
         <v>299</v>
       </c>
-      <c r="I4" s="253"/>
+      <c r="I4" s="263"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>88</v>
@@ -7711,22 +7699,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="331" t="s">
+      <c r="B5" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="284"/>
       <c r="D5" s="284"/>
-      <c r="E5" s="323" t="s">
+      <c r="E5" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F5" s="284"/>
       <c r="G5" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="364" t="s">
+      <c r="H5" s="374" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="253"/>
+      <c r="I5" s="263"/>
       <c r="L5" s="153" t="s">
         <v>92</v>
       </c>
@@ -7736,57 +7724,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="331" t="s">
+      <c r="B6" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C6" s="284"/>
       <c r="D6" s="284"/>
-      <c r="E6" s="366">
+      <c r="E6" s="375">
         <v>52.034300000000002</v>
       </c>
       <c r="F6" s="284"/>
       <c r="G6" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H6" s="385" t="s">
+      <c r="H6" s="360" t="s">
         <v>300</v>
       </c>
-      <c r="I6" s="253"/>
+      <c r="I6" s="263"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="325" t="s">
+      <c r="C7" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="284"/>
-      <c r="E7" s="372" t="s">
+      <c r="E7" s="363" t="s">
         <v>136</v>
       </c>
       <c r="F7" s="284"/>
       <c r="G7" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="344">
+      <c r="H7" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I7" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I7" s="263"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="325" t="s">
+      <c r="C8" s="346" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="284"/>
-      <c r="E8" s="363">
+      <c r="E8" s="373">
         <v>11173</v>
       </c>
       <c r="F8" s="284"/>
       <c r="G8" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="355"/>
-      <c r="I8" s="253"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="263"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -7794,7 +7782,7 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="342" t="s">
+      <c r="B9" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C9" s="284"/>
@@ -7803,7 +7791,7 @@
       <c r="F9" s="284"/>
       <c r="G9" s="284"/>
       <c r="H9" s="284"/>
-      <c r="I9" s="253"/>
+      <c r="I9" s="263"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -7811,7 +7799,7 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="324" t="s">
+      <c r="B10" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="284"/>
@@ -7834,11 +7822,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="351" t="s">
+      <c r="B11" s="383" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="352"/>
-      <c r="D11" s="352"/>
+      <c r="C11" s="384"/>
+      <c r="D11" s="384"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -7846,10 +7834,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="353">
+      <c r="G11" s="385">
         <v>1</v>
       </c>
-      <c r="H11" s="353"/>
+      <c r="H11" s="385"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -7858,7 +7846,7 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="362" t="s">
+      <c r="B12" s="372" t="s">
         <v>117</v>
       </c>
       <c r="C12" s="284"/>
@@ -7871,7 +7859,7 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="327">
+      <c r="G12" s="326">
         <v>0.8</v>
       </c>
       <c r="H12" s="284"/>
@@ -7883,7 +7871,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="373" t="s">
+      <c r="B13" s="364" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="284"/>
@@ -7896,7 +7884,7 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="327">
+      <c r="G13" s="326">
         <v>0.6</v>
       </c>
       <c r="H13" s="284"/>
@@ -7912,11 +7900,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="354" t="s">
+      <c r="B14" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="259"/>
-      <c r="D14" s="259"/>
+      <c r="C14" s="251"/>
+      <c r="D14" s="251"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -7925,11 +7913,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="350">
+      <c r="G14" s="322">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="259"/>
+      <c r="H14" s="251"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -7953,7 +7941,7 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="348" t="s">
+      <c r="B16" s="340" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="284"/>
@@ -7966,52 +7954,52 @@
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="328" t="s">
+      <c r="B17" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="329"/>
-      <c r="D17" s="329"/>
-      <c r="E17" s="326" t="s">
+      <c r="C17" s="333"/>
+      <c r="D17" s="333"/>
+      <c r="E17" s="324" t="s">
         <v>110</v>
       </c>
       <c r="F17" s="284"/>
       <c r="G17" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="338" t="s">
+      <c r="H17" s="356" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="253"/>
+      <c r="I17" s="263"/>
       <c r="K17" s="203" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="331" t="s">
+      <c r="B18" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C18" s="284"/>
       <c r="D18" s="284"/>
-      <c r="E18" s="323" t="s">
+      <c r="E18" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="284"/>
       <c r="G18" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="336" t="s">
+      <c r="H18" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="253"/>
+      <c r="I18" s="263"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="331" t="s">
+      <c r="B19" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C19" s="284"/>
       <c r="D19" s="284"/>
-      <c r="E19" s="365">
+      <c r="E19" s="368">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
@@ -8019,18 +8007,18 @@
       <c r="G19" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="357" t="s">
+      <c r="H19" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I19" s="253"/>
+      <c r="I19" s="263"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="325" t="s">
+      <c r="C20" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D20" s="284"/>
-      <c r="E20" s="371">
+      <c r="E20" s="352">
         <f>180000000</f>
         <v>180000000</v>
       </c>
@@ -8038,11 +8026,11 @@
       <c r="G20" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="360">
+      <c r="H20" s="328">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="253"/>
+      <c r="I20" s="263"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -8050,42 +8038,42 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="325" t="s">
+      <c r="C21" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D21" s="284"/>
-      <c r="E21" s="332" t="s">
+      <c r="E21" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F21" s="284"/>
       <c r="G21" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="344">
+      <c r="H21" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I21" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I21" s="263"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="325" t="s">
+      <c r="C22" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="284"/>
-      <c r="E22" s="326" t="s">
+      <c r="E22" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F22" s="284"/>
       <c r="G22" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H22" s="368"/>
-      <c r="I22" s="253"/>
+      <c r="H22" s="365"/>
+      <c r="I22" s="263"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="342" t="s">
+      <c r="B23" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="284"/>
@@ -8094,10 +8082,10 @@
       <c r="F23" s="284"/>
       <c r="G23" s="284"/>
       <c r="H23" s="284"/>
-      <c r="I23" s="253"/>
+      <c r="I23" s="263"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="324" t="s">
+      <c r="B24" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C24" s="284"/>
@@ -8115,7 +8103,7 @@
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="335" t="s">
+      <c r="B25" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C25" s="284"/>
@@ -8128,7 +8116,7 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="341">
+      <c r="G25" s="335">
         <v>1</v>
       </c>
       <c r="H25" s="284"/>
@@ -8148,14 +8136,14 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="341">
+      <c r="G26" s="335">
         <v>0.8</v>
       </c>
       <c r="H26" s="284"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="374" t="s">
+      <c r="B27" s="361" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="284"/>
@@ -8168,18 +8156,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="341">
+      <c r="G27" s="335">
         <v>0.6</v>
       </c>
       <c r="H27" s="284"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="354" t="s">
+      <c r="B28" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="259"/>
-      <c r="D28" s="259"/>
+      <c r="C28" s="251"/>
+      <c r="D28" s="251"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -8188,11 +8176,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="350">
+      <c r="G28" s="322">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="259"/>
+      <c r="H28" s="251"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -8206,7 +8194,7 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="348" t="s">
+      <c r="B30" s="340" t="s">
         <v>118</v>
       </c>
       <c r="C30" s="284"/>
@@ -8218,83 +8206,83 @@
       <c r="I30" s="284"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="328" t="s">
+      <c r="B31" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="329"/>
-      <c r="D31" s="329"/>
-      <c r="E31" s="326" t="s">
+      <c r="C31" s="333"/>
+      <c r="D31" s="333"/>
+      <c r="E31" s="324" t="s">
         <v>119</v>
       </c>
       <c r="F31" s="284"/>
       <c r="G31" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="338" t="s">
+      <c r="H31" s="356" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="253"/>
+      <c r="I31" s="263"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C32" s="284"/>
       <c r="D32" s="284"/>
-      <c r="E32" s="323" t="s">
+      <c r="E32" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F32" s="284"/>
       <c r="G32" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="336" t="s">
+      <c r="H32" s="359" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="253"/>
+      <c r="I32" s="263"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="331" t="s">
+      <c r="B33" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="284"/>
       <c r="D33" s="284"/>
-      <c r="E33" s="377">
+      <c r="E33" s="357">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="284"/>
       <c r="G33" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="336" t="s">
+      <c r="H33" s="359" t="s">
         <v>95</v>
       </c>
-      <c r="I33" s="253"/>
+      <c r="I33" s="263"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="325" t="s">
+      <c r="C34" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="284"/>
-      <c r="E34" s="371">
+      <c r="E34" s="352">
         <v>16900000</v>
       </c>
       <c r="F34" s="284"/>
       <c r="G34" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="360">
+      <c r="H34" s="328">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="253"/>
+      <c r="I34" s="263"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -8302,41 +8290,41 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="325" t="s">
+      <c r="C35" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D35" s="284"/>
-      <c r="E35" s="332" t="s">
+      <c r="E35" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F35" s="284"/>
       <c r="G35" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H35" s="344">
+      <c r="H35" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I35" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I35" s="263"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="325" t="s">
+      <c r="C36" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="284"/>
-      <c r="E36" s="326" t="s">
+      <c r="E36" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F36" s="284"/>
       <c r="G36" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="368"/>
-      <c r="I36" s="253"/>
+      <c r="H36" s="365"/>
+      <c r="I36" s="263"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="342" t="s">
+      <c r="B37" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C37" s="284"/>
@@ -8345,11 +8333,11 @@
       <c r="F37" s="284"/>
       <c r="G37" s="284"/>
       <c r="H37" s="284"/>
-      <c r="I37" s="253"/>
+      <c r="I37" s="263"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="324" t="s">
+      <c r="B38" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C38" s="284"/>
@@ -8367,7 +8355,7 @@
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="335" t="s">
+      <c r="B39" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C39" s="284"/>
@@ -8379,7 +8367,7 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="341">
+      <c r="G39" s="335">
         <v>1</v>
       </c>
       <c r="H39" s="284"/>
@@ -8399,14 +8387,14 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="341">
+      <c r="G40" s="335">
         <v>0.8</v>
       </c>
       <c r="H40" s="284"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="374" t="s">
+      <c r="B41" s="361" t="s">
         <v>107</v>
       </c>
       <c r="C41" s="284"/>
@@ -8419,18 +8407,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="341">
+      <c r="G41" s="335">
         <v>0.6</v>
       </c>
       <c r="H41" s="284"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="354" t="s">
+      <c r="B42" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="259"/>
-      <c r="D42" s="259"/>
+      <c r="C42" s="251"/>
+      <c r="D42" s="251"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -8439,11 +8427,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="350">
+      <c r="G42" s="322">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="259"/>
+      <c r="H42" s="251"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -8457,7 +8445,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="384" t="s">
+      <c r="B44" s="358" t="s">
         <v>122</v>
       </c>
       <c r="C44" s="284"/>
@@ -8469,81 +8457,81 @@
       <c r="I44" s="284"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="328" t="s">
+      <c r="B45" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="323" t="s">
+      <c r="C45" s="333"/>
+      <c r="D45" s="333"/>
+      <c r="E45" s="347" t="s">
         <v>119</v>
       </c>
       <c r="F45" s="284"/>
       <c r="G45" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H45" s="338" t="s">
+      <c r="H45" s="356" t="s">
         <v>120</v>
       </c>
-      <c r="I45" s="253"/>
+      <c r="I45" s="263"/>
       <c r="K45" s="203" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="331" t="s">
+      <c r="B46" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="284"/>
       <c r="D46" s="284"/>
-      <c r="E46" s="323" t="s">
+      <c r="E46" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F46" s="284"/>
       <c r="G46" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="336" t="s">
+      <c r="H46" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="253"/>
+      <c r="I46" s="263"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="331" t="s">
+      <c r="B47" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C47" s="284"/>
       <c r="D47" s="284"/>
-      <c r="E47" s="365">
+      <c r="E47" s="368">
         <v>430.76</v>
       </c>
       <c r="F47" s="284"/>
       <c r="G47" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H47" s="357" t="s">
+      <c r="H47" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I47" s="253"/>
+      <c r="I47" s="263"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="325" t="s">
+      <c r="C48" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D48" s="284"/>
-      <c r="E48" s="347">
+      <c r="E48" s="323">
         <v>7120000</v>
       </c>
       <c r="F48" s="284"/>
       <c r="G48" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H48" s="361">
+      <c r="H48" s="343">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="253"/>
+      <c r="I48" s="263"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -8552,42 +8540,42 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="325" t="s">
+      <c r="C49" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D49" s="284"/>
-      <c r="E49" s="332" t="s">
+      <c r="E49" s="370" t="s">
         <v>116</v>
       </c>
       <c r="F49" s="284"/>
       <c r="G49" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H49" s="344">
+      <c r="H49" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I49" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I49" s="263"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="325" t="s">
+      <c r="C50" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="284"/>
-      <c r="E50" s="326" t="s">
+      <c r="E50" s="324" t="s">
         <v>124</v>
       </c>
       <c r="F50" s="284"/>
       <c r="G50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="355"/>
-      <c r="I50" s="253"/>
+      <c r="H50" s="348"/>
+      <c r="I50" s="263"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="342" t="s">
+      <c r="B51" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C51" s="284"/>
@@ -8596,10 +8584,10 @@
       <c r="F51" s="284"/>
       <c r="G51" s="284"/>
       <c r="H51" s="284"/>
-      <c r="I51" s="253"/>
+      <c r="I51" s="263"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="324" t="s">
+      <c r="B52" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C52" s="284"/>
@@ -8617,7 +8605,7 @@
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="335" t="s">
+      <c r="B53" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="284"/>
@@ -8629,7 +8617,7 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="327">
+      <c r="G53" s="326">
         <v>1</v>
       </c>
       <c r="H53" s="284"/>
@@ -8649,7 +8637,7 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="327">
+      <c r="G54" s="326">
         <v>0.8</v>
       </c>
       <c r="H54" s="284"/>
@@ -8669,18 +8657,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="327">
+      <c r="G55" s="326">
         <v>0.6</v>
       </c>
       <c r="H55" s="284"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="354" t="s">
+      <c r="B56" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="259"/>
-      <c r="D56" s="259"/>
+      <c r="C56" s="251"/>
+      <c r="D56" s="251"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -8689,11 +8677,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="350">
+      <c r="G56" s="322">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="259"/>
+      <c r="H56" s="251"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -8707,7 +8695,7 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="340" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="284"/>
@@ -8720,80 +8708,80 @@
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="328" t="s">
+      <c r="B59" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="329"/>
-      <c r="D59" s="329"/>
-      <c r="E59" s="323" t="s">
+      <c r="C59" s="333"/>
+      <c r="D59" s="333"/>
+      <c r="E59" s="347" t="s">
         <v>126</v>
       </c>
       <c r="F59" s="284"/>
       <c r="G59" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="367" t="s">
+      <c r="H59" s="369" t="s">
         <v>127</v>
       </c>
-      <c r="I59" s="253"/>
+      <c r="I59" s="263"/>
       <c r="K59" s="203" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C60" s="284"/>
       <c r="D60" s="284"/>
-      <c r="E60" s="323" t="s">
+      <c r="E60" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F60" s="284"/>
       <c r="G60" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="336" t="s">
+      <c r="H60" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="253"/>
+      <c r="I60" s="263"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="331" t="s">
+      <c r="B61" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C61" s="284"/>
       <c r="D61" s="284"/>
-      <c r="E61" s="369">
+      <c r="E61" s="338">
         <v>626</v>
       </c>
       <c r="F61" s="284"/>
       <c r="G61" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H61" s="336" t="s">
+      <c r="H61" s="359" t="s">
         <v>129</v>
       </c>
-      <c r="I61" s="253"/>
+      <c r="I61" s="263"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="325" t="s">
+      <c r="C62" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="284"/>
-      <c r="E62" s="378">
+      <c r="E62" s="362">
         <v>10500000</v>
       </c>
       <c r="F62" s="284"/>
       <c r="G62" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="330">
+      <c r="H62" s="339">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="253"/>
+      <c r="I62" s="263"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -8802,42 +8790,42 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="325" t="s">
+      <c r="C63" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D63" s="284"/>
-      <c r="E63" s="375" t="s">
+      <c r="E63" s="366" t="s">
         <v>116</v>
       </c>
       <c r="F63" s="284"/>
       <c r="G63" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="344">
+      <c r="H63" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I63" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I63" s="263"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="325" t="s">
+      <c r="C64" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D64" s="284"/>
-      <c r="E64" s="326" t="s">
+      <c r="E64" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F64" s="284"/>
       <c r="G64" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H64" s="355"/>
-      <c r="I64" s="253"/>
+      <c r="H64" s="348"/>
+      <c r="I64" s="263"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="342" t="s">
+      <c r="B65" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C65" s="284"/>
@@ -8846,10 +8834,10 @@
       <c r="F65" s="284"/>
       <c r="G65" s="284"/>
       <c r="H65" s="284"/>
-      <c r="I65" s="253"/>
+      <c r="I65" s="263"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="324" t="s">
+      <c r="B66" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C66" s="284"/>
@@ -8879,7 +8867,7 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="327">
+      <c r="G67" s="326">
         <v>1</v>
       </c>
       <c r="H67" s="284"/>
@@ -8898,14 +8886,14 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="327">
+      <c r="G68" s="326">
         <v>0.9</v>
       </c>
       <c r="H68" s="284"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="376" t="s">
+      <c r="B69" s="367" t="s">
         <v>107</v>
       </c>
       <c r="C69" s="284"/>
@@ -8918,18 +8906,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="327">
+      <c r="G69" s="326">
         <v>0.6</v>
       </c>
       <c r="H69" s="284"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="354" t="s">
+      <c r="B70" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="259"/>
-      <c r="D70" s="259"/>
+      <c r="C70" s="251"/>
+      <c r="D70" s="251"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -8938,11 +8926,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="350">
+      <c r="G70" s="322">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="259"/>
+      <c r="H70" s="251"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -8956,7 +8944,7 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="348" t="s">
+      <c r="B72" s="340" t="s">
         <v>131</v>
       </c>
       <c r="C72" s="284"/>
@@ -8968,51 +8956,51 @@
       <c r="I72" s="284"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="328" t="s">
+      <c r="B73" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C73" s="329"/>
-      <c r="D73" s="329"/>
-      <c r="E73" s="326" t="s">
+      <c r="C73" s="333"/>
+      <c r="D73" s="333"/>
+      <c r="E73" s="324" t="s">
         <v>132</v>
       </c>
       <c r="F73" s="284"/>
       <c r="G73" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H73" s="338" t="s">
+      <c r="H73" s="356" t="s">
         <v>133</v>
       </c>
-      <c r="I73" s="253"/>
+      <c r="I73" s="263"/>
       <c r="K73" s="203" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="331" t="s">
+      <c r="B74" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="284"/>
       <c r="D74" s="284"/>
-      <c r="E74" s="326" t="s">
+      <c r="E74" s="324" t="s">
         <v>135</v>
       </c>
       <c r="F74" s="284"/>
       <c r="G74" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="336" t="s">
+      <c r="H74" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="253"/>
+      <c r="I74" s="263"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="331" t="s">
+      <c r="B75" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C75" s="284"/>
       <c r="D75" s="284"/>
-      <c r="E75" s="388">
+      <c r="E75" s="341">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -9020,48 +9008,48 @@
       <c r="G75" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H75" s="357" t="s">
+      <c r="H75" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I75" s="253"/>
+      <c r="I75" s="263"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="325" t="s">
+      <c r="C76" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D76" s="284"/>
-      <c r="E76" s="347">
+      <c r="E76" s="323">
         <v>60000000</v>
       </c>
       <c r="F76" s="284"/>
       <c r="G76" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H76" s="361">
+      <c r="H76" s="343">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="253"/>
+      <c r="I76" s="263"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="325" t="s">
+      <c r="C77" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D77" s="284"/>
-      <c r="E77" s="359" t="s">
+      <c r="E77" s="379" t="s">
         <v>116</v>
       </c>
       <c r="F77" s="284"/>
       <c r="G77" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="344">
+      <c r="H77" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I77" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I77" s="263"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -9069,22 +9057,22 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="325" t="s">
+      <c r="C78" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D78" s="284"/>
-      <c r="E78" s="326" t="s">
+      <c r="E78" s="324" t="s">
         <v>136</v>
       </c>
       <c r="F78" s="284"/>
       <c r="G78" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H78" s="355"/>
-      <c r="I78" s="253"/>
+      <c r="H78" s="348"/>
+      <c r="I78" s="263"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="342" t="s">
+      <c r="B79" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C79" s="284"/>
@@ -9093,11 +9081,11 @@
       <c r="F79" s="284"/>
       <c r="G79" s="284"/>
       <c r="H79" s="284"/>
-      <c r="I79" s="253"/>
+      <c r="I79" s="263"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="324" t="s">
+      <c r="B80" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C80" s="284"/>
@@ -9115,7 +9103,7 @@
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="334" t="s">
+      <c r="B81" s="344" t="s">
         <v>130</v>
       </c>
       <c r="C81" s="284"/>
@@ -9128,14 +9116,14 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="327">
+      <c r="G81" s="326">
         <v>0.9</v>
       </c>
       <c r="H81" s="284"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="334" t="s">
+      <c r="B82" s="344" t="s">
         <v>117</v>
       </c>
       <c r="C82" s="284"/>
@@ -9148,7 +9136,7 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="327">
+      <c r="G82" s="326">
         <v>0.8</v>
       </c>
       <c r="H82" s="284"/>
@@ -9168,18 +9156,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="327">
+      <c r="G83" s="326">
         <v>0.6</v>
       </c>
       <c r="H83" s="284"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="354" t="s">
+      <c r="B84" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="259"/>
-      <c r="D84" s="259"/>
+      <c r="C84" s="251"/>
+      <c r="D84" s="251"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -9188,11 +9176,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="350">
+      <c r="G84" s="322">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="259"/>
+      <c r="H84" s="251"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -9206,7 +9194,7 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="348" t="s">
+      <c r="B86" s="340" t="s">
         <v>137</v>
       </c>
       <c r="C86" s="284"/>
@@ -9219,52 +9207,52 @@
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="328" t="s">
+      <c r="B87" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="329"/>
-      <c r="D87" s="329"/>
-      <c r="E87" s="323" t="s">
+      <c r="C87" s="333"/>
+      <c r="D87" s="333"/>
+      <c r="E87" s="347" t="s">
         <v>119</v>
       </c>
       <c r="F87" s="284"/>
       <c r="G87" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H87" s="370" t="str">
+      <c r="H87" s="371" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="253"/>
+      <c r="I87" s="263"/>
       <c r="K87" s="203" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="331" t="s">
+      <c r="B88" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C88" s="284"/>
       <c r="D88" s="284"/>
-      <c r="E88" s="323" t="s">
+      <c r="E88" s="347" t="s">
         <v>90</v>
       </c>
       <c r="F88" s="284"/>
       <c r="G88" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="336" t="s">
+      <c r="H88" s="359" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="253"/>
+      <c r="I88" s="263"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="331" t="s">
+      <c r="B89" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="284"/>
       <c r="D89" s="284"/>
-      <c r="E89" s="377">
+      <c r="E89" s="357">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -9272,29 +9260,29 @@
       <c r="G89" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H89" s="357" t="s">
+      <c r="H89" s="327" t="s">
         <v>95</v>
       </c>
-      <c r="I89" s="253"/>
+      <c r="I89" s="263"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="325" t="s">
+      <c r="C90" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D90" s="284"/>
-      <c r="E90" s="358">
+      <c r="E90" s="349">
         <v>43980000</v>
       </c>
       <c r="F90" s="284"/>
       <c r="G90" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H90" s="330">
+      <c r="H90" s="339">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="253"/>
+      <c r="I90" s="263"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -9302,41 +9290,41 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="325" t="s">
+      <c r="C91" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D91" s="284"/>
-      <c r="E91" s="333" t="s">
+      <c r="E91" s="377" t="s">
         <v>116</v>
       </c>
       <c r="F91" s="284"/>
       <c r="G91" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H91" s="344">
+      <c r="H91" s="329">
         <f ca="1">TODAY()</f>
-        <v>45842</v>
-      </c>
-      <c r="I91" s="253"/>
+        <v>45845</v>
+      </c>
+      <c r="I91" s="263"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="325" t="s">
+      <c r="C92" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D92" s="284"/>
-      <c r="E92" s="326" t="s">
+      <c r="E92" s="324" t="s">
         <v>97</v>
       </c>
       <c r="F92" s="284"/>
       <c r="G92" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H92" s="355"/>
-      <c r="I92" s="253"/>
+      <c r="H92" s="348"/>
+      <c r="I92" s="263"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="342" t="s">
+      <c r="B93" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C93" s="284"/>
@@ -9345,10 +9333,10 @@
       <c r="F93" s="284"/>
       <c r="G93" s="284"/>
       <c r="H93" s="284"/>
-      <c r="I93" s="253"/>
+      <c r="I93" s="263"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="324" t="s">
+      <c r="B94" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C94" s="284"/>
@@ -9366,7 +9354,7 @@
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="335" t="s">
+      <c r="B95" s="334" t="s">
         <v>106</v>
       </c>
       <c r="C95" s="284"/>
@@ -9378,7 +9366,7 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="345">
+      <c r="G95" s="381">
         <v>1</v>
       </c>
       <c r="H95" s="284"/>
@@ -9398,14 +9386,14 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="345">
+      <c r="G96" s="381">
         <v>0.8</v>
       </c>
       <c r="H96" s="284"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="346" t="s">
+      <c r="B97" s="378" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="284"/>
@@ -9418,7 +9406,7 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="327">
+      <c r="G97" s="326">
         <v>0.6</v>
       </c>
       <c r="H97" s="284"/>
@@ -9427,11 +9415,11 @@
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="354" t="s">
+      <c r="B98" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C98" s="259"/>
-      <c r="D98" s="259"/>
+      <c r="C98" s="251"/>
+      <c r="D98" s="251"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -9440,11 +9428,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="350">
+      <c r="G98" s="322">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="259"/>
+      <c r="H98" s="251"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -9465,7 +9453,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="386"/>
+      <c r="B100" s="342"/>
       <c r="C100" s="284"/>
       <c r="D100" s="284"/>
       <c r="E100" s="284"/>
@@ -9477,7 +9465,7 @@
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="340" t="s">
         <v>139</v>
       </c>
       <c r="C101" s="284"/>
@@ -9491,93 +9479,93 @@
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="328" t="s">
+      <c r="B102" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="C102" s="329"/>
-      <c r="D102" s="329"/>
-      <c r="E102" s="339"/>
+      <c r="C102" s="333"/>
+      <c r="D102" s="333"/>
+      <c r="E102" s="387"/>
       <c r="F102" s="284"/>
       <c r="G102" s="163" t="s">
         <v>87</v>
       </c>
-      <c r="H102" s="387"/>
-      <c r="I102" s="253"/>
+      <c r="H102" s="325"/>
+      <c r="I102" s="263"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="331" t="s">
+      <c r="B103" s="330" t="s">
         <v>89</v>
       </c>
       <c r="C103" s="284"/>
       <c r="D103" s="284"/>
-      <c r="E103" s="349"/>
+      <c r="E103" s="382"/>
       <c r="F103" s="284"/>
       <c r="G103" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="356"/>
-      <c r="I103" s="253"/>
+      <c r="H103" s="376"/>
+      <c r="I103" s="263"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="331" t="s">
+      <c r="B104" s="330" t="s">
         <v>93</v>
       </c>
       <c r="C104" s="284"/>
       <c r="D104" s="284"/>
-      <c r="E104" s="369"/>
+      <c r="E104" s="338"/>
       <c r="F104" s="284"/>
       <c r="G104" s="163" t="s">
         <v>94</v>
       </c>
-      <c r="H104" s="380"/>
-      <c r="I104" s="253"/>
+      <c r="H104" s="351"/>
+      <c r="I104" s="263"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="325" t="s">
+      <c r="C105" s="346" t="s">
         <v>113</v>
       </c>
       <c r="D105" s="284"/>
-      <c r="E105" s="358"/>
+      <c r="E105" s="349"/>
       <c r="F105" s="284"/>
       <c r="G105" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="H105" s="330"/>
-      <c r="I105" s="253"/>
+      <c r="H105" s="339"/>
+      <c r="I105" s="263"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="325" t="s">
+      <c r="C106" s="346" t="s">
         <v>115</v>
       </c>
       <c r="D106" s="284"/>
-      <c r="E106" s="333"/>
+      <c r="E106" s="377"/>
       <c r="F106" s="284"/>
       <c r="G106" s="163" t="s">
         <v>98</v>
       </c>
-      <c r="H106" s="343"/>
-      <c r="I106" s="253"/>
+      <c r="H106" s="380"/>
+      <c r="I106" s="263"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="325" t="s">
+      <c r="C107" s="346" t="s">
         <v>96</v>
       </c>
       <c r="D107" s="284"/>
-      <c r="E107" s="379"/>
+      <c r="E107" s="350"/>
       <c r="F107" s="284"/>
       <c r="G107" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="H107" s="355"/>
-      <c r="I107" s="253"/>
+      <c r="H107" s="348"/>
+      <c r="I107" s="263"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="342" t="s">
+      <c r="B108" s="336" t="s">
         <v>101</v>
       </c>
       <c r="C108" s="284"/>
@@ -9586,10 +9574,10 @@
       <c r="F108" s="284"/>
       <c r="G108" s="284"/>
       <c r="H108" s="284"/>
-      <c r="I108" s="253"/>
+      <c r="I108" s="263"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="324" t="s">
+      <c r="B109" s="345" t="s">
         <v>102</v>
       </c>
       <c r="C109" s="284"/>
@@ -9607,35 +9595,35 @@
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="346" t="s">
+      <c r="B110" s="378" t="s">
         <v>106</v>
       </c>
       <c r="C110" s="284"/>
       <c r="D110" s="284"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="327"/>
+      <c r="G110" s="326"/>
       <c r="H110" s="284"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="378" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="284"/>
       <c r="D111" s="284"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="327"/>
+      <c r="G111" s="326"/>
       <c r="H111" s="284"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="354" t="s">
+      <c r="B112" s="331" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="259"/>
-      <c r="D112" s="259"/>
+      <c r="C112" s="251"/>
+      <c r="D112" s="251"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -9644,15 +9632,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="350">
+      <c r="G112" s="322">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="259"/>
+      <c r="H112" s="251"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E22:F22"/>
@@ -9677,211 +9870,6 @@
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="H89:I89"/>
     <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="G39:H39"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9889,7 +9877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:M10"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
@@ -10204,7 +10192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10233,7 +10221,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="396"/>
+      <c r="E1" s="390"/>
       <c r="F1" s="391"/>
       <c r="G1" s="391"/>
       <c r="H1" s="391"/>
@@ -10793,8 +10781,8 @@
       <c r="A12" s="389" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="251"/>
-      <c r="C12" s="397" t="s">
+      <c r="B12" s="249"/>
+      <c r="C12" s="392" t="s">
         <v>174</v>
       </c>
       <c r="D12" s="391"/>
@@ -10822,8 +10810,8 @@
       <c r="A13" s="389" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="251"/>
-      <c r="C13" s="397" t="s">
+      <c r="B13" s="249"/>
+      <c r="C13" s="392" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="391"/>
@@ -10852,8 +10840,8 @@
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="251"/>
-      <c r="C14" s="397" t="s">
+      <c r="B14" s="249"/>
+      <c r="C14" s="392" t="s">
         <v>179</v>
       </c>
       <c r="D14" s="391"/>
@@ -10881,8 +10869,8 @@
       <c r="A15" s="389" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="251"/>
-      <c r="C15" s="397" t="s">
+      <c r="B15" s="249"/>
+      <c r="C15" s="392" t="s">
         <v>181</v>
       </c>
       <c r="D15" s="391"/>
@@ -10910,8 +10898,8 @@
       <c r="A16" s="389" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="251"/>
-      <c r="C16" s="390" t="s">
+      <c r="B16" s="249"/>
+      <c r="C16" s="394" t="s">
         <v>183</v>
       </c>
       <c r="D16" s="391"/>
@@ -10934,8 +10922,8 @@
       <c r="A17" s="389" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="251"/>
-      <c r="C17" s="390" t="s">
+      <c r="B17" s="249"/>
+      <c r="C17" s="394" t="s">
         <v>184</v>
       </c>
       <c r="D17" s="391"/>
@@ -10967,8 +10955,8 @@
       <c r="A18" s="389" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="251"/>
-      <c r="C18" s="390" t="s">
+      <c r="B18" s="249"/>
+      <c r="C18" s="394" t="s">
         <v>187</v>
       </c>
       <c r="D18" s="391"/>
@@ -10995,8 +10983,8 @@
       <c r="A19" s="389" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="251"/>
-      <c r="C19" s="390" t="s">
+      <c r="B19" s="249"/>
+      <c r="C19" s="394" t="s">
         <v>189</v>
       </c>
       <c r="D19" s="391"/>
@@ -11024,8 +11012,8 @@
       <c r="A20" s="389" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="251"/>
-      <c r="C20" s="390" t="s">
+      <c r="B20" s="249"/>
+      <c r="C20" s="394" t="s">
         <v>191</v>
       </c>
       <c r="D20" s="391"/>
@@ -11053,8 +11041,8 @@
       <c r="A21" s="389" t="s">
         <v>186</v>
       </c>
-      <c r="B21" s="251"/>
-      <c r="C21" s="390" t="s">
+      <c r="B21" s="249"/>
+      <c r="C21" s="394" t="s">
         <v>193</v>
       </c>
       <c r="D21" s="391"/>
@@ -11082,8 +11070,8 @@
       <c r="A22" s="389" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="251"/>
-      <c r="C22" s="398" t="s">
+      <c r="B22" s="249"/>
+      <c r="C22" s="393" t="s">
         <v>195</v>
       </c>
       <c r="D22" s="391"/>
@@ -11097,7 +11085,7 @@
       <c r="L22" s="391"/>
       <c r="M22" s="391"/>
       <c r="N22" s="391"/>
-      <c r="O22" s="253"/>
+      <c r="O22" s="263"/>
       <c r="P22" s="147" t="s">
         <v>196</v>
       </c>
@@ -11111,8 +11099,8 @@
       <c r="A23" s="389" t="s">
         <v>194</v>
       </c>
-      <c r="B23" s="251"/>
-      <c r="C23" s="390" t="s">
+      <c r="B23" s="249"/>
+      <c r="C23" s="394" t="s">
         <v>197</v>
       </c>
       <c r="D23" s="391"/>
@@ -11140,8 +11128,8 @@
       <c r="A24" s="389" t="s">
         <v>196</v>
       </c>
-      <c r="B24" s="251"/>
-      <c r="C24" s="390" t="s">
+      <c r="B24" s="249"/>
+      <c r="C24" s="394" t="s">
         <v>199</v>
       </c>
       <c r="D24" s="391"/>
@@ -11169,8 +11157,8 @@
       <c r="A25" s="389" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="251"/>
-      <c r="C25" s="390" t="s">
+      <c r="B25" s="249"/>
+      <c r="C25" s="394" t="s">
         <v>201</v>
       </c>
       <c r="D25" s="391"/>
@@ -11190,21 +11178,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="392" t="s">
+      <c r="A26" s="395" t="s">
         <v>202</v>
       </c>
-      <c r="B26" s="393"/>
-      <c r="C26" s="394" t="s">
+      <c r="B26" s="396"/>
+      <c r="C26" s="397" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="395"/>
-      <c r="E26" s="395"/>
-      <c r="F26" s="395"/>
-      <c r="G26" s="395"/>
-      <c r="H26" s="395"/>
-      <c r="I26" s="395"/>
-      <c r="J26" s="395"/>
-      <c r="K26" s="395"/>
+      <c r="D26" s="398"/>
+      <c r="E26" s="398"/>
+      <c r="F26" s="398"/>
+      <c r="G26" s="398"/>
+      <c r="H26" s="398"/>
+      <c r="I26" s="398"/>
+      <c r="J26" s="398"/>
+      <c r="K26" s="398"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -11225,21 +11213,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -11256,6 +11229,21 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -11303,7 +11291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="C4:L34"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11312,367 +11300,386 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="415" t="str">
-        <f>'AREA UTIL '!C4</f>
+      <c r="C4" s="399" t="str">
+        <f>'AREA UTIL'!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="253"/>
+      <c r="F4" s="253"/>
+      <c r="G4" s="253"/>
+      <c r="H4" s="253"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="415" t="s">
+      <c r="C5" s="399" t="s">
         <v>204</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="400" t="s">
+      <c r="C6" s="404" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
       <c r="F6" s="401">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="248"/>
-      <c r="H6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="263"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="400" t="s">
+      <c r="C7" s="404" t="s">
         <v>205</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
       <c r="F7" s="401">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="400" t="s">
+      <c r="C8" s="404" t="s">
         <v>206</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="253"/>
       <c r="F8" s="401">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="400" t="s">
+      <c r="C9" s="404" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="403">
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
+      <c r="F9" s="400">
         <v>6</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="263"/>
       <c r="J9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="400" t="s">
+      <c r="C10" s="404" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
-      <c r="F10" s="403">
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
+      <c r="F10" s="400">
         <v>1</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="263"/>
       <c r="J10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="400" t="s">
+      <c r="C11" s="404" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="412">
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="415">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="248"/>
-      <c r="H11" s="253"/>
+      <c r="G11" s="253"/>
+      <c r="H11" s="263"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="400" t="s">
+      <c r="C12" s="404" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="403">
+      <c r="D12" s="253"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="400">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="248"/>
-      <c r="H12" s="253"/>
+      <c r="G12" s="253"/>
+      <c r="H12" s="263"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="400" t="s">
+      <c r="C13" s="404" t="s">
         <v>198</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
       <c r="F13" s="401">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="248"/>
-      <c r="H13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="263"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="410" t="s">
+      <c r="C14" s="412" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="409">
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="408">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="250"/>
-      <c r="H14" s="251"/>
-      <c r="J14" s="413">
+      <c r="G14" s="248"/>
+      <c r="H14" s="249"/>
+      <c r="J14" s="406">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="K14" s="253"/>
+      <c r="L14" s="253"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="417"/>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="248"/>
-      <c r="G15" s="248"/>
-      <c r="H15" s="248"/>
+      <c r="C15" s="410"/>
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="253"/>
+      <c r="G15" s="253"/>
+      <c r="H15" s="253"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="399" t="s">
+      <c r="C16" s="414" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
+      <c r="F16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="253"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="400" t="s">
+      <c r="C17" s="404" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="403">
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
+      <c r="F17" s="400">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="263"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="400" t="s">
+      <c r="C18" s="404" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
+      <c r="D18" s="253"/>
+      <c r="E18" s="253"/>
       <c r="F18" s="401">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="248"/>
-      <c r="H18" s="253"/>
+      <c r="G18" s="253"/>
+      <c r="H18" s="263"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="400" t="s">
+      <c r="C19" s="404" t="s">
         <v>215</v>
       </c>
-      <c r="D19" s="248"/>
-      <c r="E19" s="248"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
       <c r="F19" s="401">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="248"/>
-      <c r="H19" s="253"/>
+      <c r="G19" s="253"/>
+      <c r="H19" s="263"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="410" t="s">
+      <c r="C20" s="412" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="250"/>
-      <c r="E20" s="250"/>
-      <c r="F20" s="409">
+      <c r="D20" s="248"/>
+      <c r="E20" s="248"/>
+      <c r="F20" s="408">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="250"/>
-      <c r="H20" s="251"/>
+      <c r="G20" s="248"/>
+      <c r="H20" s="249"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="404"/>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="407"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
+      <c r="C21" s="405"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="253"/>
+      <c r="F21" s="402"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="404"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="407"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
+      <c r="C22" s="405"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
+      <c r="F22" s="402"/>
+      <c r="G22" s="253"/>
+      <c r="H22" s="253"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="404"/>
-      <c r="D23" s="248"/>
-      <c r="E23" s="248"/>
-      <c r="F23" s="416"/>
-      <c r="G23" s="248"/>
-      <c r="H23" s="248"/>
+      <c r="C23" s="405"/>
+      <c r="D23" s="253"/>
+      <c r="E23" s="253"/>
+      <c r="F23" s="409"/>
+      <c r="G23" s="253"/>
+      <c r="H23" s="253"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="414" t="s">
+      <c r="C24" s="407" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
-      <c r="G24" s="248"/>
-      <c r="H24" s="248"/>
+      <c r="D24" s="253"/>
+      <c r="E24" s="253"/>
+      <c r="F24" s="253"/>
+      <c r="G24" s="253"/>
+      <c r="H24" s="253"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="405" t="s">
+      <c r="C25" s="403" t="s">
         <v>218</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="408">
+      <c r="D25" s="253"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="411">
         <v>2000000</v>
       </c>
-      <c r="G25" s="248"/>
-      <c r="H25" s="253"/>
+      <c r="G25" s="253"/>
+      <c r="H25" s="263"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="405" t="s">
+      <c r="C26" s="403" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="402">
+      <c r="D26" s="253"/>
+      <c r="E26" s="253"/>
+      <c r="F26" s="416">
         <v>0.8</v>
       </c>
-      <c r="G26" s="248"/>
-      <c r="H26" s="253"/>
+      <c r="G26" s="253"/>
+      <c r="H26" s="263"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="405" t="s">
+      <c r="C27" s="403" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="408">
+      <c r="D27" s="253"/>
+      <c r="E27" s="253"/>
+      <c r="F27" s="411">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="248"/>
-      <c r="H27" s="253"/>
+      <c r="G27" s="253"/>
+      <c r="H27" s="263"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="411" t="s">
+      <c r="C28" s="413" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="250"/>
-      <c r="E28" s="250"/>
-      <c r="F28" s="406">
+      <c r="D28" s="248"/>
+      <c r="E28" s="248"/>
+      <c r="F28" s="417">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="250"/>
-      <c r="H28" s="251"/>
+      <c r="G28" s="248"/>
+      <c r="H28" s="249"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="399" t="s">
+      <c r="C31" s="414" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
+      <c r="D31" s="253"/>
+      <c r="E31" s="253"/>
+      <c r="F31" s="253"/>
+      <c r="G31" s="253"/>
+      <c r="H31" s="253"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="400" t="s">
+      <c r="C32" s="404" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="248"/>
-      <c r="E32" s="248"/>
+      <c r="D32" s="253"/>
+      <c r="E32" s="253"/>
       <c r="F32" s="401">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="248"/>
-      <c r="H32" s="253"/>
+      <c r="G32" s="253"/>
+      <c r="H32" s="263"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="400" t="s">
+      <c r="C33" s="404" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="401">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="248"/>
-      <c r="H33" s="253"/>
+      <c r="G33" s="253"/>
+      <c r="H33" s="263"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="410" t="s">
+      <c r="C34" s="412" t="s">
         <v>224</v>
       </c>
-      <c r="D34" s="250"/>
-      <c r="E34" s="250"/>
-      <c r="F34" s="409">
+      <c r="D34" s="248"/>
+      <c r="E34" s="248"/>
+      <c r="F34" s="408">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="250"/>
-      <c r="H34" s="251"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F19:H19"/>
@@ -11689,34 +11696,15 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -11724,7 +11712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="C5:K18"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11734,169 +11722,178 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="415" t="str">
+      <c r="C5" s="399" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="415" t="s">
+      <c r="C6" s="399" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="248"/>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="248"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="400" t="s">
+      <c r="C7" s="404" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
       <c r="F7" s="419">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="248"/>
-      <c r="H7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="263"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="400" t="s">
+      <c r="C8" s="404" t="s">
         <v>227</v>
       </c>
-      <c r="D8" s="248"/>
-      <c r="E8" s="248"/>
-      <c r="F8" s="403">
+      <c r="D8" s="253"/>
+      <c r="E8" s="253"/>
+      <c r="F8" s="400">
         <v>36</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="263"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="400" t="s">
+      <c r="C9" s="404" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
+      <c r="D9" s="253"/>
+      <c r="E9" s="253"/>
       <c r="F9" s="418">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="248"/>
-      <c r="H9" s="253"/>
+      <c r="G9" s="253"/>
+      <c r="H9" s="263"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="400" t="s">
+      <c r="C10" s="404" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="248"/>
-      <c r="E10" s="248"/>
+      <c r="D10" s="253"/>
+      <c r="E10" s="253"/>
       <c r="F10" s="401">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="248"/>
-      <c r="H10" s="253"/>
+      <c r="G10" s="253"/>
+      <c r="H10" s="263"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="410" t="s">
+      <c r="C11" s="412" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="409">
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="408">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="250"/>
-      <c r="H11" s="251"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="249"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="399" t="s">
+      <c r="C13" s="414" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
+      <c r="D13" s="253"/>
+      <c r="E13" s="253"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="253"/>
+      <c r="H13" s="253"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="400" t="s">
+      <c r="C14" s="404" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
+      <c r="D14" s="253"/>
+      <c r="E14" s="253"/>
       <c r="F14" s="419">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="248"/>
-      <c r="H14" s="253"/>
+      <c r="G14" s="253"/>
+      <c r="H14" s="263"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="400" t="s">
+      <c r="C15" s="404" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="248"/>
-      <c r="E15" s="248"/>
-      <c r="F15" s="403">
+      <c r="D15" s="253"/>
+      <c r="E15" s="253"/>
+      <c r="F15" s="400">
         <v>36</v>
       </c>
-      <c r="G15" s="248"/>
-      <c r="H15" s="253"/>
+      <c r="G15" s="253"/>
+      <c r="H15" s="263"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="400" t="s">
+      <c r="C16" s="404" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
+      <c r="D16" s="253"/>
+      <c r="E16" s="253"/>
       <c r="F16" s="418">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="248"/>
-      <c r="H16" s="253"/>
+      <c r="G16" s="253"/>
+      <c r="H16" s="263"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="400" t="s">
+      <c r="C17" s="404" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
+      <c r="D17" s="253"/>
+      <c r="E17" s="253"/>
       <c r="F17" s="401">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="248"/>
-      <c r="H17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="263"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="410" t="s">
+      <c r="C18" s="412" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250"/>
-      <c r="F18" s="409">
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="408">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="250"/>
-      <c r="H18" s="251"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -11911,15 +11908,6 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -2898,95 +2898,95 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3007,11 +3007,53 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3021,57 +3063,6 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3084,43 +3075,64 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3130,157 +3142,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3290,29 +3206,122 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="64" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3322,162 +3331,163 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3485,26 +3495,16 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3520,25 +3520,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3957,7 +3957,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="250" t="s">
+      <c r="B3" s="248" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="257"/>
@@ -3970,21 +3970,21 @@
       <c r="J3" s="257"/>
       <c r="K3" s="257"/>
       <c r="L3" s="257"/>
-      <c r="M3" s="262"/>
+      <c r="M3" s="258"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="263"/>
-      <c r="C4" s="260"/>
-      <c r="D4" s="260"/>
-      <c r="E4" s="260"/>
-      <c r="F4" s="260"/>
-      <c r="G4" s="260"/>
-      <c r="H4" s="260"/>
-      <c r="I4" s="260"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="260"/>
-      <c r="L4" s="260"/>
-      <c r="M4" s="264"/>
+      <c r="B4" s="270"/>
+      <c r="C4" s="252"/>
+      <c r="D4" s="252"/>
+      <c r="E4" s="252"/>
+      <c r="F4" s="252"/>
+      <c r="G4" s="252"/>
+      <c r="H4" s="252"/>
+      <c r="I4" s="252"/>
+      <c r="J4" s="252"/>
+      <c r="K4" s="252"/>
+      <c r="L4" s="252"/>
+      <c r="M4" s="260"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -4015,100 +4015,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="248" t="s">
+      <c r="B7" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="249"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="253"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
-      <c r="H7" s="249"/>
-      <c r="I7" s="249"/>
-      <c r="J7" s="249"/>
-      <c r="K7" s="249"/>
-      <c r="L7" s="249"/>
-      <c r="M7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="271"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="264"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="248" t="s">
+      <c r="B8" s="253" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="253"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="254"/>
+      <c r="C8" s="254"/>
+      <c r="D8" s="254"/>
+      <c r="E8" s="271"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="254"/>
+      <c r="J8" s="254"/>
+      <c r="K8" s="254"/>
+      <c r="L8" s="254"/>
+      <c r="M8" s="264"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="248" t="s">
+      <c r="B9" s="253" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="253"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="254"/>
+      <c r="C9" s="254"/>
+      <c r="D9" s="254"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="264"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="248" t="s">
+      <c r="B10" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="249"/>
-      <c r="K10" s="249"/>
-      <c r="L10" s="249"/>
-      <c r="M10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="254"/>
+      <c r="L10" s="254"/>
+      <c r="M10" s="264"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="248" t="s">
+      <c r="B11" s="253" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="253"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="249"/>
-      <c r="J11" s="249"/>
-      <c r="K11" s="249"/>
-      <c r="L11" s="249"/>
-      <c r="M11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="254"/>
+      <c r="H11" s="254"/>
+      <c r="I11" s="254"/>
+      <c r="J11" s="254"/>
+      <c r="K11" s="254"/>
+      <c r="L11" s="254"/>
+      <c r="M11" s="264"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="248" t="s">
+      <c r="B12" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="253"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
-      <c r="H12" s="249"/>
-      <c r="I12" s="249"/>
-      <c r="J12" s="249"/>
-      <c r="K12" s="249"/>
-      <c r="L12" s="249"/>
-      <c r="M12" s="254"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="271"/>
+      <c r="F12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="254"/>
+      <c r="J12" s="254"/>
+      <c r="K12" s="254"/>
+      <c r="L12" s="254"/>
+      <c r="M12" s="264"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4167,20 +4167,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="255" t="s">
+      <c r="B17" s="282" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="249"/>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
-      <c r="J17" s="249"/>
-      <c r="K17" s="249"/>
-      <c r="L17" s="249"/>
-      <c r="M17" s="249"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
+      <c r="J17" s="254"/>
+      <c r="K17" s="254"/>
+      <c r="L17" s="254"/>
+      <c r="M17" s="254"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4197,12 +4197,12 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="256" t="s">
+      <c r="B19" s="283" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="257"/>
       <c r="D19" s="257"/>
-      <c r="E19" s="261"/>
+      <c r="E19" s="281"/>
       <c r="F19" s="257"/>
       <c r="G19" s="257"/>
       <c r="H19" s="257"/>
@@ -4210,137 +4210,137 @@
       <c r="J19" s="257"/>
       <c r="K19" s="257"/>
       <c r="L19" s="257"/>
-      <c r="M19" s="262"/>
+      <c r="M19" s="258"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="248" t="s">
+      <c r="B20" s="253" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="249"/>
-      <c r="I20" s="249"/>
-      <c r="J20" s="249"/>
-      <c r="K20" s="249"/>
-      <c r="L20" s="249"/>
-      <c r="M20" s="254"/>
+      <c r="C20" s="254"/>
+      <c r="D20" s="254"/>
+      <c r="E20" s="271"/>
+      <c r="F20" s="254"/>
+      <c r="G20" s="254"/>
+      <c r="H20" s="254"/>
+      <c r="I20" s="254"/>
+      <c r="J20" s="254"/>
+      <c r="K20" s="254"/>
+      <c r="L20" s="254"/>
+      <c r="M20" s="264"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="248" t="s">
+      <c r="B21" s="253" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="249"/>
-      <c r="D21" s="249"/>
-      <c r="E21" s="253"/>
-      <c r="F21" s="249"/>
-      <c r="G21" s="249"/>
-      <c r="H21" s="249"/>
-      <c r="I21" s="249"/>
-      <c r="J21" s="249"/>
-      <c r="K21" s="249"/>
-      <c r="L21" s="249"/>
-      <c r="M21" s="254"/>
+      <c r="C21" s="254"/>
+      <c r="D21" s="254"/>
+      <c r="E21" s="271"/>
+      <c r="F21" s="254"/>
+      <c r="G21" s="254"/>
+      <c r="H21" s="254"/>
+      <c r="I21" s="254"/>
+      <c r="J21" s="254"/>
+      <c r="K21" s="254"/>
+      <c r="L21" s="254"/>
+      <c r="M21" s="264"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="271" t="s">
+      <c r="B22" s="278" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="260"/>
-      <c r="D22" s="260"/>
-      <c r="E22" s="265"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="260"/>
-      <c r="J22" s="260"/>
+      <c r="C22" s="252"/>
+      <c r="D22" s="252"/>
+      <c r="E22" s="272"/>
+      <c r="F22" s="252"/>
+      <c r="G22" s="252"/>
+      <c r="H22" s="252"/>
+      <c r="I22" s="252"/>
+      <c r="J22" s="252"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="269"/>
-      <c r="M22" s="264"/>
+      <c r="L22" s="276"/>
+      <c r="M22" s="260"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="250" t="s">
+      <c r="B23" s="248" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="251"/>
-      <c r="D23" s="251"/>
-      <c r="E23" s="251"/>
-      <c r="F23" s="251"/>
-      <c r="G23" s="251"/>
-      <c r="H23" s="251"/>
-      <c r="I23" s="251"/>
-      <c r="J23" s="251"/>
-      <c r="K23" s="251"/>
-      <c r="L23" s="251"/>
-      <c r="M23" s="252"/>
+      <c r="C23" s="249"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="249"/>
+      <c r="F23" s="249"/>
+      <c r="G23" s="249"/>
+      <c r="H23" s="249"/>
+      <c r="I23" s="249"/>
+      <c r="J23" s="249"/>
+      <c r="K23" s="249"/>
+      <c r="L23" s="249"/>
+      <c r="M23" s="250"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="258" t="s">
+      <c r="B24" s="261" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="251"/>
-      <c r="D24" s="252"/>
-      <c r="E24" s="258" t="s">
+      <c r="C24" s="249"/>
+      <c r="D24" s="250"/>
+      <c r="E24" s="261" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="251"/>
-      <c r="G24" s="252"/>
-      <c r="H24" s="258" t="s">
+      <c r="F24" s="249"/>
+      <c r="G24" s="250"/>
+      <c r="H24" s="261" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="251"/>
-      <c r="J24" s="252"/>
-      <c r="K24" s="258" t="s">
+      <c r="I24" s="249"/>
+      <c r="J24" s="250"/>
+      <c r="K24" s="261" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="251"/>
-      <c r="M24" s="252"/>
+      <c r="L24" s="249"/>
+      <c r="M24" s="250"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="268"/>
+      <c r="B25" s="275"/>
       <c r="C25" s="257"/>
-      <c r="D25" s="262"/>
-      <c r="E25" s="277"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="275"/>
+      <c r="D25" s="258"/>
+      <c r="E25" s="262"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="256"/>
       <c r="I25" s="257"/>
-      <c r="J25" s="262"/>
-      <c r="K25" s="270"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="277"/>
       <c r="L25" s="257"/>
-      <c r="M25" s="262"/>
+      <c r="M25" s="258"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="266"/>
-      <c r="C26" s="260"/>
-      <c r="D26" s="264"/>
-      <c r="E26" s="259"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="267"/>
-      <c r="I26" s="260"/>
-      <c r="J26" s="264"/>
-      <c r="K26" s="272"/>
-      <c r="L26" s="260"/>
-      <c r="M26" s="264"/>
+      <c r="B26" s="273"/>
+      <c r="C26" s="252"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="280"/>
+      <c r="F26" s="252"/>
+      <c r="G26" s="252"/>
+      <c r="H26" s="274"/>
+      <c r="I26" s="252"/>
+      <c r="J26" s="260"/>
+      <c r="K26" s="279"/>
+      <c r="L26" s="252"/>
+      <c r="M26" s="260"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="250" t="s">
+      <c r="B27" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="251"/>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="251"/>
-      <c r="G27" s="251"/>
-      <c r="H27" s="251"/>
-      <c r="I27" s="251"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
-      <c r="M27" s="252"/>
+      <c r="C27" s="249"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="249"/>
+      <c r="I27" s="249"/>
+      <c r="J27" s="249"/>
+      <c r="K27" s="249"/>
+      <c r="L27" s="249"/>
+      <c r="M27" s="250"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4427,100 +4427,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="250" t="s">
+      <c r="B34" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="251"/>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="251"/>
-      <c r="G34" s="251"/>
-      <c r="H34" s="251"/>
-      <c r="I34" s="251"/>
-      <c r="J34" s="251"/>
-      <c r="K34" s="251"/>
-      <c r="L34" s="251"/>
-      <c r="M34" s="252"/>
+      <c r="C34" s="249"/>
+      <c r="D34" s="249"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="249"/>
+      <c r="G34" s="249"/>
+      <c r="H34" s="249"/>
+      <c r="I34" s="249"/>
+      <c r="J34" s="249"/>
+      <c r="K34" s="249"/>
+      <c r="L34" s="249"/>
+      <c r="M34" s="250"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="258" t="s">
+      <c r="B35" s="261" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="251"/>
-      <c r="D35" s="251"/>
-      <c r="E35" s="252"/>
-      <c r="F35" s="258" t="s">
+      <c r="C35" s="249"/>
+      <c r="D35" s="249"/>
+      <c r="E35" s="250"/>
+      <c r="F35" s="261" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="251"/>
-      <c r="H35" s="251"/>
-      <c r="I35" s="252"/>
-      <c r="J35" s="258" t="s">
+      <c r="G35" s="249"/>
+      <c r="H35" s="249"/>
+      <c r="I35" s="250"/>
+      <c r="J35" s="261" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="251"/>
-      <c r="L35" s="251"/>
-      <c r="M35" s="252"/>
+      <c r="K35" s="249"/>
+      <c r="L35" s="249"/>
+      <c r="M35" s="250"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="281"/>
+      <c r="B36" s="267"/>
       <c r="C36" s="257"/>
       <c r="D36" s="257"/>
       <c r="E36" s="257"/>
-      <c r="F36" s="282"/>
+      <c r="F36" s="268"/>
       <c r="G36" s="257"/>
       <c r="H36" s="257"/>
       <c r="I36" s="257"/>
-      <c r="J36" s="283"/>
+      <c r="J36" s="269"/>
       <c r="K36" s="257"/>
       <c r="L36" s="257"/>
-      <c r="M36" s="262"/>
+      <c r="M36" s="258"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="274"/>
-      <c r="C37" s="249"/>
-      <c r="D37" s="249"/>
-      <c r="E37" s="249"/>
-      <c r="F37" s="280"/>
-      <c r="G37" s="249"/>
-      <c r="H37" s="249"/>
-      <c r="I37" s="249"/>
-      <c r="J37" s="278"/>
-      <c r="K37" s="249"/>
-      <c r="L37" s="249"/>
-      <c r="M37" s="254"/>
+      <c r="B37" s="255"/>
+      <c r="C37" s="254"/>
+      <c r="D37" s="254"/>
+      <c r="E37" s="254"/>
+      <c r="F37" s="266"/>
+      <c r="G37" s="254"/>
+      <c r="H37" s="254"/>
+      <c r="I37" s="254"/>
+      <c r="J37" s="263"/>
+      <c r="K37" s="254"/>
+      <c r="L37" s="254"/>
+      <c r="M37" s="264"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="279" t="s">
+      <c r="B38" s="265" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="260"/>
-      <c r="D38" s="260"/>
-      <c r="E38" s="260"/>
-      <c r="F38" s="273"/>
-      <c r="G38" s="260"/>
-      <c r="H38" s="260"/>
-      <c r="I38" s="260"/>
-      <c r="J38" s="276"/>
-      <c r="K38" s="260"/>
-      <c r="L38" s="260"/>
-      <c r="M38" s="264"/>
+      <c r="C38" s="252"/>
+      <c r="D38" s="252"/>
+      <c r="E38" s="252"/>
+      <c r="F38" s="251"/>
+      <c r="G38" s="252"/>
+      <c r="H38" s="252"/>
+      <c r="I38" s="252"/>
+      <c r="J38" s="259"/>
+      <c r="K38" s="252"/>
+      <c r="L38" s="252"/>
+      <c r="M38" s="260"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="250" t="s">
+      <c r="B39" s="248" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="251"/>
-      <c r="D39" s="251"/>
-      <c r="E39" s="251"/>
-      <c r="F39" s="251"/>
-      <c r="G39" s="251"/>
-      <c r="H39" s="251"/>
-      <c r="I39" s="251"/>
-      <c r="J39" s="251"/>
-      <c r="K39" s="251"/>
-      <c r="L39" s="251"/>
-      <c r="M39" s="252"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="249"/>
+      <c r="I39" s="249"/>
+      <c r="J39" s="249"/>
+      <c r="K39" s="249"/>
+      <c r="L39" s="249"/>
+      <c r="M39" s="250"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4636,6 +4636,41 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B3:M4"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="E22:J22"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="B39:M39"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B21:D21"/>
@@ -4652,41 +4687,6 @@
     <mergeCell ref="F36:I36"/>
     <mergeCell ref="J36:M36"/>
     <mergeCell ref="B34:M34"/>
-    <mergeCell ref="B3:M4"/>
-    <mergeCell ref="E7:M7"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E12:M12"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4727,37 +4727,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="439" t="s">
+      <c r="B2" s="423" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="440"/>
-      <c r="D2" s="440"/>
-      <c r="E2" s="440"/>
-      <c r="F2" s="440"/>
-      <c r="G2" s="440"/>
-      <c r="H2" s="440"/>
-      <c r="I2" s="440"/>
-      <c r="J2" s="440"/>
-      <c r="K2" s="440"/>
-      <c r="L2" s="440"/>
-      <c r="M2" s="440"/>
-      <c r="N2" s="440"/>
-      <c r="O2" s="440"/>
-      <c r="P2" s="440"/>
-      <c r="Q2" s="440"/>
-      <c r="R2" s="440"/>
-      <c r="S2" s="440"/>
-      <c r="T2" s="440"/>
-      <c r="U2" s="440"/>
-      <c r="V2" s="440"/>
-      <c r="W2" s="440"/>
-      <c r="X2" s="440"/>
-      <c r="Y2" s="440"/>
-      <c r="Z2" s="440"/>
-      <c r="AA2" s="440"/>
-      <c r="AB2" s="440"/>
-      <c r="AC2" s="440"/>
-      <c r="AD2" s="440"/>
+      <c r="C2" s="424"/>
+      <c r="D2" s="424"/>
+      <c r="E2" s="424"/>
+      <c r="F2" s="424"/>
+      <c r="G2" s="424"/>
+      <c r="H2" s="424"/>
+      <c r="I2" s="424"/>
+      <c r="J2" s="424"/>
+      <c r="K2" s="424"/>
+      <c r="L2" s="424"/>
+      <c r="M2" s="424"/>
+      <c r="N2" s="424"/>
+      <c r="O2" s="424"/>
+      <c r="P2" s="424"/>
+      <c r="Q2" s="424"/>
+      <c r="R2" s="424"/>
+      <c r="S2" s="424"/>
+      <c r="T2" s="424"/>
+      <c r="U2" s="424"/>
+      <c r="V2" s="424"/>
+      <c r="W2" s="424"/>
+      <c r="X2" s="424"/>
+      <c r="Y2" s="424"/>
+      <c r="Z2" s="424"/>
+      <c r="AA2" s="424"/>
+      <c r="AB2" s="424"/>
+      <c r="AC2" s="424"/>
+      <c r="AD2" s="424"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -4884,39 +4884,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="431">
+      <c r="B10" s="441">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="427"/>
-      <c r="D10" s="427"/>
-      <c r="E10" s="427"/>
-      <c r="F10" s="427"/>
-      <c r="G10" s="427"/>
+      <c r="C10" s="426"/>
+      <c r="D10" s="426"/>
+      <c r="E10" s="426"/>
+      <c r="F10" s="426"/>
+      <c r="G10" s="426"/>
       <c r="H10" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="I10" s="448">
+      <c r="I10" s="440">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="427"/>
-      <c r="K10" s="427"/>
-      <c r="L10" s="427"/>
-      <c r="M10" s="427"/>
-      <c r="N10" s="427"/>
-      <c r="O10" s="427"/>
-      <c r="P10" s="427"/>
+      <c r="J10" s="426"/>
+      <c r="K10" s="426"/>
+      <c r="L10" s="426"/>
+      <c r="M10" s="426"/>
+      <c r="N10" s="426"/>
+      <c r="O10" s="426"/>
+      <c r="P10" s="426"/>
       <c r="Q10" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="R10" s="426">
+      <c r="R10" s="425">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="427"/>
-      <c r="T10" s="427"/>
-      <c r="U10" s="427"/>
+      <c r="S10" s="426"/>
+      <c r="T10" s="426"/>
+      <c r="U10" s="426"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>238</v>
@@ -4951,13 +4951,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="426">
+      <c r="W11" s="425">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="427"/>
-      <c r="Y11" s="427"/>
-      <c r="Z11" s="427"/>
+      <c r="X11" s="426"/>
+      <c r="Y11" s="426"/>
+      <c r="Z11" s="426"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -4984,13 +4984,13 @@
       <c r="Q12" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="R12" s="446">
+      <c r="R12" s="437">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="427"/>
-      <c r="T12" s="427"/>
-      <c r="U12" s="427"/>
+      <c r="S12" s="426"/>
+      <c r="T12" s="426"/>
+      <c r="U12" s="426"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -5010,10 +5010,10 @@
         <v>239</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="438"/>
-      <c r="X14" s="427"/>
-      <c r="Y14" s="427"/>
-      <c r="Z14" s="427"/>
+      <c r="W14" s="430"/>
+      <c r="X14" s="426"/>
+      <c r="Y14" s="426"/>
+      <c r="Z14" s="426"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -5039,38 +5039,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="443" t="s">
+      <c r="B16" s="434" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="427"/>
-      <c r="D16" s="427"/>
-      <c r="E16" s="427"/>
-      <c r="F16" s="427"/>
-      <c r="G16" s="427"/>
+      <c r="C16" s="426"/>
+      <c r="D16" s="426"/>
+      <c r="E16" s="426"/>
+      <c r="F16" s="426"/>
+      <c r="G16" s="426"/>
       <c r="H16" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="I16" s="433" t="str">
+      <c r="I16" s="443" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="427"/>
-      <c r="K16" s="427"/>
-      <c r="L16" s="427"/>
-      <c r="M16" s="427"/>
-      <c r="N16" s="427"/>
-      <c r="O16" s="427"/>
-      <c r="P16" s="427"/>
+      <c r="J16" s="426"/>
+      <c r="K16" s="426"/>
+      <c r="L16" s="426"/>
+      <c r="M16" s="426"/>
+      <c r="N16" s="426"/>
+      <c r="O16" s="426"/>
+      <c r="P16" s="426"/>
       <c r="Q16" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="R16" s="438" t="str">
+      <c r="R16" s="430" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="427"/>
-      <c r="T16" s="427"/>
-      <c r="U16" s="427"/>
+      <c r="S16" s="426"/>
+      <c r="T16" s="426"/>
+      <c r="U16" s="426"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -5082,10 +5082,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="438"/>
-      <c r="X17" s="427"/>
-      <c r="Y17" s="427"/>
-      <c r="Z17" s="427"/>
+      <c r="W17" s="430"/>
+      <c r="X17" s="426"/>
+      <c r="Y17" s="426"/>
+      <c r="Z17" s="426"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -5109,13 +5109,13 @@
       <c r="Q18" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="437" t="str">
+      <c r="R18" s="446" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="427"/>
-      <c r="T18" s="427"/>
-      <c r="U18" s="427"/>
+      <c r="S18" s="426"/>
+      <c r="T18" s="426"/>
+      <c r="U18" s="426"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -5197,13 +5197,13 @@
       <c r="V22" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W22" s="447">
+      <c r="W22" s="438">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="430"/>
-      <c r="Y22" s="430"/>
-      <c r="Z22" s="430"/>
+      <c r="X22" s="433"/>
+      <c r="Y22" s="433"/>
+      <c r="Z22" s="433"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -5212,13 +5212,13 @@
       <c r="V23" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W23" s="429" t="str">
+      <c r="W23" s="432" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="430"/>
-      <c r="Y23" s="430"/>
-      <c r="Z23" s="430"/>
+      <c r="X23" s="433"/>
+      <c r="Y23" s="433"/>
+      <c r="Z23" s="433"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -5227,13 +5227,13 @@
       <c r="V24" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="W24" s="441">
+      <c r="W24" s="427">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="424"/>
-      <c r="Y24" s="424"/>
-      <c r="Z24" s="424"/>
+      <c r="X24" s="428"/>
+      <c r="Y24" s="428"/>
+      <c r="Z24" s="428"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -5242,13 +5242,13 @@
       <c r="V25" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W25" s="429">
+      <c r="W25" s="432">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="430"/>
-      <c r="Y25" s="430"/>
-      <c r="Z25" s="430"/>
+      <c r="X25" s="433"/>
+      <c r="Y25" s="433"/>
+      <c r="Z25" s="433"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -5257,13 +5257,13 @@
       <c r="V26" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W26" s="429">
+      <c r="W26" s="432">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="430"/>
-      <c r="Y26" s="430"/>
-      <c r="Z26" s="430"/>
+      <c r="X26" s="433"/>
+      <c r="Y26" s="433"/>
+      <c r="Z26" s="433"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -5272,13 +5272,13 @@
       <c r="V27" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W27" s="429">
+      <c r="W27" s="432">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="430"/>
-      <c r="Y27" s="430"/>
-      <c r="Z27" s="430"/>
+      <c r="X27" s="433"/>
+      <c r="Y27" s="433"/>
+      <c r="Z27" s="433"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -5287,13 +5287,13 @@
       <c r="V28" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W28" s="429">
+      <c r="W28" s="432">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="430"/>
-      <c r="Y28" s="430"/>
-      <c r="Z28" s="430"/>
+      <c r="X28" s="433"/>
+      <c r="Y28" s="433"/>
+      <c r="Z28" s="433"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -5302,13 +5302,13 @@
       <c r="V29" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W29" s="429">
+      <c r="W29" s="432">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="430"/>
-      <c r="Y29" s="430"/>
-      <c r="Z29" s="430"/>
+      <c r="X29" s="433"/>
+      <c r="Y29" s="433"/>
+      <c r="Z29" s="433"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -5317,13 +5317,13 @@
       <c r="V30" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="W30" s="442">
+      <c r="W30" s="431">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="424"/>
-      <c r="Y30" s="424"/>
-      <c r="Z30" s="424"/>
+      <c r="X30" s="428"/>
+      <c r="Y30" s="428"/>
+      <c r="Z30" s="428"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -5333,83 +5333,83 @@
       <c r="V31" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="W31" s="445">
+      <c r="W31" s="436">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="424"/>
-      <c r="Y31" s="424"/>
-      <c r="Z31" s="424"/>
+      <c r="X31" s="428"/>
+      <c r="Y31" s="428"/>
+      <c r="Z31" s="428"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="K32" s="444">
+      <c r="K32" s="435">
         <v>43009</v>
       </c>
-      <c r="L32" s="430"/>
-      <c r="M32" s="430"/>
-      <c r="N32" s="430"/>
-      <c r="O32" s="430"/>
-      <c r="P32" s="430"/>
-      <c r="Q32" s="430"/>
-      <c r="R32" s="430"/>
-      <c r="S32" s="430"/>
-      <c r="T32" s="430"/>
-      <c r="U32" s="430"/>
-      <c r="V32" s="430"/>
-      <c r="W32" s="430"/>
-      <c r="X32" s="430"/>
-      <c r="Y32" s="430"/>
-      <c r="Z32" s="430"/>
+      <c r="L32" s="433"/>
+      <c r="M32" s="433"/>
+      <c r="N32" s="433"/>
+      <c r="O32" s="433"/>
+      <c r="P32" s="433"/>
+      <c r="Q32" s="433"/>
+      <c r="R32" s="433"/>
+      <c r="S32" s="433"/>
+      <c r="T32" s="433"/>
+      <c r="U32" s="433"/>
+      <c r="V32" s="433"/>
+      <c r="W32" s="433"/>
+      <c r="X32" s="433"/>
+      <c r="Y32" s="433"/>
+      <c r="Z32" s="433"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="423" t="s">
+      <c r="O33" s="447" t="s">
         <v>254</v>
       </c>
-      <c r="P33" s="424"/>
-      <c r="Q33" s="424"/>
-      <c r="R33" s="424"/>
-      <c r="S33" s="424"/>
-      <c r="T33" s="424"/>
-      <c r="U33" s="424"/>
-      <c r="V33" s="424"/>
-      <c r="W33" s="428" t="s">
+      <c r="P33" s="428"/>
+      <c r="Q33" s="428"/>
+      <c r="R33" s="428"/>
+      <c r="S33" s="428"/>
+      <c r="T33" s="428"/>
+      <c r="U33" s="428"/>
+      <c r="V33" s="428"/>
+      <c r="W33" s="448" t="s">
         <v>255</v>
       </c>
-      <c r="X33" s="332"/>
-      <c r="Y33" s="332"/>
-      <c r="Z33" s="332"/>
-      <c r="AA33" s="332"/>
-      <c r="AB33" s="332"/>
-      <c r="AC33" s="332"/>
-      <c r="AD33" s="332"/>
+      <c r="X33" s="336"/>
+      <c r="Y33" s="336"/>
+      <c r="Z33" s="336"/>
+      <c r="AA33" s="336"/>
+      <c r="AB33" s="336"/>
+      <c r="AC33" s="336"/>
+      <c r="AD33" s="336"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="435">
+      <c r="Q34" s="439">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="430"/>
-      <c r="S34" s="430"/>
-      <c r="T34" s="430"/>
+      <c r="R34" s="433"/>
+      <c r="S34" s="433"/>
+      <c r="T34" s="433"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="435">
+      <c r="Y34" s="439">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="430"/>
-      <c r="AA34" s="430"/>
-      <c r="AB34" s="430"/>
+      <c r="Z34" s="433"/>
+      <c r="AA34" s="433"/>
+      <c r="AB34" s="433"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -5472,32 +5472,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="432"/>
-      <c r="C38" s="427"/>
+      <c r="B38" s="429"/>
+      <c r="C38" s="426"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="432"/>
-      <c r="C39" s="427"/>
+      <c r="B39" s="429"/>
+      <c r="C39" s="426"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="432"/>
-      <c r="C40" s="427"/>
+      <c r="B40" s="429"/>
+      <c r="C40" s="426"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="432"/>
-      <c r="C41" s="427"/>
+      <c r="B41" s="429"/>
+      <c r="C41" s="426"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="432"/>
-      <c r="C42" s="427"/>
+      <c r="B42" s="429"/>
+      <c r="C42" s="426"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="432"/>
-      <c r="C43" s="427"/>
+      <c r="B43" s="429"/>
+      <c r="C43" s="426"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="432"/>
-      <c r="C44" s="427"/>
+      <c r="B44" s="429"/>
+      <c r="C44" s="426"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="436"/>
-      <c r="F49" s="427"/>
-      <c r="G49" s="427"/>
-      <c r="H49" s="427"/>
+      <c r="E49" s="445"/>
+      <c r="F49" s="426"/>
+      <c r="G49" s="426"/>
+      <c r="H49" s="426"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -5594,44 +5594,66 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="425"/>
-      <c r="I52" s="332"/>
-      <c r="J52" s="332"/>
-      <c r="K52" s="332"/>
-      <c r="L52" s="332"/>
-      <c r="M52" s="332"/>
-      <c r="N52" s="332"/>
-      <c r="O52" s="332"/>
-      <c r="P52" s="332"/>
+      <c r="H52" s="442"/>
+      <c r="I52" s="336"/>
+      <c r="J52" s="336"/>
+      <c r="K52" s="336"/>
+      <c r="L52" s="336"/>
+      <c r="M52" s="336"/>
+      <c r="N52" s="336"/>
+      <c r="O52" s="336"/>
+      <c r="P52" s="336"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="434"/>
-      <c r="I55" s="332"/>
-      <c r="J55" s="332"/>
-      <c r="K55" s="332"/>
-      <c r="L55" s="332"/>
-      <c r="M55" s="332"/>
-      <c r="N55" s="332"/>
-      <c r="O55" s="332"/>
-      <c r="P55" s="332"/>
+      <c r="H55" s="444"/>
+      <c r="I55" s="336"/>
+      <c r="J55" s="336"/>
+      <c r="K55" s="336"/>
+      <c r="L55" s="336"/>
+      <c r="M55" s="336"/>
+      <c r="N55" s="336"/>
+      <c r="O55" s="336"/>
+      <c r="P55" s="336"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="425"/>
-      <c r="I57" s="332"/>
-      <c r="J57" s="332"/>
-      <c r="K57" s="332"/>
-      <c r="L57" s="332"/>
-      <c r="M57" s="332"/>
-      <c r="N57" s="332"/>
-      <c r="O57" s="332"/>
-      <c r="P57" s="332"/>
+      <c r="H57" s="442"/>
+      <c r="I57" s="336"/>
+      <c r="J57" s="336"/>
+      <c r="K57" s="336"/>
+      <c r="L57" s="336"/>
+      <c r="M57" s="336"/>
+      <c r="N57" s="336"/>
+      <c r="O57" s="336"/>
+      <c r="P57" s="336"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="H57:P57"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="I16:P16"/>
+    <mergeCell ref="W25:Z25"/>
+    <mergeCell ref="H55:P55"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="W28:Z28"/>
+    <mergeCell ref="W27:Z27"/>
+    <mergeCell ref="W17:Z17"/>
     <mergeCell ref="B2:AD2"/>
     <mergeCell ref="R10:U10"/>
     <mergeCell ref="W24:Z24"/>
@@ -5648,28 +5670,6 @@
     <mergeCell ref="W22:Z22"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="H57:P57"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="I16:P16"/>
-    <mergeCell ref="W25:Z25"/>
-    <mergeCell ref="H55:P55"/>
-    <mergeCell ref="Q34:T34"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="W28:Z28"/>
-    <mergeCell ref="W27:Z27"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
@@ -5705,24 +5705,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="464" t="s">
+      <c r="B1" s="455" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="465"/>
-      <c r="D1" s="465"/>
-      <c r="E1" s="465"/>
-      <c r="F1" s="465"/>
-      <c r="G1" s="465"/>
-      <c r="H1" s="466"/>
+      <c r="C1" s="456"/>
+      <c r="D1" s="456"/>
+      <c r="E1" s="456"/>
+      <c r="F1" s="456"/>
+      <c r="G1" s="456"/>
+      <c r="H1" s="457"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="461"/>
-      <c r="C2" s="462"/>
-      <c r="D2" s="462"/>
-      <c r="E2" s="462"/>
-      <c r="F2" s="462"/>
-      <c r="G2" s="462"/>
-      <c r="H2" s="463"/>
+      <c r="B2" s="451"/>
+      <c r="C2" s="452"/>
+      <c r="D2" s="452"/>
+      <c r="E2" s="452"/>
+      <c r="F2" s="452"/>
+      <c r="G2" s="452"/>
+      <c r="H2" s="453"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -5757,32 +5757,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="454" t="s">
+      <c r="B6" s="460" t="s">
         <v>258</v>
       </c>
-      <c r="C6" s="456" t="s">
+      <c r="C6" s="462" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="452" t="s">
+      <c r="D6" s="464" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="458" t="s">
+      <c r="E6" s="465" t="s">
         <v>261</v>
       </c>
-      <c r="F6" s="458" t="s">
+      <c r="F6" s="465" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="449" t="s">
+      <c r="G6" s="458" t="s">
         <v>263</v>
       </c>
-      <c r="H6" s="450"/>
+      <c r="H6" s="459"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="455"/>
-      <c r="C7" s="453"/>
-      <c r="D7" s="453"/>
-      <c r="E7" s="264"/>
-      <c r="F7" s="264"/>
+      <c r="B7" s="461"/>
+      <c r="C7" s="463"/>
+      <c r="D7" s="463"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="260"/>
       <c r="G7" s="47" t="s">
         <v>264</v>
       </c>
@@ -5803,14 +5803,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="451" t="s">
+      <c r="B9" s="466" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="251"/>
-      <c r="D9" s="251"/>
-      <c r="E9" s="251"/>
-      <c r="F9" s="251"/>
-      <c r="G9" s="252"/>
+      <c r="C9" s="249"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="250"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -5828,32 +5828,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="454" t="s">
+      <c r="B11" s="460" t="s">
         <v>258</v>
       </c>
-      <c r="C11" s="456" t="s">
+      <c r="C11" s="462" t="s">
         <v>259</v>
       </c>
-      <c r="D11" s="452" t="s">
+      <c r="D11" s="464" t="s">
         <v>260</v>
       </c>
-      <c r="E11" s="457" t="s">
+      <c r="E11" s="454" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="457" t="s">
+      <c r="F11" s="454" t="s">
         <v>262</v>
       </c>
-      <c r="G11" s="449" t="s">
+      <c r="G11" s="458" t="s">
         <v>263</v>
       </c>
-      <c r="H11" s="450"/>
+      <c r="H11" s="459"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="455"/>
-      <c r="C12" s="453"/>
-      <c r="D12" s="453"/>
-      <c r="E12" s="264"/>
-      <c r="F12" s="264"/>
+      <c r="B12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="260"/>
+      <c r="F12" s="260"/>
       <c r="G12" s="47" t="s">
         <v>264</v>
       </c>
@@ -5874,14 +5874,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="451" t="s">
+      <c r="B14" s="466" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="251"/>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="251"/>
-      <c r="G14" s="252"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="250"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -5899,32 +5899,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="454" t="s">
+      <c r="B16" s="460" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="456" t="s">
+      <c r="C16" s="462" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="452" t="s">
+      <c r="D16" s="464" t="s">
         <v>260</v>
       </c>
-      <c r="E16" s="457" t="s">
+      <c r="E16" s="454" t="s">
         <v>266</v>
       </c>
-      <c r="F16" s="457" t="s">
+      <c r="F16" s="454" t="s">
         <v>262</v>
       </c>
-      <c r="G16" s="449" t="s">
+      <c r="G16" s="458" t="s">
         <v>263</v>
       </c>
-      <c r="H16" s="450"/>
+      <c r="H16" s="459"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="455"/>
-      <c r="C17" s="453"/>
-      <c r="D17" s="453"/>
-      <c r="E17" s="264"/>
-      <c r="F17" s="264"/>
+      <c r="B17" s="461"/>
+      <c r="C17" s="463"/>
+      <c r="D17" s="463"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="260"/>
       <c r="G17" s="22" t="s">
         <v>264</v>
       </c>
@@ -5947,14 +5947,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="451" t="s">
+      <c r="B19" s="466" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="251"/>
-      <c r="G19" s="252"/>
+      <c r="C19" s="249"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="249"/>
+      <c r="G19" s="250"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -5972,32 +5972,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="454" t="s">
+      <c r="B21" s="460" t="s">
         <v>258</v>
       </c>
-      <c r="C21" s="456" t="s">
+      <c r="C21" s="462" t="s">
         <v>259</v>
       </c>
-      <c r="D21" s="452" t="s">
+      <c r="D21" s="464" t="s">
         <v>260</v>
       </c>
-      <c r="E21" s="457" t="s">
+      <c r="E21" s="454" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="457" t="s">
+      <c r="F21" s="454" t="s">
         <v>262</v>
       </c>
-      <c r="G21" s="449" t="s">
+      <c r="G21" s="458" t="s">
         <v>263</v>
       </c>
-      <c r="H21" s="450"/>
+      <c r="H21" s="459"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="455"/>
-      <c r="C22" s="453"/>
-      <c r="D22" s="453"/>
-      <c r="E22" s="264"/>
-      <c r="F22" s="264"/>
+      <c r="B22" s="461"/>
+      <c r="C22" s="463"/>
+      <c r="D22" s="463"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="260"/>
       <c r="G22" s="47" t="s">
         <v>264</v>
       </c>
@@ -6018,18 +6018,32 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="459" t="s">
+      <c r="B24" s="449" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="460"/>
-      <c r="D24" s="460"/>
-      <c r="E24" s="460"/>
-      <c r="F24" s="460"/>
-      <c r="G24" s="396"/>
+      <c r="C24" s="450"/>
+      <c r="D24" s="450"/>
+      <c r="E24" s="450"/>
+      <c r="F24" s="450"/>
+      <c r="G24" s="399"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -6046,20 +6060,6 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -6088,11 +6088,11 @@
       <c r="B1" s="469" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="462"/>
-      <c r="D1" s="462"/>
-      <c r="E1" s="462"/>
-      <c r="F1" s="462"/>
-      <c r="G1" s="462"/>
+      <c r="C1" s="452"/>
+      <c r="D1" s="452"/>
+      <c r="E1" s="452"/>
+      <c r="F1" s="452"/>
+      <c r="G1" s="452"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -6119,11 +6119,11 @@
       <c r="B4" s="470" t="s">
         <v>271</v>
       </c>
-      <c r="C4" s="251"/>
-      <c r="D4" s="251"/>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="252"/>
+      <c r="C4" s="249"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
+      <c r="G4" s="250"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
@@ -6142,14 +6142,14 @@
       <c r="F5" s="468" t="s">
         <v>276</v>
       </c>
-      <c r="G5" s="251"/>
+      <c r="G5" s="249"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="264"/>
-      <c r="C6" s="453"/>
-      <c r="D6" s="453"/>
-      <c r="E6" s="453"/>
+      <c r="B6" s="260"/>
+      <c r="C6" s="463"/>
+      <c r="D6" s="463"/>
+      <c r="E6" s="463"/>
       <c r="F6" s="30" t="s">
         <v>264</v>
       </c>
@@ -6201,151 +6201,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="477" t="s">
+      <c r="A1" s="479" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="249"/>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
-      <c r="G1" s="249"/>
-      <c r="H1" s="249"/>
-      <c r="I1" s="249"/>
-      <c r="J1" s="249"/>
-      <c r="K1" s="249"/>
-      <c r="L1" s="249"/>
-      <c r="M1" s="249"/>
-      <c r="N1" s="249"/>
-      <c r="O1" s="478"/>
-      <c r="P1" s="249"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="249"/>
-      <c r="S1" s="249"/>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="472"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="254"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="479" t="s">
+      <c r="A2" s="477" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="249"/>
-      <c r="C2" s="479" t="s">
+      <c r="B2" s="254"/>
+      <c r="C2" s="477" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="475" t="s">
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="254"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="478" t="s">
         <v>278</v>
       </c>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="M2" s="249"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="254"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="476" t="s">
+      <c r="A3" s="474" t="s">
         <v>279</v>
       </c>
-      <c r="B3" s="249"/>
-      <c r="C3" s="476" t="s">
+      <c r="B3" s="254"/>
+      <c r="C3" s="474" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="249"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="249"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="249"/>
-      <c r="I3" s="249"/>
-      <c r="J3" s="476" t="s">
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="254"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="474" t="s">
         <v>280</v>
       </c>
-      <c r="K3" s="249"/>
-      <c r="L3" s="249"/>
-      <c r="M3" s="249"/>
-      <c r="N3" s="249"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="M3" s="254"/>
+      <c r="N3" s="254"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="476" t="s">
+      <c r="A4" s="474" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="249"/>
-      <c r="C4" s="476" t="s">
+      <c r="B4" s="254"/>
+      <c r="C4" s="474" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="474"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="M4" s="249"/>
-      <c r="N4" s="249"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="476"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="254"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="476" t="s">
+      <c r="A5" s="474" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="249"/>
-      <c r="C5" s="476" t="s">
+      <c r="B5" s="254"/>
+      <c r="C5" s="474" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="474"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="M5" s="249"/>
-      <c r="N5" s="249"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="254"/>
+      <c r="J5" s="476"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="254"/>
+      <c r="M5" s="254"/>
+      <c r="N5" s="254"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="476" t="s">
+      <c r="A6" s="474" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="249"/>
-      <c r="C6" s="476" t="s">
+      <c r="B6" s="254"/>
+      <c r="C6" s="474" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="249"/>
-      <c r="E6" s="249"/>
-      <c r="F6" s="249"/>
-      <c r="G6" s="249"/>
-      <c r="H6" s="249"/>
-      <c r="I6" s="249"/>
-      <c r="J6" s="476" t="s">
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="254"/>
+      <c r="J6" s="474" t="s">
         <v>285</v>
       </c>
-      <c r="K6" s="249"/>
-      <c r="L6" s="249"/>
-      <c r="M6" s="249"/>
-      <c r="N6" s="249"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="254"/>
+      <c r="M6" s="254"/>
+      <c r="N6" s="254"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
       <c r="A7" s="473" t="s">
         <v>286</v>
       </c>
-      <c r="B7" s="249"/>
-      <c r="C7" s="249"/>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
-      <c r="H7" s="249"/>
-      <c r="I7" s="249"/>
-      <c r="J7" s="249"/>
-      <c r="K7" s="249"/>
-      <c r="L7" s="249"/>
-      <c r="M7" s="249"/>
-      <c r="N7" s="249"/>
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -6374,120 +6374,138 @@
       <c r="A31" s="473" t="s">
         <v>287</v>
       </c>
-      <c r="B31" s="249"/>
-      <c r="C31" s="249"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="249"/>
-      <c r="I31" s="249"/>
-      <c r="J31" s="249"/>
-      <c r="K31" s="249"/>
-      <c r="L31" s="249"/>
-      <c r="M31" s="249"/>
-      <c r="N31" s="249"/>
+      <c r="B31" s="254"/>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="254"/>
+      <c r="K31" s="254"/>
+      <c r="L31" s="254"/>
+      <c r="M31" s="254"/>
+      <c r="N31" s="254"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="472" t="s">
+      <c r="A32" s="475" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="249"/>
-      <c r="C32" s="249"/>
-      <c r="D32" s="472" t="s">
+      <c r="B32" s="254"/>
+      <c r="C32" s="254"/>
+      <c r="D32" s="475" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="249"/>
-      <c r="F32" s="249"/>
-      <c r="G32" s="472" t="s">
+      <c r="E32" s="254"/>
+      <c r="F32" s="254"/>
+      <c r="G32" s="475" t="s">
         <v>288</v>
       </c>
-      <c r="H32" s="249"/>
-      <c r="I32" s="249"/>
-      <c r="J32" s="472" t="s">
+      <c r="H32" s="254"/>
+      <c r="I32" s="254"/>
+      <c r="J32" s="475" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="249"/>
-      <c r="L32" s="249"/>
-      <c r="M32" s="249"/>
+      <c r="K32" s="254"/>
+      <c r="L32" s="254"/>
+      <c r="M32" s="254"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="472" t="s">
+      <c r="A33" s="475" t="s">
         <v>289</v>
       </c>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="472" t="s">
+      <c r="B33" s="254"/>
+      <c r="C33" s="254"/>
+      <c r="D33" s="475" t="s">
         <v>290</v>
       </c>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="472" t="s">
+      <c r="E33" s="254"/>
+      <c r="F33" s="254"/>
+      <c r="G33" s="475" t="s">
         <v>291</v>
       </c>
-      <c r="H33" s="249"/>
-      <c r="I33" s="249"/>
-      <c r="J33" s="472" t="s">
+      <c r="H33" s="254"/>
+      <c r="I33" s="254"/>
+      <c r="J33" s="475" t="s">
         <v>292</v>
       </c>
-      <c r="K33" s="249"/>
-      <c r="L33" s="249"/>
-      <c r="M33" s="249"/>
+      <c r="K33" s="254"/>
+      <c r="L33" s="254"/>
+      <c r="M33" s="254"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="473" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="249"/>
-      <c r="C34" s="249"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="249"/>
-      <c r="I34" s="249"/>
-      <c r="J34" s="249"/>
-      <c r="K34" s="249"/>
-      <c r="L34" s="249"/>
-      <c r="M34" s="249"/>
-      <c r="N34" s="249"/>
+      <c r="B34" s="254"/>
+      <c r="C34" s="254"/>
+      <c r="D34" s="254"/>
+      <c r="E34" s="254"/>
+      <c r="F34" s="254"/>
+      <c r="G34" s="254"/>
+      <c r="H34" s="254"/>
+      <c r="I34" s="254"/>
+      <c r="J34" s="254"/>
+      <c r="K34" s="254"/>
+      <c r="L34" s="254"/>
+      <c r="M34" s="254"/>
+      <c r="N34" s="254"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="472" t="s">
+      <c r="A35" s="475" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="249"/>
-      <c r="C35" s="249"/>
-      <c r="F35" s="472" t="s">
+      <c r="B35" s="254"/>
+      <c r="C35" s="254"/>
+      <c r="F35" s="475" t="s">
         <v>293</v>
       </c>
-      <c r="G35" s="249"/>
-      <c r="H35" s="249"/>
-      <c r="K35" s="472" t="s">
+      <c r="G35" s="254"/>
+      <c r="H35" s="254"/>
+      <c r="K35" s="475" t="s">
         <v>294</v>
       </c>
-      <c r="L35" s="249"/>
-      <c r="M35" s="249"/>
+      <c r="L35" s="254"/>
+      <c r="M35" s="254"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="472" t="s">
+      <c r="A36" s="475" t="s">
         <v>289</v>
       </c>
-      <c r="B36" s="249"/>
-      <c r="C36" s="249"/>
-      <c r="F36" s="472" t="s">
+      <c r="B36" s="254"/>
+      <c r="C36" s="254"/>
+      <c r="F36" s="475" t="s">
         <v>295</v>
       </c>
-      <c r="G36" s="249"/>
-      <c r="H36" s="249"/>
-      <c r="K36" s="472" t="s">
+      <c r="G36" s="254"/>
+      <c r="H36" s="254"/>
+      <c r="K36" s="475" t="s">
         <v>296</v>
       </c>
-      <c r="L36" s="249"/>
-      <c r="M36" s="249"/>
+      <c r="L36" s="254"/>
+      <c r="M36" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -6504,24 +6522,6 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -7172,24 +7172,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:I19"/>
@@ -7199,6 +7181,24 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7247,7 +7247,7 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="322" t="str">
+      <c r="C4" s="303" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -7276,22 +7276,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="319" t="s">
+      <c r="C5" s="298" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="319" t="s">
+      <c r="D5" s="260"/>
+      <c r="E5" s="298" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="264"/>
-      <c r="G5" s="319" t="s">
+      <c r="F5" s="260"/>
+      <c r="G5" s="298" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="264"/>
-      <c r="I5" s="313" t="s">
+      <c r="H5" s="260"/>
+      <c r="I5" s="310" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="264"/>
+      <c r="J5" s="260"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -7305,23 +7305,23 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="297">
+      <c r="C6" s="292">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="312" t="s">
+      <c r="D6" s="250"/>
+      <c r="E6" s="296" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="252"/>
-      <c r="G6" s="296" t="s">
+      <c r="F6" s="250"/>
+      <c r="G6" s="294" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="252"/>
-      <c r="I6" s="299" t="s">
+      <c r="H6" s="250"/>
+      <c r="I6" s="318" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="252"/>
+      <c r="J6" s="250"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -7341,16 +7341,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="318" t="s">
+      <c r="C7" s="293" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="251"/>
-      <c r="E7" s="251"/>
-      <c r="F7" s="251"/>
-      <c r="G7" s="251"/>
-      <c r="H7" s="251"/>
-      <c r="I7" s="251"/>
-      <c r="J7" s="252"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="249"/>
+      <c r="H7" s="249"/>
+      <c r="I7" s="249"/>
+      <c r="J7" s="250"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -7367,22 +7367,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="300" t="s">
+      <c r="C8" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="252"/>
-      <c r="E8" s="300" t="s">
+      <c r="D8" s="250"/>
+      <c r="E8" s="295" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="252"/>
-      <c r="G8" s="300" t="s">
+      <c r="F8" s="250"/>
+      <c r="G8" s="295" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="252"/>
-      <c r="I8" s="317" t="s">
+      <c r="H8" s="250"/>
+      <c r="I8" s="314" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="252"/>
+      <c r="J8" s="250"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -7394,22 +7394,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="312">
+      <c r="C9" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="252"/>
-      <c r="E9" s="296" t="s">
+      <c r="D9" s="250"/>
+      <c r="E9" s="294" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="252"/>
-      <c r="G9" s="297">
+      <c r="F9" s="250"/>
+      <c r="G9" s="292">
         <v>80</v>
       </c>
-      <c r="H9" s="252"/>
-      <c r="I9" s="299">
+      <c r="H9" s="250"/>
+      <c r="I9" s="318">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="252"/>
+      <c r="J9" s="250"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -7421,16 +7421,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="318" t="s">
+      <c r="C10" s="293" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="251"/>
-      <c r="J10" s="252"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="249"/>
+      <c r="I10" s="249"/>
+      <c r="J10" s="250"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -7442,171 +7442,205 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="300" t="s">
+      <c r="C11" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="252"/>
-      <c r="E11" s="300" t="s">
+      <c r="D11" s="250"/>
+      <c r="E11" s="295" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="252"/>
-      <c r="G11" s="300" t="s">
+      <c r="F11" s="250"/>
+      <c r="G11" s="295" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="252"/>
-      <c r="I11" s="317" t="s">
+      <c r="H11" s="250"/>
+      <c r="I11" s="314" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="252"/>
+      <c r="J11" s="250"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="312">
+      <c r="C12" s="296">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="252"/>
-      <c r="E12" s="312">
+      <c r="D12" s="250"/>
+      <c r="E12" s="296">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="252"/>
-      <c r="G12" s="296">
+      <c r="F12" s="250"/>
+      <c r="G12" s="294">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="252"/>
-      <c r="I12" s="324">
+      <c r="H12" s="250"/>
+      <c r="I12" s="297">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="252"/>
+      <c r="J12" s="250"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="300" t="s">
+      <c r="C13" s="295" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="252"/>
-      <c r="E13" s="296" t="s">
+      <c r="D13" s="250"/>
+      <c r="E13" s="294" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="252"/>
-      <c r="G13" s="300" t="s">
+      <c r="F13" s="250"/>
+      <c r="G13" s="295" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="252"/>
-      <c r="I13" s="299" t="s">
+      <c r="H13" s="250"/>
+      <c r="I13" s="318" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="252"/>
+      <c r="J13" s="250"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="314" t="s">
+      <c r="C16" s="311" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="315"/>
-      <c r="E16" s="315"/>
-      <c r="F16" s="315"/>
-      <c r="G16" s="315"/>
-      <c r="H16" s="315"/>
-      <c r="I16" s="316"/>
+      <c r="D16" s="312"/>
+      <c r="E16" s="312"/>
+      <c r="F16" s="312"/>
+      <c r="G16" s="312"/>
+      <c r="H16" s="312"/>
+      <c r="I16" s="313"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="318" t="s">
+      <c r="C17" s="293" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="318" t="s">
+      <c r="D17" s="249"/>
+      <c r="E17" s="250"/>
+      <c r="F17" s="293" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="252"/>
-      <c r="H17" s="318" t="s">
+      <c r="G17" s="250"/>
+      <c r="H17" s="293" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="252"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="306" t="s">
+      <c r="C18" s="322" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="307"/>
-      <c r="E18" s="308"/>
-      <c r="F18" s="310">
+      <c r="D18" s="323"/>
+      <c r="E18" s="324"/>
+      <c r="F18" s="305">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="311"/>
-      <c r="H18" s="291">
+      <c r="G18" s="306"/>
+      <c r="H18" s="315">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="292"/>
+      <c r="I18" s="316"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="309" t="s">
+      <c r="C19" s="304" t="s">
         <v>300</v>
       </c>
-      <c r="D19" s="251"/>
-      <c r="E19" s="252"/>
-      <c r="F19" s="297">
+      <c r="D19" s="249"/>
+      <c r="E19" s="250"/>
+      <c r="F19" s="292">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="252"/>
-      <c r="H19" s="298">
+      <c r="G19" s="250"/>
+      <c r="H19" s="317">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="252"/>
+      <c r="I19" s="250"/>
     </row>
     <row r="20" spans="3:10" s="247" customFormat="1">
-      <c r="C20" s="293" t="s">
+      <c r="C20" s="307" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="294"/>
-      <c r="E20" s="295"/>
-      <c r="F20" s="320">
+      <c r="D20" s="308"/>
+      <c r="E20" s="309"/>
+      <c r="F20" s="299">
         <v>1.7411000000000001</v>
       </c>
-      <c r="G20" s="321"/>
-      <c r="H20" s="302">
+      <c r="G20" s="300"/>
+      <c r="H20" s="301">
         <f>F20/C12</f>
         <v>3.3460621167191638E-2</v>
       </c>
-      <c r="I20" s="303"/>
+      <c r="I20" s="302"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="293" t="s">
+      <c r="C21" s="307" t="s">
         <v>330</v>
       </c>
-      <c r="D21" s="294"/>
-      <c r="E21" s="295"/>
-      <c r="F21" s="304">
+      <c r="D21" s="308"/>
+      <c r="E21" s="309"/>
+      <c r="F21" s="320">
         <v>18.2121</v>
       </c>
-      <c r="G21" s="305"/>
-      <c r="H21" s="302">
+      <c r="G21" s="321"/>
+      <c r="H21" s="301">
         <f>F21/C12</f>
         <v>0.35000182571880467</v>
       </c>
-      <c r="I21" s="303"/>
+      <c r="I21" s="302"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="301" t="s">
+      <c r="C22" s="319" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="251"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="323">
+      <c r="D22" s="249"/>
+      <c r="E22" s="250"/>
+      <c r="F22" s="291">
         <f>SUM(F18:G21)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G22" s="252"/>
-      <c r="H22" s="298">
+      <c r="G22" s="250"/>
+      <c r="H22" s="317">
         <f>SUM(H18:I21)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="I22" s="252"/>
+      <c r="I22" s="250"/>
       <c r="J22" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="C17:E17"/>
@@ -7620,43 +7654,9 @@
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="H18:I18"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="H22:I22"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C18:E18"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7684,38 +7684,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="384" t="s">
+      <c r="B3" s="356" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="385"/>
-      <c r="D3" s="385"/>
-      <c r="E3" s="385"/>
-      <c r="F3" s="385"/>
-      <c r="G3" s="385"/>
-      <c r="H3" s="385"/>
-      <c r="I3" s="385"/>
-      <c r="L3" s="325" t="s">
+      <c r="C3" s="357"/>
+      <c r="D3" s="357"/>
+      <c r="E3" s="357"/>
+      <c r="F3" s="357"/>
+      <c r="G3" s="357"/>
+      <c r="H3" s="357"/>
+      <c r="I3" s="357"/>
+      <c r="L3" s="389" t="s">
         <v>84</v>
       </c>
-      <c r="M3" s="252"/>
+      <c r="M3" s="250"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="331" t="s">
+      <c r="B4" s="335" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="332"/>
-      <c r="D4" s="332"/>
-      <c r="E4" s="343" t="s">
+      <c r="C4" s="336"/>
+      <c r="D4" s="336"/>
+      <c r="E4" s="391" t="s">
         <v>297</v>
       </c>
       <c r="F4" s="285"/>
       <c r="G4" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="386" t="s">
+      <c r="H4" s="358" t="s">
         <v>298</v>
       </c>
-      <c r="I4" s="254"/>
+      <c r="I4" s="264"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>87</v>
@@ -7726,22 +7726,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="334" t="s">
+      <c r="B5" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C5" s="285"/>
       <c r="D5" s="285"/>
-      <c r="E5" s="326" t="s">
+      <c r="E5" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F5" s="285"/>
       <c r="G5" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="367" t="s">
+      <c r="H5" s="377" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="254"/>
+      <c r="I5" s="264"/>
       <c r="L5" s="153" t="s">
         <v>91</v>
       </c>
@@ -7751,57 +7751,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="334" t="s">
+      <c r="B6" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="285"/>
       <c r="D6" s="285"/>
-      <c r="E6" s="369">
+      <c r="E6" s="378">
         <v>52.034300000000002</v>
       </c>
       <c r="F6" s="285"/>
       <c r="G6" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="388" t="s">
+      <c r="H6" s="363" t="s">
         <v>299</v>
       </c>
-      <c r="I6" s="254"/>
+      <c r="I6" s="264"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D7" s="285"/>
-      <c r="E7" s="375" t="s">
+      <c r="E7" s="366" t="s">
         <v>135</v>
       </c>
       <c r="F7" s="285"/>
       <c r="G7" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H7" s="347">
+      <c r="H7" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I7" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I7" s="264"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="328" t="s">
+      <c r="C8" s="349" t="s">
         <v>98</v>
       </c>
       <c r="D8" s="285"/>
-      <c r="E8" s="366">
+      <c r="E8" s="376">
         <v>11173</v>
       </c>
       <c r="F8" s="285"/>
       <c r="G8" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="358"/>
-      <c r="I8" s="254"/>
+      <c r="H8" s="351"/>
+      <c r="I8" s="264"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -7809,7 +7809,7 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="345" t="s">
+      <c r="B9" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C9" s="285"/>
@@ -7818,7 +7818,7 @@
       <c r="F9" s="285"/>
       <c r="G9" s="285"/>
       <c r="H9" s="285"/>
-      <c r="I9" s="254"/>
+      <c r="I9" s="264"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -7826,7 +7826,7 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="327" t="s">
+      <c r="B10" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C10" s="285"/>
@@ -7849,11 +7849,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="354" t="s">
+      <c r="B11" s="386" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="355"/>
-      <c r="D11" s="355"/>
+      <c r="C11" s="387"/>
+      <c r="D11" s="387"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -7861,10 +7861,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="356">
+      <c r="G11" s="388">
         <v>1</v>
       </c>
-      <c r="H11" s="356"/>
+      <c r="H11" s="388"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -7873,7 +7873,7 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="365" t="s">
+      <c r="B12" s="375" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="285"/>
@@ -7886,7 +7886,7 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="330">
+      <c r="G12" s="329">
         <v>0.8</v>
       </c>
       <c r="H12" s="285"/>
@@ -7898,7 +7898,7 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="376" t="s">
+      <c r="B13" s="367" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="285"/>
@@ -7911,7 +7911,7 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="330">
+      <c r="G13" s="329">
         <v>0.6</v>
       </c>
       <c r="H13" s="285"/>
@@ -7927,11 +7927,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="357" t="s">
+      <c r="B14" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="260"/>
-      <c r="D14" s="260"/>
+      <c r="C14" s="252"/>
+      <c r="D14" s="252"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -7940,11 +7940,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="353">
+      <c r="G14" s="325">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="260"/>
+      <c r="H14" s="252"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -7968,7 +7968,7 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="351" t="s">
+      <c r="B16" s="343" t="s">
         <v>107</v>
       </c>
       <c r="C16" s="285"/>
@@ -7981,52 +7981,52 @@
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="331" t="s">
+      <c r="B17" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="332"/>
-      <c r="D17" s="332"/>
-      <c r="E17" s="329" t="s">
+      <c r="C17" s="336"/>
+      <c r="D17" s="336"/>
+      <c r="E17" s="327" t="s">
         <v>109</v>
       </c>
       <c r="F17" s="285"/>
       <c r="G17" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="341" t="s">
+      <c r="H17" s="359" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="254"/>
+      <c r="I17" s="264"/>
       <c r="K17" s="203" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="334" t="s">
+      <c r="B18" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="285"/>
       <c r="D18" s="285"/>
-      <c r="E18" s="326" t="s">
+      <c r="E18" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F18" s="285"/>
       <c r="G18" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H18" s="339" t="s">
+      <c r="H18" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="254"/>
+      <c r="I18" s="264"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="334" t="s">
+      <c r="B19" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="285"/>
       <c r="D19" s="285"/>
-      <c r="E19" s="368">
+      <c r="E19" s="371">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
@@ -8034,18 +8034,18 @@
       <c r="G19" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="360" t="s">
+      <c r="H19" s="330" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="254"/>
+      <c r="I19" s="264"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="328" t="s">
+      <c r="C20" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="285"/>
-      <c r="E20" s="374">
+      <c r="E20" s="355">
         <f>180000000</f>
         <v>180000000</v>
       </c>
@@ -8053,11 +8053,11 @@
       <c r="G20" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="363">
+      <c r="H20" s="331">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="254"/>
+      <c r="I20" s="264"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -8065,42 +8065,42 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="328" t="s">
+      <c r="C21" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D21" s="285"/>
-      <c r="E21" s="335" t="s">
+      <c r="E21" s="373" t="s">
         <v>115</v>
       </c>
       <c r="F21" s="285"/>
       <c r="G21" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="347">
+      <c r="H21" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I21" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I21" s="264"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="328" t="s">
+      <c r="C22" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D22" s="285"/>
-      <c r="E22" s="329" t="s">
+      <c r="E22" s="327" t="s">
         <v>96</v>
       </c>
       <c r="F22" s="285"/>
       <c r="G22" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H22" s="371"/>
-      <c r="I22" s="254"/>
+      <c r="H22" s="368"/>
+      <c r="I22" s="264"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="345" t="s">
+      <c r="B23" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C23" s="285"/>
@@ -8109,10 +8109,10 @@
       <c r="F23" s="285"/>
       <c r="G23" s="285"/>
       <c r="H23" s="285"/>
-      <c r="I23" s="254"/>
+      <c r="I23" s="264"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="327" t="s">
+      <c r="B24" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C24" s="285"/>
@@ -8130,7 +8130,7 @@
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="337" t="s">
         <v>105</v>
       </c>
       <c r="C25" s="285"/>
@@ -8143,7 +8143,7 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="344">
+      <c r="G25" s="338">
         <v>1</v>
       </c>
       <c r="H25" s="285"/>
@@ -8163,14 +8163,14 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="344">
+      <c r="G26" s="338">
         <v>0.8</v>
       </c>
       <c r="H26" s="285"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="377" t="s">
+      <c r="B27" s="364" t="s">
         <v>106</v>
       </c>
       <c r="C27" s="285"/>
@@ -8183,18 +8183,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="344">
+      <c r="G27" s="338">
         <v>0.6</v>
       </c>
       <c r="H27" s="285"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="357" t="s">
+      <c r="B28" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="260"/>
-      <c r="D28" s="260"/>
+      <c r="C28" s="252"/>
+      <c r="D28" s="252"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -8203,11 +8203,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="353">
+      <c r="G28" s="325">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="260"/>
+      <c r="H28" s="252"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -8221,7 +8221,7 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="351" t="s">
+      <c r="B30" s="343" t="s">
         <v>117</v>
       </c>
       <c r="C30" s="285"/>
@@ -8233,83 +8233,83 @@
       <c r="I30" s="285"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="331" t="s">
+      <c r="B31" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="332"/>
-      <c r="D31" s="332"/>
-      <c r="E31" s="329" t="s">
+      <c r="C31" s="336"/>
+      <c r="D31" s="336"/>
+      <c r="E31" s="327" t="s">
         <v>118</v>
       </c>
       <c r="F31" s="285"/>
       <c r="G31" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="341" t="s">
+      <c r="H31" s="359" t="s">
         <v>119</v>
       </c>
-      <c r="I31" s="254"/>
+      <c r="I31" s="264"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="334" t="s">
+      <c r="B32" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="285"/>
       <c r="D32" s="285"/>
-      <c r="E32" s="326" t="s">
+      <c r="E32" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F32" s="285"/>
       <c r="G32" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H32" s="339" t="s">
+      <c r="H32" s="362" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="254"/>
+      <c r="I32" s="264"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="334" t="s">
+      <c r="B33" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C33" s="285"/>
       <c r="D33" s="285"/>
-      <c r="E33" s="380">
+      <c r="E33" s="360">
         <v>1258.4000000000001</v>
       </c>
       <c r="F33" s="285"/>
       <c r="G33" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H33" s="339" t="s">
+      <c r="H33" s="362" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="254"/>
+      <c r="I33" s="264"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="328" t="s">
+      <c r="C34" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D34" s="285"/>
-      <c r="E34" s="374">
+      <c r="E34" s="355">
         <v>16900000</v>
       </c>
       <c r="F34" s="285"/>
       <c r="G34" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="363">
+      <c r="H34" s="331">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="254"/>
+      <c r="I34" s="264"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -8317,41 +8317,41 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="328" t="s">
+      <c r="C35" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D35" s="285"/>
-      <c r="E35" s="335" t="s">
+      <c r="E35" s="373" t="s">
         <v>115</v>
       </c>
       <c r="F35" s="285"/>
       <c r="G35" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H35" s="347">
+      <c r="H35" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I35" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I35" s="264"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="328" t="s">
+      <c r="C36" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="285"/>
-      <c r="E36" s="329" t="s">
+      <c r="E36" s="327" t="s">
         <v>96</v>
       </c>
       <c r="F36" s="285"/>
       <c r="G36" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="371"/>
-      <c r="I36" s="254"/>
+      <c r="H36" s="368"/>
+      <c r="I36" s="264"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="345" t="s">
+      <c r="B37" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C37" s="285"/>
@@ -8360,11 +8360,11 @@
       <c r="F37" s="285"/>
       <c r="G37" s="285"/>
       <c r="H37" s="285"/>
-      <c r="I37" s="254"/>
+      <c r="I37" s="264"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="327" t="s">
+      <c r="B38" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C38" s="285"/>
@@ -8382,7 +8382,7 @@
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="337" t="s">
         <v>105</v>
       </c>
       <c r="C39" s="285"/>
@@ -8394,7 +8394,7 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="344">
+      <c r="G39" s="338">
         <v>1</v>
       </c>
       <c r="H39" s="285"/>
@@ -8414,14 +8414,14 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="344">
+      <c r="G40" s="338">
         <v>0.8</v>
       </c>
       <c r="H40" s="285"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="377" t="s">
+      <c r="B41" s="364" t="s">
         <v>106</v>
       </c>
       <c r="C41" s="285"/>
@@ -8434,18 +8434,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="344">
+      <c r="G41" s="338">
         <v>0.6</v>
       </c>
       <c r="H41" s="285"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="357" t="s">
+      <c r="B42" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="260"/>
-      <c r="D42" s="260"/>
+      <c r="C42" s="252"/>
+      <c r="D42" s="252"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -8454,11 +8454,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="353">
+      <c r="G42" s="325">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="260"/>
+      <c r="H42" s="252"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -8472,7 +8472,7 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="387" t="s">
+      <c r="B44" s="361" t="s">
         <v>121</v>
       </c>
       <c r="C44" s="285"/>
@@ -8484,81 +8484,81 @@
       <c r="I44" s="285"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="332"/>
-      <c r="D45" s="332"/>
-      <c r="E45" s="326" t="s">
+      <c r="C45" s="336"/>
+      <c r="D45" s="336"/>
+      <c r="E45" s="350" t="s">
         <v>118</v>
       </c>
       <c r="F45" s="285"/>
       <c r="G45" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H45" s="341" t="s">
+      <c r="H45" s="359" t="s">
         <v>119</v>
       </c>
-      <c r="I45" s="254"/>
+      <c r="I45" s="264"/>
       <c r="K45" s="203" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="334" t="s">
+      <c r="B46" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C46" s="285"/>
       <c r="D46" s="285"/>
-      <c r="E46" s="326" t="s">
+      <c r="E46" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F46" s="285"/>
       <c r="G46" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="339" t="s">
+      <c r="H46" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="254"/>
+      <c r="I46" s="264"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="334" t="s">
+      <c r="B47" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C47" s="285"/>
       <c r="D47" s="285"/>
-      <c r="E47" s="368">
+      <c r="E47" s="371">
         <v>430.76</v>
       </c>
       <c r="F47" s="285"/>
       <c r="G47" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H47" s="360" t="s">
+      <c r="H47" s="330" t="s">
         <v>94</v>
       </c>
-      <c r="I47" s="254"/>
+      <c r="I47" s="264"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="328" t="s">
+      <c r="C48" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="285"/>
-      <c r="E48" s="350">
+      <c r="E48" s="326">
         <v>7120000</v>
       </c>
       <c r="F48" s="285"/>
       <c r="G48" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H48" s="364">
+      <c r="H48" s="346">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="254"/>
+      <c r="I48" s="264"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -8567,42 +8567,42 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="328" t="s">
+      <c r="C49" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="285"/>
-      <c r="E49" s="335" t="s">
+      <c r="E49" s="373" t="s">
         <v>115</v>
       </c>
       <c r="F49" s="285"/>
       <c r="G49" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H49" s="347">
+      <c r="H49" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I49" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I49" s="264"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="328" t="s">
+      <c r="C50" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="285"/>
-      <c r="E50" s="329" t="s">
+      <c r="E50" s="327" t="s">
         <v>123</v>
       </c>
       <c r="F50" s="285"/>
       <c r="G50" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H50" s="358"/>
-      <c r="I50" s="254"/>
+      <c r="H50" s="351"/>
+      <c r="I50" s="264"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="345" t="s">
+      <c r="B51" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C51" s="285"/>
@@ -8611,10 +8611,10 @@
       <c r="F51" s="285"/>
       <c r="G51" s="285"/>
       <c r="H51" s="285"/>
-      <c r="I51" s="254"/>
+      <c r="I51" s="264"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="327" t="s">
+      <c r="B52" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C52" s="285"/>
@@ -8632,7 +8632,7 @@
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="337" t="s">
         <v>105</v>
       </c>
       <c r="C53" s="285"/>
@@ -8644,7 +8644,7 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="330">
+      <c r="G53" s="329">
         <v>1</v>
       </c>
       <c r="H53" s="285"/>
@@ -8664,7 +8664,7 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="330">
+      <c r="G54" s="329">
         <v>0.8</v>
       </c>
       <c r="H54" s="285"/>
@@ -8684,18 +8684,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="330">
+      <c r="G55" s="329">
         <v>0.6</v>
       </c>
       <c r="H55" s="285"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="357" t="s">
+      <c r="B56" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="260"/>
-      <c r="D56" s="260"/>
+      <c r="C56" s="252"/>
+      <c r="D56" s="252"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -8704,11 +8704,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="353">
+      <c r="G56" s="325">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="260"/>
+      <c r="H56" s="252"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -8722,7 +8722,7 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="343" t="s">
         <v>124</v>
       </c>
       <c r="C58" s="285"/>
@@ -8735,80 +8735,80 @@
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="331" t="s">
+      <c r="B59" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="332"/>
-      <c r="D59" s="332"/>
-      <c r="E59" s="326" t="s">
+      <c r="C59" s="336"/>
+      <c r="D59" s="336"/>
+      <c r="E59" s="350" t="s">
         <v>125</v>
       </c>
       <c r="F59" s="285"/>
       <c r="G59" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H59" s="370" t="s">
+      <c r="H59" s="372" t="s">
         <v>126</v>
       </c>
-      <c r="I59" s="254"/>
+      <c r="I59" s="264"/>
       <c r="K59" s="203" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C60" s="285"/>
       <c r="D60" s="285"/>
-      <c r="E60" s="326" t="s">
+      <c r="E60" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F60" s="285"/>
       <c r="G60" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H60" s="339" t="s">
+      <c r="H60" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="254"/>
+      <c r="I60" s="264"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="334" t="s">
+      <c r="B61" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C61" s="285"/>
       <c r="D61" s="285"/>
-      <c r="E61" s="372">
+      <c r="E61" s="341">
         <v>626</v>
       </c>
       <c r="F61" s="285"/>
       <c r="G61" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H61" s="339" t="s">
+      <c r="H61" s="362" t="s">
         <v>128</v>
       </c>
-      <c r="I61" s="254"/>
+      <c r="I61" s="264"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="328" t="s">
+      <c r="C62" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D62" s="285"/>
-      <c r="E62" s="381">
+      <c r="E62" s="365">
         <v>10500000</v>
       </c>
       <c r="F62" s="285"/>
       <c r="G62" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H62" s="333">
+      <c r="H62" s="342">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="254"/>
+      <c r="I62" s="264"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -8817,42 +8817,42 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="328" t="s">
+      <c r="C63" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D63" s="285"/>
-      <c r="E63" s="378" t="s">
+      <c r="E63" s="369" t="s">
         <v>115</v>
       </c>
       <c r="F63" s="285"/>
       <c r="G63" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H63" s="347">
+      <c r="H63" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I63" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I63" s="264"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="328" t="s">
+      <c r="C64" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D64" s="285"/>
-      <c r="E64" s="329" t="s">
+      <c r="E64" s="327" t="s">
         <v>96</v>
       </c>
       <c r="F64" s="285"/>
       <c r="G64" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H64" s="358"/>
-      <c r="I64" s="254"/>
+      <c r="H64" s="351"/>
+      <c r="I64" s="264"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="345" t="s">
+      <c r="B65" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C65" s="285"/>
@@ -8861,10 +8861,10 @@
       <c r="F65" s="285"/>
       <c r="G65" s="285"/>
       <c r="H65" s="285"/>
-      <c r="I65" s="254"/>
+      <c r="I65" s="264"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="327" t="s">
+      <c r="B66" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C66" s="285"/>
@@ -8894,7 +8894,7 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="330">
+      <c r="G67" s="329">
         <v>1</v>
       </c>
       <c r="H67" s="285"/>
@@ -8913,14 +8913,14 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="330">
+      <c r="G68" s="329">
         <v>0.9</v>
       </c>
       <c r="H68" s="285"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="379" t="s">
+      <c r="B69" s="370" t="s">
         <v>106</v>
       </c>
       <c r="C69" s="285"/>
@@ -8933,18 +8933,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="330">
+      <c r="G69" s="329">
         <v>0.6</v>
       </c>
       <c r="H69" s="285"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="357" t="s">
+      <c r="B70" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C70" s="260"/>
-      <c r="D70" s="260"/>
+      <c r="C70" s="252"/>
+      <c r="D70" s="252"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -8953,11 +8953,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="353">
+      <c r="G70" s="325">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="260"/>
+      <c r="H70" s="252"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -8971,7 +8971,7 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="351" t="s">
+      <c r="B72" s="343" t="s">
         <v>130</v>
       </c>
       <c r="C72" s="285"/>
@@ -8983,51 +8983,51 @@
       <c r="I72" s="285"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="331" t="s">
+      <c r="B73" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="332"/>
-      <c r="D73" s="332"/>
-      <c r="E73" s="329" t="s">
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="327" t="s">
         <v>131</v>
       </c>
       <c r="F73" s="285"/>
       <c r="G73" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H73" s="341" t="s">
+      <c r="H73" s="359" t="s">
         <v>132</v>
       </c>
-      <c r="I73" s="254"/>
+      <c r="I73" s="264"/>
       <c r="K73" s="203" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="334" t="s">
+      <c r="B74" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C74" s="285"/>
       <c r="D74" s="285"/>
-      <c r="E74" s="329" t="s">
+      <c r="E74" s="327" t="s">
         <v>134</v>
       </c>
       <c r="F74" s="285"/>
       <c r="G74" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H74" s="339" t="s">
+      <c r="H74" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="254"/>
+      <c r="I74" s="264"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="334" t="s">
+      <c r="B75" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C75" s="285"/>
       <c r="D75" s="285"/>
-      <c r="E75" s="391">
+      <c r="E75" s="344">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
@@ -9035,48 +9035,48 @@
       <c r="G75" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H75" s="360" t="s">
+      <c r="H75" s="330" t="s">
         <v>94</v>
       </c>
-      <c r="I75" s="254"/>
+      <c r="I75" s="264"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="328" t="s">
+      <c r="C76" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D76" s="285"/>
-      <c r="E76" s="350">
+      <c r="E76" s="326">
         <v>60000000</v>
       </c>
       <c r="F76" s="285"/>
       <c r="G76" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H76" s="364">
+      <c r="H76" s="346">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="254"/>
+      <c r="I76" s="264"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="328" t="s">
+      <c r="C77" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D77" s="285"/>
-      <c r="E77" s="362" t="s">
+      <c r="E77" s="382" t="s">
         <v>115</v>
       </c>
       <c r="F77" s="285"/>
       <c r="G77" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H77" s="347">
+      <c r="H77" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I77" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I77" s="264"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="328" t="s">
+      <c r="C78" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D78" s="285"/>
-      <c r="E78" s="329" t="s">
+      <c r="E78" s="327" t="s">
         <v>135</v>
       </c>
       <c r="F78" s="285"/>
       <c r="G78" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H78" s="358"/>
-      <c r="I78" s="254"/>
+      <c r="H78" s="351"/>
+      <c r="I78" s="264"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C79" s="285"/>
@@ -9108,11 +9108,11 @@
       <c r="F79" s="285"/>
       <c r="G79" s="285"/>
       <c r="H79" s="285"/>
-      <c r="I79" s="254"/>
+      <c r="I79" s="264"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="327" t="s">
+      <c r="B80" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C80" s="285"/>
@@ -9130,7 +9130,7 @@
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="337" t="s">
+      <c r="B81" s="347" t="s">
         <v>129</v>
       </c>
       <c r="C81" s="285"/>
@@ -9143,14 +9143,14 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="330">
+      <c r="G81" s="329">
         <v>0.9</v>
       </c>
       <c r="H81" s="285"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="337" t="s">
+      <c r="B82" s="347" t="s">
         <v>116</v>
       </c>
       <c r="C82" s="285"/>
@@ -9163,7 +9163,7 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="330">
+      <c r="G82" s="329">
         <v>0.8</v>
       </c>
       <c r="H82" s="285"/>
@@ -9183,18 +9183,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="330">
+      <c r="G83" s="329">
         <v>0.6</v>
       </c>
       <c r="H83" s="285"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="357" t="s">
+      <c r="B84" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="260"/>
-      <c r="D84" s="260"/>
+      <c r="C84" s="252"/>
+      <c r="D84" s="252"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -9203,11 +9203,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="353">
+      <c r="G84" s="325">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="260"/>
+      <c r="H84" s="252"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -9221,7 +9221,7 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="351" t="s">
+      <c r="B86" s="343" t="s">
         <v>136</v>
       </c>
       <c r="C86" s="285"/>
@@ -9234,52 +9234,52 @@
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="331" t="s">
+      <c r="B87" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C87" s="332"/>
-      <c r="D87" s="332"/>
-      <c r="E87" s="326" t="s">
+      <c r="C87" s="336"/>
+      <c r="D87" s="336"/>
+      <c r="E87" s="350" t="s">
         <v>118</v>
       </c>
       <c r="F87" s="285"/>
       <c r="G87" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H87" s="373" t="str">
+      <c r="H87" s="374" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="254"/>
+      <c r="I87" s="264"/>
       <c r="K87" s="203" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="334" t="s">
+      <c r="B88" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C88" s="285"/>
       <c r="D88" s="285"/>
-      <c r="E88" s="326" t="s">
+      <c r="E88" s="350" t="s">
         <v>89</v>
       </c>
       <c r="F88" s="285"/>
       <c r="G88" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H88" s="339" t="s">
+      <c r="H88" s="362" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="254"/>
+      <c r="I88" s="264"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="334" t="s">
+      <c r="B89" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C89" s="285"/>
       <c r="D89" s="285"/>
-      <c r="E89" s="380">
+      <c r="E89" s="360">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
@@ -9287,29 +9287,29 @@
       <c r="G89" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H89" s="360" t="s">
+      <c r="H89" s="330" t="s">
         <v>94</v>
       </c>
-      <c r="I89" s="254"/>
+      <c r="I89" s="264"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="328" t="s">
+      <c r="C90" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D90" s="285"/>
-      <c r="E90" s="361">
+      <c r="E90" s="352">
         <v>43980000</v>
       </c>
       <c r="F90" s="285"/>
       <c r="G90" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H90" s="333">
+      <c r="H90" s="342">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="254"/>
+      <c r="I90" s="264"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -9317,41 +9317,41 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="328" t="s">
+      <c r="C91" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D91" s="285"/>
-      <c r="E91" s="336" t="s">
+      <c r="E91" s="380" t="s">
         <v>115</v>
       </c>
       <c r="F91" s="285"/>
       <c r="G91" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H91" s="347">
+      <c r="H91" s="332">
         <f ca="1">TODAY()</f>
-        <v>45845</v>
-      </c>
-      <c r="I91" s="254"/>
+        <v>45847</v>
+      </c>
+      <c r="I91" s="264"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="328" t="s">
+      <c r="C92" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D92" s="285"/>
-      <c r="E92" s="329" t="s">
+      <c r="E92" s="327" t="s">
         <v>96</v>
       </c>
       <c r="F92" s="285"/>
       <c r="G92" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H92" s="358"/>
-      <c r="I92" s="254"/>
+      <c r="H92" s="351"/>
+      <c r="I92" s="264"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="345" t="s">
+      <c r="B93" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C93" s="285"/>
@@ -9360,10 +9360,10 @@
       <c r="F93" s="285"/>
       <c r="G93" s="285"/>
       <c r="H93" s="285"/>
-      <c r="I93" s="254"/>
+      <c r="I93" s="264"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="327" t="s">
+      <c r="B94" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C94" s="285"/>
@@ -9381,7 +9381,7 @@
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="338" t="s">
+      <c r="B95" s="337" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="285"/>
@@ -9393,7 +9393,7 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="348">
+      <c r="G95" s="384">
         <v>1</v>
       </c>
       <c r="H95" s="285"/>
@@ -9413,14 +9413,14 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="348">
+      <c r="G96" s="384">
         <v>0.8</v>
       </c>
       <c r="H96" s="285"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="349" t="s">
+      <c r="B97" s="381" t="s">
         <v>106</v>
       </c>
       <c r="C97" s="285"/>
@@ -9433,7 +9433,7 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="330">
+      <c r="G97" s="329">
         <v>0.6</v>
       </c>
       <c r="H97" s="285"/>
@@ -9442,11 +9442,11 @@
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="357" t="s">
+      <c r="B98" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C98" s="260"/>
-      <c r="D98" s="260"/>
+      <c r="C98" s="252"/>
+      <c r="D98" s="252"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -9455,11 +9455,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="353">
+      <c r="G98" s="325">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="260"/>
+      <c r="H98" s="252"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -9480,7 +9480,7 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="389"/>
+      <c r="B100" s="345"/>
       <c r="C100" s="285"/>
       <c r="D100" s="285"/>
       <c r="E100" s="285"/>
@@ -9492,7 +9492,7 @@
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="351" t="s">
+      <c r="B101" s="343" t="s">
         <v>138</v>
       </c>
       <c r="C101" s="285"/>
@@ -9506,93 +9506,93 @@
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="331" t="s">
+      <c r="B102" s="335" t="s">
         <v>108</v>
       </c>
-      <c r="C102" s="332"/>
-      <c r="D102" s="332"/>
-      <c r="E102" s="342"/>
+      <c r="C102" s="336"/>
+      <c r="D102" s="336"/>
+      <c r="E102" s="390"/>
       <c r="F102" s="285"/>
       <c r="G102" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H102" s="390"/>
-      <c r="I102" s="254"/>
+      <c r="H102" s="328"/>
+      <c r="I102" s="264"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="334" t="s">
+      <c r="B103" s="333" t="s">
         <v>88</v>
       </c>
       <c r="C103" s="285"/>
       <c r="D103" s="285"/>
-      <c r="E103" s="352"/>
+      <c r="E103" s="385"/>
       <c r="F103" s="285"/>
       <c r="G103" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H103" s="359"/>
-      <c r="I103" s="254"/>
+      <c r="H103" s="379"/>
+      <c r="I103" s="264"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="334" t="s">
+      <c r="B104" s="333" t="s">
         <v>92</v>
       </c>
       <c r="C104" s="285"/>
       <c r="D104" s="285"/>
-      <c r="E104" s="372"/>
+      <c r="E104" s="341"/>
       <c r="F104" s="285"/>
       <c r="G104" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H104" s="383"/>
-      <c r="I104" s="254"/>
+      <c r="H104" s="354"/>
+      <c r="I104" s="264"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="328" t="s">
+      <c r="C105" s="349" t="s">
         <v>112</v>
       </c>
       <c r="D105" s="285"/>
-      <c r="E105" s="361"/>
+      <c r="E105" s="352"/>
       <c r="F105" s="285"/>
       <c r="G105" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H105" s="333"/>
-      <c r="I105" s="254"/>
+      <c r="H105" s="342"/>
+      <c r="I105" s="264"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="328" t="s">
+      <c r="C106" s="349" t="s">
         <v>114</v>
       </c>
       <c r="D106" s="285"/>
-      <c r="E106" s="336"/>
+      <c r="E106" s="380"/>
       <c r="F106" s="285"/>
       <c r="G106" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H106" s="346"/>
-      <c r="I106" s="254"/>
+      <c r="H106" s="383"/>
+      <c r="I106" s="264"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="328" t="s">
+      <c r="C107" s="349" t="s">
         <v>95</v>
       </c>
       <c r="D107" s="285"/>
-      <c r="E107" s="382"/>
+      <c r="E107" s="353"/>
       <c r="F107" s="285"/>
       <c r="G107" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H107" s="358"/>
-      <c r="I107" s="254"/>
+      <c r="H107" s="351"/>
+      <c r="I107" s="264"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="345" t="s">
+      <c r="B108" s="339" t="s">
         <v>100</v>
       </c>
       <c r="C108" s="285"/>
@@ -9601,10 +9601,10 @@
       <c r="F108" s="285"/>
       <c r="G108" s="285"/>
       <c r="H108" s="285"/>
-      <c r="I108" s="254"/>
+      <c r="I108" s="264"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="327" t="s">
+      <c r="B109" s="348" t="s">
         <v>101</v>
       </c>
       <c r="C109" s="285"/>
@@ -9622,35 +9622,35 @@
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="349" t="s">
+      <c r="B110" s="381" t="s">
         <v>105</v>
       </c>
       <c r="C110" s="285"/>
       <c r="D110" s="285"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="330"/>
+      <c r="G110" s="329"/>
       <c r="H110" s="285"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="381" t="s">
         <v>106</v>
       </c>
       <c r="C111" s="285"/>
       <c r="D111" s="285"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="330"/>
+      <c r="G111" s="329"/>
       <c r="H111" s="285"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="357" t="s">
+      <c r="B112" s="334" t="s">
         <v>82</v>
       </c>
-      <c r="C112" s="260"/>
-      <c r="D112" s="260"/>
+      <c r="C112" s="252"/>
+      <c r="D112" s="252"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -9659,15 +9659,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="353">
+      <c r="G112" s="325">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="260"/>
+      <c r="H112" s="252"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
     <mergeCell ref="G112:H112"/>
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="E22:F22"/>
@@ -9692,211 +9897,6 @@
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="H89:I89"/>
     <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="G109:H109"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="G39:H39"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10248,7 +10248,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="399"/>
+      <c r="E1" s="393"/>
       <c r="F1" s="394"/>
       <c r="G1" s="394"/>
       <c r="H1" s="394"/>
@@ -10808,8 +10808,8 @@
       <c r="A12" s="392" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="252"/>
-      <c r="C12" s="400" t="s">
+      <c r="B12" s="250"/>
+      <c r="C12" s="395" t="s">
         <v>173</v>
       </c>
       <c r="D12" s="394"/>
@@ -10837,8 +10837,8 @@
       <c r="A13" s="392" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="252"/>
-      <c r="C13" s="400" t="s">
+      <c r="B13" s="250"/>
+      <c r="C13" s="395" t="s">
         <v>176</v>
       </c>
       <c r="D13" s="394"/>
@@ -10867,8 +10867,8 @@
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="252"/>
-      <c r="C14" s="400" t="s">
+      <c r="B14" s="250"/>
+      <c r="C14" s="395" t="s">
         <v>178</v>
       </c>
       <c r="D14" s="394"/>
@@ -10896,8 +10896,8 @@
       <c r="A15" s="392" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="252"/>
-      <c r="C15" s="400" t="s">
+      <c r="B15" s="250"/>
+      <c r="C15" s="395" t="s">
         <v>180</v>
       </c>
       <c r="D15" s="394"/>
@@ -10925,8 +10925,8 @@
       <c r="A16" s="392" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="252"/>
-      <c r="C16" s="393" t="s">
+      <c r="B16" s="250"/>
+      <c r="C16" s="397" t="s">
         <v>182</v>
       </c>
       <c r="D16" s="394"/>
@@ -10949,8 +10949,8 @@
       <c r="A17" s="392" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="252"/>
-      <c r="C17" s="393" t="s">
+      <c r="B17" s="250"/>
+      <c r="C17" s="397" t="s">
         <v>183</v>
       </c>
       <c r="D17" s="394"/>
@@ -10982,8 +10982,8 @@
       <c r="A18" s="392" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="252"/>
-      <c r="C18" s="393" t="s">
+      <c r="B18" s="250"/>
+      <c r="C18" s="397" t="s">
         <v>186</v>
       </c>
       <c r="D18" s="394"/>
@@ -11010,8 +11010,8 @@
       <c r="A19" s="392" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="252"/>
-      <c r="C19" s="393" t="s">
+      <c r="B19" s="250"/>
+      <c r="C19" s="397" t="s">
         <v>188</v>
       </c>
       <c r="D19" s="394"/>
@@ -11039,8 +11039,8 @@
       <c r="A20" s="392" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="252"/>
-      <c r="C20" s="393" t="s">
+      <c r="B20" s="250"/>
+      <c r="C20" s="397" t="s">
         <v>190</v>
       </c>
       <c r="D20" s="394"/>
@@ -11068,8 +11068,8 @@
       <c r="A21" s="392" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="252"/>
-      <c r="C21" s="393" t="s">
+      <c r="B21" s="250"/>
+      <c r="C21" s="397" t="s">
         <v>192</v>
       </c>
       <c r="D21" s="394"/>
@@ -11097,8 +11097,8 @@
       <c r="A22" s="392" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="252"/>
-      <c r="C22" s="401" t="s">
+      <c r="B22" s="250"/>
+      <c r="C22" s="396" t="s">
         <v>194</v>
       </c>
       <c r="D22" s="394"/>
@@ -11112,7 +11112,7 @@
       <c r="L22" s="394"/>
       <c r="M22" s="394"/>
       <c r="N22" s="394"/>
-      <c r="O22" s="254"/>
+      <c r="O22" s="264"/>
       <c r="P22" s="147" t="s">
         <v>195</v>
       </c>
@@ -11126,8 +11126,8 @@
       <c r="A23" s="392" t="s">
         <v>193</v>
       </c>
-      <c r="B23" s="252"/>
-      <c r="C23" s="393" t="s">
+      <c r="B23" s="250"/>
+      <c r="C23" s="397" t="s">
         <v>196</v>
       </c>
       <c r="D23" s="394"/>
@@ -11155,8 +11155,8 @@
       <c r="A24" s="392" t="s">
         <v>195</v>
       </c>
-      <c r="B24" s="252"/>
-      <c r="C24" s="393" t="s">
+      <c r="B24" s="250"/>
+      <c r="C24" s="397" t="s">
         <v>198</v>
       </c>
       <c r="D24" s="394"/>
@@ -11184,8 +11184,8 @@
       <c r="A25" s="392" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="252"/>
-      <c r="C25" s="393" t="s">
+      <c r="B25" s="250"/>
+      <c r="C25" s="397" t="s">
         <v>200</v>
       </c>
       <c r="D25" s="394"/>
@@ -11205,21 +11205,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="395" t="s">
+      <c r="A26" s="398" t="s">
         <v>201</v>
       </c>
-      <c r="B26" s="396"/>
-      <c r="C26" s="397" t="s">
+      <c r="B26" s="399"/>
+      <c r="C26" s="400" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="398"/>
-      <c r="E26" s="398"/>
-      <c r="F26" s="398"/>
-      <c r="G26" s="398"/>
-      <c r="H26" s="398"/>
-      <c r="I26" s="398"/>
-      <c r="J26" s="398"/>
-      <c r="K26" s="398"/>
+      <c r="D26" s="401"/>
+      <c r="E26" s="401"/>
+      <c r="F26" s="401"/>
+      <c r="G26" s="401"/>
+      <c r="H26" s="401"/>
+      <c r="I26" s="401"/>
+      <c r="J26" s="401"/>
+      <c r="K26" s="401"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -11240,21 +11240,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -11271,6 +11256,21 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -11327,367 +11327,386 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="418" t="str">
+      <c r="C4" s="402" t="str">
         <f>'AREA UTIL'!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="418" t="s">
+      <c r="C5" s="402" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="403" t="s">
+      <c r="C6" s="407" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="249"/>
-      <c r="E6" s="249"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
       <c r="F6" s="404">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="249"/>
-      <c r="H6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="264"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="403" t="s">
+      <c r="C7" s="407" t="s">
         <v>204</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="254"/>
       <c r="F7" s="404">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="249"/>
-      <c r="H7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="264"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="403" t="s">
+      <c r="C8" s="407" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
+      <c r="D8" s="254"/>
+      <c r="E8" s="254"/>
       <c r="F8" s="404">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="249"/>
-      <c r="H8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="264"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="403" t="s">
+      <c r="C9" s="407" t="s">
         <v>206</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="406">
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="403">
         <v>6</v>
       </c>
-      <c r="G9" s="249"/>
-      <c r="H9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="264"/>
       <c r="J9" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="403" t="s">
+      <c r="C10" s="407" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="406">
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="403">
         <v>1</v>
       </c>
-      <c r="G10" s="249"/>
-      <c r="H10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="264"/>
       <c r="J10" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="403" t="s">
+      <c r="C11" s="407" t="s">
         <v>199</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="415">
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="418">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="249"/>
-      <c r="H11" s="254"/>
+      <c r="G11" s="254"/>
+      <c r="H11" s="264"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="403" t="s">
+      <c r="C12" s="407" t="s">
         <v>209</v>
       </c>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="406">
+      <c r="D12" s="254"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="403">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="249"/>
-      <c r="H12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="264"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="403" t="s">
+      <c r="C13" s="407" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
+      <c r="D13" s="254"/>
+      <c r="E13" s="254"/>
       <c r="F13" s="404">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="249"/>
-      <c r="H13" s="254"/>
+      <c r="G13" s="254"/>
+      <c r="H13" s="264"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="413" t="s">
+      <c r="C14" s="415" t="s">
         <v>210</v>
       </c>
-      <c r="D14" s="251"/>
-      <c r="E14" s="251"/>
-      <c r="F14" s="412">
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="411">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="251"/>
-      <c r="H14" s="252"/>
-      <c r="J14" s="416">
+      <c r="G14" s="249"/>
+      <c r="H14" s="250"/>
+      <c r="J14" s="409">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="249"/>
-      <c r="L14" s="249"/>
+      <c r="K14" s="254"/>
+      <c r="L14" s="254"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="420"/>
-      <c r="D15" s="249"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="249"/>
-      <c r="H15" s="249"/>
+      <c r="C15" s="413"/>
+      <c r="D15" s="254"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="254"/>
+      <c r="G15" s="254"/>
+      <c r="H15" s="254"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="402" t="s">
+      <c r="C16" s="417" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="249"/>
-      <c r="E16" s="249"/>
-      <c r="F16" s="249"/>
-      <c r="G16" s="249"/>
-      <c r="H16" s="249"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="254"/>
+      <c r="F16" s="254"/>
+      <c r="G16" s="254"/>
+      <c r="H16" s="254"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="403" t="s">
+      <c r="C17" s="407" t="s">
         <v>212</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="406">
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="403">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="249"/>
-      <c r="H17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="264"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="403" t="s">
+      <c r="C18" s="407" t="s">
         <v>213</v>
       </c>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
       <c r="F18" s="404">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="249"/>
-      <c r="H18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="264"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="403" t="s">
+      <c r="C19" s="407" t="s">
         <v>214</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
+      <c r="D19" s="254"/>
+      <c r="E19" s="254"/>
       <c r="F19" s="404">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="249"/>
-      <c r="H19" s="254"/>
+      <c r="G19" s="254"/>
+      <c r="H19" s="264"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="413" t="s">
+      <c r="C20" s="415" t="s">
         <v>215</v>
       </c>
-      <c r="D20" s="251"/>
-      <c r="E20" s="251"/>
-      <c r="F20" s="412">
+      <c r="D20" s="249"/>
+      <c r="E20" s="249"/>
+      <c r="F20" s="411">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="251"/>
-      <c r="H20" s="252"/>
+      <c r="G20" s="249"/>
+      <c r="H20" s="250"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="407"/>
-      <c r="D21" s="249"/>
-      <c r="E21" s="249"/>
-      <c r="F21" s="410"/>
-      <c r="G21" s="249"/>
-      <c r="H21" s="249"/>
+      <c r="C21" s="408"/>
+      <c r="D21" s="254"/>
+      <c r="E21" s="254"/>
+      <c r="F21" s="405"/>
+      <c r="G21" s="254"/>
+      <c r="H21" s="254"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="407"/>
-      <c r="D22" s="249"/>
-      <c r="E22" s="249"/>
-      <c r="F22" s="410"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="249"/>
+      <c r="C22" s="408"/>
+      <c r="D22" s="254"/>
+      <c r="E22" s="254"/>
+      <c r="F22" s="405"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="254"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="407"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="419"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="249"/>
+      <c r="C23" s="408"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="412"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="417" t="s">
+      <c r="C24" s="410" t="s">
         <v>216</v>
       </c>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249"/>
-      <c r="H24" s="249"/>
+      <c r="D24" s="254"/>
+      <c r="E24" s="254"/>
+      <c r="F24" s="254"/>
+      <c r="G24" s="254"/>
+      <c r="H24" s="254"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="408" t="s">
+      <c r="C25" s="406" t="s">
         <v>217</v>
       </c>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="411">
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="414">
         <v>2000000</v>
       </c>
-      <c r="G25" s="249"/>
-      <c r="H25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="264"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="408" t="s">
+      <c r="C26" s="406" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="405">
+      <c r="D26" s="254"/>
+      <c r="E26" s="254"/>
+      <c r="F26" s="419">
         <v>0.8</v>
       </c>
-      <c r="G26" s="249"/>
-      <c r="H26" s="254"/>
+      <c r="G26" s="254"/>
+      <c r="H26" s="264"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="408" t="s">
+      <c r="C27" s="406" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="411">
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="414">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="249"/>
-      <c r="H27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="264"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="414" t="s">
+      <c r="C28" s="416" t="s">
         <v>215</v>
       </c>
-      <c r="D28" s="251"/>
-      <c r="E28" s="251"/>
-      <c r="F28" s="409">
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
+      <c r="F28" s="420">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="251"/>
-      <c r="H28" s="252"/>
+      <c r="G28" s="249"/>
+      <c r="H28" s="250"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="402" t="s">
+      <c r="C31" s="417" t="s">
         <v>220</v>
       </c>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="249"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="403" t="s">
+      <c r="C32" s="407" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="249"/>
-      <c r="E32" s="249"/>
+      <c r="D32" s="254"/>
+      <c r="E32" s="254"/>
       <c r="F32" s="404">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="249"/>
-      <c r="H32" s="254"/>
+      <c r="G32" s="254"/>
+      <c r="H32" s="264"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="403" t="s">
+      <c r="C33" s="407" t="s">
         <v>222</v>
       </c>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
+      <c r="D33" s="254"/>
+      <c r="E33" s="254"/>
       <c r="F33" s="404">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="249"/>
-      <c r="H33" s="254"/>
+      <c r="G33" s="254"/>
+      <c r="H33" s="264"/>
     </row>
     <row r="34" spans="3:8" ht="15" customHeight="1">
-      <c r="C34" s="413" t="s">
+      <c r="C34" s="415" t="s">
         <v>223</v>
       </c>
-      <c r="D34" s="251"/>
-      <c r="E34" s="251"/>
-      <c r="F34" s="412">
+      <c r="D34" s="249"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="411">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="251"/>
-      <c r="H34" s="252"/>
+      <c r="G34" s="249"/>
+      <c r="H34" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F19:H19"/>
@@ -11704,34 +11723,15 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -11749,169 +11749,178 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="418" t="str">
+      <c r="C5" s="402" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="418" t="s">
+      <c r="C6" s="402" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="249"/>
-      <c r="E6" s="249"/>
-      <c r="F6" s="249"/>
-      <c r="G6" s="249"/>
-      <c r="H6" s="249"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="403" t="s">
+      <c r="C7" s="407" t="s">
         <v>225</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="254"/>
       <c r="F7" s="422">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="249"/>
-      <c r="H7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="264"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="403" t="s">
+      <c r="C8" s="407" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="406">
+      <c r="D8" s="254"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="403">
         <v>36</v>
       </c>
-      <c r="G8" s="249"/>
-      <c r="H8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="264"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="403" t="s">
+      <c r="C9" s="407" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
       <c r="F9" s="421">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="249"/>
-      <c r="H9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="264"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="403" t="s">
+      <c r="C10" s="407" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
       <c r="F10" s="404">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="249"/>
-      <c r="H10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="264"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="413" t="s">
+      <c r="C11" s="415" t="s">
         <v>229</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="412">
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="411">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="251"/>
-      <c r="H11" s="252"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="250"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="402" t="s">
+      <c r="C13" s="417" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="249"/>
+      <c r="D13" s="254"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="254"/>
+      <c r="G13" s="254"/>
+      <c r="H13" s="254"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="403" t="s">
+      <c r="C14" s="407" t="s">
         <v>225</v>
       </c>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
       <c r="F14" s="422">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="249"/>
-      <c r="H14" s="254"/>
+      <c r="G14" s="254"/>
+      <c r="H14" s="264"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="403" t="s">
+      <c r="C15" s="407" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="249"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="406">
+      <c r="D15" s="254"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="403">
         <v>36</v>
       </c>
-      <c r="G15" s="249"/>
-      <c r="H15" s="254"/>
+      <c r="G15" s="254"/>
+      <c r="H15" s="264"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="403" t="s">
+      <c r="C16" s="407" t="s">
         <v>227</v>
       </c>
-      <c r="D16" s="249"/>
-      <c r="E16" s="249"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="254"/>
       <c r="F16" s="421">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="249"/>
-      <c r="H16" s="254"/>
+      <c r="G16" s="254"/>
+      <c r="H16" s="264"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="403" t="s">
+      <c r="C17" s="407" t="s">
         <v>228</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
       <c r="F17" s="404">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="249"/>
-      <c r="H17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="264"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="413" t="s">
+      <c r="C18" s="415" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="412">
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="411">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="251"/>
-      <c r="H18" s="252"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -11926,15 +11935,6 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\automacao_laudo\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\1. AVALIAÇÕES\01. AVALIAÇÕES SICREDI\01. RURAL\07. JULHO\Processo Nº 12941255 - JOELSON SOUSA JUNIOR\PEÇAS TÉCNICAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12135" windowHeight="6855" tabRatio="874" firstSheet="6" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="342">
   <si>
     <t>LAUDO DE AVALIAÇÃO Nº 435420</t>
   </si>
@@ -1072,6 +1072,39 @@
   </si>
   <si>
     <t xml:space="preserve">Área De Reserva Legal </t>
+  </si>
+  <si>
+    <t>VALORES ALCANÇADOS NA AVALIAÇÃO</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>(ha)</t>
+  </si>
+  <si>
+    <t>Valor Mínimo (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor Médio </t>
+  </si>
+  <si>
+    <t>(R$)</t>
+  </si>
+  <si>
+    <t>Valor Máximo (R$)</t>
+  </si>
+  <si>
+    <t>Fazenda</t>
+  </si>
+  <si>
+    <t>Valor Venal Adotado</t>
+  </si>
+  <si>
+    <t>Valor de Liquidação Forçada Adotado</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1125,7 @@
     <numFmt numFmtId="172" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="75">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1552,8 +1585,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1620,8 +1670,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F1E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9DDC8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="52">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -2256,6 +2318,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2264,7 +2400,7 @@
     <xf numFmtId="9" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="480">
+  <cellXfs count="496">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3007,15 +3143,30 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3027,33 +3178,6 @@
     </xf>
     <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3075,35 +3199,47 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3538,6 +3674,54 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="73" fillId="12" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="74" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="74" fillId="12" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7247,7 +7431,7 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="303" t="str">
+      <c r="C4" s="295" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
@@ -7276,19 +7460,19 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="298" t="s">
+      <c r="C5" s="311" t="s">
         <v>61</v>
       </c>
       <c r="D5" s="260"/>
-      <c r="E5" s="298" t="s">
+      <c r="E5" s="311" t="s">
         <v>62</v>
       </c>
       <c r="F5" s="260"/>
-      <c r="G5" s="298" t="s">
+      <c r="G5" s="311" t="s">
         <v>63</v>
       </c>
       <c r="H5" s="260"/>
-      <c r="I5" s="310" t="s">
+      <c r="I5" s="306" t="s">
         <v>64</v>
       </c>
       <c r="J5" s="260"/>
@@ -7305,20 +7489,20 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="292">
+      <c r="C6" s="298">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
       <c r="D6" s="250"/>
-      <c r="E6" s="296" t="s">
+      <c r="E6" s="301" t="s">
         <v>66</v>
       </c>
       <c r="F6" s="250"/>
-      <c r="G6" s="294" t="s">
+      <c r="G6" s="299" t="s">
         <v>67</v>
       </c>
       <c r="H6" s="250"/>
-      <c r="I6" s="318" t="s">
+      <c r="I6" s="313" t="s">
         <v>67</v>
       </c>
       <c r="J6" s="250"/>
@@ -7341,7 +7525,7 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="293" t="s">
+      <c r="C7" s="296" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="249"/>
@@ -7367,19 +7551,19 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="295" t="s">
+      <c r="C8" s="300" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="250"/>
-      <c r="E8" s="295" t="s">
+      <c r="E8" s="300" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="250"/>
-      <c r="G8" s="295" t="s">
+      <c r="G8" s="300" t="s">
         <v>71</v>
       </c>
       <c r="H8" s="250"/>
-      <c r="I8" s="314" t="s">
+      <c r="I8" s="310" t="s">
         <v>72</v>
       </c>
       <c r="J8" s="250"/>
@@ -7394,19 +7578,19 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="296">
+      <c r="C9" s="301">
         <v>52.034300000000002</v>
       </c>
       <c r="D9" s="250"/>
-      <c r="E9" s="294" t="s">
+      <c r="E9" s="299" t="s">
         <v>302</v>
       </c>
       <c r="F9" s="250"/>
-      <c r="G9" s="292">
+      <c r="G9" s="298">
         <v>80</v>
       </c>
       <c r="H9" s="250"/>
-      <c r="I9" s="318">
+      <c r="I9" s="313">
         <v>0.65039999999999998</v>
       </c>
       <c r="J9" s="250"/>
@@ -7421,7 +7605,7 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="293" t="s">
+      <c r="C10" s="296" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="249"/>
@@ -7442,163 +7626,163 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="295" t="s">
+      <c r="C11" s="300" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="250"/>
-      <c r="E11" s="295" t="s">
+      <c r="E11" s="300" t="s">
         <v>62</v>
       </c>
       <c r="F11" s="250"/>
-      <c r="G11" s="295" t="s">
+      <c r="G11" s="300" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="250"/>
-      <c r="I11" s="314" t="s">
+      <c r="I11" s="310" t="s">
         <v>74</v>
       </c>
       <c r="J11" s="250"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="296">
+      <c r="C12" s="301">
         <v>52.034300000000002</v>
       </c>
       <c r="D12" s="250"/>
-      <c r="E12" s="296">
+      <c r="E12" s="301">
         <v>18.2121</v>
       </c>
       <c r="F12" s="250"/>
-      <c r="G12" s="294">
+      <c r="G12" s="299">
         <v>1.7411000000000001</v>
       </c>
       <c r="H12" s="250"/>
-      <c r="I12" s="297">
+      <c r="I12" s="302">
         <v>9.7928999999999995</v>
       </c>
       <c r="J12" s="250"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="295" t="s">
+      <c r="C13" s="300" t="s">
         <v>75</v>
       </c>
       <c r="D13" s="250"/>
-      <c r="E13" s="294" t="s">
+      <c r="E13" s="299" t="s">
         <v>76</v>
       </c>
       <c r="F13" s="250"/>
-      <c r="G13" s="295" t="s">
+      <c r="G13" s="300" t="s">
         <v>77</v>
       </c>
       <c r="H13" s="250"/>
-      <c r="I13" s="318" t="s">
+      <c r="I13" s="313" t="s">
         <v>78</v>
       </c>
       <c r="J13" s="250"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="311" t="s">
+      <c r="C16" s="307" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="312"/>
-      <c r="E16" s="312"/>
-      <c r="F16" s="312"/>
-      <c r="G16" s="312"/>
-      <c r="H16" s="312"/>
-      <c r="I16" s="313"/>
+      <c r="D16" s="308"/>
+      <c r="E16" s="308"/>
+      <c r="F16" s="308"/>
+      <c r="G16" s="308"/>
+      <c r="H16" s="308"/>
+      <c r="I16" s="309"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="293" t="s">
+      <c r="C17" s="296" t="s">
         <v>79</v>
       </c>
       <c r="D17" s="249"/>
       <c r="E17" s="250"/>
-      <c r="F17" s="293" t="s">
+      <c r="F17" s="296" t="s">
         <v>80</v>
       </c>
       <c r="G17" s="250"/>
-      <c r="H17" s="293" t="s">
+      <c r="H17" s="296" t="s">
         <v>81</v>
       </c>
       <c r="I17" s="250"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="322" t="s">
+      <c r="C18" s="317" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="323"/>
-      <c r="E18" s="324"/>
-      <c r="F18" s="305">
+      <c r="D18" s="318"/>
+      <c r="E18" s="319"/>
+      <c r="F18" s="321">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="306"/>
-      <c r="H18" s="315">
+      <c r="G18" s="322"/>
+      <c r="H18" s="323">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="316"/>
+      <c r="I18" s="324"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="304" t="s">
+      <c r="C19" s="320" t="s">
         <v>300</v>
       </c>
       <c r="D19" s="249"/>
       <c r="E19" s="250"/>
-      <c r="F19" s="292">
+      <c r="F19" s="298">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
       <c r="G19" s="250"/>
-      <c r="H19" s="317">
+      <c r="H19" s="312">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
       <c r="I19" s="250"/>
     </row>
     <row r="20" spans="3:10" s="247" customFormat="1">
-      <c r="C20" s="307" t="s">
+      <c r="C20" s="303" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="308"/>
-      <c r="E20" s="309"/>
-      <c r="F20" s="299">
+      <c r="D20" s="304"/>
+      <c r="E20" s="305"/>
+      <c r="F20" s="291">
         <v>1.7411000000000001</v>
       </c>
-      <c r="G20" s="300"/>
-      <c r="H20" s="301">
+      <c r="G20" s="292"/>
+      <c r="H20" s="293">
         <f>F20/C12</f>
         <v>3.3460621167191638E-2</v>
       </c>
-      <c r="I20" s="302"/>
+      <c r="I20" s="294"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="307" t="s">
+      <c r="C21" s="303" t="s">
         <v>330</v>
       </c>
-      <c r="D21" s="308"/>
-      <c r="E21" s="309"/>
-      <c r="F21" s="320">
+      <c r="D21" s="304"/>
+      <c r="E21" s="305"/>
+      <c r="F21" s="315">
         <v>18.2121</v>
       </c>
-      <c r="G21" s="321"/>
-      <c r="H21" s="301">
+      <c r="G21" s="316"/>
+      <c r="H21" s="293">
         <f>F21/C12</f>
         <v>0.35000182571880467</v>
       </c>
-      <c r="I21" s="302"/>
+      <c r="I21" s="294"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="319" t="s">
+      <c r="C22" s="314" t="s">
         <v>82</v>
       </c>
       <c r="D22" s="249"/>
       <c r="E22" s="250"/>
-      <c r="F22" s="291">
+      <c r="F22" s="297">
         <f>SUM(F18:G21)</f>
         <v>52.034300000000002</v>
       </c>
       <c r="G22" s="250"/>
-      <c r="H22" s="317">
+      <c r="H22" s="312">
         <f>SUM(H18:I21)</f>
         <v>0.99999999999999989</v>
       </c>
@@ -7607,6 +7791,13 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="I13:J13"/>
@@ -7616,23 +7807,10 @@
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C10:J10"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="I8:J8"/>
@@ -7641,6 +7819,16 @@
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C10:J10"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="C17:E17"/>
@@ -7653,10 +7841,6 @@
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="H22:I22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7783,7 +7967,7 @@
       </c>
       <c r="H7" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I7" s="264"/>
     </row>
@@ -8078,7 +8262,7 @@
       </c>
       <c r="H21" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I21" s="264"/>
     </row>
@@ -8330,7 +8514,7 @@
       </c>
       <c r="H35" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I35" s="264"/>
     </row>
@@ -8580,7 +8764,7 @@
       </c>
       <c r="H49" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I49" s="264"/>
     </row>
@@ -8830,7 +9014,7 @@
       </c>
       <c r="H63" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I63" s="264"/>
     </row>
@@ -9074,7 +9258,7 @@
       </c>
       <c r="H77" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I77" s="264"/>
       <c r="K77" s="221">
@@ -9330,7 +9514,7 @@
       </c>
       <c r="H91" s="332">
         <f ca="1">TODAY()</f>
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="I91" s="264"/>
     </row>
@@ -11319,11 +11503,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C4:L34"/>
+  <dimension ref="C4:N40"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
@@ -11651,7 +11838,7 @@
       <c r="G32" s="254"/>
       <c r="H32" s="264"/>
     </row>
-    <row r="33" spans="3:8">
+    <row r="33" spans="3:14">
       <c r="C33" s="407" t="s">
         <v>222</v>
       </c>
@@ -11664,7 +11851,7 @@
       <c r="G33" s="254"/>
       <c r="H33" s="264"/>
     </row>
-    <row r="34" spans="3:8" ht="15" customHeight="1">
+    <row r="34" spans="3:14" ht="15" customHeight="1" thickBot="1">
       <c r="C34" s="415" t="s">
         <v>223</v>
       </c>
@@ -11677,8 +11864,98 @@
       <c r="G34" s="249"/>
       <c r="H34" s="250"/>
     </row>
+    <row r="35" spans="3:14" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
+      <c r="J35" s="486" t="s">
+        <v>331</v>
+      </c>
+      <c r="K35" s="487"/>
+      <c r="L35" s="487"/>
+      <c r="M35" s="487"/>
+      <c r="N35" s="488"/>
+    </row>
+    <row r="36" spans="3:14" ht="31.5" customHeight="1">
+      <c r="J36" s="489" t="s">
+        <v>332</v>
+      </c>
+      <c r="K36" s="480" t="s">
+        <v>333</v>
+      </c>
+      <c r="L36" s="489" t="s">
+        <v>335</v>
+      </c>
+      <c r="M36" s="480" t="s">
+        <v>336</v>
+      </c>
+      <c r="N36" s="489" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="3:14" ht="16.5" thickBot="1">
+      <c r="J37" s="490"/>
+      <c r="K37" s="481" t="s">
+        <v>334</v>
+      </c>
+      <c r="L37" s="490"/>
+      <c r="M37" s="481" t="s">
+        <v>337</v>
+      </c>
+      <c r="N37" s="490"/>
+    </row>
+    <row r="38" spans="3:14" ht="16.5" thickBot="1">
+      <c r="J38" s="482" t="s">
+        <v>339</v>
+      </c>
+      <c r="K38" s="483">
+        <f>AMOSTRAS!E6</f>
+        <v>52.034300000000002</v>
+      </c>
+      <c r="L38" s="484">
+        <f>F34*0.8</f>
+        <v>1829058.0243864001</v>
+      </c>
+      <c r="M38" s="485">
+        <f>F34</f>
+        <v>2286322.530483</v>
+      </c>
+      <c r="N38" s="484">
+        <f>F34 + (F34*0.8)</f>
+        <v>4115380.5548694003</v>
+      </c>
+    </row>
+    <row r="39" spans="3:14" ht="36" customHeight="1" thickBot="1">
+      <c r="J39" s="491" t="s">
+        <v>340</v>
+      </c>
+      <c r="K39" s="492"/>
+      <c r="L39" s="493"/>
+      <c r="M39" s="494">
+        <f>F34</f>
+        <v>2286322.530483</v>
+      </c>
+      <c r="N39" s="495"/>
+    </row>
+    <row r="40" spans="3:14" ht="36" customHeight="1" thickBot="1">
+      <c r="J40" s="491" t="s">
+        <v>341</v>
+      </c>
+      <c r="K40" s="492"/>
+      <c r="L40" s="493"/>
+      <c r="M40" s="494">
+        <f>LIQUIDAÇÃO!F18</f>
+        <v>1115738.3182275943</v>
+      </c>
+      <c r="N40" s="495"/>
+    </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="61">
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="J35:N35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="M39:N39"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="F32:H32"/>
@@ -11734,7 +12011,7 @@
     <mergeCell ref="C22:E22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
+++ b/models/LAUDO DE AVALIAÇÃO N° 12941255 - MAURICIO MIYASAKI.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\1. AVALIAÇÕES\01. AVALIAÇÕES SICREDI\01. RURAL\07. JULHO\Processo Nº 12941255 - JOELSON SOUSA JUNIOR\PEÇAS TÉCNICAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\automacao_laudo\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12135" windowHeight="6855" tabRatio="874" firstSheet="6" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12135" windowHeight="6855" tabRatio="874" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA DO LAUDO" sheetId="1" r:id="rId1"/>
@@ -3034,41 +3034,99 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="73" fillId="12" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3083,46 +3141,6 @@
     </xf>
     <xf numFmtId="170" fontId="51" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="50" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3143,10 +3161,37 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="55" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3155,38 +3200,32 @@
     <xf numFmtId="10" fontId="55" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="56" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3199,76 +3238,43 @@
     <xf numFmtId="0" fontId="57" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="55" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="53" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="56" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="64" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3278,61 +3284,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3342,122 +3444,29 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3467,122 +3476,134 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="74" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="74" fillId="12" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="12" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="47" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="172" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="45" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3590,18 +3611,69 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="40" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="43" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="40" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="39" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="39" fontId="46" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="45" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="46" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3612,35 +3684,11 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3656,73 +3704,25 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="69" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="70" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="62" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="73" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="73" fillId="12" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="11" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="12" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="12" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="74" fillId="12" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="74" fillId="12" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4141,34 +4141,34 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="3" spans="2:13">
-      <c r="B3" s="248" t="s">
+      <c r="B3" s="256" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="257"/>
-      <c r="D3" s="257"/>
-      <c r="E3" s="257"/>
-      <c r="F3" s="257"/>
-      <c r="G3" s="257"/>
-      <c r="H3" s="257"/>
-      <c r="I3" s="257"/>
-      <c r="J3" s="257"/>
-      <c r="K3" s="257"/>
-      <c r="L3" s="257"/>
-      <c r="M3" s="258"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="263"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="M3" s="268"/>
     </row>
     <row r="4" spans="2:13">
-      <c r="B4" s="270"/>
-      <c r="C4" s="252"/>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="M4" s="260"/>
+      <c r="B4" s="269"/>
+      <c r="C4" s="266"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="266"/>
+      <c r="I4" s="266"/>
+      <c r="J4" s="266"/>
+      <c r="K4" s="266"/>
+      <c r="L4" s="266"/>
+      <c r="M4" s="270"/>
     </row>
     <row r="5" spans="2:13" ht="19.5" customHeight="1">
       <c r="B5" s="122"/>
@@ -4199,100 +4199,100 @@
       <c r="M6" s="107"/>
     </row>
     <row r="7" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B7" s="253" t="s">
+      <c r="B7" s="254" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="254"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="271"/>
-      <c r="F7" s="254"/>
-      <c r="G7" s="254"/>
-      <c r="H7" s="254"/>
-      <c r="I7" s="254"/>
-      <c r="J7" s="254"/>
-      <c r="K7" s="254"/>
-      <c r="L7" s="254"/>
-      <c r="M7" s="264"/>
+      <c r="C7" s="255"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="255"/>
+      <c r="I7" s="255"/>
+      <c r="J7" s="255"/>
+      <c r="K7" s="255"/>
+      <c r="L7" s="255"/>
+      <c r="M7" s="260"/>
     </row>
     <row r="8" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B8" s="253" t="s">
+      <c r="B8" s="254" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="254"/>
-      <c r="D8" s="254"/>
-      <c r="E8" s="271"/>
-      <c r="F8" s="254"/>
-      <c r="G8" s="254"/>
-      <c r="H8" s="254"/>
-      <c r="I8" s="254"/>
-      <c r="J8" s="254"/>
-      <c r="K8" s="254"/>
-      <c r="L8" s="254"/>
-      <c r="M8" s="264"/>
+      <c r="C8" s="255"/>
+      <c r="D8" s="255"/>
+      <c r="E8" s="259"/>
+      <c r="F8" s="255"/>
+      <c r="G8" s="255"/>
+      <c r="H8" s="255"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="255"/>
+      <c r="K8" s="255"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="260"/>
     </row>
     <row r="9" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B9" s="253" t="s">
+      <c r="B9" s="254" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="254"/>
-      <c r="D9" s="254"/>
-      <c r="E9" s="271"/>
-      <c r="F9" s="254"/>
-      <c r="G9" s="254"/>
-      <c r="H9" s="254"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="254"/>
-      <c r="L9" s="254"/>
-      <c r="M9" s="264"/>
+      <c r="C9" s="255"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="259"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
+      <c r="M9" s="260"/>
     </row>
     <row r="10" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B10" s="253" t="s">
+      <c r="B10" s="254" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="271"/>
-      <c r="F10" s="254"/>
-      <c r="G10" s="254"/>
-      <c r="H10" s="254"/>
-      <c r="I10" s="254"/>
-      <c r="J10" s="254"/>
-      <c r="K10" s="254"/>
-      <c r="L10" s="254"/>
-      <c r="M10" s="264"/>
+      <c r="C10" s="255"/>
+      <c r="D10" s="255"/>
+      <c r="E10" s="259"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
+      <c r="M10" s="260"/>
     </row>
     <row r="11" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B11" s="253" t="s">
+      <c r="B11" s="254" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="254"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="271"/>
-      <c r="F11" s="254"/>
-      <c r="G11" s="254"/>
-      <c r="H11" s="254"/>
-      <c r="I11" s="254"/>
-      <c r="J11" s="254"/>
-      <c r="K11" s="254"/>
-      <c r="L11" s="254"/>
-      <c r="M11" s="264"/>
+      <c r="C11" s="255"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
+      <c r="M11" s="260"/>
     </row>
     <row r="12" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B12" s="253" t="s">
+      <c r="B12" s="254" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="254"/>
-      <c r="D12" s="254"/>
-      <c r="E12" s="271"/>
-      <c r="F12" s="254"/>
-      <c r="G12" s="254"/>
-      <c r="H12" s="254"/>
-      <c r="I12" s="254"/>
-      <c r="J12" s="254"/>
-      <c r="K12" s="254"/>
-      <c r="L12" s="254"/>
-      <c r="M12" s="264"/>
+      <c r="C12" s="255"/>
+      <c r="D12" s="255"/>
+      <c r="E12" s="259"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="255"/>
+      <c r="H12" s="255"/>
+      <c r="I12" s="255"/>
+      <c r="J12" s="255"/>
+      <c r="K12" s="255"/>
+      <c r="L12" s="255"/>
+      <c r="M12" s="260"/>
     </row>
     <row r="13" spans="2:13" ht="17.25" customHeight="1">
       <c r="B13" s="108"/>
@@ -4351,20 +4351,20 @@
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B17" s="282" t="s">
+      <c r="B17" s="261" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="254"/>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
-      <c r="J17" s="254"/>
-      <c r="K17" s="254"/>
-      <c r="L17" s="254"/>
-      <c r="M17" s="254"/>
+      <c r="C17" s="255"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="255"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="255"/>
+      <c r="I17" s="255"/>
+      <c r="J17" s="255"/>
+      <c r="K17" s="255"/>
+      <c r="L17" s="255"/>
+      <c r="M17" s="255"/>
     </row>
     <row r="18" spans="2:13" ht="19.5" customHeight="1">
       <c r="B18" s="111"/>
@@ -4381,150 +4381,150 @@
       <c r="M18" s="111"/>
     </row>
     <row r="19" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B19" s="283" t="s">
+      <c r="B19" s="262" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="257"/>
-      <c r="D19" s="257"/>
-      <c r="E19" s="281"/>
-      <c r="F19" s="257"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="257"/>
-      <c r="J19" s="257"/>
-      <c r="K19" s="257"/>
-      <c r="L19" s="257"/>
-      <c r="M19" s="258"/>
+      <c r="C19" s="263"/>
+      <c r="D19" s="263"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="263"/>
+      <c r="G19" s="263"/>
+      <c r="H19" s="263"/>
+      <c r="I19" s="263"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="263"/>
+      <c r="L19" s="263"/>
+      <c r="M19" s="268"/>
     </row>
     <row r="20" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B20" s="253" t="s">
+      <c r="B20" s="254" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="254"/>
-      <c r="D20" s="254"/>
-      <c r="E20" s="271"/>
-      <c r="F20" s="254"/>
-      <c r="G20" s="254"/>
-      <c r="H20" s="254"/>
-      <c r="I20" s="254"/>
-      <c r="J20" s="254"/>
-      <c r="K20" s="254"/>
-      <c r="L20" s="254"/>
-      <c r="M20" s="264"/>
+      <c r="C20" s="255"/>
+      <c r="D20" s="255"/>
+      <c r="E20" s="259"/>
+      <c r="F20" s="255"/>
+      <c r="G20" s="255"/>
+      <c r="H20" s="255"/>
+      <c r="I20" s="255"/>
+      <c r="J20" s="255"/>
+      <c r="K20" s="255"/>
+      <c r="L20" s="255"/>
+      <c r="M20" s="260"/>
     </row>
     <row r="21" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B21" s="253" t="s">
+      <c r="B21" s="254" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="254"/>
-      <c r="D21" s="254"/>
-      <c r="E21" s="271"/>
-      <c r="F21" s="254"/>
-      <c r="G21" s="254"/>
-      <c r="H21" s="254"/>
-      <c r="I21" s="254"/>
-      <c r="J21" s="254"/>
-      <c r="K21" s="254"/>
-      <c r="L21" s="254"/>
-      <c r="M21" s="264"/>
+      <c r="C21" s="255"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="255"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="255"/>
+      <c r="I21" s="255"/>
+      <c r="J21" s="255"/>
+      <c r="K21" s="255"/>
+      <c r="L21" s="255"/>
+      <c r="M21" s="260"/>
     </row>
     <row r="22" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B22" s="278" t="s">
+      <c r="B22" s="277" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="252"/>
-      <c r="D22" s="252"/>
-      <c r="E22" s="272"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
-      <c r="H22" s="252"/>
-      <c r="I22" s="252"/>
-      <c r="J22" s="252"/>
+      <c r="C22" s="266"/>
+      <c r="D22" s="266"/>
+      <c r="E22" s="271"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="266"/>
+      <c r="J22" s="266"/>
       <c r="K22" s="112"/>
-      <c r="L22" s="276"/>
-      <c r="M22" s="260"/>
+      <c r="L22" s="275"/>
+      <c r="M22" s="270"/>
     </row>
     <row r="23" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B23" s="248" t="s">
+      <c r="B23" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="249"/>
-      <c r="I23" s="249"/>
-      <c r="J23" s="249"/>
-      <c r="K23" s="249"/>
-      <c r="L23" s="249"/>
-      <c r="M23" s="250"/>
+      <c r="C23" s="257"/>
+      <c r="D23" s="257"/>
+      <c r="E23" s="257"/>
+      <c r="F23" s="257"/>
+      <c r="G23" s="257"/>
+      <c r="H23" s="257"/>
+      <c r="I23" s="257"/>
+      <c r="J23" s="257"/>
+      <c r="K23" s="257"/>
+      <c r="L23" s="257"/>
+      <c r="M23" s="258"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="261" t="s">
+      <c r="B24" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="249"/>
-      <c r="D24" s="250"/>
-      <c r="E24" s="261" t="s">
+      <c r="C24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="249"/>
-      <c r="G24" s="250"/>
-      <c r="H24" s="261" t="s">
+      <c r="F24" s="257"/>
+      <c r="G24" s="258"/>
+      <c r="H24" s="264" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="249"/>
-      <c r="J24" s="250"/>
-      <c r="K24" s="261" t="s">
+      <c r="I24" s="257"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="249"/>
-      <c r="M24" s="250"/>
+      <c r="L24" s="257"/>
+      <c r="M24" s="258"/>
     </row>
     <row r="25" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B25" s="275"/>
-      <c r="C25" s="257"/>
-      <c r="D25" s="258"/>
-      <c r="E25" s="262"/>
-      <c r="F25" s="254"/>
-      <c r="G25" s="254"/>
-      <c r="H25" s="256"/>
-      <c r="I25" s="257"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="277"/>
-      <c r="L25" s="257"/>
-      <c r="M25" s="258"/>
+      <c r="B25" s="274"/>
+      <c r="C25" s="263"/>
+      <c r="D25" s="268"/>
+      <c r="E25" s="283"/>
+      <c r="F25" s="255"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="281"/>
+      <c r="I25" s="263"/>
+      <c r="J25" s="268"/>
+      <c r="K25" s="276"/>
+      <c r="L25" s="263"/>
+      <c r="M25" s="268"/>
     </row>
     <row r="26" spans="2:13" ht="17.25" customHeight="1">
-      <c r="B26" s="273"/>
-      <c r="C26" s="252"/>
-      <c r="D26" s="260"/>
-      <c r="E26" s="280"/>
-      <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
-      <c r="H26" s="274"/>
-      <c r="I26" s="252"/>
-      <c r="J26" s="260"/>
-      <c r="K26" s="279"/>
-      <c r="L26" s="252"/>
-      <c r="M26" s="260"/>
+      <c r="B26" s="272"/>
+      <c r="C26" s="266"/>
+      <c r="D26" s="270"/>
+      <c r="E26" s="265"/>
+      <c r="F26" s="266"/>
+      <c r="G26" s="266"/>
+      <c r="H26" s="273"/>
+      <c r="I26" s="266"/>
+      <c r="J26" s="270"/>
+      <c r="K26" s="278"/>
+      <c r="L26" s="266"/>
+      <c r="M26" s="270"/>
     </row>
     <row r="27" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B27" s="248" t="s">
+      <c r="B27" s="256" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="249"/>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="249"/>
-      <c r="I27" s="249"/>
-      <c r="J27" s="249"/>
-      <c r="K27" s="249"/>
-      <c r="L27" s="249"/>
-      <c r="M27" s="250"/>
+      <c r="C27" s="257"/>
+      <c r="D27" s="257"/>
+      <c r="E27" s="257"/>
+      <c r="F27" s="257"/>
+      <c r="G27" s="257"/>
+      <c r="H27" s="257"/>
+      <c r="I27" s="257"/>
+      <c r="J27" s="257"/>
+      <c r="K27" s="257"/>
+      <c r="L27" s="257"/>
+      <c r="M27" s="258"/>
     </row>
     <row r="28" spans="2:13" ht="17.25" customHeight="1">
       <c r="B28" s="113"/>
@@ -4611,100 +4611,100 @@
       <c r="M33" s="121"/>
     </row>
     <row r="34" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B34" s="248" t="s">
+      <c r="B34" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="249"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="249"/>
-      <c r="I34" s="249"/>
-      <c r="J34" s="249"/>
-      <c r="K34" s="249"/>
-      <c r="L34" s="249"/>
-      <c r="M34" s="250"/>
+      <c r="C34" s="257"/>
+      <c r="D34" s="257"/>
+      <c r="E34" s="257"/>
+      <c r="F34" s="257"/>
+      <c r="G34" s="257"/>
+      <c r="H34" s="257"/>
+      <c r="I34" s="257"/>
+      <c r="J34" s="257"/>
+      <c r="K34" s="257"/>
+      <c r="L34" s="257"/>
+      <c r="M34" s="258"/>
     </row>
     <row r="35" spans="2:13" ht="15" customHeight="1">
-      <c r="B35" s="261" t="s">
+      <c r="B35" s="264" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="249"/>
-      <c r="D35" s="249"/>
-      <c r="E35" s="250"/>
-      <c r="F35" s="261" t="s">
+      <c r="C35" s="257"/>
+      <c r="D35" s="257"/>
+      <c r="E35" s="258"/>
+      <c r="F35" s="264" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="249"/>
-      <c r="H35" s="249"/>
-      <c r="I35" s="250"/>
-      <c r="J35" s="261" t="s">
+      <c r="G35" s="257"/>
+      <c r="H35" s="257"/>
+      <c r="I35" s="258"/>
+      <c r="J35" s="264" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="249"/>
-      <c r="L35" s="249"/>
-      <c r="M35" s="250"/>
+      <c r="K35" s="257"/>
+      <c r="L35" s="257"/>
+      <c r="M35" s="258"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1">
-      <c r="B36" s="267"/>
-      <c r="C36" s="257"/>
-      <c r="D36" s="257"/>
-      <c r="E36" s="257"/>
-      <c r="F36" s="268"/>
-      <c r="G36" s="257"/>
-      <c r="H36" s="257"/>
-      <c r="I36" s="257"/>
-      <c r="J36" s="269"/>
-      <c r="K36" s="257"/>
-      <c r="L36" s="257"/>
-      <c r="M36" s="258"/>
+      <c r="B36" s="287"/>
+      <c r="C36" s="263"/>
+      <c r="D36" s="263"/>
+      <c r="E36" s="263"/>
+      <c r="F36" s="288"/>
+      <c r="G36" s="263"/>
+      <c r="H36" s="263"/>
+      <c r="I36" s="263"/>
+      <c r="J36" s="289"/>
+      <c r="K36" s="263"/>
+      <c r="L36" s="263"/>
+      <c r="M36" s="268"/>
     </row>
     <row r="37" spans="2:13" ht="15" customHeight="1">
-      <c r="B37" s="255"/>
-      <c r="C37" s="254"/>
-      <c r="D37" s="254"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="266"/>
-      <c r="G37" s="254"/>
-      <c r="H37" s="254"/>
-      <c r="I37" s="254"/>
-      <c r="J37" s="263"/>
-      <c r="K37" s="254"/>
-      <c r="L37" s="254"/>
-      <c r="M37" s="264"/>
+      <c r="B37" s="280"/>
+      <c r="C37" s="255"/>
+      <c r="D37" s="255"/>
+      <c r="E37" s="255"/>
+      <c r="F37" s="286"/>
+      <c r="G37" s="255"/>
+      <c r="H37" s="255"/>
+      <c r="I37" s="255"/>
+      <c r="J37" s="284"/>
+      <c r="K37" s="255"/>
+      <c r="L37" s="255"/>
+      <c r="M37" s="260"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1">
-      <c r="B38" s="265" t="s">
+      <c r="B38" s="285" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="252"/>
-      <c r="D38" s="252"/>
-      <c r="E38" s="252"/>
-      <c r="F38" s="251"/>
-      <c r="G38" s="252"/>
-      <c r="H38" s="252"/>
-      <c r="I38" s="252"/>
-      <c r="J38" s="259"/>
-      <c r="K38" s="252"/>
-      <c r="L38" s="252"/>
-      <c r="M38" s="260"/>
+      <c r="C38" s="266"/>
+      <c r="D38" s="266"/>
+      <c r="E38" s="266"/>
+      <c r="F38" s="279"/>
+      <c r="G38" s="266"/>
+      <c r="H38" s="266"/>
+      <c r="I38" s="266"/>
+      <c r="J38" s="282"/>
+      <c r="K38" s="266"/>
+      <c r="L38" s="266"/>
+      <c r="M38" s="270"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" customHeight="1">
-      <c r="B39" s="248" t="s">
+      <c r="B39" s="256" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="249"/>
-      <c r="I39" s="249"/>
-      <c r="J39" s="249"/>
-      <c r="K39" s="249"/>
-      <c r="L39" s="249"/>
-      <c r="M39" s="250"/>
+      <c r="C39" s="257"/>
+      <c r="D39" s="257"/>
+      <c r="E39" s="257"/>
+      <c r="F39" s="257"/>
+      <c r="G39" s="257"/>
+      <c r="H39" s="257"/>
+      <c r="I39" s="257"/>
+      <c r="J39" s="257"/>
+      <c r="K39" s="257"/>
+      <c r="L39" s="257"/>
+      <c r="M39" s="258"/>
     </row>
     <row r="40" spans="2:13" ht="19.5" customHeight="1">
       <c r="B40" s="122"/>
@@ -4820,25 +4820,22 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B39:M39"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="B34:M34"/>
     <mergeCell ref="B3:M4"/>
     <mergeCell ref="E7:M7"/>
     <mergeCell ref="H24:J24"/>
@@ -4855,22 +4852,25 @@
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="K26:M26"/>
-    <mergeCell ref="B39:M39"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="B34:M34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4911,37 +4911,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="423" t="s">
+      <c r="B2" s="455" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="424"/>
-      <c r="D2" s="424"/>
-      <c r="E2" s="424"/>
-      <c r="F2" s="424"/>
-      <c r="G2" s="424"/>
-      <c r="H2" s="424"/>
-      <c r="I2" s="424"/>
-      <c r="J2" s="424"/>
-      <c r="K2" s="424"/>
-      <c r="L2" s="424"/>
-      <c r="M2" s="424"/>
-      <c r="N2" s="424"/>
-      <c r="O2" s="424"/>
-      <c r="P2" s="424"/>
-      <c r="Q2" s="424"/>
-      <c r="R2" s="424"/>
-      <c r="S2" s="424"/>
-      <c r="T2" s="424"/>
-      <c r="U2" s="424"/>
-      <c r="V2" s="424"/>
-      <c r="W2" s="424"/>
-      <c r="X2" s="424"/>
-      <c r="Y2" s="424"/>
-      <c r="Z2" s="424"/>
-      <c r="AA2" s="424"/>
-      <c r="AB2" s="424"/>
-      <c r="AC2" s="424"/>
-      <c r="AD2" s="424"/>
+      <c r="C2" s="456"/>
+      <c r="D2" s="456"/>
+      <c r="E2" s="456"/>
+      <c r="F2" s="456"/>
+      <c r="G2" s="456"/>
+      <c r="H2" s="456"/>
+      <c r="I2" s="456"/>
+      <c r="J2" s="456"/>
+      <c r="K2" s="456"/>
+      <c r="L2" s="456"/>
+      <c r="M2" s="456"/>
+      <c r="N2" s="456"/>
+      <c r="O2" s="456"/>
+      <c r="P2" s="456"/>
+      <c r="Q2" s="456"/>
+      <c r="R2" s="456"/>
+      <c r="S2" s="456"/>
+      <c r="T2" s="456"/>
+      <c r="U2" s="456"/>
+      <c r="V2" s="456"/>
+      <c r="W2" s="456"/>
+      <c r="X2" s="456"/>
+      <c r="Y2" s="456"/>
+      <c r="Z2" s="456"/>
+      <c r="AA2" s="456"/>
+      <c r="AB2" s="456"/>
+      <c r="AC2" s="456"/>
+      <c r="AD2" s="456"/>
     </row>
     <row r="3" spans="2:31" s="68" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B3" s="69"/>
@@ -5068,39 +5068,39 @@
       <c r="AD9" s="98"/>
     </row>
     <row r="10" spans="2:31" ht="15" customHeight="1">
-      <c r="B10" s="441">
+      <c r="B10" s="447">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="C10" s="426"/>
-      <c r="D10" s="426"/>
-      <c r="E10" s="426"/>
-      <c r="F10" s="426"/>
-      <c r="G10" s="426"/>
+      <c r="C10" s="443"/>
+      <c r="D10" s="443"/>
+      <c r="E10" s="443"/>
+      <c r="F10" s="443"/>
+      <c r="G10" s="443"/>
       <c r="H10" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="I10" s="440">
+      <c r="I10" s="464">
         <f>IF(B10=" ","",W11)</f>
         <v>13189.81</v>
       </c>
-      <c r="J10" s="426"/>
-      <c r="K10" s="426"/>
-      <c r="L10" s="426"/>
-      <c r="M10" s="426"/>
-      <c r="N10" s="426"/>
-      <c r="O10" s="426"/>
-      <c r="P10" s="426"/>
+      <c r="J10" s="443"/>
+      <c r="K10" s="443"/>
+      <c r="L10" s="443"/>
+      <c r="M10" s="443"/>
+      <c r="N10" s="443"/>
+      <c r="O10" s="443"/>
+      <c r="P10" s="443"/>
       <c r="Q10" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="R10" s="425">
+      <c r="R10" s="442">
         <f>IF(B10=" ","",I10*B10)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S10" s="426"/>
-      <c r="T10" s="426"/>
-      <c r="U10" s="426"/>
+      <c r="S10" s="443"/>
+      <c r="T10" s="443"/>
+      <c r="U10" s="443"/>
       <c r="V10" s="48"/>
       <c r="W10" s="48" t="s">
         <v>238</v>
@@ -5135,13 +5135,13 @@
       <c r="T11" s="48"/>
       <c r="U11" s="99"/>
       <c r="V11" s="48"/>
-      <c r="W11" s="425">
+      <c r="W11" s="442">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="X11" s="426"/>
-      <c r="Y11" s="426"/>
-      <c r="Z11" s="426"/>
+      <c r="X11" s="443"/>
+      <c r="Y11" s="443"/>
+      <c r="Z11" s="443"/>
       <c r="AA11" s="48"/>
       <c r="AB11" s="48"/>
       <c r="AC11" s="98"/>
@@ -5168,13 +5168,13 @@
       <c r="Q12" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="R12" s="437">
+      <c r="R12" s="462">
         <f>R10</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="S12" s="426"/>
-      <c r="T12" s="426"/>
-      <c r="U12" s="426"/>
+      <c r="S12" s="443"/>
+      <c r="T12" s="443"/>
+      <c r="U12" s="443"/>
       <c r="V12" s="48"/>
       <c r="W12" s="48"/>
       <c r="X12" s="48"/>
@@ -5194,10 +5194,10 @@
         <v>239</v>
       </c>
       <c r="V14" s="80"/>
-      <c r="W14" s="430"/>
-      <c r="X14" s="426"/>
-      <c r="Y14" s="426"/>
-      <c r="Z14" s="426"/>
+      <c r="W14" s="454"/>
+      <c r="X14" s="443"/>
+      <c r="Y14" s="443"/>
+      <c r="Z14" s="443"/>
       <c r="AA14" s="70"/>
       <c r="AB14" s="70"/>
       <c r="AC14" s="81"/>
@@ -5223,38 +5223,38 @@
       <c r="AD15" s="83"/>
     </row>
     <row r="16" spans="2:31">
-      <c r="B16" s="434" t="s">
+      <c r="B16" s="459" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="426"/>
-      <c r="D16" s="426"/>
-      <c r="E16" s="426"/>
-      <c r="F16" s="426"/>
-      <c r="G16" s="426"/>
+      <c r="C16" s="443"/>
+      <c r="D16" s="443"/>
+      <c r="E16" s="443"/>
+      <c r="F16" s="443"/>
+      <c r="G16" s="443"/>
       <c r="H16" s="67" t="s">
         <v>234</v>
       </c>
-      <c r="I16" s="443" t="str">
+      <c r="I16" s="449" t="str">
         <f>IF(B16=" ","",W11)</f>
         <v/>
       </c>
-      <c r="J16" s="426"/>
-      <c r="K16" s="426"/>
-      <c r="L16" s="426"/>
-      <c r="M16" s="426"/>
-      <c r="N16" s="426"/>
-      <c r="O16" s="426"/>
-      <c r="P16" s="426"/>
+      <c r="J16" s="443"/>
+      <c r="K16" s="443"/>
+      <c r="L16" s="443"/>
+      <c r="M16" s="443"/>
+      <c r="N16" s="443"/>
+      <c r="O16" s="443"/>
+      <c r="P16" s="443"/>
       <c r="Q16" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="R16" s="430" t="str">
+      <c r="R16" s="454" t="str">
         <f>IF(B16=" ","",I16*B16)</f>
         <v/>
       </c>
-      <c r="S16" s="426"/>
-      <c r="T16" s="426"/>
-      <c r="U16" s="426"/>
+      <c r="S16" s="443"/>
+      <c r="T16" s="443"/>
+      <c r="U16" s="443"/>
       <c r="V16" s="80"/>
       <c r="AA16" s="82"/>
       <c r="AB16" s="82"/>
@@ -5266,10 +5266,10 @@
       <c r="S17" s="75"/>
       <c r="U17" s="75"/>
       <c r="V17" s="80"/>
-      <c r="W17" s="430"/>
-      <c r="X17" s="426"/>
-      <c r="Y17" s="426"/>
-      <c r="Z17" s="426"/>
+      <c r="W17" s="454"/>
+      <c r="X17" s="443"/>
+      <c r="Y17" s="443"/>
+      <c r="Z17" s="443"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="82"/>
       <c r="AC17" s="83"/>
@@ -5293,13 +5293,13 @@
       <c r="Q18" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="446" t="str">
+      <c r="R18" s="453" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="S18" s="426"/>
-      <c r="T18" s="426"/>
-      <c r="U18" s="426"/>
+      <c r="S18" s="443"/>
+      <c r="T18" s="443"/>
+      <c r="U18" s="443"/>
       <c r="V18" s="80"/>
       <c r="W18" s="80"/>
       <c r="X18" s="80"/>
@@ -5381,13 +5381,13 @@
       <c r="V22" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W22" s="438">
+      <c r="W22" s="463">
         <f>R12</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X22" s="433"/>
-      <c r="Y22" s="433"/>
-      <c r="Z22" s="433"/>
+      <c r="X22" s="446"/>
+      <c r="Y22" s="446"/>
+      <c r="Z22" s="446"/>
     </row>
     <row r="23" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B23" s="85" t="s">
@@ -5396,13 +5396,13 @@
       <c r="V23" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W23" s="432" t="str">
+      <c r="W23" s="445" t="str">
         <f>R16</f>
         <v/>
       </c>
-      <c r="X23" s="433"/>
-      <c r="Y23" s="433"/>
-      <c r="Z23" s="433"/>
+      <c r="X23" s="446"/>
+      <c r="Y23" s="446"/>
+      <c r="Z23" s="446"/>
     </row>
     <row r="24" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B24" s="86" t="s">
@@ -5411,13 +5411,13 @@
       <c r="V24" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="W24" s="427">
+      <c r="W24" s="457">
         <f>SUM(W22:W23)</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X24" s="428"/>
-      <c r="Y24" s="428"/>
-      <c r="Z24" s="428"/>
+      <c r="X24" s="440"/>
+      <c r="Y24" s="440"/>
+      <c r="Z24" s="440"/>
     </row>
     <row r="25" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B25" s="85" t="s">
@@ -5426,13 +5426,13 @@
       <c r="V25" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W25" s="432">
+      <c r="W25" s="445">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H9</f>
         <v>0</v>
       </c>
-      <c r="X25" s="433"/>
-      <c r="Y25" s="433"/>
-      <c r="Z25" s="433"/>
+      <c r="X25" s="446"/>
+      <c r="Y25" s="446"/>
+      <c r="Z25" s="446"/>
     </row>
     <row r="26" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B26" s="85" t="s">
@@ -5441,13 +5441,13 @@
       <c r="V26" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W26" s="432">
+      <c r="W26" s="445">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H14</f>
         <v>0</v>
       </c>
-      <c r="X26" s="433"/>
-      <c r="Y26" s="433"/>
-      <c r="Z26" s="433"/>
+      <c r="X26" s="446"/>
+      <c r="Y26" s="446"/>
+      <c r="Z26" s="446"/>
     </row>
     <row r="27" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B27" s="85" t="s">
@@ -5456,13 +5456,13 @@
       <c r="V27" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W27" s="432">
+      <c r="W27" s="445">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H19</f>
         <v>0</v>
       </c>
-      <c r="X27" s="433"/>
-      <c r="Y27" s="433"/>
-      <c r="Z27" s="433"/>
+      <c r="X27" s="446"/>
+      <c r="Y27" s="446"/>
+      <c r="Z27" s="446"/>
     </row>
     <row r="28" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B28" s="85" t="s">
@@ -5471,13 +5471,13 @@
       <c r="V28" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W28" s="432">
+      <c r="W28" s="445">
         <f>'LAUDO DE AVALIAÇÃO 12-12.4'!H24</f>
         <v>0</v>
       </c>
-      <c r="X28" s="433"/>
-      <c r="Y28" s="433"/>
-      <c r="Z28" s="433"/>
+      <c r="X28" s="446"/>
+      <c r="Y28" s="446"/>
+      <c r="Z28" s="446"/>
     </row>
     <row r="29" spans="2:37" s="85" customFormat="1" ht="13.5" customHeight="1">
       <c r="B29" s="85" t="s">
@@ -5486,13 +5486,13 @@
       <c r="V29" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="W29" s="432">
+      <c r="W29" s="445">
         <f>'LAUDO DE AVALIAÇÃO 13'!G8</f>
         <v>0</v>
       </c>
-      <c r="X29" s="433"/>
-      <c r="Y29" s="433"/>
-      <c r="Z29" s="433"/>
+      <c r="X29" s="446"/>
+      <c r="Y29" s="446"/>
+      <c r="Z29" s="446"/>
     </row>
     <row r="30" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
       <c r="B30" s="86" t="s">
@@ -5501,13 +5501,13 @@
       <c r="V30" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="W30" s="431">
+      <c r="W30" s="458">
         <f>SUM(W25:Z29)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="428"/>
-      <c r="Y30" s="428"/>
-      <c r="Z30" s="428"/>
+      <c r="X30" s="440"/>
+      <c r="Y30" s="440"/>
+      <c r="Z30" s="440"/>
       <c r="AG30" s="85"/>
     </row>
     <row r="31" spans="2:37" s="86" customFormat="1" ht="13.5" customHeight="1">
@@ -5517,83 +5517,83 @@
       <c r="V31" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="W31" s="436">
+      <c r="W31" s="461">
         <f>W30+W24</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="X31" s="428"/>
-      <c r="Y31" s="428"/>
-      <c r="Z31" s="428"/>
+      <c r="X31" s="440"/>
+      <c r="Y31" s="440"/>
+      <c r="Z31" s="440"/>
       <c r="AG31" s="88"/>
     </row>
     <row r="32" spans="2:37" s="85" customFormat="1" ht="11.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="K32" s="435">
+      <c r="K32" s="460">
         <v>43009</v>
       </c>
-      <c r="L32" s="433"/>
-      <c r="M32" s="433"/>
-      <c r="N32" s="433"/>
-      <c r="O32" s="433"/>
-      <c r="P32" s="433"/>
-      <c r="Q32" s="433"/>
-      <c r="R32" s="433"/>
-      <c r="S32" s="433"/>
-      <c r="T32" s="433"/>
-      <c r="U32" s="433"/>
-      <c r="V32" s="433"/>
-      <c r="W32" s="433"/>
-      <c r="X32" s="433"/>
-      <c r="Y32" s="433"/>
-      <c r="Z32" s="433"/>
+      <c r="L32" s="446"/>
+      <c r="M32" s="446"/>
+      <c r="N32" s="446"/>
+      <c r="O32" s="446"/>
+      <c r="P32" s="446"/>
+      <c r="Q32" s="446"/>
+      <c r="R32" s="446"/>
+      <c r="S32" s="446"/>
+      <c r="T32" s="446"/>
+      <c r="U32" s="446"/>
+      <c r="V32" s="446"/>
+      <c r="W32" s="446"/>
+      <c r="X32" s="446"/>
+      <c r="Y32" s="446"/>
+      <c r="Z32" s="446"/>
       <c r="AG32" s="88"/>
     </row>
     <row r="33" spans="2:37" s="86" customFormat="1" ht="17.25" customHeight="1">
-      <c r="O33" s="447" t="s">
+      <c r="O33" s="439" t="s">
         <v>254</v>
       </c>
-      <c r="P33" s="428"/>
-      <c r="Q33" s="428"/>
-      <c r="R33" s="428"/>
-      <c r="S33" s="428"/>
-      <c r="T33" s="428"/>
-      <c r="U33" s="428"/>
-      <c r="V33" s="428"/>
-      <c r="W33" s="448" t="s">
+      <c r="P33" s="440"/>
+      <c r="Q33" s="440"/>
+      <c r="R33" s="440"/>
+      <c r="S33" s="440"/>
+      <c r="T33" s="440"/>
+      <c r="U33" s="440"/>
+      <c r="V33" s="440"/>
+      <c r="W33" s="444" t="s">
         <v>255</v>
       </c>
-      <c r="X33" s="336"/>
-      <c r="Y33" s="336"/>
-      <c r="Z33" s="336"/>
-      <c r="AA33" s="336"/>
-      <c r="AB33" s="336"/>
-      <c r="AC33" s="336"/>
-      <c r="AD33" s="336"/>
+      <c r="X33" s="338"/>
+      <c r="Y33" s="338"/>
+      <c r="Z33" s="338"/>
+      <c r="AA33" s="338"/>
+      <c r="AB33" s="338"/>
+      <c r="AC33" s="338"/>
+      <c r="AD33" s="338"/>
       <c r="AG33" s="89"/>
     </row>
     <row r="34" spans="2:37" s="85" customFormat="1" ht="19.5" customHeight="1">
       <c r="O34" s="48"/>
       <c r="P34" s="48"/>
-      <c r="Q34" s="439">
+      <c r="Q34" s="451">
         <f>W31*0.9</f>
         <v>617690.27743470005</v>
       </c>
-      <c r="R34" s="433"/>
-      <c r="S34" s="433"/>
-      <c r="T34" s="433"/>
+      <c r="R34" s="446"/>
+      <c r="S34" s="446"/>
+      <c r="T34" s="446"/>
       <c r="U34" s="48"/>
       <c r="V34" s="48"/>
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
-      <c r="Y34" s="439">
+      <c r="Y34" s="451">
         <f>W31*1.1</f>
         <v>754954.78353130003</v>
       </c>
-      <c r="Z34" s="433"/>
-      <c r="AA34" s="433"/>
-      <c r="AB34" s="433"/>
+      <c r="Z34" s="446"/>
+      <c r="AA34" s="446"/>
+      <c r="AB34" s="446"/>
       <c r="AC34" s="48"/>
       <c r="AD34" s="48"/>
       <c r="AG34" s="86"/>
@@ -5656,32 +5656,32 @@
     </row>
     <row r="37" spans="2:37" ht="10.5" customHeight="1"/>
     <row r="38" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B38" s="429"/>
-      <c r="C38" s="426"/>
+      <c r="B38" s="448"/>
+      <c r="C38" s="443"/>
     </row>
     <row r="39" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B39" s="429"/>
-      <c r="C39" s="426"/>
+      <c r="B39" s="448"/>
+      <c r="C39" s="443"/>
     </row>
     <row r="40" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B40" s="429"/>
-      <c r="C40" s="426"/>
+      <c r="B40" s="448"/>
+      <c r="C40" s="443"/>
     </row>
     <row r="41" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B41" s="429"/>
-      <c r="C41" s="426"/>
+      <c r="B41" s="448"/>
+      <c r="C41" s="443"/>
     </row>
     <row r="42" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B42" s="429"/>
-      <c r="C42" s="426"/>
+      <c r="B42" s="448"/>
+      <c r="C42" s="443"/>
     </row>
     <row r="43" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B43" s="429"/>
-      <c r="C43" s="426"/>
+      <c r="B43" s="448"/>
+      <c r="C43" s="443"/>
     </row>
     <row r="44" spans="2:37" ht="14.25" customHeight="1">
-      <c r="B44" s="429"/>
-      <c r="C44" s="426"/>
+      <c r="B44" s="448"/>
+      <c r="C44" s="443"/>
     </row>
     <row r="45" spans="2:37" ht="15" customHeight="1">
       <c r="B45" s="96"/>
@@ -5752,10 +5752,10 @@
     </row>
     <row r="48" spans="2:37" ht="14.25" customHeight="1"/>
     <row r="49" spans="5:16" ht="13.5" customHeight="1">
-      <c r="E49" s="445"/>
-      <c r="F49" s="426"/>
-      <c r="G49" s="426"/>
-      <c r="H49" s="426"/>
+      <c r="E49" s="452"/>
+      <c r="F49" s="443"/>
+      <c r="G49" s="443"/>
+      <c r="H49" s="443"/>
       <c r="I49" s="91"/>
       <c r="J49" s="91"/>
       <c r="K49" s="91"/>
@@ -5778,50 +5778,60 @@
     </row>
     <row r="51" spans="5:16" ht="11.25" customHeight="1"/>
     <row r="52" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H52" s="442"/>
-      <c r="I52" s="336"/>
-      <c r="J52" s="336"/>
-      <c r="K52" s="336"/>
-      <c r="L52" s="336"/>
-      <c r="M52" s="336"/>
-      <c r="N52" s="336"/>
-      <c r="O52" s="336"/>
-      <c r="P52" s="336"/>
+      <c r="H52" s="441"/>
+      <c r="I52" s="338"/>
+      <c r="J52" s="338"/>
+      <c r="K52" s="338"/>
+      <c r="L52" s="338"/>
+      <c r="M52" s="338"/>
+      <c r="N52" s="338"/>
+      <c r="O52" s="338"/>
+      <c r="P52" s="338"/>
     </row>
     <row r="53" spans="5:16" ht="6.75" customHeight="1"/>
     <row r="54" spans="5:16" ht="12.75" customHeight="1"/>
     <row r="55" spans="5:16" ht="13.5" customHeight="1">
-      <c r="H55" s="444"/>
-      <c r="I55" s="336"/>
-      <c r="J55" s="336"/>
-      <c r="K55" s="336"/>
-      <c r="L55" s="336"/>
-      <c r="M55" s="336"/>
-      <c r="N55" s="336"/>
-      <c r="O55" s="336"/>
-      <c r="P55" s="336"/>
+      <c r="H55" s="450"/>
+      <c r="I55" s="338"/>
+      <c r="J55" s="338"/>
+      <c r="K55" s="338"/>
+      <c r="L55" s="338"/>
+      <c r="M55" s="338"/>
+      <c r="N55" s="338"/>
+      <c r="O55" s="338"/>
+      <c r="P55" s="338"/>
     </row>
     <row r="56" spans="5:16" ht="4.5" customHeight="1"/>
     <row r="57" spans="5:16" ht="14.25" customHeight="1">
-      <c r="H57" s="442"/>
-      <c r="I57" s="336"/>
-      <c r="J57" s="336"/>
-      <c r="K57" s="336"/>
-      <c r="L57" s="336"/>
-      <c r="M57" s="336"/>
-      <c r="N57" s="336"/>
-      <c r="O57" s="336"/>
-      <c r="P57" s="336"/>
+      <c r="H57" s="441"/>
+      <c r="I57" s="338"/>
+      <c r="J57" s="338"/>
+      <c r="K57" s="338"/>
+      <c r="L57" s="338"/>
+      <c r="M57" s="338"/>
+      <c r="N57" s="338"/>
+      <c r="O57" s="338"/>
+      <c r="P57" s="338"/>
     </row>
     <row r="58" spans="5:16" ht="6.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="H52:P52"/>
-    <mergeCell ref="W11:Z11"/>
-    <mergeCell ref="W33:AD33"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="W26:Z26"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="K32:Z32"/>
+    <mergeCell ref="W31:Z31"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="Y34:AB34"/>
+    <mergeCell ref="I10:P10"/>
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H57:P57"/>
     <mergeCell ref="B42:C42"/>
@@ -5838,22 +5848,12 @@
     <mergeCell ref="W28:Z28"/>
     <mergeCell ref="W27:Z27"/>
     <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="W30:Z30"/>
-    <mergeCell ref="W26:Z26"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="K32:Z32"/>
-    <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="Y34:AB34"/>
-    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="H52:P52"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="W33:AD33"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:G10 B16:G16">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
@@ -5889,24 +5889,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="455" t="s">
+      <c r="B1" s="480" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="456"/>
-      <c r="D1" s="456"/>
-      <c r="E1" s="456"/>
-      <c r="F1" s="456"/>
-      <c r="G1" s="456"/>
-      <c r="H1" s="457"/>
+      <c r="C1" s="481"/>
+      <c r="D1" s="481"/>
+      <c r="E1" s="481"/>
+      <c r="F1" s="481"/>
+      <c r="G1" s="481"/>
+      <c r="H1" s="482"/>
     </row>
     <row r="2" spans="2:12" ht="17.100000000000001" customHeight="1">
-      <c r="B2" s="451"/>
-      <c r="C2" s="452"/>
-      <c r="D2" s="452"/>
-      <c r="E2" s="452"/>
-      <c r="F2" s="452"/>
-      <c r="G2" s="452"/>
-      <c r="H2" s="453"/>
+      <c r="B2" s="477"/>
+      <c r="C2" s="478"/>
+      <c r="D2" s="478"/>
+      <c r="E2" s="478"/>
+      <c r="F2" s="478"/>
+      <c r="G2" s="478"/>
+      <c r="H2" s="479"/>
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
@@ -5941,32 +5941,32 @@
       <c r="H5" s="55"/>
     </row>
     <row r="6" spans="2:12" s="10" customFormat="1" ht="12.75" customHeight="1">
-      <c r="B6" s="460" t="s">
+      <c r="B6" s="470" t="s">
         <v>258</v>
       </c>
-      <c r="C6" s="462" t="s">
+      <c r="C6" s="472" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="464" t="s">
+      <c r="D6" s="468" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="465" t="s">
+      <c r="E6" s="474" t="s">
         <v>261</v>
       </c>
-      <c r="F6" s="465" t="s">
+      <c r="F6" s="474" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="458" t="s">
+      <c r="G6" s="465" t="s">
         <v>263</v>
       </c>
-      <c r="H6" s="459"/>
+      <c r="H6" s="466"/>
     </row>
     <row r="7" spans="2:12" s="10" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B7" s="461"/>
-      <c r="C7" s="463"/>
-      <c r="D7" s="463"/>
-      <c r="E7" s="260"/>
-      <c r="F7" s="260"/>
+      <c r="B7" s="471"/>
+      <c r="C7" s="469"/>
+      <c r="D7" s="469"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="270"/>
       <c r="G7" s="47" t="s">
         <v>264</v>
       </c>
@@ -5987,14 +5987,14 @@
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="466" t="s">
+      <c r="B9" s="467" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="250"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="258"/>
       <c r="H9" s="59">
         <f>TRUNC(SUM(H8:H8),2)</f>
         <v>0</v>
@@ -6012,32 +6012,32 @@
       <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B11" s="460" t="s">
+      <c r="B11" s="470" t="s">
         <v>258</v>
       </c>
-      <c r="C11" s="462" t="s">
+      <c r="C11" s="472" t="s">
         <v>259</v>
       </c>
-      <c r="D11" s="464" t="s">
+      <c r="D11" s="468" t="s">
         <v>260</v>
       </c>
-      <c r="E11" s="454" t="s">
+      <c r="E11" s="473" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="454" t="s">
+      <c r="F11" s="473" t="s">
         <v>262</v>
       </c>
-      <c r="G11" s="458" t="s">
+      <c r="G11" s="465" t="s">
         <v>263</v>
       </c>
-      <c r="H11" s="459"/>
+      <c r="H11" s="466"/>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1">
-      <c r="B12" s="461"/>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="260"/>
+      <c r="B12" s="471"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="270"/>
+      <c r="F12" s="270"/>
       <c r="G12" s="47" t="s">
         <v>264</v>
       </c>
@@ -6058,14 +6058,14 @@
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="466" t="s">
+      <c r="B14" s="467" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="249"/>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="250"/>
+      <c r="C14" s="257"/>
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="257"/>
+      <c r="G14" s="258"/>
       <c r="H14" s="63">
         <f>TRUNC(SUM(H13:H13),2)</f>
         <v>0</v>
@@ -6083,32 +6083,32 @@
       <c r="H15" s="53"/>
     </row>
     <row r="16" spans="2:12" ht="12.75" customHeight="1">
-      <c r="B16" s="460" t="s">
+      <c r="B16" s="470" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="462" t="s">
+      <c r="C16" s="472" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="464" t="s">
+      <c r="D16" s="468" t="s">
         <v>260</v>
       </c>
-      <c r="E16" s="454" t="s">
+      <c r="E16" s="473" t="s">
         <v>266</v>
       </c>
-      <c r="F16" s="454" t="s">
+      <c r="F16" s="473" t="s">
         <v>262</v>
       </c>
-      <c r="G16" s="458" t="s">
+      <c r="G16" s="465" t="s">
         <v>263</v>
       </c>
-      <c r="H16" s="459"/>
+      <c r="H16" s="466"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1">
-      <c r="B17" s="461"/>
-      <c r="C17" s="463"/>
-      <c r="D17" s="463"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="260"/>
+      <c r="B17" s="471"/>
+      <c r="C17" s="469"/>
+      <c r="D17" s="469"/>
+      <c r="E17" s="270"/>
+      <c r="F17" s="270"/>
       <c r="G17" s="22" t="s">
         <v>264</v>
       </c>
@@ -6131,14 +6131,14 @@
       </c>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="466" t="s">
+      <c r="B19" s="467" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="249"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="250"/>
+      <c r="C19" s="257"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="258"/>
       <c r="H19" s="64">
         <f>TRUNC(SUM(H18:H18),2)</f>
         <v>0</v>
@@ -6156,32 +6156,32 @@
       <c r="H20" s="53"/>
     </row>
     <row r="21" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B21" s="460" t="s">
+      <c r="B21" s="470" t="s">
         <v>258</v>
       </c>
-      <c r="C21" s="462" t="s">
+      <c r="C21" s="472" t="s">
         <v>259</v>
       </c>
-      <c r="D21" s="464" t="s">
+      <c r="D21" s="468" t="s">
         <v>260</v>
       </c>
-      <c r="E21" s="454" t="s">
+      <c r="E21" s="473" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="454" t="s">
+      <c r="F21" s="473" t="s">
         <v>262</v>
       </c>
-      <c r="G21" s="458" t="s">
+      <c r="G21" s="465" t="s">
         <v>263</v>
       </c>
-      <c r="H21" s="459"/>
+      <c r="H21" s="466"/>
     </row>
     <row r="22" spans="2:8" ht="21.75" customHeight="1">
-      <c r="B22" s="461"/>
-      <c r="C22" s="463"/>
-      <c r="D22" s="463"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
+      <c r="B22" s="471"/>
+      <c r="C22" s="469"/>
+      <c r="D22" s="469"/>
+      <c r="E22" s="270"/>
+      <c r="F22" s="270"/>
       <c r="G22" s="47" t="s">
         <v>264</v>
       </c>
@@ -6202,32 +6202,18 @@
       </c>
     </row>
     <row r="24" spans="2:8" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B24" s="449" t="s">
+      <c r="B24" s="475" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="450"/>
-      <c r="D24" s="450"/>
-      <c r="E24" s="450"/>
-      <c r="F24" s="450"/>
-      <c r="G24" s="399"/>
+      <c r="C24" s="476"/>
+      <c r="D24" s="476"/>
+      <c r="E24" s="476"/>
+      <c r="F24" s="476"/>
+      <c r="G24" s="402"/>
       <c r="H24" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E16:E17"/>
@@ -6244,6 +6230,20 @@
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="F21:F22"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -6269,14 +6269,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B1" s="469" t="s">
+      <c r="B1" s="485" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="452"/>
-      <c r="D1" s="452"/>
-      <c r="E1" s="452"/>
-      <c r="F1" s="452"/>
-      <c r="G1" s="452"/>
+      <c r="C1" s="478"/>
+      <c r="D1" s="478"/>
+      <c r="E1" s="478"/>
+      <c r="F1" s="478"/>
+      <c r="G1" s="478"/>
       <c r="H1" s="41"/>
       <c r="I1" s="41"/>
     </row>
@@ -6300,40 +6300,40 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="2:13" ht="13.5" customHeight="1">
-      <c r="B4" s="470" t="s">
+      <c r="B4" s="486" t="s">
         <v>271</v>
       </c>
-      <c r="C4" s="249"/>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="250"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="258"/>
       <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="471" t="s">
+      <c r="B5" s="487" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="467" t="s">
+      <c r="C5" s="483" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="467" t="s">
+      <c r="D5" s="483" t="s">
         <v>274</v>
       </c>
-      <c r="E5" s="467" t="s">
+      <c r="E5" s="483" t="s">
         <v>275</v>
       </c>
-      <c r="F5" s="468" t="s">
+      <c r="F5" s="484" t="s">
         <v>276</v>
       </c>
-      <c r="G5" s="249"/>
+      <c r="G5" s="257"/>
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="260"/>
-      <c r="C6" s="463"/>
-      <c r="D6" s="463"/>
-      <c r="E6" s="463"/>
+      <c r="B6" s="270"/>
+      <c r="C6" s="469"/>
+      <c r="D6" s="469"/>
+      <c r="E6" s="469"/>
       <c r="F6" s="30" t="s">
         <v>264</v>
       </c>
@@ -6385,151 +6385,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15" customHeight="1">
-      <c r="A1" s="479" t="s">
+      <c r="A1" s="493" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="254"/>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-      <c r="F1" s="254"/>
-      <c r="G1" s="254"/>
-      <c r="H1" s="254"/>
-      <c r="I1" s="254"/>
-      <c r="J1" s="254"/>
-      <c r="K1" s="254"/>
-      <c r="L1" s="254"/>
-      <c r="M1" s="254"/>
-      <c r="N1" s="254"/>
-      <c r="O1" s="472"/>
-      <c r="P1" s="254"/>
-      <c r="Q1" s="254"/>
-      <c r="R1" s="254"/>
-      <c r="S1" s="254"/>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="255"/>
+      <c r="I1" s="255"/>
+      <c r="J1" s="255"/>
+      <c r="K1" s="255"/>
+      <c r="L1" s="255"/>
+      <c r="M1" s="255"/>
+      <c r="N1" s="255"/>
+      <c r="O1" s="494"/>
+      <c r="P1" s="255"/>
+      <c r="Q1" s="255"/>
+      <c r="R1" s="255"/>
+      <c r="S1" s="255"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="477" t="s">
+      <c r="A2" s="495" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="254"/>
-      <c r="C2" s="477" t="s">
+      <c r="B2" s="255"/>
+      <c r="C2" s="495" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="254"/>
-      <c r="E2" s="254"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="254"/>
-      <c r="H2" s="254"/>
-      <c r="I2" s="254"/>
-      <c r="J2" s="478" t="s">
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="491" t="s">
         <v>278</v>
       </c>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="M2" s="254"/>
+      <c r="K2" s="255"/>
+      <c r="L2" s="255"/>
+      <c r="M2" s="255"/>
       <c r="O2" s="239"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="474" t="s">
+      <c r="A3" s="492" t="s">
         <v>279</v>
       </c>
-      <c r="B3" s="254"/>
-      <c r="C3" s="474" t="s">
+      <c r="B3" s="255"/>
+      <c r="C3" s="492" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="254"/>
-      <c r="H3" s="254"/>
-      <c r="I3" s="254"/>
-      <c r="J3" s="474" t="s">
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="492" t="s">
         <v>280</v>
       </c>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="M3" s="254"/>
-      <c r="N3" s="254"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
+      <c r="M3" s="255"/>
+      <c r="N3" s="255"/>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="474" t="s">
+      <c r="A4" s="492" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="254"/>
-      <c r="C4" s="474" t="s">
+      <c r="B4" s="255"/>
+      <c r="C4" s="492" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="254"/>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="254"/>
-      <c r="I4" s="254"/>
-      <c r="J4" s="476"/>
-      <c r="K4" s="254"/>
-      <c r="L4" s="254"/>
-      <c r="M4" s="254"/>
-      <c r="N4" s="254"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="490"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="255"/>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="474" t="s">
+      <c r="A5" s="492" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="254"/>
-      <c r="C5" s="474" t="s">
+      <c r="B5" s="255"/>
+      <c r="C5" s="492" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="254"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="254"/>
-      <c r="I5" s="254"/>
-      <c r="J5" s="476"/>
-      <c r="K5" s="254"/>
-      <c r="L5" s="254"/>
-      <c r="M5" s="254"/>
-      <c r="N5" s="254"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="490"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="M5" s="255"/>
+      <c r="N5" s="255"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="474" t="s">
+      <c r="A6" s="492" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="254"/>
-      <c r="C6" s="474" t="s">
+      <c r="B6" s="255"/>
+      <c r="C6" s="492" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="254"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="254"/>
-      <c r="G6" s="254"/>
-      <c r="H6" s="254"/>
-      <c r="I6" s="254"/>
-      <c r="J6" s="474" t="s">
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="255"/>
+      <c r="G6" s="255"/>
+      <c r="H6" s="255"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="492" t="s">
         <v>285</v>
       </c>
-      <c r="K6" s="254"/>
-      <c r="L6" s="254"/>
-      <c r="M6" s="254"/>
-      <c r="N6" s="254"/>
+      <c r="K6" s="255"/>
+      <c r="L6" s="255"/>
+      <c r="M6" s="255"/>
+      <c r="N6" s="255"/>
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1">
-      <c r="A7" s="473" t="s">
+      <c r="A7" s="489" t="s">
         <v>286</v>
       </c>
-      <c r="B7" s="254"/>
-      <c r="C7" s="254"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="254"/>
-      <c r="G7" s="254"/>
-      <c r="H7" s="254"/>
-      <c r="I7" s="254"/>
-      <c r="J7" s="254"/>
-      <c r="K7" s="254"/>
-      <c r="L7" s="254"/>
-      <c r="M7" s="254"/>
-      <c r="N7" s="254"/>
+      <c r="B7" s="255"/>
+      <c r="C7" s="255"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="255"/>
+      <c r="I7" s="255"/>
+      <c r="J7" s="255"/>
+      <c r="K7" s="255"/>
+      <c r="L7" s="255"/>
+      <c r="M7" s="255"/>
+      <c r="N7" s="255"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1"/>
     <row r="9" spans="1:19" ht="15" customHeight="1"/>
@@ -6555,141 +6555,123 @@
     <row r="29" spans="1:14" ht="15" customHeight="1"/>
     <row r="30" spans="1:14" ht="15" customHeight="1"/>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="473" t="s">
+      <c r="A31" s="489" t="s">
         <v>287</v>
       </c>
-      <c r="B31" s="254"/>
-      <c r="C31" s="254"/>
-      <c r="D31" s="254"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="254"/>
-      <c r="G31" s="254"/>
-      <c r="H31" s="254"/>
-      <c r="I31" s="254"/>
-      <c r="J31" s="254"/>
-      <c r="K31" s="254"/>
-      <c r="L31" s="254"/>
-      <c r="M31" s="254"/>
-      <c r="N31" s="254"/>
+      <c r="B31" s="255"/>
+      <c r="C31" s="255"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
+      <c r="I31" s="255"/>
+      <c r="J31" s="255"/>
+      <c r="K31" s="255"/>
+      <c r="L31" s="255"/>
+      <c r="M31" s="255"/>
+      <c r="N31" s="255"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
-      <c r="A32" s="475" t="s">
+      <c r="A32" s="488" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="254"/>
-      <c r="C32" s="254"/>
-      <c r="D32" s="475" t="s">
+      <c r="B32" s="255"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="488" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="254"/>
-      <c r="F32" s="254"/>
-      <c r="G32" s="475" t="s">
+      <c r="E32" s="255"/>
+      <c r="F32" s="255"/>
+      <c r="G32" s="488" t="s">
         <v>288</v>
       </c>
-      <c r="H32" s="254"/>
-      <c r="I32" s="254"/>
-      <c r="J32" s="475" t="s">
+      <c r="H32" s="255"/>
+      <c r="I32" s="255"/>
+      <c r="J32" s="488" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="254"/>
-      <c r="L32" s="254"/>
-      <c r="M32" s="254"/>
+      <c r="K32" s="255"/>
+      <c r="L32" s="255"/>
+      <c r="M32" s="255"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
-      <c r="A33" s="475" t="s">
+      <c r="A33" s="488" t="s">
         <v>289</v>
       </c>
-      <c r="B33" s="254"/>
-      <c r="C33" s="254"/>
-      <c r="D33" s="475" t="s">
+      <c r="B33" s="255"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="488" t="s">
         <v>290</v>
       </c>
-      <c r="E33" s="254"/>
-      <c r="F33" s="254"/>
-      <c r="G33" s="475" t="s">
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="488" t="s">
         <v>291</v>
       </c>
-      <c r="H33" s="254"/>
-      <c r="I33" s="254"/>
-      <c r="J33" s="475" t="s">
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="488" t="s">
         <v>292</v>
       </c>
-      <c r="K33" s="254"/>
-      <c r="L33" s="254"/>
-      <c r="M33" s="254"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
+      <c r="M33" s="255"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
-      <c r="A34" s="473" t="s">
+      <c r="A34" s="489" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="254"/>
-      <c r="C34" s="254"/>
-      <c r="D34" s="254"/>
-      <c r="E34" s="254"/>
-      <c r="F34" s="254"/>
-      <c r="G34" s="254"/>
-      <c r="H34" s="254"/>
-      <c r="I34" s="254"/>
-      <c r="J34" s="254"/>
-      <c r="K34" s="254"/>
-      <c r="L34" s="254"/>
-      <c r="M34" s="254"/>
-      <c r="N34" s="254"/>
+      <c r="B34" s="255"/>
+      <c r="C34" s="255"/>
+      <c r="D34" s="255"/>
+      <c r="E34" s="255"/>
+      <c r="F34" s="255"/>
+      <c r="G34" s="255"/>
+      <c r="H34" s="255"/>
+      <c r="I34" s="255"/>
+      <c r="J34" s="255"/>
+      <c r="K34" s="255"/>
+      <c r="L34" s="255"/>
+      <c r="M34" s="255"/>
+      <c r="N34" s="255"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
-      <c r="A35" s="475" t="s">
+      <c r="A35" s="488" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="254"/>
-      <c r="C35" s="254"/>
-      <c r="F35" s="475" t="s">
+      <c r="B35" s="255"/>
+      <c r="C35" s="255"/>
+      <c r="F35" s="488" t="s">
         <v>293</v>
       </c>
-      <c r="G35" s="254"/>
-      <c r="H35" s="254"/>
-      <c r="K35" s="475" t="s">
+      <c r="G35" s="255"/>
+      <c r="H35" s="255"/>
+      <c r="K35" s="488" t="s">
         <v>294</v>
       </c>
-      <c r="L35" s="254"/>
-      <c r="M35" s="254"/>
+      <c r="L35" s="255"/>
+      <c r="M35" s="255"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
-      <c r="A36" s="475" t="s">
+      <c r="A36" s="488" t="s">
         <v>289</v>
       </c>
-      <c r="B36" s="254"/>
-      <c r="C36" s="254"/>
-      <c r="F36" s="475" t="s">
+      <c r="B36" s="255"/>
+      <c r="C36" s="255"/>
+      <c r="F36" s="488" t="s">
         <v>295</v>
       </c>
-      <c r="G36" s="254"/>
-      <c r="H36" s="254"/>
-      <c r="K36" s="475" t="s">
+      <c r="G36" s="255"/>
+      <c r="H36" s="255"/>
+      <c r="K36" s="488" t="s">
         <v>296</v>
       </c>
-      <c r="L36" s="254"/>
-      <c r="M36" s="254"/>
+      <c r="L36" s="255"/>
+      <c r="M36" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="J6:N6"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="A31:N31"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="C6:I6"/>
@@ -6706,6 +6688,24 @@
     <mergeCell ref="J3:N3"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="A31:N31"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="K36:M36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6803,13 +6803,13 @@
       <c r="E21" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="286" t="s">
+      <c r="H21" s="292" t="s">
         <v>304</v>
       </c>
-      <c r="I21" s="286"/>
-      <c r="J21" s="286"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="286"/>
+      <c r="I21" s="292"/>
+      <c r="J21" s="292"/>
+      <c r="K21" s="292"/>
+      <c r="L21" s="292"/>
     </row>
     <row r="22" spans="4:12" ht="15" customHeight="1">
       <c r="D22" s="153" t="s">
@@ -6818,15 +6818,15 @@
       <c r="E22" s="123">
         <v>1.2</v>
       </c>
-      <c r="H22" s="287" t="s">
+      <c r="H22" s="293" t="s">
         <v>305</v>
       </c>
-      <c r="I22" s="287" t="s">
+      <c r="I22" s="293" t="s">
         <v>306</v>
       </c>
-      <c r="J22" s="287"/>
-      <c r="K22" s="287"/>
-      <c r="L22" s="287"/>
+      <c r="J22" s="293"/>
+      <c r="K22" s="293"/>
+      <c r="L22" s="293"/>
     </row>
     <row r="23" spans="4:12" ht="15" customHeight="1">
       <c r="D23" s="153" t="s">
@@ -6835,7 +6835,7 @@
       <c r="E23" s="123">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H23" s="287"/>
+      <c r="H23" s="293"/>
       <c r="I23" s="242" t="s">
         <v>307</v>
       </c>
@@ -6959,7 +6959,7 @@
       </c>
     </row>
     <row r="32" spans="4:12" ht="15" customHeight="1">
-      <c r="D32" s="284" t="s">
+      <c r="D32" s="290" t="s">
         <v>40</v>
       </c>
       <c r="E32" s="193" t="s">
@@ -6969,7 +6969,7 @@
       <c r="G32" s="193"/>
     </row>
     <row r="33" spans="4:7" ht="30" customHeight="1">
-      <c r="D33" s="285"/>
+      <c r="D33" s="291"/>
       <c r="E33" s="194" t="s">
         <v>42</v>
       </c>
@@ -7107,155 +7107,155 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
-      <c r="A2" s="288" t="s">
+      <c r="A2" s="294" t="s">
         <v>317</v>
       </c>
-      <c r="B2" s="289" t="s">
+      <c r="B2" s="295" t="s">
         <v>318</v>
       </c>
-      <c r="C2" s="290">
+      <c r="C2" s="296">
         <v>1.3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A3" s="288"/>
-      <c r="B3" s="289"/>
-      <c r="C3" s="290"/>
+      <c r="A3" s="294"/>
+      <c r="B3" s="295"/>
+      <c r="C3" s="296"/>
     </row>
     <row r="4" spans="1:3" ht="27.75" customHeight="1">
-      <c r="A4" s="288" t="s">
+      <c r="A4" s="294" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="289" t="s">
+      <c r="B4" s="295" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="290">
+      <c r="C4" s="296">
         <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A5" s="288"/>
-      <c r="B5" s="289"/>
-      <c r="C5" s="290"/>
+      <c r="A5" s="294"/>
+      <c r="B5" s="295"/>
+      <c r="C5" s="296"/>
     </row>
     <row r="6" spans="1:3" ht="28.5" customHeight="1">
-      <c r="A6" s="288" t="s">
+      <c r="A6" s="294" t="s">
         <v>321</v>
       </c>
-      <c r="B6" s="289" t="s">
+      <c r="B6" s="295" t="s">
         <v>322</v>
       </c>
-      <c r="C6" s="290">
+      <c r="C6" s="296">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A7" s="288"/>
-      <c r="B7" s="289"/>
-      <c r="C7" s="290"/>
+      <c r="A7" s="294"/>
+      <c r="B7" s="295"/>
+      <c r="C7" s="296"/>
     </row>
     <row r="8" spans="1:3" ht="44.25" customHeight="1">
-      <c r="A8" s="288" t="s">
+      <c r="A8" s="294" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="289" t="s">
+      <c r="B8" s="295" t="s">
         <v>323</v>
       </c>
-      <c r="C8" s="290">
+      <c r="C8" s="296">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A9" s="288"/>
-      <c r="B9" s="289"/>
-      <c r="C9" s="290"/>
+      <c r="A9" s="294"/>
+      <c r="B9" s="295"/>
+      <c r="C9" s="296"/>
     </row>
     <row r="10" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A10" s="288" t="s">
+      <c r="A10" s="294" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="289" t="s">
+      <c r="B10" s="295" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="290">
+      <c r="C10" s="296">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A11" s="288"/>
-      <c r="B11" s="289"/>
-      <c r="C11" s="290"/>
+      <c r="A11" s="294"/>
+      <c r="B11" s="295"/>
+      <c r="C11" s="296"/>
     </row>
     <row r="12" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A12" s="288" t="s">
+      <c r="A12" s="294" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="289" t="s">
+      <c r="B12" s="295" t="s">
         <v>325</v>
       </c>
-      <c r="C12" s="290">
+      <c r="C12" s="296">
         <v>0.8</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A13" s="288"/>
-      <c r="B13" s="289"/>
-      <c r="C13" s="290"/>
+      <c r="A13" s="294"/>
+      <c r="B13" s="295"/>
+      <c r="C13" s="296"/>
     </row>
     <row r="14" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A14" s="288" t="s">
+      <c r="A14" s="294" t="s">
         <v>326</v>
       </c>
-      <c r="B14" s="289" t="s">
+      <c r="B14" s="295" t="s">
         <v>327</v>
       </c>
-      <c r="C14" s="290">
+      <c r="C14" s="296">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="12.75" customHeight="1">
-      <c r="A15" s="288"/>
-      <c r="B15" s="289"/>
-      <c r="C15" s="290"/>
+      <c r="A15" s="294"/>
+      <c r="B15" s="295"/>
+      <c r="C15" s="296"/>
     </row>
     <row r="16" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A16" s="288" t="s">
+      <c r="A16" s="294" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="289" t="s">
+      <c r="B16" s="295" t="s">
         <v>328</v>
       </c>
-      <c r="C16" s="290">
+      <c r="C16" s="296">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="288"/>
-      <c r="B17" s="289"/>
-      <c r="C17" s="290"/>
+      <c r="A17" s="294"/>
+      <c r="B17" s="295"/>
+      <c r="C17" s="296"/>
     </row>
     <row r="18" spans="1:9" ht="15">
-      <c r="E18" s="286" t="s">
+      <c r="E18" s="292" t="s">
         <v>304</v>
       </c>
-      <c r="F18" s="286"/>
-      <c r="G18" s="286"/>
-      <c r="H18" s="286"/>
-      <c r="I18" s="286"/>
+      <c r="F18" s="292"/>
+      <c r="G18" s="292"/>
+      <c r="H18" s="292"/>
+      <c r="I18" s="292"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="E19" s="287" t="s">
+      <c r="E19" s="293" t="s">
         <v>305</v>
       </c>
-      <c r="F19" s="287" t="s">
+      <c r="F19" s="293" t="s">
         <v>306</v>
       </c>
-      <c r="G19" s="287"/>
-      <c r="H19" s="287"/>
-      <c r="I19" s="287"/>
+      <c r="G19" s="293"/>
+      <c r="H19" s="293"/>
+      <c r="I19" s="293"/>
     </row>
     <row r="20" spans="1:9" ht="15">
-      <c r="E20" s="287"/>
+      <c r="E20" s="293"/>
       <c r="F20" s="245" t="s">
         <v>307</v>
       </c>
@@ -7356,6 +7356,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:I19"/>
@@ -7365,24 +7383,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7431,17 +7431,17 @@
       <c r="T3" s="207"/>
     </row>
     <row r="4" spans="3:20">
-      <c r="C4" s="295" t="str">
+      <c r="C4" s="328" t="str">
         <f>C16</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="285"/>
-      <c r="E4" s="285"/>
-      <c r="F4" s="285"/>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
+      <c r="D4" s="291"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
+      <c r="I4" s="291"/>
+      <c r="J4" s="291"/>
       <c r="L4" s="207"/>
       <c r="M4" s="207"/>
       <c r="N4" s="207"/>
@@ -7460,22 +7460,22 @@
       <c r="T4" s="207"/>
     </row>
     <row r="5" spans="3:20">
-      <c r="C5" s="311" t="s">
+      <c r="C5" s="325" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="311" t="s">
+      <c r="D5" s="270"/>
+      <c r="E5" s="325" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="260"/>
-      <c r="G5" s="311" t="s">
+      <c r="F5" s="270"/>
+      <c r="G5" s="325" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="260"/>
-      <c r="I5" s="306" t="s">
+      <c r="H5" s="270"/>
+      <c r="I5" s="319" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="260"/>
+      <c r="J5" s="270"/>
       <c r="L5" s="207"/>
       <c r="M5" s="207"/>
       <c r="N5" s="207" t="s">
@@ -7489,23 +7489,23 @@
       <c r="T5" s="207"/>
     </row>
     <row r="6" spans="3:20">
-      <c r="C6" s="298">
+      <c r="C6" s="303">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="D6" s="250"/>
-      <c r="E6" s="301" t="s">
+      <c r="D6" s="258"/>
+      <c r="E6" s="318" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="250"/>
-      <c r="G6" s="299" t="s">
+      <c r="F6" s="258"/>
+      <c r="G6" s="302" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="250"/>
-      <c r="I6" s="313" t="s">
+      <c r="H6" s="258"/>
+      <c r="I6" s="305" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="250"/>
+      <c r="J6" s="258"/>
       <c r="L6" s="207">
         <v>231.63</v>
       </c>
@@ -7525,16 +7525,16 @@
       <c r="T6" s="207"/>
     </row>
     <row r="7" spans="3:20">
-      <c r="C7" s="296" t="s">
+      <c r="C7" s="324" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="249"/>
-      <c r="E7" s="249"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="249"/>
-      <c r="H7" s="249"/>
-      <c r="I7" s="249"/>
-      <c r="J7" s="250"/>
+      <c r="D7" s="257"/>
+      <c r="E7" s="257"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="257"/>
+      <c r="I7" s="257"/>
+      <c r="J7" s="258"/>
       <c r="L7" s="207"/>
       <c r="M7" s="207"/>
       <c r="N7" s="207"/>
@@ -7551,22 +7551,22 @@
       <c r="T7" s="207"/>
     </row>
     <row r="8" spans="3:20">
-      <c r="C8" s="300" t="s">
+      <c r="C8" s="306" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="250"/>
-      <c r="E8" s="300" t="s">
+      <c r="D8" s="258"/>
+      <c r="E8" s="306" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="250"/>
-      <c r="G8" s="300" t="s">
+      <c r="F8" s="258"/>
+      <c r="G8" s="306" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="250"/>
-      <c r="I8" s="310" t="s">
+      <c r="H8" s="258"/>
+      <c r="I8" s="323" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="250"/>
+      <c r="J8" s="258"/>
       <c r="L8" s="207"/>
       <c r="M8" s="207"/>
       <c r="N8" s="207"/>
@@ -7578,22 +7578,22 @@
       <c r="T8" s="207"/>
     </row>
     <row r="9" spans="3:20">
-      <c r="C9" s="301">
+      <c r="C9" s="318">
         <v>52.034300000000002</v>
       </c>
-      <c r="D9" s="250"/>
-      <c r="E9" s="299" t="s">
+      <c r="D9" s="258"/>
+      <c r="E9" s="302" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="250"/>
-      <c r="G9" s="298">
+      <c r="F9" s="258"/>
+      <c r="G9" s="303">
         <v>80</v>
       </c>
-      <c r="H9" s="250"/>
-      <c r="I9" s="313">
+      <c r="H9" s="258"/>
+      <c r="I9" s="305">
         <v>0.65039999999999998</v>
       </c>
-      <c r="J9" s="250"/>
+      <c r="J9" s="258"/>
       <c r="L9" s="207"/>
       <c r="M9" s="207"/>
       <c r="N9" s="207"/>
@@ -7605,16 +7605,16 @@
       <c r="T9" s="207"/>
     </row>
     <row r="10" spans="3:20">
-      <c r="C10" s="296" t="s">
+      <c r="C10" s="324" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="249"/>
-      <c r="J10" s="250"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="257"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="257"/>
+      <c r="H10" s="257"/>
+      <c r="I10" s="257"/>
+      <c r="J10" s="258"/>
       <c r="L10" s="207"/>
       <c r="M10" s="207"/>
       <c r="N10" s="207"/>
@@ -7626,171 +7626,205 @@
       <c r="T10" s="207"/>
     </row>
     <row r="11" spans="3:20">
-      <c r="C11" s="300" t="s">
+      <c r="C11" s="306" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="250"/>
-      <c r="E11" s="300" t="s">
+      <c r="D11" s="258"/>
+      <c r="E11" s="306" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="250"/>
-      <c r="G11" s="300" t="s">
+      <c r="F11" s="258"/>
+      <c r="G11" s="306" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="250"/>
-      <c r="I11" s="310" t="s">
+      <c r="H11" s="258"/>
+      <c r="I11" s="323" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="250"/>
+      <c r="J11" s="258"/>
     </row>
     <row r="12" spans="3:20">
-      <c r="C12" s="301">
+      <c r="C12" s="318">
         <v>52.034300000000002</v>
       </c>
-      <c r="D12" s="250"/>
-      <c r="E12" s="301">
+      <c r="D12" s="258"/>
+      <c r="E12" s="318">
         <v>18.2121</v>
       </c>
-      <c r="F12" s="250"/>
-      <c r="G12" s="299">
+      <c r="F12" s="258"/>
+      <c r="G12" s="302">
         <v>1.7411000000000001</v>
       </c>
-      <c r="H12" s="250"/>
-      <c r="I12" s="302">
+      <c r="H12" s="258"/>
+      <c r="I12" s="330">
         <v>9.7928999999999995</v>
       </c>
-      <c r="J12" s="250"/>
+      <c r="J12" s="258"/>
     </row>
     <row r="13" spans="3:20">
-      <c r="C13" s="300" t="s">
+      <c r="C13" s="306" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="250"/>
-      <c r="E13" s="299" t="s">
+      <c r="D13" s="258"/>
+      <c r="E13" s="302" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="250"/>
-      <c r="G13" s="300" t="s">
+      <c r="F13" s="258"/>
+      <c r="G13" s="306" t="s">
         <v>77</v>
       </c>
-      <c r="H13" s="250"/>
-      <c r="I13" s="313" t="s">
+      <c r="H13" s="258"/>
+      <c r="I13" s="305" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="250"/>
+      <c r="J13" s="258"/>
     </row>
     <row r="16" spans="3:20">
-      <c r="C16" s="307" t="s">
+      <c r="C16" s="320" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="308"/>
-      <c r="E16" s="308"/>
-      <c r="F16" s="308"/>
-      <c r="G16" s="308"/>
-      <c r="H16" s="308"/>
-      <c r="I16" s="309"/>
+      <c r="D16" s="321"/>
+      <c r="E16" s="321"/>
+      <c r="F16" s="321"/>
+      <c r="G16" s="321"/>
+      <c r="H16" s="321"/>
+      <c r="I16" s="322"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="296" t="s">
+      <c r="C17" s="324" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="249"/>
-      <c r="E17" s="250"/>
-      <c r="F17" s="296" t="s">
+      <c r="D17" s="257"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="324" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="250"/>
-      <c r="H17" s="296" t="s">
+      <c r="G17" s="258"/>
+      <c r="H17" s="324" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="250"/>
+      <c r="I17" s="258"/>
     </row>
     <row r="18" spans="3:10" ht="15">
-      <c r="C18" s="317" t="s">
+      <c r="C18" s="312" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="318"/>
-      <c r="E18" s="319"/>
-      <c r="F18" s="321">
+      <c r="D18" s="313"/>
+      <c r="E18" s="314"/>
+      <c r="F18" s="316">
         <f>AMOSTRAS!E11</f>
         <v>7.23</v>
       </c>
-      <c r="G18" s="322"/>
-      <c r="H18" s="323">
+      <c r="G18" s="317"/>
+      <c r="H18" s="297">
         <f>F18/C6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="I18" s="324"/>
+      <c r="I18" s="298"/>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="320" t="s">
+      <c r="C19" s="315" t="s">
         <v>300</v>
       </c>
-      <c r="D19" s="249"/>
-      <c r="E19" s="250"/>
-      <c r="F19" s="298">
+      <c r="D19" s="257"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="303">
         <f>AMOSTRAS!E12</f>
         <v>24.851099999999999</v>
       </c>
-      <c r="G19" s="250"/>
-      <c r="H19" s="312">
+      <c r="G19" s="258"/>
+      <c r="H19" s="304">
         <f>AMOSTRAS!F12</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="I19" s="250"/>
+      <c r="I19" s="258"/>
     </row>
     <row r="20" spans="3:10" s="247" customFormat="1">
-      <c r="C20" s="303" t="s">
+      <c r="C20" s="299" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="304"/>
-      <c r="E20" s="305"/>
-      <c r="F20" s="291">
+      <c r="D20" s="300"/>
+      <c r="E20" s="301"/>
+      <c r="F20" s="326">
         <v>1.7411000000000001</v>
       </c>
-      <c r="G20" s="292"/>
-      <c r="H20" s="293">
+      <c r="G20" s="327"/>
+      <c r="H20" s="308">
         <f>F20/C12</f>
         <v>3.3460621167191638E-2</v>
       </c>
-      <c r="I20" s="294"/>
+      <c r="I20" s="309"/>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="303" t="s">
+      <c r="C21" s="299" t="s">
         <v>330</v>
       </c>
-      <c r="D21" s="304"/>
-      <c r="E21" s="305"/>
-      <c r="F21" s="315">
+      <c r="D21" s="300"/>
+      <c r="E21" s="301"/>
+      <c r="F21" s="310">
         <v>18.2121</v>
       </c>
-      <c r="G21" s="316"/>
-      <c r="H21" s="293">
+      <c r="G21" s="311"/>
+      <c r="H21" s="308">
         <f>F21/C12</f>
         <v>0.35000182571880467</v>
       </c>
-      <c r="I21" s="294"/>
+      <c r="I21" s="309"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="314" t="s">
+      <c r="C22" s="307" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="249"/>
-      <c r="E22" s="250"/>
-      <c r="F22" s="297">
+      <c r="D22" s="257"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="329">
         <f>SUM(F18:G21)</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G22" s="250"/>
-      <c r="H22" s="312">
+      <c r="G22" s="258"/>
+      <c r="H22" s="304">
         <f>SUM(H18:I21)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="I22" s="250"/>
+      <c r="I22" s="258"/>
       <c r="J22" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="G12:H12"/>
@@ -7807,40 +7841,6 @@
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7868,38 +7868,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:14" ht="15" customHeight="1">
-      <c r="B3" s="356" t="s">
+      <c r="B3" s="390" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="357"/>
-      <c r="D3" s="357"/>
-      <c r="E3" s="357"/>
-      <c r="F3" s="357"/>
-      <c r="G3" s="357"/>
-      <c r="H3" s="357"/>
-      <c r="I3" s="357"/>
-      <c r="L3" s="389" t="s">
+      <c r="C3" s="391"/>
+      <c r="D3" s="391"/>
+      <c r="E3" s="391"/>
+      <c r="F3" s="391"/>
+      <c r="G3" s="391"/>
+      <c r="H3" s="391"/>
+      <c r="I3" s="391"/>
+      <c r="L3" s="331" t="s">
         <v>84</v>
       </c>
-      <c r="M3" s="250"/>
+      <c r="M3" s="258"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1">
-      <c r="B4" s="335" t="s">
+      <c r="B4" s="337" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="336"/>
-      <c r="D4" s="336"/>
-      <c r="E4" s="391" t="s">
+      <c r="C4" s="338"/>
+      <c r="D4" s="338"/>
+      <c r="E4" s="349" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="285"/>
+      <c r="F4" s="291"/>
       <c r="G4" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="358" t="s">
+      <c r="H4" s="392" t="s">
         <v>298</v>
       </c>
-      <c r="I4" s="264"/>
+      <c r="I4" s="260"/>
       <c r="J4" s="186"/>
       <c r="L4" s="153" t="s">
         <v>87</v>
@@ -7910,22 +7910,22 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1">
-      <c r="B5" s="333" t="s">
+      <c r="B5" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="285"/>
-      <c r="D5" s="285"/>
-      <c r="E5" s="350" t="s">
+      <c r="C5" s="291"/>
+      <c r="D5" s="291"/>
+      <c r="E5" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="285"/>
+      <c r="F5" s="291"/>
       <c r="G5" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="377" t="s">
+      <c r="H5" s="373" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="264"/>
+      <c r="I5" s="260"/>
       <c r="L5" s="153" t="s">
         <v>91</v>
       </c>
@@ -7935,57 +7935,57 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1">
-      <c r="B6" s="333" t="s">
+      <c r="B6" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="285"/>
-      <c r="D6" s="285"/>
-      <c r="E6" s="378">
+      <c r="C6" s="291"/>
+      <c r="D6" s="291"/>
+      <c r="E6" s="375">
         <v>52.034300000000002</v>
       </c>
-      <c r="F6" s="285"/>
+      <c r="F6" s="291"/>
       <c r="G6" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="363" t="s">
+      <c r="H6" s="394" t="s">
         <v>299</v>
       </c>
-      <c r="I6" s="264"/>
+      <c r="I6" s="260"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1">
       <c r="B7" s="165"/>
-      <c r="C7" s="349" t="s">
+      <c r="C7" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="285"/>
-      <c r="E7" s="366" t="s">
+      <c r="D7" s="291"/>
+      <c r="E7" s="381" t="s">
         <v>135</v>
       </c>
-      <c r="F7" s="285"/>
+      <c r="F7" s="291"/>
       <c r="G7" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H7" s="332">
+      <c r="H7" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I7" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I7" s="260"/>
     </row>
     <row r="8" spans="2:14" ht="15" customHeight="1">
       <c r="B8" s="165"/>
-      <c r="C8" s="349" t="s">
+      <c r="C8" s="334" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="285"/>
-      <c r="E8" s="376">
+      <c r="D8" s="291"/>
+      <c r="E8" s="372">
         <v>11173</v>
       </c>
-      <c r="F8" s="285"/>
+      <c r="F8" s="291"/>
       <c r="G8" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="351"/>
-      <c r="I8" s="264"/>
+      <c r="H8" s="364"/>
+      <c r="I8" s="260"/>
       <c r="J8" s="226"/>
       <c r="K8" s="226"/>
       <c r="L8" s="226"/>
@@ -7993,16 +7993,16 @@
       <c r="N8" s="226"/>
     </row>
     <row r="9" spans="2:14" ht="15" customHeight="1">
-      <c r="B9" s="339" t="s">
+      <c r="B9" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="285"/>
-      <c r="D9" s="285"/>
-      <c r="E9" s="285"/>
-      <c r="F9" s="285"/>
-      <c r="G9" s="285"/>
-      <c r="H9" s="285"/>
-      <c r="I9" s="264"/>
+      <c r="C9" s="291"/>
+      <c r="D9" s="291"/>
+      <c r="E9" s="291"/>
+      <c r="F9" s="291"/>
+      <c r="G9" s="291"/>
+      <c r="H9" s="291"/>
+      <c r="I9" s="260"/>
       <c r="J9" s="226"/>
       <c r="K9" s="226"/>
       <c r="L9" s="226"/>
@@ -8010,21 +8010,21 @@
       <c r="N9" s="226"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1">
-      <c r="B10" s="348" t="s">
+      <c r="B10" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="285"/>
-      <c r="D10" s="285"/>
+      <c r="C10" s="291"/>
+      <c r="D10" s="291"/>
       <c r="E10" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F10" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="340" t="s">
+      <c r="G10" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="285"/>
+      <c r="H10" s="291"/>
       <c r="I10" s="167"/>
       <c r="J10" s="226"/>
       <c r="K10" s="226"/>
@@ -8033,11 +8033,11 @@
       <c r="N10" s="226"/>
     </row>
     <row r="11" spans="2:14" ht="15" customHeight="1">
-      <c r="B11" s="386" t="s">
+      <c r="B11" s="360" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="387"/>
-      <c r="D11" s="387"/>
+      <c r="C11" s="361"/>
+      <c r="D11" s="361"/>
       <c r="E11" s="240">
         <v>7.23</v>
       </c>
@@ -8045,10 +8045,10 @@
         <f>E11/E6</f>
         <v>0.13894681008488632</v>
       </c>
-      <c r="G11" s="388">
+      <c r="G11" s="362">
         <v>1</v>
       </c>
-      <c r="H11" s="388"/>
+      <c r="H11" s="362"/>
       <c r="I11" s="167"/>
       <c r="J11" s="226"/>
       <c r="K11" s="226"/>
@@ -8057,11 +8057,11 @@
       <c r="N11" s="226"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1">
-      <c r="B12" s="375" t="s">
+      <c r="B12" s="371" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="285"/>
-      <c r="D12" s="285"/>
+      <c r="C12" s="291"/>
+      <c r="D12" s="291"/>
       <c r="E12" s="220">
         <f>32.0811-E11</f>
         <v>24.851099999999999</v>
@@ -8070,10 +8070,10 @@
         <f>E12/E6</f>
         <v>0.4775907430291173</v>
       </c>
-      <c r="G12" s="329">
+      <c r="G12" s="336">
         <v>0.8</v>
       </c>
-      <c r="H12" s="285"/>
+      <c r="H12" s="291"/>
       <c r="I12" s="167"/>
       <c r="J12" s="226"/>
       <c r="K12" s="226"/>
@@ -8082,11 +8082,11 @@
       <c r="N12" s="226"/>
     </row>
     <row r="13" spans="2:14" ht="15" customHeight="1">
-      <c r="B13" s="367" t="s">
+      <c r="B13" s="382" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="285"/>
-      <c r="D13" s="285"/>
+      <c r="C13" s="291"/>
+      <c r="D13" s="291"/>
       <c r="E13" s="202">
         <f>18.2121+1.7411</f>
         <v>19.953199999999999</v>
@@ -8095,10 +8095,10 @@
         <f>E13/E6</f>
         <v>0.38346244688599634</v>
       </c>
-      <c r="G13" s="329">
+      <c r="G13" s="336">
         <v>0.6</v>
       </c>
-      <c r="H13" s="285"/>
+      <c r="H13" s="291"/>
       <c r="I13" s="167"/>
       <c r="J13" s="226"/>
       <c r="K13" s="229">
@@ -8111,11 +8111,11 @@
       <c r="N13" s="226"/>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1">
-      <c r="B14" s="334" t="s">
+      <c r="B14" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="252"/>
-      <c r="D14" s="252"/>
+      <c r="C14" s="266"/>
+      <c r="D14" s="266"/>
       <c r="E14" s="170">
         <f>SUM(E11:E13)</f>
         <v>52.034300000000002</v>
@@ -8124,11 +8124,11 @@
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="325">
+      <c r="G14" s="359">
         <f>(F12*G12)+(F13*G13)+F11*G11</f>
         <v>0.75109687263977798</v>
       </c>
-      <c r="H14" s="252"/>
+      <c r="H14" s="266"/>
       <c r="I14" s="172"/>
       <c r="J14" s="227"/>
       <c r="K14" s="228"/>
@@ -8152,96 +8152,96 @@
       <c r="N15" s="226"/>
     </row>
     <row r="16" spans="2:14" ht="15" customHeight="1">
-      <c r="B16" s="343" t="s">
+      <c r="B16" s="357" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="285"/>
-      <c r="D16" s="285"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="285"/>
-      <c r="G16" s="285"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="285"/>
+      <c r="C16" s="291"/>
+      <c r="D16" s="291"/>
+      <c r="E16" s="291"/>
+      <c r="F16" s="291"/>
+      <c r="G16" s="291"/>
+      <c r="H16" s="291"/>
+      <c r="I16" s="291"/>
       <c r="K16" s="203"/>
     </row>
     <row r="17" spans="2:11" ht="15" customHeight="1">
-      <c r="B17" s="335" t="s">
+      <c r="B17" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="336"/>
-      <c r="D17" s="336"/>
-      <c r="E17" s="327" t="s">
+      <c r="C17" s="338"/>
+      <c r="D17" s="338"/>
+      <c r="E17" s="335" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="285"/>
+      <c r="F17" s="291"/>
       <c r="G17" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="359" t="s">
+      <c r="H17" s="347" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="264"/>
+      <c r="I17" s="260"/>
       <c r="K17" s="203" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="15" customHeight="1">
-      <c r="B18" s="333" t="s">
+      <c r="B18" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="285"/>
-      <c r="D18" s="285"/>
-      <c r="E18" s="350" t="s">
+      <c r="C18" s="291"/>
+      <c r="D18" s="291"/>
+      <c r="E18" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="285"/>
+      <c r="F18" s="291"/>
       <c r="G18" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H18" s="362" t="s">
+      <c r="H18" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="264"/>
+      <c r="I18" s="260"/>
       <c r="K18" s="203"/>
     </row>
     <row r="19" spans="2:11" ht="15" customHeight="1">
-      <c r="B19" s="333" t="s">
+      <c r="B19" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="285"/>
-      <c r="D19" s="285"/>
-      <c r="E19" s="371">
+      <c r="C19" s="291"/>
+      <c r="D19" s="291"/>
+      <c r="E19" s="374">
         <f>3500*4.84</f>
         <v>16940</v>
       </c>
-      <c r="F19" s="285"/>
+      <c r="F19" s="291"/>
       <c r="G19" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="330" t="s">
+      <c r="H19" s="366" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="264"/>
+      <c r="I19" s="260"/>
     </row>
     <row r="20" spans="2:11" ht="15" customHeight="1">
       <c r="B20" s="211"/>
-      <c r="C20" s="349" t="s">
+      <c r="C20" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="285"/>
-      <c r="E20" s="355">
+      <c r="D20" s="291"/>
+      <c r="E20" s="380">
         <f>180000000</f>
         <v>180000000</v>
       </c>
-      <c r="F20" s="285"/>
+      <c r="F20" s="291"/>
       <c r="G20" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="331">
+      <c r="H20" s="369">
         <f>E20/E19</f>
         <v>10625.737898465171</v>
       </c>
-      <c r="I20" s="264"/>
+      <c r="I20" s="260"/>
       <c r="K20" s="221">
         <f>H20*4.84</f>
         <v>51428.571428571428</v>
@@ -8249,76 +8249,76 @@
     </row>
     <row r="21" spans="2:11" ht="15" customHeight="1">
       <c r="B21" s="212"/>
-      <c r="C21" s="349" t="s">
+      <c r="C21" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="285"/>
-      <c r="E21" s="373" t="s">
+      <c r="D21" s="291"/>
+      <c r="E21" s="341" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="285"/>
+      <c r="F21" s="291"/>
       <c r="G21" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="332">
+      <c r="H21" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I21" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I21" s="260"/>
     </row>
     <row r="22" spans="2:11" ht="15" customHeight="1">
       <c r="B22" s="212"/>
-      <c r="C22" s="349" t="s">
+      <c r="C22" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="285"/>
-      <c r="E22" s="327" t="s">
+      <c r="D22" s="291"/>
+      <c r="E22" s="335" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="285"/>
+      <c r="F22" s="291"/>
       <c r="G22" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H22" s="368"/>
-      <c r="I22" s="264"/>
+      <c r="H22" s="377"/>
+      <c r="I22" s="260"/>
       <c r="K22" s="238"/>
     </row>
     <row r="23" spans="2:11" ht="15" customHeight="1">
-      <c r="B23" s="339" t="s">
+      <c r="B23" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="285"/>
-      <c r="D23" s="285"/>
-      <c r="E23" s="285"/>
-      <c r="F23" s="285"/>
-      <c r="G23" s="285"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="264"/>
+      <c r="C23" s="291"/>
+      <c r="D23" s="291"/>
+      <c r="E23" s="291"/>
+      <c r="F23" s="291"/>
+      <c r="G23" s="291"/>
+      <c r="H23" s="291"/>
+      <c r="I23" s="260"/>
     </row>
     <row r="24" spans="2:11" ht="15" customHeight="1">
-      <c r="B24" s="348" t="s">
+      <c r="B24" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="285"/>
-      <c r="D24" s="285"/>
+      <c r="C24" s="291"/>
+      <c r="D24" s="291"/>
       <c r="E24" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F24" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="340" t="s">
+      <c r="G24" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="285"/>
+      <c r="H24" s="291"/>
       <c r="I24" s="213"/>
     </row>
     <row r="25" spans="2:11" ht="15" customHeight="1">
-      <c r="B25" s="337" t="s">
+      <c r="B25" s="344" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="285"/>
-      <c r="D25" s="285"/>
+      <c r="C25" s="291"/>
+      <c r="D25" s="291"/>
       <c r="E25" s="214">
         <f>600 *4.84</f>
         <v>2904</v>
@@ -8327,10 +8327,10 @@
         <f>E25/E19</f>
         <v>0.17142857142857143</v>
       </c>
-      <c r="G25" s="338">
+      <c r="G25" s="350">
         <v>1</v>
       </c>
-      <c r="H25" s="285"/>
+      <c r="H25" s="291"/>
       <c r="I25" s="213"/>
     </row>
     <row r="26" spans="2:11" ht="15" customHeight="1">
@@ -8347,18 +8347,18 @@
         <f>E26/E19</f>
         <v>0.47857142857142859</v>
       </c>
-      <c r="G26" s="338">
+      <c r="G26" s="350">
         <v>0.8</v>
       </c>
-      <c r="H26" s="285"/>
+      <c r="H26" s="291"/>
       <c r="I26" s="213"/>
     </row>
     <row r="27" spans="2:11" ht="15" customHeight="1">
-      <c r="B27" s="364" t="s">
+      <c r="B27" s="383" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="285"/>
-      <c r="D27" s="285"/>
+      <c r="C27" s="291"/>
+      <c r="D27" s="291"/>
       <c r="E27" s="214">
         <f>E19*0.35</f>
         <v>5929</v>
@@ -8367,18 +8367,18 @@
         <f>E27/E19</f>
         <v>0.35</v>
       </c>
-      <c r="G27" s="338">
+      <c r="G27" s="350">
         <v>0.6</v>
       </c>
-      <c r="H27" s="285"/>
+      <c r="H27" s="291"/>
       <c r="I27" s="213"/>
     </row>
     <row r="28" spans="2:11" ht="15" customHeight="1">
-      <c r="B28" s="334" t="s">
+      <c r="B28" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="252"/>
-      <c r="D28" s="252"/>
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
       <c r="E28" s="170">
         <f>SUM(E25:E27)</f>
         <v>16940</v>
@@ -8387,11 +8387,11 @@
         <f>SUM(F25:F27)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="325">
+      <c r="G28" s="359">
         <f>F25*G25+F26*G26+F27*G27</f>
         <v>0.76428571428571423</v>
       </c>
-      <c r="H28" s="252"/>
+      <c r="H28" s="266"/>
       <c r="I28" s="216"/>
     </row>
     <row r="29" spans="2:11" ht="15" customHeight="1">
@@ -8405,95 +8405,95 @@
       <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:11" ht="15" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="357" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="285"/>
-      <c r="D30" s="285"/>
-      <c r="E30" s="285"/>
-      <c r="F30" s="285"/>
-      <c r="G30" s="285"/>
-      <c r="H30" s="285"/>
-      <c r="I30" s="285"/>
+      <c r="C30" s="291"/>
+      <c r="D30" s="291"/>
+      <c r="E30" s="291"/>
+      <c r="F30" s="291"/>
+      <c r="G30" s="291"/>
+      <c r="H30" s="291"/>
+      <c r="I30" s="291"/>
     </row>
     <row r="31" spans="2:11" ht="15" customHeight="1">
-      <c r="B31" s="335" t="s">
+      <c r="B31" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="336"/>
-      <c r="D31" s="336"/>
-      <c r="E31" s="327" t="s">
+      <c r="C31" s="338"/>
+      <c r="D31" s="338"/>
+      <c r="E31" s="335" t="s">
         <v>118</v>
       </c>
-      <c r="F31" s="285"/>
+      <c r="F31" s="291"/>
       <c r="G31" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="359" t="s">
+      <c r="H31" s="347" t="s">
         <v>119</v>
       </c>
-      <c r="I31" s="264"/>
+      <c r="I31" s="260"/>
       <c r="J31" s="185"/>
       <c r="K31" s="152" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15" customHeight="1">
-      <c r="B32" s="333" t="s">
+      <c r="B32" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="285"/>
-      <c r="D32" s="285"/>
-      <c r="E32" s="350" t="s">
+      <c r="C32" s="291"/>
+      <c r="D32" s="291"/>
+      <c r="E32" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F32" s="285"/>
+      <c r="F32" s="291"/>
       <c r="G32" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H32" s="362" t="s">
+      <c r="H32" s="345" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="264"/>
+      <c r="I32" s="260"/>
       <c r="K32" s="203"/>
     </row>
     <row r="33" spans="2:11" ht="15" customHeight="1">
-      <c r="B33" s="333" t="s">
+      <c r="B33" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="285"/>
-      <c r="D33" s="285"/>
-      <c r="E33" s="360">
+      <c r="C33" s="291"/>
+      <c r="D33" s="291"/>
+      <c r="E33" s="386">
         <v>1258.4000000000001</v>
       </c>
-      <c r="F33" s="285"/>
+      <c r="F33" s="291"/>
       <c r="G33" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H33" s="362" t="s">
+      <c r="H33" s="345" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="264"/>
+      <c r="I33" s="260"/>
       <c r="K33" s="203"/>
     </row>
     <row r="34" spans="2:11" ht="15" customHeight="1">
       <c r="B34" s="211"/>
-      <c r="C34" s="349" t="s">
+      <c r="C34" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D34" s="285"/>
-      <c r="E34" s="355">
+      <c r="D34" s="291"/>
+      <c r="E34" s="380">
         <v>16900000</v>
       </c>
-      <c r="F34" s="285"/>
+      <c r="F34" s="291"/>
       <c r="G34" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="331">
+      <c r="H34" s="369">
         <f>E34/E33</f>
         <v>13429.752066115701</v>
       </c>
-      <c r="I34" s="264"/>
+      <c r="I34" s="260"/>
       <c r="K34" s="221">
         <f>H34*4.84</f>
         <v>64999.999999999993</v>
@@ -8501,76 +8501,76 @@
     </row>
     <row r="35" spans="2:11" ht="15" customHeight="1">
       <c r="B35" s="212"/>
-      <c r="C35" s="349" t="s">
+      <c r="C35" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="285"/>
-      <c r="E35" s="373" t="s">
+      <c r="D35" s="291"/>
+      <c r="E35" s="341" t="s">
         <v>115</v>
       </c>
-      <c r="F35" s="285"/>
+      <c r="F35" s="291"/>
       <c r="G35" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H35" s="332">
+      <c r="H35" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I35" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I35" s="260"/>
     </row>
     <row r="36" spans="2:11" ht="15" customHeight="1">
       <c r="B36" s="212"/>
-      <c r="C36" s="349" t="s">
+      <c r="C36" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="285"/>
-      <c r="E36" s="327" t="s">
+      <c r="D36" s="291"/>
+      <c r="E36" s="335" t="s">
         <v>96</v>
       </c>
-      <c r="F36" s="285"/>
+      <c r="F36" s="291"/>
       <c r="G36" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="368"/>
-      <c r="I36" s="264"/>
+      <c r="H36" s="377"/>
+      <c r="I36" s="260"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1">
-      <c r="B37" s="339" t="s">
+      <c r="B37" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="285"/>
-      <c r="D37" s="285"/>
-      <c r="E37" s="285"/>
-      <c r="F37" s="285"/>
-      <c r="G37" s="285"/>
-      <c r="H37" s="285"/>
-      <c r="I37" s="264"/>
+      <c r="C37" s="291"/>
+      <c r="D37" s="291"/>
+      <c r="E37" s="291"/>
+      <c r="F37" s="291"/>
+      <c r="G37" s="291"/>
+      <c r="H37" s="291"/>
+      <c r="I37" s="260"/>
       <c r="K37" s="238"/>
     </row>
     <row r="38" spans="2:11" ht="15" customHeight="1">
-      <c r="B38" s="348" t="s">
+      <c r="B38" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="285"/>
-      <c r="D38" s="285"/>
+      <c r="C38" s="291"/>
+      <c r="D38" s="291"/>
       <c r="E38" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F38" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G38" s="340" t="s">
+      <c r="G38" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H38" s="285"/>
+      <c r="H38" s="291"/>
       <c r="I38" s="213"/>
     </row>
     <row r="39" spans="2:11" ht="15" customHeight="1">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="344" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="285"/>
-      <c r="D39" s="285"/>
+      <c r="C39" s="291"/>
+      <c r="D39" s="291"/>
       <c r="E39" s="214">
         <v>145.19999999999999</v>
       </c>
@@ -8578,10 +8578,10 @@
         <f>E39/E33</f>
         <v>0.11538461538461536</v>
       </c>
-      <c r="G39" s="338">
+      <c r="G39" s="350">
         <v>1</v>
       </c>
-      <c r="H39" s="285"/>
+      <c r="H39" s="291"/>
       <c r="I39" s="213"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1">
@@ -8598,18 +8598,18 @@
         <f>E40/E33</f>
         <v>0.53341538461538451</v>
       </c>
-      <c r="G40" s="338">
+      <c r="G40" s="350">
         <v>0.8</v>
       </c>
-      <c r="H40" s="285"/>
+      <c r="H40" s="291"/>
       <c r="I40" s="213"/>
     </row>
     <row r="41" spans="2:11" ht="15" customHeight="1">
-      <c r="B41" s="364" t="s">
+      <c r="B41" s="383" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="285"/>
-      <c r="D41" s="285"/>
+      <c r="C41" s="291"/>
+      <c r="D41" s="291"/>
       <c r="E41" s="214">
         <f>E33*0.3512</f>
         <v>441.95008000000007</v>
@@ -8618,18 +8618,18 @@
         <f>E41/E33</f>
         <v>0.35120000000000001</v>
       </c>
-      <c r="G41" s="338">
+      <c r="G41" s="350">
         <v>0.6</v>
       </c>
-      <c r="H41" s="285"/>
+      <c r="H41" s="291"/>
       <c r="I41" s="213"/>
     </row>
     <row r="42" spans="2:11" ht="15" customHeight="1">
-      <c r="B42" s="334" t="s">
+      <c r="B42" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="252"/>
-      <c r="D42" s="252"/>
+      <c r="C42" s="266"/>
+      <c r="D42" s="266"/>
       <c r="E42" s="170">
         <f>SUM(E39:E41)</f>
         <v>1258.4000000000001</v>
@@ -8638,11 +8638,11 @@
         <f>F39+F41+F40</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G42" s="325">
+      <c r="G42" s="359">
         <f>F41*G41+F39*G39+F40*G40</f>
         <v>0.75283692307692296</v>
       </c>
-      <c r="H42" s="252"/>
+      <c r="H42" s="266"/>
       <c r="I42" s="216"/>
     </row>
     <row r="43" spans="2:11" ht="15" customHeight="1">
@@ -8656,93 +8656,93 @@
       <c r="I43" s="173"/>
     </row>
     <row r="44" spans="2:11" ht="15" customHeight="1">
-      <c r="B44" s="361" t="s">
+      <c r="B44" s="393" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="285"/>
-      <c r="D44" s="285"/>
-      <c r="E44" s="285"/>
-      <c r="F44" s="285"/>
-      <c r="G44" s="285"/>
-      <c r="H44" s="285"/>
-      <c r="I44" s="285"/>
+      <c r="C44" s="291"/>
+      <c r="D44" s="291"/>
+      <c r="E44" s="291"/>
+      <c r="F44" s="291"/>
+      <c r="G44" s="291"/>
+      <c r="H44" s="291"/>
+      <c r="I44" s="291"/>
     </row>
     <row r="45" spans="2:11" ht="15" customHeight="1">
-      <c r="B45" s="335" t="s">
+      <c r="B45" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C45" s="336"/>
-      <c r="D45" s="336"/>
-      <c r="E45" s="350" t="s">
+      <c r="C45" s="338"/>
+      <c r="D45" s="338"/>
+      <c r="E45" s="332" t="s">
         <v>118</v>
       </c>
-      <c r="F45" s="285"/>
+      <c r="F45" s="291"/>
       <c r="G45" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H45" s="359" t="s">
+      <c r="H45" s="347" t="s">
         <v>119</v>
       </c>
-      <c r="I45" s="264"/>
+      <c r="I45" s="260"/>
       <c r="K45" s="203" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1">
-      <c r="B46" s="333" t="s">
+      <c r="B46" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="285"/>
-      <c r="D46" s="285"/>
-      <c r="E46" s="350" t="s">
+      <c r="C46" s="291"/>
+      <c r="D46" s="291"/>
+      <c r="E46" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F46" s="285"/>
+      <c r="F46" s="291"/>
       <c r="G46" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H46" s="362" t="s">
+      <c r="H46" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I46" s="264"/>
+      <c r="I46" s="260"/>
     </row>
     <row r="47" spans="2:11" ht="15" customHeight="1">
-      <c r="B47" s="333" t="s">
+      <c r="B47" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="285"/>
-      <c r="D47" s="285"/>
-      <c r="E47" s="371">
+      <c r="C47" s="291"/>
+      <c r="D47" s="291"/>
+      <c r="E47" s="374">
         <v>430.76</v>
       </c>
-      <c r="F47" s="285"/>
+      <c r="F47" s="291"/>
       <c r="G47" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H47" s="330" t="s">
+      <c r="H47" s="366" t="s">
         <v>94</v>
       </c>
-      <c r="I47" s="264"/>
+      <c r="I47" s="260"/>
       <c r="K47" s="203"/>
     </row>
     <row r="48" spans="2:11" ht="15" customHeight="1">
       <c r="B48" s="164"/>
-      <c r="C48" s="349" t="s">
+      <c r="C48" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="285"/>
-      <c r="E48" s="326">
+      <c r="D48" s="291"/>
+      <c r="E48" s="356">
         <v>7120000</v>
       </c>
-      <c r="F48" s="285"/>
+      <c r="F48" s="291"/>
       <c r="G48" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H48" s="346">
+      <c r="H48" s="370">
         <f>E48/E47</f>
         <v>16528.92561983471</v>
       </c>
-      <c r="I48" s="264"/>
+      <c r="I48" s="260"/>
       <c r="J48" s="221"/>
       <c r="K48" s="221">
         <f>H48*4.84</f>
@@ -8751,76 +8751,76 @@
     </row>
     <row r="49" spans="2:11" ht="15" customHeight="1">
       <c r="B49" s="165"/>
-      <c r="C49" s="349" t="s">
+      <c r="C49" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="285"/>
-      <c r="E49" s="373" t="s">
+      <c r="D49" s="291"/>
+      <c r="E49" s="341" t="s">
         <v>115</v>
       </c>
-      <c r="F49" s="285"/>
+      <c r="F49" s="291"/>
       <c r="G49" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H49" s="332">
+      <c r="H49" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I49" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I49" s="260"/>
     </row>
     <row r="50" spans="2:11" ht="15" customHeight="1">
       <c r="B50" s="165"/>
-      <c r="C50" s="349" t="s">
+      <c r="C50" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="285"/>
-      <c r="E50" s="327" t="s">
+      <c r="D50" s="291"/>
+      <c r="E50" s="335" t="s">
         <v>123</v>
       </c>
-      <c r="F50" s="285"/>
+      <c r="F50" s="291"/>
       <c r="G50" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H50" s="351"/>
-      <c r="I50" s="264"/>
+      <c r="H50" s="364"/>
+      <c r="I50" s="260"/>
       <c r="K50" s="238"/>
     </row>
     <row r="51" spans="2:11" ht="15" customHeight="1">
-      <c r="B51" s="339" t="s">
+      <c r="B51" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="285"/>
-      <c r="D51" s="285"/>
-      <c r="E51" s="285"/>
-      <c r="F51" s="285"/>
-      <c r="G51" s="285"/>
-      <c r="H51" s="285"/>
-      <c r="I51" s="264"/>
+      <c r="C51" s="291"/>
+      <c r="D51" s="291"/>
+      <c r="E51" s="291"/>
+      <c r="F51" s="291"/>
+      <c r="G51" s="291"/>
+      <c r="H51" s="291"/>
+      <c r="I51" s="260"/>
     </row>
     <row r="52" spans="2:11" ht="15" customHeight="1">
-      <c r="B52" s="348" t="s">
+      <c r="B52" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="285"/>
-      <c r="D52" s="285"/>
+      <c r="C52" s="291"/>
+      <c r="D52" s="291"/>
       <c r="E52" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F52" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G52" s="340" t="s">
+      <c r="G52" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H52" s="285"/>
+      <c r="H52" s="291"/>
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="2:11" ht="15" customHeight="1">
-      <c r="B53" s="337" t="s">
+      <c r="B53" s="344" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="285"/>
-      <c r="D53" s="285"/>
+      <c r="C53" s="291"/>
+      <c r="D53" s="291"/>
       <c r="E53" s="168">
         <v>145.19999999999999</v>
       </c>
@@ -8828,10 +8828,10 @@
         <f>E53/E47</f>
         <v>0.33707865168539325</v>
       </c>
-      <c r="G53" s="329">
+      <c r="G53" s="336">
         <v>1</v>
       </c>
-      <c r="H53" s="285"/>
+      <c r="H53" s="291"/>
       <c r="I53" s="167"/>
     </row>
     <row r="54" spans="2:11" ht="15" customHeight="1">
@@ -8848,10 +8848,10 @@
         <f>E54/E47</f>
         <v>0.31042134831460677</v>
       </c>
-      <c r="G54" s="329">
+      <c r="G54" s="336">
         <v>0.8</v>
       </c>
-      <c r="H54" s="285"/>
+      <c r="H54" s="291"/>
       <c r="I54" s="167"/>
     </row>
     <row r="55" spans="2:11" ht="15" customHeight="1">
@@ -8868,18 +8868,18 @@
         <f>E55/E47</f>
         <v>0.35249999999999998</v>
       </c>
-      <c r="G55" s="329">
+      <c r="G55" s="336">
         <v>0.6</v>
       </c>
-      <c r="H55" s="285"/>
+      <c r="H55" s="291"/>
       <c r="I55" s="167"/>
     </row>
     <row r="56" spans="2:11" ht="15" customHeight="1">
-      <c r="B56" s="334" t="s">
+      <c r="B56" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C56" s="252"/>
-      <c r="D56" s="252"/>
+      <c r="C56" s="266"/>
+      <c r="D56" s="266"/>
       <c r="E56" s="170">
         <f>SUM(E53:E55)</f>
         <v>430.76</v>
@@ -8888,11 +8888,11 @@
         <f>SUM(F53:F55)</f>
         <v>1</v>
       </c>
-      <c r="G56" s="325">
+      <c r="G56" s="359">
         <f>F53*G53+F55*G55+F54*G54</f>
         <v>0.79691573033707863</v>
       </c>
-      <c r="H56" s="252"/>
+      <c r="H56" s="266"/>
       <c r="I56" s="172"/>
     </row>
     <row r="57" spans="2:11" ht="15" customHeight="1">
@@ -8906,93 +8906,93 @@
       <c r="I57" s="173"/>
     </row>
     <row r="58" spans="2:11" ht="15" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="357" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="285"/>
-      <c r="D58" s="285"/>
-      <c r="E58" s="285"/>
-      <c r="F58" s="285"/>
-      <c r="G58" s="285"/>
-      <c r="H58" s="285"/>
-      <c r="I58" s="285"/>
+      <c r="C58" s="291"/>
+      <c r="D58" s="291"/>
+      <c r="E58" s="291"/>
+      <c r="F58" s="291"/>
+      <c r="G58" s="291"/>
+      <c r="H58" s="291"/>
+      <c r="I58" s="291"/>
       <c r="K58" s="203"/>
     </row>
     <row r="59" spans="2:11" ht="15" customHeight="1">
-      <c r="B59" s="335" t="s">
+      <c r="B59" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="336"/>
-      <c r="D59" s="336"/>
-      <c r="E59" s="350" t="s">
+      <c r="C59" s="338"/>
+      <c r="D59" s="338"/>
+      <c r="E59" s="332" t="s">
         <v>125</v>
       </c>
-      <c r="F59" s="285"/>
+      <c r="F59" s="291"/>
       <c r="G59" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H59" s="372" t="s">
+      <c r="H59" s="376" t="s">
         <v>126</v>
       </c>
-      <c r="I59" s="264"/>
+      <c r="I59" s="260"/>
       <c r="K59" s="203" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="60" spans="2:11" ht="15" customHeight="1">
-      <c r="B60" s="333" t="s">
+      <c r="B60" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C60" s="285"/>
-      <c r="D60" s="285"/>
-      <c r="E60" s="350" t="s">
+      <c r="C60" s="291"/>
+      <c r="D60" s="291"/>
+      <c r="E60" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F60" s="285"/>
+      <c r="F60" s="291"/>
       <c r="G60" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H60" s="362" t="s">
+      <c r="H60" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="264"/>
+      <c r="I60" s="260"/>
     </row>
     <row r="61" spans="2:11" ht="15" customHeight="1">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="285"/>
-      <c r="D61" s="285"/>
-      <c r="E61" s="341">
+      <c r="C61" s="291"/>
+      <c r="D61" s="291"/>
+      <c r="E61" s="378">
         <v>626</v>
       </c>
-      <c r="F61" s="285"/>
+      <c r="F61" s="291"/>
       <c r="G61" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H61" s="362" t="s">
+      <c r="H61" s="345" t="s">
         <v>128</v>
       </c>
-      <c r="I61" s="264"/>
+      <c r="I61" s="260"/>
     </row>
     <row r="62" spans="2:11" ht="15" customHeight="1">
       <c r="B62" s="164"/>
-      <c r="C62" s="349" t="s">
+      <c r="C62" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D62" s="285"/>
-      <c r="E62" s="365">
+      <c r="D62" s="291"/>
+      <c r="E62" s="387">
         <v>10500000</v>
       </c>
-      <c r="F62" s="285"/>
+      <c r="F62" s="291"/>
       <c r="G62" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H62" s="342">
+      <c r="H62" s="339">
         <f>E62/E61</f>
         <v>16773.162939297126</v>
       </c>
-      <c r="I62" s="264"/>
+      <c r="I62" s="260"/>
       <c r="J62" s="221"/>
       <c r="K62" s="221">
         <f>H62*4.84</f>
@@ -9001,68 +9001,68 @@
     </row>
     <row r="63" spans="2:11" ht="15" customHeight="1">
       <c r="B63" s="165"/>
-      <c r="C63" s="349" t="s">
+      <c r="C63" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="285"/>
-      <c r="E63" s="369" t="s">
+      <c r="D63" s="291"/>
+      <c r="E63" s="384" t="s">
         <v>115</v>
       </c>
-      <c r="F63" s="285"/>
+      <c r="F63" s="291"/>
       <c r="G63" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H63" s="332">
+      <c r="H63" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I63" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I63" s="260"/>
     </row>
     <row r="64" spans="2:11" ht="15" customHeight="1">
       <c r="B64" s="165"/>
-      <c r="C64" s="349" t="s">
+      <c r="C64" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="285"/>
-      <c r="E64" s="327" t="s">
+      <c r="D64" s="291"/>
+      <c r="E64" s="335" t="s">
         <v>96</v>
       </c>
-      <c r="F64" s="285"/>
+      <c r="F64" s="291"/>
       <c r="G64" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H64" s="351"/>
-      <c r="I64" s="264"/>
+      <c r="H64" s="364"/>
+      <c r="I64" s="260"/>
       <c r="K64" s="238"/>
     </row>
     <row r="65" spans="2:11" ht="15" customHeight="1">
-      <c r="B65" s="339" t="s">
+      <c r="B65" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="285"/>
-      <c r="D65" s="285"/>
-      <c r="E65" s="285"/>
-      <c r="F65" s="285"/>
-      <c r="G65" s="285"/>
-      <c r="H65" s="285"/>
-      <c r="I65" s="264"/>
+      <c r="C65" s="291"/>
+      <c r="D65" s="291"/>
+      <c r="E65" s="291"/>
+      <c r="F65" s="291"/>
+      <c r="G65" s="291"/>
+      <c r="H65" s="291"/>
+      <c r="I65" s="260"/>
     </row>
     <row r="66" spans="2:11" ht="15" customHeight="1">
-      <c r="B66" s="348" t="s">
+      <c r="B66" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="285"/>
-      <c r="D66" s="285"/>
+      <c r="C66" s="291"/>
+      <c r="D66" s="291"/>
       <c r="E66" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F66" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G66" s="340" t="s">
+      <c r="G66" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H66" s="285"/>
+      <c r="H66" s="291"/>
       <c r="I66" s="167"/>
     </row>
     <row r="67" spans="2:11" ht="15" customHeight="1">
@@ -9078,10 +9078,10 @@
         <f>E67/E61</f>
         <v>0.30830670926517573</v>
       </c>
-      <c r="G67" s="329">
+      <c r="G67" s="336">
         <v>1</v>
       </c>
-      <c r="H67" s="285"/>
+      <c r="H67" s="291"/>
       <c r="I67" s="167"/>
     </row>
     <row r="68" spans="2:11" ht="15" customHeight="1">
@@ -9097,18 +9097,18 @@
         <f>E68/E61</f>
         <v>0.27156549520766771</v>
       </c>
-      <c r="G68" s="329">
+      <c r="G68" s="336">
         <v>0.9</v>
       </c>
-      <c r="H68" s="285"/>
+      <c r="H68" s="291"/>
       <c r="I68" s="167"/>
     </row>
     <row r="69" spans="2:11" ht="15" customHeight="1">
-      <c r="B69" s="370" t="s">
+      <c r="B69" s="385" t="s">
         <v>106</v>
       </c>
-      <c r="C69" s="285"/>
-      <c r="D69" s="285"/>
+      <c r="C69" s="291"/>
+      <c r="D69" s="291"/>
       <c r="E69" s="168">
         <f>E61-E67-E68</f>
         <v>263</v>
@@ -9117,18 +9117,18 @@
         <f>E69/E61</f>
         <v>0.42012779552715657</v>
       </c>
-      <c r="G69" s="329">
+      <c r="G69" s="336">
         <v>0.6</v>
       </c>
-      <c r="H69" s="285"/>
+      <c r="H69" s="291"/>
       <c r="I69" s="167"/>
     </row>
     <row r="70" spans="2:11" ht="15" customHeight="1">
-      <c r="B70" s="334" t="s">
+      <c r="B70" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C70" s="252"/>
-      <c r="D70" s="252"/>
+      <c r="C70" s="266"/>
+      <c r="D70" s="266"/>
       <c r="E70" s="170">
         <f>SUM(E67:E69)</f>
         <v>626</v>
@@ -9137,11 +9137,11 @@
         <f>SUM(F67:F69)</f>
         <v>1</v>
       </c>
-      <c r="G70" s="325">
+      <c r="G70" s="359">
         <f>F67*G67+F69*G69+F68*G68</f>
         <v>0.80479233226837055</v>
       </c>
-      <c r="H70" s="252"/>
+      <c r="H70" s="266"/>
       <c r="I70" s="172"/>
     </row>
     <row r="71" spans="2:11" ht="15" customHeight="1">
@@ -9155,112 +9155,112 @@
       <c r="I71" s="173"/>
     </row>
     <row r="72" spans="2:11" ht="15" customHeight="1">
-      <c r="B72" s="343" t="s">
+      <c r="B72" s="357" t="s">
         <v>130</v>
       </c>
-      <c r="C72" s="285"/>
-      <c r="D72" s="285"/>
-      <c r="E72" s="285"/>
-      <c r="F72" s="285"/>
-      <c r="G72" s="285"/>
-      <c r="H72" s="285"/>
-      <c r="I72" s="285"/>
+      <c r="C72" s="291"/>
+      <c r="D72" s="291"/>
+      <c r="E72" s="291"/>
+      <c r="F72" s="291"/>
+      <c r="G72" s="291"/>
+      <c r="H72" s="291"/>
+      <c r="I72" s="291"/>
     </row>
     <row r="73" spans="2:11" ht="15" customHeight="1">
-      <c r="B73" s="335" t="s">
+      <c r="B73" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="327" t="s">
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="335" t="s">
         <v>131</v>
       </c>
-      <c r="F73" s="285"/>
+      <c r="F73" s="291"/>
       <c r="G73" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H73" s="359" t="s">
+      <c r="H73" s="347" t="s">
         <v>132</v>
       </c>
-      <c r="I73" s="264"/>
+      <c r="I73" s="260"/>
       <c r="K73" s="203" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="74" spans="2:11" ht="15" customHeight="1">
-      <c r="B74" s="333" t="s">
+      <c r="B74" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C74" s="285"/>
-      <c r="D74" s="285"/>
-      <c r="E74" s="327" t="s">
+      <c r="C74" s="291"/>
+      <c r="D74" s="291"/>
+      <c r="E74" s="335" t="s">
         <v>134</v>
       </c>
-      <c r="F74" s="285"/>
+      <c r="F74" s="291"/>
       <c r="G74" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H74" s="362" t="s">
+      <c r="H74" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I74" s="264"/>
+      <c r="I74" s="260"/>
     </row>
     <row r="75" spans="2:11" ht="15" customHeight="1">
-      <c r="B75" s="333" t="s">
+      <c r="B75" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C75" s="285"/>
-      <c r="D75" s="285"/>
-      <c r="E75" s="344">
+      <c r="C75" s="291"/>
+      <c r="D75" s="291"/>
+      <c r="E75" s="397">
         <f>730 *4.84</f>
         <v>3533.2</v>
       </c>
-      <c r="F75" s="285"/>
+      <c r="F75" s="291"/>
       <c r="G75" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H75" s="330" t="s">
+      <c r="H75" s="366" t="s">
         <v>94</v>
       </c>
-      <c r="I75" s="264"/>
+      <c r="I75" s="260"/>
     </row>
     <row r="76" spans="2:11" ht="15" customHeight="1">
       <c r="B76" s="164"/>
-      <c r="C76" s="349" t="s">
+      <c r="C76" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D76" s="285"/>
-      <c r="E76" s="326">
+      <c r="D76" s="291"/>
+      <c r="E76" s="356">
         <v>60000000</v>
       </c>
-      <c r="F76" s="285"/>
+      <c r="F76" s="291"/>
       <c r="G76" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H76" s="346">
+      <c r="H76" s="370">
         <f>E76/E75</f>
         <v>16981.772897090457</v>
       </c>
-      <c r="I76" s="264"/>
+      <c r="I76" s="260"/>
     </row>
     <row r="77" spans="2:11" ht="15" customHeight="1">
       <c r="B77" s="165"/>
-      <c r="C77" s="349" t="s">
+      <c r="C77" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D77" s="285"/>
-      <c r="E77" s="382" t="s">
+      <c r="D77" s="291"/>
+      <c r="E77" s="368" t="s">
         <v>115</v>
       </c>
-      <c r="F77" s="285"/>
+      <c r="F77" s="291"/>
       <c r="G77" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H77" s="332">
+      <c r="H77" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I77" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I77" s="260"/>
       <c r="K77" s="221">
         <f>H76*4.84</f>
         <v>82191.780821917811</v>
@@ -9268,57 +9268,57 @@
     </row>
     <row r="78" spans="2:11" ht="15" customHeight="1">
       <c r="B78" s="165"/>
-      <c r="C78" s="349" t="s">
+      <c r="C78" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D78" s="285"/>
-      <c r="E78" s="327" t="s">
+      <c r="D78" s="291"/>
+      <c r="E78" s="335" t="s">
         <v>135</v>
       </c>
-      <c r="F78" s="285"/>
+      <c r="F78" s="291"/>
       <c r="G78" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H78" s="351"/>
-      <c r="I78" s="264"/>
+      <c r="H78" s="364"/>
+      <c r="I78" s="260"/>
     </row>
     <row r="79" spans="2:11" ht="15" customHeight="1">
-      <c r="B79" s="339" t="s">
+      <c r="B79" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C79" s="285"/>
-      <c r="D79" s="285"/>
-      <c r="E79" s="285"/>
-      <c r="F79" s="285"/>
-      <c r="G79" s="285"/>
-      <c r="H79" s="285"/>
-      <c r="I79" s="264"/>
+      <c r="C79" s="291"/>
+      <c r="D79" s="291"/>
+      <c r="E79" s="291"/>
+      <c r="F79" s="291"/>
+      <c r="G79" s="291"/>
+      <c r="H79" s="291"/>
+      <c r="I79" s="260"/>
       <c r="K79" s="238"/>
     </row>
     <row r="80" spans="2:11" ht="15" customHeight="1">
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C80" s="285"/>
-      <c r="D80" s="285"/>
+      <c r="C80" s="291"/>
+      <c r="D80" s="291"/>
       <c r="E80" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F80" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G80" s="340" t="s">
+      <c r="G80" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H80" s="285"/>
+      <c r="H80" s="291"/>
       <c r="I80" s="167"/>
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1">
-      <c r="B81" s="347" t="s">
+      <c r="B81" s="343" t="s">
         <v>129</v>
       </c>
-      <c r="C81" s="285"/>
-      <c r="D81" s="285"/>
+      <c r="C81" s="291"/>
+      <c r="D81" s="291"/>
       <c r="E81" s="168">
         <f>410*4.84</f>
         <v>1984.3999999999999</v>
@@ -9327,18 +9327,18 @@
         <f>E81/E75</f>
         <v>0.56164383561643838</v>
       </c>
-      <c r="G81" s="329">
+      <c r="G81" s="336">
         <v>0.9</v>
       </c>
-      <c r="H81" s="285"/>
+      <c r="H81" s="291"/>
       <c r="I81" s="167"/>
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1">
-      <c r="B82" s="347" t="s">
+      <c r="B82" s="343" t="s">
         <v>116</v>
       </c>
-      <c r="C82" s="285"/>
-      <c r="D82" s="285"/>
+      <c r="C82" s="291"/>
+      <c r="D82" s="291"/>
       <c r="E82" s="168">
         <f>E75-(E81+E83)</f>
         <v>306.52687999999989</v>
@@ -9347,10 +9347,10 @@
         <f>E82/E75</f>
         <v>8.6756164383561624E-2</v>
       </c>
-      <c r="G82" s="329">
+      <c r="G82" s="336">
         <v>0.8</v>
       </c>
-      <c r="H82" s="285"/>
+      <c r="H82" s="291"/>
       <c r="I82" s="167"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1">
@@ -9367,18 +9367,18 @@
         <f>E83/E75</f>
         <v>0.35160000000000002</v>
       </c>
-      <c r="G83" s="329">
+      <c r="G83" s="336">
         <v>0.6</v>
       </c>
-      <c r="H83" s="285"/>
+      <c r="H83" s="291"/>
       <c r="I83" s="167"/>
     </row>
     <row r="84" spans="2:11" ht="15" customHeight="1">
-      <c r="B84" s="334" t="s">
+      <c r="B84" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="252"/>
-      <c r="D84" s="252"/>
+      <c r="C84" s="266"/>
+      <c r="D84" s="266"/>
       <c r="E84" s="170">
         <f>SUM(E81:E83)</f>
         <v>3533.2</v>
@@ -9387,11 +9387,11 @@
         <f>SUM(F81:F83)</f>
         <v>1</v>
       </c>
-      <c r="G84" s="325">
+      <c r="G84" s="359">
         <f>F81*G81+F83*G83+F82*G82</f>
         <v>0.78584438356164399</v>
       </c>
-      <c r="H84" s="252"/>
+      <c r="H84" s="266"/>
       <c r="I84" s="172"/>
     </row>
     <row r="85" spans="2:11" ht="15" customHeight="1">
@@ -9405,95 +9405,95 @@
       <c r="I85" s="173"/>
     </row>
     <row r="86" spans="2:11" ht="15" customHeight="1">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="357" t="s">
         <v>136</v>
       </c>
-      <c r="C86" s="285"/>
-      <c r="D86" s="285"/>
-      <c r="E86" s="285"/>
-      <c r="F86" s="285"/>
-      <c r="G86" s="285"/>
-      <c r="H86" s="285"/>
-      <c r="I86" s="285"/>
+      <c r="C86" s="291"/>
+      <c r="D86" s="291"/>
+      <c r="E86" s="291"/>
+      <c r="F86" s="291"/>
+      <c r="G86" s="291"/>
+      <c r="H86" s="291"/>
+      <c r="I86" s="291"/>
       <c r="K86" s="203"/>
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1">
-      <c r="B87" s="335" t="s">
+      <c r="B87" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C87" s="336"/>
-      <c r="D87" s="336"/>
-      <c r="E87" s="350" t="s">
+      <c r="C87" s="338"/>
+      <c r="D87" s="338"/>
+      <c r="E87" s="332" t="s">
         <v>118</v>
       </c>
-      <c r="F87" s="285"/>
+      <c r="F87" s="291"/>
       <c r="G87" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H87" s="374" t="str">
+      <c r="H87" s="379" t="str">
         <f>H45</f>
         <v>(63) 99252-2282</v>
       </c>
-      <c r="I87" s="264"/>
+      <c r="I87" s="260"/>
       <c r="K87" s="203" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1">
-      <c r="B88" s="333" t="s">
+      <c r="B88" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="285"/>
-      <c r="D88" s="285"/>
-      <c r="E88" s="350" t="s">
+      <c r="C88" s="291"/>
+      <c r="D88" s="291"/>
+      <c r="E88" s="332" t="s">
         <v>89</v>
       </c>
-      <c r="F88" s="285"/>
+      <c r="F88" s="291"/>
       <c r="G88" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H88" s="362" t="s">
+      <c r="H88" s="345" t="s">
         <v>49</v>
       </c>
-      <c r="I88" s="264"/>
+      <c r="I88" s="260"/>
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1">
-      <c r="B89" s="333" t="s">
+      <c r="B89" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="285"/>
-      <c r="D89" s="285"/>
-      <c r="E89" s="360">
+      <c r="C89" s="291"/>
+      <c r="D89" s="291"/>
+      <c r="E89" s="386">
         <f>733*4.84</f>
         <v>3547.72</v>
       </c>
-      <c r="F89" s="285"/>
+      <c r="F89" s="291"/>
       <c r="G89" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H89" s="330" t="s">
+      <c r="H89" s="366" t="s">
         <v>94</v>
       </c>
-      <c r="I89" s="264"/>
+      <c r="I89" s="260"/>
     </row>
     <row r="90" spans="2:11" ht="15" customHeight="1">
       <c r="B90" s="164"/>
-      <c r="C90" s="349" t="s">
+      <c r="C90" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D90" s="285"/>
-      <c r="E90" s="352">
+      <c r="D90" s="291"/>
+      <c r="E90" s="367">
         <v>43980000</v>
       </c>
-      <c r="F90" s="285"/>
+      <c r="F90" s="291"/>
       <c r="G90" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H90" s="342">
+      <c r="H90" s="339">
         <f>E90/E89</f>
         <v>12396.694214876034</v>
       </c>
-      <c r="I90" s="264"/>
+      <c r="I90" s="260"/>
       <c r="K90" s="221">
         <f>H90*4.84</f>
         <v>60000</v>
@@ -9501,75 +9501,75 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1">
       <c r="B91" s="165"/>
-      <c r="C91" s="349" t="s">
+      <c r="C91" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D91" s="285"/>
-      <c r="E91" s="380" t="s">
+      <c r="D91" s="291"/>
+      <c r="E91" s="342" t="s">
         <v>115</v>
       </c>
-      <c r="F91" s="285"/>
+      <c r="F91" s="291"/>
       <c r="G91" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H91" s="332">
+      <c r="H91" s="353">
         <f ca="1">TODAY()</f>
-        <v>45848</v>
-      </c>
-      <c r="I91" s="264"/>
+        <v>45855</v>
+      </c>
+      <c r="I91" s="260"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1">
       <c r="B92" s="165"/>
-      <c r="C92" s="349" t="s">
+      <c r="C92" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="285"/>
-      <c r="E92" s="327" t="s">
+      <c r="D92" s="291"/>
+      <c r="E92" s="335" t="s">
         <v>96</v>
       </c>
-      <c r="F92" s="285"/>
+      <c r="F92" s="291"/>
       <c r="G92" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H92" s="351"/>
-      <c r="I92" s="264"/>
+      <c r="H92" s="364"/>
+      <c r="I92" s="260"/>
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1">
-      <c r="B93" s="339" t="s">
+      <c r="B93" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C93" s="285"/>
-      <c r="D93" s="285"/>
-      <c r="E93" s="285"/>
-      <c r="F93" s="285"/>
-      <c r="G93" s="285"/>
-      <c r="H93" s="285"/>
-      <c r="I93" s="264"/>
+      <c r="C93" s="291"/>
+      <c r="D93" s="291"/>
+      <c r="E93" s="291"/>
+      <c r="F93" s="291"/>
+      <c r="G93" s="291"/>
+      <c r="H93" s="291"/>
+      <c r="I93" s="260"/>
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1">
-      <c r="B94" s="348" t="s">
+      <c r="B94" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C94" s="285"/>
-      <c r="D94" s="285"/>
+      <c r="C94" s="291"/>
+      <c r="D94" s="291"/>
       <c r="E94" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F94" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G94" s="340" t="s">
+      <c r="G94" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H94" s="285"/>
+      <c r="H94" s="291"/>
       <c r="I94" s="167"/>
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1">
-      <c r="B95" s="337" t="s">
+      <c r="B95" s="344" t="s">
         <v>105</v>
       </c>
-      <c r="C95" s="285"/>
-      <c r="D95" s="285"/>
+      <c r="C95" s="291"/>
+      <c r="D95" s="291"/>
       <c r="E95" s="234">
         <v>1100</v>
       </c>
@@ -9577,10 +9577,10 @@
         <f>E95/E89</f>
         <v>0.31005829095870024</v>
       </c>
-      <c r="G95" s="384">
+      <c r="G95" s="354">
         <v>1</v>
       </c>
-      <c r="H95" s="285"/>
+      <c r="H95" s="291"/>
       <c r="I95" s="206"/>
     </row>
     <row r="96" spans="2:11" ht="15" customHeight="1">
@@ -9597,18 +9597,18 @@
         <f>E96/E89</f>
         <v>0.33854170904129977</v>
       </c>
-      <c r="G96" s="384">
+      <c r="G96" s="354">
         <v>0.8</v>
       </c>
-      <c r="H96" s="285"/>
+      <c r="H96" s="291"/>
       <c r="I96" s="206"/>
     </row>
     <row r="97" spans="2:12" ht="15" customHeight="1">
-      <c r="B97" s="381" t="s">
+      <c r="B97" s="355" t="s">
         <v>106</v>
       </c>
-      <c r="C97" s="285"/>
-      <c r="D97" s="285"/>
+      <c r="C97" s="291"/>
+      <c r="D97" s="291"/>
       <c r="E97" s="168">
         <f>E89*0.3514</f>
         <v>1246.6688079999999</v>
@@ -9617,20 +9617,20 @@
         <f>E97/E89</f>
         <v>0.35139999999999999</v>
       </c>
-      <c r="G97" s="329">
+      <c r="G97" s="336">
         <v>0.6</v>
       </c>
-      <c r="H97" s="285"/>
+      <c r="H97" s="291"/>
       <c r="I97" s="167"/>
       <c r="K97" s="207"/>
       <c r="L97" s="207"/>
     </row>
     <row r="98" spans="2:12" ht="15" customHeight="1">
-      <c r="B98" s="334" t="s">
+      <c r="B98" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C98" s="252"/>
-      <c r="D98" s="252"/>
+      <c r="C98" s="266"/>
+      <c r="D98" s="266"/>
       <c r="E98" s="170">
         <f>SUM(E95:E97)</f>
         <v>3547.72</v>
@@ -9639,11 +9639,11 @@
         <f>SUM(F95:F97)</f>
         <v>1</v>
       </c>
-      <c r="G98" s="325">
+      <c r="G98" s="359">
         <f>F97*G97+F95*G95+F96*G96</f>
         <v>0.79173165819173996</v>
       </c>
-      <c r="H98" s="252"/>
+      <c r="H98" s="266"/>
       <c r="I98" s="172"/>
       <c r="K98" s="207"/>
       <c r="L98" s="207"/>
@@ -9664,177 +9664,177 @@
       <c r="L99" s="207"/>
     </row>
     <row r="100" spans="2:12" ht="15" customHeight="1">
-      <c r="B100" s="345"/>
-      <c r="C100" s="285"/>
-      <c r="D100" s="285"/>
-      <c r="E100" s="285"/>
-      <c r="F100" s="285"/>
-      <c r="G100" s="285"/>
-      <c r="H100" s="285"/>
-      <c r="I100" s="285"/>
+      <c r="B100" s="395"/>
+      <c r="C100" s="291"/>
+      <c r="D100" s="291"/>
+      <c r="E100" s="291"/>
+      <c r="F100" s="291"/>
+      <c r="G100" s="291"/>
+      <c r="H100" s="291"/>
+      <c r="I100" s="291"/>
       <c r="K100" s="207"/>
       <c r="L100" s="207"/>
     </row>
     <row r="101" spans="2:12" ht="15" customHeight="1">
-      <c r="B101" s="343" t="s">
+      <c r="B101" s="357" t="s">
         <v>138</v>
       </c>
-      <c r="C101" s="285"/>
-      <c r="D101" s="285"/>
-      <c r="E101" s="285"/>
-      <c r="F101" s="285"/>
-      <c r="G101" s="285"/>
-      <c r="H101" s="285"/>
-      <c r="I101" s="285"/>
+      <c r="C101" s="291"/>
+      <c r="D101" s="291"/>
+      <c r="E101" s="291"/>
+      <c r="F101" s="291"/>
+      <c r="G101" s="291"/>
+      <c r="H101" s="291"/>
+      <c r="I101" s="291"/>
       <c r="K101" s="207"/>
       <c r="L101" s="207"/>
     </row>
     <row r="102" spans="2:12" ht="15" customHeight="1">
-      <c r="B102" s="335" t="s">
+      <c r="B102" s="337" t="s">
         <v>108</v>
       </c>
-      <c r="C102" s="336"/>
-      <c r="D102" s="336"/>
-      <c r="E102" s="390"/>
-      <c r="F102" s="285"/>
+      <c r="C102" s="338"/>
+      <c r="D102" s="338"/>
+      <c r="E102" s="348"/>
+      <c r="F102" s="291"/>
       <c r="G102" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="H102" s="328"/>
-      <c r="I102" s="264"/>
+      <c r="H102" s="396"/>
+      <c r="I102" s="260"/>
       <c r="K102" s="207"/>
       <c r="L102" s="207"/>
     </row>
     <row r="103" spans="2:12" ht="15" customHeight="1">
-      <c r="B103" s="333" t="s">
+      <c r="B103" s="340" t="s">
         <v>88</v>
       </c>
-      <c r="C103" s="285"/>
-      <c r="D103" s="285"/>
-      <c r="E103" s="385"/>
-      <c r="F103" s="285"/>
+      <c r="C103" s="291"/>
+      <c r="D103" s="291"/>
+      <c r="E103" s="358"/>
+      <c r="F103" s="291"/>
       <c r="G103" s="163" t="s">
         <v>90</v>
       </c>
-      <c r="H103" s="379"/>
-      <c r="I103" s="264"/>
+      <c r="H103" s="365"/>
+      <c r="I103" s="260"/>
     </row>
     <row r="104" spans="2:12" ht="15" customHeight="1">
-      <c r="B104" s="333" t="s">
+      <c r="B104" s="340" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="285"/>
-      <c r="D104" s="285"/>
-      <c r="E104" s="341"/>
-      <c r="F104" s="285"/>
+      <c r="C104" s="291"/>
+      <c r="D104" s="291"/>
+      <c r="E104" s="378"/>
+      <c r="F104" s="291"/>
       <c r="G104" s="163" t="s">
         <v>93</v>
       </c>
-      <c r="H104" s="354"/>
-      <c r="I104" s="264"/>
+      <c r="H104" s="389"/>
+      <c r="I104" s="260"/>
     </row>
     <row r="105" spans="2:12" ht="15" customHeight="1">
       <c r="B105" s="164"/>
-      <c r="C105" s="349" t="s">
+      <c r="C105" s="334" t="s">
         <v>112</v>
       </c>
-      <c r="D105" s="285"/>
-      <c r="E105" s="352"/>
-      <c r="F105" s="285"/>
+      <c r="D105" s="291"/>
+      <c r="E105" s="367"/>
+      <c r="F105" s="291"/>
       <c r="G105" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="H105" s="342"/>
-      <c r="I105" s="264"/>
+      <c r="H105" s="339"/>
+      <c r="I105" s="260"/>
     </row>
     <row r="106" spans="2:12" ht="15" customHeight="1">
       <c r="B106" s="165"/>
-      <c r="C106" s="349" t="s">
+      <c r="C106" s="334" t="s">
         <v>114</v>
       </c>
-      <c r="D106" s="285"/>
-      <c r="E106" s="380"/>
-      <c r="F106" s="285"/>
+      <c r="D106" s="291"/>
+      <c r="E106" s="342"/>
+      <c r="F106" s="291"/>
       <c r="G106" s="163" t="s">
         <v>97</v>
       </c>
-      <c r="H106" s="383"/>
-      <c r="I106" s="264"/>
+      <c r="H106" s="352"/>
+      <c r="I106" s="260"/>
     </row>
     <row r="107" spans="2:12" ht="15" customHeight="1">
       <c r="B107" s="165"/>
-      <c r="C107" s="349" t="s">
+      <c r="C107" s="334" t="s">
         <v>95</v>
       </c>
-      <c r="D107" s="285"/>
-      <c r="E107" s="353"/>
-      <c r="F107" s="285"/>
+      <c r="D107" s="291"/>
+      <c r="E107" s="388"/>
+      <c r="F107" s="291"/>
       <c r="G107" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="H107" s="351"/>
-      <c r="I107" s="264"/>
+      <c r="H107" s="364"/>
+      <c r="I107" s="260"/>
     </row>
     <row r="108" spans="2:12" ht="15" customHeight="1">
-      <c r="B108" s="339" t="s">
+      <c r="B108" s="351" t="s">
         <v>100</v>
       </c>
-      <c r="C108" s="285"/>
-      <c r="D108" s="285"/>
-      <c r="E108" s="285"/>
-      <c r="F108" s="285"/>
-      <c r="G108" s="285"/>
-      <c r="H108" s="285"/>
-      <c r="I108" s="264"/>
+      <c r="C108" s="291"/>
+      <c r="D108" s="291"/>
+      <c r="E108" s="291"/>
+      <c r="F108" s="291"/>
+      <c r="G108" s="291"/>
+      <c r="H108" s="291"/>
+      <c r="I108" s="260"/>
     </row>
     <row r="109" spans="2:12" ht="15" customHeight="1">
-      <c r="B109" s="348" t="s">
+      <c r="B109" s="333" t="s">
         <v>101</v>
       </c>
-      <c r="C109" s="285"/>
-      <c r="D109" s="285"/>
+      <c r="C109" s="291"/>
+      <c r="D109" s="291"/>
       <c r="E109" s="166" t="s">
         <v>102</v>
       </c>
       <c r="F109" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="G109" s="340" t="s">
+      <c r="G109" s="346" t="s">
         <v>104</v>
       </c>
-      <c r="H109" s="285"/>
+      <c r="H109" s="291"/>
       <c r="I109" s="167"/>
     </row>
     <row r="110" spans="2:12" ht="15" customHeight="1">
-      <c r="B110" s="381" t="s">
+      <c r="B110" s="355" t="s">
         <v>105</v>
       </c>
-      <c r="C110" s="285"/>
-      <c r="D110" s="285"/>
+      <c r="C110" s="291"/>
+      <c r="D110" s="291"/>
       <c r="E110" s="168"/>
       <c r="F110" s="169"/>
-      <c r="G110" s="329"/>
-      <c r="H110" s="285"/>
+      <c r="G110" s="336"/>
+      <c r="H110" s="291"/>
       <c r="I110" s="167"/>
     </row>
     <row r="111" spans="2:12" ht="15" customHeight="1">
-      <c r="B111" s="381" t="s">
+      <c r="B111" s="355" t="s">
         <v>106</v>
       </c>
-      <c r="C111" s="285"/>
-      <c r="D111" s="285"/>
+      <c r="C111" s="291"/>
+      <c r="D111" s="291"/>
       <c r="E111" s="168"/>
       <c r="F111" s="169"/>
-      <c r="G111" s="329"/>
-      <c r="H111" s="285"/>
+      <c r="G111" s="336"/>
+      <c r="H111" s="291"/>
       <c r="I111" s="167"/>
     </row>
     <row r="112" spans="2:12" ht="15" customHeight="1">
-      <c r="B112" s="334" t="s">
+      <c r="B112" s="363" t="s">
         <v>82</v>
       </c>
-      <c r="C112" s="252"/>
-      <c r="D112" s="252"/>
+      <c r="C112" s="266"/>
+      <c r="D112" s="266"/>
       <c r="E112" s="170">
         <f>SUM(E110:E111)</f>
         <v>0</v>
@@ -9843,15 +9843,220 @@
         <f>SUM(F110:F111)</f>
         <v>0</v>
       </c>
-      <c r="G112" s="325">
+      <c r="G112" s="359">
         <f>F110*G110+F111*G111</f>
         <v>0</v>
       </c>
-      <c r="H112" s="252"/>
+      <c r="H112" s="266"/>
       <c r="I112" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B79:I79"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C107:D107"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="E88:F88"/>
     <mergeCell ref="B38:D38"/>
@@ -9876,211 +10081,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B86:I86"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B79:I79"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="B102:D102"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="B93:I93"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="H91:I91"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B108:I108"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="G94:H94"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="G84:H84"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10432,16 +10432,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1">
-      <c r="E1" s="393"/>
-      <c r="F1" s="394"/>
-      <c r="G1" s="394"/>
-      <c r="H1" s="394"/>
-      <c r="I1" s="394"/>
-      <c r="J1" s="394"/>
-      <c r="K1" s="394"/>
-      <c r="L1" s="394"/>
-      <c r="M1" s="394"/>
-      <c r="N1" s="394"/>
+      <c r="E1" s="405"/>
+      <c r="F1" s="400"/>
+      <c r="G1" s="400"/>
+      <c r="H1" s="400"/>
+      <c r="I1" s="400"/>
+      <c r="J1" s="400"/>
+      <c r="K1" s="400"/>
+      <c r="L1" s="400"/>
+      <c r="M1" s="400"/>
+      <c r="N1" s="400"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" thickBot="1"/>
     <row r="3" spans="1:18" ht="45" customHeight="1">
@@ -10989,21 +10989,21 @@
       <c r="R11" s="146"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A12" s="392" t="s">
+      <c r="A12" s="398" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="250"/>
-      <c r="C12" s="395" t="s">
+      <c r="B12" s="258"/>
+      <c r="C12" s="406" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="394"/>
-      <c r="E12" s="394"/>
-      <c r="F12" s="394"/>
-      <c r="G12" s="394"/>
-      <c r="H12" s="394"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="394"/>
-      <c r="K12" s="394"/>
+      <c r="D12" s="400"/>
+      <c r="E12" s="400"/>
+      <c r="F12" s="400"/>
+      <c r="G12" s="400"/>
+      <c r="H12" s="400"/>
+      <c r="I12" s="400"/>
+      <c r="J12" s="400"/>
+      <c r="K12" s="400"/>
       <c r="L12" s="145"/>
       <c r="M12" s="144"/>
       <c r="N12" s="144"/>
@@ -11018,21 +11018,21 @@
       <c r="R12" s="146"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A13" s="392" t="s">
+      <c r="A13" s="398" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="250"/>
-      <c r="C13" s="395" t="s">
+      <c r="B13" s="258"/>
+      <c r="C13" s="406" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="394"/>
-      <c r="E13" s="394"/>
-      <c r="F13" s="394"/>
-      <c r="G13" s="394"/>
-      <c r="H13" s="394"/>
-      <c r="I13" s="394"/>
-      <c r="J13" s="394"/>
-      <c r="K13" s="394"/>
+      <c r="D13" s="400"/>
+      <c r="E13" s="400"/>
+      <c r="F13" s="400"/>
+      <c r="G13" s="400"/>
+      <c r="H13" s="400"/>
+      <c r="I13" s="400"/>
+      <c r="J13" s="400"/>
+      <c r="K13" s="400"/>
       <c r="L13" s="144"/>
       <c r="M13" s="144"/>
       <c r="N13" s="144"/>
@@ -11047,22 +11047,22 @@
       <c r="R13" s="146"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A14" s="392" t="str">
+      <c r="A14" s="398" t="str">
         <f>L3</f>
         <v>Benfeitorias Indexado³</v>
       </c>
-      <c r="B14" s="250"/>
-      <c r="C14" s="395" t="s">
+      <c r="B14" s="258"/>
+      <c r="C14" s="406" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="394"/>
-      <c r="E14" s="394"/>
-      <c r="F14" s="394"/>
-      <c r="G14" s="394"/>
-      <c r="H14" s="394"/>
-      <c r="I14" s="394"/>
-      <c r="J14" s="394"/>
-      <c r="K14" s="394"/>
+      <c r="D14" s="400"/>
+      <c r="E14" s="400"/>
+      <c r="F14" s="400"/>
+      <c r="G14" s="400"/>
+      <c r="H14" s="400"/>
+      <c r="I14" s="400"/>
+      <c r="J14" s="400"/>
+      <c r="K14" s="400"/>
       <c r="L14" s="144"/>
       <c r="M14" s="144"/>
       <c r="N14" s="144"/>
@@ -11077,21 +11077,21 @@
       <c r="R14" s="146"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A15" s="392" t="s">
+      <c r="A15" s="398" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="250"/>
-      <c r="C15" s="395" t="s">
+      <c r="B15" s="258"/>
+      <c r="C15" s="406" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="394"/>
-      <c r="E15" s="394"/>
-      <c r="F15" s="394"/>
-      <c r="G15" s="394"/>
-      <c r="H15" s="394"/>
-      <c r="I15" s="394"/>
-      <c r="J15" s="394"/>
-      <c r="K15" s="394"/>
+      <c r="D15" s="400"/>
+      <c r="E15" s="400"/>
+      <c r="F15" s="400"/>
+      <c r="G15" s="400"/>
+      <c r="H15" s="400"/>
+      <c r="I15" s="400"/>
+      <c r="J15" s="400"/>
+      <c r="K15" s="400"/>
       <c r="L15" s="144"/>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
@@ -11106,21 +11106,21 @@
       <c r="R15" s="146"/>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A16" s="392" t="s">
+      <c r="A16" s="398" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="250"/>
-      <c r="C16" s="397" t="s">
+      <c r="B16" s="258"/>
+      <c r="C16" s="399" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="394"/>
-      <c r="E16" s="394"/>
-      <c r="F16" s="394"/>
-      <c r="G16" s="394"/>
-      <c r="H16" s="394"/>
-      <c r="I16" s="394"/>
-      <c r="J16" s="394"/>
-      <c r="K16" s="394"/>
+      <c r="D16" s="400"/>
+      <c r="E16" s="400"/>
+      <c r="F16" s="400"/>
+      <c r="G16" s="400"/>
+      <c r="H16" s="400"/>
+      <c r="I16" s="400"/>
+      <c r="J16" s="400"/>
+      <c r="K16" s="400"/>
       <c r="L16" s="144"/>
       <c r="M16" s="144"/>
       <c r="N16" s="144"/>
@@ -11130,21 +11130,21 @@
       <c r="R16" s="146"/>
     </row>
     <row r="17" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A17" s="392" t="s">
+      <c r="A17" s="398" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="250"/>
-      <c r="C17" s="397" t="s">
+      <c r="B17" s="258"/>
+      <c r="C17" s="399" t="s">
         <v>183</v>
       </c>
-      <c r="D17" s="394"/>
-      <c r="E17" s="394"/>
-      <c r="F17" s="394"/>
-      <c r="G17" s="394"/>
-      <c r="H17" s="394"/>
-      <c r="I17" s="394"/>
-      <c r="J17" s="394"/>
-      <c r="K17" s="394"/>
+      <c r="D17" s="400"/>
+      <c r="E17" s="400"/>
+      <c r="F17" s="400"/>
+      <c r="G17" s="400"/>
+      <c r="H17" s="400"/>
+      <c r="I17" s="400"/>
+      <c r="J17" s="400"/>
+      <c r="K17" s="400"/>
       <c r="L17" s="144"/>
       <c r="M17" s="147" t="s">
         <v>184</v>
@@ -11163,21 +11163,21 @@
       <c r="R17" s="146"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A18" s="392" t="s">
+      <c r="A18" s="398" t="s">
         <v>179</v>
       </c>
-      <c r="B18" s="250"/>
-      <c r="C18" s="397" t="s">
+      <c r="B18" s="258"/>
+      <c r="C18" s="399" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="394"/>
-      <c r="E18" s="394"/>
-      <c r="F18" s="394"/>
-      <c r="G18" s="394"/>
-      <c r="H18" s="394"/>
-      <c r="I18" s="394"/>
-      <c r="J18" s="394"/>
-      <c r="K18" s="394"/>
+      <c r="D18" s="400"/>
+      <c r="E18" s="400"/>
+      <c r="F18" s="400"/>
+      <c r="G18" s="400"/>
+      <c r="H18" s="400"/>
+      <c r="I18" s="400"/>
+      <c r="J18" s="400"/>
+      <c r="K18" s="400"/>
       <c r="L18" s="144"/>
       <c r="M18" s="147" t="s">
         <v>187</v>
@@ -11191,21 +11191,21 @@
       <c r="R18" s="146"/>
     </row>
     <row r="19" spans="1:18" ht="28.5" customHeight="1">
-      <c r="A19" s="392" t="s">
+      <c r="A19" s="398" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="250"/>
-      <c r="C19" s="397" t="s">
+      <c r="B19" s="258"/>
+      <c r="C19" s="399" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="394"/>
-      <c r="E19" s="394"/>
-      <c r="F19" s="394"/>
-      <c r="G19" s="394"/>
-      <c r="H19" s="394"/>
-      <c r="I19" s="394"/>
-      <c r="J19" s="394"/>
-      <c r="K19" s="394"/>
+      <c r="D19" s="400"/>
+      <c r="E19" s="400"/>
+      <c r="F19" s="400"/>
+      <c r="G19" s="400"/>
+      <c r="H19" s="400"/>
+      <c r="I19" s="400"/>
+      <c r="J19" s="400"/>
+      <c r="K19" s="400"/>
       <c r="L19" s="144"/>
       <c r="M19" s="144"/>
       <c r="N19" s="144"/>
@@ -11220,21 +11220,21 @@
       <c r="R19" s="146"/>
     </row>
     <row r="20" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A20" s="392" t="s">
+      <c r="A20" s="398" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="250"/>
-      <c r="C20" s="397" t="s">
+      <c r="B20" s="258"/>
+      <c r="C20" s="399" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="394"/>
-      <c r="E20" s="394"/>
-      <c r="F20" s="394"/>
-      <c r="G20" s="394"/>
-      <c r="H20" s="394"/>
-      <c r="I20" s="394"/>
-      <c r="J20" s="394"/>
-      <c r="K20" s="394"/>
+      <c r="D20" s="400"/>
+      <c r="E20" s="400"/>
+      <c r="F20" s="400"/>
+      <c r="G20" s="400"/>
+      <c r="H20" s="400"/>
+      <c r="I20" s="400"/>
+      <c r="J20" s="400"/>
+      <c r="K20" s="400"/>
       <c r="L20" s="144"/>
       <c r="M20" s="144"/>
       <c r="N20" s="144"/>
@@ -11249,21 +11249,21 @@
       <c r="R20" s="146"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A21" s="392" t="s">
+      <c r="A21" s="398" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="250"/>
-      <c r="C21" s="397" t="s">
+      <c r="B21" s="258"/>
+      <c r="C21" s="399" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="394"/>
-      <c r="E21" s="394"/>
-      <c r="F21" s="394"/>
-      <c r="G21" s="394"/>
-      <c r="H21" s="394"/>
-      <c r="I21" s="394"/>
-      <c r="J21" s="394"/>
-      <c r="K21" s="394"/>
+      <c r="D21" s="400"/>
+      <c r="E21" s="400"/>
+      <c r="F21" s="400"/>
+      <c r="G21" s="400"/>
+      <c r="H21" s="400"/>
+      <c r="I21" s="400"/>
+      <c r="J21" s="400"/>
+      <c r="K21" s="400"/>
       <c r="L21" s="144"/>
       <c r="M21" s="144"/>
       <c r="N21" s="144"/>
@@ -11278,25 +11278,25 @@
       <c r="R21" s="146"/>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A22" s="392" t="s">
+      <c r="A22" s="398" t="s">
         <v>191</v>
       </c>
-      <c r="B22" s="250"/>
-      <c r="C22" s="396" t="s">
+      <c r="B22" s="258"/>
+      <c r="C22" s="407" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="394"/>
-      <c r="E22" s="394"/>
-      <c r="F22" s="394"/>
-      <c r="G22" s="394"/>
-      <c r="H22" s="394"/>
-      <c r="I22" s="394"/>
-      <c r="J22" s="394"/>
-      <c r="K22" s="394"/>
-      <c r="L22" s="394"/>
-      <c r="M22" s="394"/>
-      <c r="N22" s="394"/>
-      <c r="O22" s="264"/>
+      <c r="D22" s="400"/>
+      <c r="E22" s="400"/>
+      <c r="F22" s="400"/>
+      <c r="G22" s="400"/>
+      <c r="H22" s="400"/>
+      <c r="I22" s="400"/>
+      <c r="J22" s="400"/>
+      <c r="K22" s="400"/>
+      <c r="L22" s="400"/>
+      <c r="M22" s="400"/>
+      <c r="N22" s="400"/>
+      <c r="O22" s="260"/>
       <c r="P22" s="147" t="s">
         <v>195</v>
       </c>
@@ -11307,22 +11307,22 @@
       <c r="R22" s="146"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A23" s="392" t="s">
+      <c r="A23" s="398" t="s">
         <v>193</v>
       </c>
-      <c r="B23" s="250"/>
-      <c r="C23" s="397" t="s">
+      <c r="B23" s="258"/>
+      <c r="C23" s="399" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="394"/>
-      <c r="E23" s="394"/>
-      <c r="F23" s="394"/>
-      <c r="G23" s="394"/>
-      <c r="H23" s="394"/>
-      <c r="I23" s="394"/>
-      <c r="J23" s="394"/>
-      <c r="K23" s="394"/>
-      <c r="L23" s="394"/>
+      <c r="D23" s="400"/>
+      <c r="E23" s="400"/>
+      <c r="F23" s="400"/>
+      <c r="G23" s="400"/>
+      <c r="H23" s="400"/>
+      <c r="I23" s="400"/>
+      <c r="J23" s="400"/>
+      <c r="K23" s="400"/>
+      <c r="L23" s="400"/>
       <c r="M23" s="144"/>
       <c r="N23" s="144"/>
       <c r="O23" s="144"/>
@@ -11336,22 +11336,22 @@
       <c r="R23" s="146"/>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1">
-      <c r="A24" s="392" t="s">
+      <c r="A24" s="398" t="s">
         <v>195</v>
       </c>
-      <c r="B24" s="250"/>
-      <c r="C24" s="397" t="s">
+      <c r="B24" s="258"/>
+      <c r="C24" s="399" t="s">
         <v>198</v>
       </c>
-      <c r="D24" s="394"/>
-      <c r="E24" s="394"/>
-      <c r="F24" s="394"/>
-      <c r="G24" s="394"/>
-      <c r="H24" s="394"/>
-      <c r="I24" s="394"/>
-      <c r="J24" s="394"/>
-      <c r="K24" s="394"/>
-      <c r="L24" s="394"/>
+      <c r="D24" s="400"/>
+      <c r="E24" s="400"/>
+      <c r="F24" s="400"/>
+      <c r="G24" s="400"/>
+      <c r="H24" s="400"/>
+      <c r="I24" s="400"/>
+      <c r="J24" s="400"/>
+      <c r="K24" s="400"/>
+      <c r="L24" s="400"/>
       <c r="M24" s="144"/>
       <c r="N24" s="144"/>
       <c r="O24" s="144"/>
@@ -11365,21 +11365,21 @@
       <c r="R24" s="146"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1">
-      <c r="A25" s="392" t="s">
+      <c r="A25" s="398" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="250"/>
-      <c r="C25" s="397" t="s">
+      <c r="B25" s="258"/>
+      <c r="C25" s="399" t="s">
         <v>200</v>
       </c>
-      <c r="D25" s="394"/>
-      <c r="E25" s="394"/>
-      <c r="F25" s="394"/>
-      <c r="G25" s="394"/>
-      <c r="H25" s="394"/>
-      <c r="I25" s="394"/>
-      <c r="J25" s="394"/>
-      <c r="K25" s="394"/>
+      <c r="D25" s="400"/>
+      <c r="E25" s="400"/>
+      <c r="F25" s="400"/>
+      <c r="G25" s="400"/>
+      <c r="H25" s="400"/>
+      <c r="I25" s="400"/>
+      <c r="J25" s="400"/>
+      <c r="K25" s="400"/>
       <c r="L25" s="144"/>
       <c r="M25" s="144"/>
       <c r="N25" s="144"/>
@@ -11389,21 +11389,21 @@
       <c r="R25" s="146"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" thickBot="1">
-      <c r="A26" s="398" t="s">
+      <c r="A26" s="401" t="s">
         <v>201</v>
       </c>
-      <c r="B26" s="399"/>
-      <c r="C26" s="400" t="s">
+      <c r="B26" s="402"/>
+      <c r="C26" s="403" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="401"/>
-      <c r="E26" s="401"/>
-      <c r="F26" s="401"/>
-      <c r="G26" s="401"/>
-      <c r="H26" s="401"/>
-      <c r="I26" s="401"/>
-      <c r="J26" s="401"/>
-      <c r="K26" s="401"/>
+      <c r="D26" s="404"/>
+      <c r="E26" s="404"/>
+      <c r="F26" s="404"/>
+      <c r="G26" s="404"/>
+      <c r="H26" s="404"/>
+      <c r="I26" s="404"/>
+      <c r="J26" s="404"/>
+      <c r="K26" s="404"/>
       <c r="L26" s="150"/>
       <c r="M26" s="150"/>
       <c r="N26" s="150"/>
@@ -11424,6 +11424,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C22:O22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C14:K14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C16:K16"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C23:L23"/>
@@ -11440,21 +11455,6 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C17:K17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E1:N1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="C22:O22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C14:K14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C10">
     <cfRule type="cellIs" dxfId="8" priority="25" stopIfTrue="1" operator="equal">
@@ -11514,460 +11514,465 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12">
-      <c r="C4" s="402" t="str">
+      <c r="C4" s="434" t="str">
         <f>'AREA UTIL'!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D4" s="254"/>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="254"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="255"/>
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
     </row>
     <row r="5" spans="3:12">
-      <c r="C5" s="402" t="s">
+      <c r="C5" s="434" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="254"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="254"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
     </row>
     <row r="6" spans="3:12">
-      <c r="C6" s="407" t="s">
+      <c r="C6" s="419" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="254"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="404">
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="420">
         <f>'PLANILHA HOMOG'!Q19</f>
         <v>937.24</v>
       </c>
-      <c r="G6" s="254"/>
-      <c r="H6" s="264"/>
+      <c r="G6" s="255"/>
+      <c r="H6" s="260"/>
     </row>
     <row r="7" spans="3:12">
-      <c r="C7" s="407" t="s">
+      <c r="C7" s="419" t="s">
         <v>204</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="404">
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="420">
         <f>'PLANILHA HOMOG'!Q14</f>
         <v>14159.41</v>
       </c>
-      <c r="G7" s="254"/>
-      <c r="H7" s="264"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="260"/>
     </row>
     <row r="8" spans="3:12">
-      <c r="C8" s="407" t="s">
+      <c r="C8" s="419" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="254"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="404">
+      <c r="D8" s="255"/>
+      <c r="E8" s="255"/>
+      <c r="F8" s="420">
         <f>'PLANILHA HOMOG'!Q15</f>
         <v>11248.99</v>
       </c>
-      <c r="G8" s="254"/>
-      <c r="H8" s="264"/>
+      <c r="G8" s="255"/>
+      <c r="H8" s="260"/>
     </row>
     <row r="9" spans="3:12">
-      <c r="C9" s="407" t="s">
+      <c r="C9" s="419" t="s">
         <v>206</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="E9" s="254"/>
-      <c r="F9" s="403">
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="422">
         <v>6</v>
       </c>
-      <c r="G9" s="254"/>
-      <c r="H9" s="264"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="260"/>
       <c r="J9" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="10" spans="3:12">
-      <c r="C10" s="407" t="s">
+      <c r="C10" s="419" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="403">
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="422">
         <v>1</v>
       </c>
-      <c r="G10" s="254"/>
-      <c r="H10" s="264"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="260"/>
       <c r="J10" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="11" spans="3:12">
-      <c r="C11" s="407" t="s">
+      <c r="C11" s="419" t="s">
         <v>199</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="418">
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="431">
         <f>'PLANILHA HOMOG'!Q24</f>
         <v>1.9255773964901695</v>
       </c>
-      <c r="G11" s="254"/>
-      <c r="H11" s="264"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="260"/>
     </row>
     <row r="12" spans="3:12">
-      <c r="C12" s="407" t="s">
+      <c r="C12" s="419" t="s">
         <v>209</v>
       </c>
-      <c r="D12" s="254"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="403">
+      <c r="D12" s="255"/>
+      <c r="E12" s="255"/>
+      <c r="F12" s="422">
         <f>'PLANILHA HOMOG'!N18</f>
         <v>0.27100000000000002</v>
       </c>
-      <c r="G12" s="254"/>
-      <c r="H12" s="264"/>
+      <c r="G12" s="255"/>
+      <c r="H12" s="260"/>
     </row>
     <row r="13" spans="3:12">
-      <c r="C13" s="407" t="s">
+      <c r="C13" s="419" t="s">
         <v>197</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="404">
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="420">
         <f>'PLANILHA HOMOG'!Q23</f>
         <v>253.98</v>
       </c>
-      <c r="G13" s="254"/>
-      <c r="H13" s="264"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="260"/>
     </row>
     <row r="14" spans="3:12" ht="15" customHeight="1">
-      <c r="C14" s="415" t="s">
+      <c r="C14" s="429" t="s">
         <v>210</v>
       </c>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="411">
+      <c r="D14" s="257"/>
+      <c r="E14" s="257"/>
+      <c r="F14" s="428">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G14" s="249"/>
-      <c r="H14" s="250"/>
-      <c r="J14" s="409">
+      <c r="G14" s="257"/>
+      <c r="H14" s="258"/>
+      <c r="J14" s="432">
         <f>F14*4.84</f>
         <v>63838.680399999997</v>
       </c>
-      <c r="K14" s="254"/>
-      <c r="L14" s="254"/>
+      <c r="K14" s="255"/>
+      <c r="L14" s="255"/>
     </row>
     <row r="15" spans="3:12">
-      <c r="C15" s="413"/>
-      <c r="D15" s="254"/>
-      <c r="E15" s="254"/>
-      <c r="F15" s="254"/>
-      <c r="G15" s="254"/>
-      <c r="H15" s="254"/>
+      <c r="C15" s="436"/>
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="255"/>
+      <c r="G15" s="255"/>
+      <c r="H15" s="255"/>
     </row>
     <row r="16" spans="3:12">
-      <c r="C16" s="417" t="s">
+      <c r="C16" s="418" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="254"/>
-      <c r="G16" s="254"/>
-      <c r="H16" s="254"/>
+      <c r="D16" s="255"/>
+      <c r="E16" s="255"/>
+      <c r="F16" s="255"/>
+      <c r="G16" s="255"/>
+      <c r="H16" s="255"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="407" t="s">
+      <c r="C17" s="419" t="s">
         <v>212</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="403">
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="422">
         <f>AMOSTRAS!E14</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="G17" s="254"/>
-      <c r="H17" s="264"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="260"/>
     </row>
     <row r="18" spans="3:8">
-      <c r="C18" s="407" t="s">
+      <c r="C18" s="419" t="s">
         <v>213</v>
       </c>
-      <c r="D18" s="254"/>
-      <c r="E18" s="254"/>
-      <c r="F18" s="404">
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
+      <c r="F18" s="420">
         <f>'PLANILHA HOMOG'!Q17</f>
         <v>13189.81</v>
       </c>
-      <c r="G18" s="254"/>
-      <c r="H18" s="264"/>
+      <c r="G18" s="255"/>
+      <c r="H18" s="260"/>
     </row>
     <row r="19" spans="3:8">
-      <c r="C19" s="407" t="s">
+      <c r="C19" s="419" t="s">
         <v>214</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="404">
+      <c r="D19" s="255"/>
+      <c r="E19" s="255"/>
+      <c r="F19" s="420">
         <f>F17*F18</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G19" s="254"/>
-      <c r="H19" s="264"/>
+      <c r="G19" s="255"/>
+      <c r="H19" s="260"/>
     </row>
     <row r="20" spans="3:8" ht="15" customHeight="1">
-      <c r="C20" s="415" t="s">
+      <c r="C20" s="429" t="s">
         <v>215</v>
       </c>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="411">
+      <c r="D20" s="257"/>
+      <c r="E20" s="257"/>
+      <c r="F20" s="428">
         <f>F19</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G20" s="249"/>
-      <c r="H20" s="250"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="258"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="C21" s="408"/>
-      <c r="D21" s="254"/>
-      <c r="E21" s="254"/>
-      <c r="F21" s="405"/>
-      <c r="G21" s="254"/>
-      <c r="H21" s="254"/>
+      <c r="C21" s="423"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="255"/>
+      <c r="F21" s="426"/>
+      <c r="G21" s="255"/>
+      <c r="H21" s="255"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="C22" s="408"/>
-      <c r="D22" s="254"/>
-      <c r="E22" s="254"/>
-      <c r="F22" s="405"/>
-      <c r="G22" s="254"/>
-      <c r="H22" s="254"/>
+      <c r="C22" s="423"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
+      <c r="F22" s="426"/>
+      <c r="G22" s="255"/>
+      <c r="H22" s="255"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="C23" s="408"/>
-      <c r="D23" s="254"/>
-      <c r="E23" s="254"/>
-      <c r="F23" s="412"/>
-      <c r="G23" s="254"/>
-      <c r="H23" s="254"/>
+      <c r="C23" s="423"/>
+      <c r="D23" s="255"/>
+      <c r="E23" s="255"/>
+      <c r="F23" s="435"/>
+      <c r="G23" s="255"/>
+      <c r="H23" s="255"/>
     </row>
     <row r="24" spans="3:8">
-      <c r="C24" s="410" t="s">
+      <c r="C24" s="433" t="s">
         <v>216</v>
       </c>
-      <c r="D24" s="254"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="254"/>
-      <c r="G24" s="254"/>
-      <c r="H24" s="254"/>
+      <c r="D24" s="255"/>
+      <c r="E24" s="255"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="255"/>
+      <c r="H24" s="255"/>
     </row>
     <row r="25" spans="3:8">
-      <c r="C25" s="406" t="s">
+      <c r="C25" s="424" t="s">
         <v>217</v>
       </c>
-      <c r="D25" s="254"/>
-      <c r="E25" s="254"/>
-      <c r="F25" s="414">
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
+      <c r="F25" s="427">
         <v>2000000</v>
       </c>
-      <c r="G25" s="254"/>
-      <c r="H25" s="264"/>
+      <c r="G25" s="255"/>
+      <c r="H25" s="260"/>
     </row>
     <row r="26" spans="3:8">
-      <c r="C26" s="406" t="s">
+      <c r="C26" s="424" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="254"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="419">
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
+      <c r="F26" s="421">
         <v>0.8</v>
       </c>
-      <c r="G26" s="254"/>
-      <c r="H26" s="264"/>
+      <c r="G26" s="255"/>
+      <c r="H26" s="260"/>
     </row>
     <row r="27" spans="3:8">
-      <c r="C27" s="406" t="s">
+      <c r="C27" s="424" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="254"/>
-      <c r="E27" s="254"/>
-      <c r="F27" s="414">
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="427">
         <f>F25*F26</f>
         <v>1600000</v>
       </c>
-      <c r="G27" s="254"/>
-      <c r="H27" s="264"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="260"/>
     </row>
     <row r="28" spans="3:8" ht="15" customHeight="1">
-      <c r="C28" s="416" t="s">
+      <c r="C28" s="430" t="s">
         <v>215</v>
       </c>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
-      <c r="F28" s="420">
+      <c r="D28" s="257"/>
+      <c r="E28" s="257"/>
+      <c r="F28" s="425">
         <f>F27</f>
         <v>1600000</v>
       </c>
-      <c r="G28" s="249"/>
-      <c r="H28" s="250"/>
+      <c r="G28" s="257"/>
+      <c r="H28" s="258"/>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="417" t="s">
+      <c r="C31" s="418" t="s">
         <v>220</v>
       </c>
-      <c r="D31" s="254"/>
-      <c r="E31" s="254"/>
-      <c r="F31" s="254"/>
-      <c r="G31" s="254"/>
-      <c r="H31" s="254"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
+      <c r="F31" s="255"/>
+      <c r="G31" s="255"/>
+      <c r="H31" s="255"/>
     </row>
     <row r="32" spans="3:8">
-      <c r="C32" s="407" t="s">
+      <c r="C32" s="419" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="404">
+      <c r="D32" s="255"/>
+      <c r="E32" s="255"/>
+      <c r="F32" s="420">
         <f>F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G32" s="254"/>
-      <c r="H32" s="264"/>
+      <c r="G32" s="255"/>
+      <c r="H32" s="260"/>
     </row>
     <row r="33" spans="3:14">
-      <c r="C33" s="407" t="s">
+      <c r="C33" s="419" t="s">
         <v>222</v>
       </c>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
-      <c r="F33" s="404">
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="420">
         <f>F28</f>
         <v>1600000</v>
       </c>
-      <c r="G33" s="254"/>
-      <c r="H33" s="264"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="260"/>
     </row>
     <row r="34" spans="3:14" ht="15" customHeight="1" thickBot="1">
-      <c r="C34" s="415" t="s">
+      <c r="C34" s="429" t="s">
         <v>223</v>
       </c>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="411">
+      <c r="D34" s="257"/>
+      <c r="E34" s="257"/>
+      <c r="F34" s="428">
         <f>F32+F33</f>
         <v>2286322.530483</v>
       </c>
-      <c r="G34" s="249"/>
-      <c r="H34" s="250"/>
+      <c r="G34" s="257"/>
+      <c r="H34" s="258"/>
     </row>
     <row r="35" spans="3:14" ht="17.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="J35" s="486" t="s">
+      <c r="J35" s="413" t="s">
         <v>331</v>
       </c>
-      <c r="K35" s="487"/>
-      <c r="L35" s="487"/>
-      <c r="M35" s="487"/>
-      <c r="N35" s="488"/>
+      <c r="K35" s="414"/>
+      <c r="L35" s="414"/>
+      <c r="M35" s="414"/>
+      <c r="N35" s="415"/>
     </row>
     <row r="36" spans="3:14" ht="31.5" customHeight="1">
-      <c r="J36" s="489" t="s">
+      <c r="J36" s="416" t="s">
         <v>332</v>
       </c>
-      <c r="K36" s="480" t="s">
+      <c r="K36" s="248" t="s">
         <v>333</v>
       </c>
-      <c r="L36" s="489" t="s">
+      <c r="L36" s="416" t="s">
         <v>335</v>
       </c>
-      <c r="M36" s="480" t="s">
+      <c r="M36" s="248" t="s">
         <v>336</v>
       </c>
-      <c r="N36" s="489" t="s">
+      <c r="N36" s="416" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="37" spans="3:14" ht="16.5" thickBot="1">
-      <c r="J37" s="490"/>
-      <c r="K37" s="481" t="s">
+      <c r="J37" s="417"/>
+      <c r="K37" s="249" t="s">
         <v>334</v>
       </c>
-      <c r="L37" s="490"/>
-      <c r="M37" s="481" t="s">
+      <c r="L37" s="417"/>
+      <c r="M37" s="249" t="s">
         <v>337</v>
       </c>
-      <c r="N37" s="490"/>
+      <c r="N37" s="417"/>
     </row>
     <row r="38" spans="3:14" ht="16.5" thickBot="1">
-      <c r="J38" s="482" t="s">
+      <c r="J38" s="250" t="s">
         <v>339</v>
       </c>
-      <c r="K38" s="483">
+      <c r="K38" s="251">
         <f>AMOSTRAS!E6</f>
         <v>52.034300000000002</v>
       </c>
-      <c r="L38" s="484">
+      <c r="L38" s="252">
         <f>F34*0.8</f>
         <v>1829058.0243864001</v>
       </c>
-      <c r="M38" s="485">
+      <c r="M38" s="253">
         <f>F34</f>
         <v>2286322.530483</v>
       </c>
-      <c r="N38" s="484">
+      <c r="N38" s="252">
         <f>F34 + (F34*0.8)</f>
         <v>4115380.5548694003</v>
       </c>
     </row>
     <row r="39" spans="3:14" ht="36" customHeight="1" thickBot="1">
-      <c r="J39" s="491" t="s">
+      <c r="J39" s="408" t="s">
         <v>340</v>
       </c>
-      <c r="K39" s="492"/>
-      <c r="L39" s="493"/>
-      <c r="M39" s="494">
+      <c r="K39" s="409"/>
+      <c r="L39" s="410"/>
+      <c r="M39" s="411">
         <f>F34</f>
         <v>2286322.530483</v>
       </c>
-      <c r="N39" s="495"/>
+      <c r="N39" s="412"/>
     </row>
     <row r="40" spans="3:14" ht="36" customHeight="1" thickBot="1">
-      <c r="J40" s="491" t="s">
+      <c r="J40" s="408" t="s">
         <v>341</v>
       </c>
-      <c r="K40" s="492"/>
-      <c r="L40" s="493"/>
-      <c r="M40" s="494">
+      <c r="K40" s="409"/>
+      <c r="L40" s="410"/>
+      <c r="M40" s="411">
         <f>LIQUIDAÇÃO!F18</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="N40" s="495"/>
+      <c r="N40" s="412"/>
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="J35:N35"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="F10:H10"/>
@@ -11984,31 +11989,26 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="J35:N35"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="M39:N39"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12026,178 +12026,169 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11">
-      <c r="C5" s="402" t="str">
+      <c r="C5" s="434" t="str">
         <f>SANEAMENTO!C4</f>
         <v>MATRÍCULA 11.173</v>
       </c>
-      <c r="D5" s="254"/>
-      <c r="E5" s="254"/>
-      <c r="F5" s="254"/>
-      <c r="G5" s="254"/>
-      <c r="H5" s="254"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="255"/>
+      <c r="G5" s="255"/>
+      <c r="H5" s="255"/>
     </row>
     <row r="6" spans="3:11">
-      <c r="C6" s="402" t="s">
+      <c r="C6" s="434" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="254"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="254"/>
-      <c r="G6" s="254"/>
-      <c r="H6" s="254"/>
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="255"/>
+      <c r="G6" s="255"/>
+      <c r="H6" s="255"/>
     </row>
     <row r="7" spans="3:11">
-      <c r="C7" s="407" t="s">
+      <c r="C7" s="419" t="s">
         <v>225</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="422">
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="438">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G7" s="254"/>
-      <c r="H7" s="264"/>
+      <c r="G7" s="255"/>
+      <c r="H7" s="260"/>
     </row>
     <row r="8" spans="3:11">
-      <c r="C8" s="407" t="s">
+      <c r="C8" s="419" t="s">
         <v>226</v>
       </c>
-      <c r="D8" s="254"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="403">
+      <c r="D8" s="255"/>
+      <c r="E8" s="255"/>
+      <c r="F8" s="422">
         <v>36</v>
       </c>
-      <c r="G8" s="254"/>
-      <c r="H8" s="264"/>
+      <c r="G8" s="255"/>
+      <c r="H8" s="260"/>
     </row>
     <row r="9" spans="3:11">
-      <c r="C9" s="407" t="s">
+      <c r="C9" s="419" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="254"/>
-      <c r="E9" s="254"/>
-      <c r="F9" s="421">
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="437">
         <f>1/((1+F7)^(F8/12))</f>
         <v>0.68847055051621997</v>
       </c>
-      <c r="G9" s="254"/>
-      <c r="H9" s="264"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="260"/>
     </row>
     <row r="10" spans="3:11">
-      <c r="C10" s="407" t="s">
+      <c r="C10" s="419" t="s">
         <v>228</v>
       </c>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="404">
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="420">
         <f>SANEAMENTO!F20</f>
         <v>686322.53048299998</v>
       </c>
-      <c r="G10" s="254"/>
-      <c r="H10" s="264"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="260"/>
     </row>
     <row r="11" spans="3:11" ht="15" customHeight="1">
-      <c r="C11" s="415" t="s">
+      <c r="C11" s="429" t="s">
         <v>229</v>
       </c>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="411">
+      <c r="D11" s="257"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="428">
         <f>F10/((1+F7)^(F8/12))</f>
         <v>472512.85039331613</v>
       </c>
-      <c r="G11" s="249"/>
-      <c r="H11" s="250"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="258"/>
       <c r="K11" s="188"/>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1">
       <c r="K12" s="188"/>
     </row>
     <row r="13" spans="3:11">
-      <c r="C13" s="417" t="s">
+      <c r="C13" s="418" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="254"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="254"/>
-      <c r="G13" s="254"/>
-      <c r="H13" s="254"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="255"/>
+      <c r="G13" s="255"/>
+      <c r="H13" s="255"/>
       <c r="K13" s="187"/>
     </row>
     <row r="14" spans="3:11">
-      <c r="C14" s="407" t="s">
+      <c r="C14" s="419" t="s">
         <v>225</v>
       </c>
-      <c r="D14" s="254"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="422">
+      <c r="D14" s="255"/>
+      <c r="E14" s="255"/>
+      <c r="F14" s="438">
         <v>0.12767999999999999</v>
       </c>
-      <c r="G14" s="254"/>
-      <c r="H14" s="264"/>
+      <c r="G14" s="255"/>
+      <c r="H14" s="260"/>
     </row>
     <row r="15" spans="3:11">
-      <c r="C15" s="407" t="s">
+      <c r="C15" s="419" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="254"/>
-      <c r="E15" s="254"/>
-      <c r="F15" s="403">
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="422">
         <v>36</v>
       </c>
-      <c r="G15" s="254"/>
-      <c r="H15" s="264"/>
+      <c r="G15" s="255"/>
+      <c r="H15" s="260"/>
     </row>
     <row r="16" spans="3:11">
-      <c r="C16" s="407" t="s">
+      <c r="C16" s="419" t="s">
         <v>227</v>
       </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="421">
+      <c r="D16" s="255"/>
+      <c r="E16" s="255"/>
+      <c r="F16" s="437">
         <f>1/((1+F14)^(F15/12))</f>
         <v>0.69733644889224644</v>
       </c>
-      <c r="G16" s="254"/>
-      <c r="H16" s="264"/>
+      <c r="G16" s="255"/>
+      <c r="H16" s="260"/>
     </row>
     <row r="17" spans="3:8">
-      <c r="C17" s="407" t="s">
+      <c r="C17" s="419" t="s">
         <v>228</v>
       </c>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
-      <c r="F17" s="404">
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
+      <c r="F17" s="420">
         <f>SANEAMENTO!F28</f>
         <v>1600000</v>
       </c>
-      <c r="G17" s="254"/>
-      <c r="H17" s="264"/>
+      <c r="G17" s="255"/>
+      <c r="H17" s="260"/>
     </row>
     <row r="18" spans="3:8" ht="15" customHeight="1">
-      <c r="C18" s="415" t="s">
+      <c r="C18" s="429" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="411">
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="428">
         <f>F17/((1+F14)^(F15/12))</f>
         <v>1115738.3182275943</v>
       </c>
-      <c r="G18" s="249"/>
-      <c r="H18" s="250"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C17:E17"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="C14:E14"/>
@@ -12212,6 +12203,15 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
